--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09763F66-91EA-4026-A37C-71362B7CC5F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{383ED68F-7CF6-4E6D-893E-759242A30E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01BB175D-0DE1-4301-B8DE-5E90CDE07C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EE76D23-1D9A-46DD-98F9-14E7E343F367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="101">
   <si>
     <t>Sel</t>
   </si>
@@ -154,118 +154,175 @@
     <t>Nº Série</t>
   </si>
   <si>
+    <t>10014979</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>90201</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>UN</t>
+  </si>
+  <si>
+    <t>FORNO ELETRICO NARDELLI TOP 40 40L BLACK - NARDELLI TOP 40 - 220 V</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>FORNOS</t>
+  </si>
+  <si>
+    <t>1858600041542</t>
+  </si>
+  <si>
+    <t>10016351</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>FORNO ELETRICO NARDELLI EMBUTIR INOX 60 LITROS - NARDELLI EMBUTIR INOX 60 LITROS - 127 V</t>
+  </si>
+  <si>
+    <t>FORNOE</t>
+  </si>
+  <si>
+    <t>1858400003510</t>
+  </si>
+  <si>
+    <t>1858400003511</t>
+  </si>
+  <si>
+    <t>1858400003512</t>
+  </si>
+  <si>
+    <t>1858400003513</t>
+  </si>
+  <si>
+    <t>1858400003514</t>
+  </si>
+  <si>
+    <t>1858400003515</t>
+  </si>
+  <si>
+    <t>1858400003516</t>
+  </si>
+  <si>
     <t>10018965</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>500</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>90201</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>UN</t>
-  </si>
-  <si>
     <t>FORNO ELETRICO NARDELLI E50 BLACK 50L - NARDELLI E50 BLACK 50 L - 220 V</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>FORNOE</t>
-  </si>
-  <si>
-    <t>1879900000415</t>
-  </si>
-  <si>
-    <t>1879900000416</t>
-  </si>
-  <si>
-    <t>1879900000417</t>
-  </si>
-  <si>
-    <t>1879900000418</t>
-  </si>
-  <si>
-    <t>1879900000419</t>
-  </si>
-  <si>
-    <t>1879900000420</t>
-  </si>
-  <si>
-    <t>1879900000421</t>
-  </si>
-  <si>
-    <t>1879900000422</t>
-  </si>
-  <si>
-    <t>10098965</t>
-  </si>
-  <si>
-    <t>FORNO ELETRICO TERIM E50 BLACK 50L - TERIM E50 BLACK 50 L - 220 V</t>
-  </si>
-  <si>
-    <t>1033300000101</t>
-  </si>
-  <si>
-    <t>1033300000102</t>
-  </si>
-  <si>
-    <t>1033300000103</t>
-  </si>
-  <si>
-    <t>1033300000104</t>
-  </si>
-  <si>
-    <t>1033300000105</t>
-  </si>
-  <si>
-    <t>1033300000106</t>
-  </si>
-  <si>
-    <t>1033300000107</t>
-  </si>
-  <si>
-    <t>1033300000108</t>
-  </si>
-  <si>
-    <t>1033300000109</t>
-  </si>
-  <si>
-    <t>1033300000110</t>
-  </si>
-  <si>
-    <t>1033300000111</t>
-  </si>
-  <si>
-    <t>1033300000112</t>
-  </si>
-  <si>
-    <t>1033300000113</t>
-  </si>
-  <si>
-    <t>1033300000114</t>
-  </si>
-  <si>
-    <t>1033300000115</t>
-  </si>
-  <si>
-    <t>1033300000116</t>
-  </si>
-  <si>
-    <t>1033300000117</t>
+    <t>1879900000465</t>
+  </si>
+  <si>
+    <t>1879900000466</t>
+  </si>
+  <si>
+    <t>1879900000467</t>
+  </si>
+  <si>
+    <t>1879900000468</t>
+  </si>
+  <si>
+    <t>1879900000469</t>
+  </si>
+  <si>
+    <t>1879900000470</t>
+  </si>
+  <si>
+    <t>1879900000471</t>
+  </si>
+  <si>
+    <t>1879900000472</t>
+  </si>
+  <si>
+    <t>1879900000473</t>
+  </si>
+  <si>
+    <t>1879900000474</t>
+  </si>
+  <si>
+    <t>10056354</t>
+  </si>
+  <si>
+    <t>FORNO ELETRICO FOGATTI EMBUTIR 60L BLACK - 127 V</t>
+  </si>
+  <si>
+    <t>1030900000070</t>
+  </si>
+  <si>
+    <t>1030900000071</t>
+  </si>
+  <si>
+    <t>1030900000072</t>
+  </si>
+  <si>
+    <t>1030900000073</t>
+  </si>
+  <si>
+    <t>1030900000074</t>
+  </si>
+  <si>
+    <t>1030900000075</t>
+  </si>
+  <si>
+    <t>1030900000076</t>
+  </si>
+  <si>
+    <t>1030900000077</t>
+  </si>
+  <si>
+    <t>1030900000078</t>
+  </si>
+  <si>
+    <t>1030900000079</t>
+  </si>
+  <si>
+    <t>1030900000080</t>
+  </si>
+  <si>
+    <t>1030900000081</t>
+  </si>
+  <si>
+    <t>1030900000082</t>
+  </si>
+  <si>
+    <t>1030900000083</t>
+  </si>
+  <si>
+    <t>1030900000084</t>
+  </si>
+  <si>
+    <t>1030900000085</t>
+  </si>
+  <si>
+    <t>1030900000086</t>
+  </si>
+  <si>
+    <t>1030900000087</t>
+  </si>
+  <si>
+    <t>1030900000088</t>
+  </si>
+  <si>
+    <t>1030900000089</t>
   </si>
 </sst>
 </file>
@@ -841,7 +898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR26"/>
+  <dimension ref="A1:AR39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -995,10 +1052,10 @@
         <v>46</v>
       </c>
       <c r="F2" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G2" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>47</v>
@@ -1013,10 +1070,10 @@
         <v>50</v>
       </c>
       <c r="L2" s="6">
-        <v>77</v>
+        <v>915</v>
       </c>
       <c r="M2" s="7">
-        <v>26766.79</v>
+        <v>171252.21</v>
       </c>
       <c r="N2" s="6">
         <v>1</v>
@@ -1025,7 +1082,7 @@
         <v>51</v>
       </c>
       <c r="P2" s="8">
-        <v>347.62</v>
+        <v>187.16</v>
       </c>
       <c r="Q2" s="6">
         <v>0</v>
@@ -1040,16 +1097,16 @@
         <v>52</v>
       </c>
       <c r="U2" s="10">
-        <v>67347</v>
+        <v>67407</v>
       </c>
       <c r="V2" s="11">
         <v>11</v>
       </c>
       <c r="W2" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X2" s="12">
-        <v>0.43055559999999998</v>
+        <v>0.39027780000000001</v>
       </c>
       <c r="Y2" s="10">
         <v>0</v>
@@ -1120,19 +1177,19 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>47</v>
@@ -1147,19 +1204,19 @@
         <v>50</v>
       </c>
       <c r="L3" s="6">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M3" s="7">
-        <v>27114.41</v>
+        <v>27544.42</v>
       </c>
       <c r="N3" s="6">
         <v>1</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="P3" s="8">
-        <v>347.62</v>
+        <v>377.32</v>
       </c>
       <c r="Q3" s="6">
         <v>0</v>
@@ -1174,16 +1231,16 @@
         <v>52</v>
       </c>
       <c r="U3" s="10">
-        <v>67347</v>
+        <v>66798</v>
       </c>
       <c r="V3" s="11">
         <v>11</v>
       </c>
       <c r="W3" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X3" s="12">
-        <v>0.43055559999999998</v>
+        <v>0.4583333</v>
       </c>
       <c r="Y3" s="10">
         <v>0</v>
@@ -1216,7 +1273,7 @@
         <v>53</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ3" s="3" t="s">
         <v>52</v>
@@ -1243,7 +1300,7 @@
         <v>53</v>
       </c>
       <c r="AR3" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.3">
@@ -1254,19 +1311,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F4" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G4" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>47</v>
@@ -1281,19 +1338,19 @@
         <v>50</v>
       </c>
       <c r="L4" s="6">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="M4" s="7">
-        <v>27462.03</v>
+        <v>27921.74</v>
       </c>
       <c r="N4" s="6">
         <v>1</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="P4" s="8">
-        <v>347.62</v>
+        <v>377.32</v>
       </c>
       <c r="Q4" s="6">
         <v>0</v>
@@ -1308,16 +1365,16 @@
         <v>52</v>
       </c>
       <c r="U4" s="10">
-        <v>67347</v>
+        <v>66798</v>
       </c>
       <c r="V4" s="11">
         <v>11</v>
       </c>
       <c r="W4" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X4" s="12">
-        <v>0.43055559999999998</v>
+        <v>0.4583333</v>
       </c>
       <c r="Y4" s="10">
         <v>0</v>
@@ -1350,7 +1407,7 @@
         <v>53</v>
       </c>
       <c r="AI4" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ4" s="3" t="s">
         <v>52</v>
@@ -1377,7 +1434,7 @@
         <v>53</v>
       </c>
       <c r="AR4" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
@@ -1388,19 +1445,19 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F5" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G5" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>47</v>
@@ -1415,19 +1472,19 @@
         <v>50</v>
       </c>
       <c r="L5" s="6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="M5" s="7">
-        <v>27809.65</v>
+        <v>28299.06</v>
       </c>
       <c r="N5" s="6">
         <v>1</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="P5" s="8">
-        <v>347.62</v>
+        <v>377.32</v>
       </c>
       <c r="Q5" s="6">
         <v>0</v>
@@ -1442,16 +1499,16 @@
         <v>52</v>
       </c>
       <c r="U5" s="10">
-        <v>67347</v>
+        <v>66798</v>
       </c>
       <c r="V5" s="11">
         <v>11</v>
       </c>
       <c r="W5" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X5" s="12">
-        <v>0.43055559999999998</v>
+        <v>0.4583333</v>
       </c>
       <c r="Y5" s="10">
         <v>0</v>
@@ -1484,7 +1541,7 @@
         <v>53</v>
       </c>
       <c r="AI5" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ5" s="3" t="s">
         <v>52</v>
@@ -1511,7 +1568,7 @@
         <v>53</v>
       </c>
       <c r="AR5" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
@@ -1522,19 +1579,19 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F6" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G6" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>47</v>
@@ -1549,19 +1606,19 @@
         <v>50</v>
       </c>
       <c r="L6" s="6">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="M6" s="7">
-        <v>28157.27</v>
+        <v>28676.39</v>
       </c>
       <c r="N6" s="6">
         <v>1</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="P6" s="8">
-        <v>347.62</v>
+        <v>377.32</v>
       </c>
       <c r="Q6" s="6">
         <v>0</v>
@@ -1576,16 +1633,16 @@
         <v>52</v>
       </c>
       <c r="U6" s="10">
-        <v>67347</v>
+        <v>66798</v>
       </c>
       <c r="V6" s="11">
         <v>11</v>
       </c>
       <c r="W6" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X6" s="12">
-        <v>0.43055559999999998</v>
+        <v>0.4583333</v>
       </c>
       <c r="Y6" s="10">
         <v>0</v>
@@ -1618,7 +1675,7 @@
         <v>53</v>
       </c>
       <c r="AI6" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ6" s="3" t="s">
         <v>52</v>
@@ -1645,7 +1702,7 @@
         <v>53</v>
       </c>
       <c r="AR6" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
@@ -1656,19 +1713,19 @@
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F7" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G7" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>47</v>
@@ -1683,19 +1740,19 @@
         <v>50</v>
       </c>
       <c r="L7" s="6">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="M7" s="7">
-        <v>28504.89</v>
+        <v>29053.71</v>
       </c>
       <c r="N7" s="6">
         <v>1</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="P7" s="8">
-        <v>347.62</v>
+        <v>377.32</v>
       </c>
       <c r="Q7" s="6">
         <v>0</v>
@@ -1710,16 +1767,16 @@
         <v>52</v>
       </c>
       <c r="U7" s="10">
-        <v>67347</v>
+        <v>66798</v>
       </c>
       <c r="V7" s="11">
         <v>11</v>
       </c>
       <c r="W7" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X7" s="12">
-        <v>0.43055559999999998</v>
+        <v>0.4583333</v>
       </c>
       <c r="Y7" s="10">
         <v>0</v>
@@ -1752,7 +1809,7 @@
         <v>53</v>
       </c>
       <c r="AI7" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ7" s="3" t="s">
         <v>52</v>
@@ -1779,7 +1836,7 @@
         <v>53</v>
       </c>
       <c r="AR7" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
@@ -1790,19 +1847,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F8" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G8" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>47</v>
@@ -1817,19 +1874,19 @@
         <v>50</v>
       </c>
       <c r="L8" s="6">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="M8" s="7">
-        <v>28852.51</v>
+        <v>29431.03</v>
       </c>
       <c r="N8" s="6">
         <v>1</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="P8" s="8">
-        <v>347.62</v>
+        <v>377.32</v>
       </c>
       <c r="Q8" s="6">
         <v>0</v>
@@ -1844,16 +1901,16 @@
         <v>52</v>
       </c>
       <c r="U8" s="10">
-        <v>67347</v>
+        <v>66798</v>
       </c>
       <c r="V8" s="11">
         <v>11</v>
       </c>
       <c r="W8" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X8" s="12">
-        <v>0.43055559999999998</v>
+        <v>0.4583333</v>
       </c>
       <c r="Y8" s="10">
         <v>0</v>
@@ -1886,7 +1943,7 @@
         <v>53</v>
       </c>
       <c r="AI8" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ8" s="3" t="s">
         <v>52</v>
@@ -1913,7 +1970,7 @@
         <v>53</v>
       </c>
       <c r="AR8" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
@@ -1924,19 +1981,19 @@
         <v>2</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F9" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G9" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>47</v>
@@ -1951,19 +2008,19 @@
         <v>50</v>
       </c>
       <c r="L9" s="6">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M9" s="7">
-        <v>29200.13</v>
+        <v>29808.35</v>
       </c>
       <c r="N9" s="6">
         <v>1</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="P9" s="8">
-        <v>347.62</v>
+        <v>377.32</v>
       </c>
       <c r="Q9" s="6">
         <v>0</v>
@@ -1978,16 +2035,16 @@
         <v>52</v>
       </c>
       <c r="U9" s="10">
-        <v>67347</v>
+        <v>66798</v>
       </c>
       <c r="V9" s="11">
         <v>11</v>
       </c>
       <c r="W9" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X9" s="12">
-        <v>0.43055559999999998</v>
+        <v>0.4583333</v>
       </c>
       <c r="Y9" s="10">
         <v>0</v>
@@ -2020,7 +2077,7 @@
         <v>53</v>
       </c>
       <c r="AI9" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ9" s="3" t="s">
         <v>52</v>
@@ -2047,7 +2104,7 @@
         <v>53</v>
       </c>
       <c r="AR9" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
@@ -2058,7 +2115,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>45</v>
@@ -2067,10 +2124,10 @@
         <v>46</v>
       </c>
       <c r="F10" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G10" s="5">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>47</v>
@@ -2085,19 +2142,19 @@
         <v>50</v>
       </c>
       <c r="L10" s="6">
-        <v>3</v>
+        <v>127</v>
       </c>
       <c r="M10" s="7">
-        <v>1158.57</v>
+        <v>44105.13</v>
       </c>
       <c r="N10" s="6">
         <v>1</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P10" s="8">
-        <v>386.19</v>
+        <v>347.28</v>
       </c>
       <c r="Q10" s="6">
         <v>0</v>
@@ -2112,16 +2169,16 @@
         <v>52</v>
       </c>
       <c r="U10" s="10">
-        <v>67357</v>
+        <v>67347</v>
       </c>
       <c r="V10" s="11">
         <v>11</v>
       </c>
       <c r="W10" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X10" s="12">
-        <v>0.30555559999999998</v>
+        <v>0.38958330000000002</v>
       </c>
       <c r="Y10" s="10">
         <v>0</v>
@@ -2154,7 +2211,7 @@
         <v>53</v>
       </c>
       <c r="AI10" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ10" s="3" t="s">
         <v>52</v>
@@ -2181,7 +2238,7 @@
         <v>53</v>
       </c>
       <c r="AR10" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
@@ -2192,7 +2249,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>45</v>
@@ -2201,10 +2258,10 @@
         <v>46</v>
       </c>
       <c r="F11" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G11" s="5">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>47</v>
@@ -2219,19 +2276,19 @@
         <v>50</v>
       </c>
       <c r="L11" s="6">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="M11" s="7">
-        <v>1544.76</v>
+        <v>44452.41</v>
       </c>
       <c r="N11" s="6">
         <v>1</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P11" s="8">
-        <v>386.19</v>
+        <v>347.28</v>
       </c>
       <c r="Q11" s="6">
         <v>0</v>
@@ -2246,16 +2303,16 @@
         <v>52</v>
       </c>
       <c r="U11" s="10">
-        <v>67357</v>
+        <v>67347</v>
       </c>
       <c r="V11" s="11">
         <v>11</v>
       </c>
       <c r="W11" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X11" s="12">
-        <v>0.30555559999999998</v>
+        <v>0.38958330000000002</v>
       </c>
       <c r="Y11" s="10">
         <v>0</v>
@@ -2288,7 +2345,7 @@
         <v>53</v>
       </c>
       <c r="AI11" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ11" s="3" t="s">
         <v>52</v>
@@ -2315,7 +2372,7 @@
         <v>53</v>
       </c>
       <c r="AR11" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
@@ -2326,7 +2383,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>45</v>
@@ -2335,10 +2392,10 @@
         <v>46</v>
       </c>
       <c r="F12" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G12" s="5">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>47</v>
@@ -2353,19 +2410,19 @@
         <v>50</v>
       </c>
       <c r="L12" s="6">
-        <v>5</v>
+        <v>129</v>
       </c>
       <c r="M12" s="7">
-        <v>1930.95</v>
+        <v>44799.7</v>
       </c>
       <c r="N12" s="6">
         <v>1</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P12" s="8">
-        <v>386.19</v>
+        <v>347.28</v>
       </c>
       <c r="Q12" s="6">
         <v>0</v>
@@ -2380,16 +2437,16 @@
         <v>52</v>
       </c>
       <c r="U12" s="10">
-        <v>67357</v>
+        <v>67347</v>
       </c>
       <c r="V12" s="11">
         <v>11</v>
       </c>
       <c r="W12" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X12" s="12">
-        <v>0.30555559999999998</v>
+        <v>0.38958330000000002</v>
       </c>
       <c r="Y12" s="10">
         <v>0</v>
@@ -2422,7 +2479,7 @@
         <v>53</v>
       </c>
       <c r="AI12" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ12" s="3" t="s">
         <v>52</v>
@@ -2449,7 +2506,7 @@
         <v>53</v>
       </c>
       <c r="AR12" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.3">
@@ -2460,7 +2517,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>45</v>
@@ -2469,10 +2526,10 @@
         <v>46</v>
       </c>
       <c r="F13" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G13" s="5">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>47</v>
@@ -2487,19 +2544,19 @@
         <v>50</v>
       </c>
       <c r="L13" s="6">
-        <v>6</v>
+        <v>130</v>
       </c>
       <c r="M13" s="7">
-        <v>2317.14</v>
+        <v>45146.98</v>
       </c>
       <c r="N13" s="6">
         <v>1</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P13" s="8">
-        <v>386.19</v>
+        <v>347.28</v>
       </c>
       <c r="Q13" s="6">
         <v>0</v>
@@ -2514,16 +2571,16 @@
         <v>52</v>
       </c>
       <c r="U13" s="10">
-        <v>67357</v>
+        <v>67347</v>
       </c>
       <c r="V13" s="11">
         <v>11</v>
       </c>
       <c r="W13" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X13" s="12">
-        <v>0.36111110000000002</v>
+        <v>0.38958330000000002</v>
       </c>
       <c r="Y13" s="10">
         <v>0</v>
@@ -2556,7 +2613,7 @@
         <v>53</v>
       </c>
       <c r="AI13" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ13" s="3" t="s">
         <v>52</v>
@@ -2583,7 +2640,7 @@
         <v>53</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
@@ -2594,7 +2651,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>45</v>
@@ -2603,10 +2660,10 @@
         <v>46</v>
       </c>
       <c r="F14" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G14" s="5">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>47</v>
@@ -2621,19 +2678,19 @@
         <v>50</v>
       </c>
       <c r="L14" s="6">
-        <v>7</v>
+        <v>131</v>
       </c>
       <c r="M14" s="7">
-        <v>2703.33</v>
+        <v>45494.27</v>
       </c>
       <c r="N14" s="6">
         <v>1</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P14" s="8">
-        <v>386.19</v>
+        <v>347.28</v>
       </c>
       <c r="Q14" s="6">
         <v>0</v>
@@ -2648,16 +2705,16 @@
         <v>52</v>
       </c>
       <c r="U14" s="10">
-        <v>67357</v>
+        <v>67347</v>
       </c>
       <c r="V14" s="11">
         <v>11</v>
       </c>
       <c r="W14" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X14" s="12">
-        <v>0.36111110000000002</v>
+        <v>0.38958330000000002</v>
       </c>
       <c r="Y14" s="10">
         <v>0</v>
@@ -2690,7 +2747,7 @@
         <v>53</v>
       </c>
       <c r="AI14" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>52</v>
@@ -2717,7 +2774,7 @@
         <v>53</v>
       </c>
       <c r="AR14" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
@@ -2728,7 +2785,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>45</v>
@@ -2737,10 +2794,10 @@
         <v>46</v>
       </c>
       <c r="F15" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G15" s="5">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>47</v>
@@ -2755,19 +2812,19 @@
         <v>50</v>
       </c>
       <c r="L15" s="6">
-        <v>8</v>
+        <v>132</v>
       </c>
       <c r="M15" s="7">
-        <v>3089.52</v>
+        <v>45841.55</v>
       </c>
       <c r="N15" s="6">
         <v>1</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P15" s="8">
-        <v>386.19</v>
+        <v>347.28</v>
       </c>
       <c r="Q15" s="6">
         <v>0</v>
@@ -2782,16 +2839,16 @@
         <v>52</v>
       </c>
       <c r="U15" s="10">
-        <v>67357</v>
+        <v>67347</v>
       </c>
       <c r="V15" s="11">
         <v>11</v>
       </c>
       <c r="W15" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X15" s="12">
-        <v>0.36111110000000002</v>
+        <v>0.38958330000000002</v>
       </c>
       <c r="Y15" s="10">
         <v>0</v>
@@ -2824,7 +2881,7 @@
         <v>53</v>
       </c>
       <c r="AI15" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ15" s="3" t="s">
         <v>52</v>
@@ -2851,7 +2908,7 @@
         <v>53</v>
       </c>
       <c r="AR15" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.3">
@@ -2862,7 +2919,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>45</v>
@@ -2871,10 +2928,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G16" s="5">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>47</v>
@@ -2889,19 +2946,19 @@
         <v>50</v>
       </c>
       <c r="L16" s="6">
-        <v>9</v>
+        <v>133</v>
       </c>
       <c r="M16" s="7">
-        <v>3475.71</v>
+        <v>46188.83</v>
       </c>
       <c r="N16" s="6">
         <v>1</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P16" s="8">
-        <v>386.19</v>
+        <v>347.28</v>
       </c>
       <c r="Q16" s="6">
         <v>0</v>
@@ -2916,16 +2973,16 @@
         <v>52</v>
       </c>
       <c r="U16" s="10">
-        <v>67357</v>
+        <v>67347</v>
       </c>
       <c r="V16" s="11">
         <v>11</v>
       </c>
       <c r="W16" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X16" s="12">
-        <v>0.36111110000000002</v>
+        <v>0.38958330000000002</v>
       </c>
       <c r="Y16" s="10">
         <v>0</v>
@@ -2958,7 +3015,7 @@
         <v>53</v>
       </c>
       <c r="AI16" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ16" s="3" t="s">
         <v>52</v>
@@ -2985,7 +3042,7 @@
         <v>53</v>
       </c>
       <c r="AR16" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.3">
@@ -2996,7 +3053,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>45</v>
@@ -3005,10 +3062,10 @@
         <v>46</v>
       </c>
       <c r="F17" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G17" s="5">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>47</v>
@@ -3023,19 +3080,19 @@
         <v>50</v>
       </c>
       <c r="L17" s="6">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="M17" s="7">
-        <v>3861.9</v>
+        <v>46536.12</v>
       </c>
       <c r="N17" s="6">
         <v>1</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P17" s="8">
-        <v>386.19</v>
+        <v>347.28</v>
       </c>
       <c r="Q17" s="6">
         <v>0</v>
@@ -3050,16 +3107,16 @@
         <v>52</v>
       </c>
       <c r="U17" s="10">
-        <v>67357</v>
+        <v>67347</v>
       </c>
       <c r="V17" s="11">
         <v>11</v>
       </c>
       <c r="W17" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X17" s="12">
-        <v>0.36111110000000002</v>
+        <v>0.38958330000000002</v>
       </c>
       <c r="Y17" s="10">
         <v>0</v>
@@ -3092,7 +3149,7 @@
         <v>53</v>
       </c>
       <c r="AI17" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ17" s="3" t="s">
         <v>52</v>
@@ -3119,7 +3176,7 @@
         <v>53</v>
       </c>
       <c r="AR17" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:44" x14ac:dyDescent="0.3">
@@ -3130,7 +3187,7 @@
         <v>2</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>45</v>
@@ -3139,10 +3196,10 @@
         <v>46</v>
       </c>
       <c r="F18" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G18" s="5">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>47</v>
@@ -3157,19 +3214,19 @@
         <v>50</v>
       </c>
       <c r="L18" s="6">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="M18" s="7">
-        <v>4248.09</v>
+        <v>46883.4</v>
       </c>
       <c r="N18" s="6">
         <v>1</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P18" s="8">
-        <v>386.19</v>
+        <v>347.28</v>
       </c>
       <c r="Q18" s="6">
         <v>0</v>
@@ -3184,16 +3241,16 @@
         <v>52</v>
       </c>
       <c r="U18" s="10">
-        <v>67357</v>
+        <v>67347</v>
       </c>
       <c r="V18" s="11">
         <v>11</v>
       </c>
       <c r="W18" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X18" s="12">
-        <v>0.36111110000000002</v>
+        <v>0.38958330000000002</v>
       </c>
       <c r="Y18" s="10">
         <v>0</v>
@@ -3226,7 +3283,7 @@
         <v>53</v>
       </c>
       <c r="AI18" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ18" s="3" t="s">
         <v>52</v>
@@ -3253,7 +3310,7 @@
         <v>53</v>
       </c>
       <c r="AR18" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.3">
@@ -3264,7 +3321,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>45</v>
@@ -3273,10 +3330,10 @@
         <v>46</v>
       </c>
       <c r="F19" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G19" s="5">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>47</v>
@@ -3291,19 +3348,19 @@
         <v>50</v>
       </c>
       <c r="L19" s="6">
-        <v>12</v>
+        <v>136</v>
       </c>
       <c r="M19" s="7">
-        <v>4634.28</v>
+        <v>47230.69</v>
       </c>
       <c r="N19" s="6">
         <v>1</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P19" s="8">
-        <v>386.19</v>
+        <v>347.28</v>
       </c>
       <c r="Q19" s="6">
         <v>0</v>
@@ -3318,16 +3375,16 @@
         <v>52</v>
       </c>
       <c r="U19" s="10">
-        <v>67357</v>
+        <v>67347</v>
       </c>
       <c r="V19" s="11">
         <v>11</v>
       </c>
       <c r="W19" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X19" s="12">
-        <v>0.40277780000000002</v>
+        <v>0.38958330000000002</v>
       </c>
       <c r="Y19" s="10">
         <v>0</v>
@@ -3360,7 +3417,7 @@
         <v>53</v>
       </c>
       <c r="AI19" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ19" s="3" t="s">
         <v>52</v>
@@ -3387,7 +3444,7 @@
         <v>53</v>
       </c>
       <c r="AR19" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.3">
@@ -3398,19 +3455,19 @@
         <v>2</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F20" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G20" s="5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>47</v>
@@ -3425,19 +3482,19 @@
         <v>50</v>
       </c>
       <c r="L20" s="6">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M20" s="7">
-        <v>5020.47</v>
+        <v>650.74</v>
       </c>
       <c r="N20" s="6">
         <v>1</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="P20" s="8">
-        <v>386.19</v>
+        <v>325.37</v>
       </c>
       <c r="Q20" s="6">
         <v>0</v>
@@ -3452,16 +3509,16 @@
         <v>52</v>
       </c>
       <c r="U20" s="10">
-        <v>67357</v>
+        <v>67488</v>
       </c>
       <c r="V20" s="11">
         <v>11</v>
       </c>
       <c r="W20" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X20" s="12">
-        <v>0.40277780000000002</v>
+        <v>0.41041670000000002</v>
       </c>
       <c r="Y20" s="10">
         <v>0</v>
@@ -3494,7 +3551,7 @@
         <v>53</v>
       </c>
       <c r="AI20" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ20" s="3" t="s">
         <v>52</v>
@@ -3521,7 +3578,7 @@
         <v>53</v>
       </c>
       <c r="AR20" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:44" x14ac:dyDescent="0.3">
@@ -3532,19 +3589,19 @@
         <v>2</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F21" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G21" s="5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>47</v>
@@ -3559,19 +3616,19 @@
         <v>50</v>
       </c>
       <c r="L21" s="6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="M21" s="7">
-        <v>5406.66</v>
+        <v>976.11</v>
       </c>
       <c r="N21" s="6">
         <v>1</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="P21" s="8">
-        <v>386.19</v>
+        <v>325.37</v>
       </c>
       <c r="Q21" s="6">
         <v>0</v>
@@ -3586,16 +3643,16 @@
         <v>52</v>
       </c>
       <c r="U21" s="10">
-        <v>67357</v>
+        <v>67488</v>
       </c>
       <c r="V21" s="11">
         <v>11</v>
       </c>
       <c r="W21" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X21" s="12">
-        <v>0.4034722</v>
+        <v>0.41041670000000002</v>
       </c>
       <c r="Y21" s="10">
         <v>0</v>
@@ -3628,7 +3685,7 @@
         <v>53</v>
       </c>
       <c r="AI21" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ21" s="3" t="s">
         <v>52</v>
@@ -3655,7 +3712,7 @@
         <v>53</v>
       </c>
       <c r="AR21" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:44" x14ac:dyDescent="0.3">
@@ -3666,19 +3723,19 @@
         <v>2</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F22" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G22" s="5">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>47</v>
@@ -3693,19 +3750,19 @@
         <v>50</v>
       </c>
       <c r="L22" s="6">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M22" s="7">
-        <v>5792.85</v>
+        <v>1301.48</v>
       </c>
       <c r="N22" s="6">
         <v>1</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="P22" s="8">
-        <v>386.19</v>
+        <v>325.37</v>
       </c>
       <c r="Q22" s="6">
         <v>0</v>
@@ -3720,16 +3777,16 @@
         <v>52</v>
       </c>
       <c r="U22" s="10">
-        <v>67357</v>
+        <v>67488</v>
       </c>
       <c r="V22" s="11">
         <v>11</v>
       </c>
       <c r="W22" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X22" s="12">
-        <v>0.4034722</v>
+        <v>0.41041670000000002</v>
       </c>
       <c r="Y22" s="10">
         <v>0</v>
@@ -3762,7 +3819,7 @@
         <v>53</v>
       </c>
       <c r="AI22" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ22" s="3" t="s">
         <v>52</v>
@@ -3789,7 +3846,7 @@
         <v>53</v>
       </c>
       <c r="AR22" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:44" x14ac:dyDescent="0.3">
@@ -3800,19 +3857,19 @@
         <v>2</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F23" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G23" s="5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>47</v>
@@ -3827,19 +3884,19 @@
         <v>50</v>
       </c>
       <c r="L23" s="6">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="M23" s="7">
-        <v>6179.04</v>
+        <v>1626.85</v>
       </c>
       <c r="N23" s="6">
         <v>1</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="P23" s="8">
-        <v>386.19</v>
+        <v>325.37</v>
       </c>
       <c r="Q23" s="6">
         <v>0</v>
@@ -3854,16 +3911,16 @@
         <v>52</v>
       </c>
       <c r="U23" s="10">
-        <v>67357</v>
+        <v>67488</v>
       </c>
       <c r="V23" s="11">
         <v>11</v>
       </c>
       <c r="W23" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X23" s="12">
-        <v>0.4034722</v>
+        <v>0.41041670000000002</v>
       </c>
       <c r="Y23" s="10">
         <v>0</v>
@@ -3896,7 +3953,7 @@
         <v>53</v>
       </c>
       <c r="AI23" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ23" s="3" t="s">
         <v>52</v>
@@ -3923,7 +3980,7 @@
         <v>53</v>
       </c>
       <c r="AR23" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.3">
@@ -3934,19 +3991,19 @@
         <v>2</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F24" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G24" s="5">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>47</v>
@@ -3961,19 +4018,19 @@
         <v>50</v>
       </c>
       <c r="L24" s="6">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="M24" s="7">
-        <v>6565.23</v>
+        <v>1952.22</v>
       </c>
       <c r="N24" s="6">
         <v>1</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="P24" s="8">
-        <v>386.19</v>
+        <v>325.37</v>
       </c>
       <c r="Q24" s="6">
         <v>0</v>
@@ -3988,16 +4045,16 @@
         <v>52</v>
       </c>
       <c r="U24" s="10">
-        <v>67357</v>
+        <v>67488</v>
       </c>
       <c r="V24" s="11">
         <v>11</v>
       </c>
       <c r="W24" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X24" s="12">
-        <v>0.4034722</v>
+        <v>0.41041670000000002</v>
       </c>
       <c r="Y24" s="10">
         <v>0</v>
@@ -4030,7 +4087,7 @@
         <v>53</v>
       </c>
       <c r="AI24" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ24" s="3" t="s">
         <v>52</v>
@@ -4057,7 +4114,7 @@
         <v>53</v>
       </c>
       <c r="AR24" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:44" x14ac:dyDescent="0.3">
@@ -4068,19 +4125,19 @@
         <v>2</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F25" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G25" s="5">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>47</v>
@@ -4095,19 +4152,19 @@
         <v>50</v>
       </c>
       <c r="L25" s="6">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="M25" s="7">
-        <v>6951.42</v>
+        <v>2277.59</v>
       </c>
       <c r="N25" s="6">
         <v>1</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="P25" s="8">
-        <v>386.19</v>
+        <v>325.37</v>
       </c>
       <c r="Q25" s="6">
         <v>0</v>
@@ -4122,16 +4179,16 @@
         <v>52</v>
       </c>
       <c r="U25" s="10">
-        <v>67357</v>
+        <v>67488</v>
       </c>
       <c r="V25" s="11">
         <v>11</v>
       </c>
       <c r="W25" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X25" s="12">
-        <v>0.4034722</v>
+        <v>0.41041670000000002</v>
       </c>
       <c r="Y25" s="10">
         <v>0</v>
@@ -4164,7 +4221,7 @@
         <v>53</v>
       </c>
       <c r="AI25" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ25" s="3" t="s">
         <v>52</v>
@@ -4191,7 +4248,7 @@
         <v>53</v>
       </c>
       <c r="AR25" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:44" x14ac:dyDescent="0.3">
@@ -4202,19 +4259,19 @@
         <v>2</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F26" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G26" s="5">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>47</v>
@@ -4229,19 +4286,19 @@
         <v>50</v>
       </c>
       <c r="L26" s="6">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="M26" s="7">
-        <v>7337.61</v>
+        <v>2602.96</v>
       </c>
       <c r="N26" s="6">
         <v>1</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="P26" s="8">
-        <v>386.19</v>
+        <v>325.37</v>
       </c>
       <c r="Q26" s="6">
         <v>0</v>
@@ -4256,16 +4313,16 @@
         <v>52</v>
       </c>
       <c r="U26" s="10">
-        <v>67357</v>
+        <v>67488</v>
       </c>
       <c r="V26" s="11">
         <v>11</v>
       </c>
       <c r="W26" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="X26" s="12">
-        <v>0.4034722</v>
+        <v>0.44583329999999999</v>
       </c>
       <c r="Y26" s="10">
         <v>0</v>
@@ -4298,7 +4355,7 @@
         <v>53</v>
       </c>
       <c r="AI26" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AJ26" s="3" t="s">
         <v>52</v>
@@ -4325,7 +4382,1749 @@
         <v>53</v>
       </c>
       <c r="AR26" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>1</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="4">
+        <v>46281</v>
+      </c>
+      <c r="G27" s="5">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L27" s="6">
+        <v>9</v>
+      </c>
+      <c r="M27" s="7">
+        <v>2928.33</v>
+      </c>
+      <c r="N27" s="6">
+        <v>1</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P27" s="8">
+        <v>325.37</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>0</v>
+      </c>
+      <c r="R27" s="7">
+        <v>0</v>
+      </c>
+      <c r="S27" s="9">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U27" s="10">
+        <v>67488</v>
+      </c>
+      <c r="V27" s="11">
+        <v>11</v>
+      </c>
+      <c r="W27" s="4">
+        <v>46281</v>
+      </c>
+      <c r="X27" s="12">
+        <v>0.44583329999999999</v>
+      </c>
+      <c r="Y27" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG27" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ27" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK27" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR27" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>1</v>
+      </c>
+      <c r="B28" s="2">
+        <v>2</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F28" s="4">
+        <v>46281</v>
+      </c>
+      <c r="G28" s="5">
+        <v>9</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L28" s="6">
+        <v>10</v>
+      </c>
+      <c r="M28" s="7">
+        <v>3253.7</v>
+      </c>
+      <c r="N28" s="6">
+        <v>1</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P28" s="8">
+        <v>325.37</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>0</v>
+      </c>
+      <c r="R28" s="7">
+        <v>0</v>
+      </c>
+      <c r="S28" s="9">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U28" s="10">
+        <v>67488</v>
+      </c>
+      <c r="V28" s="11">
+        <v>11</v>
+      </c>
+      <c r="W28" s="4">
+        <v>46281</v>
+      </c>
+      <c r="X28" s="12">
+        <v>0.44583329999999999</v>
+      </c>
+      <c r="Y28" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG28" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK28" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR28" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>1</v>
+      </c>
+      <c r="B29" s="2">
+        <v>2</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" s="4">
+        <v>46281</v>
+      </c>
+      <c r="G29" s="5">
+        <v>10</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L29" s="6">
+        <v>11</v>
+      </c>
+      <c r="M29" s="7">
+        <v>3579.07</v>
+      </c>
+      <c r="N29" s="6">
+        <v>1</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P29" s="8">
+        <v>325.37</v>
+      </c>
+      <c r="Q29" s="6">
+        <v>0</v>
+      </c>
+      <c r="R29" s="7">
+        <v>0</v>
+      </c>
+      <c r="S29" s="9">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U29" s="10">
+        <v>67488</v>
+      </c>
+      <c r="V29" s="11">
+        <v>11</v>
+      </c>
+      <c r="W29" s="4">
+        <v>46281</v>
+      </c>
+      <c r="X29" s="12">
+        <v>0.44583329999999999</v>
+      </c>
+      <c r="Y29" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG29" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ29" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK29" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR29" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>1</v>
+      </c>
+      <c r="B30" s="2">
+        <v>2</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F30" s="4">
+        <v>46281</v>
+      </c>
+      <c r="G30" s="5">
+        <v>11</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L30" s="6">
+        <v>12</v>
+      </c>
+      <c r="M30" s="7">
+        <v>3904.44</v>
+      </c>
+      <c r="N30" s="6">
+        <v>1</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P30" s="8">
+        <v>325.37</v>
+      </c>
+      <c r="Q30" s="6">
+        <v>0</v>
+      </c>
+      <c r="R30" s="7">
+        <v>0</v>
+      </c>
+      <c r="S30" s="9">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U30" s="10">
+        <v>67488</v>
+      </c>
+      <c r="V30" s="11">
+        <v>11</v>
+      </c>
+      <c r="W30" s="4">
+        <v>46281</v>
+      </c>
+      <c r="X30" s="12">
+        <v>0.44583329999999999</v>
+      </c>
+      <c r="Y30" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG30" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ30" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK30" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR30" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>1</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F31" s="4">
+        <v>46281</v>
+      </c>
+      <c r="G31" s="5">
+        <v>12</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L31" s="6">
+        <v>13</v>
+      </c>
+      <c r="M31" s="7">
+        <v>4229.8100000000004</v>
+      </c>
+      <c r="N31" s="6">
+        <v>1</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P31" s="8">
+        <v>325.37</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>0</v>
+      </c>
+      <c r="R31" s="7">
+        <v>0</v>
+      </c>
+      <c r="S31" s="9">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U31" s="10">
+        <v>67488</v>
+      </c>
+      <c r="V31" s="11">
+        <v>11</v>
+      </c>
+      <c r="W31" s="4">
+        <v>46281</v>
+      </c>
+      <c r="X31" s="12">
+        <v>0.44583329999999999</v>
+      </c>
+      <c r="Y31" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG31" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ31" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK31" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR31" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>1</v>
+      </c>
+      <c r="B32" s="2">
+        <v>2</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" s="4">
+        <v>46281</v>
+      </c>
+      <c r="G32" s="5">
+        <v>13</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L32" s="6">
+        <v>14</v>
+      </c>
+      <c r="M32" s="7">
+        <v>4555.18</v>
+      </c>
+      <c r="N32" s="6">
+        <v>1</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P32" s="8">
+        <v>325.37</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>0</v>
+      </c>
+      <c r="R32" s="7">
+        <v>0</v>
+      </c>
+      <c r="S32" s="9">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U32" s="10">
+        <v>67488</v>
+      </c>
+      <c r="V32" s="11">
+        <v>11</v>
+      </c>
+      <c r="W32" s="4">
+        <v>46281</v>
+      </c>
+      <c r="X32" s="12">
+        <v>0.44583329999999999</v>
+      </c>
+      <c r="Y32" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI32" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ32" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK32" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR32" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>1</v>
+      </c>
+      <c r="B33" s="2">
+        <v>2</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" s="4">
+        <v>46281</v>
+      </c>
+      <c r="G33" s="5">
+        <v>14</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L33" s="6">
+        <v>15</v>
+      </c>
+      <c r="M33" s="7">
+        <v>4880.55</v>
+      </c>
+      <c r="N33" s="6">
+        <v>1</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P33" s="8">
+        <v>325.37</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>0</v>
+      </c>
+      <c r="R33" s="7">
+        <v>0</v>
+      </c>
+      <c r="S33" s="9">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U33" s="10">
+        <v>67488</v>
+      </c>
+      <c r="V33" s="11">
+        <v>11</v>
+      </c>
+      <c r="W33" s="4">
+        <v>46281</v>
+      </c>
+      <c r="X33" s="12">
+        <v>0.44583329999999999</v>
+      </c>
+      <c r="Y33" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG33" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI33" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ33" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK33" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR33" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>1</v>
+      </c>
+      <c r="B34" s="2">
+        <v>2</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" s="4">
+        <v>46281</v>
+      </c>
+      <c r="G34" s="5">
+        <v>15</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L34" s="6">
+        <v>16</v>
+      </c>
+      <c r="M34" s="7">
+        <v>5205.92</v>
+      </c>
+      <c r="N34" s="6">
+        <v>1</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P34" s="8">
+        <v>325.37</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>0</v>
+      </c>
+      <c r="R34" s="7">
+        <v>0</v>
+      </c>
+      <c r="S34" s="9">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U34" s="10">
+        <v>67488</v>
+      </c>
+      <c r="V34" s="11">
+        <v>11</v>
+      </c>
+      <c r="W34" s="4">
+        <v>46281</v>
+      </c>
+      <c r="X34" s="12">
+        <v>0.44583329999999999</v>
+      </c>
+      <c r="Y34" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG34" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI34" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ34" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK34" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR34" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>1</v>
+      </c>
+      <c r="B35" s="2">
+        <v>2</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F35" s="4">
+        <v>46281</v>
+      </c>
+      <c r="G35" s="5">
+        <v>16</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L35" s="6">
+        <v>17</v>
+      </c>
+      <c r="M35" s="7">
+        <v>5531.29</v>
+      </c>
+      <c r="N35" s="6">
+        <v>1</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P35" s="8">
+        <v>325.37</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>0</v>
+      </c>
+      <c r="R35" s="7">
+        <v>0</v>
+      </c>
+      <c r="S35" s="9">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U35" s="10">
+        <v>67488</v>
+      </c>
+      <c r="V35" s="11">
+        <v>11</v>
+      </c>
+      <c r="W35" s="4">
+        <v>46281</v>
+      </c>
+      <c r="X35" s="12">
+        <v>0.44583329999999999</v>
+      </c>
+      <c r="Y35" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG35" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI35" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ35" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK35" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM35" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR35" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>1</v>
+      </c>
+      <c r="B36" s="2">
+        <v>2</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F36" s="4">
+        <v>46281</v>
+      </c>
+      <c r="G36" s="5">
+        <v>17</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L36" s="6">
+        <v>18</v>
+      </c>
+      <c r="M36" s="7">
+        <v>5856.66</v>
+      </c>
+      <c r="N36" s="6">
+        <v>1</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P36" s="8">
+        <v>325.37</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0</v>
+      </c>
+      <c r="R36" s="7">
+        <v>0</v>
+      </c>
+      <c r="S36" s="9">
+        <v>0</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U36" s="10">
+        <v>67488</v>
+      </c>
+      <c r="V36" s="11">
+        <v>11</v>
+      </c>
+      <c r="W36" s="4">
+        <v>46281</v>
+      </c>
+      <c r="X36" s="12">
+        <v>0.44583329999999999</v>
+      </c>
+      <c r="Y36" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI36" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ36" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK36" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR36" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>1</v>
+      </c>
+      <c r="B37" s="2">
+        <v>2</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F37" s="4">
+        <v>46281</v>
+      </c>
+      <c r="G37" s="5">
+        <v>18</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L37" s="6">
+        <v>19</v>
+      </c>
+      <c r="M37" s="7">
+        <v>6182.03</v>
+      </c>
+      <c r="N37" s="6">
+        <v>1</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P37" s="8">
+        <v>325.37</v>
+      </c>
+      <c r="Q37" s="6">
+        <v>0</v>
+      </c>
+      <c r="R37" s="7">
+        <v>0</v>
+      </c>
+      <c r="S37" s="9">
+        <v>0</v>
+      </c>
+      <c r="T37" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U37" s="10">
+        <v>67488</v>
+      </c>
+      <c r="V37" s="11">
+        <v>11</v>
+      </c>
+      <c r="W37" s="4">
+        <v>46281</v>
+      </c>
+      <c r="X37" s="12">
+        <v>0.44583329999999999</v>
+      </c>
+      <c r="Y37" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG37" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI37" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ37" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK37" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL37" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM37" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR37" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>1</v>
+      </c>
+      <c r="B38" s="2">
+        <v>2</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F38" s="4">
+        <v>46281</v>
+      </c>
+      <c r="G38" s="5">
+        <v>19</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L38" s="6">
+        <v>20</v>
+      </c>
+      <c r="M38" s="7">
+        <v>6507.4</v>
+      </c>
+      <c r="N38" s="6">
+        <v>1</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P38" s="8">
+        <v>325.37</v>
+      </c>
+      <c r="Q38" s="6">
+        <v>0</v>
+      </c>
+      <c r="R38" s="7">
+        <v>0</v>
+      </c>
+      <c r="S38" s="9">
+        <v>0</v>
+      </c>
+      <c r="T38" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U38" s="10">
+        <v>67488</v>
+      </c>
+      <c r="V38" s="11">
+        <v>11</v>
+      </c>
+      <c r="W38" s="4">
+        <v>46281</v>
+      </c>
+      <c r="X38" s="12">
+        <v>0.44583329999999999</v>
+      </c>
+      <c r="Y38" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG38" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI38" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ38" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK38" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL38" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM38" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN38" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO38" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP38" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ38" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR38" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>1</v>
+      </c>
+      <c r="B39" s="2">
+        <v>2</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F39" s="4">
+        <v>46281</v>
+      </c>
+      <c r="G39" s="5">
+        <v>20</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L39" s="6">
+        <v>21</v>
+      </c>
+      <c r="M39" s="7">
+        <v>6832.77</v>
+      </c>
+      <c r="N39" s="6">
+        <v>1</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P39" s="8">
+        <v>325.37</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>0</v>
+      </c>
+      <c r="R39" s="7">
+        <v>0</v>
+      </c>
+      <c r="S39" s="9">
+        <v>0</v>
+      </c>
+      <c r="T39" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U39" s="10">
+        <v>67488</v>
+      </c>
+      <c r="V39" s="11">
+        <v>11</v>
+      </c>
+      <c r="W39" s="4">
+        <v>46281</v>
+      </c>
+      <c r="X39" s="12">
+        <v>0.4611111</v>
+      </c>
+      <c r="Y39" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF39" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI39" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ39" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK39" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL39" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM39" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO39" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP39" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ39" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR39" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EE76D23-1D9A-46DD-98F9-14E7E343F367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4AA511D-7C10-4420-8CF1-6FF825804445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="91">
   <si>
     <t>Sel</t>
   </si>
@@ -154,10 +154,10 @@
     <t>Nº Série</t>
   </si>
   <si>
-    <t>10014979</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>10096354</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>500</t>
@@ -175,7 +175,7 @@
     <t>UN</t>
   </si>
   <si>
-    <t>FORNO ELETRICO NARDELLI TOP 40 40L BLACK - NARDELLI TOP 40 - 220 V</t>
+    <t>FORNO ELETRICO TERIM EMBUTIR 60L BLACK - 127 V</t>
   </si>
   <si>
     <t>100</t>
@@ -184,145 +184,115 @@
     <t/>
   </si>
   <si>
-    <t>FORNOS</t>
-  </si>
-  <si>
-    <t>1858600041542</t>
-  </si>
-  <si>
-    <t>10016351</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>FORNO ELETRICO NARDELLI EMBUTIR INOX 60 LITROS - NARDELLI EMBUTIR INOX 60 LITROS - 127 V</t>
-  </si>
-  <si>
     <t>FORNOE</t>
   </si>
   <si>
-    <t>1858400003510</t>
-  </si>
-  <si>
-    <t>1858400003511</t>
-  </si>
-  <si>
-    <t>1858400003512</t>
-  </si>
-  <si>
-    <t>1858400003513</t>
-  </si>
-  <si>
-    <t>1858400003514</t>
-  </si>
-  <si>
-    <t>1858400003515</t>
-  </si>
-  <si>
-    <t>1858400003516</t>
-  </si>
-  <si>
-    <t>10018965</t>
-  </si>
-  <si>
-    <t>FORNO ELETRICO NARDELLI E50 BLACK 50L - NARDELLI E50 BLACK 50 L - 220 V</t>
-  </si>
-  <si>
-    <t>1879900000465</t>
-  </si>
-  <si>
-    <t>1879900000466</t>
-  </si>
-  <si>
-    <t>1879900000467</t>
-  </si>
-  <si>
-    <t>1879900000468</t>
-  </si>
-  <si>
-    <t>1879900000469</t>
-  </si>
-  <si>
-    <t>1879900000470</t>
-  </si>
-  <si>
-    <t>1879900000471</t>
-  </si>
-  <si>
-    <t>1879900000472</t>
-  </si>
-  <si>
-    <t>1879900000473</t>
-  </si>
-  <si>
-    <t>1879900000474</t>
-  </si>
-  <si>
-    <t>10056354</t>
-  </si>
-  <si>
-    <t>FORNO ELETRICO FOGATTI EMBUTIR 60L BLACK - 127 V</t>
-  </si>
-  <si>
-    <t>1030900000070</t>
-  </si>
-  <si>
-    <t>1030900000071</t>
-  </si>
-  <si>
-    <t>1030900000072</t>
-  </si>
-  <si>
-    <t>1030900000073</t>
-  </si>
-  <si>
-    <t>1030900000074</t>
-  </si>
-  <si>
-    <t>1030900000075</t>
-  </si>
-  <si>
-    <t>1030900000076</t>
-  </si>
-  <si>
-    <t>1030900000077</t>
-  </si>
-  <si>
-    <t>1030900000078</t>
-  </si>
-  <si>
-    <t>1030900000079</t>
-  </si>
-  <si>
-    <t>1030900000080</t>
-  </si>
-  <si>
-    <t>1030900000081</t>
-  </si>
-  <si>
-    <t>1030900000082</t>
-  </si>
-  <si>
-    <t>1030900000083</t>
-  </si>
-  <si>
-    <t>1030900000084</t>
-  </si>
-  <si>
-    <t>1030900000085</t>
-  </si>
-  <si>
-    <t>1030900000086</t>
-  </si>
-  <si>
-    <t>1030900000087</t>
-  </si>
-  <si>
-    <t>1030900000088</t>
-  </si>
-  <si>
-    <t>1030900000089</t>
+    <t>1031100000267</t>
+  </si>
+  <si>
+    <t>1031100000268</t>
+  </si>
+  <si>
+    <t>1031100000269</t>
+  </si>
+  <si>
+    <t>1031100000270</t>
+  </si>
+  <si>
+    <t>1031100000271</t>
+  </si>
+  <si>
+    <t>1031100000272</t>
+  </si>
+  <si>
+    <t>1031100000273</t>
+  </si>
+  <si>
+    <t>1031100000274</t>
+  </si>
+  <si>
+    <t>1031100000275</t>
+  </si>
+  <si>
+    <t>1031100000276</t>
+  </si>
+  <si>
+    <t>1031100000277</t>
+  </si>
+  <si>
+    <t>1031100000278</t>
+  </si>
+  <si>
+    <t>1031100000279</t>
+  </si>
+  <si>
+    <t>1031100000280</t>
+  </si>
+  <si>
+    <t>1031100000281</t>
+  </si>
+  <si>
+    <t>1031100000282</t>
+  </si>
+  <si>
+    <t>1031100000283</t>
+  </si>
+  <si>
+    <t>1031100000284</t>
+  </si>
+  <si>
+    <t>1031100000285</t>
+  </si>
+  <si>
+    <t>1031100000286</t>
+  </si>
+  <si>
+    <t>1031100000287</t>
+  </si>
+  <si>
+    <t>1031100000288</t>
+  </si>
+  <si>
+    <t>1031100000289</t>
+  </si>
+  <si>
+    <t>1031100000290</t>
+  </si>
+  <si>
+    <t>1031100000291</t>
+  </si>
+  <si>
+    <t>1031100000292</t>
+  </si>
+  <si>
+    <t>1031100000293</t>
+  </si>
+  <si>
+    <t>1031100000294</t>
+  </si>
+  <si>
+    <t>1031100000295</t>
+  </si>
+  <si>
+    <t>1031100000296</t>
+  </si>
+  <si>
+    <t>1031100000297</t>
+  </si>
+  <si>
+    <t>1031100000298</t>
+  </si>
+  <si>
+    <t>1031100000299</t>
+  </si>
+  <si>
+    <t>1031100000300</t>
+  </si>
+  <si>
+    <t>1031100000301</t>
+  </si>
+  <si>
+    <t>1031100000302</t>
   </si>
 </sst>
 </file>
@@ -898,7 +868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR39"/>
+  <dimension ref="A1:AR37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -1052,10 +1022,10 @@
         <v>46</v>
       </c>
       <c r="F2" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G2" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>47</v>
@@ -1070,10 +1040,10 @@
         <v>50</v>
       </c>
       <c r="L2" s="6">
-        <v>915</v>
+        <v>39</v>
       </c>
       <c r="M2" s="7">
-        <v>171252.21</v>
+        <v>14223.69</v>
       </c>
       <c r="N2" s="6">
         <v>1</v>
@@ -1082,7 +1052,7 @@
         <v>51</v>
       </c>
       <c r="P2" s="8">
-        <v>187.16</v>
+        <v>364.71</v>
       </c>
       <c r="Q2" s="6">
         <v>0</v>
@@ -1097,16 +1067,16 @@
         <v>52</v>
       </c>
       <c r="U2" s="10">
-        <v>67407</v>
+        <v>67518</v>
       </c>
       <c r="V2" s="11">
         <v>11</v>
       </c>
       <c r="W2" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X2" s="12">
-        <v>0.39027780000000001</v>
+        <v>0.32847219999999999</v>
       </c>
       <c r="Y2" s="10">
         <v>0</v>
@@ -1177,19 +1147,19 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>47</v>
@@ -1204,19 +1174,19 @@
         <v>50</v>
       </c>
       <c r="L3" s="6">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="M3" s="7">
-        <v>27544.42</v>
+        <v>14588.4</v>
       </c>
       <c r="N3" s="6">
         <v>1</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="P3" s="8">
-        <v>377.32</v>
+        <v>364.71</v>
       </c>
       <c r="Q3" s="6">
         <v>0</v>
@@ -1231,16 +1201,16 @@
         <v>52</v>
       </c>
       <c r="U3" s="10">
-        <v>66798</v>
+        <v>67518</v>
       </c>
       <c r="V3" s="11">
         <v>11</v>
       </c>
       <c r="W3" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X3" s="12">
-        <v>0.4583333</v>
+        <v>0.32847219999999999</v>
       </c>
       <c r="Y3" s="10">
         <v>0</v>
@@ -1273,7 +1243,7 @@
         <v>53</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ3" s="3" t="s">
         <v>52</v>
@@ -1300,7 +1270,7 @@
         <v>53</v>
       </c>
       <c r="AR3" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.3">
@@ -1311,19 +1281,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F4" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>47</v>
@@ -1338,19 +1308,19 @@
         <v>50</v>
       </c>
       <c r="L4" s="6">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="M4" s="7">
-        <v>27921.74</v>
+        <v>14953.11</v>
       </c>
       <c r="N4" s="6">
         <v>1</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="P4" s="8">
-        <v>377.32</v>
+        <v>364.71</v>
       </c>
       <c r="Q4" s="6">
         <v>0</v>
@@ -1365,16 +1335,16 @@
         <v>52</v>
       </c>
       <c r="U4" s="10">
-        <v>66798</v>
+        <v>67518</v>
       </c>
       <c r="V4" s="11">
         <v>11</v>
       </c>
       <c r="W4" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X4" s="12">
-        <v>0.4583333</v>
+        <v>0.32847219999999999</v>
       </c>
       <c r="Y4" s="10">
         <v>0</v>
@@ -1407,7 +1377,7 @@
         <v>53</v>
       </c>
       <c r="AI4" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ4" s="3" t="s">
         <v>52</v>
@@ -1434,7 +1404,7 @@
         <v>53</v>
       </c>
       <c r="AR4" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
@@ -1445,19 +1415,19 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F5" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>47</v>
@@ -1472,19 +1442,19 @@
         <v>50</v>
       </c>
       <c r="L5" s="6">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="M5" s="7">
-        <v>28299.06</v>
+        <v>15317.82</v>
       </c>
       <c r="N5" s="6">
         <v>1</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="P5" s="8">
-        <v>377.32</v>
+        <v>364.71</v>
       </c>
       <c r="Q5" s="6">
         <v>0</v>
@@ -1499,16 +1469,16 @@
         <v>52</v>
       </c>
       <c r="U5" s="10">
-        <v>66798</v>
+        <v>67518</v>
       </c>
       <c r="V5" s="11">
         <v>11</v>
       </c>
       <c r="W5" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X5" s="12">
-        <v>0.4583333</v>
+        <v>0.32847219999999999</v>
       </c>
       <c r="Y5" s="10">
         <v>0</v>
@@ -1541,7 +1511,7 @@
         <v>53</v>
       </c>
       <c r="AI5" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ5" s="3" t="s">
         <v>52</v>
@@ -1568,7 +1538,7 @@
         <v>53</v>
       </c>
       <c r="AR5" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
@@ -1579,19 +1549,19 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F6" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G6" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>47</v>
@@ -1606,19 +1576,19 @@
         <v>50</v>
       </c>
       <c r="L6" s="6">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="M6" s="7">
-        <v>28676.39</v>
+        <v>15682.53</v>
       </c>
       <c r="N6" s="6">
         <v>1</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="P6" s="8">
-        <v>377.32</v>
+        <v>364.71</v>
       </c>
       <c r="Q6" s="6">
         <v>0</v>
@@ -1633,16 +1603,16 @@
         <v>52</v>
       </c>
       <c r="U6" s="10">
-        <v>66798</v>
+        <v>67518</v>
       </c>
       <c r="V6" s="11">
         <v>11</v>
       </c>
       <c r="W6" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X6" s="12">
-        <v>0.4583333</v>
+        <v>0.32847219999999999</v>
       </c>
       <c r="Y6" s="10">
         <v>0</v>
@@ -1675,34 +1645,34 @@
         <v>53</v>
       </c>
       <c r="AI6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK6" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR6" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="AJ6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK6" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM6" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR6" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
@@ -1713,19 +1683,19 @@
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F7" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G7" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>47</v>
@@ -1740,19 +1710,19 @@
         <v>50</v>
       </c>
       <c r="L7" s="6">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="M7" s="7">
-        <v>29053.71</v>
+        <v>16047.24</v>
       </c>
       <c r="N7" s="6">
         <v>1</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="P7" s="8">
-        <v>377.32</v>
+        <v>364.71</v>
       </c>
       <c r="Q7" s="6">
         <v>0</v>
@@ -1767,16 +1737,16 @@
         <v>52</v>
       </c>
       <c r="U7" s="10">
-        <v>66798</v>
+        <v>67518</v>
       </c>
       <c r="V7" s="11">
         <v>11</v>
       </c>
       <c r="W7" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X7" s="12">
-        <v>0.4583333</v>
+        <v>0.32847219999999999</v>
       </c>
       <c r="Y7" s="10">
         <v>0</v>
@@ -1809,7 +1779,7 @@
         <v>53</v>
       </c>
       <c r="AI7" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ7" s="3" t="s">
         <v>52</v>
@@ -1836,7 +1806,7 @@
         <v>53</v>
       </c>
       <c r="AR7" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
@@ -1847,19 +1817,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F8" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G8" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>47</v>
@@ -1874,19 +1844,19 @@
         <v>50</v>
       </c>
       <c r="L8" s="6">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="M8" s="7">
-        <v>29431.03</v>
+        <v>16411.95</v>
       </c>
       <c r="N8" s="6">
         <v>1</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="P8" s="8">
-        <v>377.32</v>
+        <v>364.71</v>
       </c>
       <c r="Q8" s="6">
         <v>0</v>
@@ -1901,16 +1871,16 @@
         <v>52</v>
       </c>
       <c r="U8" s="10">
-        <v>66798</v>
+        <v>67518</v>
       </c>
       <c r="V8" s="11">
         <v>11</v>
       </c>
       <c r="W8" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X8" s="12">
-        <v>0.4583333</v>
+        <v>0.37152780000000002</v>
       </c>
       <c r="Y8" s="10">
         <v>0</v>
@@ -1943,7 +1913,7 @@
         <v>53</v>
       </c>
       <c r="AI8" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ8" s="3" t="s">
         <v>52</v>
@@ -1970,7 +1940,7 @@
         <v>53</v>
       </c>
       <c r="AR8" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
@@ -1981,19 +1951,19 @@
         <v>2</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F9" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G9" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>47</v>
@@ -2008,19 +1978,19 @@
         <v>50</v>
       </c>
       <c r="L9" s="6">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="M9" s="7">
-        <v>29808.35</v>
+        <v>16776.66</v>
       </c>
       <c r="N9" s="6">
         <v>1</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="P9" s="8">
-        <v>377.32</v>
+        <v>364.71</v>
       </c>
       <c r="Q9" s="6">
         <v>0</v>
@@ -2035,16 +2005,16 @@
         <v>52</v>
       </c>
       <c r="U9" s="10">
-        <v>66798</v>
+        <v>67518</v>
       </c>
       <c r="V9" s="11">
         <v>11</v>
       </c>
       <c r="W9" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X9" s="12">
-        <v>0.4583333</v>
+        <v>0.37152780000000002</v>
       </c>
       <c r="Y9" s="10">
         <v>0</v>
@@ -2077,7 +2047,7 @@
         <v>53</v>
       </c>
       <c r="AI9" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ9" s="3" t="s">
         <v>52</v>
@@ -2104,7 +2074,7 @@
         <v>53</v>
       </c>
       <c r="AR9" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
@@ -2115,7 +2085,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>45</v>
@@ -2124,10 +2094,10 @@
         <v>46</v>
       </c>
       <c r="F10" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G10" s="5">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>47</v>
@@ -2142,19 +2112,19 @@
         <v>50</v>
       </c>
       <c r="L10" s="6">
-        <v>127</v>
+        <v>47</v>
       </c>
       <c r="M10" s="7">
-        <v>44105.13</v>
+        <v>17141.37</v>
       </c>
       <c r="N10" s="6">
         <v>1</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="P10" s="8">
-        <v>347.28</v>
+        <v>364.71</v>
       </c>
       <c r="Q10" s="6">
         <v>0</v>
@@ -2169,16 +2139,16 @@
         <v>52</v>
       </c>
       <c r="U10" s="10">
-        <v>67347</v>
+        <v>67518</v>
       </c>
       <c r="V10" s="11">
         <v>11</v>
       </c>
       <c r="W10" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X10" s="12">
-        <v>0.38958330000000002</v>
+        <v>0.37152780000000002</v>
       </c>
       <c r="Y10" s="10">
         <v>0</v>
@@ -2211,7 +2181,7 @@
         <v>53</v>
       </c>
       <c r="AI10" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ10" s="3" t="s">
         <v>52</v>
@@ -2238,7 +2208,7 @@
         <v>53</v>
       </c>
       <c r="AR10" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
@@ -2249,7 +2219,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>45</v>
@@ -2258,10 +2228,10 @@
         <v>46</v>
       </c>
       <c r="F11" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G11" s="5">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>47</v>
@@ -2276,19 +2246,19 @@
         <v>50</v>
       </c>
       <c r="L11" s="6">
-        <v>128</v>
+        <v>48</v>
       </c>
       <c r="M11" s="7">
-        <v>44452.41</v>
+        <v>17506.080000000002</v>
       </c>
       <c r="N11" s="6">
         <v>1</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="P11" s="8">
-        <v>347.28</v>
+        <v>364.71</v>
       </c>
       <c r="Q11" s="6">
         <v>0</v>
@@ -2303,16 +2273,16 @@
         <v>52</v>
       </c>
       <c r="U11" s="10">
-        <v>67347</v>
+        <v>67518</v>
       </c>
       <c r="V11" s="11">
         <v>11</v>
       </c>
       <c r="W11" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X11" s="12">
-        <v>0.38958330000000002</v>
+        <v>0.37152780000000002</v>
       </c>
       <c r="Y11" s="10">
         <v>0</v>
@@ -2345,7 +2315,7 @@
         <v>53</v>
       </c>
       <c r="AI11" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ11" s="3" t="s">
         <v>52</v>
@@ -2372,7 +2342,7 @@
         <v>53</v>
       </c>
       <c r="AR11" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
@@ -2383,7 +2353,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>45</v>
@@ -2392,10 +2362,10 @@
         <v>46</v>
       </c>
       <c r="F12" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G12" s="5">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>47</v>
@@ -2410,19 +2380,19 @@
         <v>50</v>
       </c>
       <c r="L12" s="6">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="M12" s="7">
-        <v>44799.7</v>
+        <v>17870.79</v>
       </c>
       <c r="N12" s="6">
         <v>1</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="P12" s="8">
-        <v>347.28</v>
+        <v>364.71</v>
       </c>
       <c r="Q12" s="6">
         <v>0</v>
@@ -2437,16 +2407,16 @@
         <v>52</v>
       </c>
       <c r="U12" s="10">
-        <v>67347</v>
+        <v>67518</v>
       </c>
       <c r="V12" s="11">
         <v>11</v>
       </c>
       <c r="W12" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X12" s="12">
-        <v>0.38958330000000002</v>
+        <v>0.37152780000000002</v>
       </c>
       <c r="Y12" s="10">
         <v>0</v>
@@ -2479,7 +2449,7 @@
         <v>53</v>
       </c>
       <c r="AI12" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ12" s="3" t="s">
         <v>52</v>
@@ -2506,7 +2476,7 @@
         <v>53</v>
       </c>
       <c r="AR12" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.3">
@@ -2517,7 +2487,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>45</v>
@@ -2526,10 +2496,10 @@
         <v>46</v>
       </c>
       <c r="F13" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G13" s="5">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>47</v>
@@ -2544,19 +2514,19 @@
         <v>50</v>
       </c>
       <c r="L13" s="6">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="M13" s="7">
-        <v>45146.98</v>
+        <v>18235.5</v>
       </c>
       <c r="N13" s="6">
         <v>1</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="P13" s="8">
-        <v>347.28</v>
+        <v>364.71</v>
       </c>
       <c r="Q13" s="6">
         <v>0</v>
@@ -2571,16 +2541,16 @@
         <v>52</v>
       </c>
       <c r="U13" s="10">
-        <v>67347</v>
+        <v>67518</v>
       </c>
       <c r="V13" s="11">
         <v>11</v>
       </c>
       <c r="W13" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X13" s="12">
-        <v>0.38958330000000002</v>
+        <v>0.37152780000000002</v>
       </c>
       <c r="Y13" s="10">
         <v>0</v>
@@ -2613,7 +2583,7 @@
         <v>53</v>
       </c>
       <c r="AI13" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ13" s="3" t="s">
         <v>52</v>
@@ -2640,7 +2610,7 @@
         <v>53</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
@@ -2651,7 +2621,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>45</v>
@@ -2660,10 +2630,10 @@
         <v>46</v>
       </c>
       <c r="F14" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G14" s="5">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>47</v>
@@ -2678,19 +2648,19 @@
         <v>50</v>
       </c>
       <c r="L14" s="6">
-        <v>131</v>
+        <v>51</v>
       </c>
       <c r="M14" s="7">
-        <v>45494.27</v>
+        <v>18600.21</v>
       </c>
       <c r="N14" s="6">
         <v>1</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="P14" s="8">
-        <v>347.28</v>
+        <v>364.71</v>
       </c>
       <c r="Q14" s="6">
         <v>0</v>
@@ -2705,16 +2675,16 @@
         <v>52</v>
       </c>
       <c r="U14" s="10">
-        <v>67347</v>
+        <v>67518</v>
       </c>
       <c r="V14" s="11">
         <v>11</v>
       </c>
       <c r="W14" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X14" s="12">
-        <v>0.38958330000000002</v>
+        <v>0.42152780000000001</v>
       </c>
       <c r="Y14" s="10">
         <v>0</v>
@@ -2747,7 +2717,7 @@
         <v>53</v>
       </c>
       <c r="AI14" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>52</v>
@@ -2774,7 +2744,7 @@
         <v>53</v>
       </c>
       <c r="AR14" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
@@ -2785,7 +2755,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>45</v>
@@ -2794,10 +2764,10 @@
         <v>46</v>
       </c>
       <c r="F15" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G15" s="5">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>47</v>
@@ -2812,19 +2782,19 @@
         <v>50</v>
       </c>
       <c r="L15" s="6">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="M15" s="7">
-        <v>45841.55</v>
+        <v>18964.919999999998</v>
       </c>
       <c r="N15" s="6">
         <v>1</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="P15" s="8">
-        <v>347.28</v>
+        <v>364.71</v>
       </c>
       <c r="Q15" s="6">
         <v>0</v>
@@ -2839,16 +2809,16 @@
         <v>52</v>
       </c>
       <c r="U15" s="10">
-        <v>67347</v>
+        <v>67518</v>
       </c>
       <c r="V15" s="11">
         <v>11</v>
       </c>
       <c r="W15" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X15" s="12">
-        <v>0.38958330000000002</v>
+        <v>0.42152780000000001</v>
       </c>
       <c r="Y15" s="10">
         <v>0</v>
@@ -2881,7 +2851,7 @@
         <v>53</v>
       </c>
       <c r="AI15" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ15" s="3" t="s">
         <v>52</v>
@@ -2908,7 +2878,7 @@
         <v>53</v>
       </c>
       <c r="AR15" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.3">
@@ -2919,7 +2889,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>45</v>
@@ -2928,10 +2898,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G16" s="5">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>47</v>
@@ -2946,19 +2916,19 @@
         <v>50</v>
       </c>
       <c r="L16" s="6">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="M16" s="7">
-        <v>46188.83</v>
+        <v>19329.63</v>
       </c>
       <c r="N16" s="6">
         <v>1</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="P16" s="8">
-        <v>347.28</v>
+        <v>364.71</v>
       </c>
       <c r="Q16" s="6">
         <v>0</v>
@@ -2973,16 +2943,16 @@
         <v>52</v>
       </c>
       <c r="U16" s="10">
-        <v>67347</v>
+        <v>67518</v>
       </c>
       <c r="V16" s="11">
         <v>11</v>
       </c>
       <c r="W16" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X16" s="12">
-        <v>0.38958330000000002</v>
+        <v>0.42152780000000001</v>
       </c>
       <c r="Y16" s="10">
         <v>0</v>
@@ -3015,7 +2985,7 @@
         <v>53</v>
       </c>
       <c r="AI16" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ16" s="3" t="s">
         <v>52</v>
@@ -3042,7 +3012,7 @@
         <v>53</v>
       </c>
       <c r="AR16" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.3">
@@ -3053,7 +3023,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>45</v>
@@ -3062,10 +3032,10 @@
         <v>46</v>
       </c>
       <c r="F17" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G17" s="5">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>47</v>
@@ -3080,19 +3050,19 @@
         <v>50</v>
       </c>
       <c r="L17" s="6">
-        <v>134</v>
+        <v>54</v>
       </c>
       <c r="M17" s="7">
-        <v>46536.12</v>
+        <v>19694.34</v>
       </c>
       <c r="N17" s="6">
         <v>1</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="P17" s="8">
-        <v>347.28</v>
+        <v>364.71</v>
       </c>
       <c r="Q17" s="6">
         <v>0</v>
@@ -3107,16 +3077,16 @@
         <v>52</v>
       </c>
       <c r="U17" s="10">
-        <v>67347</v>
+        <v>67518</v>
       </c>
       <c r="V17" s="11">
         <v>11</v>
       </c>
       <c r="W17" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X17" s="12">
-        <v>0.38958330000000002</v>
+        <v>0.42152780000000001</v>
       </c>
       <c r="Y17" s="10">
         <v>0</v>
@@ -3149,7 +3119,7 @@
         <v>53</v>
       </c>
       <c r="AI17" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ17" s="3" t="s">
         <v>52</v>
@@ -3176,7 +3146,7 @@
         <v>53</v>
       </c>
       <c r="AR17" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:44" x14ac:dyDescent="0.3">
@@ -3187,7 +3157,7 @@
         <v>2</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>45</v>
@@ -3196,10 +3166,10 @@
         <v>46</v>
       </c>
       <c r="F18" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G18" s="5">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>47</v>
@@ -3214,19 +3184,19 @@
         <v>50</v>
       </c>
       <c r="L18" s="6">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="M18" s="7">
-        <v>46883.4</v>
+        <v>20059.05</v>
       </c>
       <c r="N18" s="6">
         <v>1</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="P18" s="8">
-        <v>347.28</v>
+        <v>364.71</v>
       </c>
       <c r="Q18" s="6">
         <v>0</v>
@@ -3241,16 +3211,16 @@
         <v>52</v>
       </c>
       <c r="U18" s="10">
-        <v>67347</v>
+        <v>67518</v>
       </c>
       <c r="V18" s="11">
         <v>11</v>
       </c>
       <c r="W18" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X18" s="12">
-        <v>0.38958330000000002</v>
+        <v>0.42152780000000001</v>
       </c>
       <c r="Y18" s="10">
         <v>0</v>
@@ -3283,7 +3253,7 @@
         <v>53</v>
       </c>
       <c r="AI18" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ18" s="3" t="s">
         <v>52</v>
@@ -3310,7 +3280,7 @@
         <v>53</v>
       </c>
       <c r="AR18" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.3">
@@ -3321,7 +3291,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>45</v>
@@ -3330,10 +3300,10 @@
         <v>46</v>
       </c>
       <c r="F19" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G19" s="5">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>47</v>
@@ -3348,19 +3318,19 @@
         <v>50</v>
       </c>
       <c r="L19" s="6">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="M19" s="7">
-        <v>47230.69</v>
+        <v>20423.759999999998</v>
       </c>
       <c r="N19" s="6">
         <v>1</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="P19" s="8">
-        <v>347.28</v>
+        <v>364.71</v>
       </c>
       <c r="Q19" s="6">
         <v>0</v>
@@ -3375,16 +3345,16 @@
         <v>52</v>
       </c>
       <c r="U19" s="10">
-        <v>67347</v>
+        <v>67518</v>
       </c>
       <c r="V19" s="11">
         <v>11</v>
       </c>
       <c r="W19" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X19" s="12">
-        <v>0.38958330000000002</v>
+        <v>0.42152780000000001</v>
       </c>
       <c r="Y19" s="10">
         <v>0</v>
@@ -3417,7 +3387,7 @@
         <v>53</v>
       </c>
       <c r="AI19" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ19" s="3" t="s">
         <v>52</v>
@@ -3444,7 +3414,7 @@
         <v>53</v>
       </c>
       <c r="AR19" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.3">
@@ -3455,19 +3425,19 @@
         <v>2</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F20" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G20" s="5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>47</v>
@@ -3482,19 +3452,19 @@
         <v>50</v>
       </c>
       <c r="L20" s="6">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="M20" s="7">
-        <v>650.74</v>
+        <v>20788.47</v>
       </c>
       <c r="N20" s="6">
         <v>1</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P20" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q20" s="6">
         <v>0</v>
@@ -3509,16 +3479,16 @@
         <v>52</v>
       </c>
       <c r="U20" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V20" s="11">
         <v>11</v>
       </c>
       <c r="W20" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X20" s="12">
-        <v>0.41041670000000002</v>
+        <v>0.42152780000000001</v>
       </c>
       <c r="Y20" s="10">
         <v>0</v>
@@ -3551,7 +3521,7 @@
         <v>53</v>
       </c>
       <c r="AI20" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ20" s="3" t="s">
         <v>52</v>
@@ -3578,7 +3548,7 @@
         <v>53</v>
       </c>
       <c r="AR20" s="3" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:44" x14ac:dyDescent="0.3">
@@ -3589,19 +3559,19 @@
         <v>2</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F21" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G21" s="5">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>47</v>
@@ -3616,19 +3586,19 @@
         <v>50</v>
       </c>
       <c r="L21" s="6">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="M21" s="7">
-        <v>976.11</v>
+        <v>21153.18</v>
       </c>
       <c r="N21" s="6">
         <v>1</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P21" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q21" s="6">
         <v>0</v>
@@ -3643,16 +3613,16 @@
         <v>52</v>
       </c>
       <c r="U21" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V21" s="11">
         <v>11</v>
       </c>
       <c r="W21" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X21" s="12">
-        <v>0.41041670000000002</v>
+        <v>0.42152780000000001</v>
       </c>
       <c r="Y21" s="10">
         <v>0</v>
@@ -3685,7 +3655,7 @@
         <v>53</v>
       </c>
       <c r="AI21" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ21" s="3" t="s">
         <v>52</v>
@@ -3712,7 +3682,7 @@
         <v>53</v>
       </c>
       <c r="AR21" s="3" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:44" x14ac:dyDescent="0.3">
@@ -3723,19 +3693,19 @@
         <v>2</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F22" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G22" s="5">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>47</v>
@@ -3750,19 +3720,19 @@
         <v>50</v>
       </c>
       <c r="L22" s="6">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="M22" s="7">
-        <v>1301.48</v>
+        <v>21517.89</v>
       </c>
       <c r="N22" s="6">
         <v>1</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P22" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q22" s="6">
         <v>0</v>
@@ -3777,16 +3747,16 @@
         <v>52</v>
       </c>
       <c r="U22" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V22" s="11">
         <v>11</v>
       </c>
       <c r="W22" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X22" s="12">
-        <v>0.41041670000000002</v>
+        <v>0.42152780000000001</v>
       </c>
       <c r="Y22" s="10">
         <v>0</v>
@@ -3819,7 +3789,7 @@
         <v>53</v>
       </c>
       <c r="AI22" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ22" s="3" t="s">
         <v>52</v>
@@ -3846,7 +3816,7 @@
         <v>53</v>
       </c>
       <c r="AR22" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:44" x14ac:dyDescent="0.3">
@@ -3857,19 +3827,19 @@
         <v>2</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F23" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G23" s="5">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>47</v>
@@ -3884,19 +3854,19 @@
         <v>50</v>
       </c>
       <c r="L23" s="6">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="M23" s="7">
-        <v>1626.85</v>
+        <v>21882.6</v>
       </c>
       <c r="N23" s="6">
         <v>1</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P23" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q23" s="6">
         <v>0</v>
@@ -3911,16 +3881,16 @@
         <v>52</v>
       </c>
       <c r="U23" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V23" s="11">
         <v>11</v>
       </c>
       <c r="W23" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X23" s="12">
-        <v>0.41041670000000002</v>
+        <v>0.42152780000000001</v>
       </c>
       <c r="Y23" s="10">
         <v>0</v>
@@ -3953,7 +3923,7 @@
         <v>53</v>
       </c>
       <c r="AI23" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ23" s="3" t="s">
         <v>52</v>
@@ -3980,7 +3950,7 @@
         <v>53</v>
       </c>
       <c r="AR23" s="3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.3">
@@ -3991,19 +3961,19 @@
         <v>2</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F24" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G24" s="5">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>47</v>
@@ -4018,19 +3988,19 @@
         <v>50</v>
       </c>
       <c r="L24" s="6">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="M24" s="7">
-        <v>1952.22</v>
+        <v>22247.31</v>
       </c>
       <c r="N24" s="6">
         <v>1</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P24" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q24" s="6">
         <v>0</v>
@@ -4045,16 +4015,16 @@
         <v>52</v>
       </c>
       <c r="U24" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V24" s="11">
         <v>11</v>
       </c>
       <c r="W24" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X24" s="12">
-        <v>0.41041670000000002</v>
+        <v>0.42152780000000001</v>
       </c>
       <c r="Y24" s="10">
         <v>0</v>
@@ -4087,7 +4057,7 @@
         <v>53</v>
       </c>
       <c r="AI24" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ24" s="3" t="s">
         <v>52</v>
@@ -4114,7 +4084,7 @@
         <v>53</v>
       </c>
       <c r="AR24" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:44" x14ac:dyDescent="0.3">
@@ -4125,19 +4095,19 @@
         <v>2</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F25" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G25" s="5">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>47</v>
@@ -4152,19 +4122,19 @@
         <v>50</v>
       </c>
       <c r="L25" s="6">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="M25" s="7">
-        <v>2277.59</v>
+        <v>22612.02</v>
       </c>
       <c r="N25" s="6">
         <v>1</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P25" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q25" s="6">
         <v>0</v>
@@ -4179,16 +4149,16 @@
         <v>52</v>
       </c>
       <c r="U25" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V25" s="11">
         <v>11</v>
       </c>
       <c r="W25" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X25" s="12">
-        <v>0.41041670000000002</v>
+        <v>0.42152780000000001</v>
       </c>
       <c r="Y25" s="10">
         <v>0</v>
@@ -4221,7 +4191,7 @@
         <v>53</v>
       </c>
       <c r="AI25" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ25" s="3" t="s">
         <v>52</v>
@@ -4248,7 +4218,7 @@
         <v>53</v>
       </c>
       <c r="AR25" s="3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:44" x14ac:dyDescent="0.3">
@@ -4259,19 +4229,19 @@
         <v>2</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F26" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G26" s="5">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>47</v>
@@ -4286,19 +4256,19 @@
         <v>50</v>
       </c>
       <c r="L26" s="6">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="M26" s="7">
-        <v>2602.96</v>
+        <v>22976.73</v>
       </c>
       <c r="N26" s="6">
         <v>1</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P26" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q26" s="6">
         <v>0</v>
@@ -4313,16 +4283,16 @@
         <v>52</v>
       </c>
       <c r="U26" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V26" s="11">
         <v>11</v>
       </c>
       <c r="W26" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X26" s="12">
-        <v>0.44583329999999999</v>
+        <v>0.46180559999999998</v>
       </c>
       <c r="Y26" s="10">
         <v>0</v>
@@ -4355,7 +4325,7 @@
         <v>53</v>
       </c>
       <c r="AI26" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ26" s="3" t="s">
         <v>52</v>
@@ -4382,7 +4352,7 @@
         <v>53</v>
       </c>
       <c r="AR26" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:44" x14ac:dyDescent="0.3">
@@ -4393,19 +4363,19 @@
         <v>2</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F27" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G27" s="5">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>47</v>
@@ -4420,19 +4390,19 @@
         <v>50</v>
       </c>
       <c r="L27" s="6">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="M27" s="7">
-        <v>2928.33</v>
+        <v>23341.439999999999</v>
       </c>
       <c r="N27" s="6">
         <v>1</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P27" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q27" s="6">
         <v>0</v>
@@ -4447,16 +4417,16 @@
         <v>52</v>
       </c>
       <c r="U27" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V27" s="11">
         <v>11</v>
       </c>
       <c r="W27" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X27" s="12">
-        <v>0.44583329999999999</v>
+        <v>0.46180559999999998</v>
       </c>
       <c r="Y27" s="10">
         <v>0</v>
@@ -4489,7 +4459,7 @@
         <v>53</v>
       </c>
       <c r="AI27" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ27" s="3" t="s">
         <v>52</v>
@@ -4516,7 +4486,7 @@
         <v>53</v>
       </c>
       <c r="AR27" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:44" x14ac:dyDescent="0.3">
@@ -4527,19 +4497,19 @@
         <v>2</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F28" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G28" s="5">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>47</v>
@@ -4554,19 +4524,19 @@
         <v>50</v>
       </c>
       <c r="L28" s="6">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="M28" s="7">
-        <v>3253.7</v>
+        <v>23706.15</v>
       </c>
       <c r="N28" s="6">
         <v>1</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P28" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q28" s="6">
         <v>0</v>
@@ -4581,16 +4551,16 @@
         <v>52</v>
       </c>
       <c r="U28" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V28" s="11">
         <v>11</v>
       </c>
       <c r="W28" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X28" s="12">
-        <v>0.44583329999999999</v>
+        <v>0.46180559999999998</v>
       </c>
       <c r="Y28" s="10">
         <v>0</v>
@@ -4623,7 +4593,7 @@
         <v>53</v>
       </c>
       <c r="AI28" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ28" s="3" t="s">
         <v>52</v>
@@ -4650,7 +4620,7 @@
         <v>53</v>
       </c>
       <c r="AR28" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.3">
@@ -4661,19 +4631,19 @@
         <v>2</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F29" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G29" s="5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>47</v>
@@ -4688,19 +4658,19 @@
         <v>50</v>
       </c>
       <c r="L29" s="6">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="M29" s="7">
-        <v>3579.07</v>
+        <v>24070.86</v>
       </c>
       <c r="N29" s="6">
         <v>1</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P29" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q29" s="6">
         <v>0</v>
@@ -4715,16 +4685,16 @@
         <v>52</v>
       </c>
       <c r="U29" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V29" s="11">
         <v>11</v>
       </c>
       <c r="W29" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X29" s="12">
-        <v>0.44583329999999999</v>
+        <v>0.46180559999999998</v>
       </c>
       <c r="Y29" s="10">
         <v>0</v>
@@ -4757,7 +4727,7 @@
         <v>53</v>
       </c>
       <c r="AI29" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>52</v>
@@ -4784,7 +4754,7 @@
         <v>53</v>
       </c>
       <c r="AR29" s="3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:44" x14ac:dyDescent="0.3">
@@ -4795,19 +4765,19 @@
         <v>2</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F30" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G30" s="5">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>47</v>
@@ -4822,19 +4792,19 @@
         <v>50</v>
       </c>
       <c r="L30" s="6">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="M30" s="7">
-        <v>3904.44</v>
+        <v>24435.57</v>
       </c>
       <c r="N30" s="6">
         <v>1</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P30" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q30" s="6">
         <v>0</v>
@@ -4849,16 +4819,16 @@
         <v>52</v>
       </c>
       <c r="U30" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V30" s="11">
         <v>11</v>
       </c>
       <c r="W30" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X30" s="12">
-        <v>0.44583329999999999</v>
+        <v>0.46180559999999998</v>
       </c>
       <c r="Y30" s="10">
         <v>0</v>
@@ -4891,7 +4861,7 @@
         <v>53</v>
       </c>
       <c r="AI30" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ30" s="3" t="s">
         <v>52</v>
@@ -4918,7 +4888,7 @@
         <v>53</v>
       </c>
       <c r="AR30" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:44" x14ac:dyDescent="0.3">
@@ -4929,19 +4899,19 @@
         <v>2</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F31" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G31" s="5">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>47</v>
@@ -4956,19 +4926,19 @@
         <v>50</v>
       </c>
       <c r="L31" s="6">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="M31" s="7">
-        <v>4229.8100000000004</v>
+        <v>24800.28</v>
       </c>
       <c r="N31" s="6">
         <v>1</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P31" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q31" s="6">
         <v>0</v>
@@ -4983,16 +4953,16 @@
         <v>52</v>
       </c>
       <c r="U31" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V31" s="11">
         <v>11</v>
       </c>
       <c r="W31" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X31" s="12">
-        <v>0.44583329999999999</v>
+        <v>0.46180559999999998</v>
       </c>
       <c r="Y31" s="10">
         <v>0</v>
@@ -5025,7 +4995,7 @@
         <v>53</v>
       </c>
       <c r="AI31" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ31" s="3" t="s">
         <v>52</v>
@@ -5052,7 +5022,7 @@
         <v>53</v>
       </c>
       <c r="AR31" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.3">
@@ -5063,19 +5033,19 @@
         <v>2</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F32" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G32" s="5">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>47</v>
@@ -5090,19 +5060,19 @@
         <v>50</v>
       </c>
       <c r="L32" s="6">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="M32" s="7">
-        <v>4555.18</v>
+        <v>25164.99</v>
       </c>
       <c r="N32" s="6">
         <v>1</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P32" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q32" s="6">
         <v>0</v>
@@ -5117,16 +5087,16 @@
         <v>52</v>
       </c>
       <c r="U32" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V32" s="11">
         <v>11</v>
       </c>
       <c r="W32" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X32" s="12">
-        <v>0.44583329999999999</v>
+        <v>0.46180559999999998</v>
       </c>
       <c r="Y32" s="10">
         <v>0</v>
@@ -5159,7 +5129,7 @@
         <v>53</v>
       </c>
       <c r="AI32" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ32" s="3" t="s">
         <v>52</v>
@@ -5186,7 +5156,7 @@
         <v>53</v>
       </c>
       <c r="AR32" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.3">
@@ -5197,19 +5167,19 @@
         <v>2</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F33" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G33" s="5">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>47</v>
@@ -5224,19 +5194,19 @@
         <v>50</v>
       </c>
       <c r="L33" s="6">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="M33" s="7">
-        <v>4880.55</v>
+        <v>25529.7</v>
       </c>
       <c r="N33" s="6">
         <v>1</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P33" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q33" s="6">
         <v>0</v>
@@ -5251,16 +5221,16 @@
         <v>52</v>
       </c>
       <c r="U33" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V33" s="11">
         <v>11</v>
       </c>
       <c r="W33" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X33" s="12">
-        <v>0.44583329999999999</v>
+        <v>0.46180559999999998</v>
       </c>
       <c r="Y33" s="10">
         <v>0</v>
@@ -5293,7 +5263,7 @@
         <v>53</v>
       </c>
       <c r="AI33" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ33" s="3" t="s">
         <v>52</v>
@@ -5320,7 +5290,7 @@
         <v>53</v>
       </c>
       <c r="AR33" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:44" x14ac:dyDescent="0.3">
@@ -5331,19 +5301,19 @@
         <v>2</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F34" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G34" s="5">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>47</v>
@@ -5358,19 +5328,19 @@
         <v>50</v>
       </c>
       <c r="L34" s="6">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="M34" s="7">
-        <v>5205.92</v>
+        <v>25894.41</v>
       </c>
       <c r="N34" s="6">
         <v>1</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P34" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q34" s="6">
         <v>0</v>
@@ -5385,16 +5355,16 @@
         <v>52</v>
       </c>
       <c r="U34" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V34" s="11">
         <v>11</v>
       </c>
       <c r="W34" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X34" s="12">
-        <v>0.44583329999999999</v>
+        <v>0.46180559999999998</v>
       </c>
       <c r="Y34" s="10">
         <v>0</v>
@@ -5427,7 +5397,7 @@
         <v>53</v>
       </c>
       <c r="AI34" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ34" s="3" t="s">
         <v>52</v>
@@ -5454,7 +5424,7 @@
         <v>53</v>
       </c>
       <c r="AR34" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.3">
@@ -5465,19 +5435,19 @@
         <v>2</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F35" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G35" s="5">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>47</v>
@@ -5492,19 +5462,19 @@
         <v>50</v>
       </c>
       <c r="L35" s="6">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="M35" s="7">
-        <v>5531.29</v>
+        <v>26259.119999999999</v>
       </c>
       <c r="N35" s="6">
         <v>1</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P35" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q35" s="6">
         <v>0</v>
@@ -5519,16 +5489,16 @@
         <v>52</v>
       </c>
       <c r="U35" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V35" s="11">
         <v>11</v>
       </c>
       <c r="W35" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X35" s="12">
-        <v>0.44583329999999999</v>
+        <v>0.46180559999999998</v>
       </c>
       <c r="Y35" s="10">
         <v>0</v>
@@ -5561,7 +5531,7 @@
         <v>53</v>
       </c>
       <c r="AI35" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ35" s="3" t="s">
         <v>52</v>
@@ -5588,7 +5558,7 @@
         <v>53</v>
       </c>
       <c r="AR35" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.3">
@@ -5599,19 +5569,19 @@
         <v>2</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F36" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G36" s="5">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>47</v>
@@ -5626,19 +5596,19 @@
         <v>50</v>
       </c>
       <c r="L36" s="6">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="M36" s="7">
-        <v>5856.66</v>
+        <v>26623.83</v>
       </c>
       <c r="N36" s="6">
         <v>1</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P36" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q36" s="6">
         <v>0</v>
@@ -5653,16 +5623,16 @@
         <v>52</v>
       </c>
       <c r="U36" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V36" s="11">
         <v>11</v>
       </c>
       <c r="W36" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X36" s="12">
-        <v>0.44583329999999999</v>
+        <v>0.46180559999999998</v>
       </c>
       <c r="Y36" s="10">
         <v>0</v>
@@ -5695,7 +5665,7 @@
         <v>53</v>
       </c>
       <c r="AI36" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ36" s="3" t="s">
         <v>52</v>
@@ -5722,7 +5692,7 @@
         <v>53</v>
       </c>
       <c r="AR36" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.3">
@@ -5733,19 +5703,19 @@
         <v>2</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F37" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="G37" s="5">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>47</v>
@@ -5760,19 +5730,19 @@
         <v>50</v>
       </c>
       <c r="L37" s="6">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="M37" s="7">
-        <v>6182.03</v>
+        <v>26988.54</v>
       </c>
       <c r="N37" s="6">
         <v>1</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="P37" s="8">
-        <v>325.37</v>
+        <v>364.71</v>
       </c>
       <c r="Q37" s="6">
         <v>0</v>
@@ -5787,16 +5757,16 @@
         <v>52</v>
       </c>
       <c r="U37" s="10">
-        <v>67488</v>
+        <v>67518</v>
       </c>
       <c r="V37" s="11">
         <v>11</v>
       </c>
       <c r="W37" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="X37" s="12">
-        <v>0.44583329999999999</v>
+        <v>0.46180559999999998</v>
       </c>
       <c r="Y37" s="10">
         <v>0</v>
@@ -5829,7 +5799,7 @@
         <v>53</v>
       </c>
       <c r="AI37" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AJ37" s="3" t="s">
         <v>52</v>
@@ -5856,275 +5826,7 @@
         <v>53</v>
       </c>
       <c r="AR37" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="38" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
-        <v>1</v>
-      </c>
-      <c r="B38" s="2">
-        <v>2</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F38" s="4">
-        <v>46281</v>
-      </c>
-      <c r="G38" s="5">
-        <v>19</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L38" s="6">
-        <v>20</v>
-      </c>
-      <c r="M38" s="7">
-        <v>6507.4</v>
-      </c>
-      <c r="N38" s="6">
-        <v>1</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="P38" s="8">
-        <v>325.37</v>
-      </c>
-      <c r="Q38" s="6">
-        <v>0</v>
-      </c>
-      <c r="R38" s="7">
-        <v>0</v>
-      </c>
-      <c r="S38" s="9">
-        <v>0</v>
-      </c>
-      <c r="T38" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U38" s="10">
-        <v>67488</v>
-      </c>
-      <c r="V38" s="11">
-        <v>11</v>
-      </c>
-      <c r="W38" s="4">
-        <v>46281</v>
-      </c>
-      <c r="X38" s="12">
-        <v>0.44583329999999999</v>
-      </c>
-      <c r="Y38" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB38" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE38" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG38" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI38" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AJ38" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK38" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL38" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM38" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN38" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO38" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP38" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ38" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR38" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="39" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
-        <v>1</v>
-      </c>
-      <c r="B39" s="2">
-        <v>2</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F39" s="4">
-        <v>46281</v>
-      </c>
-      <c r="G39" s="5">
-        <v>20</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L39" s="6">
-        <v>21</v>
-      </c>
-      <c r="M39" s="7">
-        <v>6832.77</v>
-      </c>
-      <c r="N39" s="6">
-        <v>1</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="P39" s="8">
-        <v>325.37</v>
-      </c>
-      <c r="Q39" s="6">
-        <v>0</v>
-      </c>
-      <c r="R39" s="7">
-        <v>0</v>
-      </c>
-      <c r="S39" s="9">
-        <v>0</v>
-      </c>
-      <c r="T39" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U39" s="10">
-        <v>67488</v>
-      </c>
-      <c r="V39" s="11">
-        <v>11</v>
-      </c>
-      <c r="W39" s="4">
-        <v>46281</v>
-      </c>
-      <c r="X39" s="12">
-        <v>0.4611111</v>
-      </c>
-      <c r="Y39" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF39" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG39" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH39" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI39" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AJ39" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK39" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL39" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM39" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN39" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO39" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP39" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ39" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR39" s="3" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2315FED9-C0A8-43D0-B427-330A9A8AD4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85933B69-2595-4DD7-BAD8-F095038DF865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{286152DB-2E06-401B-8555-01F0897E1C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{588BF4C9-D300-492E-854A-9AD5CF047911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2546" uniqueCount="201">
   <si>
     <t>Sel</t>
   </si>
@@ -445,12 +445,126 @@
     <t>1854300129788</t>
   </si>
   <si>
+    <t>1854300129789</t>
+  </si>
+  <si>
+    <t>1854300129790</t>
+  </si>
+  <si>
+    <t>1854300129791</t>
+  </si>
+  <si>
+    <t>1854300129792</t>
+  </si>
+  <si>
+    <t>1854300129793</t>
+  </si>
+  <si>
+    <t>1854300129794</t>
+  </si>
+  <si>
+    <t>1854300129795</t>
+  </si>
+  <si>
+    <t>1854300129796</t>
+  </si>
+  <si>
+    <t>1854300129797</t>
+  </si>
+  <si>
+    <t>10019364</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>FORNO ELETRICO NARDELLI TOP 70L BLACK - NARDELLI TOP 70L - 220 V</t>
+  </si>
+  <si>
+    <t>1883500000006</t>
+  </si>
+  <si>
+    <t>10059364</t>
+  </si>
+  <si>
+    <t>FORNO ELETRICO FOGATTI TOP 70L BLACK - FOGATTI TOP 70L - 220 V</t>
+  </si>
+  <si>
+    <t>1883700000019</t>
+  </si>
+  <si>
+    <t>1883700000020</t>
+  </si>
+  <si>
+    <t>1883700000021</t>
+  </si>
+  <si>
+    <t>1883700000022</t>
+  </si>
+  <si>
+    <t>1883700000023</t>
+  </si>
+  <si>
+    <t>1883700000024</t>
+  </si>
+  <si>
+    <t>1883700000025</t>
+  </si>
+  <si>
+    <t>1883700000026</t>
+  </si>
+  <si>
+    <t>1883700000027</t>
+  </si>
+  <si>
+    <t>1883700000028</t>
+  </si>
+  <si>
+    <t>1883700000029</t>
+  </si>
+  <si>
+    <t>1883700000030</t>
+  </si>
+  <si>
+    <t>1883700000031</t>
+  </si>
+  <si>
+    <t>1883700000032</t>
+  </si>
+  <si>
+    <t>1883700000033</t>
+  </si>
+  <si>
+    <t>1883700000034</t>
+  </si>
+  <si>
+    <t>1883700000035</t>
+  </si>
+  <si>
+    <t>1883700000036</t>
+  </si>
+  <si>
+    <t>1883700000037</t>
+  </si>
+  <si>
+    <t>1883700000038</t>
+  </si>
+  <si>
+    <t>1883700000039</t>
+  </si>
+  <si>
+    <t>1883700000040</t>
+  </si>
+  <si>
+    <t>1883700000041</t>
+  </si>
+  <si>
+    <t>1883700000042</t>
+  </si>
+  <si>
     <t>10099364</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>FORNO ELETRICO TERIM TOP 70L BLACK - TERIM TOP 70L - 220 V</t>
   </si>
   <si>
@@ -470,6 +584,45 @@
   </si>
   <si>
     <t>1883900000009</t>
+  </si>
+  <si>
+    <t>1883900000010</t>
+  </si>
+  <si>
+    <t>1883900000011</t>
+  </si>
+  <si>
+    <t>1883900000012</t>
+  </si>
+  <si>
+    <t>1883900000013</t>
+  </si>
+  <si>
+    <t>1883900000014</t>
+  </si>
+  <si>
+    <t>1883900000015</t>
+  </si>
+  <si>
+    <t>1883900000016</t>
+  </si>
+  <si>
+    <t>1883900000017</t>
+  </si>
+  <si>
+    <t>1883900000018</t>
+  </si>
+  <si>
+    <t>1883900000019</t>
+  </si>
+  <si>
+    <t>1883900000020</t>
+  </si>
+  <si>
+    <t>1883900000021</t>
+  </si>
+  <si>
+    <t>1883900000022</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR93"/>
+  <dimension ref="A1:AR140"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -12714,10 +12867,10 @@
         <v>2</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>142</v>
+        <v>45</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>46</v>
@@ -12726,7 +12879,7 @@
         <v>46286</v>
       </c>
       <c r="G88" s="5">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>47</v>
@@ -12741,19 +12894,19 @@
         <v>50</v>
       </c>
       <c r="L88" s="6">
-        <v>0</v>
+        <v>3007</v>
       </c>
       <c r="M88" s="7">
-        <v>0</v>
+        <v>550310.56000000006</v>
       </c>
       <c r="N88" s="6">
         <v>1</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="P88" s="8">
-        <v>179.6</v>
+        <v>183.01</v>
       </c>
       <c r="Q88" s="6">
         <v>0</v>
@@ -12768,7 +12921,7 @@
         <v>52</v>
       </c>
       <c r="U88" s="10">
-        <v>67522</v>
+        <v>67498</v>
       </c>
       <c r="V88" s="11">
         <v>11</v>
@@ -12777,7 +12930,7 @@
         <v>46286</v>
       </c>
       <c r="X88" s="12">
-        <v>0.34027780000000002</v>
+        <v>0.35277779999999997</v>
       </c>
       <c r="Y88" s="10">
         <v>0</v>
@@ -12837,7 +12990,7 @@
         <v>53</v>
       </c>
       <c r="AR88" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89" spans="1:44" x14ac:dyDescent="0.3">
@@ -12848,10 +13001,10 @@
         <v>2</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>142</v>
+        <v>45</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>46</v>
@@ -12860,7 +13013,7 @@
         <v>46286</v>
       </c>
       <c r="G89" s="5">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>47</v>
@@ -12875,19 +13028,19 @@
         <v>50</v>
       </c>
       <c r="L89" s="6">
-        <v>1</v>
+        <v>3008</v>
       </c>
       <c r="M89" s="7">
-        <v>179.6</v>
+        <v>550493.56999999995</v>
       </c>
       <c r="N89" s="6">
         <v>1</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="P89" s="8">
-        <v>179.6</v>
+        <v>183.01</v>
       </c>
       <c r="Q89" s="6">
         <v>0</v>
@@ -12902,7 +13055,7 @@
         <v>52</v>
       </c>
       <c r="U89" s="10">
-        <v>67522</v>
+        <v>67498</v>
       </c>
       <c r="V89" s="11">
         <v>11</v>
@@ -12911,7 +13064,7 @@
         <v>46286</v>
       </c>
       <c r="X89" s="12">
-        <v>0.34027780000000002</v>
+        <v>0.35277779999999997</v>
       </c>
       <c r="Y89" s="10">
         <v>0</v>
@@ -12971,7 +13124,7 @@
         <v>53</v>
       </c>
       <c r="AR89" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="90" spans="1:44" x14ac:dyDescent="0.3">
@@ -12982,10 +13135,10 @@
         <v>2</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>142</v>
+        <v>45</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>46</v>
@@ -12994,7 +13147,7 @@
         <v>46286</v>
       </c>
       <c r="G90" s="5">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>47</v>
@@ -13009,19 +13162,19 @@
         <v>50</v>
       </c>
       <c r="L90" s="6">
-        <v>2</v>
+        <v>3009</v>
       </c>
       <c r="M90" s="7">
-        <v>359.2</v>
+        <v>550676.57999999996</v>
       </c>
       <c r="N90" s="6">
         <v>1</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="P90" s="8">
-        <v>179.6</v>
+        <v>183.01</v>
       </c>
       <c r="Q90" s="6">
         <v>0</v>
@@ -13036,7 +13189,7 @@
         <v>52</v>
       </c>
       <c r="U90" s="10">
-        <v>67522</v>
+        <v>67498</v>
       </c>
       <c r="V90" s="11">
         <v>11</v>
@@ -13045,7 +13198,7 @@
         <v>46286</v>
       </c>
       <c r="X90" s="12">
-        <v>0.34027780000000002</v>
+        <v>0.35277779999999997</v>
       </c>
       <c r="Y90" s="10">
         <v>0</v>
@@ -13105,7 +13258,7 @@
         <v>53</v>
       </c>
       <c r="AR90" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="91" spans="1:44" x14ac:dyDescent="0.3">
@@ -13116,10 +13269,10 @@
         <v>2</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>142</v>
+        <v>45</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>46</v>
@@ -13128,7 +13281,7 @@
         <v>46286</v>
       </c>
       <c r="G91" s="5">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>47</v>
@@ -13143,19 +13296,19 @@
         <v>50</v>
       </c>
       <c r="L91" s="6">
-        <v>3</v>
+        <v>3010</v>
       </c>
       <c r="M91" s="7">
-        <v>538.79999999999995</v>
+        <v>550859.59</v>
       </c>
       <c r="N91" s="6">
         <v>1</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="P91" s="8">
-        <v>179.6</v>
+        <v>183.01</v>
       </c>
       <c r="Q91" s="6">
         <v>0</v>
@@ -13170,7 +13323,7 @@
         <v>52</v>
       </c>
       <c r="U91" s="10">
-        <v>67522</v>
+        <v>67498</v>
       </c>
       <c r="V91" s="11">
         <v>11</v>
@@ -13179,7 +13332,7 @@
         <v>46286</v>
       </c>
       <c r="X91" s="12">
-        <v>0.34027780000000002</v>
+        <v>0.35277779999999997</v>
       </c>
       <c r="Y91" s="10">
         <v>0</v>
@@ -13239,7 +13392,7 @@
         <v>53</v>
       </c>
       <c r="AR91" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="92" spans="1:44" x14ac:dyDescent="0.3">
@@ -13250,10 +13403,10 @@
         <v>2</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>142</v>
+        <v>45</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>46</v>
@@ -13262,7 +13415,7 @@
         <v>46286</v>
       </c>
       <c r="G92" s="5">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>47</v>
@@ -13277,19 +13430,19 @@
         <v>50</v>
       </c>
       <c r="L92" s="6">
-        <v>4</v>
+        <v>3011</v>
       </c>
       <c r="M92" s="7">
-        <v>718.4</v>
+        <v>551042.6</v>
       </c>
       <c r="N92" s="6">
         <v>1</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="P92" s="8">
-        <v>179.6</v>
+        <v>183.01</v>
       </c>
       <c r="Q92" s="6">
         <v>0</v>
@@ -13304,7 +13457,7 @@
         <v>52</v>
       </c>
       <c r="U92" s="10">
-        <v>67522</v>
+        <v>67498</v>
       </c>
       <c r="V92" s="11">
         <v>11</v>
@@ -13313,7 +13466,7 @@
         <v>46286</v>
       </c>
       <c r="X92" s="12">
-        <v>0.34027780000000002</v>
+        <v>0.35277779999999997</v>
       </c>
       <c r="Y92" s="10">
         <v>0</v>
@@ -13373,7 +13526,7 @@
         <v>53</v>
       </c>
       <c r="AR92" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="93" spans="1:44" x14ac:dyDescent="0.3">
@@ -13384,10 +13537,10 @@
         <v>2</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>142</v>
+        <v>45</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>46</v>
@@ -13396,7 +13549,7 @@
         <v>46286</v>
       </c>
       <c r="G93" s="5">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>47</v>
@@ -13411,19 +13564,19 @@
         <v>50</v>
       </c>
       <c r="L93" s="6">
-        <v>5</v>
+        <v>3012</v>
       </c>
       <c r="M93" s="7">
-        <v>898</v>
+        <v>551225.61</v>
       </c>
       <c r="N93" s="6">
         <v>1</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="P93" s="8">
-        <v>179.6</v>
+        <v>183.01</v>
       </c>
       <c r="Q93" s="6">
         <v>0</v>
@@ -13438,7 +13591,7 @@
         <v>52</v>
       </c>
       <c r="U93" s="10">
-        <v>67522</v>
+        <v>67498</v>
       </c>
       <c r="V93" s="11">
         <v>11</v>
@@ -13447,7 +13600,7 @@
         <v>46286</v>
       </c>
       <c r="X93" s="12">
-        <v>0.34027780000000002</v>
+        <v>0.35277779999999997</v>
       </c>
       <c r="Y93" s="10">
         <v>0</v>
@@ -13507,7 +13660,6305 @@
         <v>53</v>
       </c>
       <c r="AR93" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="94" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>1</v>
+      </c>
+      <c r="B94" s="2">
+        <v>2</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F94" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G94" s="5">
+        <v>95</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L94" s="6">
+        <v>3013</v>
+      </c>
+      <c r="M94" s="7">
+        <v>551408.62</v>
+      </c>
+      <c r="N94" s="6">
+        <v>1</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P94" s="8">
+        <v>183.01</v>
+      </c>
+      <c r="Q94" s="6">
+        <v>0</v>
+      </c>
+      <c r="R94" s="7">
+        <v>0</v>
+      </c>
+      <c r="S94" s="9">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U94" s="10">
+        <v>67498</v>
+      </c>
+      <c r="V94" s="11">
+        <v>11</v>
+      </c>
+      <c r="W94" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X94" s="12">
+        <v>0.35277779999999997</v>
+      </c>
+      <c r="Y94" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG94" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI94" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ94" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK94" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM94" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR94" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="95" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>1</v>
+      </c>
+      <c r="B95" s="2">
+        <v>2</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F95" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G95" s="5">
+        <v>96</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L95" s="6">
+        <v>3014</v>
+      </c>
+      <c r="M95" s="7">
+        <v>551591.63</v>
+      </c>
+      <c r="N95" s="6">
+        <v>1</v>
+      </c>
+      <c r="O95" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P95" s="8">
+        <v>183.01</v>
+      </c>
+      <c r="Q95" s="6">
+        <v>0</v>
+      </c>
+      <c r="R95" s="7">
+        <v>0</v>
+      </c>
+      <c r="S95" s="9">
+        <v>0</v>
+      </c>
+      <c r="T95" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U95" s="10">
+        <v>67498</v>
+      </c>
+      <c r="V95" s="11">
+        <v>11</v>
+      </c>
+      <c r="W95" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X95" s="12">
+        <v>0.35277779999999997</v>
+      </c>
+      <c r="Y95" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB95" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG95" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI95" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ95" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK95" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM95" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR95" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="96" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>1</v>
+      </c>
+      <c r="B96" s="2">
+        <v>2</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F96" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G96" s="5">
+        <v>97</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L96" s="6">
+        <v>3015</v>
+      </c>
+      <c r="M96" s="7">
+        <v>551774.64</v>
+      </c>
+      <c r="N96" s="6">
+        <v>1</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P96" s="8">
+        <v>183.01</v>
+      </c>
+      <c r="Q96" s="6">
+        <v>0</v>
+      </c>
+      <c r="R96" s="7">
+        <v>0</v>
+      </c>
+      <c r="S96" s="9">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U96" s="10">
+        <v>67498</v>
+      </c>
+      <c r="V96" s="11">
+        <v>11</v>
+      </c>
+      <c r="W96" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X96" s="12">
+        <v>0.35277779999999997</v>
+      </c>
+      <c r="Y96" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG96" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI96" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ96" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK96" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR96" s="3" t="s">
         <v>149</v>
+      </c>
+    </row>
+    <row r="97" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>1</v>
+      </c>
+      <c r="B97" s="2">
+        <v>2</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F97" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G97" s="5">
+        <v>1</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L97" s="6">
+        <v>0</v>
+      </c>
+      <c r="M97" s="7">
+        <v>0</v>
+      </c>
+      <c r="N97" s="6">
+        <v>1</v>
+      </c>
+      <c r="O97" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="P97" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q97" s="6">
+        <v>0</v>
+      </c>
+      <c r="R97" s="7">
+        <v>0</v>
+      </c>
+      <c r="S97" s="9">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U97" s="10">
+        <v>67512</v>
+      </c>
+      <c r="V97" s="11">
+        <v>11</v>
+      </c>
+      <c r="W97" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X97" s="12">
+        <v>0.46458329999999998</v>
+      </c>
+      <c r="Y97" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG97" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI97" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ97" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK97" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR97" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="98" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>1</v>
+      </c>
+      <c r="B98" s="2">
+        <v>2</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F98" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G98" s="5">
+        <v>1</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L98" s="6">
+        <v>0</v>
+      </c>
+      <c r="M98" s="7">
+        <v>0</v>
+      </c>
+      <c r="N98" s="6">
+        <v>1</v>
+      </c>
+      <c r="O98" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P98" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q98" s="6">
+        <v>0</v>
+      </c>
+      <c r="R98" s="7">
+        <v>0</v>
+      </c>
+      <c r="S98" s="9">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U98" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V98" s="11">
+        <v>11</v>
+      </c>
+      <c r="W98" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X98" s="12">
+        <v>0.42291669999999998</v>
+      </c>
+      <c r="Y98" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG98" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI98" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ98" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK98" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR98" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="99" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>1</v>
+      </c>
+      <c r="B99" s="2">
+        <v>2</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F99" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G99" s="5">
+        <v>2</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L99" s="6">
+        <v>1</v>
+      </c>
+      <c r="M99" s="7">
+        <v>179.6</v>
+      </c>
+      <c r="N99" s="6">
+        <v>1</v>
+      </c>
+      <c r="O99" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P99" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q99" s="6">
+        <v>0</v>
+      </c>
+      <c r="R99" s="7">
+        <v>0</v>
+      </c>
+      <c r="S99" s="9">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U99" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V99" s="11">
+        <v>11</v>
+      </c>
+      <c r="W99" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X99" s="12">
+        <v>0.42291669999999998</v>
+      </c>
+      <c r="Y99" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG99" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI99" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ99" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK99" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR99" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="100" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>1</v>
+      </c>
+      <c r="B100" s="2">
+        <v>2</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F100" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G100" s="5">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L100" s="6">
+        <v>2</v>
+      </c>
+      <c r="M100" s="7">
+        <v>359.2</v>
+      </c>
+      <c r="N100" s="6">
+        <v>1</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P100" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q100" s="6">
+        <v>0</v>
+      </c>
+      <c r="R100" s="7">
+        <v>0</v>
+      </c>
+      <c r="S100" s="9">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U100" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V100" s="11">
+        <v>11</v>
+      </c>
+      <c r="W100" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X100" s="12">
+        <v>0.42291669999999998</v>
+      </c>
+      <c r="Y100" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG100" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI100" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ100" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK100" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM100" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR100" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="101" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>1</v>
+      </c>
+      <c r="B101" s="2">
+        <v>2</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F101" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G101" s="5">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L101" s="6">
+        <v>3</v>
+      </c>
+      <c r="M101" s="7">
+        <v>538.79999999999995</v>
+      </c>
+      <c r="N101" s="6">
+        <v>1</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P101" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q101" s="6">
+        <v>0</v>
+      </c>
+      <c r="R101" s="7">
+        <v>0</v>
+      </c>
+      <c r="S101" s="9">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U101" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V101" s="11">
+        <v>11</v>
+      </c>
+      <c r="W101" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X101" s="12">
+        <v>0.42291669999999998</v>
+      </c>
+      <c r="Y101" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG101" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI101" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ101" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK101" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO101" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP101" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ101" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR101" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="102" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>1</v>
+      </c>
+      <c r="B102" s="2">
+        <v>2</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F102" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G102" s="5">
+        <v>5</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L102" s="6">
+        <v>4</v>
+      </c>
+      <c r="M102" s="7">
+        <v>718.4</v>
+      </c>
+      <c r="N102" s="6">
+        <v>1</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P102" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>0</v>
+      </c>
+      <c r="R102" s="7">
+        <v>0</v>
+      </c>
+      <c r="S102" s="9">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U102" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V102" s="11">
+        <v>11</v>
+      </c>
+      <c r="W102" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X102" s="12">
+        <v>0.42291669999999998</v>
+      </c>
+      <c r="Y102" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI102" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK102" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO102" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP102" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ102" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR102" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="103" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>1</v>
+      </c>
+      <c r="B103" s="2">
+        <v>2</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F103" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G103" s="5">
+        <v>6</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J103" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K103" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L103" s="6">
+        <v>5</v>
+      </c>
+      <c r="M103" s="7">
+        <v>898</v>
+      </c>
+      <c r="N103" s="6">
+        <v>1</v>
+      </c>
+      <c r="O103" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P103" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q103" s="6">
+        <v>0</v>
+      </c>
+      <c r="R103" s="7">
+        <v>0</v>
+      </c>
+      <c r="S103" s="9">
+        <v>0</v>
+      </c>
+      <c r="T103" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U103" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V103" s="11">
+        <v>11</v>
+      </c>
+      <c r="W103" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X103" s="12">
+        <v>0.42291669999999998</v>
+      </c>
+      <c r="Y103" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z103" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA103" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB103" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC103" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD103" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF103" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG103" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH103" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI103" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ103" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK103" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL103" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM103" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN103" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO103" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP103" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ103" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR103" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="104" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>1</v>
+      </c>
+      <c r="B104" s="2">
+        <v>2</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F104" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G104" s="5">
+        <v>7</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K104" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L104" s="6">
+        <v>6</v>
+      </c>
+      <c r="M104" s="7">
+        <v>1077.5999999999999</v>
+      </c>
+      <c r="N104" s="6">
+        <v>1</v>
+      </c>
+      <c r="O104" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P104" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q104" s="6">
+        <v>0</v>
+      </c>
+      <c r="R104" s="7">
+        <v>0</v>
+      </c>
+      <c r="S104" s="9">
+        <v>0</v>
+      </c>
+      <c r="T104" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U104" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V104" s="11">
+        <v>11</v>
+      </c>
+      <c r="W104" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X104" s="12">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="Y104" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z104" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA104" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB104" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC104" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD104" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE104" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF104" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG104" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH104" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI104" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ104" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK104" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL104" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM104" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN104" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO104" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP104" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ104" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR104" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="105" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>1</v>
+      </c>
+      <c r="B105" s="2">
+        <v>2</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F105" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G105" s="5">
+        <v>8</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J105" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K105" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L105" s="6">
+        <v>7</v>
+      </c>
+      <c r="M105" s="7">
+        <v>1257.2</v>
+      </c>
+      <c r="N105" s="6">
+        <v>1</v>
+      </c>
+      <c r="O105" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P105" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q105" s="6">
+        <v>0</v>
+      </c>
+      <c r="R105" s="7">
+        <v>0</v>
+      </c>
+      <c r="S105" s="9">
+        <v>0</v>
+      </c>
+      <c r="T105" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U105" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V105" s="11">
+        <v>11</v>
+      </c>
+      <c r="W105" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X105" s="12">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="Y105" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z105" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA105" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB105" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC105" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD105" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE105" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF105" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG105" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH105" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI105" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ105" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK105" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL105" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM105" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN105" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO105" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP105" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ105" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR105" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="106" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>1</v>
+      </c>
+      <c r="B106" s="2">
+        <v>2</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F106" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G106" s="5">
+        <v>9</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J106" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K106" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L106" s="6">
+        <v>8</v>
+      </c>
+      <c r="M106" s="7">
+        <v>1436.8</v>
+      </c>
+      <c r="N106" s="6">
+        <v>1</v>
+      </c>
+      <c r="O106" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P106" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q106" s="6">
+        <v>0</v>
+      </c>
+      <c r="R106" s="7">
+        <v>0</v>
+      </c>
+      <c r="S106" s="9">
+        <v>0</v>
+      </c>
+      <c r="T106" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U106" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V106" s="11">
+        <v>11</v>
+      </c>
+      <c r="W106" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X106" s="12">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="Y106" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z106" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA106" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB106" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC106" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD106" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE106" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF106" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG106" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH106" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI106" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ106" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK106" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL106" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM106" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN106" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO106" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP106" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ106" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR106" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="107" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>1</v>
+      </c>
+      <c r="B107" s="2">
+        <v>2</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F107" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G107" s="5">
+        <v>10</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J107" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K107" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L107" s="6">
+        <v>9</v>
+      </c>
+      <c r="M107" s="7">
+        <v>1616.4</v>
+      </c>
+      <c r="N107" s="6">
+        <v>1</v>
+      </c>
+      <c r="O107" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P107" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q107" s="6">
+        <v>0</v>
+      </c>
+      <c r="R107" s="7">
+        <v>0</v>
+      </c>
+      <c r="S107" s="9">
+        <v>0</v>
+      </c>
+      <c r="T107" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U107" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V107" s="11">
+        <v>11</v>
+      </c>
+      <c r="W107" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X107" s="12">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="Y107" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB107" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC107" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD107" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE107" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF107" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG107" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH107" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI107" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ107" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK107" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL107" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM107" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN107" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO107" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP107" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ107" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR107" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="108" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>1</v>
+      </c>
+      <c r="B108" s="2">
+        <v>2</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F108" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G108" s="5">
+        <v>11</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J108" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K108" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L108" s="6">
+        <v>10</v>
+      </c>
+      <c r="M108" s="7">
+        <v>1796</v>
+      </c>
+      <c r="N108" s="6">
+        <v>1</v>
+      </c>
+      <c r="O108" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P108" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q108" s="6">
+        <v>0</v>
+      </c>
+      <c r="R108" s="7">
+        <v>0</v>
+      </c>
+      <c r="S108" s="9">
+        <v>0</v>
+      </c>
+      <c r="T108" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U108" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V108" s="11">
+        <v>11</v>
+      </c>
+      <c r="W108" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X108" s="12">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="Y108" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z108" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA108" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB108" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC108" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD108" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE108" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF108" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG108" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH108" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI108" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ108" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK108" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL108" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM108" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN108" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO108" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP108" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ108" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR108" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="109" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>1</v>
+      </c>
+      <c r="B109" s="2">
+        <v>2</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F109" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G109" s="5">
+        <v>12</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J109" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K109" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L109" s="6">
+        <v>11</v>
+      </c>
+      <c r="M109" s="7">
+        <v>1975.6</v>
+      </c>
+      <c r="N109" s="6">
+        <v>1</v>
+      </c>
+      <c r="O109" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P109" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q109" s="6">
+        <v>0</v>
+      </c>
+      <c r="R109" s="7">
+        <v>0</v>
+      </c>
+      <c r="S109" s="9">
+        <v>0</v>
+      </c>
+      <c r="T109" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U109" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V109" s="11">
+        <v>11</v>
+      </c>
+      <c r="W109" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X109" s="12">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="Y109" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB109" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC109" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD109" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE109" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF109" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG109" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH109" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI109" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ109" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK109" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL109" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM109" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN109" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO109" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP109" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ109" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR109" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="110" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>1</v>
+      </c>
+      <c r="B110" s="2">
+        <v>2</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F110" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G110" s="5">
+        <v>13</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K110" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L110" s="6">
+        <v>12</v>
+      </c>
+      <c r="M110" s="7">
+        <v>2155.1999999999998</v>
+      </c>
+      <c r="N110" s="6">
+        <v>1</v>
+      </c>
+      <c r="O110" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P110" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q110" s="6">
+        <v>0</v>
+      </c>
+      <c r="R110" s="7">
+        <v>0</v>
+      </c>
+      <c r="S110" s="9">
+        <v>0</v>
+      </c>
+      <c r="T110" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U110" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V110" s="11">
+        <v>11</v>
+      </c>
+      <c r="W110" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X110" s="12">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="Y110" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z110" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA110" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB110" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC110" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD110" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE110" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF110" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG110" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH110" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI110" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ110" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK110" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL110" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM110" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN110" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO110" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP110" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ110" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR110" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="111" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>1</v>
+      </c>
+      <c r="B111" s="2">
+        <v>2</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F111" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G111" s="5">
+        <v>14</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J111" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K111" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L111" s="6">
+        <v>13</v>
+      </c>
+      <c r="M111" s="7">
+        <v>2334.8000000000002</v>
+      </c>
+      <c r="N111" s="6">
+        <v>1</v>
+      </c>
+      <c r="O111" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P111" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q111" s="6">
+        <v>0</v>
+      </c>
+      <c r="R111" s="7">
+        <v>0</v>
+      </c>
+      <c r="S111" s="9">
+        <v>0</v>
+      </c>
+      <c r="T111" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U111" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V111" s="11">
+        <v>11</v>
+      </c>
+      <c r="W111" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X111" s="12">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="Y111" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG111" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH111" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI111" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ111" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK111" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL111" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM111" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN111" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO111" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP111" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ111" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR111" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="112" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>1</v>
+      </c>
+      <c r="B112" s="2">
+        <v>2</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F112" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G112" s="5">
+        <v>15</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J112" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K112" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L112" s="6">
+        <v>14</v>
+      </c>
+      <c r="M112" s="7">
+        <v>2514.4</v>
+      </c>
+      <c r="N112" s="6">
+        <v>1</v>
+      </c>
+      <c r="O112" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P112" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q112" s="6">
+        <v>0</v>
+      </c>
+      <c r="R112" s="7">
+        <v>0</v>
+      </c>
+      <c r="S112" s="9">
+        <v>0</v>
+      </c>
+      <c r="T112" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U112" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V112" s="11">
+        <v>11</v>
+      </c>
+      <c r="W112" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X112" s="12">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="Y112" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z112" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA112" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB112" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC112" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD112" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE112" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF112" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG112" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH112" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI112" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ112" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK112" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL112" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM112" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN112" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO112" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP112" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ112" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR112" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="113" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>1</v>
+      </c>
+      <c r="B113" s="2">
+        <v>2</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F113" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G113" s="5">
+        <v>16</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J113" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K113" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L113" s="6">
+        <v>15</v>
+      </c>
+      <c r="M113" s="7">
+        <v>2694</v>
+      </c>
+      <c r="N113" s="6">
+        <v>1</v>
+      </c>
+      <c r="O113" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P113" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q113" s="6">
+        <v>0</v>
+      </c>
+      <c r="R113" s="7">
+        <v>0</v>
+      </c>
+      <c r="S113" s="9">
+        <v>0</v>
+      </c>
+      <c r="T113" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U113" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V113" s="11">
+        <v>11</v>
+      </c>
+      <c r="W113" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X113" s="12">
+        <v>0.46527780000000002</v>
+      </c>
+      <c r="Y113" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z113" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA113" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB113" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC113" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD113" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE113" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF113" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG113" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH113" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI113" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ113" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK113" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL113" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM113" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN113" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO113" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP113" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ113" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR113" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="114" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>1</v>
+      </c>
+      <c r="B114" s="2">
+        <v>2</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F114" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G114" s="5">
+        <v>17</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K114" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L114" s="6">
+        <v>16</v>
+      </c>
+      <c r="M114" s="7">
+        <v>2873.6</v>
+      </c>
+      <c r="N114" s="6">
+        <v>1</v>
+      </c>
+      <c r="O114" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P114" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q114" s="6">
+        <v>0</v>
+      </c>
+      <c r="R114" s="7">
+        <v>0</v>
+      </c>
+      <c r="S114" s="9">
+        <v>0</v>
+      </c>
+      <c r="T114" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U114" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V114" s="11">
+        <v>11</v>
+      </c>
+      <c r="W114" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X114" s="12">
+        <v>0.46527780000000002</v>
+      </c>
+      <c r="Y114" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA114" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB114" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC114" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD114" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE114" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF114" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG114" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH114" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI114" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ114" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK114" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL114" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM114" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN114" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO114" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP114" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ114" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR114" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="115" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>1</v>
+      </c>
+      <c r="B115" s="2">
+        <v>2</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F115" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G115" s="5">
+        <v>18</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J115" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K115" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L115" s="6">
+        <v>17</v>
+      </c>
+      <c r="M115" s="7">
+        <v>3053.2</v>
+      </c>
+      <c r="N115" s="6">
+        <v>1</v>
+      </c>
+      <c r="O115" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P115" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q115" s="6">
+        <v>0</v>
+      </c>
+      <c r="R115" s="7">
+        <v>0</v>
+      </c>
+      <c r="S115" s="9">
+        <v>0</v>
+      </c>
+      <c r="T115" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U115" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V115" s="11">
+        <v>11</v>
+      </c>
+      <c r="W115" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X115" s="12">
+        <v>0.46527780000000002</v>
+      </c>
+      <c r="Y115" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z115" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA115" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB115" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC115" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD115" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE115" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF115" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG115" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH115" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI115" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ115" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK115" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL115" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM115" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN115" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO115" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP115" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ115" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR115" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="116" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>1</v>
+      </c>
+      <c r="B116" s="2">
+        <v>2</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F116" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G116" s="5">
+        <v>19</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J116" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K116" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L116" s="6">
+        <v>18</v>
+      </c>
+      <c r="M116" s="7">
+        <v>3232.8</v>
+      </c>
+      <c r="N116" s="6">
+        <v>1</v>
+      </c>
+      <c r="O116" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P116" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q116" s="6">
+        <v>0</v>
+      </c>
+      <c r="R116" s="7">
+        <v>0</v>
+      </c>
+      <c r="S116" s="9">
+        <v>0</v>
+      </c>
+      <c r="T116" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U116" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V116" s="11">
+        <v>11</v>
+      </c>
+      <c r="W116" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X116" s="12">
+        <v>0.46527780000000002</v>
+      </c>
+      <c r="Y116" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB116" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE116" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF116" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG116" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI116" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ116" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK116" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL116" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM116" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN116" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO116" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP116" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ116" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR116" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="117" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>1</v>
+      </c>
+      <c r="B117" s="2">
+        <v>2</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F117" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G117" s="5">
+        <v>20</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J117" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K117" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L117" s="6">
+        <v>19</v>
+      </c>
+      <c r="M117" s="7">
+        <v>3412.4</v>
+      </c>
+      <c r="N117" s="6">
+        <v>1</v>
+      </c>
+      <c r="O117" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P117" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q117" s="6">
+        <v>0</v>
+      </c>
+      <c r="R117" s="7">
+        <v>0</v>
+      </c>
+      <c r="S117" s="9">
+        <v>0</v>
+      </c>
+      <c r="T117" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U117" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V117" s="11">
+        <v>11</v>
+      </c>
+      <c r="W117" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X117" s="12">
+        <v>0.46527780000000002</v>
+      </c>
+      <c r="Y117" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z117" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA117" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB117" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC117" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD117" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE117" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF117" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG117" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH117" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI117" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ117" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK117" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL117" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM117" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN117" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO117" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP117" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ117" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR117" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="118" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>1</v>
+      </c>
+      <c r="B118" s="2">
+        <v>2</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F118" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G118" s="5">
+        <v>21</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J118" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K118" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L118" s="6">
+        <v>20</v>
+      </c>
+      <c r="M118" s="7">
+        <v>3592</v>
+      </c>
+      <c r="N118" s="6">
+        <v>1</v>
+      </c>
+      <c r="O118" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P118" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q118" s="6">
+        <v>0</v>
+      </c>
+      <c r="R118" s="7">
+        <v>0</v>
+      </c>
+      <c r="S118" s="9">
+        <v>0</v>
+      </c>
+      <c r="T118" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U118" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V118" s="11">
+        <v>11</v>
+      </c>
+      <c r="W118" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X118" s="12">
+        <v>0.46527780000000002</v>
+      </c>
+      <c r="Y118" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z118" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA118" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB118" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC118" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD118" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE118" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF118" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG118" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH118" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI118" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ118" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK118" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL118" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM118" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN118" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO118" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP118" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ118" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR118" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="119" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>1</v>
+      </c>
+      <c r="B119" s="2">
+        <v>2</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F119" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G119" s="5">
+        <v>22</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J119" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K119" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L119" s="6">
+        <v>21</v>
+      </c>
+      <c r="M119" s="7">
+        <v>3771.6</v>
+      </c>
+      <c r="N119" s="6">
+        <v>1</v>
+      </c>
+      <c r="O119" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P119" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q119" s="6">
+        <v>0</v>
+      </c>
+      <c r="R119" s="7">
+        <v>0</v>
+      </c>
+      <c r="S119" s="9">
+        <v>0</v>
+      </c>
+      <c r="T119" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U119" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V119" s="11">
+        <v>11</v>
+      </c>
+      <c r="W119" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X119" s="12">
+        <v>0.46527780000000002</v>
+      </c>
+      <c r="Y119" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z119" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA119" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB119" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC119" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD119" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE119" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF119" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG119" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH119" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI119" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ119" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK119" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL119" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM119" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN119" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO119" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP119" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ119" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR119" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="120" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>1</v>
+      </c>
+      <c r="B120" s="2">
+        <v>2</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F120" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G120" s="5">
+        <v>23</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J120" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K120" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L120" s="6">
+        <v>22</v>
+      </c>
+      <c r="M120" s="7">
+        <v>3951.2</v>
+      </c>
+      <c r="N120" s="6">
+        <v>1</v>
+      </c>
+      <c r="O120" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P120" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q120" s="6">
+        <v>0</v>
+      </c>
+      <c r="R120" s="7">
+        <v>0</v>
+      </c>
+      <c r="S120" s="9">
+        <v>0</v>
+      </c>
+      <c r="T120" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U120" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V120" s="11">
+        <v>11</v>
+      </c>
+      <c r="W120" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X120" s="12">
+        <v>0.46527780000000002</v>
+      </c>
+      <c r="Y120" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z120" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA120" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB120" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC120" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD120" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE120" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF120" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG120" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH120" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI120" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ120" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK120" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL120" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM120" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN120" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO120" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP120" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ120" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR120" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="121" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>1</v>
+      </c>
+      <c r="B121" s="2">
+        <v>2</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F121" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G121" s="5">
+        <v>24</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J121" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K121" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L121" s="6">
+        <v>23</v>
+      </c>
+      <c r="M121" s="7">
+        <v>4130.8</v>
+      </c>
+      <c r="N121" s="6">
+        <v>1</v>
+      </c>
+      <c r="O121" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P121" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q121" s="6">
+        <v>0</v>
+      </c>
+      <c r="R121" s="7">
+        <v>0</v>
+      </c>
+      <c r="S121" s="9">
+        <v>0</v>
+      </c>
+      <c r="T121" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U121" s="10">
+        <v>67517</v>
+      </c>
+      <c r="V121" s="11">
+        <v>11</v>
+      </c>
+      <c r="W121" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X121" s="12">
+        <v>0.46527780000000002</v>
+      </c>
+      <c r="Y121" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z121" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA121" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB121" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC121" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD121" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE121" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF121" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG121" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH121" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI121" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ121" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK121" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL121" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM121" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN121" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO121" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP121" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ121" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR121" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="122" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>1</v>
+      </c>
+      <c r="B122" s="2">
+        <v>2</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F122" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G122" s="5">
+        <v>7</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J122" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K122" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L122" s="6">
+        <v>0</v>
+      </c>
+      <c r="M122" s="7">
+        <v>0</v>
+      </c>
+      <c r="N122" s="6">
+        <v>1</v>
+      </c>
+      <c r="O122" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P122" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q122" s="6">
+        <v>0</v>
+      </c>
+      <c r="R122" s="7">
+        <v>0</v>
+      </c>
+      <c r="S122" s="9">
+        <v>0</v>
+      </c>
+      <c r="T122" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U122" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V122" s="11">
+        <v>11</v>
+      </c>
+      <c r="W122" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X122" s="12">
+        <v>0.34027780000000002</v>
+      </c>
+      <c r="Y122" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z122" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA122" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB122" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC122" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD122" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE122" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF122" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG122" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH122" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI122" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ122" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK122" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL122" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM122" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN122" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO122" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP122" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ122" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR122" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="123" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>1</v>
+      </c>
+      <c r="B123" s="2">
+        <v>2</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F123" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G123" s="5">
+        <v>8</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J123" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K123" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L123" s="6">
+        <v>1</v>
+      </c>
+      <c r="M123" s="7">
+        <v>179.6</v>
+      </c>
+      <c r="N123" s="6">
+        <v>1</v>
+      </c>
+      <c r="O123" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P123" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q123" s="6">
+        <v>0</v>
+      </c>
+      <c r="R123" s="7">
+        <v>0</v>
+      </c>
+      <c r="S123" s="9">
+        <v>0</v>
+      </c>
+      <c r="T123" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U123" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V123" s="11">
+        <v>11</v>
+      </c>
+      <c r="W123" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X123" s="12">
+        <v>0.34027780000000002</v>
+      </c>
+      <c r="Y123" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z123" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA123" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB123" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC123" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD123" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE123" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF123" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG123" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH123" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI123" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ123" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK123" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL123" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM123" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN123" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO123" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP123" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ123" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR123" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="124" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>1</v>
+      </c>
+      <c r="B124" s="2">
+        <v>2</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F124" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G124" s="5">
+        <v>9</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K124" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L124" s="6">
+        <v>2</v>
+      </c>
+      <c r="M124" s="7">
+        <v>359.2</v>
+      </c>
+      <c r="N124" s="6">
+        <v>1</v>
+      </c>
+      <c r="O124" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P124" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q124" s="6">
+        <v>0</v>
+      </c>
+      <c r="R124" s="7">
+        <v>0</v>
+      </c>
+      <c r="S124" s="9">
+        <v>0</v>
+      </c>
+      <c r="T124" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U124" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V124" s="11">
+        <v>11</v>
+      </c>
+      <c r="W124" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X124" s="12">
+        <v>0.34027780000000002</v>
+      </c>
+      <c r="Y124" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z124" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA124" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB124" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC124" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD124" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE124" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF124" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG124" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH124" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI124" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ124" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK124" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL124" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM124" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN124" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO124" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP124" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ124" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR124" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="125" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>1</v>
+      </c>
+      <c r="B125" s="2">
+        <v>2</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F125" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G125" s="5">
+        <v>10</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J125" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K125" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L125" s="6">
+        <v>3</v>
+      </c>
+      <c r="M125" s="7">
+        <v>538.79999999999995</v>
+      </c>
+      <c r="N125" s="6">
+        <v>1</v>
+      </c>
+      <c r="O125" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P125" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q125" s="6">
+        <v>0</v>
+      </c>
+      <c r="R125" s="7">
+        <v>0</v>
+      </c>
+      <c r="S125" s="9">
+        <v>0</v>
+      </c>
+      <c r="T125" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U125" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V125" s="11">
+        <v>11</v>
+      </c>
+      <c r="W125" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X125" s="12">
+        <v>0.34027780000000002</v>
+      </c>
+      <c r="Y125" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z125" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA125" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB125" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC125" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD125" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE125" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF125" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG125" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH125" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI125" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ125" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK125" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL125" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM125" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN125" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO125" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP125" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ125" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR125" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="126" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>1</v>
+      </c>
+      <c r="B126" s="2">
+        <v>2</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F126" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G126" s="5">
+        <v>11</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J126" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K126" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L126" s="6">
+        <v>4</v>
+      </c>
+      <c r="M126" s="7">
+        <v>718.4</v>
+      </c>
+      <c r="N126" s="6">
+        <v>1</v>
+      </c>
+      <c r="O126" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P126" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q126" s="6">
+        <v>0</v>
+      </c>
+      <c r="R126" s="7">
+        <v>0</v>
+      </c>
+      <c r="S126" s="9">
+        <v>0</v>
+      </c>
+      <c r="T126" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U126" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V126" s="11">
+        <v>11</v>
+      </c>
+      <c r="W126" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X126" s="12">
+        <v>0.34027780000000002</v>
+      </c>
+      <c r="Y126" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z126" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA126" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB126" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC126" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD126" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE126" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF126" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG126" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH126" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI126" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ126" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK126" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL126" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM126" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN126" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO126" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP126" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ126" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR126" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="127" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>1</v>
+      </c>
+      <c r="B127" s="2">
+        <v>2</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F127" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G127" s="5">
+        <v>12</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J127" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K127" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L127" s="6">
+        <v>5</v>
+      </c>
+      <c r="M127" s="7">
+        <v>898</v>
+      </c>
+      <c r="N127" s="6">
+        <v>1</v>
+      </c>
+      <c r="O127" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P127" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q127" s="6">
+        <v>0</v>
+      </c>
+      <c r="R127" s="7">
+        <v>0</v>
+      </c>
+      <c r="S127" s="9">
+        <v>0</v>
+      </c>
+      <c r="T127" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U127" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V127" s="11">
+        <v>11</v>
+      </c>
+      <c r="W127" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X127" s="12">
+        <v>0.34027780000000002</v>
+      </c>
+      <c r="Y127" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z127" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA127" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB127" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC127" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD127" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE127" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF127" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG127" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH127" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI127" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ127" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK127" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL127" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM127" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN127" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO127" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP127" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ127" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR127" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="128" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>1</v>
+      </c>
+      <c r="B128" s="2">
+        <v>2</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F128" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G128" s="5">
+        <v>13</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J128" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K128" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L128" s="6">
+        <v>6</v>
+      </c>
+      <c r="M128" s="7">
+        <v>1077.5999999999999</v>
+      </c>
+      <c r="N128" s="6">
+        <v>1</v>
+      </c>
+      <c r="O128" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P128" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q128" s="6">
+        <v>0</v>
+      </c>
+      <c r="R128" s="7">
+        <v>0</v>
+      </c>
+      <c r="S128" s="9">
+        <v>0</v>
+      </c>
+      <c r="T128" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U128" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V128" s="11">
+        <v>11</v>
+      </c>
+      <c r="W128" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X128" s="12">
+        <v>0.36805559999999998</v>
+      </c>
+      <c r="Y128" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z128" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA128" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB128" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC128" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD128" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE128" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF128" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG128" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH128" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI128" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ128" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK128" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL128" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM128" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN128" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO128" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP128" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ128" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR128" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="129" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>1</v>
+      </c>
+      <c r="B129" s="2">
+        <v>2</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F129" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G129" s="5">
+        <v>14</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J129" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K129" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L129" s="6">
+        <v>7</v>
+      </c>
+      <c r="M129" s="7">
+        <v>1257.2</v>
+      </c>
+      <c r="N129" s="6">
+        <v>1</v>
+      </c>
+      <c r="O129" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P129" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q129" s="6">
+        <v>0</v>
+      </c>
+      <c r="R129" s="7">
+        <v>0</v>
+      </c>
+      <c r="S129" s="9">
+        <v>0</v>
+      </c>
+      <c r="T129" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U129" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V129" s="11">
+        <v>11</v>
+      </c>
+      <c r="W129" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X129" s="12">
+        <v>0.36805559999999998</v>
+      </c>
+      <c r="Y129" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z129" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA129" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB129" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC129" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD129" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE129" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF129" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG129" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH129" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI129" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ129" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK129" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL129" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM129" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN129" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO129" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP129" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ129" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR129" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="130" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>1</v>
+      </c>
+      <c r="B130" s="2">
+        <v>2</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F130" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G130" s="5">
+        <v>15</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I130" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J130" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K130" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L130" s="6">
+        <v>8</v>
+      </c>
+      <c r="M130" s="7">
+        <v>1436.8</v>
+      </c>
+      <c r="N130" s="6">
+        <v>1</v>
+      </c>
+      <c r="O130" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P130" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q130" s="6">
+        <v>0</v>
+      </c>
+      <c r="R130" s="7">
+        <v>0</v>
+      </c>
+      <c r="S130" s="9">
+        <v>0</v>
+      </c>
+      <c r="T130" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U130" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V130" s="11">
+        <v>11</v>
+      </c>
+      <c r="W130" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X130" s="12">
+        <v>0.36805559999999998</v>
+      </c>
+      <c r="Y130" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z130" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA130" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB130" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC130" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD130" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE130" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF130" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG130" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH130" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI130" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ130" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK130" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL130" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM130" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN130" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO130" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP130" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ130" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR130" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="131" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>1</v>
+      </c>
+      <c r="B131" s="2">
+        <v>2</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F131" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G131" s="5">
+        <v>16</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J131" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K131" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L131" s="6">
+        <v>9</v>
+      </c>
+      <c r="M131" s="7">
+        <v>1616.4</v>
+      </c>
+      <c r="N131" s="6">
+        <v>1</v>
+      </c>
+      <c r="O131" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P131" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q131" s="6">
+        <v>0</v>
+      </c>
+      <c r="R131" s="7">
+        <v>0</v>
+      </c>
+      <c r="S131" s="9">
+        <v>0</v>
+      </c>
+      <c r="T131" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U131" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V131" s="11">
+        <v>11</v>
+      </c>
+      <c r="W131" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X131" s="12">
+        <v>0.36805559999999998</v>
+      </c>
+      <c r="Y131" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z131" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA131" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB131" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC131" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD131" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE131" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF131" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG131" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH131" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI131" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ131" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK131" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL131" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM131" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN131" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO131" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP131" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ131" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR131" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="132" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>1</v>
+      </c>
+      <c r="B132" s="2">
+        <v>2</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F132" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G132" s="5">
+        <v>17</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J132" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K132" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L132" s="6">
+        <v>10</v>
+      </c>
+      <c r="M132" s="7">
+        <v>1796</v>
+      </c>
+      <c r="N132" s="6">
+        <v>1</v>
+      </c>
+      <c r="O132" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P132" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q132" s="6">
+        <v>0</v>
+      </c>
+      <c r="R132" s="7">
+        <v>0</v>
+      </c>
+      <c r="S132" s="9">
+        <v>0</v>
+      </c>
+      <c r="T132" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U132" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V132" s="11">
+        <v>11</v>
+      </c>
+      <c r="W132" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X132" s="12">
+        <v>0.36805559999999998</v>
+      </c>
+      <c r="Y132" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z132" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA132" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB132" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC132" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD132" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE132" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF132" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG132" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH132" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI132" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ132" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK132" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL132" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM132" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN132" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO132" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP132" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ132" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR132" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="133" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>1</v>
+      </c>
+      <c r="B133" s="2">
+        <v>2</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F133" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G133" s="5">
+        <v>18</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I133" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J133" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K133" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L133" s="6">
+        <v>11</v>
+      </c>
+      <c r="M133" s="7">
+        <v>1975.6</v>
+      </c>
+      <c r="N133" s="6">
+        <v>1</v>
+      </c>
+      <c r="O133" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P133" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q133" s="6">
+        <v>0</v>
+      </c>
+      <c r="R133" s="7">
+        <v>0</v>
+      </c>
+      <c r="S133" s="9">
+        <v>0</v>
+      </c>
+      <c r="T133" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U133" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V133" s="11">
+        <v>11</v>
+      </c>
+      <c r="W133" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X133" s="12">
+        <v>0.36805559999999998</v>
+      </c>
+      <c r="Y133" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z133" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA133" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB133" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC133" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD133" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE133" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF133" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG133" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH133" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI133" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ133" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK133" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL133" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM133" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN133" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO133" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP133" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ133" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR133" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="134" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>1</v>
+      </c>
+      <c r="B134" s="2">
+        <v>2</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F134" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G134" s="5">
+        <v>19</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J134" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K134" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L134" s="6">
+        <v>12</v>
+      </c>
+      <c r="M134" s="7">
+        <v>2155.1999999999998</v>
+      </c>
+      <c r="N134" s="6">
+        <v>1</v>
+      </c>
+      <c r="O134" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P134" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q134" s="6">
+        <v>0</v>
+      </c>
+      <c r="R134" s="7">
+        <v>0</v>
+      </c>
+      <c r="S134" s="9">
+        <v>0</v>
+      </c>
+      <c r="T134" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U134" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V134" s="11">
+        <v>11</v>
+      </c>
+      <c r="W134" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X134" s="12">
+        <v>0.40277780000000002</v>
+      </c>
+      <c r="Y134" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z134" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA134" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB134" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC134" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD134" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE134" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF134" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG134" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH134" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI134" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ134" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK134" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL134" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM134" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN134" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO134" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP134" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ134" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR134" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="135" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>1</v>
+      </c>
+      <c r="B135" s="2">
+        <v>2</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F135" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G135" s="5">
+        <v>20</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I135" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J135" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K135" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L135" s="6">
+        <v>13</v>
+      </c>
+      <c r="M135" s="7">
+        <v>2334.8000000000002</v>
+      </c>
+      <c r="N135" s="6">
+        <v>1</v>
+      </c>
+      <c r="O135" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P135" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q135" s="6">
+        <v>0</v>
+      </c>
+      <c r="R135" s="7">
+        <v>0</v>
+      </c>
+      <c r="S135" s="9">
+        <v>0</v>
+      </c>
+      <c r="T135" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U135" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V135" s="11">
+        <v>11</v>
+      </c>
+      <c r="W135" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X135" s="12">
+        <v>0.40277780000000002</v>
+      </c>
+      <c r="Y135" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z135" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA135" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB135" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC135" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD135" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE135" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF135" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG135" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH135" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI135" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ135" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK135" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL135" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM135" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN135" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO135" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP135" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ135" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR135" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="136" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>1</v>
+      </c>
+      <c r="B136" s="2">
+        <v>2</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F136" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G136" s="5">
+        <v>21</v>
+      </c>
+      <c r="H136" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J136" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K136" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L136" s="6">
+        <v>14</v>
+      </c>
+      <c r="M136" s="7">
+        <v>2514.4</v>
+      </c>
+      <c r="N136" s="6">
+        <v>1</v>
+      </c>
+      <c r="O136" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P136" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q136" s="6">
+        <v>0</v>
+      </c>
+      <c r="R136" s="7">
+        <v>0</v>
+      </c>
+      <c r="S136" s="9">
+        <v>0</v>
+      </c>
+      <c r="T136" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U136" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V136" s="11">
+        <v>11</v>
+      </c>
+      <c r="W136" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X136" s="12">
+        <v>0.40277780000000002</v>
+      </c>
+      <c r="Y136" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA136" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB136" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC136" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD136" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE136" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF136" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG136" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH136" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI136" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ136" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK136" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL136" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM136" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN136" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO136" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP136" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ136" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR136" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="137" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>1</v>
+      </c>
+      <c r="B137" s="2">
+        <v>2</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F137" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G137" s="5">
+        <v>22</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J137" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K137" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L137" s="6">
+        <v>15</v>
+      </c>
+      <c r="M137" s="7">
+        <v>2694</v>
+      </c>
+      <c r="N137" s="6">
+        <v>1</v>
+      </c>
+      <c r="O137" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P137" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q137" s="6">
+        <v>0</v>
+      </c>
+      <c r="R137" s="7">
+        <v>0</v>
+      </c>
+      <c r="S137" s="9">
+        <v>0</v>
+      </c>
+      <c r="T137" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U137" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V137" s="11">
+        <v>11</v>
+      </c>
+      <c r="W137" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X137" s="12">
+        <v>0.40277780000000002</v>
+      </c>
+      <c r="Y137" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z137" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA137" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB137" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC137" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD137" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE137" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF137" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG137" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH137" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI137" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ137" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK137" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL137" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM137" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN137" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO137" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP137" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ137" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR137" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="138" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>1</v>
+      </c>
+      <c r="B138" s="2">
+        <v>2</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F138" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G138" s="5">
+        <v>23</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J138" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K138" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L138" s="6">
+        <v>16</v>
+      </c>
+      <c r="M138" s="7">
+        <v>2873.6</v>
+      </c>
+      <c r="N138" s="6">
+        <v>1</v>
+      </c>
+      <c r="O138" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P138" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q138" s="6">
+        <v>0</v>
+      </c>
+      <c r="R138" s="7">
+        <v>0</v>
+      </c>
+      <c r="S138" s="9">
+        <v>0</v>
+      </c>
+      <c r="T138" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U138" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V138" s="11">
+        <v>11</v>
+      </c>
+      <c r="W138" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X138" s="12">
+        <v>0.40277780000000002</v>
+      </c>
+      <c r="Y138" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z138" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA138" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB138" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC138" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD138" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE138" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF138" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG138" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH138" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI138" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ138" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK138" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL138" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM138" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN138" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO138" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP138" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ138" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR138" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="139" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>1</v>
+      </c>
+      <c r="B139" s="2">
+        <v>2</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F139" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G139" s="5">
+        <v>24</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J139" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K139" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L139" s="6">
+        <v>17</v>
+      </c>
+      <c r="M139" s="7">
+        <v>3053.2</v>
+      </c>
+      <c r="N139" s="6">
+        <v>1</v>
+      </c>
+      <c r="O139" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P139" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q139" s="6">
+        <v>0</v>
+      </c>
+      <c r="R139" s="7">
+        <v>0</v>
+      </c>
+      <c r="S139" s="9">
+        <v>0</v>
+      </c>
+      <c r="T139" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U139" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V139" s="11">
+        <v>11</v>
+      </c>
+      <c r="W139" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X139" s="12">
+        <v>0.42361110000000002</v>
+      </c>
+      <c r="Y139" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z139" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA139" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB139" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC139" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD139" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE139" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF139" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG139" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH139" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI139" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ139" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK139" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL139" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM139" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN139" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO139" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP139" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ139" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR139" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="140" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>1</v>
+      </c>
+      <c r="B140" s="2">
+        <v>2</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F140" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G140" s="5">
+        <v>25</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J140" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K140" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L140" s="6">
+        <v>18</v>
+      </c>
+      <c r="M140" s="7">
+        <v>3232.8</v>
+      </c>
+      <c r="N140" s="6">
+        <v>1</v>
+      </c>
+      <c r="O140" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P140" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q140" s="6">
+        <v>0</v>
+      </c>
+      <c r="R140" s="7">
+        <v>0</v>
+      </c>
+      <c r="S140" s="9">
+        <v>0</v>
+      </c>
+      <c r="T140" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U140" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V140" s="11">
+        <v>11</v>
+      </c>
+      <c r="W140" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X140" s="12">
+        <v>0.42361110000000002</v>
+      </c>
+      <c r="Y140" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z140" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA140" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB140" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC140" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD140" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE140" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF140" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG140" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH140" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI140" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ140" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK140" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL140" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM140" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN140" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO140" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP140" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ140" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR140" s="3" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{886A17D8-D919-4C73-AB01-BAD1D2AE56E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{47490F82-4881-428F-BFA1-9FB160A65523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47490F82-4881-428F-BFA1-9FB160A65523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E589B419-BF85-4E70-AAF1-541DC232E3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9494" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9638" uniqueCount="597">
   <si>
     <t>Sel</t>
   </si>
@@ -1723,6 +1723,30 @@
     <t>1883700000042</t>
   </si>
   <si>
+    <t>1883700000043</t>
+  </si>
+  <si>
+    <t>1883700000044</t>
+  </si>
+  <si>
+    <t>1883700000045</t>
+  </si>
+  <si>
+    <t>1883700000046</t>
+  </si>
+  <si>
+    <t>1883700000047</t>
+  </si>
+  <si>
+    <t>1883700000048</t>
+  </si>
+  <si>
+    <t>1883700000049</t>
+  </si>
+  <si>
+    <t>1883700000050</t>
+  </si>
+  <si>
     <t>10099364</t>
   </si>
   <si>
@@ -2362,7 +2386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR526"/>
+  <dimension ref="A1:AR534"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -70177,7 +70201,7 @@
         <v>2</v>
       </c>
       <c r="C507" s="3" t="s">
-        <v>567</v>
+        <v>541</v>
       </c>
       <c r="D507" s="3" t="s">
         <v>151</v>
@@ -70189,7 +70213,7 @@
         <v>46286</v>
       </c>
       <c r="G507" s="5">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="H507" s="3" t="s">
         <v>47</v>
@@ -70204,16 +70228,16 @@
         <v>50</v>
       </c>
       <c r="L507" s="6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M507" s="7">
-        <v>0</v>
+        <v>4310.3999999999996</v>
       </c>
       <c r="N507" s="6">
         <v>1</v>
       </c>
       <c r="O507" s="3" t="s">
-        <v>568</v>
+        <v>542</v>
       </c>
       <c r="P507" s="8">
         <v>179.6</v>
@@ -70231,7 +70255,7 @@
         <v>52</v>
       </c>
       <c r="U507" s="10">
-        <v>67522</v>
+        <v>67517</v>
       </c>
       <c r="V507" s="11">
         <v>11</v>
@@ -70240,7 +70264,7 @@
         <v>46286</v>
       </c>
       <c r="X507" s="12">
-        <v>0.34027780000000002</v>
+        <v>0.54027780000000003</v>
       </c>
       <c r="Y507" s="10">
         <v>0</v>
@@ -70300,7 +70324,7 @@
         <v>53</v>
       </c>
       <c r="AR507" s="3" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="508" spans="1:44" x14ac:dyDescent="0.3">
@@ -70311,7 +70335,7 @@
         <v>2</v>
       </c>
       <c r="C508" s="3" t="s">
-        <v>567</v>
+        <v>541</v>
       </c>
       <c r="D508" s="3" t="s">
         <v>151</v>
@@ -70323,7 +70347,7 @@
         <v>46286</v>
       </c>
       <c r="G508" s="5">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H508" s="3" t="s">
         <v>47</v>
@@ -70338,16 +70362,16 @@
         <v>50</v>
       </c>
       <c r="L508" s="6">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="M508" s="7">
-        <v>179.6</v>
+        <v>4490</v>
       </c>
       <c r="N508" s="6">
         <v>1</v>
       </c>
       <c r="O508" s="3" t="s">
-        <v>568</v>
+        <v>542</v>
       </c>
       <c r="P508" s="8">
         <v>179.6</v>
@@ -70365,7 +70389,7 @@
         <v>52</v>
       </c>
       <c r="U508" s="10">
-        <v>67522</v>
+        <v>67517</v>
       </c>
       <c r="V508" s="11">
         <v>11</v>
@@ -70374,7 +70398,7 @@
         <v>46286</v>
       </c>
       <c r="X508" s="12">
-        <v>0.34027780000000002</v>
+        <v>0.54027780000000003</v>
       </c>
       <c r="Y508" s="10">
         <v>0</v>
@@ -70434,7 +70458,7 @@
         <v>53</v>
       </c>
       <c r="AR508" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="509" spans="1:44" x14ac:dyDescent="0.3">
@@ -70445,7 +70469,7 @@
         <v>2</v>
       </c>
       <c r="C509" s="3" t="s">
-        <v>567</v>
+        <v>541</v>
       </c>
       <c r="D509" s="3" t="s">
         <v>151</v>
@@ -70457,7 +70481,7 @@
         <v>46286</v>
       </c>
       <c r="G509" s="5">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H509" s="3" t="s">
         <v>47</v>
@@ -70472,16 +70496,16 @@
         <v>50</v>
       </c>
       <c r="L509" s="6">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="M509" s="7">
-        <v>359.2</v>
+        <v>4669.6000000000004</v>
       </c>
       <c r="N509" s="6">
         <v>1</v>
       </c>
       <c r="O509" s="3" t="s">
-        <v>568</v>
+        <v>542</v>
       </c>
       <c r="P509" s="8">
         <v>179.6</v>
@@ -70499,7 +70523,7 @@
         <v>52</v>
       </c>
       <c r="U509" s="10">
-        <v>67522</v>
+        <v>67517</v>
       </c>
       <c r="V509" s="11">
         <v>11</v>
@@ -70508,7 +70532,7 @@
         <v>46286</v>
       </c>
       <c r="X509" s="12">
-        <v>0.34027780000000002</v>
+        <v>0.54027780000000003</v>
       </c>
       <c r="Y509" s="10">
         <v>0</v>
@@ -70568,7 +70592,7 @@
         <v>53</v>
       </c>
       <c r="AR509" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="510" spans="1:44" x14ac:dyDescent="0.3">
@@ -70579,7 +70603,7 @@
         <v>2</v>
       </c>
       <c r="C510" s="3" t="s">
-        <v>567</v>
+        <v>541</v>
       </c>
       <c r="D510" s="3" t="s">
         <v>151</v>
@@ -70591,7 +70615,7 @@
         <v>46286</v>
       </c>
       <c r="G510" s="5">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H510" s="3" t="s">
         <v>47</v>
@@ -70606,16 +70630,16 @@
         <v>50</v>
       </c>
       <c r="L510" s="6">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="M510" s="7">
-        <v>538.79999999999995</v>
+        <v>4849.2</v>
       </c>
       <c r="N510" s="6">
         <v>1</v>
       </c>
       <c r="O510" s="3" t="s">
-        <v>568</v>
+        <v>542</v>
       </c>
       <c r="P510" s="8">
         <v>179.6</v>
@@ -70633,7 +70657,7 @@
         <v>52</v>
       </c>
       <c r="U510" s="10">
-        <v>67522</v>
+        <v>67517</v>
       </c>
       <c r="V510" s="11">
         <v>11</v>
@@ -70642,7 +70666,7 @@
         <v>46286</v>
       </c>
       <c r="X510" s="12">
-        <v>0.34027780000000002</v>
+        <v>0.54027780000000003</v>
       </c>
       <c r="Y510" s="10">
         <v>0</v>
@@ -70702,7 +70726,7 @@
         <v>53</v>
       </c>
       <c r="AR510" s="3" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="511" spans="1:44" x14ac:dyDescent="0.3">
@@ -70713,7 +70737,7 @@
         <v>2</v>
       </c>
       <c r="C511" s="3" t="s">
-        <v>567</v>
+        <v>541</v>
       </c>
       <c r="D511" s="3" t="s">
         <v>151</v>
@@ -70725,7 +70749,7 @@
         <v>46286</v>
       </c>
       <c r="G511" s="5">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="H511" s="3" t="s">
         <v>47</v>
@@ -70740,16 +70764,16 @@
         <v>50</v>
       </c>
       <c r="L511" s="6">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="M511" s="7">
-        <v>718.4</v>
+        <v>5028.8</v>
       </c>
       <c r="N511" s="6">
         <v>1</v>
       </c>
       <c r="O511" s="3" t="s">
-        <v>568</v>
+        <v>542</v>
       </c>
       <c r="P511" s="8">
         <v>179.6</v>
@@ -70767,7 +70791,7 @@
         <v>52</v>
       </c>
       <c r="U511" s="10">
-        <v>67522</v>
+        <v>67517</v>
       </c>
       <c r="V511" s="11">
         <v>11</v>
@@ -70776,7 +70800,7 @@
         <v>46286</v>
       </c>
       <c r="X511" s="12">
-        <v>0.34027780000000002</v>
+        <v>0.54027780000000003</v>
       </c>
       <c r="Y511" s="10">
         <v>0</v>
@@ -70836,7 +70860,7 @@
         <v>53</v>
       </c>
       <c r="AR511" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="512" spans="1:44" x14ac:dyDescent="0.3">
@@ -70847,7 +70871,7 @@
         <v>2</v>
       </c>
       <c r="C512" s="3" t="s">
-        <v>567</v>
+        <v>541</v>
       </c>
       <c r="D512" s="3" t="s">
         <v>151</v>
@@ -70859,7 +70883,7 @@
         <v>46286</v>
       </c>
       <c r="G512" s="5">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H512" s="3" t="s">
         <v>47</v>
@@ -70874,16 +70898,16 @@
         <v>50</v>
       </c>
       <c r="L512" s="6">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="M512" s="7">
-        <v>898</v>
+        <v>5208.3999999999996</v>
       </c>
       <c r="N512" s="6">
         <v>1</v>
       </c>
       <c r="O512" s="3" t="s">
-        <v>568</v>
+        <v>542</v>
       </c>
       <c r="P512" s="8">
         <v>179.6</v>
@@ -70901,7 +70925,7 @@
         <v>52</v>
       </c>
       <c r="U512" s="10">
-        <v>67522</v>
+        <v>67517</v>
       </c>
       <c r="V512" s="11">
         <v>11</v>
@@ -70910,7 +70934,7 @@
         <v>46286</v>
       </c>
       <c r="X512" s="12">
-        <v>0.34027780000000002</v>
+        <v>0.54027780000000003</v>
       </c>
       <c r="Y512" s="10">
         <v>0</v>
@@ -70970,7 +70994,7 @@
         <v>53</v>
       </c>
       <c r="AR512" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="513" spans="1:44" x14ac:dyDescent="0.3">
@@ -70981,7 +71005,7 @@
         <v>2</v>
       </c>
       <c r="C513" s="3" t="s">
-        <v>567</v>
+        <v>541</v>
       </c>
       <c r="D513" s="3" t="s">
         <v>151</v>
@@ -70993,7 +71017,7 @@
         <v>46286</v>
       </c>
       <c r="G513" s="5">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="H513" s="3" t="s">
         <v>47</v>
@@ -71008,16 +71032,16 @@
         <v>50</v>
       </c>
       <c r="L513" s="6">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="M513" s="7">
-        <v>1077.5999999999999</v>
+        <v>5388</v>
       </c>
       <c r="N513" s="6">
         <v>1</v>
       </c>
       <c r="O513" s="3" t="s">
-        <v>568</v>
+        <v>542</v>
       </c>
       <c r="P513" s="8">
         <v>179.6</v>
@@ -71035,7 +71059,7 @@
         <v>52</v>
       </c>
       <c r="U513" s="10">
-        <v>67522</v>
+        <v>67517</v>
       </c>
       <c r="V513" s="11">
         <v>11</v>
@@ -71044,7 +71068,7 @@
         <v>46286</v>
       </c>
       <c r="X513" s="12">
-        <v>0.36805559999999998</v>
+        <v>0.54027780000000003</v>
       </c>
       <c r="Y513" s="10">
         <v>0</v>
@@ -71104,7 +71128,7 @@
         <v>53</v>
       </c>
       <c r="AR513" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="514" spans="1:44" x14ac:dyDescent="0.3">
@@ -71115,7 +71139,7 @@
         <v>2</v>
       </c>
       <c r="C514" s="3" t="s">
-        <v>567</v>
+        <v>541</v>
       </c>
       <c r="D514" s="3" t="s">
         <v>151</v>
@@ -71127,7 +71151,7 @@
         <v>46286</v>
       </c>
       <c r="G514" s="5">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H514" s="3" t="s">
         <v>47</v>
@@ -71142,16 +71166,16 @@
         <v>50</v>
       </c>
       <c r="L514" s="6">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="M514" s="7">
-        <v>1257.2</v>
+        <v>5567.6</v>
       </c>
       <c r="N514" s="6">
         <v>1</v>
       </c>
       <c r="O514" s="3" t="s">
-        <v>568</v>
+        <v>542</v>
       </c>
       <c r="P514" s="8">
         <v>179.6</v>
@@ -71169,7 +71193,7 @@
         <v>52</v>
       </c>
       <c r="U514" s="10">
-        <v>67522</v>
+        <v>67517</v>
       </c>
       <c r="V514" s="11">
         <v>11</v>
@@ -71178,7 +71202,7 @@
         <v>46286</v>
       </c>
       <c r="X514" s="12">
-        <v>0.36805559999999998</v>
+        <v>0.54027780000000003</v>
       </c>
       <c r="Y514" s="10">
         <v>0</v>
@@ -71238,7 +71262,7 @@
         <v>53</v>
       </c>
       <c r="AR514" s="3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="515" spans="1:44" x14ac:dyDescent="0.3">
@@ -71249,7 +71273,7 @@
         <v>2</v>
       </c>
       <c r="C515" s="3" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="D515" s="3" t="s">
         <v>151</v>
@@ -71261,7 +71285,7 @@
         <v>46286</v>
       </c>
       <c r="G515" s="5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H515" s="3" t="s">
         <v>47</v>
@@ -71276,16 +71300,16 @@
         <v>50</v>
       </c>
       <c r="L515" s="6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M515" s="7">
-        <v>1436.8</v>
+        <v>0</v>
       </c>
       <c r="N515" s="6">
         <v>1</v>
       </c>
       <c r="O515" s="3" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="P515" s="8">
         <v>179.6</v>
@@ -71312,7 +71336,7 @@
         <v>46286</v>
       </c>
       <c r="X515" s="12">
-        <v>0.36805559999999998</v>
+        <v>0.34027780000000002</v>
       </c>
       <c r="Y515" s="10">
         <v>0</v>
@@ -71383,7 +71407,7 @@
         <v>2</v>
       </c>
       <c r="C516" s="3" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="D516" s="3" t="s">
         <v>151</v>
@@ -71395,7 +71419,7 @@
         <v>46286</v>
       </c>
       <c r="G516" s="5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H516" s="3" t="s">
         <v>47</v>
@@ -71410,16 +71434,16 @@
         <v>50</v>
       </c>
       <c r="L516" s="6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M516" s="7">
-        <v>1616.4</v>
+        <v>179.6</v>
       </c>
       <c r="N516" s="6">
         <v>1</v>
       </c>
       <c r="O516" s="3" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="P516" s="8">
         <v>179.6</v>
@@ -71446,7 +71470,7 @@
         <v>46286</v>
       </c>
       <c r="X516" s="12">
-        <v>0.36805559999999998</v>
+        <v>0.34027780000000002</v>
       </c>
       <c r="Y516" s="10">
         <v>0</v>
@@ -71517,7 +71541,7 @@
         <v>2</v>
       </c>
       <c r="C517" s="3" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="D517" s="3" t="s">
         <v>151</v>
@@ -71529,7 +71553,7 @@
         <v>46286</v>
       </c>
       <c r="G517" s="5">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H517" s="3" t="s">
         <v>47</v>
@@ -71544,16 +71568,16 @@
         <v>50</v>
       </c>
       <c r="L517" s="6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M517" s="7">
-        <v>1796</v>
+        <v>359.2</v>
       </c>
       <c r="N517" s="6">
         <v>1</v>
       </c>
       <c r="O517" s="3" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="P517" s="8">
         <v>179.6</v>
@@ -71580,7 +71604,7 @@
         <v>46286</v>
       </c>
       <c r="X517" s="12">
-        <v>0.36805559999999998</v>
+        <v>0.34027780000000002</v>
       </c>
       <c r="Y517" s="10">
         <v>0</v>
@@ -71651,7 +71675,7 @@
         <v>2</v>
       </c>
       <c r="C518" s="3" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="D518" s="3" t="s">
         <v>151</v>
@@ -71663,7 +71687,7 @@
         <v>46286</v>
       </c>
       <c r="G518" s="5">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H518" s="3" t="s">
         <v>47</v>
@@ -71678,16 +71702,16 @@
         <v>50</v>
       </c>
       <c r="L518" s="6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M518" s="7">
-        <v>1975.6</v>
+        <v>538.79999999999995</v>
       </c>
       <c r="N518" s="6">
         <v>1</v>
       </c>
       <c r="O518" s="3" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="P518" s="8">
         <v>179.6</v>
@@ -71714,7 +71738,7 @@
         <v>46286</v>
       </c>
       <c r="X518" s="12">
-        <v>0.36805559999999998</v>
+        <v>0.34027780000000002</v>
       </c>
       <c r="Y518" s="10">
         <v>0</v>
@@ -71785,7 +71809,7 @@
         <v>2</v>
       </c>
       <c r="C519" s="3" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="D519" s="3" t="s">
         <v>151</v>
@@ -71797,7 +71821,7 @@
         <v>46286</v>
       </c>
       <c r="G519" s="5">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H519" s="3" t="s">
         <v>47</v>
@@ -71812,16 +71836,16 @@
         <v>50</v>
       </c>
       <c r="L519" s="6">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M519" s="7">
-        <v>2155.1999999999998</v>
+        <v>718.4</v>
       </c>
       <c r="N519" s="6">
         <v>1</v>
       </c>
       <c r="O519" s="3" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="P519" s="8">
         <v>179.6</v>
@@ -71848,7 +71872,7 @@
         <v>46286</v>
       </c>
       <c r="X519" s="12">
-        <v>0.40277780000000002</v>
+        <v>0.34027780000000002</v>
       </c>
       <c r="Y519" s="10">
         <v>0</v>
@@ -71919,7 +71943,7 @@
         <v>2</v>
       </c>
       <c r="C520" s="3" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="D520" s="3" t="s">
         <v>151</v>
@@ -71931,7 +71955,7 @@
         <v>46286</v>
       </c>
       <c r="G520" s="5">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H520" s="3" t="s">
         <v>47</v>
@@ -71946,16 +71970,16 @@
         <v>50</v>
       </c>
       <c r="L520" s="6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M520" s="7">
-        <v>2334.8000000000002</v>
+        <v>898</v>
       </c>
       <c r="N520" s="6">
         <v>1</v>
       </c>
       <c r="O520" s="3" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="P520" s="8">
         <v>179.6</v>
@@ -71982,7 +72006,7 @@
         <v>46286</v>
       </c>
       <c r="X520" s="12">
-        <v>0.40277780000000002</v>
+        <v>0.34027780000000002</v>
       </c>
       <c r="Y520" s="10">
         <v>0</v>
@@ -72053,7 +72077,7 @@
         <v>2</v>
       </c>
       <c r="C521" s="3" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="D521" s="3" t="s">
         <v>151</v>
@@ -72065,7 +72089,7 @@
         <v>46286</v>
       </c>
       <c r="G521" s="5">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H521" s="3" t="s">
         <v>47</v>
@@ -72080,16 +72104,16 @@
         <v>50</v>
       </c>
       <c r="L521" s="6">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M521" s="7">
-        <v>2514.4</v>
+        <v>1077.5999999999999</v>
       </c>
       <c r="N521" s="6">
         <v>1</v>
       </c>
       <c r="O521" s="3" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="P521" s="8">
         <v>179.6</v>
@@ -72116,7 +72140,7 @@
         <v>46286</v>
       </c>
       <c r="X521" s="12">
-        <v>0.40277780000000002</v>
+        <v>0.36805559999999998</v>
       </c>
       <c r="Y521" s="10">
         <v>0</v>
@@ -72187,7 +72211,7 @@
         <v>2</v>
       </c>
       <c r="C522" s="3" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="D522" s="3" t="s">
         <v>151</v>
@@ -72199,7 +72223,7 @@
         <v>46286</v>
       </c>
       <c r="G522" s="5">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H522" s="3" t="s">
         <v>47</v>
@@ -72214,16 +72238,16 @@
         <v>50</v>
       </c>
       <c r="L522" s="6">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M522" s="7">
-        <v>2694</v>
+        <v>1257.2</v>
       </c>
       <c r="N522" s="6">
         <v>1</v>
       </c>
       <c r="O522" s="3" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="P522" s="8">
         <v>179.6</v>
@@ -72250,7 +72274,7 @@
         <v>46286</v>
       </c>
       <c r="X522" s="12">
-        <v>0.40277780000000002</v>
+        <v>0.36805559999999998</v>
       </c>
       <c r="Y522" s="10">
         <v>0</v>
@@ -72321,7 +72345,7 @@
         <v>2</v>
       </c>
       <c r="C523" s="3" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="D523" s="3" t="s">
         <v>151</v>
@@ -72333,7 +72357,7 @@
         <v>46286</v>
       </c>
       <c r="G523" s="5">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H523" s="3" t="s">
         <v>47</v>
@@ -72348,16 +72372,16 @@
         <v>50</v>
       </c>
       <c r="L523" s="6">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M523" s="7">
-        <v>2873.6</v>
+        <v>1436.8</v>
       </c>
       <c r="N523" s="6">
         <v>1</v>
       </c>
       <c r="O523" s="3" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="P523" s="8">
         <v>179.6</v>
@@ -72384,7 +72408,7 @@
         <v>46286</v>
       </c>
       <c r="X523" s="12">
-        <v>0.40277780000000002</v>
+        <v>0.36805559999999998</v>
       </c>
       <c r="Y523" s="10">
         <v>0</v>
@@ -72455,7 +72479,7 @@
         <v>2</v>
       </c>
       <c r="C524" s="3" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="D524" s="3" t="s">
         <v>151</v>
@@ -72467,7 +72491,7 @@
         <v>46286</v>
       </c>
       <c r="G524" s="5">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H524" s="3" t="s">
         <v>47</v>
@@ -72482,16 +72506,16 @@
         <v>50</v>
       </c>
       <c r="L524" s="6">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="M524" s="7">
-        <v>3053.2</v>
+        <v>1616.4</v>
       </c>
       <c r="N524" s="6">
         <v>1</v>
       </c>
       <c r="O524" s="3" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="P524" s="8">
         <v>179.6</v>
@@ -72518,7 +72542,7 @@
         <v>46286</v>
       </c>
       <c r="X524" s="12">
-        <v>0.42361110000000002</v>
+        <v>0.36805559999999998</v>
       </c>
       <c r="Y524" s="10">
         <v>0</v>
@@ -72589,7 +72613,7 @@
         <v>2</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="D525" s="3" t="s">
         <v>151</v>
@@ -72601,7 +72625,7 @@
         <v>46286</v>
       </c>
       <c r="G525" s="5">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H525" s="3" t="s">
         <v>47</v>
@@ -72616,16 +72640,16 @@
         <v>50</v>
       </c>
       <c r="L525" s="6">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="M525" s="7">
-        <v>3232.8</v>
+        <v>1796</v>
       </c>
       <c r="N525" s="6">
         <v>1</v>
       </c>
       <c r="O525" s="3" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="P525" s="8">
         <v>179.6</v>
@@ -72652,7 +72676,7 @@
         <v>46286</v>
       </c>
       <c r="X525" s="12">
-        <v>0.42361110000000002</v>
+        <v>0.36805559999999998</v>
       </c>
       <c r="Y525" s="10">
         <v>0</v>
@@ -72723,7 +72747,7 @@
         <v>2</v>
       </c>
       <c r="C526" s="3" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="D526" s="3" t="s">
         <v>151</v>
@@ -72735,7 +72759,7 @@
         <v>46286</v>
       </c>
       <c r="G526" s="5">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H526" s="3" t="s">
         <v>47</v>
@@ -72750,16 +72774,16 @@
         <v>50</v>
       </c>
       <c r="L526" s="6">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="M526" s="7">
-        <v>3412.4</v>
+        <v>1975.6</v>
       </c>
       <c r="N526" s="6">
         <v>1</v>
       </c>
       <c r="O526" s="3" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="P526" s="8">
         <v>179.6</v>
@@ -72786,7 +72810,7 @@
         <v>46286</v>
       </c>
       <c r="X526" s="12">
-        <v>0.48472219999999999</v>
+        <v>0.36805559999999998</v>
       </c>
       <c r="Y526" s="10">
         <v>0</v>
@@ -72847,6 +72871,1078 @@
       </c>
       <c r="AR526" s="3" t="s">
         <v>588</v>
+      </c>
+    </row>
+    <row r="527" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A527" s="1">
+        <v>1</v>
+      </c>
+      <c r="B527" s="2">
+        <v>2</v>
+      </c>
+      <c r="C527" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="D527" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E527" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F527" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G527" s="5">
+        <v>19</v>
+      </c>
+      <c r="H527" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I527" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J527" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K527" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L527" s="6">
+        <v>12</v>
+      </c>
+      <c r="M527" s="7">
+        <v>2155.1999999999998</v>
+      </c>
+      <c r="N527" s="6">
+        <v>1</v>
+      </c>
+      <c r="O527" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="P527" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q527" s="6">
+        <v>0</v>
+      </c>
+      <c r="R527" s="7">
+        <v>0</v>
+      </c>
+      <c r="S527" s="9">
+        <v>0</v>
+      </c>
+      <c r="T527" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U527" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V527" s="11">
+        <v>11</v>
+      </c>
+      <c r="W527" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X527" s="12">
+        <v>0.40277780000000002</v>
+      </c>
+      <c r="Y527" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z527" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA527" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB527" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC527" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD527" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE527" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF527" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG527" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH527" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI527" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ527" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK527" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL527" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM527" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN527" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO527" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP527" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ527" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR527" s="3" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="528" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A528" s="1">
+        <v>1</v>
+      </c>
+      <c r="B528" s="2">
+        <v>2</v>
+      </c>
+      <c r="C528" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="D528" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E528" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F528" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G528" s="5">
+        <v>20</v>
+      </c>
+      <c r="H528" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I528" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J528" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K528" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L528" s="6">
+        <v>13</v>
+      </c>
+      <c r="M528" s="7">
+        <v>2334.8000000000002</v>
+      </c>
+      <c r="N528" s="6">
+        <v>1</v>
+      </c>
+      <c r="O528" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="P528" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q528" s="6">
+        <v>0</v>
+      </c>
+      <c r="R528" s="7">
+        <v>0</v>
+      </c>
+      <c r="S528" s="9">
+        <v>0</v>
+      </c>
+      <c r="T528" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U528" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V528" s="11">
+        <v>11</v>
+      </c>
+      <c r="W528" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X528" s="12">
+        <v>0.40277780000000002</v>
+      </c>
+      <c r="Y528" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z528" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA528" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB528" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC528" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD528" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE528" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF528" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG528" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH528" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI528" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ528" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK528" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL528" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM528" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN528" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO528" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP528" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ528" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR528" s="3" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="529" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A529" s="1">
+        <v>1</v>
+      </c>
+      <c r="B529" s="2">
+        <v>2</v>
+      </c>
+      <c r="C529" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="D529" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E529" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F529" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G529" s="5">
+        <v>21</v>
+      </c>
+      <c r="H529" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I529" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J529" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K529" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L529" s="6">
+        <v>14</v>
+      </c>
+      <c r="M529" s="7">
+        <v>2514.4</v>
+      </c>
+      <c r="N529" s="6">
+        <v>1</v>
+      </c>
+      <c r="O529" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="P529" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q529" s="6">
+        <v>0</v>
+      </c>
+      <c r="R529" s="7">
+        <v>0</v>
+      </c>
+      <c r="S529" s="9">
+        <v>0</v>
+      </c>
+      <c r="T529" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U529" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V529" s="11">
+        <v>11</v>
+      </c>
+      <c r="W529" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X529" s="12">
+        <v>0.40277780000000002</v>
+      </c>
+      <c r="Y529" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z529" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA529" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB529" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC529" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD529" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE529" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF529" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG529" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH529" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI529" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ529" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK529" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL529" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM529" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN529" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO529" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP529" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ529" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR529" s="3" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="530" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A530" s="1">
+        <v>1</v>
+      </c>
+      <c r="B530" s="2">
+        <v>2</v>
+      </c>
+      <c r="C530" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="D530" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E530" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F530" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G530" s="5">
+        <v>22</v>
+      </c>
+      <c r="H530" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I530" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J530" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K530" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L530" s="6">
+        <v>15</v>
+      </c>
+      <c r="M530" s="7">
+        <v>2694</v>
+      </c>
+      <c r="N530" s="6">
+        <v>1</v>
+      </c>
+      <c r="O530" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="P530" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q530" s="6">
+        <v>0</v>
+      </c>
+      <c r="R530" s="7">
+        <v>0</v>
+      </c>
+      <c r="S530" s="9">
+        <v>0</v>
+      </c>
+      <c r="T530" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U530" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V530" s="11">
+        <v>11</v>
+      </c>
+      <c r="W530" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X530" s="12">
+        <v>0.40277780000000002</v>
+      </c>
+      <c r="Y530" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z530" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA530" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB530" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC530" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD530" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE530" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF530" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG530" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH530" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI530" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ530" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK530" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL530" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM530" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN530" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO530" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP530" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ530" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR530" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="531" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A531" s="1">
+        <v>1</v>
+      </c>
+      <c r="B531" s="2">
+        <v>2</v>
+      </c>
+      <c r="C531" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="D531" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E531" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F531" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G531" s="5">
+        <v>23</v>
+      </c>
+      <c r="H531" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I531" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J531" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K531" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L531" s="6">
+        <v>16</v>
+      </c>
+      <c r="M531" s="7">
+        <v>2873.6</v>
+      </c>
+      <c r="N531" s="6">
+        <v>1</v>
+      </c>
+      <c r="O531" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="P531" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q531" s="6">
+        <v>0</v>
+      </c>
+      <c r="R531" s="7">
+        <v>0</v>
+      </c>
+      <c r="S531" s="9">
+        <v>0</v>
+      </c>
+      <c r="T531" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U531" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V531" s="11">
+        <v>11</v>
+      </c>
+      <c r="W531" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X531" s="12">
+        <v>0.40277780000000002</v>
+      </c>
+      <c r="Y531" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z531" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA531" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB531" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC531" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD531" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE531" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF531" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG531" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH531" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI531" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ531" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK531" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL531" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM531" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN531" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO531" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP531" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ531" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR531" s="3" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="532" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A532" s="1">
+        <v>1</v>
+      </c>
+      <c r="B532" s="2">
+        <v>2</v>
+      </c>
+      <c r="C532" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="D532" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E532" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F532" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G532" s="5">
+        <v>24</v>
+      </c>
+      <c r="H532" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I532" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J532" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K532" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L532" s="6">
+        <v>17</v>
+      </c>
+      <c r="M532" s="7">
+        <v>3053.2</v>
+      </c>
+      <c r="N532" s="6">
+        <v>1</v>
+      </c>
+      <c r="O532" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="P532" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q532" s="6">
+        <v>0</v>
+      </c>
+      <c r="R532" s="7">
+        <v>0</v>
+      </c>
+      <c r="S532" s="9">
+        <v>0</v>
+      </c>
+      <c r="T532" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U532" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V532" s="11">
+        <v>11</v>
+      </c>
+      <c r="W532" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X532" s="12">
+        <v>0.42361110000000002</v>
+      </c>
+      <c r="Y532" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z532" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA532" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB532" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC532" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD532" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE532" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF532" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG532" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH532" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI532" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ532" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK532" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL532" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM532" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN532" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO532" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP532" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ532" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR532" s="3" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="533" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A533" s="1">
+        <v>1</v>
+      </c>
+      <c r="B533" s="2">
+        <v>2</v>
+      </c>
+      <c r="C533" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="D533" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E533" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F533" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G533" s="5">
+        <v>25</v>
+      </c>
+      <c r="H533" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I533" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J533" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K533" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L533" s="6">
+        <v>18</v>
+      </c>
+      <c r="M533" s="7">
+        <v>3232.8</v>
+      </c>
+      <c r="N533" s="6">
+        <v>1</v>
+      </c>
+      <c r="O533" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="P533" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q533" s="6">
+        <v>0</v>
+      </c>
+      <c r="R533" s="7">
+        <v>0</v>
+      </c>
+      <c r="S533" s="9">
+        <v>0</v>
+      </c>
+      <c r="T533" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U533" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V533" s="11">
+        <v>11</v>
+      </c>
+      <c r="W533" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X533" s="12">
+        <v>0.42361110000000002</v>
+      </c>
+      <c r="Y533" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z533" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA533" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB533" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC533" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD533" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE533" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF533" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG533" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH533" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI533" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ533" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK533" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL533" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM533" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN533" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO533" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP533" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ533" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR533" s="3" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="534" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A534" s="1">
+        <v>1</v>
+      </c>
+      <c r="B534" s="2">
+        <v>2</v>
+      </c>
+      <c r="C534" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="D534" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E534" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F534" s="4">
+        <v>46286</v>
+      </c>
+      <c r="G534" s="5">
+        <v>28</v>
+      </c>
+      <c r="H534" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I534" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J534" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K534" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L534" s="6">
+        <v>19</v>
+      </c>
+      <c r="M534" s="7">
+        <v>3412.4</v>
+      </c>
+      <c r="N534" s="6">
+        <v>1</v>
+      </c>
+      <c r="O534" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="P534" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q534" s="6">
+        <v>0</v>
+      </c>
+      <c r="R534" s="7">
+        <v>0</v>
+      </c>
+      <c r="S534" s="9">
+        <v>0</v>
+      </c>
+      <c r="T534" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U534" s="10">
+        <v>67522</v>
+      </c>
+      <c r="V534" s="11">
+        <v>11</v>
+      </c>
+      <c r="W534" s="4">
+        <v>46286</v>
+      </c>
+      <c r="X534" s="12">
+        <v>0.48472219999999999</v>
+      </c>
+      <c r="Y534" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z534" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA534" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB534" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC534" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD534" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE534" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF534" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG534" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH534" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI534" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ534" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK534" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL534" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM534" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN534" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO534" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP534" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ534" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR534" s="3" t="s">
+        <v>596</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E589B419-BF85-4E70-AAF1-541DC232E3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{464147C2-9D7B-475C-80ED-5AB2DBCD4618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8194ABE4-7B91-49C3-B513-F9CF7AB13EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2E4AE85-235A-40EB-BBC8-BBA6A3D6D6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2384" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3104" uniqueCount="225">
   <si>
     <t>Sel</t>
   </si>
@@ -575,6 +575,126 @@
   </si>
   <si>
     <t>1881600002757</t>
+  </si>
+  <si>
+    <t>1881600002758</t>
+  </si>
+  <si>
+    <t>1881600002759</t>
+  </si>
+  <si>
+    <t>1881600002760</t>
+  </si>
+  <si>
+    <t>1881600002761</t>
+  </si>
+  <si>
+    <t>1881600002762</t>
+  </si>
+  <si>
+    <t>1881600002763</t>
+  </si>
+  <si>
+    <t>1881600002764</t>
+  </si>
+  <si>
+    <t>1881600002765</t>
+  </si>
+  <si>
+    <t>1881600002766</t>
+  </si>
+  <si>
+    <t>1881600002767</t>
+  </si>
+  <si>
+    <t>1881600002768</t>
+  </si>
+  <si>
+    <t>1881600002769</t>
+  </si>
+  <si>
+    <t>1881600002770</t>
+  </si>
+  <si>
+    <t>1881600002771</t>
+  </si>
+  <si>
+    <t>1881600002772</t>
+  </si>
+  <si>
+    <t>1881600002773</t>
+  </si>
+  <si>
+    <t>1881600002774</t>
+  </si>
+  <si>
+    <t>1881600002775</t>
+  </si>
+  <si>
+    <t>1881600002776</t>
+  </si>
+  <si>
+    <t>1881600002777</t>
+  </si>
+  <si>
+    <t>1881600002778</t>
+  </si>
+  <si>
+    <t>1881600002779</t>
+  </si>
+  <si>
+    <t>1881600002780</t>
+  </si>
+  <si>
+    <t>1881600002781</t>
+  </si>
+  <si>
+    <t>1881600002782</t>
+  </si>
+  <si>
+    <t>1881600002783</t>
+  </si>
+  <si>
+    <t>1881600002784</t>
+  </si>
+  <si>
+    <t>1881600002785</t>
+  </si>
+  <si>
+    <t>1881600002786</t>
+  </si>
+  <si>
+    <t>1881600002787</t>
+  </si>
+  <si>
+    <t>1881600002788</t>
+  </si>
+  <si>
+    <t>1881600002789</t>
+  </si>
+  <si>
+    <t>1881600002790</t>
+  </si>
+  <si>
+    <t>1881600002791</t>
+  </si>
+  <si>
+    <t>1881600002792</t>
+  </si>
+  <si>
+    <t>1881600002793</t>
+  </si>
+  <si>
+    <t>1881600002794</t>
+  </si>
+  <si>
+    <t>1881600002795</t>
+  </si>
+  <si>
+    <t>1881600002796</t>
+  </si>
+  <si>
+    <t>1881600002797</t>
   </si>
 </sst>
 </file>
@@ -1150,7 +1270,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR131"/>
+  <dimension ref="A1:AR171"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -18705,6 +18825,5366 @@
       </c>
       <c r="AR131" s="3" t="s">
         <v>184</v>
+      </c>
+    </row>
+    <row r="132" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>1</v>
+      </c>
+      <c r="B132" s="2">
+        <v>2</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F132" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G132" s="5">
+        <v>131</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J132" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K132" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L132" s="6">
+        <v>543</v>
+      </c>
+      <c r="M132" s="7">
+        <v>95079.17</v>
+      </c>
+      <c r="N132" s="6">
+        <v>1</v>
+      </c>
+      <c r="O132" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P132" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q132" s="6">
+        <v>0</v>
+      </c>
+      <c r="R132" s="7">
+        <v>0</v>
+      </c>
+      <c r="S132" s="9">
+        <v>0</v>
+      </c>
+      <c r="T132" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U132" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V132" s="11">
+        <v>11</v>
+      </c>
+      <c r="W132" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X132" s="12">
+        <v>0.35555560000000003</v>
+      </c>
+      <c r="Y132" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z132" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA132" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB132" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC132" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD132" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE132" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF132" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG132" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH132" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI132" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ132" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK132" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL132" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM132" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN132" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO132" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP132" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ132" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR132" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="133" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>1</v>
+      </c>
+      <c r="B133" s="2">
+        <v>2</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F133" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G133" s="5">
+        <v>132</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I133" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J133" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K133" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L133" s="6">
+        <v>544</v>
+      </c>
+      <c r="M133" s="7">
+        <v>95254.27</v>
+      </c>
+      <c r="N133" s="6">
+        <v>1</v>
+      </c>
+      <c r="O133" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P133" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q133" s="6">
+        <v>0</v>
+      </c>
+      <c r="R133" s="7">
+        <v>0</v>
+      </c>
+      <c r="S133" s="9">
+        <v>0</v>
+      </c>
+      <c r="T133" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U133" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V133" s="11">
+        <v>11</v>
+      </c>
+      <c r="W133" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X133" s="12">
+        <v>0.35555560000000003</v>
+      </c>
+      <c r="Y133" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z133" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA133" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB133" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC133" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD133" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE133" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF133" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG133" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH133" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI133" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ133" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK133" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL133" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM133" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN133" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO133" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP133" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ133" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR133" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="134" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>1</v>
+      </c>
+      <c r="B134" s="2">
+        <v>2</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F134" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G134" s="5">
+        <v>133</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J134" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K134" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L134" s="6">
+        <v>545</v>
+      </c>
+      <c r="M134" s="7">
+        <v>95429.37</v>
+      </c>
+      <c r="N134" s="6">
+        <v>1</v>
+      </c>
+      <c r="O134" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P134" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q134" s="6">
+        <v>0</v>
+      </c>
+      <c r="R134" s="7">
+        <v>0</v>
+      </c>
+      <c r="S134" s="9">
+        <v>0</v>
+      </c>
+      <c r="T134" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U134" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V134" s="11">
+        <v>11</v>
+      </c>
+      <c r="W134" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X134" s="12">
+        <v>0.35555560000000003</v>
+      </c>
+      <c r="Y134" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z134" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA134" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB134" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC134" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD134" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE134" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF134" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG134" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH134" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI134" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ134" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK134" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL134" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM134" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN134" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO134" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP134" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ134" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR134" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="135" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>1</v>
+      </c>
+      <c r="B135" s="2">
+        <v>2</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F135" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G135" s="5">
+        <v>134</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I135" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J135" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K135" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L135" s="6">
+        <v>546</v>
+      </c>
+      <c r="M135" s="7">
+        <v>95604.47</v>
+      </c>
+      <c r="N135" s="6">
+        <v>1</v>
+      </c>
+      <c r="O135" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P135" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q135" s="6">
+        <v>0</v>
+      </c>
+      <c r="R135" s="7">
+        <v>0</v>
+      </c>
+      <c r="S135" s="9">
+        <v>0</v>
+      </c>
+      <c r="T135" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U135" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V135" s="11">
+        <v>11</v>
+      </c>
+      <c r="W135" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X135" s="12">
+        <v>0.35555560000000003</v>
+      </c>
+      <c r="Y135" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z135" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA135" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB135" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC135" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD135" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE135" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF135" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG135" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH135" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI135" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ135" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK135" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL135" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM135" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN135" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO135" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP135" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ135" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR135" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="136" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>1</v>
+      </c>
+      <c r="B136" s="2">
+        <v>2</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F136" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G136" s="5">
+        <v>135</v>
+      </c>
+      <c r="H136" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J136" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K136" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L136" s="6">
+        <v>547</v>
+      </c>
+      <c r="M136" s="7">
+        <v>95779.57</v>
+      </c>
+      <c r="N136" s="6">
+        <v>1</v>
+      </c>
+      <c r="O136" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P136" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q136" s="6">
+        <v>0</v>
+      </c>
+      <c r="R136" s="7">
+        <v>0</v>
+      </c>
+      <c r="S136" s="9">
+        <v>0</v>
+      </c>
+      <c r="T136" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U136" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V136" s="11">
+        <v>11</v>
+      </c>
+      <c r="W136" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X136" s="12">
+        <v>0.35555560000000003</v>
+      </c>
+      <c r="Y136" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA136" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB136" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC136" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD136" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE136" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF136" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG136" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH136" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI136" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ136" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK136" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL136" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM136" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN136" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO136" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP136" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ136" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR136" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="137" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>1</v>
+      </c>
+      <c r="B137" s="2">
+        <v>2</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F137" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G137" s="5">
+        <v>136</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J137" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K137" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L137" s="6">
+        <v>548</v>
+      </c>
+      <c r="M137" s="7">
+        <v>95954.67</v>
+      </c>
+      <c r="N137" s="6">
+        <v>1</v>
+      </c>
+      <c r="O137" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P137" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q137" s="6">
+        <v>0</v>
+      </c>
+      <c r="R137" s="7">
+        <v>0</v>
+      </c>
+      <c r="S137" s="9">
+        <v>0</v>
+      </c>
+      <c r="T137" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U137" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V137" s="11">
+        <v>11</v>
+      </c>
+      <c r="W137" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X137" s="12">
+        <v>0.35555560000000003</v>
+      </c>
+      <c r="Y137" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z137" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA137" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB137" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC137" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD137" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE137" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF137" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG137" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH137" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI137" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ137" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK137" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL137" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM137" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN137" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO137" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP137" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ137" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR137" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="138" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>1</v>
+      </c>
+      <c r="B138" s="2">
+        <v>2</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F138" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G138" s="5">
+        <v>137</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J138" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K138" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L138" s="6">
+        <v>549</v>
+      </c>
+      <c r="M138" s="7">
+        <v>96129.77</v>
+      </c>
+      <c r="N138" s="6">
+        <v>1</v>
+      </c>
+      <c r="O138" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P138" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q138" s="6">
+        <v>0</v>
+      </c>
+      <c r="R138" s="7">
+        <v>0</v>
+      </c>
+      <c r="S138" s="9">
+        <v>0</v>
+      </c>
+      <c r="T138" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U138" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V138" s="11">
+        <v>11</v>
+      </c>
+      <c r="W138" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X138" s="12">
+        <v>0.35555560000000003</v>
+      </c>
+      <c r="Y138" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z138" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA138" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB138" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC138" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD138" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE138" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF138" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG138" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH138" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI138" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ138" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK138" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL138" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM138" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN138" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO138" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP138" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ138" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR138" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="139" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>1</v>
+      </c>
+      <c r="B139" s="2">
+        <v>2</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F139" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G139" s="5">
+        <v>138</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J139" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K139" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L139" s="6">
+        <v>550</v>
+      </c>
+      <c r="M139" s="7">
+        <v>96304.87</v>
+      </c>
+      <c r="N139" s="6">
+        <v>1</v>
+      </c>
+      <c r="O139" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P139" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q139" s="6">
+        <v>0</v>
+      </c>
+      <c r="R139" s="7">
+        <v>0</v>
+      </c>
+      <c r="S139" s="9">
+        <v>0</v>
+      </c>
+      <c r="T139" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U139" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V139" s="11">
+        <v>11</v>
+      </c>
+      <c r="W139" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X139" s="12">
+        <v>0.35555560000000003</v>
+      </c>
+      <c r="Y139" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z139" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA139" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB139" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC139" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD139" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE139" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF139" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG139" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH139" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI139" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ139" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK139" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL139" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM139" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN139" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO139" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP139" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ139" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR139" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="140" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>1</v>
+      </c>
+      <c r="B140" s="2">
+        <v>2</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F140" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G140" s="5">
+        <v>139</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J140" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K140" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L140" s="6">
+        <v>551</v>
+      </c>
+      <c r="M140" s="7">
+        <v>96479.97</v>
+      </c>
+      <c r="N140" s="6">
+        <v>1</v>
+      </c>
+      <c r="O140" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P140" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q140" s="6">
+        <v>0</v>
+      </c>
+      <c r="R140" s="7">
+        <v>0</v>
+      </c>
+      <c r="S140" s="9">
+        <v>0</v>
+      </c>
+      <c r="T140" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U140" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V140" s="11">
+        <v>11</v>
+      </c>
+      <c r="W140" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X140" s="12">
+        <v>0.35555560000000003</v>
+      </c>
+      <c r="Y140" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z140" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA140" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB140" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC140" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD140" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE140" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF140" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG140" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH140" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI140" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ140" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK140" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL140" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM140" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN140" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO140" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP140" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ140" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR140" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="141" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>1</v>
+      </c>
+      <c r="B141" s="2">
+        <v>2</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F141" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G141" s="5">
+        <v>140</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J141" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K141" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L141" s="6">
+        <v>552</v>
+      </c>
+      <c r="M141" s="7">
+        <v>96655.07</v>
+      </c>
+      <c r="N141" s="6">
+        <v>1</v>
+      </c>
+      <c r="O141" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P141" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>0</v>
+      </c>
+      <c r="R141" s="7">
+        <v>0</v>
+      </c>
+      <c r="S141" s="9">
+        <v>0</v>
+      </c>
+      <c r="T141" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U141" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V141" s="11">
+        <v>11</v>
+      </c>
+      <c r="W141" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X141" s="12">
+        <v>0.35555560000000003</v>
+      </c>
+      <c r="Y141" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB141" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC141" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD141" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE141" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF141" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG141" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH141" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI141" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ141" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK141" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL141" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM141" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN141" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO141" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP141" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ141" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR141" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="142" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
+        <v>1</v>
+      </c>
+      <c r="B142" s="2">
+        <v>2</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F142" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G142" s="5">
+        <v>141</v>
+      </c>
+      <c r="H142" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J142" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K142" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L142" s="6">
+        <v>553</v>
+      </c>
+      <c r="M142" s="7">
+        <v>96830.17</v>
+      </c>
+      <c r="N142" s="6">
+        <v>1</v>
+      </c>
+      <c r="O142" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P142" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q142" s="6">
+        <v>0</v>
+      </c>
+      <c r="R142" s="7">
+        <v>0</v>
+      </c>
+      <c r="S142" s="9">
+        <v>0</v>
+      </c>
+      <c r="T142" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U142" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V142" s="11">
+        <v>11</v>
+      </c>
+      <c r="W142" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X142" s="12">
+        <v>0.35555560000000003</v>
+      </c>
+      <c r="Y142" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z142" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA142" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB142" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC142" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD142" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE142" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF142" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG142" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH142" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI142" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ142" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK142" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL142" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM142" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN142" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO142" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP142" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ142" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR142" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="143" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
+        <v>1</v>
+      </c>
+      <c r="B143" s="2">
+        <v>2</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F143" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G143" s="5">
+        <v>142</v>
+      </c>
+      <c r="H143" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J143" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K143" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L143" s="6">
+        <v>554</v>
+      </c>
+      <c r="M143" s="7">
+        <v>97005.27</v>
+      </c>
+      <c r="N143" s="6">
+        <v>1</v>
+      </c>
+      <c r="O143" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P143" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q143" s="6">
+        <v>0</v>
+      </c>
+      <c r="R143" s="7">
+        <v>0</v>
+      </c>
+      <c r="S143" s="9">
+        <v>0</v>
+      </c>
+      <c r="T143" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U143" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V143" s="11">
+        <v>11</v>
+      </c>
+      <c r="W143" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X143" s="12">
+        <v>0.35555560000000003</v>
+      </c>
+      <c r="Y143" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z143" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA143" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB143" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC143" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD143" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE143" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF143" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG143" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH143" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI143" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ143" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK143" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL143" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM143" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN143" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO143" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP143" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ143" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR143" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="144" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A144" s="1">
+        <v>1</v>
+      </c>
+      <c r="B144" s="2">
+        <v>2</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F144" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G144" s="5">
+        <v>143</v>
+      </c>
+      <c r="H144" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J144" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K144" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L144" s="6">
+        <v>555</v>
+      </c>
+      <c r="M144" s="7">
+        <v>97180.37</v>
+      </c>
+      <c r="N144" s="6">
+        <v>1</v>
+      </c>
+      <c r="O144" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P144" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q144" s="6">
+        <v>0</v>
+      </c>
+      <c r="R144" s="7">
+        <v>0</v>
+      </c>
+      <c r="S144" s="9">
+        <v>0</v>
+      </c>
+      <c r="T144" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U144" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V144" s="11">
+        <v>11</v>
+      </c>
+      <c r="W144" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X144" s="12">
+        <v>0.35555560000000003</v>
+      </c>
+      <c r="Y144" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z144" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA144" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB144" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC144" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD144" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE144" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF144" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG144" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH144" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI144" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ144" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK144" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL144" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM144" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN144" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO144" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP144" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ144" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR144" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="145" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A145" s="1">
+        <v>1</v>
+      </c>
+      <c r="B145" s="2">
+        <v>2</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F145" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G145" s="5">
+        <v>144</v>
+      </c>
+      <c r="H145" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J145" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K145" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L145" s="6">
+        <v>556</v>
+      </c>
+      <c r="M145" s="7">
+        <v>97355.47</v>
+      </c>
+      <c r="N145" s="6">
+        <v>1</v>
+      </c>
+      <c r="O145" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P145" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q145" s="6">
+        <v>0</v>
+      </c>
+      <c r="R145" s="7">
+        <v>0</v>
+      </c>
+      <c r="S145" s="9">
+        <v>0</v>
+      </c>
+      <c r="T145" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U145" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V145" s="11">
+        <v>11</v>
+      </c>
+      <c r="W145" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X145" s="12">
+        <v>0.35555560000000003</v>
+      </c>
+      <c r="Y145" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z145" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA145" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB145" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC145" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD145" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE145" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF145" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG145" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH145" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI145" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ145" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK145" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL145" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM145" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN145" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO145" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP145" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ145" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR145" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="146" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>1</v>
+      </c>
+      <c r="B146" s="2">
+        <v>2</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F146" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G146" s="5">
+        <v>145</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J146" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K146" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L146" s="6">
+        <v>557</v>
+      </c>
+      <c r="M146" s="7">
+        <v>97530.57</v>
+      </c>
+      <c r="N146" s="6">
+        <v>1</v>
+      </c>
+      <c r="O146" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P146" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q146" s="6">
+        <v>0</v>
+      </c>
+      <c r="R146" s="7">
+        <v>0</v>
+      </c>
+      <c r="S146" s="9">
+        <v>0</v>
+      </c>
+      <c r="T146" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U146" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V146" s="11">
+        <v>11</v>
+      </c>
+      <c r="W146" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X146" s="12">
+        <v>0.35555560000000003</v>
+      </c>
+      <c r="Y146" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z146" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA146" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB146" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC146" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD146" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE146" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF146" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG146" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH146" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI146" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ146" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK146" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL146" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM146" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN146" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO146" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP146" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ146" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR146" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="147" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>1</v>
+      </c>
+      <c r="B147" s="2">
+        <v>2</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F147" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G147" s="5">
+        <v>146</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J147" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K147" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L147" s="6">
+        <v>558</v>
+      </c>
+      <c r="M147" s="7">
+        <v>97705.67</v>
+      </c>
+      <c r="N147" s="6">
+        <v>1</v>
+      </c>
+      <c r="O147" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P147" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q147" s="6">
+        <v>0</v>
+      </c>
+      <c r="R147" s="7">
+        <v>0</v>
+      </c>
+      <c r="S147" s="9">
+        <v>0</v>
+      </c>
+      <c r="T147" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U147" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V147" s="11">
+        <v>11</v>
+      </c>
+      <c r="W147" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X147" s="12">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="Y147" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z147" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA147" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB147" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC147" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD147" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE147" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF147" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG147" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH147" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI147" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ147" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK147" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL147" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM147" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN147" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO147" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP147" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ147" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR147" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="148" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>1</v>
+      </c>
+      <c r="B148" s="2">
+        <v>2</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F148" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G148" s="5">
+        <v>147</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I148" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J148" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K148" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L148" s="6">
+        <v>559</v>
+      </c>
+      <c r="M148" s="7">
+        <v>97880.76</v>
+      </c>
+      <c r="N148" s="6">
+        <v>1</v>
+      </c>
+      <c r="O148" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P148" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q148" s="6">
+        <v>0</v>
+      </c>
+      <c r="R148" s="7">
+        <v>0</v>
+      </c>
+      <c r="S148" s="9">
+        <v>0</v>
+      </c>
+      <c r="T148" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U148" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V148" s="11">
+        <v>11</v>
+      </c>
+      <c r="W148" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X148" s="12">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="Y148" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z148" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA148" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB148" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC148" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD148" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE148" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF148" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG148" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH148" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI148" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ148" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK148" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL148" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM148" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN148" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO148" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP148" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ148" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR148" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="149" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>1</v>
+      </c>
+      <c r="B149" s="2">
+        <v>2</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F149" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G149" s="5">
+        <v>148</v>
+      </c>
+      <c r="H149" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I149" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J149" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K149" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L149" s="6">
+        <v>560</v>
+      </c>
+      <c r="M149" s="7">
+        <v>98055.86</v>
+      </c>
+      <c r="N149" s="6">
+        <v>1</v>
+      </c>
+      <c r="O149" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P149" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q149" s="6">
+        <v>0</v>
+      </c>
+      <c r="R149" s="7">
+        <v>0</v>
+      </c>
+      <c r="S149" s="9">
+        <v>0</v>
+      </c>
+      <c r="T149" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U149" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V149" s="11">
+        <v>11</v>
+      </c>
+      <c r="W149" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X149" s="12">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="Y149" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z149" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA149" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB149" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC149" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD149" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE149" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF149" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG149" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH149" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI149" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ149" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK149" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL149" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM149" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN149" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO149" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP149" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ149" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR149" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="150" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>1</v>
+      </c>
+      <c r="B150" s="2">
+        <v>2</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F150" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G150" s="5">
+        <v>149</v>
+      </c>
+      <c r="H150" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J150" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K150" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L150" s="6">
+        <v>561</v>
+      </c>
+      <c r="M150" s="7">
+        <v>98230.96</v>
+      </c>
+      <c r="N150" s="6">
+        <v>1</v>
+      </c>
+      <c r="O150" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P150" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q150" s="6">
+        <v>0</v>
+      </c>
+      <c r="R150" s="7">
+        <v>0</v>
+      </c>
+      <c r="S150" s="9">
+        <v>0</v>
+      </c>
+      <c r="T150" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U150" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V150" s="11">
+        <v>11</v>
+      </c>
+      <c r="W150" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X150" s="12">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="Y150" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z150" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA150" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB150" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC150" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD150" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE150" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF150" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG150" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH150" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI150" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ150" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK150" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL150" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM150" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN150" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO150" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP150" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ150" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR150" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="151" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>1</v>
+      </c>
+      <c r="B151" s="2">
+        <v>2</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F151" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G151" s="5">
+        <v>150</v>
+      </c>
+      <c r="H151" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I151" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J151" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K151" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L151" s="6">
+        <v>562</v>
+      </c>
+      <c r="M151" s="7">
+        <v>98406.06</v>
+      </c>
+      <c r="N151" s="6">
+        <v>1</v>
+      </c>
+      <c r="O151" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P151" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>0</v>
+      </c>
+      <c r="R151" s="7">
+        <v>0</v>
+      </c>
+      <c r="S151" s="9">
+        <v>0</v>
+      </c>
+      <c r="T151" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U151" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V151" s="11">
+        <v>11</v>
+      </c>
+      <c r="W151" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X151" s="12">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="Y151" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB151" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE151" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF151" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI151" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ151" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK151" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL151" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO151" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP151" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ151" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR151" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="152" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A152" s="1">
+        <v>1</v>
+      </c>
+      <c r="B152" s="2">
+        <v>2</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F152" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G152" s="5">
+        <v>151</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I152" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J152" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K152" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L152" s="6">
+        <v>563</v>
+      </c>
+      <c r="M152" s="7">
+        <v>98581.16</v>
+      </c>
+      <c r="N152" s="6">
+        <v>1</v>
+      </c>
+      <c r="O152" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P152" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q152" s="6">
+        <v>0</v>
+      </c>
+      <c r="R152" s="7">
+        <v>0</v>
+      </c>
+      <c r="S152" s="9">
+        <v>0</v>
+      </c>
+      <c r="T152" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U152" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V152" s="11">
+        <v>11</v>
+      </c>
+      <c r="W152" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X152" s="12">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="Y152" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z152" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA152" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB152" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC152" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD152" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE152" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF152" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG152" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH152" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI152" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ152" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK152" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL152" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM152" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN152" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO152" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP152" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ152" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR152" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="153" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A153" s="1">
+        <v>1</v>
+      </c>
+      <c r="B153" s="2">
+        <v>2</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F153" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G153" s="5">
+        <v>152</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I153" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J153" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K153" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L153" s="6">
+        <v>564</v>
+      </c>
+      <c r="M153" s="7">
+        <v>98756.26</v>
+      </c>
+      <c r="N153" s="6">
+        <v>1</v>
+      </c>
+      <c r="O153" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P153" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q153" s="6">
+        <v>0</v>
+      </c>
+      <c r="R153" s="7">
+        <v>0</v>
+      </c>
+      <c r="S153" s="9">
+        <v>0</v>
+      </c>
+      <c r="T153" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U153" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V153" s="11">
+        <v>11</v>
+      </c>
+      <c r="W153" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X153" s="12">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="Y153" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z153" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA153" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB153" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC153" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD153" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE153" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF153" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG153" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH153" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI153" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ153" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK153" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL153" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM153" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN153" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO153" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP153" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ153" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR153" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="154" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A154" s="1">
+        <v>1</v>
+      </c>
+      <c r="B154" s="2">
+        <v>2</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F154" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G154" s="5">
+        <v>153</v>
+      </c>
+      <c r="H154" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I154" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J154" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K154" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L154" s="6">
+        <v>565</v>
+      </c>
+      <c r="M154" s="7">
+        <v>98931.36</v>
+      </c>
+      <c r="N154" s="6">
+        <v>1</v>
+      </c>
+      <c r="O154" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P154" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q154" s="6">
+        <v>0</v>
+      </c>
+      <c r="R154" s="7">
+        <v>0</v>
+      </c>
+      <c r="S154" s="9">
+        <v>0</v>
+      </c>
+      <c r="T154" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U154" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V154" s="11">
+        <v>11</v>
+      </c>
+      <c r="W154" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X154" s="12">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="Y154" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB154" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF154" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG154" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH154" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI154" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ154" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK154" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM154" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN154" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO154" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP154" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ154" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR154" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="155" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A155" s="1">
+        <v>1</v>
+      </c>
+      <c r="B155" s="2">
+        <v>2</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F155" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G155" s="5">
+        <v>154</v>
+      </c>
+      <c r="H155" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I155" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J155" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K155" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L155" s="6">
+        <v>566</v>
+      </c>
+      <c r="M155" s="7">
+        <v>99106.46</v>
+      </c>
+      <c r="N155" s="6">
+        <v>1</v>
+      </c>
+      <c r="O155" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P155" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q155" s="6">
+        <v>0</v>
+      </c>
+      <c r="R155" s="7">
+        <v>0</v>
+      </c>
+      <c r="S155" s="9">
+        <v>0</v>
+      </c>
+      <c r="T155" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U155" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V155" s="11">
+        <v>11</v>
+      </c>
+      <c r="W155" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X155" s="12">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="Y155" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z155" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA155" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB155" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC155" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD155" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE155" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF155" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG155" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH155" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI155" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ155" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK155" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL155" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM155" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN155" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO155" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP155" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ155" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR155" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="156" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A156" s="1">
+        <v>1</v>
+      </c>
+      <c r="B156" s="2">
+        <v>2</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F156" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G156" s="5">
+        <v>155</v>
+      </c>
+      <c r="H156" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I156" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J156" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K156" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L156" s="6">
+        <v>567</v>
+      </c>
+      <c r="M156" s="7">
+        <v>99281.56</v>
+      </c>
+      <c r="N156" s="6">
+        <v>1</v>
+      </c>
+      <c r="O156" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P156" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q156" s="6">
+        <v>0</v>
+      </c>
+      <c r="R156" s="7">
+        <v>0</v>
+      </c>
+      <c r="S156" s="9">
+        <v>0</v>
+      </c>
+      <c r="T156" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U156" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V156" s="11">
+        <v>11</v>
+      </c>
+      <c r="W156" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X156" s="12">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="Y156" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z156" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA156" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB156" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC156" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD156" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE156" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF156" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG156" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH156" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI156" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ156" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK156" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL156" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM156" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN156" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO156" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP156" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ156" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR156" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="157" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A157" s="1">
+        <v>1</v>
+      </c>
+      <c r="B157" s="2">
+        <v>2</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F157" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G157" s="5">
+        <v>156</v>
+      </c>
+      <c r="H157" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I157" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J157" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K157" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L157" s="6">
+        <v>568</v>
+      </c>
+      <c r="M157" s="7">
+        <v>99456.66</v>
+      </c>
+      <c r="N157" s="6">
+        <v>1</v>
+      </c>
+      <c r="O157" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P157" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>0</v>
+      </c>
+      <c r="R157" s="7">
+        <v>0</v>
+      </c>
+      <c r="S157" s="9">
+        <v>0</v>
+      </c>
+      <c r="T157" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U157" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V157" s="11">
+        <v>11</v>
+      </c>
+      <c r="W157" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X157" s="12">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="Y157" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB157" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE157" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF157" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG157" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI157" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ157" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK157" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL157" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO157" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP157" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ157" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR157" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="158" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A158" s="1">
+        <v>1</v>
+      </c>
+      <c r="B158" s="2">
+        <v>2</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F158" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G158" s="5">
+        <v>157</v>
+      </c>
+      <c r="H158" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I158" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J158" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K158" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L158" s="6">
+        <v>569</v>
+      </c>
+      <c r="M158" s="7">
+        <v>99631.76</v>
+      </c>
+      <c r="N158" s="6">
+        <v>1</v>
+      </c>
+      <c r="O158" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P158" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>0</v>
+      </c>
+      <c r="R158" s="7">
+        <v>0</v>
+      </c>
+      <c r="S158" s="9">
+        <v>0</v>
+      </c>
+      <c r="T158" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U158" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V158" s="11">
+        <v>11</v>
+      </c>
+      <c r="W158" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X158" s="12">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="Y158" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE158" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF158" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI158" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ158" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK158" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO158" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP158" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ158" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR158" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="159" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A159" s="1">
+        <v>1</v>
+      </c>
+      <c r="B159" s="2">
+        <v>2</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F159" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G159" s="5">
+        <v>158</v>
+      </c>
+      <c r="H159" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I159" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J159" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K159" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L159" s="6">
+        <v>570</v>
+      </c>
+      <c r="M159" s="7">
+        <v>99806.86</v>
+      </c>
+      <c r="N159" s="6">
+        <v>1</v>
+      </c>
+      <c r="O159" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P159" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q159" s="6">
+        <v>0</v>
+      </c>
+      <c r="R159" s="7">
+        <v>0</v>
+      </c>
+      <c r="S159" s="9">
+        <v>0</v>
+      </c>
+      <c r="T159" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U159" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V159" s="11">
+        <v>11</v>
+      </c>
+      <c r="W159" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X159" s="12">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="Y159" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z159" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA159" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB159" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC159" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD159" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE159" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF159" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG159" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH159" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI159" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ159" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK159" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL159" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM159" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN159" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO159" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP159" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ159" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR159" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="160" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A160" s="1">
+        <v>1</v>
+      </c>
+      <c r="B160" s="2">
+        <v>2</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F160" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G160" s="5">
+        <v>159</v>
+      </c>
+      <c r="H160" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I160" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J160" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K160" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L160" s="6">
+        <v>571</v>
+      </c>
+      <c r="M160" s="7">
+        <v>99981.96</v>
+      </c>
+      <c r="N160" s="6">
+        <v>1</v>
+      </c>
+      <c r="O160" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P160" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q160" s="6">
+        <v>0</v>
+      </c>
+      <c r="R160" s="7">
+        <v>0</v>
+      </c>
+      <c r="S160" s="9">
+        <v>0</v>
+      </c>
+      <c r="T160" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U160" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V160" s="11">
+        <v>11</v>
+      </c>
+      <c r="W160" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X160" s="12">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="Y160" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z160" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA160" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB160" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC160" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD160" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE160" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF160" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG160" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH160" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI160" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ160" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK160" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL160" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM160" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN160" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO160" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP160" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ160" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR160" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="161" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A161" s="1">
+        <v>1</v>
+      </c>
+      <c r="B161" s="2">
+        <v>2</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F161" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G161" s="5">
+        <v>160</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I161" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J161" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K161" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L161" s="6">
+        <v>572</v>
+      </c>
+      <c r="M161" s="7">
+        <v>100157.06</v>
+      </c>
+      <c r="N161" s="6">
+        <v>1</v>
+      </c>
+      <c r="O161" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P161" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q161" s="6">
+        <v>0</v>
+      </c>
+      <c r="R161" s="7">
+        <v>0</v>
+      </c>
+      <c r="S161" s="9">
+        <v>0</v>
+      </c>
+      <c r="T161" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U161" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V161" s="11">
+        <v>11</v>
+      </c>
+      <c r="W161" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X161" s="12">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="Y161" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z161" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA161" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB161" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC161" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD161" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE161" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF161" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG161" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH161" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI161" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ161" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK161" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL161" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM161" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN161" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO161" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP161" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ161" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR161" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="162" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A162" s="1">
+        <v>1</v>
+      </c>
+      <c r="B162" s="2">
+        <v>2</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F162" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G162" s="5">
+        <v>161</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I162" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J162" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K162" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L162" s="6">
+        <v>573</v>
+      </c>
+      <c r="M162" s="7">
+        <v>100332.16</v>
+      </c>
+      <c r="N162" s="6">
+        <v>1</v>
+      </c>
+      <c r="O162" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P162" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q162" s="6">
+        <v>0</v>
+      </c>
+      <c r="R162" s="7">
+        <v>0</v>
+      </c>
+      <c r="S162" s="9">
+        <v>0</v>
+      </c>
+      <c r="T162" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U162" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V162" s="11">
+        <v>11</v>
+      </c>
+      <c r="W162" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X162" s="12">
+        <v>0.36944440000000001</v>
+      </c>
+      <c r="Y162" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z162" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB162" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC162" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD162" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE162" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF162" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG162" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH162" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI162" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ162" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK162" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL162" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM162" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN162" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO162" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP162" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ162" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR162" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="163" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A163" s="1">
+        <v>1</v>
+      </c>
+      <c r="B163" s="2">
+        <v>2</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F163" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G163" s="5">
+        <v>162</v>
+      </c>
+      <c r="H163" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I163" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J163" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K163" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L163" s="6">
+        <v>574</v>
+      </c>
+      <c r="M163" s="7">
+        <v>100507.26</v>
+      </c>
+      <c r="N163" s="6">
+        <v>1</v>
+      </c>
+      <c r="O163" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P163" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q163" s="6">
+        <v>0</v>
+      </c>
+      <c r="R163" s="7">
+        <v>0</v>
+      </c>
+      <c r="S163" s="9">
+        <v>0</v>
+      </c>
+      <c r="T163" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U163" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V163" s="11">
+        <v>11</v>
+      </c>
+      <c r="W163" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X163" s="12">
+        <v>0.36944440000000001</v>
+      </c>
+      <c r="Y163" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z163" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA163" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB163" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC163" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD163" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE163" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF163" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG163" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH163" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI163" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ163" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK163" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL163" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM163" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN163" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO163" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP163" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ163" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR163" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="164" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A164" s="1">
+        <v>1</v>
+      </c>
+      <c r="B164" s="2">
+        <v>2</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F164" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G164" s="5">
+        <v>163</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I164" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J164" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K164" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L164" s="6">
+        <v>575</v>
+      </c>
+      <c r="M164" s="7">
+        <v>100682.36</v>
+      </c>
+      <c r="N164" s="6">
+        <v>1</v>
+      </c>
+      <c r="O164" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P164" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q164" s="6">
+        <v>0</v>
+      </c>
+      <c r="R164" s="7">
+        <v>0</v>
+      </c>
+      <c r="S164" s="9">
+        <v>0</v>
+      </c>
+      <c r="T164" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U164" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V164" s="11">
+        <v>11</v>
+      </c>
+      <c r="W164" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X164" s="12">
+        <v>0.36944440000000001</v>
+      </c>
+      <c r="Y164" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z164" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA164" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB164" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC164" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD164" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE164" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF164" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG164" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH164" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI164" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ164" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK164" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL164" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM164" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN164" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO164" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP164" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ164" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR164" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="165" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A165" s="1">
+        <v>1</v>
+      </c>
+      <c r="B165" s="2">
+        <v>2</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F165" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G165" s="5">
+        <v>164</v>
+      </c>
+      <c r="H165" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I165" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J165" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K165" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L165" s="6">
+        <v>576</v>
+      </c>
+      <c r="M165" s="7">
+        <v>100857.46</v>
+      </c>
+      <c r="N165" s="6">
+        <v>1</v>
+      </c>
+      <c r="O165" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P165" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>0</v>
+      </c>
+      <c r="R165" s="7">
+        <v>0</v>
+      </c>
+      <c r="S165" s="9">
+        <v>0</v>
+      </c>
+      <c r="T165" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U165" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V165" s="11">
+        <v>11</v>
+      </c>
+      <c r="W165" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X165" s="12">
+        <v>0.36944440000000001</v>
+      </c>
+      <c r="Y165" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE165" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF165" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG165" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI165" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ165" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK165" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL165" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN165" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO165" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP165" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ165" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR165" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="166" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A166" s="1">
+        <v>1</v>
+      </c>
+      <c r="B166" s="2">
+        <v>2</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F166" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G166" s="5">
+        <v>165</v>
+      </c>
+      <c r="H166" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I166" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J166" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K166" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L166" s="6">
+        <v>577</v>
+      </c>
+      <c r="M166" s="7">
+        <v>101032.56</v>
+      </c>
+      <c r="N166" s="6">
+        <v>1</v>
+      </c>
+      <c r="O166" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P166" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q166" s="6">
+        <v>0</v>
+      </c>
+      <c r="R166" s="7">
+        <v>0</v>
+      </c>
+      <c r="S166" s="9">
+        <v>0</v>
+      </c>
+      <c r="T166" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U166" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V166" s="11">
+        <v>11</v>
+      </c>
+      <c r="W166" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X166" s="12">
+        <v>0.36944440000000001</v>
+      </c>
+      <c r="Y166" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z166" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA166" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB166" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC166" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD166" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE166" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF166" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG166" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH166" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI166" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ166" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK166" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL166" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM166" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN166" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO166" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP166" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ166" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR166" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="167" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A167" s="1">
+        <v>1</v>
+      </c>
+      <c r="B167" s="2">
+        <v>2</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F167" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G167" s="5">
+        <v>166</v>
+      </c>
+      <c r="H167" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I167" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J167" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K167" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L167" s="6">
+        <v>578</v>
+      </c>
+      <c r="M167" s="7">
+        <v>101207.66</v>
+      </c>
+      <c r="N167" s="6">
+        <v>1</v>
+      </c>
+      <c r="O167" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P167" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q167" s="6">
+        <v>0</v>
+      </c>
+      <c r="R167" s="7">
+        <v>0</v>
+      </c>
+      <c r="S167" s="9">
+        <v>0</v>
+      </c>
+      <c r="T167" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U167" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V167" s="11">
+        <v>11</v>
+      </c>
+      <c r="W167" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X167" s="12">
+        <v>0.36944440000000001</v>
+      </c>
+      <c r="Y167" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z167" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA167" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB167" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC167" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD167" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE167" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF167" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG167" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH167" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI167" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ167" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK167" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL167" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM167" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN167" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO167" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP167" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ167" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR167" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="168" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A168" s="1">
+        <v>1</v>
+      </c>
+      <c r="B168" s="2">
+        <v>2</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F168" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G168" s="5">
+        <v>167</v>
+      </c>
+      <c r="H168" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I168" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J168" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K168" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L168" s="6">
+        <v>579</v>
+      </c>
+      <c r="M168" s="7">
+        <v>101382.76</v>
+      </c>
+      <c r="N168" s="6">
+        <v>1</v>
+      </c>
+      <c r="O168" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P168" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q168" s="6">
+        <v>0</v>
+      </c>
+      <c r="R168" s="7">
+        <v>0</v>
+      </c>
+      <c r="S168" s="9">
+        <v>0</v>
+      </c>
+      <c r="T168" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U168" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V168" s="11">
+        <v>11</v>
+      </c>
+      <c r="W168" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X168" s="12">
+        <v>0.36944440000000001</v>
+      </c>
+      <c r="Y168" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z168" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA168" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB168" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC168" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD168" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE168" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF168" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG168" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH168" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI168" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ168" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK168" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL168" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM168" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN168" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO168" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP168" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ168" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR168" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="169" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A169" s="1">
+        <v>1</v>
+      </c>
+      <c r="B169" s="2">
+        <v>2</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F169" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G169" s="5">
+        <v>168</v>
+      </c>
+      <c r="H169" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I169" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J169" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K169" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L169" s="6">
+        <v>580</v>
+      </c>
+      <c r="M169" s="7">
+        <v>101557.86</v>
+      </c>
+      <c r="N169" s="6">
+        <v>1</v>
+      </c>
+      <c r="O169" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P169" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q169" s="6">
+        <v>0</v>
+      </c>
+      <c r="R169" s="7">
+        <v>0</v>
+      </c>
+      <c r="S169" s="9">
+        <v>0</v>
+      </c>
+      <c r="T169" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U169" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V169" s="11">
+        <v>11</v>
+      </c>
+      <c r="W169" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X169" s="12">
+        <v>0.36944440000000001</v>
+      </c>
+      <c r="Y169" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z169" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA169" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB169" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC169" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD169" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE169" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF169" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG169" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH169" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI169" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ169" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK169" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL169" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM169" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN169" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO169" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP169" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ169" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR169" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="170" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A170" s="1">
+        <v>1</v>
+      </c>
+      <c r="B170" s="2">
+        <v>2</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F170" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G170" s="5">
+        <v>169</v>
+      </c>
+      <c r="H170" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I170" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J170" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K170" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L170" s="6">
+        <v>581</v>
+      </c>
+      <c r="M170" s="7">
+        <v>101732.96</v>
+      </c>
+      <c r="N170" s="6">
+        <v>1</v>
+      </c>
+      <c r="O170" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P170" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q170" s="6">
+        <v>0</v>
+      </c>
+      <c r="R170" s="7">
+        <v>0</v>
+      </c>
+      <c r="S170" s="9">
+        <v>0</v>
+      </c>
+      <c r="T170" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U170" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V170" s="11">
+        <v>11</v>
+      </c>
+      <c r="W170" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X170" s="12">
+        <v>0.36944440000000001</v>
+      </c>
+      <c r="Y170" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z170" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA170" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB170" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC170" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD170" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE170" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF170" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG170" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH170" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI170" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ170" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK170" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL170" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM170" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN170" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO170" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP170" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ170" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR170" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="171" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A171" s="1">
+        <v>1</v>
+      </c>
+      <c r="B171" s="2">
+        <v>2</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F171" s="4">
+        <v>46293</v>
+      </c>
+      <c r="G171" s="5">
+        <v>170</v>
+      </c>
+      <c r="H171" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I171" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J171" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K171" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L171" s="6">
+        <v>582</v>
+      </c>
+      <c r="M171" s="7">
+        <v>101908.06</v>
+      </c>
+      <c r="N171" s="6">
+        <v>1</v>
+      </c>
+      <c r="O171" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P171" s="8">
+        <v>175.1</v>
+      </c>
+      <c r="Q171" s="6">
+        <v>0</v>
+      </c>
+      <c r="R171" s="7">
+        <v>0</v>
+      </c>
+      <c r="S171" s="9">
+        <v>0</v>
+      </c>
+      <c r="T171" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U171" s="10">
+        <v>67878</v>
+      </c>
+      <c r="V171" s="11">
+        <v>11</v>
+      </c>
+      <c r="W171" s="4">
+        <v>46293</v>
+      </c>
+      <c r="X171" s="12">
+        <v>0.36944440000000001</v>
+      </c>
+      <c r="Y171" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z171" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA171" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB171" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC171" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD171" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE171" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF171" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG171" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH171" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI171" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ171" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK171" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL171" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM171" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN171" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO171" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP171" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ171" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR171" s="3" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2E4AE85-235A-40EB-BBC8-BBA6A3D6D6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD4430EB-920F-4D7B-9BAC-5FD67EA6A0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD4430EB-920F-4D7B-9BAC-5FD67EA6A0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A4E0C01-0C9E-4295-BA6C-CFB8CF8FABE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A4E0C01-0C9E-4295-BA6C-CFB8CF8FABE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{231278D2-57EC-48B2-8263-40FB39F6EC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A1F2155-290E-4E81-815C-60D6297A31ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{066C9073-3BBA-4FB3-B322-5F38662DDB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{066C9073-3BBA-4FB3-B322-5F38662DDB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1988AABC-3E81-423C-B2BD-2BB38A6CAA82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="122">
   <si>
     <t>Sel</t>
   </si>
@@ -305,6 +305,87 @@
   </si>
   <si>
     <t>1883500000069</t>
+  </si>
+  <si>
+    <t>1883500000070</t>
+  </si>
+  <si>
+    <t>1883500000071</t>
+  </si>
+  <si>
+    <t>1883500000072</t>
+  </si>
+  <si>
+    <t>1883500000073</t>
+  </si>
+  <si>
+    <t>1883500000074</t>
+  </si>
+  <si>
+    <t>1883500000075</t>
+  </si>
+  <si>
+    <t>1883500000076</t>
+  </si>
+  <si>
+    <t>1883500000077</t>
+  </si>
+  <si>
+    <t>1883500000078</t>
+  </si>
+  <si>
+    <t>1883500000079</t>
+  </si>
+  <si>
+    <t>1883500000080</t>
+  </si>
+  <si>
+    <t>1883500000081</t>
+  </si>
+  <si>
+    <t>1883500000082</t>
+  </si>
+  <si>
+    <t>1883500000083</t>
+  </si>
+  <si>
+    <t>1883500000084</t>
+  </si>
+  <si>
+    <t>1883500000085</t>
+  </si>
+  <si>
+    <t>1883500000086</t>
+  </si>
+  <si>
+    <t>1883500000087</t>
+  </si>
+  <si>
+    <t>1883500000088</t>
+  </si>
+  <si>
+    <t>1883500000089</t>
+  </si>
+  <si>
+    <t>1883500000090</t>
+  </si>
+  <si>
+    <t>1883500000091</t>
+  </si>
+  <si>
+    <t>1883500000092</t>
+  </si>
+  <si>
+    <t>1883500000093</t>
+  </si>
+  <si>
+    <t>1883500000094</t>
+  </si>
+  <si>
+    <t>1883500000095</t>
+  </si>
+  <si>
+    <t>1883500000096</t>
   </si>
 </sst>
 </file>
@@ -880,7 +961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR38"/>
+  <dimension ref="A1:AR65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -5973,6 +6054,3624 @@
       </c>
       <c r="AR38" s="3" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="39" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>1</v>
+      </c>
+      <c r="B39" s="2">
+        <v>2</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F39" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G39" s="5">
+        <v>131</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L39" s="6">
+        <v>4</v>
+      </c>
+      <c r="M39" s="7">
+        <v>718.4</v>
+      </c>
+      <c r="N39" s="6">
+        <v>1</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P39" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>0</v>
+      </c>
+      <c r="R39" s="7">
+        <v>0</v>
+      </c>
+      <c r="S39" s="9">
+        <v>0</v>
+      </c>
+      <c r="T39" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U39" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V39" s="11">
+        <v>11</v>
+      </c>
+      <c r="W39" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X39" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y39" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF39" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI39" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ39" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK39" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL39" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM39" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO39" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP39" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ39" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR39" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>1</v>
+      </c>
+      <c r="B40" s="2">
+        <v>2</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F40" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G40" s="5">
+        <v>132</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L40" s="6">
+        <v>5</v>
+      </c>
+      <c r="M40" s="7">
+        <v>898</v>
+      </c>
+      <c r="N40" s="6">
+        <v>1</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P40" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q40" s="6">
+        <v>0</v>
+      </c>
+      <c r="R40" s="7">
+        <v>0</v>
+      </c>
+      <c r="S40" s="9">
+        <v>0</v>
+      </c>
+      <c r="T40" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U40" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V40" s="11">
+        <v>11</v>
+      </c>
+      <c r="W40" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X40" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y40" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH40" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI40" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ40" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK40" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL40" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM40" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN40" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO40" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP40" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ40" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR40" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>1</v>
+      </c>
+      <c r="B41" s="2">
+        <v>2</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F41" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G41" s="5">
+        <v>133</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L41" s="6">
+        <v>6</v>
+      </c>
+      <c r="M41" s="7">
+        <v>1077.5999999999999</v>
+      </c>
+      <c r="N41" s="6">
+        <v>1</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P41" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q41" s="6">
+        <v>0</v>
+      </c>
+      <c r="R41" s="7">
+        <v>0</v>
+      </c>
+      <c r="S41" s="9">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U41" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V41" s="11">
+        <v>11</v>
+      </c>
+      <c r="W41" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X41" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y41" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG41" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI41" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ41" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK41" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL41" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM41" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN41" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO41" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP41" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ41" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR41" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>1</v>
+      </c>
+      <c r="B42" s="2">
+        <v>2</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F42" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G42" s="5">
+        <v>134</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L42" s="6">
+        <v>7</v>
+      </c>
+      <c r="M42" s="7">
+        <v>1257.2</v>
+      </c>
+      <c r="N42" s="6">
+        <v>1</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P42" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0</v>
+      </c>
+      <c r="R42" s="7">
+        <v>0</v>
+      </c>
+      <c r="S42" s="9">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U42" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V42" s="11">
+        <v>11</v>
+      </c>
+      <c r="W42" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X42" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y42" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI42" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ42" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK42" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR42" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>1</v>
+      </c>
+      <c r="B43" s="2">
+        <v>2</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F43" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G43" s="5">
+        <v>135</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L43" s="6">
+        <v>8</v>
+      </c>
+      <c r="M43" s="7">
+        <v>1436.8</v>
+      </c>
+      <c r="N43" s="6">
+        <v>1</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P43" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>0</v>
+      </c>
+      <c r="R43" s="7">
+        <v>0</v>
+      </c>
+      <c r="S43" s="9">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U43" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V43" s="11">
+        <v>11</v>
+      </c>
+      <c r="W43" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X43" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y43" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG43" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI43" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ43" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK43" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM43" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN43" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO43" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP43" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ43" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR43" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>1</v>
+      </c>
+      <c r="B44" s="2">
+        <v>2</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F44" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G44" s="5">
+        <v>136</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L44" s="6">
+        <v>9</v>
+      </c>
+      <c r="M44" s="7">
+        <v>1616.4</v>
+      </c>
+      <c r="N44" s="6">
+        <v>1</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P44" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q44" s="6">
+        <v>0</v>
+      </c>
+      <c r="R44" s="7">
+        <v>0</v>
+      </c>
+      <c r="S44" s="9">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U44" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V44" s="11">
+        <v>11</v>
+      </c>
+      <c r="W44" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X44" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y44" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG44" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI44" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ44" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK44" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM44" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN44" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO44" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP44" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ44" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR44" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>1</v>
+      </c>
+      <c r="B45" s="2">
+        <v>2</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F45" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G45" s="5">
+        <v>137</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L45" s="6">
+        <v>10</v>
+      </c>
+      <c r="M45" s="7">
+        <v>1796</v>
+      </c>
+      <c r="N45" s="6">
+        <v>1</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P45" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q45" s="6">
+        <v>0</v>
+      </c>
+      <c r="R45" s="7">
+        <v>0</v>
+      </c>
+      <c r="S45" s="9">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U45" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V45" s="11">
+        <v>11</v>
+      </c>
+      <c r="W45" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X45" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y45" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG45" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI45" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ45" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK45" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL45" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM45" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN45" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO45" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP45" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ45" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR45" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>1</v>
+      </c>
+      <c r="B46" s="2">
+        <v>2</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F46" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G46" s="5">
+        <v>138</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L46" s="6">
+        <v>11</v>
+      </c>
+      <c r="M46" s="7">
+        <v>1975.6</v>
+      </c>
+      <c r="N46" s="6">
+        <v>1</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P46" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>0</v>
+      </c>
+      <c r="R46" s="7">
+        <v>0</v>
+      </c>
+      <c r="S46" s="9">
+        <v>0</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U46" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V46" s="11">
+        <v>11</v>
+      </c>
+      <c r="W46" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X46" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y46" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI46" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ46" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK46" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM46" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR46" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>1</v>
+      </c>
+      <c r="B47" s="2">
+        <v>2</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F47" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G47" s="5">
+        <v>139</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L47" s="6">
+        <v>12</v>
+      </c>
+      <c r="M47" s="7">
+        <v>2155.1999999999998</v>
+      </c>
+      <c r="N47" s="6">
+        <v>1</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P47" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>0</v>
+      </c>
+      <c r="R47" s="7">
+        <v>0</v>
+      </c>
+      <c r="S47" s="9">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U47" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V47" s="11">
+        <v>11</v>
+      </c>
+      <c r="W47" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X47" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y47" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI47" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK47" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL47" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM47" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN47" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO47" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP47" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ47" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR47" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>1</v>
+      </c>
+      <c r="B48" s="2">
+        <v>2</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F48" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G48" s="5">
+        <v>140</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L48" s="6">
+        <v>13</v>
+      </c>
+      <c r="M48" s="7">
+        <v>2334.8000000000002</v>
+      </c>
+      <c r="N48" s="6">
+        <v>1</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P48" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q48" s="6">
+        <v>0</v>
+      </c>
+      <c r="R48" s="7">
+        <v>0</v>
+      </c>
+      <c r="S48" s="9">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U48" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V48" s="11">
+        <v>11</v>
+      </c>
+      <c r="W48" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X48" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y48" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI48" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ48" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK48" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL48" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM48" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR48" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="49" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>1</v>
+      </c>
+      <c r="B49" s="2">
+        <v>2</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F49" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G49" s="5">
+        <v>141</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L49" s="6">
+        <v>14</v>
+      </c>
+      <c r="M49" s="7">
+        <v>2514.4</v>
+      </c>
+      <c r="N49" s="6">
+        <v>1</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P49" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>0</v>
+      </c>
+      <c r="R49" s="7">
+        <v>0</v>
+      </c>
+      <c r="S49" s="9">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U49" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V49" s="11">
+        <v>11</v>
+      </c>
+      <c r="W49" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X49" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y49" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI49" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ49" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK49" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL49" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM49" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN49" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO49" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP49" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ49" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR49" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>1</v>
+      </c>
+      <c r="B50" s="2">
+        <v>2</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F50" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G50" s="5">
+        <v>142</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L50" s="6">
+        <v>15</v>
+      </c>
+      <c r="M50" s="7">
+        <v>2694</v>
+      </c>
+      <c r="N50" s="6">
+        <v>1</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P50" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>0</v>
+      </c>
+      <c r="R50" s="7">
+        <v>0</v>
+      </c>
+      <c r="S50" s="9">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U50" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V50" s="11">
+        <v>11</v>
+      </c>
+      <c r="W50" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X50" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y50" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI50" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ50" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK50" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO50" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP50" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ50" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR50" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="51" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>1</v>
+      </c>
+      <c r="B51" s="2">
+        <v>2</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F51" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G51" s="5">
+        <v>143</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L51" s="6">
+        <v>16</v>
+      </c>
+      <c r="M51" s="7">
+        <v>2873.6</v>
+      </c>
+      <c r="N51" s="6">
+        <v>1</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P51" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>0</v>
+      </c>
+      <c r="R51" s="7">
+        <v>0</v>
+      </c>
+      <c r="S51" s="9">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U51" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V51" s="11">
+        <v>11</v>
+      </c>
+      <c r="W51" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X51" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y51" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI51" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ51" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK51" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO51" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP51" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ51" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR51" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>1</v>
+      </c>
+      <c r="B52" s="2">
+        <v>2</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F52" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G52" s="5">
+        <v>144</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L52" s="6">
+        <v>17</v>
+      </c>
+      <c r="M52" s="7">
+        <v>3053.2</v>
+      </c>
+      <c r="N52" s="6">
+        <v>1</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P52" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q52" s="6">
+        <v>0</v>
+      </c>
+      <c r="R52" s="7">
+        <v>0</v>
+      </c>
+      <c r="S52" s="9">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U52" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V52" s="11">
+        <v>11</v>
+      </c>
+      <c r="W52" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X52" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y52" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG52" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI52" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ52" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK52" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM52" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR52" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>1</v>
+      </c>
+      <c r="B53" s="2">
+        <v>2</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F53" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G53" s="5">
+        <v>145</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L53" s="6">
+        <v>18</v>
+      </c>
+      <c r="M53" s="7">
+        <v>3232.8</v>
+      </c>
+      <c r="N53" s="6">
+        <v>1</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P53" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q53" s="6">
+        <v>0</v>
+      </c>
+      <c r="R53" s="7">
+        <v>0</v>
+      </c>
+      <c r="S53" s="9">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U53" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V53" s="11">
+        <v>11</v>
+      </c>
+      <c r="W53" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X53" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y53" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG53" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI53" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ53" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK53" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR53" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="54" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>1</v>
+      </c>
+      <c r="B54" s="2">
+        <v>2</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F54" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G54" s="5">
+        <v>146</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L54" s="6">
+        <v>19</v>
+      </c>
+      <c r="M54" s="7">
+        <v>3412.4</v>
+      </c>
+      <c r="N54" s="6">
+        <v>1</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P54" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q54" s="6">
+        <v>0</v>
+      </c>
+      <c r="R54" s="7">
+        <v>0</v>
+      </c>
+      <c r="S54" s="9">
+        <v>0</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U54" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V54" s="11">
+        <v>11</v>
+      </c>
+      <c r="W54" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X54" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y54" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI54" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ54" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK54" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM54" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR54" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>1</v>
+      </c>
+      <c r="B55" s="2">
+        <v>2</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F55" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G55" s="5">
+        <v>147</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L55" s="6">
+        <v>20</v>
+      </c>
+      <c r="M55" s="7">
+        <v>3592</v>
+      </c>
+      <c r="N55" s="6">
+        <v>1</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P55" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>0</v>
+      </c>
+      <c r="R55" s="7">
+        <v>0</v>
+      </c>
+      <c r="S55" s="9">
+        <v>0</v>
+      </c>
+      <c r="T55" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U55" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V55" s="11">
+        <v>11</v>
+      </c>
+      <c r="W55" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X55" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y55" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI55" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ55" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK55" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM55" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR55" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>1</v>
+      </c>
+      <c r="B56" s="2">
+        <v>2</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F56" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G56" s="5">
+        <v>148</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L56" s="6">
+        <v>21</v>
+      </c>
+      <c r="M56" s="7">
+        <v>3771.6</v>
+      </c>
+      <c r="N56" s="6">
+        <v>1</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P56" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q56" s="6">
+        <v>0</v>
+      </c>
+      <c r="R56" s="7">
+        <v>0</v>
+      </c>
+      <c r="S56" s="9">
+        <v>0</v>
+      </c>
+      <c r="T56" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U56" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V56" s="11">
+        <v>11</v>
+      </c>
+      <c r="W56" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X56" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y56" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI56" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ56" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK56" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM56" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR56" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>1</v>
+      </c>
+      <c r="B57" s="2">
+        <v>2</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F57" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G57" s="5">
+        <v>149</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L57" s="6">
+        <v>22</v>
+      </c>
+      <c r="M57" s="7">
+        <v>3951.2</v>
+      </c>
+      <c r="N57" s="6">
+        <v>1</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P57" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q57" s="6">
+        <v>0</v>
+      </c>
+      <c r="R57" s="7">
+        <v>0</v>
+      </c>
+      <c r="S57" s="9">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U57" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V57" s="11">
+        <v>11</v>
+      </c>
+      <c r="W57" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X57" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y57" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG57" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI57" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ57" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK57" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM57" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR57" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>1</v>
+      </c>
+      <c r="B58" s="2">
+        <v>2</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F58" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G58" s="5">
+        <v>150</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L58" s="6">
+        <v>23</v>
+      </c>
+      <c r="M58" s="7">
+        <v>4130.8</v>
+      </c>
+      <c r="N58" s="6">
+        <v>1</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P58" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0</v>
+      </c>
+      <c r="R58" s="7">
+        <v>0</v>
+      </c>
+      <c r="S58" s="9">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U58" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V58" s="11">
+        <v>11</v>
+      </c>
+      <c r="W58" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X58" s="12">
+        <v>0.4243056</v>
+      </c>
+      <c r="Y58" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI58" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ58" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK58" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR58" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>1</v>
+      </c>
+      <c r="B59" s="2">
+        <v>2</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F59" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G59" s="5">
+        <v>151</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L59" s="6">
+        <v>24</v>
+      </c>
+      <c r="M59" s="7">
+        <v>4310.3999999999996</v>
+      </c>
+      <c r="N59" s="6">
+        <v>1</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P59" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q59" s="6">
+        <v>0</v>
+      </c>
+      <c r="R59" s="7">
+        <v>0</v>
+      </c>
+      <c r="S59" s="9">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U59" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V59" s="11">
+        <v>11</v>
+      </c>
+      <c r="W59" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X59" s="12">
+        <v>0.43125000000000002</v>
+      </c>
+      <c r="Y59" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG59" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI59" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ59" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK59" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM59" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR59" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="60" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>1</v>
+      </c>
+      <c r="B60" s="2">
+        <v>2</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F60" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G60" s="5">
+        <v>152</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L60" s="6">
+        <v>25</v>
+      </c>
+      <c r="M60" s="7">
+        <v>4490</v>
+      </c>
+      <c r="N60" s="6">
+        <v>1</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P60" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q60" s="6">
+        <v>0</v>
+      </c>
+      <c r="R60" s="7">
+        <v>0</v>
+      </c>
+      <c r="S60" s="9">
+        <v>0</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U60" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V60" s="11">
+        <v>11</v>
+      </c>
+      <c r="W60" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X60" s="12">
+        <v>0.43125000000000002</v>
+      </c>
+      <c r="Y60" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI60" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ60" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK60" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM60" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR60" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>1</v>
+      </c>
+      <c r="B61" s="2">
+        <v>2</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F61" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G61" s="5">
+        <v>153</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L61" s="6">
+        <v>26</v>
+      </c>
+      <c r="M61" s="7">
+        <v>4669.6000000000004</v>
+      </c>
+      <c r="N61" s="6">
+        <v>1</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P61" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q61" s="6">
+        <v>0</v>
+      </c>
+      <c r="R61" s="7">
+        <v>0</v>
+      </c>
+      <c r="S61" s="9">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U61" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V61" s="11">
+        <v>11</v>
+      </c>
+      <c r="W61" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X61" s="12">
+        <v>0.4451389</v>
+      </c>
+      <c r="Y61" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG61" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI61" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ61" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK61" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR61" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>1</v>
+      </c>
+      <c r="B62" s="2">
+        <v>2</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F62" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G62" s="5">
+        <v>154</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L62" s="6">
+        <v>27</v>
+      </c>
+      <c r="M62" s="7">
+        <v>4849.2</v>
+      </c>
+      <c r="N62" s="6">
+        <v>1</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P62" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>0</v>
+      </c>
+      <c r="R62" s="7">
+        <v>0</v>
+      </c>
+      <c r="S62" s="9">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U62" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V62" s="11">
+        <v>11</v>
+      </c>
+      <c r="W62" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X62" s="12">
+        <v>0.4451389</v>
+      </c>
+      <c r="Y62" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI62" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ62" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK62" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM62" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR62" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="63" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>1</v>
+      </c>
+      <c r="B63" s="2">
+        <v>2</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F63" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G63" s="5">
+        <v>155</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L63" s="6">
+        <v>28</v>
+      </c>
+      <c r="M63" s="7">
+        <v>5028.8</v>
+      </c>
+      <c r="N63" s="6">
+        <v>1</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P63" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>0</v>
+      </c>
+      <c r="R63" s="7">
+        <v>0</v>
+      </c>
+      <c r="S63" s="9">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U63" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V63" s="11">
+        <v>11</v>
+      </c>
+      <c r="W63" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X63" s="12">
+        <v>0.4451389</v>
+      </c>
+      <c r="Y63" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI63" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ63" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK63" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR63" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="64" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>1</v>
+      </c>
+      <c r="B64" s="2">
+        <v>2</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F64" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G64" s="5">
+        <v>156</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L64" s="6">
+        <v>29</v>
+      </c>
+      <c r="M64" s="7">
+        <v>5208.3999999999996</v>
+      </c>
+      <c r="N64" s="6">
+        <v>1</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P64" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q64" s="6">
+        <v>0</v>
+      </c>
+      <c r="R64" s="7">
+        <v>0</v>
+      </c>
+      <c r="S64" s="9">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U64" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V64" s="11">
+        <v>11</v>
+      </c>
+      <c r="W64" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X64" s="12">
+        <v>0.4451389</v>
+      </c>
+      <c r="Y64" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI64" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ64" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK64" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR64" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="65" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>1</v>
+      </c>
+      <c r="B65" s="2">
+        <v>2</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F65" s="4">
+        <v>46294</v>
+      </c>
+      <c r="G65" s="5">
+        <v>157</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L65" s="6">
+        <v>30</v>
+      </c>
+      <c r="M65" s="7">
+        <v>5388</v>
+      </c>
+      <c r="N65" s="6">
+        <v>1</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P65" s="8">
+        <v>179.6</v>
+      </c>
+      <c r="Q65" s="6">
+        <v>0</v>
+      </c>
+      <c r="R65" s="7">
+        <v>0</v>
+      </c>
+      <c r="S65" s="9">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U65" s="10">
+        <v>67757</v>
+      </c>
+      <c r="V65" s="11">
+        <v>11</v>
+      </c>
+      <c r="W65" s="4">
+        <v>46294</v>
+      </c>
+      <c r="X65" s="12">
+        <v>0.4451389</v>
+      </c>
+      <c r="Y65" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG65" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI65" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ65" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK65" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR65" s="3" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DC00DC7-3BD8-4046-89DE-C90AC9EE9402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5159EF4-79E1-4A3A-BC2E-86054DE6C167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="96">
   <si>
     <t>Sel</t>
   </si>
@@ -154,10 +154,10 @@
     <t>Nº Série</t>
   </si>
   <si>
-    <t>10016354</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>10016351</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>500</t>
@@ -175,7 +175,7 @@
     <t>UN</t>
   </si>
   <si>
-    <t>FORNO ELETRICO NARDELLI EMBUTIR 60L BLACK - NARDELLI EMBUTIR 60L BLACK - 127 V</t>
+    <t>FORNO ELETRICO NARDELLI EMBUTIR INOX 60 LITROS - NARDELLI EMBUTIR INOX 60 LITROS - 220 V</t>
   </si>
   <si>
     <t>100</t>
@@ -187,142 +187,127 @@
     <t>FORNOE</t>
   </si>
   <si>
-    <t>1871400013047</t>
-  </si>
-  <si>
-    <t>1871400013048</t>
-  </si>
-  <si>
-    <t>1871400013049</t>
-  </si>
-  <si>
-    <t>1871400013050</t>
-  </si>
-  <si>
-    <t>1871400013051</t>
-  </si>
-  <si>
-    <t>1871400013052</t>
-  </si>
-  <si>
-    <t>1871400013053</t>
-  </si>
-  <si>
-    <t>1871400013054</t>
-  </si>
-  <si>
-    <t>1871400013055</t>
-  </si>
-  <si>
-    <t>1871400013056</t>
-  </si>
-  <si>
-    <t>1871400013057</t>
-  </si>
-  <si>
-    <t>1871400013058</t>
-  </si>
-  <si>
-    <t>1871400013059</t>
-  </si>
-  <si>
-    <t>1871400013060</t>
-  </si>
-  <si>
-    <t>1871400013061</t>
-  </si>
-  <si>
-    <t>1871400013062</t>
-  </si>
-  <si>
-    <t>1871400013063</t>
-  </si>
-  <si>
-    <t>1871400013064</t>
-  </si>
-  <si>
-    <t>1871400013065</t>
-  </si>
-  <si>
-    <t>1871400013066</t>
-  </si>
-  <si>
-    <t>1871400013067</t>
-  </si>
-  <si>
-    <t>1871400013068</t>
-  </si>
-  <si>
-    <t>1871400013069</t>
-  </si>
-  <si>
-    <t>1871400013070</t>
-  </si>
-  <si>
-    <t>1871400013071</t>
-  </si>
-  <si>
-    <t>1871400013072</t>
-  </si>
-  <si>
-    <t>1871400013073</t>
-  </si>
-  <si>
-    <t>1871400013074</t>
-  </si>
-  <si>
-    <t>1871400013075</t>
-  </si>
-  <si>
-    <t>1871400013076</t>
-  </si>
-  <si>
-    <t>1871400013077</t>
-  </si>
-  <si>
-    <t>1871400013078</t>
-  </si>
-  <si>
-    <t>1871400013079</t>
-  </si>
-  <si>
-    <t>1871400013080</t>
-  </si>
-  <si>
-    <t>10056354</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>FORNO ELETRICO FOGATTI EMBUTIR 60L BLACK - 220 V</t>
-  </si>
-  <si>
-    <t>1031000000104</t>
-  </si>
-  <si>
-    <t>1031000000105</t>
-  </si>
-  <si>
-    <t>1031000000106</t>
-  </si>
-  <si>
-    <t>1031000000107</t>
-  </si>
-  <si>
-    <t>1031000000108</t>
-  </si>
-  <si>
-    <t>1031000000109</t>
-  </si>
-  <si>
-    <t>1031000000110</t>
-  </si>
-  <si>
-    <t>1031000000111</t>
-  </si>
-  <si>
-    <t>1031000000112</t>
+    <t>1875400003126</t>
+  </si>
+  <si>
+    <t>1875400003127</t>
+  </si>
+  <si>
+    <t>1875400003128</t>
+  </si>
+  <si>
+    <t>1875400003129</t>
+  </si>
+  <si>
+    <t>1875400003130</t>
+  </si>
+  <si>
+    <t>1875400003131</t>
+  </si>
+  <si>
+    <t>1875400003132</t>
+  </si>
+  <si>
+    <t>1875400003133</t>
+  </si>
+  <si>
+    <t>1875400003134</t>
+  </si>
+  <si>
+    <t>1875400003135</t>
+  </si>
+  <si>
+    <t>1875400003136</t>
+  </si>
+  <si>
+    <t>1875400003137</t>
+  </si>
+  <si>
+    <t>1875400003138</t>
+  </si>
+  <si>
+    <t>1875400003139</t>
+  </si>
+  <si>
+    <t>1875400003140</t>
+  </si>
+  <si>
+    <t>1875400003141</t>
+  </si>
+  <si>
+    <t>1875400003142</t>
+  </si>
+  <si>
+    <t>1875400003143</t>
+  </si>
+  <si>
+    <t>1875400003144</t>
+  </si>
+  <si>
+    <t>1875400003145</t>
+  </si>
+  <si>
+    <t>1875400003146</t>
+  </si>
+  <si>
+    <t>1875400003147</t>
+  </si>
+  <si>
+    <t>1875400003148</t>
+  </si>
+  <si>
+    <t>1875400003149</t>
+  </si>
+  <si>
+    <t>1875400003150</t>
+  </si>
+  <si>
+    <t>1875400003151</t>
+  </si>
+  <si>
+    <t>1875400003152</t>
+  </si>
+  <si>
+    <t>1875400003153</t>
+  </si>
+  <si>
+    <t>1875400003154</t>
+  </si>
+  <si>
+    <t>1875400003155</t>
+  </si>
+  <si>
+    <t>1875400003156</t>
+  </si>
+  <si>
+    <t>1875400003157</t>
+  </si>
+  <si>
+    <t>1875400003158</t>
+  </si>
+  <si>
+    <t>1875400003159</t>
+  </si>
+  <si>
+    <t>1875400003160</t>
+  </si>
+  <si>
+    <t>1875400003161</t>
+  </si>
+  <si>
+    <t>1875400003162</t>
+  </si>
+  <si>
+    <t>1875400003163</t>
+  </si>
+  <si>
+    <t>1875400003164</t>
+  </si>
+  <si>
+    <t>1875400003165</t>
+  </si>
+  <si>
+    <t>1875400003166</t>
   </si>
 </sst>
 </file>
@@ -898,7 +883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR44"/>
+  <dimension ref="A1:AR42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -1052,10 +1037,10 @@
         <v>46</v>
       </c>
       <c r="F2" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G2" s="5">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>47</v>
@@ -1070,10 +1055,10 @@
         <v>50</v>
       </c>
       <c r="L2" s="6">
-        <v>571</v>
+        <v>77</v>
       </c>
       <c r="M2" s="7">
-        <v>191724.92</v>
+        <v>28797.17</v>
       </c>
       <c r="N2" s="6">
         <v>1</v>
@@ -1082,7 +1067,7 @@
         <v>51</v>
       </c>
       <c r="P2" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q2" s="6">
         <v>0</v>
@@ -1097,16 +1082,16 @@
         <v>52</v>
       </c>
       <c r="U2" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V2" s="11">
         <v>11</v>
       </c>
       <c r="W2" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X2" s="12">
-        <v>0.35486109999999998</v>
+        <v>0.31388890000000003</v>
       </c>
       <c r="Y2" s="10">
         <v>0</v>
@@ -1186,10 +1171,10 @@
         <v>46</v>
       </c>
       <c r="F3" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G3" s="5">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>47</v>
@@ -1204,10 +1189,10 @@
         <v>50</v>
       </c>
       <c r="L3" s="6">
-        <v>572</v>
+        <v>78</v>
       </c>
       <c r="M3" s="7">
-        <v>192060.69</v>
+        <v>29171.16</v>
       </c>
       <c r="N3" s="6">
         <v>1</v>
@@ -1216,7 +1201,7 @@
         <v>51</v>
       </c>
       <c r="P3" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q3" s="6">
         <v>0</v>
@@ -1231,16 +1216,16 @@
         <v>52</v>
       </c>
       <c r="U3" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V3" s="11">
         <v>11</v>
       </c>
       <c r="W3" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X3" s="12">
-        <v>0.35486109999999998</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y3" s="10">
         <v>0</v>
@@ -1320,10 +1305,10 @@
         <v>46</v>
       </c>
       <c r="F4" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G4" s="5">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>47</v>
@@ -1338,10 +1323,10 @@
         <v>50</v>
       </c>
       <c r="L4" s="6">
-        <v>573</v>
+        <v>79</v>
       </c>
       <c r="M4" s="7">
-        <v>192396.46</v>
+        <v>29545.15</v>
       </c>
       <c r="N4" s="6">
         <v>1</v>
@@ -1350,7 +1335,7 @@
         <v>51</v>
       </c>
       <c r="P4" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q4" s="6">
         <v>0</v>
@@ -1365,16 +1350,16 @@
         <v>52</v>
       </c>
       <c r="U4" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V4" s="11">
         <v>11</v>
       </c>
       <c r="W4" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X4" s="12">
-        <v>0.35486109999999998</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y4" s="10">
         <v>0</v>
@@ -1454,10 +1439,10 @@
         <v>46</v>
       </c>
       <c r="F5" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G5" s="5">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>47</v>
@@ -1472,10 +1457,10 @@
         <v>50</v>
       </c>
       <c r="L5" s="6">
-        <v>574</v>
+        <v>80</v>
       </c>
       <c r="M5" s="7">
-        <v>192732.23</v>
+        <v>29919.14</v>
       </c>
       <c r="N5" s="6">
         <v>1</v>
@@ -1484,7 +1469,7 @@
         <v>51</v>
       </c>
       <c r="P5" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q5" s="6">
         <v>0</v>
@@ -1499,16 +1484,16 @@
         <v>52</v>
       </c>
       <c r="U5" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V5" s="11">
         <v>11</v>
       </c>
       <c r="W5" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X5" s="12">
-        <v>0.35486109999999998</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y5" s="10">
         <v>0</v>
@@ -1588,10 +1573,10 @@
         <v>46</v>
       </c>
       <c r="F6" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G6" s="5">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>47</v>
@@ -1606,10 +1591,10 @@
         <v>50</v>
       </c>
       <c r="L6" s="6">
-        <v>575</v>
+        <v>81</v>
       </c>
       <c r="M6" s="7">
-        <v>193068</v>
+        <v>30293.13</v>
       </c>
       <c r="N6" s="6">
         <v>1</v>
@@ -1618,7 +1603,7 @@
         <v>51</v>
       </c>
       <c r="P6" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q6" s="6">
         <v>0</v>
@@ -1633,16 +1618,16 @@
         <v>52</v>
       </c>
       <c r="U6" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V6" s="11">
         <v>11</v>
       </c>
       <c r="W6" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X6" s="12">
-        <v>0.35486109999999998</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y6" s="10">
         <v>0</v>
@@ -1722,10 +1707,10 @@
         <v>46</v>
       </c>
       <c r="F7" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G7" s="5">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>47</v>
@@ -1740,10 +1725,10 @@
         <v>50</v>
       </c>
       <c r="L7" s="6">
-        <v>576</v>
+        <v>82</v>
       </c>
       <c r="M7" s="7">
-        <v>193403.77</v>
+        <v>30667.119999999999</v>
       </c>
       <c r="N7" s="6">
         <v>1</v>
@@ -1752,7 +1737,7 @@
         <v>51</v>
       </c>
       <c r="P7" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q7" s="6">
         <v>0</v>
@@ -1767,16 +1752,16 @@
         <v>52</v>
       </c>
       <c r="U7" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V7" s="11">
         <v>11</v>
       </c>
       <c r="W7" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X7" s="12">
-        <v>0.35486109999999998</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y7" s="10">
         <v>0</v>
@@ -1856,10 +1841,10 @@
         <v>46</v>
       </c>
       <c r="F8" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G8" s="5">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>47</v>
@@ -1874,10 +1859,10 @@
         <v>50</v>
       </c>
       <c r="L8" s="6">
-        <v>577</v>
+        <v>83</v>
       </c>
       <c r="M8" s="7">
-        <v>193739.54</v>
+        <v>31041.11</v>
       </c>
       <c r="N8" s="6">
         <v>1</v>
@@ -1886,7 +1871,7 @@
         <v>51</v>
       </c>
       <c r="P8" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q8" s="6">
         <v>0</v>
@@ -1901,16 +1886,16 @@
         <v>52</v>
       </c>
       <c r="U8" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V8" s="11">
         <v>11</v>
       </c>
       <c r="W8" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X8" s="12">
-        <v>0.35486109999999998</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y8" s="10">
         <v>0</v>
@@ -1990,10 +1975,10 @@
         <v>46</v>
       </c>
       <c r="F9" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G9" s="5">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>47</v>
@@ -2008,10 +1993,10 @@
         <v>50</v>
       </c>
       <c r="L9" s="6">
-        <v>578</v>
+        <v>84</v>
       </c>
       <c r="M9" s="7">
-        <v>194075.31</v>
+        <v>31415.1</v>
       </c>
       <c r="N9" s="6">
         <v>1</v>
@@ -2020,7 +2005,7 @@
         <v>51</v>
       </c>
       <c r="P9" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q9" s="6">
         <v>0</v>
@@ -2035,16 +2020,16 @@
         <v>52</v>
       </c>
       <c r="U9" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V9" s="11">
         <v>11</v>
       </c>
       <c r="W9" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X9" s="12">
-        <v>0.35486109999999998</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y9" s="10">
         <v>0</v>
@@ -2124,10 +2109,10 @@
         <v>46</v>
       </c>
       <c r="F10" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G10" s="5">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>47</v>
@@ -2142,10 +2127,10 @@
         <v>50</v>
       </c>
       <c r="L10" s="6">
-        <v>579</v>
+        <v>85</v>
       </c>
       <c r="M10" s="7">
-        <v>194411.08</v>
+        <v>31789.09</v>
       </c>
       <c r="N10" s="6">
         <v>1</v>
@@ -2154,7 +2139,7 @@
         <v>51</v>
       </c>
       <c r="P10" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q10" s="6">
         <v>0</v>
@@ -2169,16 +2154,16 @@
         <v>52</v>
       </c>
       <c r="U10" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V10" s="11">
         <v>11</v>
       </c>
       <c r="W10" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X10" s="12">
-        <v>0.35486109999999998</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y10" s="10">
         <v>0</v>
@@ -2258,10 +2243,10 @@
         <v>46</v>
       </c>
       <c r="F11" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G11" s="5">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>47</v>
@@ -2276,10 +2261,10 @@
         <v>50</v>
       </c>
       <c r="L11" s="6">
-        <v>580</v>
+        <v>86</v>
       </c>
       <c r="M11" s="7">
-        <v>194746.85</v>
+        <v>32163.08</v>
       </c>
       <c r="N11" s="6">
         <v>1</v>
@@ -2288,7 +2273,7 @@
         <v>51</v>
       </c>
       <c r="P11" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q11" s="6">
         <v>0</v>
@@ -2303,16 +2288,16 @@
         <v>52</v>
       </c>
       <c r="U11" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V11" s="11">
         <v>11</v>
       </c>
       <c r="W11" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X11" s="12">
-        <v>0.35486109999999998</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y11" s="10">
         <v>0</v>
@@ -2392,10 +2377,10 @@
         <v>46</v>
       </c>
       <c r="F12" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G12" s="5">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>47</v>
@@ -2410,10 +2395,10 @@
         <v>50</v>
       </c>
       <c r="L12" s="6">
-        <v>581</v>
+        <v>87</v>
       </c>
       <c r="M12" s="7">
-        <v>195082.62</v>
+        <v>32537.07</v>
       </c>
       <c r="N12" s="6">
         <v>1</v>
@@ -2422,7 +2407,7 @@
         <v>51</v>
       </c>
       <c r="P12" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q12" s="6">
         <v>0</v>
@@ -2437,16 +2422,16 @@
         <v>52</v>
       </c>
       <c r="U12" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V12" s="11">
         <v>11</v>
       </c>
       <c r="W12" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X12" s="12">
-        <v>0.35486109999999998</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y12" s="10">
         <v>0</v>
@@ -2526,10 +2511,10 @@
         <v>46</v>
       </c>
       <c r="F13" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G13" s="5">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>47</v>
@@ -2544,10 +2529,10 @@
         <v>50</v>
       </c>
       <c r="L13" s="6">
-        <v>582</v>
+        <v>88</v>
       </c>
       <c r="M13" s="7">
-        <v>195418.39</v>
+        <v>32911.06</v>
       </c>
       <c r="N13" s="6">
         <v>1</v>
@@ -2556,7 +2541,7 @@
         <v>51</v>
       </c>
       <c r="P13" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q13" s="6">
         <v>0</v>
@@ -2571,16 +2556,16 @@
         <v>52</v>
       </c>
       <c r="U13" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V13" s="11">
         <v>11</v>
       </c>
       <c r="W13" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X13" s="12">
-        <v>0.35486109999999998</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y13" s="10">
         <v>0</v>
@@ -2660,10 +2645,10 @@
         <v>46</v>
       </c>
       <c r="F14" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G14" s="5">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>47</v>
@@ -2678,10 +2663,10 @@
         <v>50</v>
       </c>
       <c r="L14" s="6">
-        <v>583</v>
+        <v>89</v>
       </c>
       <c r="M14" s="7">
-        <v>195754.17</v>
+        <v>33285.050000000003</v>
       </c>
       <c r="N14" s="6">
         <v>1</v>
@@ -2690,7 +2675,7 @@
         <v>51</v>
       </c>
       <c r="P14" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q14" s="6">
         <v>0</v>
@@ -2705,16 +2690,16 @@
         <v>52</v>
       </c>
       <c r="U14" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V14" s="11">
         <v>11</v>
       </c>
       <c r="W14" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X14" s="12">
-        <v>0.3618056</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y14" s="10">
         <v>0</v>
@@ -2794,10 +2779,10 @@
         <v>46</v>
       </c>
       <c r="F15" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G15" s="5">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>47</v>
@@ -2812,10 +2797,10 @@
         <v>50</v>
       </c>
       <c r="L15" s="6">
-        <v>584</v>
+        <v>90</v>
       </c>
       <c r="M15" s="7">
-        <v>196089.94</v>
+        <v>33659.03</v>
       </c>
       <c r="N15" s="6">
         <v>1</v>
@@ -2824,7 +2809,7 @@
         <v>51</v>
       </c>
       <c r="P15" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q15" s="6">
         <v>0</v>
@@ -2839,16 +2824,16 @@
         <v>52</v>
       </c>
       <c r="U15" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V15" s="11">
         <v>11</v>
       </c>
       <c r="W15" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X15" s="12">
-        <v>0.3618056</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y15" s="10">
         <v>0</v>
@@ -2928,10 +2913,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G16" s="5">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>47</v>
@@ -2946,10 +2931,10 @@
         <v>50</v>
       </c>
       <c r="L16" s="6">
-        <v>585</v>
+        <v>91</v>
       </c>
       <c r="M16" s="7">
-        <v>196425.71</v>
+        <v>34033.019999999997</v>
       </c>
       <c r="N16" s="6">
         <v>1</v>
@@ -2958,7 +2943,7 @@
         <v>51</v>
       </c>
       <c r="P16" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q16" s="6">
         <v>0</v>
@@ -2973,16 +2958,16 @@
         <v>52</v>
       </c>
       <c r="U16" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V16" s="11">
         <v>11</v>
       </c>
       <c r="W16" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X16" s="12">
-        <v>0.3618056</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y16" s="10">
         <v>0</v>
@@ -3062,10 +3047,10 @@
         <v>46</v>
       </c>
       <c r="F17" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G17" s="5">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>47</v>
@@ -3080,10 +3065,10 @@
         <v>50</v>
       </c>
       <c r="L17" s="6">
-        <v>586</v>
+        <v>92</v>
       </c>
       <c r="M17" s="7">
-        <v>196761.48</v>
+        <v>34407.01</v>
       </c>
       <c r="N17" s="6">
         <v>1</v>
@@ -3092,7 +3077,7 @@
         <v>51</v>
       </c>
       <c r="P17" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q17" s="6">
         <v>0</v>
@@ -3107,16 +3092,16 @@
         <v>52</v>
       </c>
       <c r="U17" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V17" s="11">
         <v>11</v>
       </c>
       <c r="W17" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X17" s="12">
-        <v>0.3826389</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y17" s="10">
         <v>0</v>
@@ -3196,10 +3181,10 @@
         <v>46</v>
       </c>
       <c r="F18" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G18" s="5">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>47</v>
@@ -3214,10 +3199,10 @@
         <v>50</v>
       </c>
       <c r="L18" s="6">
-        <v>587</v>
+        <v>93</v>
       </c>
       <c r="M18" s="7">
-        <v>197097.25</v>
+        <v>34781</v>
       </c>
       <c r="N18" s="6">
         <v>1</v>
@@ -3226,7 +3211,7 @@
         <v>51</v>
       </c>
       <c r="P18" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q18" s="6">
         <v>0</v>
@@ -3241,16 +3226,16 @@
         <v>52</v>
       </c>
       <c r="U18" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V18" s="11">
         <v>11</v>
       </c>
       <c r="W18" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X18" s="12">
-        <v>0.3826389</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y18" s="10">
         <v>0</v>
@@ -3330,10 +3315,10 @@
         <v>46</v>
       </c>
       <c r="F19" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G19" s="5">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>47</v>
@@ -3348,10 +3333,10 @@
         <v>50</v>
       </c>
       <c r="L19" s="6">
-        <v>588</v>
+        <v>94</v>
       </c>
       <c r="M19" s="7">
-        <v>197433.02</v>
+        <v>35154.99</v>
       </c>
       <c r="N19" s="6">
         <v>1</v>
@@ -3360,7 +3345,7 @@
         <v>51</v>
       </c>
       <c r="P19" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q19" s="6">
         <v>0</v>
@@ -3375,16 +3360,16 @@
         <v>52</v>
       </c>
       <c r="U19" s="10">
-        <v>67391</v>
+        <v>67750</v>
       </c>
       <c r="V19" s="11">
         <v>11</v>
       </c>
       <c r="W19" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X19" s="12">
-        <v>0.3826389</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y19" s="10">
         <v>0</v>
@@ -3464,10 +3449,10 @@
         <v>46</v>
       </c>
       <c r="F20" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G20" s="5">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>47</v>
@@ -3482,10 +3467,10 @@
         <v>50</v>
       </c>
       <c r="L20" s="6">
-        <v>589</v>
+        <v>95</v>
       </c>
       <c r="M20" s="7">
-        <v>197768.79</v>
+        <v>35528.980000000003</v>
       </c>
       <c r="N20" s="6">
         <v>1</v>
@@ -3494,7 +3479,7 @@
         <v>51</v>
       </c>
       <c r="P20" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q20" s="6">
         <v>0</v>
@@ -3509,16 +3494,16 @@
         <v>52</v>
       </c>
       <c r="U20" s="10">
-        <v>67506</v>
+        <v>67750</v>
       </c>
       <c r="V20" s="11">
         <v>11</v>
       </c>
       <c r="W20" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X20" s="12">
-        <v>0.38958330000000002</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y20" s="10">
         <v>0</v>
@@ -3598,10 +3583,10 @@
         <v>46</v>
       </c>
       <c r="F21" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G21" s="5">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>47</v>
@@ -3616,10 +3601,10 @@
         <v>50</v>
       </c>
       <c r="L21" s="6">
-        <v>590</v>
+        <v>96</v>
       </c>
       <c r="M21" s="7">
-        <v>198104.56</v>
+        <v>35902.97</v>
       </c>
       <c r="N21" s="6">
         <v>1</v>
@@ -3628,7 +3613,7 @@
         <v>51</v>
       </c>
       <c r="P21" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q21" s="6">
         <v>0</v>
@@ -3643,16 +3628,16 @@
         <v>52</v>
       </c>
       <c r="U21" s="10">
-        <v>67506</v>
+        <v>67750</v>
       </c>
       <c r="V21" s="11">
         <v>11</v>
       </c>
       <c r="W21" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X21" s="12">
-        <v>0.4034722</v>
+        <v>0.37708330000000001</v>
       </c>
       <c r="Y21" s="10">
         <v>0</v>
@@ -3732,10 +3717,10 @@
         <v>46</v>
       </c>
       <c r="F22" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G22" s="5">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>47</v>
@@ -3750,10 +3735,10 @@
         <v>50</v>
       </c>
       <c r="L22" s="6">
-        <v>591</v>
+        <v>97</v>
       </c>
       <c r="M22" s="7">
-        <v>198440.33</v>
+        <v>36276.959999999999</v>
       </c>
       <c r="N22" s="6">
         <v>1</v>
@@ -3762,7 +3747,7 @@
         <v>51</v>
       </c>
       <c r="P22" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q22" s="6">
         <v>0</v>
@@ -3777,16 +3762,16 @@
         <v>52</v>
       </c>
       <c r="U22" s="10">
-        <v>67506</v>
+        <v>67750</v>
       </c>
       <c r="V22" s="11">
         <v>11</v>
       </c>
       <c r="W22" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X22" s="12">
-        <v>0.4034722</v>
+        <v>0.39791670000000001</v>
       </c>
       <c r="Y22" s="10">
         <v>0</v>
@@ -3866,10 +3851,10 @@
         <v>46</v>
       </c>
       <c r="F23" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G23" s="5">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>47</v>
@@ -3884,10 +3869,10 @@
         <v>50</v>
       </c>
       <c r="L23" s="6">
-        <v>592</v>
+        <v>98</v>
       </c>
       <c r="M23" s="7">
-        <v>198776.1</v>
+        <v>36650.949999999997</v>
       </c>
       <c r="N23" s="6">
         <v>1</v>
@@ -3896,7 +3881,7 @@
         <v>51</v>
       </c>
       <c r="P23" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q23" s="6">
         <v>0</v>
@@ -3911,16 +3896,16 @@
         <v>52</v>
       </c>
       <c r="U23" s="10">
-        <v>67506</v>
+        <v>67750</v>
       </c>
       <c r="V23" s="11">
         <v>11</v>
       </c>
       <c r="W23" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X23" s="12">
-        <v>0.4034722</v>
+        <v>0.39791670000000001</v>
       </c>
       <c r="Y23" s="10">
         <v>0</v>
@@ -4000,10 +3985,10 @@
         <v>46</v>
       </c>
       <c r="F24" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G24" s="5">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>47</v>
@@ -4018,10 +4003,10 @@
         <v>50</v>
       </c>
       <c r="L24" s="6">
-        <v>593</v>
+        <v>99</v>
       </c>
       <c r="M24" s="7">
-        <v>199111.87</v>
+        <v>37024.94</v>
       </c>
       <c r="N24" s="6">
         <v>1</v>
@@ -4030,7 +4015,7 @@
         <v>51</v>
       </c>
       <c r="P24" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q24" s="6">
         <v>0</v>
@@ -4045,16 +4030,16 @@
         <v>52</v>
       </c>
       <c r="U24" s="10">
-        <v>67506</v>
+        <v>67750</v>
       </c>
       <c r="V24" s="11">
         <v>11</v>
       </c>
       <c r="W24" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X24" s="12">
-        <v>0.41041670000000002</v>
+        <v>0.39791670000000001</v>
       </c>
       <c r="Y24" s="10">
         <v>0</v>
@@ -4134,10 +4119,10 @@
         <v>46</v>
       </c>
       <c r="F25" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G25" s="5">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>47</v>
@@ -4152,10 +4137,10 @@
         <v>50</v>
       </c>
       <c r="L25" s="6">
-        <v>594</v>
+        <v>100</v>
       </c>
       <c r="M25" s="7">
-        <v>199447.64</v>
+        <v>37398.93</v>
       </c>
       <c r="N25" s="6">
         <v>1</v>
@@ -4164,7 +4149,7 @@
         <v>51</v>
       </c>
       <c r="P25" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q25" s="6">
         <v>0</v>
@@ -4179,16 +4164,16 @@
         <v>52</v>
       </c>
       <c r="U25" s="10">
-        <v>67506</v>
+        <v>67750</v>
       </c>
       <c r="V25" s="11">
         <v>11</v>
       </c>
       <c r="W25" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X25" s="12">
-        <v>0.4243056</v>
+        <v>0.39791670000000001</v>
       </c>
       <c r="Y25" s="10">
         <v>0</v>
@@ -4268,10 +4253,10 @@
         <v>46</v>
       </c>
       <c r="F26" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G26" s="5">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>47</v>
@@ -4286,10 +4271,10 @@
         <v>50</v>
       </c>
       <c r="L26" s="6">
-        <v>595</v>
+        <v>101</v>
       </c>
       <c r="M26" s="7">
-        <v>199783.41</v>
+        <v>37772.92</v>
       </c>
       <c r="N26" s="6">
         <v>1</v>
@@ -4298,7 +4283,7 @@
         <v>51</v>
       </c>
       <c r="P26" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q26" s="6">
         <v>0</v>
@@ -4313,16 +4298,16 @@
         <v>52</v>
       </c>
       <c r="U26" s="10">
-        <v>67506</v>
+        <v>67750</v>
       </c>
       <c r="V26" s="11">
         <v>11</v>
       </c>
       <c r="W26" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X26" s="12">
-        <v>0.4243056</v>
+        <v>0.39791670000000001</v>
       </c>
       <c r="Y26" s="10">
         <v>0</v>
@@ -4402,10 +4387,10 @@
         <v>46</v>
       </c>
       <c r="F27" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G27" s="5">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>47</v>
@@ -4420,10 +4405,10 @@
         <v>50</v>
       </c>
       <c r="L27" s="6">
-        <v>596</v>
+        <v>102</v>
       </c>
       <c r="M27" s="7">
-        <v>200119.18</v>
+        <v>38146.910000000003</v>
       </c>
       <c r="N27" s="6">
         <v>1</v>
@@ -4432,7 +4417,7 @@
         <v>51</v>
       </c>
       <c r="P27" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q27" s="6">
         <v>0</v>
@@ -4447,16 +4432,16 @@
         <v>52</v>
       </c>
       <c r="U27" s="10">
-        <v>67506</v>
+        <v>67750</v>
       </c>
       <c r="V27" s="11">
         <v>11</v>
       </c>
       <c r="W27" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X27" s="12">
-        <v>0.4243056</v>
+        <v>0.39791670000000001</v>
       </c>
       <c r="Y27" s="10">
         <v>0</v>
@@ -4536,10 +4521,10 @@
         <v>46</v>
       </c>
       <c r="F28" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G28" s="5">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>47</v>
@@ -4554,10 +4539,10 @@
         <v>50</v>
       </c>
       <c r="L28" s="6">
-        <v>597</v>
+        <v>103</v>
       </c>
       <c r="M28" s="7">
-        <v>200454.95</v>
+        <v>38520.9</v>
       </c>
       <c r="N28" s="6">
         <v>1</v>
@@ -4566,7 +4551,7 @@
         <v>51</v>
       </c>
       <c r="P28" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q28" s="6">
         <v>0</v>
@@ -4581,16 +4566,16 @@
         <v>52</v>
       </c>
       <c r="U28" s="10">
-        <v>67506</v>
+        <v>67750</v>
       </c>
       <c r="V28" s="11">
         <v>11</v>
       </c>
       <c r="W28" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X28" s="12">
-        <v>0.4243056</v>
+        <v>0.39791670000000001</v>
       </c>
       <c r="Y28" s="10">
         <v>0</v>
@@ -4670,10 +4655,10 @@
         <v>46</v>
       </c>
       <c r="F29" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G29" s="5">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>47</v>
@@ -4688,10 +4673,10 @@
         <v>50</v>
       </c>
       <c r="L29" s="6">
-        <v>598</v>
+        <v>104</v>
       </c>
       <c r="M29" s="7">
-        <v>200790.72</v>
+        <v>38894.879999999997</v>
       </c>
       <c r="N29" s="6">
         <v>1</v>
@@ -4700,7 +4685,7 @@
         <v>51</v>
       </c>
       <c r="P29" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q29" s="6">
         <v>0</v>
@@ -4715,16 +4700,16 @@
         <v>52</v>
       </c>
       <c r="U29" s="10">
-        <v>67506</v>
+        <v>67750</v>
       </c>
       <c r="V29" s="11">
         <v>11</v>
       </c>
       <c r="W29" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X29" s="12">
-        <v>0.4243056</v>
+        <v>0.39791670000000001</v>
       </c>
       <c r="Y29" s="10">
         <v>0</v>
@@ -4804,10 +4789,10 @@
         <v>46</v>
       </c>
       <c r="F30" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G30" s="5">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>47</v>
@@ -4822,10 +4807,10 @@
         <v>50</v>
       </c>
       <c r="L30" s="6">
-        <v>599</v>
+        <v>105</v>
       </c>
       <c r="M30" s="7">
-        <v>201126.49</v>
+        <v>39268.870000000003</v>
       </c>
       <c r="N30" s="6">
         <v>1</v>
@@ -4834,7 +4819,7 @@
         <v>51</v>
       </c>
       <c r="P30" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q30" s="6">
         <v>0</v>
@@ -4849,16 +4834,16 @@
         <v>52</v>
       </c>
       <c r="U30" s="10">
-        <v>67506</v>
+        <v>67750</v>
       </c>
       <c r="V30" s="11">
         <v>11</v>
       </c>
       <c r="W30" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X30" s="12">
-        <v>0.4243056</v>
+        <v>0.39791670000000001</v>
       </c>
       <c r="Y30" s="10">
         <v>0</v>
@@ -4938,10 +4923,10 @@
         <v>46</v>
       </c>
       <c r="F31" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G31" s="5">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>47</v>
@@ -4956,10 +4941,10 @@
         <v>50</v>
       </c>
       <c r="L31" s="6">
-        <v>600</v>
+        <v>106</v>
       </c>
       <c r="M31" s="7">
-        <v>201462.26</v>
+        <v>39642.86</v>
       </c>
       <c r="N31" s="6">
         <v>1</v>
@@ -4968,7 +4953,7 @@
         <v>51</v>
       </c>
       <c r="P31" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q31" s="6">
         <v>0</v>
@@ -4983,16 +4968,16 @@
         <v>52</v>
       </c>
       <c r="U31" s="10">
-        <v>67506</v>
+        <v>67750</v>
       </c>
       <c r="V31" s="11">
         <v>11</v>
       </c>
       <c r="W31" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X31" s="12">
-        <v>0.4243056</v>
+        <v>0.39791670000000001</v>
       </c>
       <c r="Y31" s="10">
         <v>0</v>
@@ -5072,10 +5057,10 @@
         <v>46</v>
       </c>
       <c r="F32" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G32" s="5">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>47</v>
@@ -5090,10 +5075,10 @@
         <v>50</v>
       </c>
       <c r="L32" s="6">
-        <v>601</v>
+        <v>107</v>
       </c>
       <c r="M32" s="7">
-        <v>201798.03</v>
+        <v>40016.85</v>
       </c>
       <c r="N32" s="6">
         <v>1</v>
@@ -5102,7 +5087,7 @@
         <v>51</v>
       </c>
       <c r="P32" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q32" s="6">
         <v>0</v>
@@ -5117,16 +5102,16 @@
         <v>52</v>
       </c>
       <c r="U32" s="10">
-        <v>67506</v>
+        <v>67750</v>
       </c>
       <c r="V32" s="11">
         <v>11</v>
       </c>
       <c r="W32" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X32" s="12">
-        <v>0.43819439999999998</v>
+        <v>0.41875000000000001</v>
       </c>
       <c r="Y32" s="10">
         <v>0</v>
@@ -5206,10 +5191,10 @@
         <v>46</v>
       </c>
       <c r="F33" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G33" s="5">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>47</v>
@@ -5224,10 +5209,10 @@
         <v>50</v>
       </c>
       <c r="L33" s="6">
-        <v>602</v>
+        <v>108</v>
       </c>
       <c r="M33" s="7">
-        <v>202133.8</v>
+        <v>40390.839999999997</v>
       </c>
       <c r="N33" s="6">
         <v>1</v>
@@ -5236,7 +5221,7 @@
         <v>51</v>
       </c>
       <c r="P33" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q33" s="6">
         <v>0</v>
@@ -5251,16 +5236,16 @@
         <v>52</v>
       </c>
       <c r="U33" s="10">
-        <v>67506</v>
+        <v>67750</v>
       </c>
       <c r="V33" s="11">
         <v>11</v>
       </c>
       <c r="W33" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X33" s="12">
-        <v>0.43819439999999998</v>
+        <v>0.41875000000000001</v>
       </c>
       <c r="Y33" s="10">
         <v>0</v>
@@ -5340,10 +5325,10 @@
         <v>46</v>
       </c>
       <c r="F34" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G34" s="5">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>47</v>
@@ -5358,10 +5343,10 @@
         <v>50</v>
       </c>
       <c r="L34" s="6">
-        <v>603</v>
+        <v>109</v>
       </c>
       <c r="M34" s="7">
-        <v>202469.57</v>
+        <v>40764.83</v>
       </c>
       <c r="N34" s="6">
         <v>1</v>
@@ -5370,7 +5355,7 @@
         <v>51</v>
       </c>
       <c r="P34" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q34" s="6">
         <v>0</v>
@@ -5385,16 +5370,16 @@
         <v>52</v>
       </c>
       <c r="U34" s="10">
-        <v>67506</v>
+        <v>67750</v>
       </c>
       <c r="V34" s="11">
         <v>11</v>
       </c>
       <c r="W34" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X34" s="12">
-        <v>0.43819439999999998</v>
+        <v>0.41875000000000001</v>
       </c>
       <c r="Y34" s="10">
         <v>0</v>
@@ -5474,10 +5459,10 @@
         <v>46</v>
       </c>
       <c r="F35" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G35" s="5">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>47</v>
@@ -5492,10 +5477,10 @@
         <v>50</v>
       </c>
       <c r="L35" s="6">
-        <v>604</v>
+        <v>110</v>
       </c>
       <c r="M35" s="7">
-        <v>202805.34</v>
+        <v>41138.82</v>
       </c>
       <c r="N35" s="6">
         <v>1</v>
@@ -5504,7 +5489,7 @@
         <v>51</v>
       </c>
       <c r="P35" s="8">
-        <v>335.77</v>
+        <v>373.99</v>
       </c>
       <c r="Q35" s="6">
         <v>0</v>
@@ -5519,16 +5504,16 @@
         <v>52</v>
       </c>
       <c r="U35" s="10">
-        <v>67506</v>
+        <v>67750</v>
       </c>
       <c r="V35" s="11">
         <v>11</v>
       </c>
       <c r="W35" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X35" s="12">
-        <v>0.43819439999999998</v>
+        <v>0.43888890000000003</v>
       </c>
       <c r="Y35" s="10">
         <v>0</v>
@@ -5599,19 +5584,19 @@
         <v>2</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F36" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G36" s="5">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>47</v>
@@ -5626,19 +5611,19 @@
         <v>50</v>
       </c>
       <c r="L36" s="6">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="M36" s="7">
-        <v>5115.3599999999997</v>
+        <v>41512.81</v>
       </c>
       <c r="N36" s="6">
         <v>1</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="P36" s="8">
-        <v>319.70999999999998</v>
+        <v>373.99</v>
       </c>
       <c r="Q36" s="6">
         <v>0</v>
@@ -5653,16 +5638,16 @@
         <v>52</v>
       </c>
       <c r="U36" s="10">
-        <v>68001</v>
+        <v>67750</v>
       </c>
       <c r="V36" s="11">
         <v>11</v>
       </c>
       <c r="W36" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X36" s="12">
-        <v>0.46458329999999998</v>
+        <v>0.43888890000000003</v>
       </c>
       <c r="Y36" s="10">
         <v>0</v>
@@ -5722,7 +5707,7 @@
         <v>53</v>
       </c>
       <c r="AR36" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.3">
@@ -5733,19 +5718,19 @@
         <v>2</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F37" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G37" s="5">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>47</v>
@@ -5760,19 +5745,19 @@
         <v>50</v>
       </c>
       <c r="L37" s="6">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="M37" s="7">
-        <v>5435.07</v>
+        <v>41886.800000000003</v>
       </c>
       <c r="N37" s="6">
         <v>1</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="P37" s="8">
-        <v>319.70999999999998</v>
+        <v>373.99</v>
       </c>
       <c r="Q37" s="6">
         <v>0</v>
@@ -5787,16 +5772,16 @@
         <v>52</v>
       </c>
       <c r="U37" s="10">
-        <v>68001</v>
+        <v>67750</v>
       </c>
       <c r="V37" s="11">
         <v>11</v>
       </c>
       <c r="W37" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X37" s="12">
-        <v>0.46458329999999998</v>
+        <v>0.43888890000000003</v>
       </c>
       <c r="Y37" s="10">
         <v>0</v>
@@ -5856,7 +5841,7 @@
         <v>53</v>
       </c>
       <c r="AR37" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:44" x14ac:dyDescent="0.3">
@@ -5867,19 +5852,19 @@
         <v>2</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F38" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G38" s="5">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>47</v>
@@ -5894,19 +5879,19 @@
         <v>50</v>
       </c>
       <c r="L38" s="6">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="M38" s="7">
-        <v>5754.78</v>
+        <v>42260.79</v>
       </c>
       <c r="N38" s="6">
         <v>1</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="P38" s="8">
-        <v>319.70999999999998</v>
+        <v>373.99</v>
       </c>
       <c r="Q38" s="6">
         <v>0</v>
@@ -5921,16 +5906,16 @@
         <v>52</v>
       </c>
       <c r="U38" s="10">
-        <v>68001</v>
+        <v>67750</v>
       </c>
       <c r="V38" s="11">
         <v>11</v>
       </c>
       <c r="W38" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X38" s="12">
-        <v>0.46458329999999998</v>
+        <v>0.43888890000000003</v>
       </c>
       <c r="Y38" s="10">
         <v>0</v>
@@ -5990,7 +5975,7 @@
         <v>53</v>
       </c>
       <c r="AR38" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:44" x14ac:dyDescent="0.3">
@@ -6001,19 +5986,19 @@
         <v>2</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F39" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G39" s="5">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>47</v>
@@ -6028,19 +6013,19 @@
         <v>50</v>
       </c>
       <c r="L39" s="6">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="M39" s="7">
-        <v>6074.49</v>
+        <v>42634.78</v>
       </c>
       <c r="N39" s="6">
         <v>1</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="P39" s="8">
-        <v>319.70999999999998</v>
+        <v>373.99</v>
       </c>
       <c r="Q39" s="6">
         <v>0</v>
@@ -6055,16 +6040,16 @@
         <v>52</v>
       </c>
       <c r="U39" s="10">
-        <v>68001</v>
+        <v>67750</v>
       </c>
       <c r="V39" s="11">
         <v>11</v>
       </c>
       <c r="W39" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X39" s="12">
-        <v>0.46458329999999998</v>
+        <v>0.43888890000000003</v>
       </c>
       <c r="Y39" s="10">
         <v>0</v>
@@ -6124,7 +6109,7 @@
         <v>53</v>
       </c>
       <c r="AR39" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:44" x14ac:dyDescent="0.3">
@@ -6135,19 +6120,19 @@
         <v>2</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F40" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G40" s="5">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>47</v>
@@ -6162,19 +6147,19 @@
         <v>50</v>
       </c>
       <c r="L40" s="6">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="M40" s="7">
-        <v>6394.2</v>
+        <v>43008.77</v>
       </c>
       <c r="N40" s="6">
         <v>1</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="P40" s="8">
-        <v>319.70999999999998</v>
+        <v>373.99</v>
       </c>
       <c r="Q40" s="6">
         <v>0</v>
@@ -6189,16 +6174,16 @@
         <v>52</v>
       </c>
       <c r="U40" s="10">
-        <v>68001</v>
+        <v>67750</v>
       </c>
       <c r="V40" s="11">
         <v>11</v>
       </c>
       <c r="W40" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X40" s="12">
-        <v>0.46458329999999998</v>
+        <v>0.43888890000000003</v>
       </c>
       <c r="Y40" s="10">
         <v>0</v>
@@ -6258,7 +6243,7 @@
         <v>53</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:44" x14ac:dyDescent="0.3">
@@ -6269,19 +6254,19 @@
         <v>2</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F41" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G41" s="5">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>47</v>
@@ -6296,19 +6281,19 @@
         <v>50</v>
       </c>
       <c r="L41" s="6">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="M41" s="7">
-        <v>6713.91</v>
+        <v>43382.76</v>
       </c>
       <c r="N41" s="6">
         <v>1</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="P41" s="8">
-        <v>319.70999999999998</v>
+        <v>373.99</v>
       </c>
       <c r="Q41" s="6">
         <v>0</v>
@@ -6323,16 +6308,16 @@
         <v>52</v>
       </c>
       <c r="U41" s="10">
-        <v>68001</v>
+        <v>67750</v>
       </c>
       <c r="V41" s="11">
         <v>11</v>
       </c>
       <c r="W41" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X41" s="12">
-        <v>0.46458329999999998</v>
+        <v>0.43958330000000001</v>
       </c>
       <c r="Y41" s="10">
         <v>0</v>
@@ -6392,7 +6377,7 @@
         <v>53</v>
       </c>
       <c r="AR41" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:44" x14ac:dyDescent="0.3">
@@ -6403,19 +6388,19 @@
         <v>2</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F42" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="G42" s="5">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>47</v>
@@ -6430,19 +6415,19 @@
         <v>50</v>
       </c>
       <c r="L42" s="6">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="M42" s="7">
-        <v>7033.62</v>
+        <v>43756.74</v>
       </c>
       <c r="N42" s="6">
         <v>1</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="P42" s="8">
-        <v>319.70999999999998</v>
+        <v>373.99</v>
       </c>
       <c r="Q42" s="6">
         <v>0</v>
@@ -6457,16 +6442,16 @@
         <v>52</v>
       </c>
       <c r="U42" s="10">
-        <v>68001</v>
+        <v>67750</v>
       </c>
       <c r="V42" s="11">
         <v>11</v>
       </c>
       <c r="W42" s="4">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="X42" s="12">
-        <v>0.46458329999999998</v>
+        <v>0.43958330000000001</v>
       </c>
       <c r="Y42" s="10">
         <v>0</v>
@@ -6526,275 +6511,7 @@
         <v>53</v>
       </c>
       <c r="AR42" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="43" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
-        <v>1</v>
-      </c>
-      <c r="B43" s="2">
-        <v>2</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F43" s="4">
-        <v>46296</v>
-      </c>
-      <c r="G43" s="5">
-        <v>9</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L43" s="6">
-        <v>23</v>
-      </c>
-      <c r="M43" s="7">
-        <v>7353.33</v>
-      </c>
-      <c r="N43" s="6">
-        <v>1</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P43" s="8">
-        <v>319.70999999999998</v>
-      </c>
-      <c r="Q43" s="6">
-        <v>0</v>
-      </c>
-      <c r="R43" s="7">
-        <v>0</v>
-      </c>
-      <c r="S43" s="9">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U43" s="10">
-        <v>68001</v>
-      </c>
-      <c r="V43" s="11">
-        <v>11</v>
-      </c>
-      <c r="W43" s="4">
-        <v>46296</v>
-      </c>
-      <c r="X43" s="12">
-        <v>0.46458329999999998</v>
-      </c>
-      <c r="Y43" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC43" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG43" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH43" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI43" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ43" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK43" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL43" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM43" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN43" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO43" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP43" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ43" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR43" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="44" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
-        <v>1</v>
-      </c>
-      <c r="B44" s="2">
-        <v>2</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F44" s="4">
-        <v>46296</v>
-      </c>
-      <c r="G44" s="5">
-        <v>10</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L44" s="6">
-        <v>24</v>
-      </c>
-      <c r="M44" s="7">
-        <v>7673.04</v>
-      </c>
-      <c r="N44" s="6">
-        <v>1</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P44" s="8">
-        <v>319.70999999999998</v>
-      </c>
-      <c r="Q44" s="6">
-        <v>0</v>
-      </c>
-      <c r="R44" s="7">
-        <v>0</v>
-      </c>
-      <c r="S44" s="9">
-        <v>0</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U44" s="10">
-        <v>68001</v>
-      </c>
-      <c r="V44" s="11">
-        <v>11</v>
-      </c>
-      <c r="W44" s="4">
-        <v>46296</v>
-      </c>
-      <c r="X44" s="12">
-        <v>0.46458329999999998</v>
-      </c>
-      <c r="Y44" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB44" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC44" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD44" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE44" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF44" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG44" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH44" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI44" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ44" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK44" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL44" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM44" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN44" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO44" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP44" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ44" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR44" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DBAA370-2D3D-4944-9A79-98F93344EDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F85FF7FF-7D37-423E-930B-97DE3135060D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="42210" yWindow="7665" windowWidth="7080" windowHeight="3630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2D5D4BE-8E91-473C-BF80-6395432B3627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B49F2B91-308A-47EB-A497-06FC1C56F5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3F97B20-A19F-4DCD-9CB1-B8F60FF5B8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51A17FD6-8EA3-46F6-ADDB-A478C5185A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="42210" yWindow="7275" windowWidth="7080" windowHeight="3630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6848" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7406" uniqueCount="841">
   <si>
     <t>Sel</t>
   </si>
@@ -2234,6 +2234,99 @@
   </si>
   <si>
     <t>1025400000093</t>
+  </si>
+  <si>
+    <t>1025400000094</t>
+  </si>
+  <si>
+    <t>1025400000095</t>
+  </si>
+  <si>
+    <t>1025400000096</t>
+  </si>
+  <si>
+    <t>1025400000097</t>
+  </si>
+  <si>
+    <t>1025400000098</t>
+  </si>
+  <si>
+    <t>1025400000099</t>
+  </si>
+  <si>
+    <t>1025400000100</t>
+  </si>
+  <si>
+    <t>1025400000101</t>
+  </si>
+  <si>
+    <t>1025400000102</t>
+  </si>
+  <si>
+    <t>1025400000103</t>
+  </si>
+  <si>
+    <t>1025400000104</t>
+  </si>
+  <si>
+    <t>1025400000105</t>
+  </si>
+  <si>
+    <t>1025400000106</t>
+  </si>
+  <si>
+    <t>1025400000107</t>
+  </si>
+  <si>
+    <t>1025400000108</t>
+  </si>
+  <si>
+    <t>1025400000109</t>
+  </si>
+  <si>
+    <t>1025400000110</t>
+  </si>
+  <si>
+    <t>1025400000111</t>
+  </si>
+  <si>
+    <t>1025400000112</t>
+  </si>
+  <si>
+    <t>1025400000113</t>
+  </si>
+  <si>
+    <t>1025400000114</t>
+  </si>
+  <si>
+    <t>1025400000115</t>
+  </si>
+  <si>
+    <t>1025400000116</t>
+  </si>
+  <si>
+    <t>1025400000117</t>
+  </si>
+  <si>
+    <t>1025400000118</t>
+  </si>
+  <si>
+    <t>1025400000119</t>
+  </si>
+  <si>
+    <t>1025400000120</t>
+  </si>
+  <si>
+    <t>1025400000121</t>
+  </si>
+  <si>
+    <t>1025400000122</t>
+  </si>
+  <si>
+    <t>1025400000123</t>
+  </si>
+  <si>
+    <t>1025400000124</t>
   </si>
   <si>
     <t>2</t>
@@ -3025,7 +3118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR379"/>
+  <dimension ref="A1:AR410"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -49135,7 +49228,7 @@
         <v>719</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E345" s="3" t="s">
         <v>46</v>
@@ -49144,7 +49237,7 @@
         <v>46303</v>
       </c>
       <c r="G345" s="5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H345" s="3" t="s">
         <v>47</v>
@@ -49159,34 +49252,34 @@
         <v>50</v>
       </c>
       <c r="L345" s="6">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="M345" s="7">
-        <v>5817.35</v>
+        <v>2655.95</v>
       </c>
       <c r="N345" s="6">
         <v>1</v>
       </c>
       <c r="O345" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P345" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q345" s="6">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="R345" s="7">
-        <v>5983.56</v>
+        <v>0</v>
       </c>
       <c r="S345" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T345" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U345" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V345" s="11">
         <v>11</v>
@@ -49195,7 +49288,7 @@
         <v>46303</v>
       </c>
       <c r="X345" s="12">
-        <v>0.30555559999999998</v>
+        <v>0.53472220000000004</v>
       </c>
       <c r="Y345" s="10">
         <v>0</v>
@@ -49252,10 +49345,10 @@
         <v>53</v>
       </c>
       <c r="AQ345" s="3" t="s">
-        <v>740</v>
+        <v>53</v>
       </c>
       <c r="AR345" s="3" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="346" spans="1:44" x14ac:dyDescent="0.3">
@@ -49269,7 +49362,7 @@
         <v>719</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E346" s="3" t="s">
         <v>46</v>
@@ -49278,7 +49371,7 @@
         <v>46303</v>
       </c>
       <c r="G346" s="5">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H346" s="3" t="s">
         <v>47</v>
@@ -49293,34 +49386,34 @@
         <v>50</v>
       </c>
       <c r="L346" s="6">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="M346" s="7">
-        <v>5983.56</v>
+        <v>2897.4</v>
       </c>
       <c r="N346" s="6">
         <v>1</v>
       </c>
       <c r="O346" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P346" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q346" s="6">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="R346" s="7">
-        <v>6149.77</v>
+        <v>0</v>
       </c>
       <c r="S346" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T346" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U346" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V346" s="11">
         <v>11</v>
@@ -49329,7 +49422,7 @@
         <v>46303</v>
       </c>
       <c r="X346" s="12">
-        <v>0.3125</v>
+        <v>0.53472220000000004</v>
       </c>
       <c r="Y346" s="10">
         <v>0</v>
@@ -49386,10 +49479,10 @@
         <v>53</v>
       </c>
       <c r="AQ346" s="3" t="s">
-        <v>742</v>
+        <v>53</v>
       </c>
       <c r="AR346" s="3" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
     </row>
     <row r="347" spans="1:44" x14ac:dyDescent="0.3">
@@ -49403,7 +49496,7 @@
         <v>719</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E347" s="3" t="s">
         <v>46</v>
@@ -49412,7 +49505,7 @@
         <v>46303</v>
       </c>
       <c r="G347" s="5">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H347" s="3" t="s">
         <v>47</v>
@@ -49427,34 +49520,34 @@
         <v>50</v>
       </c>
       <c r="L347" s="6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="M347" s="7">
-        <v>6149.77</v>
+        <v>3138.85</v>
       </c>
       <c r="N347" s="6">
         <v>1</v>
       </c>
       <c r="O347" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P347" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q347" s="6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R347" s="7">
-        <v>6315.98</v>
+        <v>0</v>
       </c>
       <c r="S347" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T347" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U347" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V347" s="11">
         <v>11</v>
@@ -49463,7 +49556,7 @@
         <v>46303</v>
       </c>
       <c r="X347" s="12">
-        <v>0.31944440000000002</v>
+        <v>0.53472220000000004</v>
       </c>
       <c r="Y347" s="10">
         <v>0</v>
@@ -49520,10 +49613,10 @@
         <v>53</v>
       </c>
       <c r="AQ347" s="3" t="s">
-        <v>744</v>
+        <v>53</v>
       </c>
       <c r="AR347" s="3" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="348" spans="1:44" x14ac:dyDescent="0.3">
@@ -49537,7 +49630,7 @@
         <v>719</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E348" s="3" t="s">
         <v>46</v>
@@ -49546,7 +49639,7 @@
         <v>46303</v>
       </c>
       <c r="G348" s="5">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H348" s="3" t="s">
         <v>47</v>
@@ -49561,34 +49654,34 @@
         <v>50</v>
       </c>
       <c r="L348" s="6">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="M348" s="7">
-        <v>6315.98</v>
+        <v>3380.3</v>
       </c>
       <c r="N348" s="6">
         <v>1</v>
       </c>
       <c r="O348" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P348" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q348" s="6">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R348" s="7">
-        <v>6482.19</v>
+        <v>0</v>
       </c>
       <c r="S348" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T348" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U348" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V348" s="11">
         <v>11</v>
@@ -49597,7 +49690,7 @@
         <v>46303</v>
       </c>
       <c r="X348" s="12">
-        <v>0.31944440000000002</v>
+        <v>0.53472220000000004</v>
       </c>
       <c r="Y348" s="10">
         <v>0</v>
@@ -49654,10 +49747,10 @@
         <v>53</v>
       </c>
       <c r="AQ348" s="3" t="s">
-        <v>746</v>
+        <v>53</v>
       </c>
       <c r="AR348" s="3" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
     </row>
     <row r="349" spans="1:44" x14ac:dyDescent="0.3">
@@ -49671,7 +49764,7 @@
         <v>719</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E349" s="3" t="s">
         <v>46</v>
@@ -49680,7 +49773,7 @@
         <v>46303</v>
       </c>
       <c r="G349" s="5">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H349" s="3" t="s">
         <v>47</v>
@@ -49695,34 +49788,34 @@
         <v>50</v>
       </c>
       <c r="L349" s="6">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="M349" s="7">
-        <v>6482.19</v>
+        <v>3621.75</v>
       </c>
       <c r="N349" s="6">
         <v>1</v>
       </c>
       <c r="O349" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P349" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q349" s="6">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R349" s="7">
-        <v>6648.4</v>
+        <v>0</v>
       </c>
       <c r="S349" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T349" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U349" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V349" s="11">
         <v>11</v>
@@ -49731,7 +49824,7 @@
         <v>46303</v>
       </c>
       <c r="X349" s="12">
-        <v>0.31944440000000002</v>
+        <v>0.53472220000000004</v>
       </c>
       <c r="Y349" s="10">
         <v>0</v>
@@ -49788,10 +49881,10 @@
         <v>53</v>
       </c>
       <c r="AQ349" s="3" t="s">
-        <v>748</v>
+        <v>53</v>
       </c>
       <c r="AR349" s="3" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
     </row>
     <row r="350" spans="1:44" x14ac:dyDescent="0.3">
@@ -49805,7 +49898,7 @@
         <v>719</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E350" s="3" t="s">
         <v>46</v>
@@ -49814,7 +49907,7 @@
         <v>46303</v>
       </c>
       <c r="G350" s="5">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H350" s="3" t="s">
         <v>47</v>
@@ -49829,34 +49922,34 @@
         <v>50</v>
       </c>
       <c r="L350" s="6">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="M350" s="7">
-        <v>6648.4</v>
+        <v>3863.2</v>
       </c>
       <c r="N350" s="6">
         <v>1</v>
       </c>
       <c r="O350" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P350" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q350" s="6">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="R350" s="7">
-        <v>6814.61</v>
+        <v>0</v>
       </c>
       <c r="S350" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T350" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U350" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V350" s="11">
         <v>11</v>
@@ -49865,7 +49958,7 @@
         <v>46303</v>
       </c>
       <c r="X350" s="12">
-        <v>0.31944440000000002</v>
+        <v>0.53472220000000004</v>
       </c>
       <c r="Y350" s="10">
         <v>0</v>
@@ -49922,10 +50015,10 @@
         <v>53</v>
       </c>
       <c r="AQ350" s="3" t="s">
-        <v>750</v>
+        <v>53</v>
       </c>
       <c r="AR350" s="3" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
     </row>
     <row r="351" spans="1:44" x14ac:dyDescent="0.3">
@@ -49939,7 +50032,7 @@
         <v>719</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E351" s="3" t="s">
         <v>46</v>
@@ -49948,7 +50041,7 @@
         <v>46303</v>
       </c>
       <c r="G351" s="5">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H351" s="3" t="s">
         <v>47</v>
@@ -49963,34 +50056,34 @@
         <v>50</v>
       </c>
       <c r="L351" s="6">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="M351" s="7">
-        <v>6814.61</v>
+        <v>4104.6499999999996</v>
       </c>
       <c r="N351" s="6">
         <v>1</v>
       </c>
       <c r="O351" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P351" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q351" s="6">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R351" s="7">
-        <v>6980.82</v>
+        <v>0</v>
       </c>
       <c r="S351" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T351" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U351" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V351" s="11">
         <v>11</v>
@@ -49999,7 +50092,7 @@
         <v>46303</v>
       </c>
       <c r="X351" s="12">
-        <v>0.32638889999999998</v>
+        <v>0.53472220000000004</v>
       </c>
       <c r="Y351" s="10">
         <v>0</v>
@@ -50056,10 +50149,10 @@
         <v>53</v>
       </c>
       <c r="AQ351" s="3" t="s">
-        <v>752</v>
+        <v>53</v>
       </c>
       <c r="AR351" s="3" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
     </row>
     <row r="352" spans="1:44" x14ac:dyDescent="0.3">
@@ -50073,7 +50166,7 @@
         <v>719</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E352" s="3" t="s">
         <v>46</v>
@@ -50082,7 +50175,7 @@
         <v>46303</v>
       </c>
       <c r="G352" s="5">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H352" s="3" t="s">
         <v>47</v>
@@ -50097,34 +50190,34 @@
         <v>50</v>
       </c>
       <c r="L352" s="6">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="M352" s="7">
-        <v>6980.82</v>
+        <v>4346.1000000000004</v>
       </c>
       <c r="N352" s="6">
         <v>1</v>
       </c>
       <c r="O352" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P352" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q352" s="6">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R352" s="7">
-        <v>7147.03</v>
+        <v>0</v>
       </c>
       <c r="S352" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T352" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U352" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V352" s="11">
         <v>11</v>
@@ -50133,7 +50226,7 @@
         <v>46303</v>
       </c>
       <c r="X352" s="12">
-        <v>0.32638889999999998</v>
+        <v>0.53472220000000004</v>
       </c>
       <c r="Y352" s="10">
         <v>0</v>
@@ -50190,10 +50283,10 @@
         <v>53</v>
       </c>
       <c r="AQ352" s="3" t="s">
-        <v>754</v>
+        <v>53</v>
       </c>
       <c r="AR352" s="3" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
     </row>
     <row r="353" spans="1:44" x14ac:dyDescent="0.3">
@@ -50207,7 +50300,7 @@
         <v>719</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E353" s="3" t="s">
         <v>46</v>
@@ -50216,7 +50309,7 @@
         <v>46303</v>
       </c>
       <c r="G353" s="5">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H353" s="3" t="s">
         <v>47</v>
@@ -50231,34 +50324,34 @@
         <v>50</v>
       </c>
       <c r="L353" s="6">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="M353" s="7">
-        <v>7147.03</v>
+        <v>4587.55</v>
       </c>
       <c r="N353" s="6">
         <v>1</v>
       </c>
       <c r="O353" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P353" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q353" s="6">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="R353" s="7">
-        <v>7313.24</v>
+        <v>0</v>
       </c>
       <c r="S353" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T353" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U353" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V353" s="11">
         <v>11</v>
@@ -50267,7 +50360,7 @@
         <v>46303</v>
       </c>
       <c r="X353" s="12">
-        <v>0.32638889999999998</v>
+        <v>0.53472220000000004</v>
       </c>
       <c r="Y353" s="10">
         <v>0</v>
@@ -50324,10 +50417,10 @@
         <v>53</v>
       </c>
       <c r="AQ353" s="3" t="s">
-        <v>756</v>
+        <v>53</v>
       </c>
       <c r="AR353" s="3" t="s">
-        <v>757</v>
+        <v>746</v>
       </c>
     </row>
     <row r="354" spans="1:44" x14ac:dyDescent="0.3">
@@ -50341,7 +50434,7 @@
         <v>719</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E354" s="3" t="s">
         <v>46</v>
@@ -50350,7 +50443,7 @@
         <v>46303</v>
       </c>
       <c r="G354" s="5">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H354" s="3" t="s">
         <v>47</v>
@@ -50365,34 +50458,34 @@
         <v>50</v>
       </c>
       <c r="L354" s="6">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="M354" s="7">
-        <v>7313.24</v>
+        <v>4829</v>
       </c>
       <c r="N354" s="6">
         <v>1</v>
       </c>
       <c r="O354" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P354" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q354" s="6">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="R354" s="7">
-        <v>7479.45</v>
+        <v>0</v>
       </c>
       <c r="S354" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T354" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U354" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V354" s="11">
         <v>11</v>
@@ -50401,7 +50494,7 @@
         <v>46303</v>
       </c>
       <c r="X354" s="12">
-        <v>0.36111110000000002</v>
+        <v>0.54166669999999995</v>
       </c>
       <c r="Y354" s="10">
         <v>0</v>
@@ -50458,10 +50551,10 @@
         <v>53</v>
       </c>
       <c r="AQ354" s="3" t="s">
-        <v>758</v>
+        <v>53</v>
       </c>
       <c r="AR354" s="3" t="s">
-        <v>759</v>
+        <v>747</v>
       </c>
     </row>
     <row r="355" spans="1:44" x14ac:dyDescent="0.3">
@@ -50475,7 +50568,7 @@
         <v>719</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E355" s="3" t="s">
         <v>46</v>
@@ -50484,7 +50577,7 @@
         <v>46303</v>
       </c>
       <c r="G355" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H355" s="3" t="s">
         <v>47</v>
@@ -50499,34 +50592,34 @@
         <v>50</v>
       </c>
       <c r="L355" s="6">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="M355" s="7">
-        <v>7479.45</v>
+        <v>5070.45</v>
       </c>
       <c r="N355" s="6">
         <v>1</v>
       </c>
       <c r="O355" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P355" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q355" s="6">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R355" s="7">
-        <v>7645.66</v>
+        <v>0</v>
       </c>
       <c r="S355" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T355" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U355" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V355" s="11">
         <v>11</v>
@@ -50535,7 +50628,7 @@
         <v>46303</v>
       </c>
       <c r="X355" s="12">
-        <v>0.36111110000000002</v>
+        <v>0.54166669999999995</v>
       </c>
       <c r="Y355" s="10">
         <v>0</v>
@@ -50592,10 +50685,10 @@
         <v>53</v>
       </c>
       <c r="AQ355" s="3" t="s">
-        <v>760</v>
+        <v>53</v>
       </c>
       <c r="AR355" s="3" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
     </row>
     <row r="356" spans="1:44" x14ac:dyDescent="0.3">
@@ -50609,7 +50702,7 @@
         <v>719</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E356" s="3" t="s">
         <v>46</v>
@@ -50618,7 +50711,7 @@
         <v>46303</v>
       </c>
       <c r="G356" s="5">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H356" s="3" t="s">
         <v>47</v>
@@ -50633,34 +50726,34 @@
         <v>50</v>
       </c>
       <c r="L356" s="6">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="M356" s="7">
-        <v>7645.66</v>
+        <v>5311.9</v>
       </c>
       <c r="N356" s="6">
         <v>1</v>
       </c>
       <c r="O356" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P356" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q356" s="6">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="R356" s="7">
-        <v>7811.87</v>
+        <v>0</v>
       </c>
       <c r="S356" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T356" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U356" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V356" s="11">
         <v>11</v>
@@ -50669,7 +50762,7 @@
         <v>46303</v>
       </c>
       <c r="X356" s="12">
-        <v>0.36111110000000002</v>
+        <v>0.54166669999999995</v>
       </c>
       <c r="Y356" s="10">
         <v>0</v>
@@ -50726,10 +50819,10 @@
         <v>53</v>
       </c>
       <c r="AQ356" s="3" t="s">
-        <v>762</v>
+        <v>53</v>
       </c>
       <c r="AR356" s="3" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
     </row>
     <row r="357" spans="1:44" x14ac:dyDescent="0.3">
@@ -50743,7 +50836,7 @@
         <v>719</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E357" s="3" t="s">
         <v>46</v>
@@ -50752,7 +50845,7 @@
         <v>46303</v>
       </c>
       <c r="G357" s="5">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H357" s="3" t="s">
         <v>47</v>
@@ -50767,34 +50860,34 @@
         <v>50</v>
       </c>
       <c r="L357" s="6">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="M357" s="7">
-        <v>7811.87</v>
+        <v>5553.35</v>
       </c>
       <c r="N357" s="6">
         <v>1</v>
       </c>
       <c r="O357" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P357" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q357" s="6">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="R357" s="7">
-        <v>7978.08</v>
+        <v>0</v>
       </c>
       <c r="S357" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T357" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U357" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V357" s="11">
         <v>11</v>
@@ -50803,7 +50896,7 @@
         <v>46303</v>
       </c>
       <c r="X357" s="12">
-        <v>0.36111110000000002</v>
+        <v>0.54166669999999995</v>
       </c>
       <c r="Y357" s="10">
         <v>0</v>
@@ -50860,10 +50953,10 @@
         <v>53</v>
       </c>
       <c r="AQ357" s="3" t="s">
-        <v>764</v>
+        <v>53</v>
       </c>
       <c r="AR357" s="3" t="s">
-        <v>765</v>
+        <v>750</v>
       </c>
     </row>
     <row r="358" spans="1:44" x14ac:dyDescent="0.3">
@@ -50877,7 +50970,7 @@
         <v>719</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E358" s="3" t="s">
         <v>46</v>
@@ -50886,7 +50979,7 @@
         <v>46303</v>
       </c>
       <c r="G358" s="5">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H358" s="3" t="s">
         <v>47</v>
@@ -50901,34 +50994,34 @@
         <v>50</v>
       </c>
       <c r="L358" s="6">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="M358" s="7">
-        <v>7978.08</v>
+        <v>5794.8</v>
       </c>
       <c r="N358" s="6">
         <v>1</v>
       </c>
       <c r="O358" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P358" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q358" s="6">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="R358" s="7">
-        <v>8144.29</v>
+        <v>0</v>
       </c>
       <c r="S358" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T358" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U358" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V358" s="11">
         <v>11</v>
@@ -50937,7 +51030,7 @@
         <v>46303</v>
       </c>
       <c r="X358" s="12">
-        <v>0.36111110000000002</v>
+        <v>0.54166669999999995</v>
       </c>
       <c r="Y358" s="10">
         <v>0</v>
@@ -50994,10 +51087,10 @@
         <v>53</v>
       </c>
       <c r="AQ358" s="3" t="s">
-        <v>766</v>
+        <v>53</v>
       </c>
       <c r="AR358" s="3" t="s">
-        <v>767</v>
+        <v>751</v>
       </c>
     </row>
     <row r="359" spans="1:44" x14ac:dyDescent="0.3">
@@ -51011,7 +51104,7 @@
         <v>719</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E359" s="3" t="s">
         <v>46</v>
@@ -51020,7 +51113,7 @@
         <v>46303</v>
       </c>
       <c r="G359" s="5">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H359" s="3" t="s">
         <v>47</v>
@@ -51035,34 +51128,34 @@
         <v>50</v>
       </c>
       <c r="L359" s="6">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="M359" s="7">
-        <v>8144.29</v>
+        <v>6036.25</v>
       </c>
       <c r="N359" s="6">
         <v>1</v>
       </c>
       <c r="O359" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P359" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q359" s="6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R359" s="7">
-        <v>8310.5</v>
+        <v>0</v>
       </c>
       <c r="S359" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T359" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U359" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V359" s="11">
         <v>11</v>
@@ -51071,7 +51164,7 @@
         <v>46303</v>
       </c>
       <c r="X359" s="12">
-        <v>0.36111110000000002</v>
+        <v>0.56944439999999996</v>
       </c>
       <c r="Y359" s="10">
         <v>0</v>
@@ -51128,10 +51221,10 @@
         <v>53</v>
       </c>
       <c r="AQ359" s="3" t="s">
-        <v>768</v>
+        <v>53</v>
       </c>
       <c r="AR359" s="3" t="s">
-        <v>769</v>
+        <v>752</v>
       </c>
     </row>
     <row r="360" spans="1:44" x14ac:dyDescent="0.3">
@@ -51145,7 +51238,7 @@
         <v>719</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E360" s="3" t="s">
         <v>46</v>
@@ -51154,7 +51247,7 @@
         <v>46303</v>
       </c>
       <c r="G360" s="5">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H360" s="3" t="s">
         <v>47</v>
@@ -51169,34 +51262,34 @@
         <v>50</v>
       </c>
       <c r="L360" s="6">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="M360" s="7">
-        <v>8310.5</v>
+        <v>6277.7</v>
       </c>
       <c r="N360" s="6">
         <v>1</v>
       </c>
       <c r="O360" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P360" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q360" s="6">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="R360" s="7">
-        <v>8476.7099999999991</v>
+        <v>0</v>
       </c>
       <c r="S360" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T360" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U360" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V360" s="11">
         <v>11</v>
@@ -51205,7 +51298,7 @@
         <v>46303</v>
       </c>
       <c r="X360" s="12">
-        <v>0.36111110000000002</v>
+        <v>0.56944439999999996</v>
       </c>
       <c r="Y360" s="10">
         <v>0</v>
@@ -51262,10 +51355,10 @@
         <v>53</v>
       </c>
       <c r="AQ360" s="3" t="s">
-        <v>770</v>
+        <v>53</v>
       </c>
       <c r="AR360" s="3" t="s">
-        <v>771</v>
+        <v>753</v>
       </c>
     </row>
     <row r="361" spans="1:44" x14ac:dyDescent="0.3">
@@ -51279,7 +51372,7 @@
         <v>719</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E361" s="3" t="s">
         <v>46</v>
@@ -51288,7 +51381,7 @@
         <v>46303</v>
       </c>
       <c r="G361" s="5">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H361" s="3" t="s">
         <v>47</v>
@@ -51303,34 +51396,34 @@
         <v>50</v>
       </c>
       <c r="L361" s="6">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="M361" s="7">
-        <v>8476.7099999999991</v>
+        <v>6519.15</v>
       </c>
       <c r="N361" s="6">
         <v>1</v>
       </c>
       <c r="O361" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P361" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q361" s="6">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="R361" s="7">
-        <v>8642.92</v>
+        <v>0</v>
       </c>
       <c r="S361" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T361" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U361" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V361" s="11">
         <v>11</v>
@@ -51339,7 +51432,7 @@
         <v>46303</v>
       </c>
       <c r="X361" s="12">
-        <v>0.36111110000000002</v>
+        <v>0.56944439999999996</v>
       </c>
       <c r="Y361" s="10">
         <v>0</v>
@@ -51396,10 +51489,10 @@
         <v>53</v>
       </c>
       <c r="AQ361" s="3" t="s">
-        <v>772</v>
+        <v>53</v>
       </c>
       <c r="AR361" s="3" t="s">
-        <v>773</v>
+        <v>754</v>
       </c>
     </row>
     <row r="362" spans="1:44" x14ac:dyDescent="0.3">
@@ -51413,7 +51506,7 @@
         <v>719</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E362" s="3" t="s">
         <v>46</v>
@@ -51422,7 +51515,7 @@
         <v>46303</v>
       </c>
       <c r="G362" s="5">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H362" s="3" t="s">
         <v>47</v>
@@ -51437,34 +51530,34 @@
         <v>50</v>
       </c>
       <c r="L362" s="6">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="M362" s="7">
-        <v>8642.92</v>
+        <v>6760.6</v>
       </c>
       <c r="N362" s="6">
         <v>1</v>
       </c>
       <c r="O362" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P362" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q362" s="6">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="R362" s="7">
-        <v>8809.1299999999992</v>
+        <v>0</v>
       </c>
       <c r="S362" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T362" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U362" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V362" s="11">
         <v>11</v>
@@ -51473,7 +51566,7 @@
         <v>46303</v>
       </c>
       <c r="X362" s="12">
-        <v>0.36111110000000002</v>
+        <v>0.56944439999999996</v>
       </c>
       <c r="Y362" s="10">
         <v>0</v>
@@ -51530,10 +51623,10 @@
         <v>53</v>
       </c>
       <c r="AQ362" s="3" t="s">
-        <v>774</v>
+        <v>53</v>
       </c>
       <c r="AR362" s="3" t="s">
-        <v>775</v>
+        <v>755</v>
       </c>
     </row>
     <row r="363" spans="1:44" x14ac:dyDescent="0.3">
@@ -51547,7 +51640,7 @@
         <v>719</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E363" s="3" t="s">
         <v>46</v>
@@ -51556,7 +51649,7 @@
         <v>46303</v>
       </c>
       <c r="G363" s="5">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H363" s="3" t="s">
         <v>47</v>
@@ -51571,34 +51664,34 @@
         <v>50</v>
       </c>
       <c r="L363" s="6">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="M363" s="7">
-        <v>8809.1299999999992</v>
+        <v>7002.05</v>
       </c>
       <c r="N363" s="6">
         <v>1</v>
       </c>
       <c r="O363" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P363" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q363" s="6">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="R363" s="7">
-        <v>8975.34</v>
+        <v>0</v>
       </c>
       <c r="S363" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T363" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U363" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V363" s="11">
         <v>11</v>
@@ -51607,7 +51700,7 @@
         <v>46303</v>
       </c>
       <c r="X363" s="12">
-        <v>0.36111110000000002</v>
+        <v>0.56944439999999996</v>
       </c>
       <c r="Y363" s="10">
         <v>0</v>
@@ -51664,10 +51757,10 @@
         <v>53</v>
       </c>
       <c r="AQ363" s="3" t="s">
-        <v>776</v>
+        <v>53</v>
       </c>
       <c r="AR363" s="3" t="s">
-        <v>777</v>
+        <v>756</v>
       </c>
     </row>
     <row r="364" spans="1:44" x14ac:dyDescent="0.3">
@@ -51681,7 +51774,7 @@
         <v>719</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E364" s="3" t="s">
         <v>46</v>
@@ -51690,7 +51783,7 @@
         <v>46303</v>
       </c>
       <c r="G364" s="5">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H364" s="3" t="s">
         <v>47</v>
@@ -51705,34 +51798,34 @@
         <v>50</v>
       </c>
       <c r="L364" s="6">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="M364" s="7">
-        <v>8975.34</v>
+        <v>7243.5</v>
       </c>
       <c r="N364" s="6">
         <v>1</v>
       </c>
       <c r="O364" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P364" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q364" s="6">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="R364" s="7">
-        <v>9141.5499999999993</v>
+        <v>0</v>
       </c>
       <c r="S364" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T364" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U364" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V364" s="11">
         <v>11</v>
@@ -51741,7 +51834,7 @@
         <v>46303</v>
       </c>
       <c r="X364" s="12">
-        <v>0.38194440000000002</v>
+        <v>0.56944439999999996</v>
       </c>
       <c r="Y364" s="10">
         <v>0</v>
@@ -51798,10 +51891,10 @@
         <v>53</v>
       </c>
       <c r="AQ364" s="3" t="s">
-        <v>778</v>
+        <v>53</v>
       </c>
       <c r="AR364" s="3" t="s">
-        <v>779</v>
+        <v>757</v>
       </c>
     </row>
     <row r="365" spans="1:44" x14ac:dyDescent="0.3">
@@ -51815,7 +51908,7 @@
         <v>719</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E365" s="3" t="s">
         <v>46</v>
@@ -51824,7 +51917,7 @@
         <v>46303</v>
       </c>
       <c r="G365" s="5">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H365" s="3" t="s">
         <v>47</v>
@@ -51839,34 +51932,34 @@
         <v>50</v>
       </c>
       <c r="L365" s="6">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="M365" s="7">
-        <v>9141.5499999999993</v>
+        <v>7484.95</v>
       </c>
       <c r="N365" s="6">
         <v>1</v>
       </c>
       <c r="O365" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P365" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q365" s="6">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="R365" s="7">
-        <v>9307.76</v>
+        <v>0</v>
       </c>
       <c r="S365" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T365" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U365" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V365" s="11">
         <v>11</v>
@@ -51875,7 +51968,7 @@
         <v>46303</v>
       </c>
       <c r="X365" s="12">
-        <v>0.38194440000000002</v>
+        <v>0.56944439999999996</v>
       </c>
       <c r="Y365" s="10">
         <v>0</v>
@@ -51932,10 +52025,10 @@
         <v>53</v>
       </c>
       <c r="AQ365" s="3" t="s">
-        <v>780</v>
+        <v>53</v>
       </c>
       <c r="AR365" s="3" t="s">
-        <v>781</v>
+        <v>758</v>
       </c>
     </row>
     <row r="366" spans="1:44" x14ac:dyDescent="0.3">
@@ -51949,7 +52042,7 @@
         <v>719</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E366" s="3" t="s">
         <v>46</v>
@@ -51958,7 +52051,7 @@
         <v>46303</v>
       </c>
       <c r="G366" s="5">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H366" s="3" t="s">
         <v>47</v>
@@ -51973,34 +52066,34 @@
         <v>50</v>
       </c>
       <c r="L366" s="6">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="M366" s="7">
-        <v>9307.76</v>
+        <v>7726.4</v>
       </c>
       <c r="N366" s="6">
         <v>1</v>
       </c>
       <c r="O366" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P366" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q366" s="6">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="R366" s="7">
-        <v>9473.9699999999993</v>
+        <v>0</v>
       </c>
       <c r="S366" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T366" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U366" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V366" s="11">
         <v>11</v>
@@ -52009,7 +52102,7 @@
         <v>46303</v>
       </c>
       <c r="X366" s="12">
-        <v>0.38194440000000002</v>
+        <v>0.56944439999999996</v>
       </c>
       <c r="Y366" s="10">
         <v>0</v>
@@ -52066,10 +52159,10 @@
         <v>53</v>
       </c>
       <c r="AQ366" s="3" t="s">
-        <v>782</v>
+        <v>53</v>
       </c>
       <c r="AR366" s="3" t="s">
-        <v>783</v>
+        <v>759</v>
       </c>
     </row>
     <row r="367" spans="1:44" x14ac:dyDescent="0.3">
@@ -52083,7 +52176,7 @@
         <v>719</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E367" s="3" t="s">
         <v>46</v>
@@ -52092,7 +52185,7 @@
         <v>46303</v>
       </c>
       <c r="G367" s="5">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H367" s="3" t="s">
         <v>47</v>
@@ -52107,34 +52200,34 @@
         <v>50</v>
       </c>
       <c r="L367" s="6">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="M367" s="7">
-        <v>9473.9699999999993</v>
+        <v>7967.85</v>
       </c>
       <c r="N367" s="6">
         <v>1</v>
       </c>
       <c r="O367" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P367" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q367" s="6">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R367" s="7">
-        <v>9640.18</v>
+        <v>0</v>
       </c>
       <c r="S367" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T367" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U367" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V367" s="11">
         <v>11</v>
@@ -52143,7 +52236,7 @@
         <v>46303</v>
       </c>
       <c r="X367" s="12">
-        <v>0.38194440000000002</v>
+        <v>0.56944439999999996</v>
       </c>
       <c r="Y367" s="10">
         <v>0</v>
@@ -52200,10 +52293,10 @@
         <v>53</v>
       </c>
       <c r="AQ367" s="3" t="s">
-        <v>784</v>
+        <v>53</v>
       </c>
       <c r="AR367" s="3" t="s">
-        <v>785</v>
+        <v>760</v>
       </c>
     </row>
     <row r="368" spans="1:44" x14ac:dyDescent="0.3">
@@ -52217,7 +52310,7 @@
         <v>719</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E368" s="3" t="s">
         <v>46</v>
@@ -52226,7 +52319,7 @@
         <v>46303</v>
       </c>
       <c r="G368" s="5">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H368" s="3" t="s">
         <v>47</v>
@@ -52241,34 +52334,34 @@
         <v>50</v>
       </c>
       <c r="L368" s="6">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="M368" s="7">
-        <v>9640.18</v>
+        <v>8209.2999999999993</v>
       </c>
       <c r="N368" s="6">
         <v>1</v>
       </c>
       <c r="O368" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P368" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q368" s="6">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="R368" s="7">
-        <v>9806.39</v>
+        <v>0</v>
       </c>
       <c r="S368" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T368" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U368" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V368" s="11">
         <v>11</v>
@@ -52277,7 +52370,7 @@
         <v>46303</v>
       </c>
       <c r="X368" s="12">
-        <v>0.38194440000000002</v>
+        <v>0.56944439999999996</v>
       </c>
       <c r="Y368" s="10">
         <v>0</v>
@@ -52334,10 +52427,10 @@
         <v>53</v>
       </c>
       <c r="AQ368" s="3" t="s">
-        <v>786</v>
+        <v>53</v>
       </c>
       <c r="AR368" s="3" t="s">
-        <v>787</v>
+        <v>761</v>
       </c>
     </row>
     <row r="369" spans="1:44" x14ac:dyDescent="0.3">
@@ -52351,7 +52444,7 @@
         <v>719</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E369" s="3" t="s">
         <v>46</v>
@@ -52360,7 +52453,7 @@
         <v>46303</v>
       </c>
       <c r="G369" s="5">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H369" s="3" t="s">
         <v>47</v>
@@ -52375,34 +52468,34 @@
         <v>50</v>
       </c>
       <c r="L369" s="6">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="M369" s="7">
-        <v>9806.39</v>
+        <v>8450.75</v>
       </c>
       <c r="N369" s="6">
         <v>1</v>
       </c>
       <c r="O369" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P369" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q369" s="6">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R369" s="7">
-        <v>9972.6</v>
+        <v>0</v>
       </c>
       <c r="S369" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T369" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U369" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V369" s="11">
         <v>11</v>
@@ -52411,7 +52504,7 @@
         <v>46303</v>
       </c>
       <c r="X369" s="12">
-        <v>0.38194440000000002</v>
+        <v>0.56944439999999996</v>
       </c>
       <c r="Y369" s="10">
         <v>0</v>
@@ -52468,10 +52561,10 @@
         <v>53</v>
       </c>
       <c r="AQ369" s="3" t="s">
-        <v>788</v>
+        <v>53</v>
       </c>
       <c r="AR369" s="3" t="s">
-        <v>789</v>
+        <v>762</v>
       </c>
     </row>
     <row r="370" spans="1:44" x14ac:dyDescent="0.3">
@@ -52485,7 +52578,7 @@
         <v>719</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E370" s="3" t="s">
         <v>46</v>
@@ -52494,7 +52587,7 @@
         <v>46303</v>
       </c>
       <c r="G370" s="5">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H370" s="3" t="s">
         <v>47</v>
@@ -52509,34 +52602,34 @@
         <v>50</v>
       </c>
       <c r="L370" s="6">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="M370" s="7">
-        <v>9972.6</v>
+        <v>8692.2000000000007</v>
       </c>
       <c r="N370" s="6">
         <v>1</v>
       </c>
       <c r="O370" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P370" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q370" s="6">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="R370" s="7">
-        <v>10138.81</v>
+        <v>0</v>
       </c>
       <c r="S370" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T370" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U370" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V370" s="11">
         <v>11</v>
@@ -52545,7 +52638,7 @@
         <v>46303</v>
       </c>
       <c r="X370" s="12">
-        <v>0.38194440000000002</v>
+        <v>0.56944439999999996</v>
       </c>
       <c r="Y370" s="10">
         <v>0</v>
@@ -52602,10 +52695,10 @@
         <v>53</v>
       </c>
       <c r="AQ370" s="3" t="s">
-        <v>790</v>
+        <v>53</v>
       </c>
       <c r="AR370" s="3" t="s">
-        <v>791</v>
+        <v>763</v>
       </c>
     </row>
     <row r="371" spans="1:44" x14ac:dyDescent="0.3">
@@ -52619,7 +52712,7 @@
         <v>719</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E371" s="3" t="s">
         <v>46</v>
@@ -52628,7 +52721,7 @@
         <v>46303</v>
       </c>
       <c r="G371" s="5">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H371" s="3" t="s">
         <v>47</v>
@@ -52643,34 +52736,34 @@
         <v>50</v>
       </c>
       <c r="L371" s="6">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="M371" s="7">
-        <v>10138.81</v>
+        <v>8933.65</v>
       </c>
       <c r="N371" s="6">
         <v>1</v>
       </c>
       <c r="O371" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P371" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q371" s="6">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="R371" s="7">
-        <v>10305.02</v>
+        <v>0</v>
       </c>
       <c r="S371" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T371" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U371" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V371" s="11">
         <v>11</v>
@@ -52679,7 +52772,7 @@
         <v>46303</v>
       </c>
       <c r="X371" s="12">
-        <v>0.38194440000000002</v>
+        <v>0.56944439999999996</v>
       </c>
       <c r="Y371" s="10">
         <v>0</v>
@@ -52736,10 +52829,10 @@
         <v>53</v>
       </c>
       <c r="AQ371" s="3" t="s">
-        <v>792</v>
+        <v>53</v>
       </c>
       <c r="AR371" s="3" t="s">
-        <v>793</v>
+        <v>764</v>
       </c>
     </row>
     <row r="372" spans="1:44" x14ac:dyDescent="0.3">
@@ -52753,7 +52846,7 @@
         <v>719</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E372" s="3" t="s">
         <v>46</v>
@@ -52762,7 +52855,7 @@
         <v>46303</v>
       </c>
       <c r="G372" s="5">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H372" s="3" t="s">
         <v>47</v>
@@ -52777,34 +52870,34 @@
         <v>50</v>
       </c>
       <c r="L372" s="6">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="M372" s="7">
-        <v>10305.02</v>
+        <v>9175.1</v>
       </c>
       <c r="N372" s="6">
         <v>1</v>
       </c>
       <c r="O372" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P372" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q372" s="6">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="R372" s="7">
-        <v>10471.23</v>
+        <v>0</v>
       </c>
       <c r="S372" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T372" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U372" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V372" s="11">
         <v>11</v>
@@ -52813,7 +52906,7 @@
         <v>46303</v>
       </c>
       <c r="X372" s="12">
-        <v>0.38194440000000002</v>
+        <v>0.56944439999999996</v>
       </c>
       <c r="Y372" s="10">
         <v>0</v>
@@ -52870,10 +52963,10 @@
         <v>53</v>
       </c>
       <c r="AQ372" s="3" t="s">
-        <v>794</v>
+        <v>53</v>
       </c>
       <c r="AR372" s="3" t="s">
-        <v>795</v>
+        <v>765</v>
       </c>
     </row>
     <row r="373" spans="1:44" x14ac:dyDescent="0.3">
@@ -52887,7 +52980,7 @@
         <v>719</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E373" s="3" t="s">
         <v>46</v>
@@ -52896,7 +52989,7 @@
         <v>46303</v>
       </c>
       <c r="G373" s="5">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="H373" s="3" t="s">
         <v>47</v>
@@ -52911,34 +53004,34 @@
         <v>50</v>
       </c>
       <c r="L373" s="6">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="M373" s="7">
-        <v>10471.23</v>
+        <v>9416.5499999999993</v>
       </c>
       <c r="N373" s="6">
         <v>1</v>
       </c>
       <c r="O373" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P373" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q373" s="6">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R373" s="7">
-        <v>10637.44</v>
+        <v>0</v>
       </c>
       <c r="S373" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T373" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U373" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V373" s="11">
         <v>11</v>
@@ -52947,7 +53040,7 @@
         <v>46303</v>
       </c>
       <c r="X373" s="12">
-        <v>0.38194440000000002</v>
+        <v>0.56944439999999996</v>
       </c>
       <c r="Y373" s="10">
         <v>0</v>
@@ -53004,10 +53097,10 @@
         <v>53</v>
       </c>
       <c r="AQ373" s="3" t="s">
-        <v>796</v>
+        <v>53</v>
       </c>
       <c r="AR373" s="3" t="s">
-        <v>797</v>
+        <v>766</v>
       </c>
     </row>
     <row r="374" spans="1:44" x14ac:dyDescent="0.3">
@@ -53021,7 +53114,7 @@
         <v>719</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E374" s="3" t="s">
         <v>46</v>
@@ -53030,7 +53123,7 @@
         <v>46303</v>
       </c>
       <c r="G374" s="5">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="H374" s="3" t="s">
         <v>47</v>
@@ -53045,34 +53138,34 @@
         <v>50</v>
       </c>
       <c r="L374" s="6">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="M374" s="7">
-        <v>10637.44</v>
+        <v>9658</v>
       </c>
       <c r="N374" s="6">
         <v>1</v>
       </c>
       <c r="O374" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P374" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q374" s="6">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="R374" s="7">
-        <v>10803.65</v>
+        <v>0</v>
       </c>
       <c r="S374" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T374" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U374" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V374" s="11">
         <v>11</v>
@@ -53081,7 +53174,7 @@
         <v>46303</v>
       </c>
       <c r="X374" s="12">
-        <v>0.38194440000000002</v>
+        <v>0.56944439999999996</v>
       </c>
       <c r="Y374" s="10">
         <v>0</v>
@@ -53138,10 +53231,10 @@
         <v>53</v>
       </c>
       <c r="AQ374" s="3" t="s">
-        <v>798</v>
+        <v>53</v>
       </c>
       <c r="AR374" s="3" t="s">
-        <v>799</v>
+        <v>767</v>
       </c>
     </row>
     <row r="375" spans="1:44" x14ac:dyDescent="0.3">
@@ -53155,7 +53248,7 @@
         <v>719</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="E375" s="3" t="s">
         <v>46</v>
@@ -53164,7 +53257,7 @@
         <v>46303</v>
       </c>
       <c r="G375" s="5">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H375" s="3" t="s">
         <v>47</v>
@@ -53179,34 +53272,34 @@
         <v>50</v>
       </c>
       <c r="L375" s="6">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="M375" s="7">
-        <v>10803.65</v>
+        <v>9899.4500000000007</v>
       </c>
       <c r="N375" s="6">
         <v>1</v>
       </c>
       <c r="O375" s="3" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="P375" s="8">
-        <v>166.21</v>
+        <v>241.45</v>
       </c>
       <c r="Q375" s="6">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="R375" s="7">
-        <v>10969.86</v>
+        <v>0</v>
       </c>
       <c r="S375" s="9">
-        <v>166.21</v>
+        <v>0</v>
       </c>
       <c r="T375" s="3" t="s">
         <v>52</v>
       </c>
       <c r="U375" s="10">
-        <v>67994</v>
+        <v>67993</v>
       </c>
       <c r="V375" s="11">
         <v>11</v>
@@ -53215,7 +53308,7 @@
         <v>46303</v>
       </c>
       <c r="X375" s="12">
-        <v>0.38194440000000002</v>
+        <v>0.56944439999999996</v>
       </c>
       <c r="Y375" s="10">
         <v>0</v>
@@ -53272,10 +53365,10 @@
         <v>53</v>
       </c>
       <c r="AQ375" s="3" t="s">
-        <v>800</v>
+        <v>53</v>
       </c>
       <c r="AR375" s="3" t="s">
-        <v>801</v>
+        <v>768</v>
       </c>
     </row>
     <row r="376" spans="1:44" x14ac:dyDescent="0.3">
@@ -53289,7 +53382,7 @@
         <v>719</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>738</v>
+        <v>769</v>
       </c>
       <c r="E376" s="3" t="s">
         <v>46</v>
@@ -53298,7 +53391,7 @@
         <v>46303</v>
       </c>
       <c r="G376" s="5">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H376" s="3" t="s">
         <v>47</v>
@@ -53313,25 +53406,25 @@
         <v>50</v>
       </c>
       <c r="L376" s="6">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="M376" s="7">
-        <v>10969.86</v>
+        <v>5817.35</v>
       </c>
       <c r="N376" s="6">
         <v>1</v>
       </c>
       <c r="O376" s="3" t="s">
-        <v>739</v>
+        <v>770</v>
       </c>
       <c r="P376" s="8">
         <v>166.21</v>
       </c>
       <c r="Q376" s="6">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="R376" s="7">
-        <v>11136.07</v>
+        <v>5983.56</v>
       </c>
       <c r="S376" s="9">
         <v>166.21</v>
@@ -53349,7 +53442,7 @@
         <v>46303</v>
       </c>
       <c r="X376" s="12">
-        <v>0.38194440000000002</v>
+        <v>0.30555559999999998</v>
       </c>
       <c r="Y376" s="10">
         <v>0</v>
@@ -53406,10 +53499,10 @@
         <v>53</v>
       </c>
       <c r="AQ376" s="3" t="s">
-        <v>802</v>
+        <v>771</v>
       </c>
       <c r="AR376" s="3" t="s">
-        <v>803</v>
+        <v>772</v>
       </c>
     </row>
     <row r="377" spans="1:44" x14ac:dyDescent="0.3">
@@ -53423,7 +53516,7 @@
         <v>719</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>738</v>
+        <v>769</v>
       </c>
       <c r="E377" s="3" t="s">
         <v>46</v>
@@ -53432,7 +53525,7 @@
         <v>46303</v>
       </c>
       <c r="G377" s="5">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H377" s="3" t="s">
         <v>47</v>
@@ -53447,25 +53540,25 @@
         <v>50</v>
       </c>
       <c r="L377" s="6">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="M377" s="7">
-        <v>11136.07</v>
+        <v>5983.56</v>
       </c>
       <c r="N377" s="6">
         <v>1</v>
       </c>
       <c r="O377" s="3" t="s">
-        <v>739</v>
+        <v>770</v>
       </c>
       <c r="P377" s="8">
         <v>166.21</v>
       </c>
       <c r="Q377" s="6">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="R377" s="7">
-        <v>11302.28</v>
+        <v>6149.77</v>
       </c>
       <c r="S377" s="9">
         <v>166.21</v>
@@ -53483,7 +53576,7 @@
         <v>46303</v>
       </c>
       <c r="X377" s="12">
-        <v>0.40277780000000002</v>
+        <v>0.3125</v>
       </c>
       <c r="Y377" s="10">
         <v>0</v>
@@ -53540,10 +53633,10 @@
         <v>53</v>
       </c>
       <c r="AQ377" s="3" t="s">
-        <v>804</v>
+        <v>773</v>
       </c>
       <c r="AR377" s="3" t="s">
-        <v>805</v>
+        <v>774</v>
       </c>
     </row>
     <row r="378" spans="1:44" x14ac:dyDescent="0.3">
@@ -53557,7 +53650,7 @@
         <v>719</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>738</v>
+        <v>769</v>
       </c>
       <c r="E378" s="3" t="s">
         <v>46</v>
@@ -53566,7 +53659,7 @@
         <v>46303</v>
       </c>
       <c r="G378" s="5">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="H378" s="3" t="s">
         <v>47</v>
@@ -53581,25 +53674,25 @@
         <v>50</v>
       </c>
       <c r="L378" s="6">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="M378" s="7">
-        <v>11302.28</v>
+        <v>6149.77</v>
       </c>
       <c r="N378" s="6">
         <v>1</v>
       </c>
       <c r="O378" s="3" t="s">
-        <v>739</v>
+        <v>770</v>
       </c>
       <c r="P378" s="8">
         <v>166.21</v>
       </c>
       <c r="Q378" s="6">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="R378" s="7">
-        <v>11468.49</v>
+        <v>6315.98</v>
       </c>
       <c r="S378" s="9">
         <v>166.21</v>
@@ -53617,7 +53710,7 @@
         <v>46303</v>
       </c>
       <c r="X378" s="12">
-        <v>0.40277780000000002</v>
+        <v>0.31944440000000002</v>
       </c>
       <c r="Y378" s="10">
         <v>0</v>
@@ -53674,10 +53767,10 @@
         <v>53</v>
       </c>
       <c r="AQ378" s="3" t="s">
-        <v>806</v>
+        <v>775</v>
       </c>
       <c r="AR378" s="3" t="s">
-        <v>807</v>
+        <v>776</v>
       </c>
     </row>
     <row r="379" spans="1:44" x14ac:dyDescent="0.3">
@@ -53691,7 +53784,7 @@
         <v>719</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>738</v>
+        <v>769</v>
       </c>
       <c r="E379" s="3" t="s">
         <v>46</v>
@@ -53700,7 +53793,7 @@
         <v>46303</v>
       </c>
       <c r="G379" s="5">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="H379" s="3" t="s">
         <v>47</v>
@@ -53715,25 +53808,25 @@
         <v>50</v>
       </c>
       <c r="L379" s="6">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="M379" s="7">
-        <v>11468.49</v>
+        <v>6315.98</v>
       </c>
       <c r="N379" s="6">
         <v>1</v>
       </c>
       <c r="O379" s="3" t="s">
-        <v>739</v>
+        <v>770</v>
       </c>
       <c r="P379" s="8">
         <v>166.21</v>
       </c>
       <c r="Q379" s="6">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="R379" s="7">
-        <v>11634.7</v>
+        <v>6482.19</v>
       </c>
       <c r="S379" s="9">
         <v>166.21</v>
@@ -53751,7 +53844,7 @@
         <v>46303</v>
       </c>
       <c r="X379" s="12">
-        <v>0.40277780000000002</v>
+        <v>0.31944440000000002</v>
       </c>
       <c r="Y379" s="10">
         <v>0</v>
@@ -53808,10 +53901,4164 @@
         <v>53</v>
       </c>
       <c r="AQ379" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="AR379" s="3" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="380" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A380" s="1">
+        <v>1</v>
+      </c>
+      <c r="B380" s="2">
+        <v>2</v>
+      </c>
+      <c r="C380" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D380" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E380" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F380" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G380" s="5">
+        <v>5</v>
+      </c>
+      <c r="H380" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I380" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J380" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K380" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L380" s="6">
+        <v>39</v>
+      </c>
+      <c r="M380" s="7">
+        <v>6482.19</v>
+      </c>
+      <c r="N380" s="6">
+        <v>1</v>
+      </c>
+      <c r="O380" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P380" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q380" s="6">
+        <v>40</v>
+      </c>
+      <c r="R380" s="7">
+        <v>6648.4</v>
+      </c>
+      <c r="S380" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T380" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U380" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V380" s="11">
+        <v>11</v>
+      </c>
+      <c r="W380" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X380" s="12">
+        <v>0.31944440000000002</v>
+      </c>
+      <c r="Y380" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB380" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG380" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI380" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ380" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK380" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM380" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ380" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="AR380" s="3" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="381" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A381" s="1">
+        <v>1</v>
+      </c>
+      <c r="B381" s="2">
+        <v>2</v>
+      </c>
+      <c r="C381" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D381" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E381" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F381" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G381" s="5">
+        <v>6</v>
+      </c>
+      <c r="H381" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I381" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J381" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K381" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L381" s="6">
+        <v>40</v>
+      </c>
+      <c r="M381" s="7">
+        <v>6648.4</v>
+      </c>
+      <c r="N381" s="6">
+        <v>1</v>
+      </c>
+      <c r="O381" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P381" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q381" s="6">
+        <v>41</v>
+      </c>
+      <c r="R381" s="7">
+        <v>6814.61</v>
+      </c>
+      <c r="S381" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T381" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U381" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V381" s="11">
+        <v>11</v>
+      </c>
+      <c r="W381" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X381" s="12">
+        <v>0.31944440000000002</v>
+      </c>
+      <c r="Y381" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z381" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA381" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB381" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC381" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD381" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE381" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF381" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG381" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH381" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI381" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ381" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK381" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL381" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM381" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN381" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO381" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP381" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ381" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="AR381" s="3" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="382" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A382" s="1">
+        <v>1</v>
+      </c>
+      <c r="B382" s="2">
+        <v>2</v>
+      </c>
+      <c r="C382" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D382" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E382" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F382" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G382" s="5">
+        <v>7</v>
+      </c>
+      <c r="H382" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I382" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J382" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K382" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L382" s="6">
+        <v>41</v>
+      </c>
+      <c r="M382" s="7">
+        <v>6814.61</v>
+      </c>
+      <c r="N382" s="6">
+        <v>1</v>
+      </c>
+      <c r="O382" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P382" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q382" s="6">
+        <v>42</v>
+      </c>
+      <c r="R382" s="7">
+        <v>6980.82</v>
+      </c>
+      <c r="S382" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T382" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U382" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V382" s="11">
+        <v>11</v>
+      </c>
+      <c r="W382" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X382" s="12">
+        <v>0.32638889999999998</v>
+      </c>
+      <c r="Y382" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z382" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA382" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB382" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC382" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD382" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE382" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF382" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG382" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH382" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI382" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ382" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK382" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL382" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM382" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN382" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO382" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP382" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ382" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="AR382" s="3" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="383" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A383" s="1">
+        <v>1</v>
+      </c>
+      <c r="B383" s="2">
+        <v>2</v>
+      </c>
+      <c r="C383" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D383" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E383" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F383" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G383" s="5">
+        <v>8</v>
+      </c>
+      <c r="H383" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I383" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J383" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K383" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L383" s="6">
+        <v>42</v>
+      </c>
+      <c r="M383" s="7">
+        <v>6980.82</v>
+      </c>
+      <c r="N383" s="6">
+        <v>1</v>
+      </c>
+      <c r="O383" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P383" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q383" s="6">
+        <v>43</v>
+      </c>
+      <c r="R383" s="7">
+        <v>7147.03</v>
+      </c>
+      <c r="S383" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T383" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U383" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V383" s="11">
+        <v>11</v>
+      </c>
+      <c r="W383" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X383" s="12">
+        <v>0.32638889999999998</v>
+      </c>
+      <c r="Y383" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z383" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA383" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB383" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC383" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD383" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE383" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF383" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG383" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH383" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI383" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ383" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK383" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL383" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM383" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN383" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO383" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP383" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ383" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="AR383" s="3" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="384" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A384" s="1">
+        <v>1</v>
+      </c>
+      <c r="B384" s="2">
+        <v>2</v>
+      </c>
+      <c r="C384" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D384" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E384" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F384" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G384" s="5">
+        <v>9</v>
+      </c>
+      <c r="H384" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I384" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J384" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K384" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L384" s="6">
+        <v>43</v>
+      </c>
+      <c r="M384" s="7">
+        <v>7147.03</v>
+      </c>
+      <c r="N384" s="6">
+        <v>1</v>
+      </c>
+      <c r="O384" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P384" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q384" s="6">
+        <v>44</v>
+      </c>
+      <c r="R384" s="7">
+        <v>7313.24</v>
+      </c>
+      <c r="S384" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T384" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U384" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V384" s="11">
+        <v>11</v>
+      </c>
+      <c r="W384" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X384" s="12">
+        <v>0.32638889999999998</v>
+      </c>
+      <c r="Y384" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z384" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA384" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB384" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC384" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD384" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE384" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF384" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG384" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH384" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI384" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ384" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK384" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL384" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM384" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN384" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO384" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP384" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ384" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="AR384" s="3" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="385" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A385" s="1">
+        <v>1</v>
+      </c>
+      <c r="B385" s="2">
+        <v>2</v>
+      </c>
+      <c r="C385" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D385" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E385" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F385" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G385" s="5">
+        <v>10</v>
+      </c>
+      <c r="H385" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I385" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J385" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K385" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L385" s="6">
+        <v>44</v>
+      </c>
+      <c r="M385" s="7">
+        <v>7313.24</v>
+      </c>
+      <c r="N385" s="6">
+        <v>1</v>
+      </c>
+      <c r="O385" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P385" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q385" s="6">
+        <v>45</v>
+      </c>
+      <c r="R385" s="7">
+        <v>7479.45</v>
+      </c>
+      <c r="S385" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T385" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U385" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V385" s="11">
+        <v>11</v>
+      </c>
+      <c r="W385" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X385" s="12">
+        <v>0.36111110000000002</v>
+      </c>
+      <c r="Y385" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z385" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA385" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB385" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC385" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD385" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE385" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF385" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG385" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH385" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI385" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ385" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK385" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL385" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM385" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN385" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO385" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP385" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ385" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="AR385" s="3" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="386" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A386" s="1">
+        <v>1</v>
+      </c>
+      <c r="B386" s="2">
+        <v>2</v>
+      </c>
+      <c r="C386" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D386" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E386" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F386" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G386" s="5">
+        <v>11</v>
+      </c>
+      <c r="H386" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I386" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J386" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K386" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L386" s="6">
+        <v>45</v>
+      </c>
+      <c r="M386" s="7">
+        <v>7479.45</v>
+      </c>
+      <c r="N386" s="6">
+        <v>1</v>
+      </c>
+      <c r="O386" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P386" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q386" s="6">
+        <v>46</v>
+      </c>
+      <c r="R386" s="7">
+        <v>7645.66</v>
+      </c>
+      <c r="S386" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T386" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U386" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V386" s="11">
+        <v>11</v>
+      </c>
+      <c r="W386" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X386" s="12">
+        <v>0.36111110000000002</v>
+      </c>
+      <c r="Y386" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z386" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA386" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB386" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC386" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD386" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE386" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF386" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG386" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH386" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI386" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ386" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK386" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL386" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM386" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN386" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO386" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP386" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ386" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="AR386" s="3" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="387" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A387" s="1">
+        <v>1</v>
+      </c>
+      <c r="B387" s="2">
+        <v>2</v>
+      </c>
+      <c r="C387" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D387" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E387" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F387" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G387" s="5">
+        <v>12</v>
+      </c>
+      <c r="H387" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I387" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J387" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K387" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L387" s="6">
+        <v>46</v>
+      </c>
+      <c r="M387" s="7">
+        <v>7645.66</v>
+      </c>
+      <c r="N387" s="6">
+        <v>1</v>
+      </c>
+      <c r="O387" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P387" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q387" s="6">
+        <v>47</v>
+      </c>
+      <c r="R387" s="7">
+        <v>7811.87</v>
+      </c>
+      <c r="S387" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T387" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U387" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V387" s="11">
+        <v>11</v>
+      </c>
+      <c r="W387" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X387" s="12">
+        <v>0.36111110000000002</v>
+      </c>
+      <c r="Y387" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z387" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA387" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB387" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC387" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD387" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE387" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF387" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG387" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH387" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI387" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ387" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK387" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL387" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM387" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN387" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO387" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP387" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ387" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="AR387" s="3" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="388" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A388" s="1">
+        <v>1</v>
+      </c>
+      <c r="B388" s="2">
+        <v>2</v>
+      </c>
+      <c r="C388" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D388" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E388" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F388" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G388" s="5">
+        <v>13</v>
+      </c>
+      <c r="H388" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I388" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J388" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K388" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L388" s="6">
+        <v>47</v>
+      </c>
+      <c r="M388" s="7">
+        <v>7811.87</v>
+      </c>
+      <c r="N388" s="6">
+        <v>1</v>
+      </c>
+      <c r="O388" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P388" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q388" s="6">
+        <v>48</v>
+      </c>
+      <c r="R388" s="7">
+        <v>7978.08</v>
+      </c>
+      <c r="S388" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T388" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U388" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V388" s="11">
+        <v>11</v>
+      </c>
+      <c r="W388" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X388" s="12">
+        <v>0.36111110000000002</v>
+      </c>
+      <c r="Y388" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z388" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA388" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB388" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC388" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD388" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE388" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF388" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG388" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH388" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI388" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ388" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK388" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL388" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM388" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN388" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO388" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP388" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ388" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="AR388" s="3" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="389" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A389" s="1">
+        <v>1</v>
+      </c>
+      <c r="B389" s="2">
+        <v>2</v>
+      </c>
+      <c r="C389" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D389" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E389" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F389" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G389" s="5">
+        <v>14</v>
+      </c>
+      <c r="H389" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I389" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J389" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K389" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L389" s="6">
+        <v>48</v>
+      </c>
+      <c r="M389" s="7">
+        <v>7978.08</v>
+      </c>
+      <c r="N389" s="6">
+        <v>1</v>
+      </c>
+      <c r="O389" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P389" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q389" s="6">
+        <v>49</v>
+      </c>
+      <c r="R389" s="7">
+        <v>8144.29</v>
+      </c>
+      <c r="S389" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T389" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U389" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V389" s="11">
+        <v>11</v>
+      </c>
+      <c r="W389" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X389" s="12">
+        <v>0.36111110000000002</v>
+      </c>
+      <c r="Y389" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z389" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA389" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB389" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC389" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD389" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE389" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF389" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG389" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH389" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI389" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ389" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK389" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL389" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM389" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN389" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO389" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP389" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ389" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="AR389" s="3" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="390" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A390" s="1">
+        <v>1</v>
+      </c>
+      <c r="B390" s="2">
+        <v>2</v>
+      </c>
+      <c r="C390" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D390" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E390" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F390" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G390" s="5">
+        <v>15</v>
+      </c>
+      <c r="H390" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I390" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J390" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K390" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L390" s="6">
+        <v>49</v>
+      </c>
+      <c r="M390" s="7">
+        <v>8144.29</v>
+      </c>
+      <c r="N390" s="6">
+        <v>1</v>
+      </c>
+      <c r="O390" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P390" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q390" s="6">
+        <v>50</v>
+      </c>
+      <c r="R390" s="7">
+        <v>8310.5</v>
+      </c>
+      <c r="S390" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T390" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U390" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V390" s="11">
+        <v>11</v>
+      </c>
+      <c r="W390" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X390" s="12">
+        <v>0.36111110000000002</v>
+      </c>
+      <c r="Y390" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z390" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA390" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB390" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC390" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD390" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE390" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF390" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG390" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH390" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI390" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ390" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK390" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL390" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM390" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN390" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO390" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP390" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ390" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="AR390" s="3" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="391" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A391" s="1">
+        <v>1</v>
+      </c>
+      <c r="B391" s="2">
+        <v>2</v>
+      </c>
+      <c r="C391" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D391" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E391" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F391" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G391" s="5">
+        <v>16</v>
+      </c>
+      <c r="H391" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I391" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J391" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K391" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L391" s="6">
+        <v>50</v>
+      </c>
+      <c r="M391" s="7">
+        <v>8310.5</v>
+      </c>
+      <c r="N391" s="6">
+        <v>1</v>
+      </c>
+      <c r="O391" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P391" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q391" s="6">
+        <v>51</v>
+      </c>
+      <c r="R391" s="7">
+        <v>8476.7099999999991</v>
+      </c>
+      <c r="S391" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T391" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U391" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V391" s="11">
+        <v>11</v>
+      </c>
+      <c r="W391" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X391" s="12">
+        <v>0.36111110000000002</v>
+      </c>
+      <c r="Y391" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z391" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA391" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB391" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC391" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD391" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE391" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF391" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG391" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH391" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI391" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ391" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK391" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL391" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM391" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN391" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO391" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP391" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ391" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="AR391" s="3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="392" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A392" s="1">
+        <v>1</v>
+      </c>
+      <c r="B392" s="2">
+        <v>2</v>
+      </c>
+      <c r="C392" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D392" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E392" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F392" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G392" s="5">
+        <v>17</v>
+      </c>
+      <c r="H392" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I392" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J392" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K392" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L392" s="6">
+        <v>51</v>
+      </c>
+      <c r="M392" s="7">
+        <v>8476.7099999999991</v>
+      </c>
+      <c r="N392" s="6">
+        <v>1</v>
+      </c>
+      <c r="O392" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P392" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q392" s="6">
+        <v>52</v>
+      </c>
+      <c r="R392" s="7">
+        <v>8642.92</v>
+      </c>
+      <c r="S392" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T392" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U392" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V392" s="11">
+        <v>11</v>
+      </c>
+      <c r="W392" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X392" s="12">
+        <v>0.36111110000000002</v>
+      </c>
+      <c r="Y392" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z392" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA392" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB392" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC392" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD392" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE392" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF392" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG392" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH392" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI392" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ392" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK392" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL392" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM392" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN392" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO392" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP392" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ392" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="AR392" s="3" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="393" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A393" s="1">
+        <v>1</v>
+      </c>
+      <c r="B393" s="2">
+        <v>2</v>
+      </c>
+      <c r="C393" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D393" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E393" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F393" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G393" s="5">
+        <v>18</v>
+      </c>
+      <c r="H393" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I393" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J393" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K393" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L393" s="6">
+        <v>52</v>
+      </c>
+      <c r="M393" s="7">
+        <v>8642.92</v>
+      </c>
+      <c r="N393" s="6">
+        <v>1</v>
+      </c>
+      <c r="O393" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P393" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q393" s="6">
+        <v>53</v>
+      </c>
+      <c r="R393" s="7">
+        <v>8809.1299999999992</v>
+      </c>
+      <c r="S393" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T393" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U393" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V393" s="11">
+        <v>11</v>
+      </c>
+      <c r="W393" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X393" s="12">
+        <v>0.36111110000000002</v>
+      </c>
+      <c r="Y393" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z393" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA393" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB393" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC393" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD393" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE393" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF393" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG393" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH393" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI393" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ393" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK393" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL393" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM393" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN393" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO393" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP393" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ393" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="AR393" s="3" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="394" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A394" s="1">
+        <v>1</v>
+      </c>
+      <c r="B394" s="2">
+        <v>2</v>
+      </c>
+      <c r="C394" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D394" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E394" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F394" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G394" s="5">
+        <v>19</v>
+      </c>
+      <c r="H394" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I394" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J394" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K394" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L394" s="6">
+        <v>53</v>
+      </c>
+      <c r="M394" s="7">
+        <v>8809.1299999999992</v>
+      </c>
+      <c r="N394" s="6">
+        <v>1</v>
+      </c>
+      <c r="O394" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P394" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q394" s="6">
+        <v>54</v>
+      </c>
+      <c r="R394" s="7">
+        <v>8975.34</v>
+      </c>
+      <c r="S394" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T394" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U394" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V394" s="11">
+        <v>11</v>
+      </c>
+      <c r="W394" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X394" s="12">
+        <v>0.36111110000000002</v>
+      </c>
+      <c r="Y394" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z394" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA394" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB394" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC394" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD394" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE394" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF394" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG394" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH394" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI394" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ394" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK394" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL394" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM394" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN394" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO394" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP394" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ394" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="AR394" s="3" t="s">
         <v>808</v>
       </c>
-      <c r="AR379" s="3" t="s">
+    </row>
+    <row r="395" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A395" s="1">
+        <v>1</v>
+      </c>
+      <c r="B395" s="2">
+        <v>2</v>
+      </c>
+      <c r="C395" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D395" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E395" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F395" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G395" s="5">
+        <v>20</v>
+      </c>
+      <c r="H395" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I395" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J395" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K395" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L395" s="6">
+        <v>54</v>
+      </c>
+      <c r="M395" s="7">
+        <v>8975.34</v>
+      </c>
+      <c r="N395" s="6">
+        <v>1</v>
+      </c>
+      <c r="O395" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P395" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q395" s="6">
+        <v>55</v>
+      </c>
+      <c r="R395" s="7">
+        <v>9141.5499999999993</v>
+      </c>
+      <c r="S395" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T395" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U395" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V395" s="11">
+        <v>11</v>
+      </c>
+      <c r="W395" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X395" s="12">
+        <v>0.38194440000000002</v>
+      </c>
+      <c r="Y395" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z395" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA395" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB395" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC395" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD395" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE395" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF395" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG395" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH395" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI395" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ395" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK395" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL395" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM395" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN395" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO395" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP395" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ395" s="3" t="s">
         <v>809</v>
+      </c>
+      <c r="AR395" s="3" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="396" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A396" s="1">
+        <v>1</v>
+      </c>
+      <c r="B396" s="2">
+        <v>2</v>
+      </c>
+      <c r="C396" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D396" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E396" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F396" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G396" s="5">
+        <v>21</v>
+      </c>
+      <c r="H396" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I396" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J396" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K396" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L396" s="6">
+        <v>55</v>
+      </c>
+      <c r="M396" s="7">
+        <v>9141.5499999999993</v>
+      </c>
+      <c r="N396" s="6">
+        <v>1</v>
+      </c>
+      <c r="O396" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P396" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q396" s="6">
+        <v>56</v>
+      </c>
+      <c r="R396" s="7">
+        <v>9307.76</v>
+      </c>
+      <c r="S396" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T396" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U396" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V396" s="11">
+        <v>11</v>
+      </c>
+      <c r="W396" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X396" s="12">
+        <v>0.38194440000000002</v>
+      </c>
+      <c r="Y396" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z396" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA396" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB396" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC396" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD396" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE396" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF396" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG396" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH396" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI396" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ396" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK396" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL396" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM396" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN396" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO396" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP396" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ396" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="AR396" s="3" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="397" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A397" s="1">
+        <v>1</v>
+      </c>
+      <c r="B397" s="2">
+        <v>2</v>
+      </c>
+      <c r="C397" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D397" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E397" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F397" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G397" s="5">
+        <v>22</v>
+      </c>
+      <c r="H397" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I397" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J397" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K397" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L397" s="6">
+        <v>56</v>
+      </c>
+      <c r="M397" s="7">
+        <v>9307.76</v>
+      </c>
+      <c r="N397" s="6">
+        <v>1</v>
+      </c>
+      <c r="O397" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P397" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q397" s="6">
+        <v>57</v>
+      </c>
+      <c r="R397" s="7">
+        <v>9473.9699999999993</v>
+      </c>
+      <c r="S397" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T397" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U397" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V397" s="11">
+        <v>11</v>
+      </c>
+      <c r="W397" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X397" s="12">
+        <v>0.38194440000000002</v>
+      </c>
+      <c r="Y397" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z397" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA397" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB397" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC397" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD397" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE397" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF397" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG397" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH397" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI397" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ397" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK397" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL397" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM397" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN397" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO397" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP397" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ397" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="AR397" s="3" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="398" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A398" s="1">
+        <v>1</v>
+      </c>
+      <c r="B398" s="2">
+        <v>2</v>
+      </c>
+      <c r="C398" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D398" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E398" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F398" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G398" s="5">
+        <v>23</v>
+      </c>
+      <c r="H398" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I398" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J398" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K398" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L398" s="6">
+        <v>57</v>
+      </c>
+      <c r="M398" s="7">
+        <v>9473.9699999999993</v>
+      </c>
+      <c r="N398" s="6">
+        <v>1</v>
+      </c>
+      <c r="O398" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P398" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q398" s="6">
+        <v>58</v>
+      </c>
+      <c r="R398" s="7">
+        <v>9640.18</v>
+      </c>
+      <c r="S398" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T398" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U398" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V398" s="11">
+        <v>11</v>
+      </c>
+      <c r="W398" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X398" s="12">
+        <v>0.38194440000000002</v>
+      </c>
+      <c r="Y398" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z398" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA398" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB398" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC398" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD398" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE398" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF398" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG398" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH398" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI398" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ398" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK398" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL398" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM398" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN398" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO398" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP398" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ398" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="AR398" s="3" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="399" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A399" s="1">
+        <v>1</v>
+      </c>
+      <c r="B399" s="2">
+        <v>2</v>
+      </c>
+      <c r="C399" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D399" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E399" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F399" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G399" s="5">
+        <v>24</v>
+      </c>
+      <c r="H399" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I399" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J399" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K399" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L399" s="6">
+        <v>58</v>
+      </c>
+      <c r="M399" s="7">
+        <v>9640.18</v>
+      </c>
+      <c r="N399" s="6">
+        <v>1</v>
+      </c>
+      <c r="O399" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P399" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q399" s="6">
+        <v>59</v>
+      </c>
+      <c r="R399" s="7">
+        <v>9806.39</v>
+      </c>
+      <c r="S399" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T399" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U399" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V399" s="11">
+        <v>11</v>
+      </c>
+      <c r="W399" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X399" s="12">
+        <v>0.38194440000000002</v>
+      </c>
+      <c r="Y399" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z399" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA399" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB399" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC399" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD399" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE399" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF399" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG399" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH399" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI399" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ399" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK399" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL399" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM399" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN399" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO399" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP399" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ399" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="AR399" s="3" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="400" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A400" s="1">
+        <v>1</v>
+      </c>
+      <c r="B400" s="2">
+        <v>2</v>
+      </c>
+      <c r="C400" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D400" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E400" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F400" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G400" s="5">
+        <v>25</v>
+      </c>
+      <c r="H400" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I400" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J400" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K400" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L400" s="6">
+        <v>59</v>
+      </c>
+      <c r="M400" s="7">
+        <v>9806.39</v>
+      </c>
+      <c r="N400" s="6">
+        <v>1</v>
+      </c>
+      <c r="O400" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P400" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q400" s="6">
+        <v>60</v>
+      </c>
+      <c r="R400" s="7">
+        <v>9972.6</v>
+      </c>
+      <c r="S400" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T400" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U400" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V400" s="11">
+        <v>11</v>
+      </c>
+      <c r="W400" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X400" s="12">
+        <v>0.38194440000000002</v>
+      </c>
+      <c r="Y400" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z400" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA400" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB400" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC400" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD400" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE400" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF400" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG400" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH400" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI400" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ400" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK400" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL400" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM400" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN400" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO400" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP400" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ400" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="AR400" s="3" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="401" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A401" s="1">
+        <v>1</v>
+      </c>
+      <c r="B401" s="2">
+        <v>2</v>
+      </c>
+      <c r="C401" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D401" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E401" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F401" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G401" s="5">
+        <v>26</v>
+      </c>
+      <c r="H401" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I401" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J401" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K401" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L401" s="6">
+        <v>60</v>
+      </c>
+      <c r="M401" s="7">
+        <v>9972.6</v>
+      </c>
+      <c r="N401" s="6">
+        <v>1</v>
+      </c>
+      <c r="O401" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P401" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q401" s="6">
+        <v>61</v>
+      </c>
+      <c r="R401" s="7">
+        <v>10138.81</v>
+      </c>
+      <c r="S401" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T401" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U401" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V401" s="11">
+        <v>11</v>
+      </c>
+      <c r="W401" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X401" s="12">
+        <v>0.38194440000000002</v>
+      </c>
+      <c r="Y401" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z401" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA401" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB401" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC401" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD401" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE401" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF401" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG401" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH401" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI401" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ401" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK401" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL401" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM401" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN401" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO401" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP401" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ401" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="AR401" s="3" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="402" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A402" s="1">
+        <v>1</v>
+      </c>
+      <c r="B402" s="2">
+        <v>2</v>
+      </c>
+      <c r="C402" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D402" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E402" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F402" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G402" s="5">
+        <v>27</v>
+      </c>
+      <c r="H402" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I402" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J402" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K402" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L402" s="6">
+        <v>61</v>
+      </c>
+      <c r="M402" s="7">
+        <v>10138.81</v>
+      </c>
+      <c r="N402" s="6">
+        <v>1</v>
+      </c>
+      <c r="O402" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P402" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q402" s="6">
+        <v>62</v>
+      </c>
+      <c r="R402" s="7">
+        <v>10305.02</v>
+      </c>
+      <c r="S402" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T402" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U402" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V402" s="11">
+        <v>11</v>
+      </c>
+      <c r="W402" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X402" s="12">
+        <v>0.38194440000000002</v>
+      </c>
+      <c r="Y402" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z402" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA402" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB402" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC402" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD402" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE402" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF402" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG402" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH402" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI402" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ402" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK402" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL402" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM402" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN402" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO402" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP402" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ402" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="AR402" s="3" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="403" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A403" s="1">
+        <v>1</v>
+      </c>
+      <c r="B403" s="2">
+        <v>2</v>
+      </c>
+      <c r="C403" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D403" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E403" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F403" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G403" s="5">
+        <v>28</v>
+      </c>
+      <c r="H403" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I403" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J403" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K403" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L403" s="6">
+        <v>62</v>
+      </c>
+      <c r="M403" s="7">
+        <v>10305.02</v>
+      </c>
+      <c r="N403" s="6">
+        <v>1</v>
+      </c>
+      <c r="O403" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P403" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q403" s="6">
+        <v>63</v>
+      </c>
+      <c r="R403" s="7">
+        <v>10471.23</v>
+      </c>
+      <c r="S403" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T403" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U403" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V403" s="11">
+        <v>11</v>
+      </c>
+      <c r="W403" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X403" s="12">
+        <v>0.38194440000000002</v>
+      </c>
+      <c r="Y403" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z403" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA403" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB403" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC403" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD403" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE403" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF403" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG403" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH403" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI403" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ403" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK403" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL403" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM403" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN403" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO403" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP403" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ403" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="AR403" s="3" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="404" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A404" s="1">
+        <v>1</v>
+      </c>
+      <c r="B404" s="2">
+        <v>2</v>
+      </c>
+      <c r="C404" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D404" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E404" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F404" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G404" s="5">
+        <v>29</v>
+      </c>
+      <c r="H404" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I404" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J404" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K404" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L404" s="6">
+        <v>63</v>
+      </c>
+      <c r="M404" s="7">
+        <v>10471.23</v>
+      </c>
+      <c r="N404" s="6">
+        <v>1</v>
+      </c>
+      <c r="O404" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P404" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q404" s="6">
+        <v>64</v>
+      </c>
+      <c r="R404" s="7">
+        <v>10637.44</v>
+      </c>
+      <c r="S404" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T404" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U404" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V404" s="11">
+        <v>11</v>
+      </c>
+      <c r="W404" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X404" s="12">
+        <v>0.38194440000000002</v>
+      </c>
+      <c r="Y404" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z404" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA404" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB404" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC404" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD404" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE404" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF404" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG404" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH404" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI404" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ404" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK404" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL404" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM404" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN404" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO404" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP404" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ404" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="AR404" s="3" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="405" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A405" s="1">
+        <v>1</v>
+      </c>
+      <c r="B405" s="2">
+        <v>2</v>
+      </c>
+      <c r="C405" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D405" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E405" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F405" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G405" s="5">
+        <v>30</v>
+      </c>
+      <c r="H405" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I405" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J405" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K405" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L405" s="6">
+        <v>64</v>
+      </c>
+      <c r="M405" s="7">
+        <v>10637.44</v>
+      </c>
+      <c r="N405" s="6">
+        <v>1</v>
+      </c>
+      <c r="O405" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P405" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q405" s="6">
+        <v>65</v>
+      </c>
+      <c r="R405" s="7">
+        <v>10803.65</v>
+      </c>
+      <c r="S405" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T405" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U405" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V405" s="11">
+        <v>11</v>
+      </c>
+      <c r="W405" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X405" s="12">
+        <v>0.38194440000000002</v>
+      </c>
+      <c r="Y405" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z405" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA405" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB405" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC405" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD405" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE405" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF405" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG405" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH405" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI405" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ405" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK405" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL405" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM405" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN405" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO405" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP405" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ405" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="AR405" s="3" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="406" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A406" s="1">
+        <v>1</v>
+      </c>
+      <c r="B406" s="2">
+        <v>2</v>
+      </c>
+      <c r="C406" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D406" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E406" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F406" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G406" s="5">
+        <v>31</v>
+      </c>
+      <c r="H406" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I406" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J406" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K406" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L406" s="6">
+        <v>65</v>
+      </c>
+      <c r="M406" s="7">
+        <v>10803.65</v>
+      </c>
+      <c r="N406" s="6">
+        <v>1</v>
+      </c>
+      <c r="O406" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P406" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q406" s="6">
+        <v>66</v>
+      </c>
+      <c r="R406" s="7">
+        <v>10969.86</v>
+      </c>
+      <c r="S406" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T406" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U406" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V406" s="11">
+        <v>11</v>
+      </c>
+      <c r="W406" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X406" s="12">
+        <v>0.38194440000000002</v>
+      </c>
+      <c r="Y406" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z406" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA406" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB406" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC406" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD406" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE406" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF406" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG406" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH406" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI406" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ406" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK406" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL406" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM406" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN406" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO406" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP406" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ406" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="AR406" s="3" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="407" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A407" s="1">
+        <v>1</v>
+      </c>
+      <c r="B407" s="2">
+        <v>2</v>
+      </c>
+      <c r="C407" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D407" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E407" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F407" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G407" s="5">
+        <v>32</v>
+      </c>
+      <c r="H407" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I407" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J407" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K407" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L407" s="6">
+        <v>66</v>
+      </c>
+      <c r="M407" s="7">
+        <v>10969.86</v>
+      </c>
+      <c r="N407" s="6">
+        <v>1</v>
+      </c>
+      <c r="O407" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P407" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q407" s="6">
+        <v>67</v>
+      </c>
+      <c r="R407" s="7">
+        <v>11136.07</v>
+      </c>
+      <c r="S407" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T407" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U407" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V407" s="11">
+        <v>11</v>
+      </c>
+      <c r="W407" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X407" s="12">
+        <v>0.38194440000000002</v>
+      </c>
+      <c r="Y407" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z407" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA407" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB407" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC407" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD407" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE407" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF407" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG407" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH407" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI407" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ407" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK407" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL407" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM407" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN407" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO407" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP407" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ407" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="AR407" s="3" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="408" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A408" s="1">
+        <v>1</v>
+      </c>
+      <c r="B408" s="2">
+        <v>2</v>
+      </c>
+      <c r="C408" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D408" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E408" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F408" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G408" s="5">
+        <v>33</v>
+      </c>
+      <c r="H408" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I408" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J408" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K408" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L408" s="6">
+        <v>67</v>
+      </c>
+      <c r="M408" s="7">
+        <v>11136.07</v>
+      </c>
+      <c r="N408" s="6">
+        <v>1</v>
+      </c>
+      <c r="O408" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P408" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q408" s="6">
+        <v>68</v>
+      </c>
+      <c r="R408" s="7">
+        <v>11302.28</v>
+      </c>
+      <c r="S408" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T408" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U408" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V408" s="11">
+        <v>11</v>
+      </c>
+      <c r="W408" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X408" s="12">
+        <v>0.40277780000000002</v>
+      </c>
+      <c r="Y408" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z408" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA408" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB408" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC408" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD408" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE408" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF408" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG408" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH408" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI408" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ408" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK408" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL408" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM408" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN408" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO408" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP408" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ408" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="AR408" s="3" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="409" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A409" s="1">
+        <v>1</v>
+      </c>
+      <c r="B409" s="2">
+        <v>2</v>
+      </c>
+      <c r="C409" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D409" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E409" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F409" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G409" s="5">
+        <v>34</v>
+      </c>
+      <c r="H409" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I409" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J409" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K409" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L409" s="6">
+        <v>68</v>
+      </c>
+      <c r="M409" s="7">
+        <v>11302.28</v>
+      </c>
+      <c r="N409" s="6">
+        <v>1</v>
+      </c>
+      <c r="O409" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P409" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q409" s="6">
+        <v>69</v>
+      </c>
+      <c r="R409" s="7">
+        <v>11468.49</v>
+      </c>
+      <c r="S409" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T409" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U409" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V409" s="11">
+        <v>11</v>
+      </c>
+      <c r="W409" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X409" s="12">
+        <v>0.40277780000000002</v>
+      </c>
+      <c r="Y409" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z409" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA409" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB409" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC409" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD409" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE409" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF409" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG409" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH409" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI409" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ409" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK409" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL409" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM409" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN409" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO409" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP409" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ409" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="AR409" s="3" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="410" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A410" s="1">
+        <v>1</v>
+      </c>
+      <c r="B410" s="2">
+        <v>2</v>
+      </c>
+      <c r="C410" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D410" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E410" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F410" s="4">
+        <v>46303</v>
+      </c>
+      <c r="G410" s="5">
+        <v>35</v>
+      </c>
+      <c r="H410" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I410" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J410" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K410" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L410" s="6">
+        <v>69</v>
+      </c>
+      <c r="M410" s="7">
+        <v>11468.49</v>
+      </c>
+      <c r="N410" s="6">
+        <v>1</v>
+      </c>
+      <c r="O410" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="P410" s="8">
+        <v>166.21</v>
+      </c>
+      <c r="Q410" s="6">
+        <v>70</v>
+      </c>
+      <c r="R410" s="7">
+        <v>11634.7</v>
+      </c>
+      <c r="S410" s="9">
+        <v>166.21</v>
+      </c>
+      <c r="T410" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U410" s="10">
+        <v>67994</v>
+      </c>
+      <c r="V410" s="11">
+        <v>11</v>
+      </c>
+      <c r="W410" s="4">
+        <v>46303</v>
+      </c>
+      <c r="X410" s="12">
+        <v>0.40277780000000002</v>
+      </c>
+      <c r="Y410" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z410" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA410" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB410" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC410" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD410" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE410" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF410" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG410" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH410" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI410" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ410" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK410" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL410" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM410" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN410" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO410" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP410" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ410" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="AR410" s="3" t="s">
+        <v>840</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01544216-88A7-4099-A7FD-0E787C4AB636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9119AE7-58B9-4BD1-A1D9-71962A60CC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="42210" yWindow="7275" windowWidth="7080" windowHeight="3630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="154">
   <si>
     <t>Sel</t>
   </si>
@@ -341,6 +341,147 @@
   </si>
   <si>
     <t>1858700156656</t>
+  </si>
+  <si>
+    <t>1858700156657</t>
+  </si>
+  <si>
+    <t>1858700156658</t>
+  </si>
+  <si>
+    <t>1858700156659</t>
+  </si>
+  <si>
+    <t>1858700156660</t>
+  </si>
+  <si>
+    <t>1858700156661</t>
+  </si>
+  <si>
+    <t>1858700156662</t>
+  </si>
+  <si>
+    <t>1858700156663</t>
+  </si>
+  <si>
+    <t>1858700156664</t>
+  </si>
+  <si>
+    <t>1858700156665</t>
+  </si>
+  <si>
+    <t>1858700156666</t>
+  </si>
+  <si>
+    <t>1858700156667</t>
+  </si>
+  <si>
+    <t>1858700156668</t>
+  </si>
+  <si>
+    <t>1858700156669</t>
+  </si>
+  <si>
+    <t>1858700156670</t>
+  </si>
+  <si>
+    <t>1858700156671</t>
+  </si>
+  <si>
+    <t>1858700156672</t>
+  </si>
+  <si>
+    <t>1858700156673</t>
+  </si>
+  <si>
+    <t>1858700156674</t>
+  </si>
+  <si>
+    <t>1858700156675</t>
+  </si>
+  <si>
+    <t>1858700156676</t>
+  </si>
+  <si>
+    <t>1858700156677</t>
+  </si>
+  <si>
+    <t>1858700156678</t>
+  </si>
+  <si>
+    <t>1858700156679</t>
+  </si>
+  <si>
+    <t>1858700156680</t>
+  </si>
+  <si>
+    <t>1858700156681</t>
+  </si>
+  <si>
+    <t>1858700156682</t>
+  </si>
+  <si>
+    <t>1858700156683</t>
+  </si>
+  <si>
+    <t>1858700156684</t>
+  </si>
+  <si>
+    <t>1858700156685</t>
+  </si>
+  <si>
+    <t>1858700156686</t>
+  </si>
+  <si>
+    <t>1858700156687</t>
+  </si>
+  <si>
+    <t>1858700156688</t>
+  </si>
+  <si>
+    <t>1858700156689</t>
+  </si>
+  <si>
+    <t>1858700156690</t>
+  </si>
+  <si>
+    <t>1858700156691</t>
+  </si>
+  <si>
+    <t>1858700156692</t>
+  </si>
+  <si>
+    <t>1858700156693</t>
+  </si>
+  <si>
+    <t>1858700156694</t>
+  </si>
+  <si>
+    <t>1858700156695</t>
+  </si>
+  <si>
+    <t>1858700156696</t>
+  </si>
+  <si>
+    <t>1858700156697</t>
+  </si>
+  <si>
+    <t>1858700156698</t>
+  </si>
+  <si>
+    <t>1858700156699</t>
+  </si>
+  <si>
+    <t>1858700156700</t>
+  </si>
+  <si>
+    <t>1858700156701</t>
+  </si>
+  <si>
+    <t>1858700156702</t>
+  </si>
+  <si>
+    <t>1858700156703</t>
   </si>
 </sst>
 </file>
@@ -916,7 +1057,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR53"/>
+  <dimension ref="A1:AR100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -8019,6 +8160,6304 @@
       </c>
       <c r="AR53" s="3" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="54" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>1</v>
+      </c>
+      <c r="B54" s="2">
+        <v>2</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F54" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G54" s="5">
+        <v>53</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L54" s="6">
+        <v>4365</v>
+      </c>
+      <c r="M54" s="7">
+        <v>695091.93</v>
+      </c>
+      <c r="N54" s="6">
+        <v>1</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P54" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q54" s="6">
+        <v>0</v>
+      </c>
+      <c r="R54" s="7">
+        <v>0</v>
+      </c>
+      <c r="S54" s="9">
+        <v>0</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U54" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V54" s="11">
+        <v>11</v>
+      </c>
+      <c r="W54" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X54" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y54" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI54" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ54" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK54" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM54" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR54" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>1</v>
+      </c>
+      <c r="B55" s="2">
+        <v>2</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F55" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G55" s="5">
+        <v>54</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L55" s="6">
+        <v>4366</v>
+      </c>
+      <c r="M55" s="7">
+        <v>695251.17</v>
+      </c>
+      <c r="N55" s="6">
+        <v>1</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P55" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>0</v>
+      </c>
+      <c r="R55" s="7">
+        <v>0</v>
+      </c>
+      <c r="S55" s="9">
+        <v>0</v>
+      </c>
+      <c r="T55" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U55" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V55" s="11">
+        <v>11</v>
+      </c>
+      <c r="W55" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X55" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y55" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI55" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ55" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK55" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM55" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR55" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>1</v>
+      </c>
+      <c r="B56" s="2">
+        <v>2</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F56" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G56" s="5">
+        <v>55</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L56" s="6">
+        <v>4367</v>
+      </c>
+      <c r="M56" s="7">
+        <v>695410.41</v>
+      </c>
+      <c r="N56" s="6">
+        <v>1</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P56" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q56" s="6">
+        <v>0</v>
+      </c>
+      <c r="R56" s="7">
+        <v>0</v>
+      </c>
+      <c r="S56" s="9">
+        <v>0</v>
+      </c>
+      <c r="T56" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U56" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V56" s="11">
+        <v>11</v>
+      </c>
+      <c r="W56" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X56" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y56" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI56" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ56" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK56" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM56" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR56" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="57" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>1</v>
+      </c>
+      <c r="B57" s="2">
+        <v>2</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F57" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G57" s="5">
+        <v>56</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L57" s="6">
+        <v>4368</v>
+      </c>
+      <c r="M57" s="7">
+        <v>695569.65</v>
+      </c>
+      <c r="N57" s="6">
+        <v>1</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P57" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q57" s="6">
+        <v>0</v>
+      </c>
+      <c r="R57" s="7">
+        <v>0</v>
+      </c>
+      <c r="S57" s="9">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U57" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V57" s="11">
+        <v>11</v>
+      </c>
+      <c r="W57" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X57" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y57" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG57" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI57" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ57" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK57" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM57" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR57" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>1</v>
+      </c>
+      <c r="B58" s="2">
+        <v>2</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F58" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G58" s="5">
+        <v>57</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L58" s="6">
+        <v>4369</v>
+      </c>
+      <c r="M58" s="7">
+        <v>695728.89</v>
+      </c>
+      <c r="N58" s="6">
+        <v>1</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P58" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0</v>
+      </c>
+      <c r="R58" s="7">
+        <v>0</v>
+      </c>
+      <c r="S58" s="9">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U58" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V58" s="11">
+        <v>11</v>
+      </c>
+      <c r="W58" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X58" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y58" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI58" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ58" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK58" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR58" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>1</v>
+      </c>
+      <c r="B59" s="2">
+        <v>2</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F59" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G59" s="5">
+        <v>58</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L59" s="6">
+        <v>4370</v>
+      </c>
+      <c r="M59" s="7">
+        <v>695888.14</v>
+      </c>
+      <c r="N59" s="6">
+        <v>1</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P59" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q59" s="6">
+        <v>0</v>
+      </c>
+      <c r="R59" s="7">
+        <v>0</v>
+      </c>
+      <c r="S59" s="9">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U59" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V59" s="11">
+        <v>11</v>
+      </c>
+      <c r="W59" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X59" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y59" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG59" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI59" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ59" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK59" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM59" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR59" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>1</v>
+      </c>
+      <c r="B60" s="2">
+        <v>2</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F60" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G60" s="5">
+        <v>59</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L60" s="6">
+        <v>4371</v>
+      </c>
+      <c r="M60" s="7">
+        <v>696047.38</v>
+      </c>
+      <c r="N60" s="6">
+        <v>1</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P60" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q60" s="6">
+        <v>0</v>
+      </c>
+      <c r="R60" s="7">
+        <v>0</v>
+      </c>
+      <c r="S60" s="9">
+        <v>0</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U60" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V60" s="11">
+        <v>11</v>
+      </c>
+      <c r="W60" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X60" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y60" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI60" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ60" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK60" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM60" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR60" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>1</v>
+      </c>
+      <c r="B61" s="2">
+        <v>2</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F61" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G61" s="5">
+        <v>60</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L61" s="6">
+        <v>4372</v>
+      </c>
+      <c r="M61" s="7">
+        <v>696206.62</v>
+      </c>
+      <c r="N61" s="6">
+        <v>1</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P61" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q61" s="6">
+        <v>0</v>
+      </c>
+      <c r="R61" s="7">
+        <v>0</v>
+      </c>
+      <c r="S61" s="9">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U61" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V61" s="11">
+        <v>11</v>
+      </c>
+      <c r="W61" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X61" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y61" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG61" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI61" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ61" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK61" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR61" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="62" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>1</v>
+      </c>
+      <c r="B62" s="2">
+        <v>2</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F62" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G62" s="5">
+        <v>61</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L62" s="6">
+        <v>4373</v>
+      </c>
+      <c r="M62" s="7">
+        <v>696365.86</v>
+      </c>
+      <c r="N62" s="6">
+        <v>1</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P62" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>0</v>
+      </c>
+      <c r="R62" s="7">
+        <v>0</v>
+      </c>
+      <c r="S62" s="9">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U62" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V62" s="11">
+        <v>11</v>
+      </c>
+      <c r="W62" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X62" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y62" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI62" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ62" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK62" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM62" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR62" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="63" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>1</v>
+      </c>
+      <c r="B63" s="2">
+        <v>2</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F63" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G63" s="5">
+        <v>62</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L63" s="6">
+        <v>4374</v>
+      </c>
+      <c r="M63" s="7">
+        <v>696525.1</v>
+      </c>
+      <c r="N63" s="6">
+        <v>1</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P63" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>0</v>
+      </c>
+      <c r="R63" s="7">
+        <v>0</v>
+      </c>
+      <c r="S63" s="9">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U63" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V63" s="11">
+        <v>11</v>
+      </c>
+      <c r="W63" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X63" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y63" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI63" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ63" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK63" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR63" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="64" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>1</v>
+      </c>
+      <c r="B64" s="2">
+        <v>2</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F64" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G64" s="5">
+        <v>63</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L64" s="6">
+        <v>4375</v>
+      </c>
+      <c r="M64" s="7">
+        <v>696684.35</v>
+      </c>
+      <c r="N64" s="6">
+        <v>1</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P64" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q64" s="6">
+        <v>0</v>
+      </c>
+      <c r="R64" s="7">
+        <v>0</v>
+      </c>
+      <c r="S64" s="9">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U64" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V64" s="11">
+        <v>11</v>
+      </c>
+      <c r="W64" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X64" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y64" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI64" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ64" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK64" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR64" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="65" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>1</v>
+      </c>
+      <c r="B65" s="2">
+        <v>2</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F65" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G65" s="5">
+        <v>64</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L65" s="6">
+        <v>4376</v>
+      </c>
+      <c r="M65" s="7">
+        <v>696843.59</v>
+      </c>
+      <c r="N65" s="6">
+        <v>1</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P65" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q65" s="6">
+        <v>0</v>
+      </c>
+      <c r="R65" s="7">
+        <v>0</v>
+      </c>
+      <c r="S65" s="9">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U65" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V65" s="11">
+        <v>11</v>
+      </c>
+      <c r="W65" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X65" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y65" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG65" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI65" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ65" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK65" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR65" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="66" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>1</v>
+      </c>
+      <c r="B66" s="2">
+        <v>2</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F66" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G66" s="5">
+        <v>65</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L66" s="6">
+        <v>4377</v>
+      </c>
+      <c r="M66" s="7">
+        <v>697002.83</v>
+      </c>
+      <c r="N66" s="6">
+        <v>1</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P66" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q66" s="6">
+        <v>0</v>
+      </c>
+      <c r="R66" s="7">
+        <v>0</v>
+      </c>
+      <c r="S66" s="9">
+        <v>0</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U66" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V66" s="11">
+        <v>11</v>
+      </c>
+      <c r="W66" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X66" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y66" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB66" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI66" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ66" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK66" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM66" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR66" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="67" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>1</v>
+      </c>
+      <c r="B67" s="2">
+        <v>2</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F67" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G67" s="5">
+        <v>66</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L67" s="6">
+        <v>4378</v>
+      </c>
+      <c r="M67" s="7">
+        <v>697162.07</v>
+      </c>
+      <c r="N67" s="6">
+        <v>1</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P67" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q67" s="6">
+        <v>0</v>
+      </c>
+      <c r="R67" s="7">
+        <v>0</v>
+      </c>
+      <c r="S67" s="9">
+        <v>0</v>
+      </c>
+      <c r="T67" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U67" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V67" s="11">
+        <v>11</v>
+      </c>
+      <c r="W67" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X67" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y67" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB67" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG67" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI67" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ67" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK67" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM67" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR67" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="68" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>1</v>
+      </c>
+      <c r="B68" s="2">
+        <v>2</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F68" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G68" s="5">
+        <v>67</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L68" s="6">
+        <v>4379</v>
+      </c>
+      <c r="M68" s="7">
+        <v>697321.32</v>
+      </c>
+      <c r="N68" s="6">
+        <v>1</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P68" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q68" s="6">
+        <v>0</v>
+      </c>
+      <c r="R68" s="7">
+        <v>0</v>
+      </c>
+      <c r="S68" s="9">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U68" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V68" s="11">
+        <v>11</v>
+      </c>
+      <c r="W68" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X68" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y68" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI68" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ68" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK68" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR68" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="69" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>1</v>
+      </c>
+      <c r="B69" s="2">
+        <v>2</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F69" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G69" s="5">
+        <v>68</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L69" s="6">
+        <v>4380</v>
+      </c>
+      <c r="M69" s="7">
+        <v>697480.56</v>
+      </c>
+      <c r="N69" s="6">
+        <v>1</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P69" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q69" s="6">
+        <v>0</v>
+      </c>
+      <c r="R69" s="7">
+        <v>0</v>
+      </c>
+      <c r="S69" s="9">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U69" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V69" s="11">
+        <v>11</v>
+      </c>
+      <c r="W69" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X69" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y69" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG69" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI69" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ69" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK69" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR69" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="70" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>1</v>
+      </c>
+      <c r="B70" s="2">
+        <v>2</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F70" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G70" s="5">
+        <v>69</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L70" s="6">
+        <v>4381</v>
+      </c>
+      <c r="M70" s="7">
+        <v>697639.8</v>
+      </c>
+      <c r="N70" s="6">
+        <v>1</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P70" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q70" s="6">
+        <v>0</v>
+      </c>
+      <c r="R70" s="7">
+        <v>0</v>
+      </c>
+      <c r="S70" s="9">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U70" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V70" s="11">
+        <v>11</v>
+      </c>
+      <c r="W70" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X70" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y70" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI70" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ70" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK70" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR70" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="71" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>1</v>
+      </c>
+      <c r="B71" s="2">
+        <v>2</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F71" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G71" s="5">
+        <v>70</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L71" s="6">
+        <v>4382</v>
+      </c>
+      <c r="M71" s="7">
+        <v>697799.04</v>
+      </c>
+      <c r="N71" s="6">
+        <v>1</v>
+      </c>
+      <c r="O71" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P71" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>0</v>
+      </c>
+      <c r="R71" s="7">
+        <v>0</v>
+      </c>
+      <c r="S71" s="9">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U71" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V71" s="11">
+        <v>11</v>
+      </c>
+      <c r="W71" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X71" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y71" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG71" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI71" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ71" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK71" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR71" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="72" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>1</v>
+      </c>
+      <c r="B72" s="2">
+        <v>2</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F72" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G72" s="5">
+        <v>71</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L72" s="6">
+        <v>4383</v>
+      </c>
+      <c r="M72" s="7">
+        <v>697958.28</v>
+      </c>
+      <c r="N72" s="6">
+        <v>1</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P72" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q72" s="6">
+        <v>0</v>
+      </c>
+      <c r="R72" s="7">
+        <v>0</v>
+      </c>
+      <c r="S72" s="9">
+        <v>0</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U72" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V72" s="11">
+        <v>11</v>
+      </c>
+      <c r="W72" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X72" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y72" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG72" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI72" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ72" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK72" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM72" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR72" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="73" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>1</v>
+      </c>
+      <c r="B73" s="2">
+        <v>2</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F73" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G73" s="5">
+        <v>72</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L73" s="6">
+        <v>4384</v>
+      </c>
+      <c r="M73" s="7">
+        <v>698117.53</v>
+      </c>
+      <c r="N73" s="6">
+        <v>1</v>
+      </c>
+      <c r="O73" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P73" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q73" s="6">
+        <v>0</v>
+      </c>
+      <c r="R73" s="7">
+        <v>0</v>
+      </c>
+      <c r="S73" s="9">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U73" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V73" s="11">
+        <v>11</v>
+      </c>
+      <c r="W73" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X73" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y73" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG73" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI73" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ73" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK73" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR73" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="74" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>1</v>
+      </c>
+      <c r="B74" s="2">
+        <v>2</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F74" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G74" s="5">
+        <v>73</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L74" s="6">
+        <v>4385</v>
+      </c>
+      <c r="M74" s="7">
+        <v>698276.77</v>
+      </c>
+      <c r="N74" s="6">
+        <v>1</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P74" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q74" s="6">
+        <v>0</v>
+      </c>
+      <c r="R74" s="7">
+        <v>0</v>
+      </c>
+      <c r="S74" s="9">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U74" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V74" s="11">
+        <v>11</v>
+      </c>
+      <c r="W74" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X74" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y74" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG74" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI74" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ74" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK74" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR74" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="75" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>1</v>
+      </c>
+      <c r="B75" s="2">
+        <v>2</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F75" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G75" s="5">
+        <v>74</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L75" s="6">
+        <v>4386</v>
+      </c>
+      <c r="M75" s="7">
+        <v>698436.01</v>
+      </c>
+      <c r="N75" s="6">
+        <v>1</v>
+      </c>
+      <c r="O75" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P75" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>0</v>
+      </c>
+      <c r="R75" s="7">
+        <v>0</v>
+      </c>
+      <c r="S75" s="9">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U75" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V75" s="11">
+        <v>11</v>
+      </c>
+      <c r="W75" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X75" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y75" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG75" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI75" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ75" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK75" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR75" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="76" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>1</v>
+      </c>
+      <c r="B76" s="2">
+        <v>2</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F76" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G76" s="5">
+        <v>75</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L76" s="6">
+        <v>4387</v>
+      </c>
+      <c r="M76" s="7">
+        <v>698595.25</v>
+      </c>
+      <c r="N76" s="6">
+        <v>1</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P76" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>0</v>
+      </c>
+      <c r="R76" s="7">
+        <v>0</v>
+      </c>
+      <c r="S76" s="9">
+        <v>0</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U76" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V76" s="11">
+        <v>11</v>
+      </c>
+      <c r="W76" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X76" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y76" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG76" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI76" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ76" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK76" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR76" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="77" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>1</v>
+      </c>
+      <c r="B77" s="2">
+        <v>2</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F77" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G77" s="5">
+        <v>76</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L77" s="6">
+        <v>4388</v>
+      </c>
+      <c r="M77" s="7">
+        <v>698754.49</v>
+      </c>
+      <c r="N77" s="6">
+        <v>1</v>
+      </c>
+      <c r="O77" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P77" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q77" s="6">
+        <v>0</v>
+      </c>
+      <c r="R77" s="7">
+        <v>0</v>
+      </c>
+      <c r="S77" s="9">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U77" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V77" s="11">
+        <v>11</v>
+      </c>
+      <c r="W77" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X77" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y77" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG77" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI77" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ77" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK77" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR77" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="78" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>1</v>
+      </c>
+      <c r="B78" s="2">
+        <v>2</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F78" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G78" s="5">
+        <v>77</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L78" s="6">
+        <v>4389</v>
+      </c>
+      <c r="M78" s="7">
+        <v>698913.74</v>
+      </c>
+      <c r="N78" s="6">
+        <v>1</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P78" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q78" s="6">
+        <v>0</v>
+      </c>
+      <c r="R78" s="7">
+        <v>0</v>
+      </c>
+      <c r="S78" s="9">
+        <v>0</v>
+      </c>
+      <c r="T78" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U78" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V78" s="11">
+        <v>11</v>
+      </c>
+      <c r="W78" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X78" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y78" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG78" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI78" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ78" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK78" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM78" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR78" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="79" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>1</v>
+      </c>
+      <c r="B79" s="2">
+        <v>2</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F79" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G79" s="5">
+        <v>78</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L79" s="6">
+        <v>4390</v>
+      </c>
+      <c r="M79" s="7">
+        <v>699072.98</v>
+      </c>
+      <c r="N79" s="6">
+        <v>1</v>
+      </c>
+      <c r="O79" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P79" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q79" s="6">
+        <v>0</v>
+      </c>
+      <c r="R79" s="7">
+        <v>0</v>
+      </c>
+      <c r="S79" s="9">
+        <v>0</v>
+      </c>
+      <c r="T79" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U79" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V79" s="11">
+        <v>11</v>
+      </c>
+      <c r="W79" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X79" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y79" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG79" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI79" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ79" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK79" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM79" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR79" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="80" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>1</v>
+      </c>
+      <c r="B80" s="2">
+        <v>2</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F80" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G80" s="5">
+        <v>79</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L80" s="6">
+        <v>4391</v>
+      </c>
+      <c r="M80" s="7">
+        <v>699232.22</v>
+      </c>
+      <c r="N80" s="6">
+        <v>1</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P80" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q80" s="6">
+        <v>0</v>
+      </c>
+      <c r="R80" s="7">
+        <v>0</v>
+      </c>
+      <c r="S80" s="9">
+        <v>0</v>
+      </c>
+      <c r="T80" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U80" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V80" s="11">
+        <v>11</v>
+      </c>
+      <c r="W80" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X80" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y80" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG80" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI80" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ80" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK80" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM80" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR80" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="81" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>1</v>
+      </c>
+      <c r="B81" s="2">
+        <v>2</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F81" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G81" s="5">
+        <v>80</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L81" s="6">
+        <v>4392</v>
+      </c>
+      <c r="M81" s="7">
+        <v>699391.46</v>
+      </c>
+      <c r="N81" s="6">
+        <v>1</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P81" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q81" s="6">
+        <v>0</v>
+      </c>
+      <c r="R81" s="7">
+        <v>0</v>
+      </c>
+      <c r="S81" s="9">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U81" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V81" s="11">
+        <v>11</v>
+      </c>
+      <c r="W81" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X81" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y81" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG81" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI81" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ81" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK81" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM81" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR81" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="82" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>1</v>
+      </c>
+      <c r="B82" s="2">
+        <v>2</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F82" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G82" s="5">
+        <v>81</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L82" s="6">
+        <v>4393</v>
+      </c>
+      <c r="M82" s="7">
+        <v>699550.71</v>
+      </c>
+      <c r="N82" s="6">
+        <v>1</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P82" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q82" s="6">
+        <v>0</v>
+      </c>
+      <c r="R82" s="7">
+        <v>0</v>
+      </c>
+      <c r="S82" s="9">
+        <v>0</v>
+      </c>
+      <c r="T82" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U82" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V82" s="11">
+        <v>11</v>
+      </c>
+      <c r="W82" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X82" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y82" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA82" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB82" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD82" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG82" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH82" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI82" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ82" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK82" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL82" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM82" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN82" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO82" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP82" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ82" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR82" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="83" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>1</v>
+      </c>
+      <c r="B83" s="2">
+        <v>2</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F83" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G83" s="5">
+        <v>82</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L83" s="6">
+        <v>4394</v>
+      </c>
+      <c r="M83" s="7">
+        <v>699709.95</v>
+      </c>
+      <c r="N83" s="6">
+        <v>1</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P83" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q83" s="6">
+        <v>0</v>
+      </c>
+      <c r="R83" s="7">
+        <v>0</v>
+      </c>
+      <c r="S83" s="9">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U83" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V83" s="11">
+        <v>11</v>
+      </c>
+      <c r="W83" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X83" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y83" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG83" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI83" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ83" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK83" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL83" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM83" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN83" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO83" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP83" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ83" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR83" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="84" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>1</v>
+      </c>
+      <c r="B84" s="2">
+        <v>2</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F84" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G84" s="5">
+        <v>83</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L84" s="6">
+        <v>4395</v>
+      </c>
+      <c r="M84" s="7">
+        <v>699869.19</v>
+      </c>
+      <c r="N84" s="6">
+        <v>1</v>
+      </c>
+      <c r="O84" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P84" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q84" s="6">
+        <v>0</v>
+      </c>
+      <c r="R84" s="7">
+        <v>0</v>
+      </c>
+      <c r="S84" s="9">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U84" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V84" s="11">
+        <v>11</v>
+      </c>
+      <c r="W84" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X84" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y84" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG84" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI84" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ84" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK84" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN84" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO84" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP84" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ84" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR84" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="85" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>1</v>
+      </c>
+      <c r="B85" s="2">
+        <v>2</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F85" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G85" s="5">
+        <v>84</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L85" s="6">
+        <v>4396</v>
+      </c>
+      <c r="M85" s="7">
+        <v>700028.43</v>
+      </c>
+      <c r="N85" s="6">
+        <v>1</v>
+      </c>
+      <c r="O85" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P85" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q85" s="6">
+        <v>0</v>
+      </c>
+      <c r="R85" s="7">
+        <v>0</v>
+      </c>
+      <c r="S85" s="9">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U85" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V85" s="11">
+        <v>11</v>
+      </c>
+      <c r="W85" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X85" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y85" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG85" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI85" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ85" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK85" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN85" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO85" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP85" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ85" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR85" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="86" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>1</v>
+      </c>
+      <c r="B86" s="2">
+        <v>2</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F86" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G86" s="5">
+        <v>85</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L86" s="6">
+        <v>4397</v>
+      </c>
+      <c r="M86" s="7">
+        <v>700187.67</v>
+      </c>
+      <c r="N86" s="6">
+        <v>1</v>
+      </c>
+      <c r="O86" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P86" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q86" s="6">
+        <v>0</v>
+      </c>
+      <c r="R86" s="7">
+        <v>0</v>
+      </c>
+      <c r="S86" s="9">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U86" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V86" s="11">
+        <v>11</v>
+      </c>
+      <c r="W86" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X86" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y86" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG86" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI86" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ86" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK86" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN86" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO86" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP86" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ86" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR86" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="87" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>1</v>
+      </c>
+      <c r="B87" s="2">
+        <v>2</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F87" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G87" s="5">
+        <v>86</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L87" s="6">
+        <v>4398</v>
+      </c>
+      <c r="M87" s="7">
+        <v>700346.92</v>
+      </c>
+      <c r="N87" s="6">
+        <v>1</v>
+      </c>
+      <c r="O87" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P87" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q87" s="6">
+        <v>0</v>
+      </c>
+      <c r="R87" s="7">
+        <v>0</v>
+      </c>
+      <c r="S87" s="9">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U87" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V87" s="11">
+        <v>11</v>
+      </c>
+      <c r="W87" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X87" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y87" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG87" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI87" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ87" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK87" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN87" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO87" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP87" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ87" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR87" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="88" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>1</v>
+      </c>
+      <c r="B88" s="2">
+        <v>2</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F88" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G88" s="5">
+        <v>87</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L88" s="6">
+        <v>4399</v>
+      </c>
+      <c r="M88" s="7">
+        <v>700506.16</v>
+      </c>
+      <c r="N88" s="6">
+        <v>1</v>
+      </c>
+      <c r="O88" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P88" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q88" s="6">
+        <v>0</v>
+      </c>
+      <c r="R88" s="7">
+        <v>0</v>
+      </c>
+      <c r="S88" s="9">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U88" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V88" s="11">
+        <v>11</v>
+      </c>
+      <c r="W88" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X88" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y88" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG88" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI88" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ88" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK88" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN88" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO88" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP88" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ88" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR88" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="89" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>1</v>
+      </c>
+      <c r="B89" s="2">
+        <v>2</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F89" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G89" s="5">
+        <v>88</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L89" s="6">
+        <v>4400</v>
+      </c>
+      <c r="M89" s="7">
+        <v>700665.4</v>
+      </c>
+      <c r="N89" s="6">
+        <v>1</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P89" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>0</v>
+      </c>
+      <c r="R89" s="7">
+        <v>0</v>
+      </c>
+      <c r="S89" s="9">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U89" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V89" s="11">
+        <v>11</v>
+      </c>
+      <c r="W89" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X89" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y89" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI89" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ89" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK89" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM89" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN89" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO89" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP89" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ89" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR89" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="90" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>1</v>
+      </c>
+      <c r="B90" s="2">
+        <v>2</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F90" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G90" s="5">
+        <v>89</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L90" s="6">
+        <v>4401</v>
+      </c>
+      <c r="M90" s="7">
+        <v>700824.64</v>
+      </c>
+      <c r="N90" s="6">
+        <v>1</v>
+      </c>
+      <c r="O90" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P90" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q90" s="6">
+        <v>0</v>
+      </c>
+      <c r="R90" s="7">
+        <v>0</v>
+      </c>
+      <c r="S90" s="9">
+        <v>0</v>
+      </c>
+      <c r="T90" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U90" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V90" s="11">
+        <v>11</v>
+      </c>
+      <c r="W90" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X90" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y90" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF90" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG90" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI90" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ90" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK90" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM90" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN90" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO90" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP90" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ90" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR90" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="91" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>1</v>
+      </c>
+      <c r="B91" s="2">
+        <v>2</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F91" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G91" s="5">
+        <v>90</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L91" s="6">
+        <v>4402</v>
+      </c>
+      <c r="M91" s="7">
+        <v>700983.88</v>
+      </c>
+      <c r="N91" s="6">
+        <v>1</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P91" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q91" s="6">
+        <v>0</v>
+      </c>
+      <c r="R91" s="7">
+        <v>0</v>
+      </c>
+      <c r="S91" s="9">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U91" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V91" s="11">
+        <v>11</v>
+      </c>
+      <c r="W91" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X91" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y91" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG91" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI91" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ91" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK91" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM91" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN91" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO91" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP91" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ91" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR91" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="92" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>1</v>
+      </c>
+      <c r="B92" s="2">
+        <v>2</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F92" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G92" s="5">
+        <v>91</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L92" s="6">
+        <v>4403</v>
+      </c>
+      <c r="M92" s="7">
+        <v>701143.13</v>
+      </c>
+      <c r="N92" s="6">
+        <v>1</v>
+      </c>
+      <c r="O92" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P92" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q92" s="6">
+        <v>0</v>
+      </c>
+      <c r="R92" s="7">
+        <v>0</v>
+      </c>
+      <c r="S92" s="9">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U92" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V92" s="11">
+        <v>11</v>
+      </c>
+      <c r="W92" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X92" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y92" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG92" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI92" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ92" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK92" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN92" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO92" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP92" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ92" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR92" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="93" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>1</v>
+      </c>
+      <c r="B93" s="2">
+        <v>2</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F93" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G93" s="5">
+        <v>92</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K93" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L93" s="6">
+        <v>4404</v>
+      </c>
+      <c r="M93" s="7">
+        <v>701302.37</v>
+      </c>
+      <c r="N93" s="6">
+        <v>1</v>
+      </c>
+      <c r="O93" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P93" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q93" s="6">
+        <v>0</v>
+      </c>
+      <c r="R93" s="7">
+        <v>0</v>
+      </c>
+      <c r="S93" s="9">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U93" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V93" s="11">
+        <v>11</v>
+      </c>
+      <c r="W93" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X93" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y93" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG93" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI93" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ93" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK93" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM93" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN93" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO93" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP93" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ93" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR93" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="94" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>1</v>
+      </c>
+      <c r="B94" s="2">
+        <v>2</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F94" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G94" s="5">
+        <v>93</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L94" s="6">
+        <v>4405</v>
+      </c>
+      <c r="M94" s="7">
+        <v>701461.61</v>
+      </c>
+      <c r="N94" s="6">
+        <v>1</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P94" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q94" s="6">
+        <v>0</v>
+      </c>
+      <c r="R94" s="7">
+        <v>0</v>
+      </c>
+      <c r="S94" s="9">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U94" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V94" s="11">
+        <v>11</v>
+      </c>
+      <c r="W94" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X94" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y94" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG94" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI94" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ94" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK94" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM94" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR94" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="95" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>1</v>
+      </c>
+      <c r="B95" s="2">
+        <v>2</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F95" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G95" s="5">
+        <v>94</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L95" s="6">
+        <v>4406</v>
+      </c>
+      <c r="M95" s="7">
+        <v>701620.85</v>
+      </c>
+      <c r="N95" s="6">
+        <v>1</v>
+      </c>
+      <c r="O95" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P95" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q95" s="6">
+        <v>0</v>
+      </c>
+      <c r="R95" s="7">
+        <v>0</v>
+      </c>
+      <c r="S95" s="9">
+        <v>0</v>
+      </c>
+      <c r="T95" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U95" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V95" s="11">
+        <v>11</v>
+      </c>
+      <c r="W95" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X95" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y95" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB95" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG95" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI95" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ95" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK95" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM95" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR95" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="96" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>1</v>
+      </c>
+      <c r="B96" s="2">
+        <v>2</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F96" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G96" s="5">
+        <v>95</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L96" s="6">
+        <v>4407</v>
+      </c>
+      <c r="M96" s="7">
+        <v>701780.1</v>
+      </c>
+      <c r="N96" s="6">
+        <v>1</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P96" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q96" s="6">
+        <v>0</v>
+      </c>
+      <c r="R96" s="7">
+        <v>0</v>
+      </c>
+      <c r="S96" s="9">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U96" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V96" s="11">
+        <v>11</v>
+      </c>
+      <c r="W96" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X96" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y96" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG96" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI96" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ96" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK96" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR96" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="97" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>1</v>
+      </c>
+      <c r="B97" s="2">
+        <v>2</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F97" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G97" s="5">
+        <v>96</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L97" s="6">
+        <v>4408</v>
+      </c>
+      <c r="M97" s="7">
+        <v>701939.34</v>
+      </c>
+      <c r="N97" s="6">
+        <v>1</v>
+      </c>
+      <c r="O97" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P97" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q97" s="6">
+        <v>0</v>
+      </c>
+      <c r="R97" s="7">
+        <v>0</v>
+      </c>
+      <c r="S97" s="9">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U97" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V97" s="11">
+        <v>11</v>
+      </c>
+      <c r="W97" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X97" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y97" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG97" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI97" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ97" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK97" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR97" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="98" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>1</v>
+      </c>
+      <c r="B98" s="2">
+        <v>2</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F98" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G98" s="5">
+        <v>97</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L98" s="6">
+        <v>4409</v>
+      </c>
+      <c r="M98" s="7">
+        <v>702098.58</v>
+      </c>
+      <c r="N98" s="6">
+        <v>1</v>
+      </c>
+      <c r="O98" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P98" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q98" s="6">
+        <v>0</v>
+      </c>
+      <c r="R98" s="7">
+        <v>0</v>
+      </c>
+      <c r="S98" s="9">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U98" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V98" s="11">
+        <v>11</v>
+      </c>
+      <c r="W98" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X98" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y98" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG98" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI98" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ98" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK98" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR98" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="99" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>1</v>
+      </c>
+      <c r="B99" s="2">
+        <v>2</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F99" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G99" s="5">
+        <v>98</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L99" s="6">
+        <v>4410</v>
+      </c>
+      <c r="M99" s="7">
+        <v>702257.82</v>
+      </c>
+      <c r="N99" s="6">
+        <v>1</v>
+      </c>
+      <c r="O99" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P99" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q99" s="6">
+        <v>0</v>
+      </c>
+      <c r="R99" s="7">
+        <v>0</v>
+      </c>
+      <c r="S99" s="9">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U99" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V99" s="11">
+        <v>11</v>
+      </c>
+      <c r="W99" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X99" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y99" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG99" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI99" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ99" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK99" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR99" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="100" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>1</v>
+      </c>
+      <c r="B100" s="2">
+        <v>2</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F100" s="4">
+        <v>46304</v>
+      </c>
+      <c r="G100" s="5">
+        <v>99</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L100" s="6">
+        <v>4411</v>
+      </c>
+      <c r="M100" s="7">
+        <v>702417.06</v>
+      </c>
+      <c r="N100" s="6">
+        <v>1</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P100" s="8">
+        <v>159.24</v>
+      </c>
+      <c r="Q100" s="6">
+        <v>0</v>
+      </c>
+      <c r="R100" s="7">
+        <v>0</v>
+      </c>
+      <c r="S100" s="9">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U100" s="10">
+        <v>68174</v>
+      </c>
+      <c r="V100" s="11">
+        <v>11</v>
+      </c>
+      <c r="W100" s="4">
+        <v>46304</v>
+      </c>
+      <c r="X100" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y100" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG100" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI100" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ100" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK100" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM100" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR100" s="3" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5065AE5E-4ACF-47D6-9DC9-F70C82E33F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDE10212-F98F-43BC-80EA-26185F1B8912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8036" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8072" uniqueCount="506">
   <si>
     <t>Sel</t>
   </si>
@@ -1306,6 +1306,12 @@
     <t>1871400013178</t>
   </si>
   <si>
+    <t>1871400013179</t>
+  </si>
+  <si>
+    <t>1871400013180</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
@@ -2107,7 +2113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR445"/>
+  <dimension ref="A1:AR447"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -51835,7 +51841,7 @@
         <v>411</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>428</v>
+        <v>45</v>
       </c>
       <c r="E372" s="3" t="s">
         <v>46</v>
@@ -51844,7 +51850,7 @@
         <v>46309</v>
       </c>
       <c r="G372" s="5">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H372" s="3" t="s">
         <v>47</v>
@@ -51859,19 +51865,19 @@
         <v>50</v>
       </c>
       <c r="L372" s="6">
-        <v>662</v>
+        <v>485</v>
       </c>
       <c r="M372" s="7">
-        <v>215971.5</v>
+        <v>161790.49</v>
       </c>
       <c r="N372" s="6">
         <v>1</v>
       </c>
       <c r="O372" s="3" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="P372" s="8">
-        <v>326.24</v>
+        <v>333.59</v>
       </c>
       <c r="Q372" s="6">
         <v>0</v>
@@ -51886,7 +51892,7 @@
         <v>52</v>
       </c>
       <c r="U372" s="10">
-        <v>68241</v>
+        <v>68286</v>
       </c>
       <c r="V372" s="11">
         <v>11</v>
@@ -51895,7 +51901,7 @@
         <v>46309</v>
       </c>
       <c r="X372" s="12">
-        <v>0.3125</v>
+        <v>0.49305559999999998</v>
       </c>
       <c r="Y372" s="10">
         <v>0</v>
@@ -51955,7 +51961,7 @@
         <v>53</v>
       </c>
       <c r="AR372" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="373" spans="1:44" x14ac:dyDescent="0.3">
@@ -51969,7 +51975,7 @@
         <v>411</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>428</v>
+        <v>45</v>
       </c>
       <c r="E373" s="3" t="s">
         <v>46</v>
@@ -51978,7 +51984,7 @@
         <v>46309</v>
       </c>
       <c r="G373" s="5">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H373" s="3" t="s">
         <v>47</v>
@@ -51993,19 +51999,19 @@
         <v>50</v>
       </c>
       <c r="L373" s="6">
-        <v>663</v>
+        <v>486</v>
       </c>
       <c r="M373" s="7">
-        <v>216297.75</v>
+        <v>162124.07</v>
       </c>
       <c r="N373" s="6">
         <v>1</v>
       </c>
       <c r="O373" s="3" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="P373" s="8">
-        <v>326.24</v>
+        <v>333.59</v>
       </c>
       <c r="Q373" s="6">
         <v>0</v>
@@ -52020,7 +52026,7 @@
         <v>52</v>
       </c>
       <c r="U373" s="10">
-        <v>68241</v>
+        <v>68286</v>
       </c>
       <c r="V373" s="11">
         <v>11</v>
@@ -52029,7 +52035,7 @@
         <v>46309</v>
       </c>
       <c r="X373" s="12">
-        <v>0.3125</v>
+        <v>0.49305559999999998</v>
       </c>
       <c r="Y373" s="10">
         <v>0</v>
@@ -52089,7 +52095,7 @@
         <v>53</v>
       </c>
       <c r="AR373" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="374" spans="1:44" x14ac:dyDescent="0.3">
@@ -52103,7 +52109,7 @@
         <v>411</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E374" s="3" t="s">
         <v>46</v>
@@ -52112,7 +52118,7 @@
         <v>46309</v>
       </c>
       <c r="G374" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H374" s="3" t="s">
         <v>47</v>
@@ -52127,16 +52133,16 @@
         <v>50</v>
       </c>
       <c r="L374" s="6">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="M374" s="7">
-        <v>216623.99</v>
+        <v>215971.5</v>
       </c>
       <c r="N374" s="6">
         <v>1</v>
       </c>
       <c r="O374" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P374" s="8">
         <v>326.24</v>
@@ -52237,7 +52243,7 @@
         <v>411</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E375" s="3" t="s">
         <v>46</v>
@@ -52246,7 +52252,7 @@
         <v>46309</v>
       </c>
       <c r="G375" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H375" s="3" t="s">
         <v>47</v>
@@ -52261,16 +52267,16 @@
         <v>50</v>
       </c>
       <c r="L375" s="6">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="M375" s="7">
-        <v>216950.23</v>
+        <v>216297.75</v>
       </c>
       <c r="N375" s="6">
         <v>1</v>
       </c>
       <c r="O375" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P375" s="8">
         <v>326.24</v>
@@ -52371,7 +52377,7 @@
         <v>411</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E376" s="3" t="s">
         <v>46</v>
@@ -52380,7 +52386,7 @@
         <v>46309</v>
       </c>
       <c r="G376" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H376" s="3" t="s">
         <v>47</v>
@@ -52395,16 +52401,16 @@
         <v>50</v>
       </c>
       <c r="L376" s="6">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="M376" s="7">
-        <v>217276.47</v>
+        <v>216623.99</v>
       </c>
       <c r="N376" s="6">
         <v>1</v>
       </c>
       <c r="O376" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P376" s="8">
         <v>326.24</v>
@@ -52505,7 +52511,7 @@
         <v>411</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E377" s="3" t="s">
         <v>46</v>
@@ -52514,7 +52520,7 @@
         <v>46309</v>
       </c>
       <c r="G377" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H377" s="3" t="s">
         <v>47</v>
@@ -52529,16 +52535,16 @@
         <v>50</v>
       </c>
       <c r="L377" s="6">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="M377" s="7">
-        <v>217602.71</v>
+        <v>216950.23</v>
       </c>
       <c r="N377" s="6">
         <v>1</v>
       </c>
       <c r="O377" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P377" s="8">
         <v>326.24</v>
@@ -52639,7 +52645,7 @@
         <v>411</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E378" s="3" t="s">
         <v>46</v>
@@ -52648,7 +52654,7 @@
         <v>46309</v>
       </c>
       <c r="G378" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H378" s="3" t="s">
         <v>47</v>
@@ -52663,16 +52669,16 @@
         <v>50</v>
       </c>
       <c r="L378" s="6">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="M378" s="7">
-        <v>217928.95</v>
+        <v>217276.47</v>
       </c>
       <c r="N378" s="6">
         <v>1</v>
       </c>
       <c r="O378" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P378" s="8">
         <v>326.24</v>
@@ -52773,7 +52779,7 @@
         <v>411</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E379" s="3" t="s">
         <v>46</v>
@@ -52782,7 +52788,7 @@
         <v>46309</v>
       </c>
       <c r="G379" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H379" s="3" t="s">
         <v>47</v>
@@ -52797,16 +52803,16 @@
         <v>50</v>
       </c>
       <c r="L379" s="6">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="M379" s="7">
-        <v>218255.19</v>
+        <v>217602.71</v>
       </c>
       <c r="N379" s="6">
         <v>1</v>
       </c>
       <c r="O379" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P379" s="8">
         <v>326.24</v>
@@ -52833,7 +52839,7 @@
         <v>46309</v>
       </c>
       <c r="X379" s="12">
-        <v>0.32708330000000002</v>
+        <v>0.3125</v>
       </c>
       <c r="Y379" s="10">
         <v>0</v>
@@ -52907,7 +52913,7 @@
         <v>411</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E380" s="3" t="s">
         <v>46</v>
@@ -52916,7 +52922,7 @@
         <v>46309</v>
       </c>
       <c r="G380" s="5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H380" s="3" t="s">
         <v>47</v>
@@ -52931,16 +52937,16 @@
         <v>50</v>
       </c>
       <c r="L380" s="6">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="M380" s="7">
-        <v>218581.43</v>
+        <v>217928.95</v>
       </c>
       <c r="N380" s="6">
         <v>1</v>
       </c>
       <c r="O380" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P380" s="8">
         <v>326.24</v>
@@ -52967,7 +52973,7 @@
         <v>46309</v>
       </c>
       <c r="X380" s="12">
-        <v>0.32708330000000002</v>
+        <v>0.3125</v>
       </c>
       <c r="Y380" s="10">
         <v>0</v>
@@ -53041,7 +53047,7 @@
         <v>411</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E381" s="3" t="s">
         <v>46</v>
@@ -53050,7 +53056,7 @@
         <v>46309</v>
       </c>
       <c r="G381" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H381" s="3" t="s">
         <v>47</v>
@@ -53065,16 +53071,16 @@
         <v>50</v>
       </c>
       <c r="L381" s="6">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="M381" s="7">
-        <v>218907.67</v>
+        <v>218255.19</v>
       </c>
       <c r="N381" s="6">
         <v>1</v>
       </c>
       <c r="O381" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P381" s="8">
         <v>326.24</v>
@@ -53175,7 +53181,7 @@
         <v>411</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E382" s="3" t="s">
         <v>46</v>
@@ -53184,7 +53190,7 @@
         <v>46309</v>
       </c>
       <c r="G382" s="5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H382" s="3" t="s">
         <v>47</v>
@@ -53199,16 +53205,16 @@
         <v>50</v>
       </c>
       <c r="L382" s="6">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="M382" s="7">
-        <v>219233.91</v>
+        <v>218581.43</v>
       </c>
       <c r="N382" s="6">
         <v>1</v>
       </c>
       <c r="O382" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P382" s="8">
         <v>326.24</v>
@@ -53309,7 +53315,7 @@
         <v>411</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E383" s="3" t="s">
         <v>46</v>
@@ -53318,7 +53324,7 @@
         <v>46309</v>
       </c>
       <c r="G383" s="5">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H383" s="3" t="s">
         <v>47</v>
@@ -53333,16 +53339,16 @@
         <v>50</v>
       </c>
       <c r="L383" s="6">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="M383" s="7">
-        <v>219560.15</v>
+        <v>218907.67</v>
       </c>
       <c r="N383" s="6">
         <v>1</v>
       </c>
       <c r="O383" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P383" s="8">
         <v>326.24</v>
@@ -53443,7 +53449,7 @@
         <v>411</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E384" s="3" t="s">
         <v>46</v>
@@ -53452,7 +53458,7 @@
         <v>46309</v>
       </c>
       <c r="G384" s="5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H384" s="3" t="s">
         <v>47</v>
@@ -53467,16 +53473,16 @@
         <v>50</v>
       </c>
       <c r="L384" s="6">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="M384" s="7">
-        <v>219886.4</v>
+        <v>219233.91</v>
       </c>
       <c r="N384" s="6">
         <v>1</v>
       </c>
       <c r="O384" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P384" s="8">
         <v>326.24</v>
@@ -53577,7 +53583,7 @@
         <v>411</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E385" s="3" t="s">
         <v>46</v>
@@ -53586,7 +53592,7 @@
         <v>46309</v>
       </c>
       <c r="G385" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H385" s="3" t="s">
         <v>47</v>
@@ -53601,16 +53607,16 @@
         <v>50</v>
       </c>
       <c r="L385" s="6">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="M385" s="7">
-        <v>220212.64</v>
+        <v>219560.15</v>
       </c>
       <c r="N385" s="6">
         <v>1</v>
       </c>
       <c r="O385" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P385" s="8">
         <v>326.24</v>
@@ -53637,7 +53643,7 @@
         <v>46309</v>
       </c>
       <c r="X385" s="12">
-        <v>0.34027780000000002</v>
+        <v>0.32708330000000002</v>
       </c>
       <c r="Y385" s="10">
         <v>0</v>
@@ -53711,7 +53717,7 @@
         <v>411</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E386" s="3" t="s">
         <v>46</v>
@@ -53720,7 +53726,7 @@
         <v>46309</v>
       </c>
       <c r="G386" s="5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H386" s="3" t="s">
         <v>47</v>
@@ -53735,16 +53741,16 @@
         <v>50</v>
       </c>
       <c r="L386" s="6">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="M386" s="7">
-        <v>220538.88</v>
+        <v>219886.4</v>
       </c>
       <c r="N386" s="6">
         <v>1</v>
       </c>
       <c r="O386" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P386" s="8">
         <v>326.24</v>
@@ -53771,7 +53777,7 @@
         <v>46309</v>
       </c>
       <c r="X386" s="12">
-        <v>0.34027780000000002</v>
+        <v>0.32708330000000002</v>
       </c>
       <c r="Y386" s="10">
         <v>0</v>
@@ -53845,7 +53851,7 @@
         <v>411</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E387" s="3" t="s">
         <v>46</v>
@@ -53854,7 +53860,7 @@
         <v>46309</v>
       </c>
       <c r="G387" s="5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H387" s="3" t="s">
         <v>47</v>
@@ -53869,16 +53875,16 @@
         <v>50</v>
       </c>
       <c r="L387" s="6">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="M387" s="7">
-        <v>220865.12</v>
+        <v>220212.64</v>
       </c>
       <c r="N387" s="6">
         <v>1</v>
       </c>
       <c r="O387" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P387" s="8">
         <v>326.24</v>
@@ -53979,7 +53985,7 @@
         <v>411</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E388" s="3" t="s">
         <v>46</v>
@@ -53988,7 +53994,7 @@
         <v>46309</v>
       </c>
       <c r="G388" s="5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H388" s="3" t="s">
         <v>47</v>
@@ -54003,16 +54009,16 @@
         <v>50</v>
       </c>
       <c r="L388" s="6">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="M388" s="7">
-        <v>221191.36</v>
+        <v>220538.88</v>
       </c>
       <c r="N388" s="6">
         <v>1</v>
       </c>
       <c r="O388" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P388" s="8">
         <v>326.24</v>
@@ -54113,7 +54119,7 @@
         <v>411</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E389" s="3" t="s">
         <v>46</v>
@@ -54122,7 +54128,7 @@
         <v>46309</v>
       </c>
       <c r="G389" s="5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H389" s="3" t="s">
         <v>47</v>
@@ -54137,16 +54143,16 @@
         <v>50</v>
       </c>
       <c r="L389" s="6">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="M389" s="7">
-        <v>221517.6</v>
+        <v>220865.12</v>
       </c>
       <c r="N389" s="6">
         <v>1</v>
       </c>
       <c r="O389" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P389" s="8">
         <v>326.24</v>
@@ -54247,7 +54253,7 @@
         <v>411</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E390" s="3" t="s">
         <v>46</v>
@@ -54256,7 +54262,7 @@
         <v>46309</v>
       </c>
       <c r="G390" s="5">
-        <v>310</v>
+        <v>21</v>
       </c>
       <c r="H390" s="3" t="s">
         <v>47</v>
@@ -54271,16 +54277,16 @@
         <v>50</v>
       </c>
       <c r="L390" s="6">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="M390" s="7">
-        <v>221843.84</v>
+        <v>221191.36</v>
       </c>
       <c r="N390" s="6">
         <v>1</v>
       </c>
       <c r="O390" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P390" s="8">
         <v>326.24</v>
@@ -54307,7 +54313,7 @@
         <v>46309</v>
       </c>
       <c r="X390" s="12">
-        <v>0.4819444</v>
+        <v>0.34027780000000002</v>
       </c>
       <c r="Y390" s="10">
         <v>0</v>
@@ -54381,7 +54387,7 @@
         <v>411</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E391" s="3" t="s">
         <v>46</v>
@@ -54390,7 +54396,7 @@
         <v>46309</v>
       </c>
       <c r="G391" s="5">
-        <v>311</v>
+        <v>22</v>
       </c>
       <c r="H391" s="3" t="s">
         <v>47</v>
@@ -54405,16 +54411,16 @@
         <v>50</v>
       </c>
       <c r="L391" s="6">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="M391" s="7">
-        <v>222170.08</v>
+        <v>221517.6</v>
       </c>
       <c r="N391" s="6">
         <v>1</v>
       </c>
       <c r="O391" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P391" s="8">
         <v>326.24</v>
@@ -54441,7 +54447,7 @@
         <v>46309</v>
       </c>
       <c r="X391" s="12">
-        <v>0.4819444</v>
+        <v>0.34027780000000002</v>
       </c>
       <c r="Y391" s="10">
         <v>0</v>
@@ -54515,7 +54521,7 @@
         <v>411</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E392" s="3" t="s">
         <v>46</v>
@@ -54524,7 +54530,7 @@
         <v>46309</v>
       </c>
       <c r="G392" s="5">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H392" s="3" t="s">
         <v>47</v>
@@ -54539,16 +54545,16 @@
         <v>50</v>
       </c>
       <c r="L392" s="6">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="M392" s="7">
-        <v>222496.32</v>
+        <v>221843.84</v>
       </c>
       <c r="N392" s="6">
         <v>1</v>
       </c>
       <c r="O392" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P392" s="8">
         <v>326.24</v>
@@ -54649,7 +54655,7 @@
         <v>411</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E393" s="3" t="s">
         <v>46</v>
@@ -54658,7 +54664,7 @@
         <v>46309</v>
       </c>
       <c r="G393" s="5">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H393" s="3" t="s">
         <v>47</v>
@@ -54673,16 +54679,16 @@
         <v>50</v>
       </c>
       <c r="L393" s="6">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="M393" s="7">
-        <v>222822.56</v>
+        <v>222170.08</v>
       </c>
       <c r="N393" s="6">
         <v>1</v>
       </c>
       <c r="O393" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P393" s="8">
         <v>326.24</v>
@@ -54783,7 +54789,7 @@
         <v>411</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E394" s="3" t="s">
         <v>46</v>
@@ -54792,7 +54798,7 @@
         <v>46309</v>
       </c>
       <c r="G394" s="5">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H394" s="3" t="s">
         <v>47</v>
@@ -54807,16 +54813,16 @@
         <v>50</v>
       </c>
       <c r="L394" s="6">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="M394" s="7">
-        <v>223148.81</v>
+        <v>222496.32</v>
       </c>
       <c r="N394" s="6">
         <v>1</v>
       </c>
       <c r="O394" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P394" s="8">
         <v>326.24</v>
@@ -54917,7 +54923,7 @@
         <v>411</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E395" s="3" t="s">
         <v>46</v>
@@ -54926,7 +54932,7 @@
         <v>46309</v>
       </c>
       <c r="G395" s="5">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H395" s="3" t="s">
         <v>47</v>
@@ -54941,16 +54947,16 @@
         <v>50</v>
       </c>
       <c r="L395" s="6">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="M395" s="7">
-        <v>223475.05</v>
+        <v>222822.56</v>
       </c>
       <c r="N395" s="6">
         <v>1</v>
       </c>
       <c r="O395" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P395" s="8">
         <v>326.24</v>
@@ -55051,7 +55057,7 @@
         <v>411</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E396" s="3" t="s">
         <v>46</v>
@@ -55060,7 +55066,7 @@
         <v>46309</v>
       </c>
       <c r="G396" s="5">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H396" s="3" t="s">
         <v>47</v>
@@ -55075,16 +55081,16 @@
         <v>50</v>
       </c>
       <c r="L396" s="6">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="M396" s="7">
-        <v>223801.29</v>
+        <v>223148.81</v>
       </c>
       <c r="N396" s="6">
         <v>1</v>
       </c>
       <c r="O396" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P396" s="8">
         <v>326.24</v>
@@ -55185,7 +55191,7 @@
         <v>411</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E397" s="3" t="s">
         <v>46</v>
@@ -55194,7 +55200,7 @@
         <v>46309</v>
       </c>
       <c r="G397" s="5">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H397" s="3" t="s">
         <v>47</v>
@@ -55209,16 +55215,16 @@
         <v>50</v>
       </c>
       <c r="L397" s="6">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="M397" s="7">
-        <v>224127.53</v>
+        <v>223475.05</v>
       </c>
       <c r="N397" s="6">
         <v>1</v>
       </c>
       <c r="O397" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P397" s="8">
         <v>326.24</v>
@@ -55319,7 +55325,7 @@
         <v>411</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E398" s="3" t="s">
         <v>46</v>
@@ -55328,7 +55334,7 @@
         <v>46309</v>
       </c>
       <c r="G398" s="5">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H398" s="3" t="s">
         <v>47</v>
@@ -55343,16 +55349,16 @@
         <v>50</v>
       </c>
       <c r="L398" s="6">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="M398" s="7">
-        <v>224453.77</v>
+        <v>223801.29</v>
       </c>
       <c r="N398" s="6">
         <v>1</v>
       </c>
       <c r="O398" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P398" s="8">
         <v>326.24</v>
@@ -55453,7 +55459,7 @@
         <v>411</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E399" s="3" t="s">
         <v>46</v>
@@ -55462,7 +55468,7 @@
         <v>46309</v>
       </c>
       <c r="G399" s="5">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H399" s="3" t="s">
         <v>47</v>
@@ -55477,16 +55483,16 @@
         <v>50</v>
       </c>
       <c r="L399" s="6">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="M399" s="7">
-        <v>224780.01</v>
+        <v>224127.53</v>
       </c>
       <c r="N399" s="6">
         <v>1</v>
       </c>
       <c r="O399" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P399" s="8">
         <v>326.24</v>
@@ -55587,7 +55593,7 @@
         <v>411</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E400" s="3" t="s">
         <v>46</v>
@@ -55596,7 +55602,7 @@
         <v>46309</v>
       </c>
       <c r="G400" s="5">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H400" s="3" t="s">
         <v>47</v>
@@ -55611,16 +55617,16 @@
         <v>50</v>
       </c>
       <c r="L400" s="6">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="M400" s="7">
-        <v>225106.25</v>
+        <v>224453.77</v>
       </c>
       <c r="N400" s="6">
         <v>1</v>
       </c>
       <c r="O400" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P400" s="8">
         <v>326.24</v>
@@ -55721,7 +55727,7 @@
         <v>411</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E401" s="3" t="s">
         <v>46</v>
@@ -55730,7 +55736,7 @@
         <v>46309</v>
       </c>
       <c r="G401" s="5">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H401" s="3" t="s">
         <v>47</v>
@@ -55745,16 +55751,16 @@
         <v>50</v>
       </c>
       <c r="L401" s="6">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="M401" s="7">
-        <v>225432.49</v>
+        <v>224780.01</v>
       </c>
       <c r="N401" s="6">
         <v>1</v>
       </c>
       <c r="O401" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P401" s="8">
         <v>326.24</v>
@@ -55855,7 +55861,7 @@
         <v>411</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E402" s="3" t="s">
         <v>46</v>
@@ -55864,7 +55870,7 @@
         <v>46309</v>
       </c>
       <c r="G402" s="5">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H402" s="3" t="s">
         <v>47</v>
@@ -55879,16 +55885,16 @@
         <v>50</v>
       </c>
       <c r="L402" s="6">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="M402" s="7">
-        <v>225758.73</v>
+        <v>225106.25</v>
       </c>
       <c r="N402" s="6">
         <v>1</v>
       </c>
       <c r="O402" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P402" s="8">
         <v>326.24</v>
@@ -55989,7 +55995,7 @@
         <v>411</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E403" s="3" t="s">
         <v>46</v>
@@ -55998,7 +56004,7 @@
         <v>46309</v>
       </c>
       <c r="G403" s="5">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H403" s="3" t="s">
         <v>47</v>
@@ -56013,16 +56019,16 @@
         <v>50</v>
       </c>
       <c r="L403" s="6">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="M403" s="7">
-        <v>226084.97</v>
+        <v>225432.49</v>
       </c>
       <c r="N403" s="6">
         <v>1</v>
       </c>
       <c r="O403" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P403" s="8">
         <v>326.24</v>
@@ -56123,7 +56129,7 @@
         <v>411</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E404" s="3" t="s">
         <v>46</v>
@@ -56132,7 +56138,7 @@
         <v>46309</v>
       </c>
       <c r="G404" s="5">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H404" s="3" t="s">
         <v>47</v>
@@ -56147,16 +56153,16 @@
         <v>50</v>
       </c>
       <c r="L404" s="6">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="M404" s="7">
-        <v>226411.21</v>
+        <v>225758.73</v>
       </c>
       <c r="N404" s="6">
         <v>1</v>
       </c>
       <c r="O404" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P404" s="8">
         <v>326.24</v>
@@ -56257,7 +56263,7 @@
         <v>411</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E405" s="3" t="s">
         <v>46</v>
@@ -56266,7 +56272,7 @@
         <v>46309</v>
       </c>
       <c r="G405" s="5">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H405" s="3" t="s">
         <v>47</v>
@@ -56281,16 +56287,16 @@
         <v>50</v>
       </c>
       <c r="L405" s="6">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="M405" s="7">
-        <v>226737.46</v>
+        <v>226084.97</v>
       </c>
       <c r="N405" s="6">
         <v>1</v>
       </c>
       <c r="O405" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P405" s="8">
         <v>326.24</v>
@@ -56391,7 +56397,7 @@
         <v>411</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E406" s="3" t="s">
         <v>46</v>
@@ -56400,7 +56406,7 @@
         <v>46309</v>
       </c>
       <c r="G406" s="5">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H406" s="3" t="s">
         <v>47</v>
@@ -56415,16 +56421,16 @@
         <v>50</v>
       </c>
       <c r="L406" s="6">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="M406" s="7">
-        <v>227063.7</v>
+        <v>226411.21</v>
       </c>
       <c r="N406" s="6">
         <v>1</v>
       </c>
       <c r="O406" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P406" s="8">
         <v>326.24</v>
@@ -56525,7 +56531,7 @@
         <v>411</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E407" s="3" t="s">
         <v>46</v>
@@ -56534,7 +56540,7 @@
         <v>46309</v>
       </c>
       <c r="G407" s="5">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H407" s="3" t="s">
         <v>47</v>
@@ -56549,16 +56555,16 @@
         <v>50</v>
       </c>
       <c r="L407" s="6">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="M407" s="7">
-        <v>227389.94</v>
+        <v>226737.46</v>
       </c>
       <c r="N407" s="6">
         <v>1</v>
       </c>
       <c r="O407" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P407" s="8">
         <v>326.24</v>
@@ -56659,7 +56665,7 @@
         <v>411</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E408" s="3" t="s">
         <v>46</v>
@@ -56668,7 +56674,7 @@
         <v>46309</v>
       </c>
       <c r="G408" s="5">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H408" s="3" t="s">
         <v>47</v>
@@ -56683,16 +56689,16 @@
         <v>50</v>
       </c>
       <c r="L408" s="6">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="M408" s="7">
-        <v>227716.18</v>
+        <v>227063.7</v>
       </c>
       <c r="N408" s="6">
         <v>1</v>
       </c>
       <c r="O408" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P408" s="8">
         <v>326.24</v>
@@ -56793,7 +56799,7 @@
         <v>411</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E409" s="3" t="s">
         <v>46</v>
@@ -56802,7 +56808,7 @@
         <v>46309</v>
       </c>
       <c r="G409" s="5">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H409" s="3" t="s">
         <v>47</v>
@@ -56817,16 +56823,16 @@
         <v>50</v>
       </c>
       <c r="L409" s="6">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="M409" s="7">
-        <v>228042.42</v>
+        <v>227389.94</v>
       </c>
       <c r="N409" s="6">
         <v>1</v>
       </c>
       <c r="O409" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P409" s="8">
         <v>326.24</v>
@@ -56927,7 +56933,7 @@
         <v>411</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E410" s="3" t="s">
         <v>46</v>
@@ -56936,7 +56942,7 @@
         <v>46309</v>
       </c>
       <c r="G410" s="5">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H410" s="3" t="s">
         <v>47</v>
@@ -56951,16 +56957,16 @@
         <v>50</v>
       </c>
       <c r="L410" s="6">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="M410" s="7">
-        <v>228368.66</v>
+        <v>227716.18</v>
       </c>
       <c r="N410" s="6">
         <v>1</v>
       </c>
       <c r="O410" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P410" s="8">
         <v>326.24</v>
@@ -57061,7 +57067,7 @@
         <v>411</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E411" s="3" t="s">
         <v>46</v>
@@ -57070,7 +57076,7 @@
         <v>46309</v>
       </c>
       <c r="G411" s="5">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H411" s="3" t="s">
         <v>47</v>
@@ -57085,16 +57091,16 @@
         <v>50</v>
       </c>
       <c r="L411" s="6">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="M411" s="7">
-        <v>228694.9</v>
+        <v>228042.42</v>
       </c>
       <c r="N411" s="6">
         <v>1</v>
       </c>
       <c r="O411" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P411" s="8">
         <v>326.24</v>
@@ -57195,7 +57201,7 @@
         <v>411</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E412" s="3" t="s">
         <v>46</v>
@@ -57204,7 +57210,7 @@
         <v>46309</v>
       </c>
       <c r="G412" s="5">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H412" s="3" t="s">
         <v>47</v>
@@ -57219,16 +57225,16 @@
         <v>50</v>
       </c>
       <c r="L412" s="6">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="M412" s="7">
-        <v>229021.14</v>
+        <v>228368.66</v>
       </c>
       <c r="N412" s="6">
         <v>1</v>
       </c>
       <c r="O412" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P412" s="8">
         <v>326.24</v>
@@ -57329,7 +57335,7 @@
         <v>411</v>
       </c>
       <c r="D413" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E413" s="3" t="s">
         <v>46</v>
@@ -57338,7 +57344,7 @@
         <v>46309</v>
       </c>
       <c r="G413" s="5">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H413" s="3" t="s">
         <v>47</v>
@@ -57353,16 +57359,16 @@
         <v>50</v>
       </c>
       <c r="L413" s="6">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="M413" s="7">
-        <v>229347.38</v>
+        <v>228694.9</v>
       </c>
       <c r="N413" s="6">
         <v>1</v>
       </c>
       <c r="O413" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P413" s="8">
         <v>326.24</v>
@@ -57463,7 +57469,7 @@
         <v>411</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E414" s="3" t="s">
         <v>46</v>
@@ -57472,7 +57478,7 @@
         <v>46309</v>
       </c>
       <c r="G414" s="5">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H414" s="3" t="s">
         <v>47</v>
@@ -57487,16 +57493,16 @@
         <v>50</v>
       </c>
       <c r="L414" s="6">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="M414" s="7">
-        <v>229673.62</v>
+        <v>229021.14</v>
       </c>
       <c r="N414" s="6">
         <v>1</v>
       </c>
       <c r="O414" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P414" s="8">
         <v>326.24</v>
@@ -57597,7 +57603,7 @@
         <v>411</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E415" s="3" t="s">
         <v>46</v>
@@ -57606,7 +57612,7 @@
         <v>46309</v>
       </c>
       <c r="G415" s="5">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H415" s="3" t="s">
         <v>47</v>
@@ -57621,16 +57627,16 @@
         <v>50</v>
       </c>
       <c r="L415" s="6">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="M415" s="7">
-        <v>229999.86</v>
+        <v>229347.38</v>
       </c>
       <c r="N415" s="6">
         <v>1</v>
       </c>
       <c r="O415" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P415" s="8">
         <v>326.24</v>
@@ -57731,7 +57737,7 @@
         <v>411</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E416" s="3" t="s">
         <v>46</v>
@@ -57740,7 +57746,7 @@
         <v>46309</v>
       </c>
       <c r="G416" s="5">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H416" s="3" t="s">
         <v>47</v>
@@ -57755,16 +57761,16 @@
         <v>50</v>
       </c>
       <c r="L416" s="6">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="M416" s="7">
-        <v>230326.11</v>
+        <v>229673.62</v>
       </c>
       <c r="N416" s="6">
         <v>1</v>
       </c>
       <c r="O416" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P416" s="8">
         <v>326.24</v>
@@ -57865,7 +57871,7 @@
         <v>411</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E417" s="3" t="s">
         <v>46</v>
@@ -57874,7 +57880,7 @@
         <v>46309</v>
       </c>
       <c r="G417" s="5">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H417" s="3" t="s">
         <v>47</v>
@@ -57889,16 +57895,16 @@
         <v>50</v>
       </c>
       <c r="L417" s="6">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="M417" s="7">
-        <v>230652.35</v>
+        <v>229999.86</v>
       </c>
       <c r="N417" s="6">
         <v>1</v>
       </c>
       <c r="O417" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P417" s="8">
         <v>326.24</v>
@@ -57999,7 +58005,7 @@
         <v>411</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E418" s="3" t="s">
         <v>46</v>
@@ -58008,7 +58014,7 @@
         <v>46309</v>
       </c>
       <c r="G418" s="5">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H418" s="3" t="s">
         <v>47</v>
@@ -58023,16 +58029,16 @@
         <v>50</v>
       </c>
       <c r="L418" s="6">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="M418" s="7">
-        <v>230978.59</v>
+        <v>230326.11</v>
       </c>
       <c r="N418" s="6">
         <v>1</v>
       </c>
       <c r="O418" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P418" s="8">
         <v>326.24</v>
@@ -58133,7 +58139,7 @@
         <v>411</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E419" s="3" t="s">
         <v>46</v>
@@ -58142,7 +58148,7 @@
         <v>46309</v>
       </c>
       <c r="G419" s="5">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H419" s="3" t="s">
         <v>47</v>
@@ -58157,16 +58163,16 @@
         <v>50</v>
       </c>
       <c r="L419" s="6">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="M419" s="7">
-        <v>231304.83</v>
+        <v>230652.35</v>
       </c>
       <c r="N419" s="6">
         <v>1</v>
       </c>
       <c r="O419" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P419" s="8">
         <v>326.24</v>
@@ -58193,7 +58199,7 @@
         <v>46309</v>
       </c>
       <c r="X419" s="12">
-        <v>0.48263889999999998</v>
+        <v>0.4819444</v>
       </c>
       <c r="Y419" s="10">
         <v>0</v>
@@ -58267,7 +58273,7 @@
         <v>411</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E420" s="3" t="s">
         <v>46</v>
@@ -58276,7 +58282,7 @@
         <v>46309</v>
       </c>
       <c r="G420" s="5">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H420" s="3" t="s">
         <v>47</v>
@@ -58291,16 +58297,16 @@
         <v>50</v>
       </c>
       <c r="L420" s="6">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="M420" s="7">
-        <v>231631.07</v>
+        <v>230978.59</v>
       </c>
       <c r="N420" s="6">
         <v>1</v>
       </c>
       <c r="O420" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P420" s="8">
         <v>326.24</v>
@@ -58327,7 +58333,7 @@
         <v>46309</v>
       </c>
       <c r="X420" s="12">
-        <v>0.48263889999999998</v>
+        <v>0.4819444</v>
       </c>
       <c r="Y420" s="10">
         <v>0</v>
@@ -58401,7 +58407,7 @@
         <v>411</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E421" s="3" t="s">
         <v>46</v>
@@ -58410,7 +58416,7 @@
         <v>46309</v>
       </c>
       <c r="G421" s="5">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H421" s="3" t="s">
         <v>47</v>
@@ -58425,16 +58431,16 @@
         <v>50</v>
       </c>
       <c r="L421" s="6">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="M421" s="7">
-        <v>231957.31</v>
+        <v>231304.83</v>
       </c>
       <c r="N421" s="6">
         <v>1</v>
       </c>
       <c r="O421" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P421" s="8">
         <v>326.24</v>
@@ -58535,7 +58541,7 @@
         <v>411</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E422" s="3" t="s">
         <v>46</v>
@@ -58544,7 +58550,7 @@
         <v>46309</v>
       </c>
       <c r="G422" s="5">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H422" s="3" t="s">
         <v>47</v>
@@ -58559,16 +58565,16 @@
         <v>50</v>
       </c>
       <c r="L422" s="6">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="M422" s="7">
-        <v>232283.55</v>
+        <v>231631.07</v>
       </c>
       <c r="N422" s="6">
         <v>1</v>
       </c>
       <c r="O422" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P422" s="8">
         <v>326.24</v>
@@ -58669,7 +58675,7 @@
         <v>411</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E423" s="3" t="s">
         <v>46</v>
@@ -58678,7 +58684,7 @@
         <v>46309</v>
       </c>
       <c r="G423" s="5">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H423" s="3" t="s">
         <v>47</v>
@@ -58693,16 +58699,16 @@
         <v>50</v>
       </c>
       <c r="L423" s="6">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="M423" s="7">
-        <v>232609.79</v>
+        <v>231957.31</v>
       </c>
       <c r="N423" s="6">
         <v>1</v>
       </c>
       <c r="O423" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P423" s="8">
         <v>326.24</v>
@@ -58803,7 +58809,7 @@
         <v>411</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E424" s="3" t="s">
         <v>46</v>
@@ -58812,7 +58818,7 @@
         <v>46309</v>
       </c>
       <c r="G424" s="5">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H424" s="3" t="s">
         <v>47</v>
@@ -58827,16 +58833,16 @@
         <v>50</v>
       </c>
       <c r="L424" s="6">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="M424" s="7">
-        <v>232936.03</v>
+        <v>232283.55</v>
       </c>
       <c r="N424" s="6">
         <v>1</v>
       </c>
       <c r="O424" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P424" s="8">
         <v>326.24</v>
@@ -58937,7 +58943,7 @@
         <v>411</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E425" s="3" t="s">
         <v>46</v>
@@ -58946,7 +58952,7 @@
         <v>46309</v>
       </c>
       <c r="G425" s="5">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H425" s="3" t="s">
         <v>47</v>
@@ -58961,16 +58967,16 @@
         <v>50</v>
       </c>
       <c r="L425" s="6">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="M425" s="7">
-        <v>233262.27</v>
+        <v>232609.79</v>
       </c>
       <c r="N425" s="6">
         <v>1</v>
       </c>
       <c r="O425" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P425" s="8">
         <v>326.24</v>
@@ -59071,7 +59077,7 @@
         <v>411</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E426" s="3" t="s">
         <v>46</v>
@@ -59080,7 +59086,7 @@
         <v>46309</v>
       </c>
       <c r="G426" s="5">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H426" s="3" t="s">
         <v>47</v>
@@ -59095,16 +59101,16 @@
         <v>50</v>
       </c>
       <c r="L426" s="6">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="M426" s="7">
-        <v>233588.52</v>
+        <v>232936.03</v>
       </c>
       <c r="N426" s="6">
         <v>1</v>
       </c>
       <c r="O426" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P426" s="8">
         <v>326.24</v>
@@ -59205,7 +59211,7 @@
         <v>411</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E427" s="3" t="s">
         <v>46</v>
@@ -59214,7 +59220,7 @@
         <v>46309</v>
       </c>
       <c r="G427" s="5">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H427" s="3" t="s">
         <v>47</v>
@@ -59229,16 +59235,16 @@
         <v>50</v>
       </c>
       <c r="L427" s="6">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="M427" s="7">
-        <v>233914.76</v>
+        <v>233262.27</v>
       </c>
       <c r="N427" s="6">
         <v>1</v>
       </c>
       <c r="O427" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P427" s="8">
         <v>326.24</v>
@@ -59339,7 +59345,7 @@
         <v>411</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E428" s="3" t="s">
         <v>46</v>
@@ -59348,7 +59354,7 @@
         <v>46309</v>
       </c>
       <c r="G428" s="5">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H428" s="3" t="s">
         <v>47</v>
@@ -59363,16 +59369,16 @@
         <v>50</v>
       </c>
       <c r="L428" s="6">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="M428" s="7">
-        <v>234241</v>
+        <v>233588.52</v>
       </c>
       <c r="N428" s="6">
         <v>1</v>
       </c>
       <c r="O428" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P428" s="8">
         <v>326.24</v>
@@ -59473,7 +59479,7 @@
         <v>411</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E429" s="3" t="s">
         <v>46</v>
@@ -59482,7 +59488,7 @@
         <v>46309</v>
       </c>
       <c r="G429" s="5">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H429" s="3" t="s">
         <v>47</v>
@@ -59497,16 +59503,16 @@
         <v>50</v>
       </c>
       <c r="L429" s="6">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="M429" s="7">
-        <v>234567.24</v>
+        <v>233914.76</v>
       </c>
       <c r="N429" s="6">
         <v>1</v>
       </c>
       <c r="O429" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P429" s="8">
         <v>326.24</v>
@@ -59607,7 +59613,7 @@
         <v>411</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E430" s="3" t="s">
         <v>46</v>
@@ -59616,7 +59622,7 @@
         <v>46309</v>
       </c>
       <c r="G430" s="5">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H430" s="3" t="s">
         <v>47</v>
@@ -59631,16 +59637,16 @@
         <v>50</v>
       </c>
       <c r="L430" s="6">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="M430" s="7">
-        <v>234893.48</v>
+        <v>234241</v>
       </c>
       <c r="N430" s="6">
         <v>1</v>
       </c>
       <c r="O430" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P430" s="8">
         <v>326.24</v>
@@ -59741,7 +59747,7 @@
         <v>411</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E431" s="3" t="s">
         <v>46</v>
@@ -59750,7 +59756,7 @@
         <v>46309</v>
       </c>
       <c r="G431" s="5">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H431" s="3" t="s">
         <v>47</v>
@@ -59765,16 +59771,16 @@
         <v>50</v>
       </c>
       <c r="L431" s="6">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="M431" s="7">
-        <v>235219.72</v>
+        <v>234567.24</v>
       </c>
       <c r="N431" s="6">
         <v>1</v>
       </c>
       <c r="O431" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P431" s="8">
         <v>326.24</v>
@@ -59875,7 +59881,7 @@
         <v>411</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E432" s="3" t="s">
         <v>46</v>
@@ -59884,7 +59890,7 @@
         <v>46309</v>
       </c>
       <c r="G432" s="5">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="H432" s="3" t="s">
         <v>47</v>
@@ -59899,16 +59905,16 @@
         <v>50</v>
       </c>
       <c r="L432" s="6">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="M432" s="7">
-        <v>235545.96</v>
+        <v>234893.48</v>
       </c>
       <c r="N432" s="6">
         <v>1</v>
       </c>
       <c r="O432" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P432" s="8">
         <v>326.24</v>
@@ -60009,7 +60015,7 @@
         <v>411</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E433" s="3" t="s">
         <v>46</v>
@@ -60018,7 +60024,7 @@
         <v>46309</v>
       </c>
       <c r="G433" s="5">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H433" s="3" t="s">
         <v>47</v>
@@ -60033,16 +60039,16 @@
         <v>50</v>
       </c>
       <c r="L433" s="6">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M433" s="7">
-        <v>235872.2</v>
+        <v>235219.72</v>
       </c>
       <c r="N433" s="6">
         <v>1</v>
       </c>
       <c r="O433" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P433" s="8">
         <v>326.24</v>
@@ -60143,7 +60149,7 @@
         <v>411</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E434" s="3" t="s">
         <v>46</v>
@@ -60152,7 +60158,7 @@
         <v>46309</v>
       </c>
       <c r="G434" s="5">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H434" s="3" t="s">
         <v>47</v>
@@ -60167,16 +60173,16 @@
         <v>50</v>
       </c>
       <c r="L434" s="6">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="M434" s="7">
-        <v>236198.44</v>
+        <v>235545.96</v>
       </c>
       <c r="N434" s="6">
         <v>1</v>
       </c>
       <c r="O434" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P434" s="8">
         <v>326.24</v>
@@ -60277,7 +60283,7 @@
         <v>411</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E435" s="3" t="s">
         <v>46</v>
@@ -60286,7 +60292,7 @@
         <v>46309</v>
       </c>
       <c r="G435" s="5">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H435" s="3" t="s">
         <v>47</v>
@@ -60301,16 +60307,16 @@
         <v>50</v>
       </c>
       <c r="L435" s="6">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="M435" s="7">
-        <v>236524.68</v>
+        <v>235872.2</v>
       </c>
       <c r="N435" s="6">
         <v>1</v>
       </c>
       <c r="O435" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P435" s="8">
         <v>326.24</v>
@@ -60411,7 +60417,7 @@
         <v>411</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E436" s="3" t="s">
         <v>46</v>
@@ -60420,7 +60426,7 @@
         <v>46309</v>
       </c>
       <c r="G436" s="5">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H436" s="3" t="s">
         <v>47</v>
@@ -60435,16 +60441,16 @@
         <v>50</v>
       </c>
       <c r="L436" s="6">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="M436" s="7">
-        <v>236850.92</v>
+        <v>236198.44</v>
       </c>
       <c r="N436" s="6">
         <v>1</v>
       </c>
       <c r="O436" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P436" s="8">
         <v>326.24</v>
@@ -60545,7 +60551,7 @@
         <v>411</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E437" s="3" t="s">
         <v>46</v>
@@ -60554,7 +60560,7 @@
         <v>46309</v>
       </c>
       <c r="G437" s="5">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H437" s="3" t="s">
         <v>47</v>
@@ -60569,16 +60575,16 @@
         <v>50</v>
       </c>
       <c r="L437" s="6">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="M437" s="7">
-        <v>237177.17</v>
+        <v>236524.68</v>
       </c>
       <c r="N437" s="6">
         <v>1</v>
       </c>
       <c r="O437" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P437" s="8">
         <v>326.24</v>
@@ -60679,7 +60685,7 @@
         <v>411</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E438" s="3" t="s">
         <v>46</v>
@@ -60688,7 +60694,7 @@
         <v>46309</v>
       </c>
       <c r="G438" s="5">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H438" s="3" t="s">
         <v>47</v>
@@ -60703,16 +60709,16 @@
         <v>50</v>
       </c>
       <c r="L438" s="6">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="M438" s="7">
-        <v>237503.41</v>
+        <v>236850.92</v>
       </c>
       <c r="N438" s="6">
         <v>1</v>
       </c>
       <c r="O438" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P438" s="8">
         <v>326.24</v>
@@ -60813,7 +60819,7 @@
         <v>411</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E439" s="3" t="s">
         <v>46</v>
@@ -60822,7 +60828,7 @@
         <v>46309</v>
       </c>
       <c r="G439" s="5">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H439" s="3" t="s">
         <v>47</v>
@@ -60837,16 +60843,16 @@
         <v>50</v>
       </c>
       <c r="L439" s="6">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="M439" s="7">
-        <v>237829.65</v>
+        <v>237177.17</v>
       </c>
       <c r="N439" s="6">
         <v>1</v>
       </c>
       <c r="O439" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P439" s="8">
         <v>326.24</v>
@@ -60947,7 +60953,7 @@
         <v>411</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E440" s="3" t="s">
         <v>46</v>
@@ -60956,7 +60962,7 @@
         <v>46309</v>
       </c>
       <c r="G440" s="5">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H440" s="3" t="s">
         <v>47</v>
@@ -60971,16 +60977,16 @@
         <v>50</v>
       </c>
       <c r="L440" s="6">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="M440" s="7">
-        <v>238155.89</v>
+        <v>237503.41</v>
       </c>
       <c r="N440" s="6">
         <v>1</v>
       </c>
       <c r="O440" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P440" s="8">
         <v>326.24</v>
@@ -61081,7 +61087,7 @@
         <v>411</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E441" s="3" t="s">
         <v>46</v>
@@ -61090,7 +61096,7 @@
         <v>46309</v>
       </c>
       <c r="G441" s="5">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H441" s="3" t="s">
         <v>47</v>
@@ -61105,16 +61111,16 @@
         <v>50</v>
       </c>
       <c r="L441" s="6">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="M441" s="7">
-        <v>238482.13</v>
+        <v>237829.65</v>
       </c>
       <c r="N441" s="6">
         <v>1</v>
       </c>
       <c r="O441" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P441" s="8">
         <v>326.24</v>
@@ -61215,7 +61221,7 @@
         <v>411</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E442" s="3" t="s">
         <v>46</v>
@@ -61224,7 +61230,7 @@
         <v>46309</v>
       </c>
       <c r="G442" s="5">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H442" s="3" t="s">
         <v>47</v>
@@ -61239,16 +61245,16 @@
         <v>50</v>
       </c>
       <c r="L442" s="6">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="M442" s="7">
-        <v>238808.37</v>
+        <v>238155.89</v>
       </c>
       <c r="N442" s="6">
         <v>1</v>
       </c>
       <c r="O442" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P442" s="8">
         <v>326.24</v>
@@ -61349,7 +61355,7 @@
         <v>411</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E443" s="3" t="s">
         <v>46</v>
@@ -61358,7 +61364,7 @@
         <v>46309</v>
       </c>
       <c r="G443" s="5">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H443" s="3" t="s">
         <v>47</v>
@@ -61373,16 +61379,16 @@
         <v>50</v>
       </c>
       <c r="L443" s="6">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="M443" s="7">
-        <v>239134.61</v>
+        <v>238482.13</v>
       </c>
       <c r="N443" s="6">
         <v>1</v>
       </c>
       <c r="O443" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P443" s="8">
         <v>326.24</v>
@@ -61483,7 +61489,7 @@
         <v>411</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E444" s="3" t="s">
         <v>46</v>
@@ -61492,7 +61498,7 @@
         <v>46309</v>
       </c>
       <c r="G444" s="5">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="H444" s="3" t="s">
         <v>47</v>
@@ -61507,16 +61513,16 @@
         <v>50</v>
       </c>
       <c r="L444" s="6">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="M444" s="7">
-        <v>239460.85</v>
+        <v>238808.37</v>
       </c>
       <c r="N444" s="6">
         <v>1</v>
       </c>
       <c r="O444" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P444" s="8">
         <v>326.24</v>
@@ -61617,7 +61623,7 @@
         <v>411</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E445" s="3" t="s">
         <v>46</v>
@@ -61626,7 +61632,7 @@
         <v>46309</v>
       </c>
       <c r="G445" s="5">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H445" s="3" t="s">
         <v>47</v>
@@ -61641,16 +61647,16 @@
         <v>50</v>
       </c>
       <c r="L445" s="6">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="M445" s="7">
-        <v>239787.09</v>
+        <v>239134.61</v>
       </c>
       <c r="N445" s="6">
         <v>1</v>
       </c>
       <c r="O445" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P445" s="8">
         <v>326.24</v>
@@ -61738,6 +61744,274 @@
       </c>
       <c r="AR445" s="3" t="s">
         <v>503</v>
+      </c>
+    </row>
+    <row r="446" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A446" s="1">
+        <v>1</v>
+      </c>
+      <c r="B446" s="2">
+        <v>2</v>
+      </c>
+      <c r="C446" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D446" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="E446" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F446" s="4">
+        <v>46309</v>
+      </c>
+      <c r="G446" s="5">
+        <v>364</v>
+      </c>
+      <c r="H446" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I446" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J446" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K446" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L446" s="6">
+        <v>734</v>
+      </c>
+      <c r="M446" s="7">
+        <v>239460.85</v>
+      </c>
+      <c r="N446" s="6">
+        <v>1</v>
+      </c>
+      <c r="O446" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="P446" s="8">
+        <v>326.24</v>
+      </c>
+      <c r="Q446" s="6">
+        <v>0</v>
+      </c>
+      <c r="R446" s="7">
+        <v>0</v>
+      </c>
+      <c r="S446" s="9">
+        <v>0</v>
+      </c>
+      <c r="T446" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U446" s="10">
+        <v>68241</v>
+      </c>
+      <c r="V446" s="11">
+        <v>11</v>
+      </c>
+      <c r="W446" s="4">
+        <v>46309</v>
+      </c>
+      <c r="X446" s="12">
+        <v>0.48263889999999998</v>
+      </c>
+      <c r="Y446" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z446" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA446" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB446" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC446" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD446" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE446" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF446" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG446" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH446" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI446" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ446" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK446" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL446" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM446" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN446" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO446" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP446" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ446" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR446" s="3" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="447" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A447" s="1">
+        <v>1</v>
+      </c>
+      <c r="B447" s="2">
+        <v>2</v>
+      </c>
+      <c r="C447" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D447" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="E447" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F447" s="4">
+        <v>46309</v>
+      </c>
+      <c r="G447" s="5">
+        <v>365</v>
+      </c>
+      <c r="H447" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I447" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J447" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K447" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L447" s="6">
+        <v>735</v>
+      </c>
+      <c r="M447" s="7">
+        <v>239787.09</v>
+      </c>
+      <c r="N447" s="6">
+        <v>1</v>
+      </c>
+      <c r="O447" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="P447" s="8">
+        <v>326.24</v>
+      </c>
+      <c r="Q447" s="6">
+        <v>0</v>
+      </c>
+      <c r="R447" s="7">
+        <v>0</v>
+      </c>
+      <c r="S447" s="9">
+        <v>0</v>
+      </c>
+      <c r="T447" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U447" s="10">
+        <v>68241</v>
+      </c>
+      <c r="V447" s="11">
+        <v>11</v>
+      </c>
+      <c r="W447" s="4">
+        <v>46309</v>
+      </c>
+      <c r="X447" s="12">
+        <v>0.48263889999999998</v>
+      </c>
+      <c r="Y447" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z447" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA447" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB447" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC447" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD447" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE447" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF447" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG447" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH447" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI447" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ447" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK447" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL447" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM447" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN447" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO447" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP447" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ447" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR447" s="3" t="s">
+        <v>505</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D6A882B-F241-46A0-AECF-52FC6496C1D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDB3656D-40FD-45C7-B998-DA5DF92238CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6326" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6578" uniqueCount="420">
   <si>
     <t>Sel</t>
   </si>
@@ -1239,6 +1239,48 @@
   <si>
     <t>1883500000331</t>
   </si>
+  <si>
+    <t>1883500000332</t>
+  </si>
+  <si>
+    <t>1883500000333</t>
+  </si>
+  <si>
+    <t>1883500000334</t>
+  </si>
+  <si>
+    <t>1883500000335</t>
+  </si>
+  <si>
+    <t>1883500000336</t>
+  </si>
+  <si>
+    <t>1883500000337</t>
+  </si>
+  <si>
+    <t>1883500000338</t>
+  </si>
+  <si>
+    <t>1883500000339</t>
+  </si>
+  <si>
+    <t>1883500000340</t>
+  </si>
+  <si>
+    <t>1883500000341</t>
+  </si>
+  <si>
+    <t>1883500000342</t>
+  </si>
+  <si>
+    <t>1883500000343</t>
+  </si>
+  <si>
+    <t>1883500000344</t>
+  </si>
+  <si>
+    <t>1883500000345</t>
+  </si>
 </sst>
 </file>
 
@@ -1813,7 +1855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR350"/>
+  <dimension ref="A1:AR364"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -48714,6 +48756,1882 @@
       </c>
       <c r="AR350" s="3" t="s">
         <v>405</v>
+      </c>
+    </row>
+    <row r="351" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A351" s="1">
+        <v>1</v>
+      </c>
+      <c r="B351" s="2">
+        <v>2</v>
+      </c>
+      <c r="C351" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D351" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E351" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F351" s="4">
+        <v>46310</v>
+      </c>
+      <c r="G351" s="5">
+        <v>69</v>
+      </c>
+      <c r="H351" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I351" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J351" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K351" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L351" s="6">
+        <v>109</v>
+      </c>
+      <c r="M351" s="7">
+        <v>19334.419999999998</v>
+      </c>
+      <c r="N351" s="6">
+        <v>1</v>
+      </c>
+      <c r="O351" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="P351" s="8">
+        <v>177.38</v>
+      </c>
+      <c r="Q351" s="6">
+        <v>0</v>
+      </c>
+      <c r="R351" s="7">
+        <v>0</v>
+      </c>
+      <c r="S351" s="9">
+        <v>0</v>
+      </c>
+      <c r="T351" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U351" s="10">
+        <v>68297</v>
+      </c>
+      <c r="V351" s="11">
+        <v>11</v>
+      </c>
+      <c r="W351" s="4">
+        <v>46310</v>
+      </c>
+      <c r="X351" s="12">
+        <v>0.45624999999999999</v>
+      </c>
+      <c r="Y351" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z351" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA351" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB351" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC351" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD351" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE351" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF351" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG351" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH351" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI351" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ351" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK351" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL351" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM351" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN351" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO351" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP351" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ351" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR351" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="352" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A352" s="1">
+        <v>1</v>
+      </c>
+      <c r="B352" s="2">
+        <v>2</v>
+      </c>
+      <c r="C352" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D352" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E352" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F352" s="4">
+        <v>46310</v>
+      </c>
+      <c r="G352" s="5">
+        <v>70</v>
+      </c>
+      <c r="H352" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I352" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J352" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K352" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L352" s="6">
+        <v>110</v>
+      </c>
+      <c r="M352" s="7">
+        <v>19511.8</v>
+      </c>
+      <c r="N352" s="6">
+        <v>1</v>
+      </c>
+      <c r="O352" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="P352" s="8">
+        <v>177.38</v>
+      </c>
+      <c r="Q352" s="6">
+        <v>0</v>
+      </c>
+      <c r="R352" s="7">
+        <v>0</v>
+      </c>
+      <c r="S352" s="9">
+        <v>0</v>
+      </c>
+      <c r="T352" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U352" s="10">
+        <v>68297</v>
+      </c>
+      <c r="V352" s="11">
+        <v>11</v>
+      </c>
+      <c r="W352" s="4">
+        <v>46310</v>
+      </c>
+      <c r="X352" s="12">
+        <v>0.45624999999999999</v>
+      </c>
+      <c r="Y352" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z352" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA352" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB352" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC352" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD352" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE352" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF352" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG352" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH352" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI352" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ352" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK352" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL352" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM352" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN352" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO352" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP352" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ352" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR352" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="353" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A353" s="1">
+        <v>1</v>
+      </c>
+      <c r="B353" s="2">
+        <v>2</v>
+      </c>
+      <c r="C353" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D353" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E353" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F353" s="4">
+        <v>46310</v>
+      </c>
+      <c r="G353" s="5">
+        <v>71</v>
+      </c>
+      <c r="H353" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I353" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J353" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K353" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L353" s="6">
+        <v>111</v>
+      </c>
+      <c r="M353" s="7">
+        <v>19689.18</v>
+      </c>
+      <c r="N353" s="6">
+        <v>1</v>
+      </c>
+      <c r="O353" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="P353" s="8">
+        <v>177.38</v>
+      </c>
+      <c r="Q353" s="6">
+        <v>0</v>
+      </c>
+      <c r="R353" s="7">
+        <v>0</v>
+      </c>
+      <c r="S353" s="9">
+        <v>0</v>
+      </c>
+      <c r="T353" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U353" s="10">
+        <v>68297</v>
+      </c>
+      <c r="V353" s="11">
+        <v>11</v>
+      </c>
+      <c r="W353" s="4">
+        <v>46310</v>
+      </c>
+      <c r="X353" s="12">
+        <v>0.45624999999999999</v>
+      </c>
+      <c r="Y353" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z353" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA353" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB353" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC353" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD353" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE353" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF353" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG353" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH353" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI353" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ353" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK353" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL353" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM353" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN353" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO353" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP353" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ353" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR353" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="354" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A354" s="1">
+        <v>1</v>
+      </c>
+      <c r="B354" s="2">
+        <v>2</v>
+      </c>
+      <c r="C354" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D354" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E354" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F354" s="4">
+        <v>46310</v>
+      </c>
+      <c r="G354" s="5">
+        <v>72</v>
+      </c>
+      <c r="H354" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I354" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J354" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K354" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L354" s="6">
+        <v>112</v>
+      </c>
+      <c r="M354" s="7">
+        <v>19866.560000000001</v>
+      </c>
+      <c r="N354" s="6">
+        <v>1</v>
+      </c>
+      <c r="O354" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="P354" s="8">
+        <v>177.38</v>
+      </c>
+      <c r="Q354" s="6">
+        <v>0</v>
+      </c>
+      <c r="R354" s="7">
+        <v>0</v>
+      </c>
+      <c r="S354" s="9">
+        <v>0</v>
+      </c>
+      <c r="T354" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U354" s="10">
+        <v>68297</v>
+      </c>
+      <c r="V354" s="11">
+        <v>11</v>
+      </c>
+      <c r="W354" s="4">
+        <v>46310</v>
+      </c>
+      <c r="X354" s="12">
+        <v>0.46388889999999999</v>
+      </c>
+      <c r="Y354" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z354" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA354" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB354" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC354" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD354" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE354" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF354" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG354" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH354" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI354" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ354" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK354" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL354" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM354" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN354" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO354" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP354" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ354" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR354" s="3" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="355" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A355" s="1">
+        <v>1</v>
+      </c>
+      <c r="B355" s="2">
+        <v>2</v>
+      </c>
+      <c r="C355" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D355" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E355" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F355" s="4">
+        <v>46310</v>
+      </c>
+      <c r="G355" s="5">
+        <v>73</v>
+      </c>
+      <c r="H355" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I355" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J355" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K355" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L355" s="6">
+        <v>113</v>
+      </c>
+      <c r="M355" s="7">
+        <v>20043.939999999999</v>
+      </c>
+      <c r="N355" s="6">
+        <v>1</v>
+      </c>
+      <c r="O355" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="P355" s="8">
+        <v>177.38</v>
+      </c>
+      <c r="Q355" s="6">
+        <v>0</v>
+      </c>
+      <c r="R355" s="7">
+        <v>0</v>
+      </c>
+      <c r="S355" s="9">
+        <v>0</v>
+      </c>
+      <c r="T355" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U355" s="10">
+        <v>68297</v>
+      </c>
+      <c r="V355" s="11">
+        <v>11</v>
+      </c>
+      <c r="W355" s="4">
+        <v>46310</v>
+      </c>
+      <c r="X355" s="12">
+        <v>0.46388889999999999</v>
+      </c>
+      <c r="Y355" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z355" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA355" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB355" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC355" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD355" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE355" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF355" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG355" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH355" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI355" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ355" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK355" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL355" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM355" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN355" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO355" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP355" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ355" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR355" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="356" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A356" s="1">
+        <v>1</v>
+      </c>
+      <c r="B356" s="2">
+        <v>2</v>
+      </c>
+      <c r="C356" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D356" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E356" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F356" s="4">
+        <v>46310</v>
+      </c>
+      <c r="G356" s="5">
+        <v>74</v>
+      </c>
+      <c r="H356" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I356" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J356" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K356" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L356" s="6">
+        <v>114</v>
+      </c>
+      <c r="M356" s="7">
+        <v>20221.32</v>
+      </c>
+      <c r="N356" s="6">
+        <v>1</v>
+      </c>
+      <c r="O356" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="P356" s="8">
+        <v>177.38</v>
+      </c>
+      <c r="Q356" s="6">
+        <v>0</v>
+      </c>
+      <c r="R356" s="7">
+        <v>0</v>
+      </c>
+      <c r="S356" s="9">
+        <v>0</v>
+      </c>
+      <c r="T356" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U356" s="10">
+        <v>68297</v>
+      </c>
+      <c r="V356" s="11">
+        <v>11</v>
+      </c>
+      <c r="W356" s="4">
+        <v>46310</v>
+      </c>
+      <c r="X356" s="12">
+        <v>0.46388889999999999</v>
+      </c>
+      <c r="Y356" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z356" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA356" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB356" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC356" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD356" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE356" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF356" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG356" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH356" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI356" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ356" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK356" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL356" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM356" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN356" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO356" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP356" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ356" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR356" s="3" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="357" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A357" s="1">
+        <v>1</v>
+      </c>
+      <c r="B357" s="2">
+        <v>2</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D357" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E357" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F357" s="4">
+        <v>46310</v>
+      </c>
+      <c r="G357" s="5">
+        <v>75</v>
+      </c>
+      <c r="H357" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I357" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J357" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K357" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L357" s="6">
+        <v>115</v>
+      </c>
+      <c r="M357" s="7">
+        <v>20398.7</v>
+      </c>
+      <c r="N357" s="6">
+        <v>1</v>
+      </c>
+      <c r="O357" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="P357" s="8">
+        <v>177.38</v>
+      </c>
+      <c r="Q357" s="6">
+        <v>0</v>
+      </c>
+      <c r="R357" s="7">
+        <v>0</v>
+      </c>
+      <c r="S357" s="9">
+        <v>0</v>
+      </c>
+      <c r="T357" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U357" s="10">
+        <v>68297</v>
+      </c>
+      <c r="V357" s="11">
+        <v>11</v>
+      </c>
+      <c r="W357" s="4">
+        <v>46310</v>
+      </c>
+      <c r="X357" s="12">
+        <v>0.47013890000000003</v>
+      </c>
+      <c r="Y357" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z357" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA357" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB357" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC357" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD357" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE357" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF357" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG357" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH357" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI357" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ357" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK357" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL357" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM357" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN357" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO357" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP357" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ357" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR357" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="358" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A358" s="1">
+        <v>1</v>
+      </c>
+      <c r="B358" s="2">
+        <v>2</v>
+      </c>
+      <c r="C358" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D358" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E358" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F358" s="4">
+        <v>46310</v>
+      </c>
+      <c r="G358" s="5">
+        <v>76</v>
+      </c>
+      <c r="H358" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I358" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J358" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K358" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L358" s="6">
+        <v>116</v>
+      </c>
+      <c r="M358" s="7">
+        <v>20576.080000000002</v>
+      </c>
+      <c r="N358" s="6">
+        <v>1</v>
+      </c>
+      <c r="O358" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="P358" s="8">
+        <v>177.38</v>
+      </c>
+      <c r="Q358" s="6">
+        <v>0</v>
+      </c>
+      <c r="R358" s="7">
+        <v>0</v>
+      </c>
+      <c r="S358" s="9">
+        <v>0</v>
+      </c>
+      <c r="T358" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U358" s="10">
+        <v>68297</v>
+      </c>
+      <c r="V358" s="11">
+        <v>11</v>
+      </c>
+      <c r="W358" s="4">
+        <v>46310</v>
+      </c>
+      <c r="X358" s="12">
+        <v>0.47013890000000003</v>
+      </c>
+      <c r="Y358" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z358" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA358" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB358" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC358" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD358" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE358" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF358" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG358" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH358" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI358" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ358" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK358" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL358" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM358" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN358" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO358" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP358" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ358" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR358" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="359" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A359" s="1">
+        <v>1</v>
+      </c>
+      <c r="B359" s="2">
+        <v>2</v>
+      </c>
+      <c r="C359" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D359" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E359" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F359" s="4">
+        <v>46310</v>
+      </c>
+      <c r="G359" s="5">
+        <v>77</v>
+      </c>
+      <c r="H359" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I359" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J359" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K359" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L359" s="6">
+        <v>117</v>
+      </c>
+      <c r="M359" s="7">
+        <v>20753.46</v>
+      </c>
+      <c r="N359" s="6">
+        <v>1</v>
+      </c>
+      <c r="O359" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="P359" s="8">
+        <v>177.38</v>
+      </c>
+      <c r="Q359" s="6">
+        <v>0</v>
+      </c>
+      <c r="R359" s="7">
+        <v>0</v>
+      </c>
+      <c r="S359" s="9">
+        <v>0</v>
+      </c>
+      <c r="T359" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U359" s="10">
+        <v>68297</v>
+      </c>
+      <c r="V359" s="11">
+        <v>11</v>
+      </c>
+      <c r="W359" s="4">
+        <v>46310</v>
+      </c>
+      <c r="X359" s="12">
+        <v>0.47013890000000003</v>
+      </c>
+      <c r="Y359" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z359" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA359" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB359" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC359" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD359" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE359" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF359" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG359" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH359" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI359" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ359" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK359" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL359" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM359" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN359" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO359" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP359" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ359" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR359" s="3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="360" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A360" s="1">
+        <v>1</v>
+      </c>
+      <c r="B360" s="2">
+        <v>2</v>
+      </c>
+      <c r="C360" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D360" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E360" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F360" s="4">
+        <v>46310</v>
+      </c>
+      <c r="G360" s="5">
+        <v>78</v>
+      </c>
+      <c r="H360" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I360" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J360" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K360" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L360" s="6">
+        <v>118</v>
+      </c>
+      <c r="M360" s="7">
+        <v>20930.84</v>
+      </c>
+      <c r="N360" s="6">
+        <v>1</v>
+      </c>
+      <c r="O360" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="P360" s="8">
+        <v>177.38</v>
+      </c>
+      <c r="Q360" s="6">
+        <v>0</v>
+      </c>
+      <c r="R360" s="7">
+        <v>0</v>
+      </c>
+      <c r="S360" s="9">
+        <v>0</v>
+      </c>
+      <c r="T360" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U360" s="10">
+        <v>68297</v>
+      </c>
+      <c r="V360" s="11">
+        <v>11</v>
+      </c>
+      <c r="W360" s="4">
+        <v>46310</v>
+      </c>
+      <c r="X360" s="12">
+        <v>0.47013890000000003</v>
+      </c>
+      <c r="Y360" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z360" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA360" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB360" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC360" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD360" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE360" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF360" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG360" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH360" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI360" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ360" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK360" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL360" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM360" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN360" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO360" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP360" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ360" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR360" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="361" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A361" s="1">
+        <v>1</v>
+      </c>
+      <c r="B361" s="2">
+        <v>2</v>
+      </c>
+      <c r="C361" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D361" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E361" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F361" s="4">
+        <v>46310</v>
+      </c>
+      <c r="G361" s="5">
+        <v>79</v>
+      </c>
+      <c r="H361" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I361" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J361" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K361" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L361" s="6">
+        <v>119</v>
+      </c>
+      <c r="M361" s="7">
+        <v>21108.22</v>
+      </c>
+      <c r="N361" s="6">
+        <v>1</v>
+      </c>
+      <c r="O361" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="P361" s="8">
+        <v>177.38</v>
+      </c>
+      <c r="Q361" s="6">
+        <v>0</v>
+      </c>
+      <c r="R361" s="7">
+        <v>0</v>
+      </c>
+      <c r="S361" s="9">
+        <v>0</v>
+      </c>
+      <c r="T361" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U361" s="10">
+        <v>68297</v>
+      </c>
+      <c r="V361" s="11">
+        <v>11</v>
+      </c>
+      <c r="W361" s="4">
+        <v>46310</v>
+      </c>
+      <c r="X361" s="12">
+        <v>0.48472219999999999</v>
+      </c>
+      <c r="Y361" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z361" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA361" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB361" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC361" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD361" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE361" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF361" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG361" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH361" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI361" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ361" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK361" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL361" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM361" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN361" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO361" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP361" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ361" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR361" s="3" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="362" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A362" s="1">
+        <v>1</v>
+      </c>
+      <c r="B362" s="2">
+        <v>2</v>
+      </c>
+      <c r="C362" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D362" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E362" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F362" s="4">
+        <v>46310</v>
+      </c>
+      <c r="G362" s="5">
+        <v>80</v>
+      </c>
+      <c r="H362" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I362" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J362" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K362" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L362" s="6">
+        <v>120</v>
+      </c>
+      <c r="M362" s="7">
+        <v>21285.599999999999</v>
+      </c>
+      <c r="N362" s="6">
+        <v>1</v>
+      </c>
+      <c r="O362" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="P362" s="8">
+        <v>177.38</v>
+      </c>
+      <c r="Q362" s="6">
+        <v>0</v>
+      </c>
+      <c r="R362" s="7">
+        <v>0</v>
+      </c>
+      <c r="S362" s="9">
+        <v>0</v>
+      </c>
+      <c r="T362" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U362" s="10">
+        <v>68297</v>
+      </c>
+      <c r="V362" s="11">
+        <v>11</v>
+      </c>
+      <c r="W362" s="4">
+        <v>46310</v>
+      </c>
+      <c r="X362" s="12">
+        <v>0.48472219999999999</v>
+      </c>
+      <c r="Y362" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z362" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA362" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB362" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC362" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD362" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE362" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF362" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG362" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH362" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI362" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ362" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK362" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL362" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM362" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN362" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO362" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP362" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ362" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR362" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="363" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A363" s="1">
+        <v>1</v>
+      </c>
+      <c r="B363" s="2">
+        <v>2</v>
+      </c>
+      <c r="C363" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D363" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E363" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F363" s="4">
+        <v>46310</v>
+      </c>
+      <c r="G363" s="5">
+        <v>81</v>
+      </c>
+      <c r="H363" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I363" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J363" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K363" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L363" s="6">
+        <v>121</v>
+      </c>
+      <c r="M363" s="7">
+        <v>21462.98</v>
+      </c>
+      <c r="N363" s="6">
+        <v>1</v>
+      </c>
+      <c r="O363" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="P363" s="8">
+        <v>177.38</v>
+      </c>
+      <c r="Q363" s="6">
+        <v>0</v>
+      </c>
+      <c r="R363" s="7">
+        <v>0</v>
+      </c>
+      <c r="S363" s="9">
+        <v>0</v>
+      </c>
+      <c r="T363" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U363" s="10">
+        <v>68297</v>
+      </c>
+      <c r="V363" s="11">
+        <v>11</v>
+      </c>
+      <c r="W363" s="4">
+        <v>46310</v>
+      </c>
+      <c r="X363" s="12">
+        <v>0.48472219999999999</v>
+      </c>
+      <c r="Y363" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z363" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA363" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB363" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC363" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD363" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE363" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF363" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG363" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH363" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI363" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ363" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK363" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL363" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM363" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN363" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO363" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP363" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ363" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR363" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="364" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A364" s="1">
+        <v>1</v>
+      </c>
+      <c r="B364" s="2">
+        <v>2</v>
+      </c>
+      <c r="C364" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D364" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E364" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F364" s="4">
+        <v>46310</v>
+      </c>
+      <c r="G364" s="5">
+        <v>82</v>
+      </c>
+      <c r="H364" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I364" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J364" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K364" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L364" s="6">
+        <v>122</v>
+      </c>
+      <c r="M364" s="7">
+        <v>21640.36</v>
+      </c>
+      <c r="N364" s="6">
+        <v>1</v>
+      </c>
+      <c r="O364" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="P364" s="8">
+        <v>177.38</v>
+      </c>
+      <c r="Q364" s="6">
+        <v>0</v>
+      </c>
+      <c r="R364" s="7">
+        <v>0</v>
+      </c>
+      <c r="S364" s="9">
+        <v>0</v>
+      </c>
+      <c r="T364" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U364" s="10">
+        <v>68297</v>
+      </c>
+      <c r="V364" s="11">
+        <v>11</v>
+      </c>
+      <c r="W364" s="4">
+        <v>46310</v>
+      </c>
+      <c r="X364" s="12">
+        <v>0.48472219999999999</v>
+      </c>
+      <c r="Y364" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z364" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA364" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB364" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC364" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD364" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE364" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF364" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG364" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH364" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI364" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ364" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK364" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL364" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM364" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN364" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO364" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP364" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ364" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR364" s="3" t="s">
+        <v>419</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{412AE7C6-BFF6-4968-B1E3-16D2C20440C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0B86848-D91F-41EF-A757-FE548C0FF71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="72">
   <si>
     <t>Sel</t>
   </si>
@@ -187,106 +187,55 @@
     <t>FORNOE</t>
   </si>
   <si>
-    <t>1858400003702</t>
-  </si>
-  <si>
-    <t>1858400003703</t>
-  </si>
-  <si>
-    <t>1858400003704</t>
-  </si>
-  <si>
-    <t>1858400003705</t>
-  </si>
-  <si>
-    <t>1858400003706</t>
-  </si>
-  <si>
-    <t>1858400003707</t>
-  </si>
-  <si>
-    <t>1858400003708</t>
-  </si>
-  <si>
-    <t>1858400003709</t>
-  </si>
-  <si>
-    <t>1858400003710</t>
-  </si>
-  <si>
-    <t>1858400003711</t>
-  </si>
-  <si>
-    <t>1858400003712</t>
-  </si>
-  <si>
-    <t>1858400003713</t>
-  </si>
-  <si>
-    <t>1858400003714</t>
-  </si>
-  <si>
-    <t>1858400003715</t>
-  </si>
-  <si>
-    <t>1858400003716</t>
-  </si>
-  <si>
-    <t>1858400003717</t>
-  </si>
-  <si>
-    <t>1858400003718</t>
-  </si>
-  <si>
-    <t>1858400003719</t>
-  </si>
-  <si>
-    <t>1858400003720</t>
-  </si>
-  <si>
-    <t>1858400003721</t>
-  </si>
-  <si>
-    <t>1858400003722</t>
-  </si>
-  <si>
-    <t>1858400003723</t>
-  </si>
-  <si>
-    <t>1858400003724</t>
-  </si>
-  <si>
-    <t>1858400003725</t>
-  </si>
-  <si>
-    <t>1858400003726</t>
-  </si>
-  <si>
-    <t>1858400003727</t>
-  </si>
-  <si>
-    <t>1858400003728</t>
-  </si>
-  <si>
-    <t>1858400003729</t>
-  </si>
-  <si>
-    <t>1858400003730</t>
-  </si>
-  <si>
-    <t>1858400003731</t>
-  </si>
-  <si>
-    <t>1858400003732</t>
-  </si>
-  <si>
-    <t>1858400003733</t>
-  </si>
-  <si>
-    <t>1858400003734</t>
-  </si>
-  <si>
-    <t>1858400003735</t>
+    <t>1858400003814</t>
+  </si>
+  <si>
+    <t>1858400003815</t>
+  </si>
+  <si>
+    <t>1858400003816</t>
+  </si>
+  <si>
+    <t>1858400003817</t>
+  </si>
+  <si>
+    <t>1858400003818</t>
+  </si>
+  <si>
+    <t>1858400003819</t>
+  </si>
+  <si>
+    <t>1858400003820</t>
+  </si>
+  <si>
+    <t>1858400003821</t>
+  </si>
+  <si>
+    <t>1858400003822</t>
+  </si>
+  <si>
+    <t>1858400003823</t>
+  </si>
+  <si>
+    <t>1858400003824</t>
+  </si>
+  <si>
+    <t>1858400003825</t>
+  </si>
+  <si>
+    <t>1858400003826</t>
+  </si>
+  <si>
+    <t>1858400003827</t>
+  </si>
+  <si>
+    <t>1858400003828</t>
+  </si>
+  <si>
+    <t>1858400003829</t>
+  </si>
+  <si>
+    <t>1858400003830</t>
   </si>
 </sst>
 </file>
@@ -862,7 +811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR35"/>
+  <dimension ref="A1:AR18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -1016,10 +965,10 @@
         <v>46</v>
       </c>
       <c r="F2" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="G2" s="5">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>47</v>
@@ -1034,10 +983,10 @@
         <v>50</v>
       </c>
       <c r="L2" s="6">
-        <v>57</v>
+        <v>169</v>
       </c>
       <c r="M2" s="7">
-        <v>19805.669999999998</v>
+        <v>64537.37</v>
       </c>
       <c r="N2" s="6">
         <v>1</v>
@@ -1046,7 +995,7 @@
         <v>51</v>
       </c>
       <c r="P2" s="8">
-        <v>347.47</v>
+        <v>381.88</v>
       </c>
       <c r="Q2" s="6">
         <v>0</v>
@@ -1067,10 +1016,10 @@
         <v>11</v>
       </c>
       <c r="W2" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="X2" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.3020833</v>
       </c>
       <c r="Y2" s="10">
         <v>0</v>
@@ -1150,10 +1099,10 @@
         <v>46</v>
       </c>
       <c r="F3" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="G3" s="5">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>47</v>
@@ -1168,10 +1117,10 @@
         <v>50</v>
       </c>
       <c r="L3" s="6">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="M3" s="7">
-        <v>20153.14</v>
+        <v>64919.25</v>
       </c>
       <c r="N3" s="6">
         <v>1</v>
@@ -1180,7 +1129,7 @@
         <v>51</v>
       </c>
       <c r="P3" s="8">
-        <v>347.47</v>
+        <v>381.88</v>
       </c>
       <c r="Q3" s="6">
         <v>0</v>
@@ -1201,10 +1150,10 @@
         <v>11</v>
       </c>
       <c r="W3" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="X3" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.3020833</v>
       </c>
       <c r="Y3" s="10">
         <v>0</v>
@@ -1284,10 +1233,10 @@
         <v>46</v>
       </c>
       <c r="F4" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="G4" s="5">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>47</v>
@@ -1302,10 +1251,10 @@
         <v>50</v>
       </c>
       <c r="L4" s="6">
-        <v>59</v>
+        <v>171</v>
       </c>
       <c r="M4" s="7">
-        <v>20500.61</v>
+        <v>65301.13</v>
       </c>
       <c r="N4" s="6">
         <v>1</v>
@@ -1314,7 +1263,7 @@
         <v>51</v>
       </c>
       <c r="P4" s="8">
-        <v>347.47</v>
+        <v>381.88</v>
       </c>
       <c r="Q4" s="6">
         <v>0</v>
@@ -1335,10 +1284,10 @@
         <v>11</v>
       </c>
       <c r="W4" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="X4" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.3020833</v>
       </c>
       <c r="Y4" s="10">
         <v>0</v>
@@ -1418,10 +1367,10 @@
         <v>46</v>
       </c>
       <c r="F5" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="G5" s="5">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>47</v>
@@ -1436,10 +1385,10 @@
         <v>50</v>
       </c>
       <c r="L5" s="6">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="M5" s="7">
-        <v>20848.080000000002</v>
+        <v>65683.009999999995</v>
       </c>
       <c r="N5" s="6">
         <v>1</v>
@@ -1448,7 +1397,7 @@
         <v>51</v>
       </c>
       <c r="P5" s="8">
-        <v>347.47</v>
+        <v>381.88</v>
       </c>
       <c r="Q5" s="6">
         <v>0</v>
@@ -1469,10 +1418,10 @@
         <v>11</v>
       </c>
       <c r="W5" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="X5" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.30625000000000002</v>
       </c>
       <c r="Y5" s="10">
         <v>0</v>
@@ -1552,10 +1501,10 @@
         <v>46</v>
       </c>
       <c r="F6" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="G6" s="5">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>47</v>
@@ -1570,10 +1519,10 @@
         <v>50</v>
       </c>
       <c r="L6" s="6">
-        <v>61</v>
+        <v>173</v>
       </c>
       <c r="M6" s="7">
-        <v>21195.54</v>
+        <v>66064.89</v>
       </c>
       <c r="N6" s="6">
         <v>1</v>
@@ -1582,7 +1531,7 @@
         <v>51</v>
       </c>
       <c r="P6" s="8">
-        <v>347.47</v>
+        <v>381.88</v>
       </c>
       <c r="Q6" s="6">
         <v>0</v>
@@ -1603,10 +1552,10 @@
         <v>11</v>
       </c>
       <c r="W6" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="X6" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.30625000000000002</v>
       </c>
       <c r="Y6" s="10">
         <v>0</v>
@@ -1686,10 +1635,10 @@
         <v>46</v>
       </c>
       <c r="F7" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="G7" s="5">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>47</v>
@@ -1704,10 +1653,10 @@
         <v>50</v>
       </c>
       <c r="L7" s="6">
-        <v>62</v>
+        <v>174</v>
       </c>
       <c r="M7" s="7">
-        <v>21543.01</v>
+        <v>66446.759999999995</v>
       </c>
       <c r="N7" s="6">
         <v>1</v>
@@ -1716,7 +1665,7 @@
         <v>51</v>
       </c>
       <c r="P7" s="8">
-        <v>347.47</v>
+        <v>381.88</v>
       </c>
       <c r="Q7" s="6">
         <v>0</v>
@@ -1737,10 +1686,10 @@
         <v>11</v>
       </c>
       <c r="W7" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="X7" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.31388890000000003</v>
       </c>
       <c r="Y7" s="10">
         <v>0</v>
@@ -1820,10 +1769,10 @@
         <v>46</v>
       </c>
       <c r="F8" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="G8" s="5">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>47</v>
@@ -1838,10 +1787,10 @@
         <v>50</v>
       </c>
       <c r="L8" s="6">
-        <v>63</v>
+        <v>175</v>
       </c>
       <c r="M8" s="7">
-        <v>21890.48</v>
+        <v>66828.639999999999</v>
       </c>
       <c r="N8" s="6">
         <v>1</v>
@@ -1850,7 +1799,7 @@
         <v>51</v>
       </c>
       <c r="P8" s="8">
-        <v>347.47</v>
+        <v>381.88</v>
       </c>
       <c r="Q8" s="6">
         <v>0</v>
@@ -1871,10 +1820,10 @@
         <v>11</v>
       </c>
       <c r="W8" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="X8" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.31388890000000003</v>
       </c>
       <c r="Y8" s="10">
         <v>0</v>
@@ -1954,10 +1903,10 @@
         <v>46</v>
       </c>
       <c r="F9" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="G9" s="5">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>47</v>
@@ -1972,10 +1921,10 @@
         <v>50</v>
       </c>
       <c r="L9" s="6">
-        <v>64</v>
+        <v>176</v>
       </c>
       <c r="M9" s="7">
-        <v>22237.95</v>
+        <v>67210.52</v>
       </c>
       <c r="N9" s="6">
         <v>1</v>
@@ -1984,7 +1933,7 @@
         <v>51</v>
       </c>
       <c r="P9" s="8">
-        <v>347.47</v>
+        <v>381.88</v>
       </c>
       <c r="Q9" s="6">
         <v>0</v>
@@ -2005,10 +1954,10 @@
         <v>11</v>
       </c>
       <c r="W9" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="X9" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.32083329999999999</v>
       </c>
       <c r="Y9" s="10">
         <v>0</v>
@@ -2088,10 +2037,10 @@
         <v>46</v>
       </c>
       <c r="F10" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="G10" s="5">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>47</v>
@@ -2106,10 +2055,10 @@
         <v>50</v>
       </c>
       <c r="L10" s="6">
-        <v>65</v>
+        <v>177</v>
       </c>
       <c r="M10" s="7">
-        <v>22585.42</v>
+        <v>67592.399999999994</v>
       </c>
       <c r="N10" s="6">
         <v>1</v>
@@ -2118,7 +2067,7 @@
         <v>51</v>
       </c>
       <c r="P10" s="8">
-        <v>347.47</v>
+        <v>381.88</v>
       </c>
       <c r="Q10" s="6">
         <v>0</v>
@@ -2139,10 +2088,10 @@
         <v>11</v>
       </c>
       <c r="W10" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="X10" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.32083329999999999</v>
       </c>
       <c r="Y10" s="10">
         <v>0</v>
@@ -2222,10 +2171,10 @@
         <v>46</v>
       </c>
       <c r="F11" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="G11" s="5">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>47</v>
@@ -2240,10 +2189,10 @@
         <v>50</v>
       </c>
       <c r="L11" s="6">
-        <v>66</v>
+        <v>178</v>
       </c>
       <c r="M11" s="7">
-        <v>22932.880000000001</v>
+        <v>67974.28</v>
       </c>
       <c r="N11" s="6">
         <v>1</v>
@@ -2252,7 +2201,7 @@
         <v>51</v>
       </c>
       <c r="P11" s="8">
-        <v>347.47</v>
+        <v>381.88</v>
       </c>
       <c r="Q11" s="6">
         <v>0</v>
@@ -2273,10 +2222,10 @@
         <v>11</v>
       </c>
       <c r="W11" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="X11" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.32777780000000001</v>
       </c>
       <c r="Y11" s="10">
         <v>0</v>
@@ -2356,10 +2305,10 @@
         <v>46</v>
       </c>
       <c r="F12" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="G12" s="5">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>47</v>
@@ -2374,10 +2323,10 @@
         <v>50</v>
       </c>
       <c r="L12" s="6">
-        <v>67</v>
+        <v>179</v>
       </c>
       <c r="M12" s="7">
-        <v>23280.35</v>
+        <v>68356.149999999994</v>
       </c>
       <c r="N12" s="6">
         <v>1</v>
@@ -2386,7 +2335,7 @@
         <v>51</v>
       </c>
       <c r="P12" s="8">
-        <v>347.47</v>
+        <v>381.88</v>
       </c>
       <c r="Q12" s="6">
         <v>0</v>
@@ -2407,10 +2356,10 @@
         <v>11</v>
       </c>
       <c r="W12" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="X12" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.32777780000000001</v>
       </c>
       <c r="Y12" s="10">
         <v>0</v>
@@ -2490,10 +2439,10 @@
         <v>46</v>
       </c>
       <c r="F13" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="G13" s="5">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>47</v>
@@ -2508,10 +2457,10 @@
         <v>50</v>
       </c>
       <c r="L13" s="6">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="M13" s="7">
-        <v>23627.82</v>
+        <v>68738.03</v>
       </c>
       <c r="N13" s="6">
         <v>1</v>
@@ -2520,7 +2469,7 @@
         <v>51</v>
       </c>
       <c r="P13" s="8">
-        <v>347.47</v>
+        <v>381.88</v>
       </c>
       <c r="Q13" s="6">
         <v>0</v>
@@ -2541,10 +2490,10 @@
         <v>11</v>
       </c>
       <c r="W13" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="X13" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.33472220000000003</v>
       </c>
       <c r="Y13" s="10">
         <v>0</v>
@@ -2624,10 +2573,10 @@
         <v>46</v>
       </c>
       <c r="F14" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="G14" s="5">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>47</v>
@@ -2642,10 +2591,10 @@
         <v>50</v>
       </c>
       <c r="L14" s="6">
-        <v>69</v>
+        <v>181</v>
       </c>
       <c r="M14" s="7">
-        <v>23975.29</v>
+        <v>69119.91</v>
       </c>
       <c r="N14" s="6">
         <v>1</v>
@@ -2654,7 +2603,7 @@
         <v>51</v>
       </c>
       <c r="P14" s="8">
-        <v>347.47</v>
+        <v>381.88</v>
       </c>
       <c r="Q14" s="6">
         <v>0</v>
@@ -2675,10 +2624,10 @@
         <v>11</v>
       </c>
       <c r="W14" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="X14" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.33472220000000003</v>
       </c>
       <c r="Y14" s="10">
         <v>0</v>
@@ -2758,10 +2707,10 @@
         <v>46</v>
       </c>
       <c r="F15" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="G15" s="5">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>47</v>
@@ -2776,10 +2725,10 @@
         <v>50</v>
       </c>
       <c r="L15" s="6">
-        <v>70</v>
+        <v>182</v>
       </c>
       <c r="M15" s="7">
-        <v>24322.76</v>
+        <v>69501.789999999994</v>
       </c>
       <c r="N15" s="6">
         <v>1</v>
@@ -2788,7 +2737,7 @@
         <v>51</v>
       </c>
       <c r="P15" s="8">
-        <v>347.47</v>
+        <v>381.88</v>
       </c>
       <c r="Q15" s="6">
         <v>0</v>
@@ -2809,10 +2758,10 @@
         <v>11</v>
       </c>
       <c r="W15" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="X15" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.33472220000000003</v>
       </c>
       <c r="Y15" s="10">
         <v>0</v>
@@ -2892,10 +2841,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="G16" s="5">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>47</v>
@@ -2910,10 +2859,10 @@
         <v>50</v>
       </c>
       <c r="L16" s="6">
-        <v>71</v>
+        <v>183</v>
       </c>
       <c r="M16" s="7">
-        <v>24670.22</v>
+        <v>69883.67</v>
       </c>
       <c r="N16" s="6">
         <v>1</v>
@@ -2922,7 +2871,7 @@
         <v>51</v>
       </c>
       <c r="P16" s="8">
-        <v>347.47</v>
+        <v>381.88</v>
       </c>
       <c r="Q16" s="6">
         <v>0</v>
@@ -2943,10 +2892,10 @@
         <v>11</v>
       </c>
       <c r="W16" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="X16" s="12">
-        <v>0.35833330000000002</v>
+        <v>0.33472220000000003</v>
       </c>
       <c r="Y16" s="10">
         <v>0</v>
@@ -3026,10 +2975,10 @@
         <v>46</v>
       </c>
       <c r="F17" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="G17" s="5">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>47</v>
@@ -3044,10 +2993,10 @@
         <v>50</v>
       </c>
       <c r="L17" s="6">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="M17" s="7">
-        <v>25017.69</v>
+        <v>70265.539999999994</v>
       </c>
       <c r="N17" s="6">
         <v>1</v>
@@ -3056,7 +3005,7 @@
         <v>51</v>
       </c>
       <c r="P17" s="8">
-        <v>347.47</v>
+        <v>381.88</v>
       </c>
       <c r="Q17" s="6">
         <v>0</v>
@@ -3077,10 +3026,10 @@
         <v>11</v>
       </c>
       <c r="W17" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="X17" s="12">
-        <v>0.35833330000000002</v>
+        <v>0.34236109999999997</v>
       </c>
       <c r="Y17" s="10">
         <v>0</v>
@@ -3160,10 +3109,10 @@
         <v>46</v>
       </c>
       <c r="F18" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="G18" s="5">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>47</v>
@@ -3178,10 +3127,10 @@
         <v>50</v>
       </c>
       <c r="L18" s="6">
-        <v>73</v>
+        <v>185</v>
       </c>
       <c r="M18" s="7">
-        <v>25365.16</v>
+        <v>70647.42</v>
       </c>
       <c r="N18" s="6">
         <v>1</v>
@@ -3190,7 +3139,7 @@
         <v>51</v>
       </c>
       <c r="P18" s="8">
-        <v>347.47</v>
+        <v>381.88</v>
       </c>
       <c r="Q18" s="6">
         <v>0</v>
@@ -3211,10 +3160,10 @@
         <v>11</v>
       </c>
       <c r="W18" s="4">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="X18" s="12">
-        <v>0.35833330000000002</v>
+        <v>0.34236109999999997</v>
       </c>
       <c r="Y18" s="10">
         <v>0</v>
@@ -3275,2284 +3224,6 @@
       </c>
       <c r="AR18" s="3" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
-        <v>1</v>
-      </c>
-      <c r="B19" s="2">
-        <v>2</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" s="4">
-        <v>46311</v>
-      </c>
-      <c r="G19" s="5">
-        <v>67</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L19" s="6">
-        <v>74</v>
-      </c>
-      <c r="M19" s="7">
-        <v>25712.63</v>
-      </c>
-      <c r="N19" s="6">
-        <v>1</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P19" s="8">
-        <v>347.47</v>
-      </c>
-      <c r="Q19" s="6">
-        <v>0</v>
-      </c>
-      <c r="R19" s="7">
-        <v>0</v>
-      </c>
-      <c r="S19" s="9">
-        <v>0</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U19" s="10">
-        <v>68405</v>
-      </c>
-      <c r="V19" s="11">
-        <v>11</v>
-      </c>
-      <c r="W19" s="4">
-        <v>46311</v>
-      </c>
-      <c r="X19" s="12">
-        <v>0.35833330000000002</v>
-      </c>
-      <c r="Y19" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE19" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG19" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI19" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ19" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK19" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL19" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM19" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR19" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>1</v>
-      </c>
-      <c r="B20" s="2">
-        <v>2</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="4">
-        <v>46311</v>
-      </c>
-      <c r="G20" s="5">
-        <v>68</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" s="6">
-        <v>75</v>
-      </c>
-      <c r="M20" s="7">
-        <v>26060.09</v>
-      </c>
-      <c r="N20" s="6">
-        <v>1</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P20" s="8">
-        <v>347.47</v>
-      </c>
-      <c r="Q20" s="6">
-        <v>0</v>
-      </c>
-      <c r="R20" s="7">
-        <v>0</v>
-      </c>
-      <c r="S20" s="9">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U20" s="10">
-        <v>68405</v>
-      </c>
-      <c r="V20" s="11">
-        <v>11</v>
-      </c>
-      <c r="W20" s="4">
-        <v>46311</v>
-      </c>
-      <c r="X20" s="12">
-        <v>0.35833330000000002</v>
-      </c>
-      <c r="Y20" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG20" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ20" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK20" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL20" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM20" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR20" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>1</v>
-      </c>
-      <c r="B21" s="2">
-        <v>2</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" s="4">
-        <v>46311</v>
-      </c>
-      <c r="G21" s="5">
-        <v>69</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L21" s="6">
-        <v>76</v>
-      </c>
-      <c r="M21" s="7">
-        <v>26407.56</v>
-      </c>
-      <c r="N21" s="6">
-        <v>1</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P21" s="8">
-        <v>347.47</v>
-      </c>
-      <c r="Q21" s="6">
-        <v>0</v>
-      </c>
-      <c r="R21" s="7">
-        <v>0</v>
-      </c>
-      <c r="S21" s="9">
-        <v>0</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U21" s="10">
-        <v>68405</v>
-      </c>
-      <c r="V21" s="11">
-        <v>11</v>
-      </c>
-      <c r="W21" s="4">
-        <v>46311</v>
-      </c>
-      <c r="X21" s="12">
-        <v>0.35833330000000002</v>
-      </c>
-      <c r="Y21" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG21" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI21" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ21" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK21" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL21" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM21" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR21" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>1</v>
-      </c>
-      <c r="B22" s="2">
-        <v>2</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="4">
-        <v>46311</v>
-      </c>
-      <c r="G22" s="5">
-        <v>70</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L22" s="6">
-        <v>77</v>
-      </c>
-      <c r="M22" s="7">
-        <v>26755.03</v>
-      </c>
-      <c r="N22" s="6">
-        <v>1</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P22" s="8">
-        <v>347.47</v>
-      </c>
-      <c r="Q22" s="6">
-        <v>0</v>
-      </c>
-      <c r="R22" s="7">
-        <v>0</v>
-      </c>
-      <c r="S22" s="9">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U22" s="10">
-        <v>68405</v>
-      </c>
-      <c r="V22" s="11">
-        <v>11</v>
-      </c>
-      <c r="W22" s="4">
-        <v>46311</v>
-      </c>
-      <c r="X22" s="12">
-        <v>0.35833330000000002</v>
-      </c>
-      <c r="Y22" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG22" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI22" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ22" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK22" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL22" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM22" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR22" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>1</v>
-      </c>
-      <c r="B23" s="2">
-        <v>2</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23" s="4">
-        <v>46311</v>
-      </c>
-      <c r="G23" s="5">
-        <v>71</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L23" s="6">
-        <v>78</v>
-      </c>
-      <c r="M23" s="7">
-        <v>27102.5</v>
-      </c>
-      <c r="N23" s="6">
-        <v>1</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P23" s="8">
-        <v>347.47</v>
-      </c>
-      <c r="Q23" s="6">
-        <v>0</v>
-      </c>
-      <c r="R23" s="7">
-        <v>0</v>
-      </c>
-      <c r="S23" s="9">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U23" s="10">
-        <v>68405</v>
-      </c>
-      <c r="V23" s="11">
-        <v>11</v>
-      </c>
-      <c r="W23" s="4">
-        <v>46311</v>
-      </c>
-      <c r="X23" s="12">
-        <v>0.35833330000000002</v>
-      </c>
-      <c r="Y23" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG23" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI23" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ23" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK23" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL23" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM23" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR23" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>1</v>
-      </c>
-      <c r="B24" s="2">
-        <v>2</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" s="4">
-        <v>46311</v>
-      </c>
-      <c r="G24" s="5">
-        <v>72</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L24" s="6">
-        <v>79</v>
-      </c>
-      <c r="M24" s="7">
-        <v>27449.97</v>
-      </c>
-      <c r="N24" s="6">
-        <v>1</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P24" s="8">
-        <v>347.47</v>
-      </c>
-      <c r="Q24" s="6">
-        <v>0</v>
-      </c>
-      <c r="R24" s="7">
-        <v>0</v>
-      </c>
-      <c r="S24" s="9">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U24" s="10">
-        <v>68405</v>
-      </c>
-      <c r="V24" s="11">
-        <v>11</v>
-      </c>
-      <c r="W24" s="4">
-        <v>46311</v>
-      </c>
-      <c r="X24" s="12">
-        <v>0.35833330000000002</v>
-      </c>
-      <c r="Y24" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG24" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI24" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK24" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL24" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM24" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN24" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO24" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP24" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ24" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR24" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>1</v>
-      </c>
-      <c r="B25" s="2">
-        <v>2</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F25" s="4">
-        <v>46311</v>
-      </c>
-      <c r="G25" s="5">
-        <v>73</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L25" s="6">
-        <v>80</v>
-      </c>
-      <c r="M25" s="7">
-        <v>27797.43</v>
-      </c>
-      <c r="N25" s="6">
-        <v>1</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P25" s="8">
-        <v>347.47</v>
-      </c>
-      <c r="Q25" s="6">
-        <v>0</v>
-      </c>
-      <c r="R25" s="7">
-        <v>0</v>
-      </c>
-      <c r="S25" s="9">
-        <v>0</v>
-      </c>
-      <c r="T25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U25" s="10">
-        <v>68405</v>
-      </c>
-      <c r="V25" s="11">
-        <v>11</v>
-      </c>
-      <c r="W25" s="4">
-        <v>46311</v>
-      </c>
-      <c r="X25" s="12">
-        <v>0.35833330000000002</v>
-      </c>
-      <c r="Y25" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD25" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE25" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG25" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI25" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK25" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL25" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM25" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR25" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>1</v>
-      </c>
-      <c r="B26" s="2">
-        <v>2</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F26" s="4">
-        <v>46311</v>
-      </c>
-      <c r="G26" s="5">
-        <v>74</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L26" s="6">
-        <v>81</v>
-      </c>
-      <c r="M26" s="7">
-        <v>28144.9</v>
-      </c>
-      <c r="N26" s="6">
-        <v>1</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P26" s="8">
-        <v>347.47</v>
-      </c>
-      <c r="Q26" s="6">
-        <v>0</v>
-      </c>
-      <c r="R26" s="7">
-        <v>0</v>
-      </c>
-      <c r="S26" s="9">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U26" s="10">
-        <v>68405</v>
-      </c>
-      <c r="V26" s="11">
-        <v>11</v>
-      </c>
-      <c r="W26" s="4">
-        <v>46311</v>
-      </c>
-      <c r="X26" s="12">
-        <v>0.35833330000000002</v>
-      </c>
-      <c r="Y26" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE26" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG26" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH26" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ26" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK26" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL26" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM26" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN26" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO26" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP26" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ26" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR26" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <v>1</v>
-      </c>
-      <c r="B27" s="2">
-        <v>2</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F27" s="4">
-        <v>46311</v>
-      </c>
-      <c r="G27" s="5">
-        <v>75</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L27" s="6">
-        <v>82</v>
-      </c>
-      <c r="M27" s="7">
-        <v>28492.37</v>
-      </c>
-      <c r="N27" s="6">
-        <v>1</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P27" s="8">
-        <v>347.47</v>
-      </c>
-      <c r="Q27" s="6">
-        <v>0</v>
-      </c>
-      <c r="R27" s="7">
-        <v>0</v>
-      </c>
-      <c r="S27" s="9">
-        <v>0</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U27" s="10">
-        <v>68405</v>
-      </c>
-      <c r="V27" s="11">
-        <v>11</v>
-      </c>
-      <c r="W27" s="4">
-        <v>46311</v>
-      </c>
-      <c r="X27" s="12">
-        <v>0.35833330000000002</v>
-      </c>
-      <c r="Y27" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE27" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG27" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH27" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI27" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ27" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK27" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL27" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM27" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN27" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO27" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP27" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ27" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR27" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
-        <v>1</v>
-      </c>
-      <c r="B28" s="2">
-        <v>2</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F28" s="4">
-        <v>46311</v>
-      </c>
-      <c r="G28" s="5">
-        <v>76</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L28" s="6">
-        <v>83</v>
-      </c>
-      <c r="M28" s="7">
-        <v>28839.84</v>
-      </c>
-      <c r="N28" s="6">
-        <v>1</v>
-      </c>
-      <c r="O28" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P28" s="8">
-        <v>347.47</v>
-      </c>
-      <c r="Q28" s="6">
-        <v>0</v>
-      </c>
-      <c r="R28" s="7">
-        <v>0</v>
-      </c>
-      <c r="S28" s="9">
-        <v>0</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U28" s="10">
-        <v>68405</v>
-      </c>
-      <c r="V28" s="11">
-        <v>11</v>
-      </c>
-      <c r="W28" s="4">
-        <v>46311</v>
-      </c>
-      <c r="X28" s="12">
-        <v>0.35833330000000002</v>
-      </c>
-      <c r="Y28" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC28" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE28" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG28" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI28" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ28" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK28" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL28" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM28" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR28" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="29" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
-        <v>1</v>
-      </c>
-      <c r="B29" s="2">
-        <v>2</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F29" s="4">
-        <v>46311</v>
-      </c>
-      <c r="G29" s="5">
-        <v>77</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L29" s="6">
-        <v>84</v>
-      </c>
-      <c r="M29" s="7">
-        <v>29187.31</v>
-      </c>
-      <c r="N29" s="6">
-        <v>1</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P29" s="8">
-        <v>347.47</v>
-      </c>
-      <c r="Q29" s="6">
-        <v>0</v>
-      </c>
-      <c r="R29" s="7">
-        <v>0</v>
-      </c>
-      <c r="S29" s="9">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U29" s="10">
-        <v>68405</v>
-      </c>
-      <c r="V29" s="11">
-        <v>11</v>
-      </c>
-      <c r="W29" s="4">
-        <v>46311</v>
-      </c>
-      <c r="X29" s="12">
-        <v>0.35833330000000002</v>
-      </c>
-      <c r="Y29" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG29" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK29" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM29" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN29" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO29" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP29" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ29" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR29" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
-        <v>1</v>
-      </c>
-      <c r="B30" s="2">
-        <v>2</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F30" s="4">
-        <v>46311</v>
-      </c>
-      <c r="G30" s="5">
-        <v>78</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L30" s="6">
-        <v>85</v>
-      </c>
-      <c r="M30" s="7">
-        <v>29534.77</v>
-      </c>
-      <c r="N30" s="6">
-        <v>1</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P30" s="8">
-        <v>347.47</v>
-      </c>
-      <c r="Q30" s="6">
-        <v>0</v>
-      </c>
-      <c r="R30" s="7">
-        <v>0</v>
-      </c>
-      <c r="S30" s="9">
-        <v>0</v>
-      </c>
-      <c r="T30" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U30" s="10">
-        <v>68405</v>
-      </c>
-      <c r="V30" s="11">
-        <v>11</v>
-      </c>
-      <c r="W30" s="4">
-        <v>46311</v>
-      </c>
-      <c r="X30" s="12">
-        <v>0.35833330000000002</v>
-      </c>
-      <c r="Y30" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC30" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD30" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE30" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF30" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG30" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH30" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI30" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ30" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK30" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL30" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM30" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN30" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO30" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP30" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ30" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR30" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
-        <v>1</v>
-      </c>
-      <c r="B31" s="2">
-        <v>2</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F31" s="4">
-        <v>46311</v>
-      </c>
-      <c r="G31" s="5">
-        <v>79</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L31" s="6">
-        <v>86</v>
-      </c>
-      <c r="M31" s="7">
-        <v>29882.240000000002</v>
-      </c>
-      <c r="N31" s="6">
-        <v>1</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P31" s="8">
-        <v>347.47</v>
-      </c>
-      <c r="Q31" s="6">
-        <v>0</v>
-      </c>
-      <c r="R31" s="7">
-        <v>0</v>
-      </c>
-      <c r="S31" s="9">
-        <v>0</v>
-      </c>
-      <c r="T31" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U31" s="10">
-        <v>68405</v>
-      </c>
-      <c r="V31" s="11">
-        <v>11</v>
-      </c>
-      <c r="W31" s="4">
-        <v>46311</v>
-      </c>
-      <c r="X31" s="12">
-        <v>0.35833330000000002</v>
-      </c>
-      <c r="Y31" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC31" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE31" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF31" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG31" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH31" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI31" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ31" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK31" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL31" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM31" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN31" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO31" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP31" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ31" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR31" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
-        <v>1</v>
-      </c>
-      <c r="B32" s="2">
-        <v>2</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F32" s="4">
-        <v>46311</v>
-      </c>
-      <c r="G32" s="5">
-        <v>80</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L32" s="6">
-        <v>87</v>
-      </c>
-      <c r="M32" s="7">
-        <v>30229.71</v>
-      </c>
-      <c r="N32" s="6">
-        <v>1</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P32" s="8">
-        <v>347.47</v>
-      </c>
-      <c r="Q32" s="6">
-        <v>0</v>
-      </c>
-      <c r="R32" s="7">
-        <v>0</v>
-      </c>
-      <c r="S32" s="9">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U32" s="10">
-        <v>68405</v>
-      </c>
-      <c r="V32" s="11">
-        <v>11</v>
-      </c>
-      <c r="W32" s="4">
-        <v>46311</v>
-      </c>
-      <c r="X32" s="12">
-        <v>0.35833330000000002</v>
-      </c>
-      <c r="Y32" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG32" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI32" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ32" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK32" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL32" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM32" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN32" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO32" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP32" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ32" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR32" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
-        <v>1</v>
-      </c>
-      <c r="B33" s="2">
-        <v>2</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F33" s="4">
-        <v>46311</v>
-      </c>
-      <c r="G33" s="5">
-        <v>81</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L33" s="6">
-        <v>88</v>
-      </c>
-      <c r="M33" s="7">
-        <v>30577.18</v>
-      </c>
-      <c r="N33" s="6">
-        <v>1</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P33" s="8">
-        <v>347.47</v>
-      </c>
-      <c r="Q33" s="6">
-        <v>0</v>
-      </c>
-      <c r="R33" s="7">
-        <v>0</v>
-      </c>
-      <c r="S33" s="9">
-        <v>0</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U33" s="10">
-        <v>68405</v>
-      </c>
-      <c r="V33" s="11">
-        <v>11</v>
-      </c>
-      <c r="W33" s="4">
-        <v>46311</v>
-      </c>
-      <c r="X33" s="12">
-        <v>0.37083329999999998</v>
-      </c>
-      <c r="Y33" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE33" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF33" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG33" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH33" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI33" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ33" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK33" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL33" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM33" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN33" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO33" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP33" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ33" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR33" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="34" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
-        <v>1</v>
-      </c>
-      <c r="B34" s="2">
-        <v>2</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F34" s="4">
-        <v>46311</v>
-      </c>
-      <c r="G34" s="5">
-        <v>82</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L34" s="6">
-        <v>89</v>
-      </c>
-      <c r="M34" s="7">
-        <v>30924.65</v>
-      </c>
-      <c r="N34" s="6">
-        <v>1</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P34" s="8">
-        <v>347.47</v>
-      </c>
-      <c r="Q34" s="6">
-        <v>0</v>
-      </c>
-      <c r="R34" s="7">
-        <v>0</v>
-      </c>
-      <c r="S34" s="9">
-        <v>0</v>
-      </c>
-      <c r="T34" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U34" s="10">
-        <v>68405</v>
-      </c>
-      <c r="V34" s="11">
-        <v>11</v>
-      </c>
-      <c r="W34" s="4">
-        <v>46311</v>
-      </c>
-      <c r="X34" s="12">
-        <v>0.37083329999999998</v>
-      </c>
-      <c r="Y34" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB34" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC34" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE34" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG34" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH34" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI34" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ34" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK34" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL34" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM34" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN34" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO34" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP34" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ34" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR34" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="35" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
-        <v>1</v>
-      </c>
-      <c r="B35" s="2">
-        <v>2</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F35" s="4">
-        <v>46311</v>
-      </c>
-      <c r="G35" s="5">
-        <v>83</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L35" s="6">
-        <v>90</v>
-      </c>
-      <c r="M35" s="7">
-        <v>31272.11</v>
-      </c>
-      <c r="N35" s="6">
-        <v>1</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P35" s="8">
-        <v>347.47</v>
-      </c>
-      <c r="Q35" s="6">
-        <v>0</v>
-      </c>
-      <c r="R35" s="7">
-        <v>0</v>
-      </c>
-      <c r="S35" s="9">
-        <v>0</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U35" s="10">
-        <v>68405</v>
-      </c>
-      <c r="V35" s="11">
-        <v>11</v>
-      </c>
-      <c r="W35" s="4">
-        <v>46311</v>
-      </c>
-      <c r="X35" s="12">
-        <v>0.37083329999999998</v>
-      </c>
-      <c r="Y35" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG35" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH35" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI35" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ35" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK35" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL35" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM35" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN35" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO35" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP35" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ35" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR35" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0B86848-D91F-41EF-A757-FE548C0FF71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9467281-37A1-492B-813F-256A2F3EF1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="93">
   <si>
     <t>Sel</t>
   </si>
@@ -236,6 +236,69 @@
   </si>
   <si>
     <t>1858400003830</t>
+  </si>
+  <si>
+    <t>1858400003831</t>
+  </si>
+  <si>
+    <t>1858400003832</t>
+  </si>
+  <si>
+    <t>1858400003833</t>
+  </si>
+  <si>
+    <t>1858400003834</t>
+  </si>
+  <si>
+    <t>1858400003835</t>
+  </si>
+  <si>
+    <t>1858400003836</t>
+  </si>
+  <si>
+    <t>1858400003837</t>
+  </si>
+  <si>
+    <t>1858400003838</t>
+  </si>
+  <si>
+    <t>1858400003839</t>
+  </si>
+  <si>
+    <t>1858400003840</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>FORNO ELETRICO NARDELLI EMBUTIR INOX 60 LITROS - NARDELLI EMBUTIR INOX 60 LITROS - 220 V</t>
+  </si>
+  <si>
+    <t>1875400003196</t>
+  </si>
+  <si>
+    <t>1875400003197</t>
+  </si>
+  <si>
+    <t>1875400003198</t>
+  </si>
+  <si>
+    <t>1875400003199</t>
+  </si>
+  <si>
+    <t>1875400003200</t>
+  </si>
+  <si>
+    <t>1875400003201</t>
+  </si>
+  <si>
+    <t>1875400003202</t>
+  </si>
+  <si>
+    <t>1875400003203</t>
+  </si>
+  <si>
+    <t>1875400003204</t>
   </si>
 </sst>
 </file>
@@ -811,7 +874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR18"/>
+  <dimension ref="A1:AR37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -3224,6 +3287,2552 @@
       </c>
       <c r="AR18" s="3" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>1</v>
+      </c>
+      <c r="B19" s="2">
+        <v>2</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G19" s="5">
+        <v>18</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L19" s="6">
+        <v>186</v>
+      </c>
+      <c r="M19" s="7">
+        <v>71029.3</v>
+      </c>
+      <c r="N19" s="6">
+        <v>1</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P19" s="8">
+        <v>381.88</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>0</v>
+      </c>
+      <c r="R19" s="7">
+        <v>0</v>
+      </c>
+      <c r="S19" s="9">
+        <v>0</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U19" s="10">
+        <v>68405</v>
+      </c>
+      <c r="V19" s="11">
+        <v>11</v>
+      </c>
+      <c r="W19" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X19" s="12">
+        <v>0.35</v>
+      </c>
+      <c r="Y19" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG19" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI19" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK19" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM19" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR19" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>1</v>
+      </c>
+      <c r="B20" s="2">
+        <v>2</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G20" s="5">
+        <v>19</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L20" s="6">
+        <v>187</v>
+      </c>
+      <c r="M20" s="7">
+        <v>71411.179999999993</v>
+      </c>
+      <c r="N20" s="6">
+        <v>1</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P20" s="8">
+        <v>381.88</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>0</v>
+      </c>
+      <c r="R20" s="7">
+        <v>0</v>
+      </c>
+      <c r="S20" s="9">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U20" s="10">
+        <v>68405</v>
+      </c>
+      <c r="V20" s="11">
+        <v>11</v>
+      </c>
+      <c r="W20" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X20" s="12">
+        <v>0.35</v>
+      </c>
+      <c r="Y20" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG20" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK20" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR20" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>1</v>
+      </c>
+      <c r="B21" s="2">
+        <v>2</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G21" s="5">
+        <v>20</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L21" s="6">
+        <v>188</v>
+      </c>
+      <c r="M21" s="7">
+        <v>71793.06</v>
+      </c>
+      <c r="N21" s="6">
+        <v>1</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P21" s="8">
+        <v>381.88</v>
+      </c>
+      <c r="Q21" s="6">
+        <v>0</v>
+      </c>
+      <c r="R21" s="7">
+        <v>0</v>
+      </c>
+      <c r="S21" s="9">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U21" s="10">
+        <v>68405</v>
+      </c>
+      <c r="V21" s="11">
+        <v>11</v>
+      </c>
+      <c r="W21" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X21" s="12">
+        <v>0.35</v>
+      </c>
+      <c r="Y21" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG21" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK21" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR21" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>1</v>
+      </c>
+      <c r="B22" s="2">
+        <v>2</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G22" s="5">
+        <v>21</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L22" s="6">
+        <v>189</v>
+      </c>
+      <c r="M22" s="7">
+        <v>72174.929999999993</v>
+      </c>
+      <c r="N22" s="6">
+        <v>1</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P22" s="8">
+        <v>381.88</v>
+      </c>
+      <c r="Q22" s="6">
+        <v>0</v>
+      </c>
+      <c r="R22" s="7">
+        <v>0</v>
+      </c>
+      <c r="S22" s="9">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U22" s="10">
+        <v>68405</v>
+      </c>
+      <c r="V22" s="11">
+        <v>11</v>
+      </c>
+      <c r="W22" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X22" s="12">
+        <v>0.35625000000000001</v>
+      </c>
+      <c r="Y22" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG22" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK22" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR22" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>1</v>
+      </c>
+      <c r="B23" s="2">
+        <v>2</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G23" s="5">
+        <v>22</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L23" s="6">
+        <v>190</v>
+      </c>
+      <c r="M23" s="7">
+        <v>72556.81</v>
+      </c>
+      <c r="N23" s="6">
+        <v>1</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P23" s="8">
+        <v>381.88</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>0</v>
+      </c>
+      <c r="R23" s="7">
+        <v>0</v>
+      </c>
+      <c r="S23" s="9">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U23" s="10">
+        <v>68405</v>
+      </c>
+      <c r="V23" s="11">
+        <v>11</v>
+      </c>
+      <c r="W23" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X23" s="12">
+        <v>0.35625000000000001</v>
+      </c>
+      <c r="Y23" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG23" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK23" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR23" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>1</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G24" s="5">
+        <v>23</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L24" s="6">
+        <v>191</v>
+      </c>
+      <c r="M24" s="7">
+        <v>72938.69</v>
+      </c>
+      <c r="N24" s="6">
+        <v>1</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P24" s="8">
+        <v>381.88</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0</v>
+      </c>
+      <c r="R24" s="7">
+        <v>0</v>
+      </c>
+      <c r="S24" s="9">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U24" s="10">
+        <v>68405</v>
+      </c>
+      <c r="V24" s="11">
+        <v>11</v>
+      </c>
+      <c r="W24" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X24" s="12">
+        <v>0.35625000000000001</v>
+      </c>
+      <c r="Y24" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG24" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ24" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK24" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR24" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>1</v>
+      </c>
+      <c r="B25" s="2">
+        <v>2</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F25" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G25" s="5">
+        <v>24</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L25" s="6">
+        <v>192</v>
+      </c>
+      <c r="M25" s="7">
+        <v>73320.570000000007</v>
+      </c>
+      <c r="N25" s="6">
+        <v>1</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P25" s="8">
+        <v>381.88</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>0</v>
+      </c>
+      <c r="R25" s="7">
+        <v>0</v>
+      </c>
+      <c r="S25" s="9">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U25" s="10">
+        <v>68405</v>
+      </c>
+      <c r="V25" s="11">
+        <v>11</v>
+      </c>
+      <c r="W25" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X25" s="12">
+        <v>0.35625000000000001</v>
+      </c>
+      <c r="Y25" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG25" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ25" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK25" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR25" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>1</v>
+      </c>
+      <c r="B26" s="2">
+        <v>2</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F26" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G26" s="5">
+        <v>25</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L26" s="6">
+        <v>193</v>
+      </c>
+      <c r="M26" s="7">
+        <v>73702.45</v>
+      </c>
+      <c r="N26" s="6">
+        <v>1</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P26" s="8">
+        <v>381.88</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>0</v>
+      </c>
+      <c r="R26" s="7">
+        <v>0</v>
+      </c>
+      <c r="S26" s="9">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U26" s="10">
+        <v>68405</v>
+      </c>
+      <c r="V26" s="11">
+        <v>11</v>
+      </c>
+      <c r="W26" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X26" s="12">
+        <v>0.36388890000000002</v>
+      </c>
+      <c r="Y26" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG26" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK26" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN26" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO26" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP26" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ26" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR26" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>1</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G27" s="5">
+        <v>26</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L27" s="6">
+        <v>194</v>
+      </c>
+      <c r="M27" s="7">
+        <v>74084.320000000007</v>
+      </c>
+      <c r="N27" s="6">
+        <v>1</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P27" s="8">
+        <v>381.88</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>0</v>
+      </c>
+      <c r="R27" s="7">
+        <v>0</v>
+      </c>
+      <c r="S27" s="9">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U27" s="10">
+        <v>68405</v>
+      </c>
+      <c r="V27" s="11">
+        <v>11</v>
+      </c>
+      <c r="W27" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X27" s="12">
+        <v>0.36388890000000002</v>
+      </c>
+      <c r="Y27" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG27" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI27" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ27" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK27" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR27" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>1</v>
+      </c>
+      <c r="B28" s="2">
+        <v>2</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F28" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G28" s="5">
+        <v>27</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L28" s="6">
+        <v>195</v>
+      </c>
+      <c r="M28" s="7">
+        <v>74466.2</v>
+      </c>
+      <c r="N28" s="6">
+        <v>1</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P28" s="8">
+        <v>381.88</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>0</v>
+      </c>
+      <c r="R28" s="7">
+        <v>0</v>
+      </c>
+      <c r="S28" s="9">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U28" s="10">
+        <v>68405</v>
+      </c>
+      <c r="V28" s="11">
+        <v>11</v>
+      </c>
+      <c r="W28" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X28" s="12">
+        <v>0.36388890000000002</v>
+      </c>
+      <c r="Y28" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG28" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI28" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK28" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR28" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>1</v>
+      </c>
+      <c r="B29" s="2">
+        <v>2</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G29" s="5">
+        <v>1</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L29" s="6">
+        <v>35</v>
+      </c>
+      <c r="M29" s="7">
+        <v>13094.6</v>
+      </c>
+      <c r="N29" s="6">
+        <v>1</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P29" s="8">
+        <v>374.13</v>
+      </c>
+      <c r="Q29" s="6">
+        <v>0</v>
+      </c>
+      <c r="R29" s="7">
+        <v>0</v>
+      </c>
+      <c r="S29" s="9">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U29" s="10">
+        <v>68418</v>
+      </c>
+      <c r="V29" s="11">
+        <v>11</v>
+      </c>
+      <c r="W29" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X29" s="12">
+        <v>0.37083329999999998</v>
+      </c>
+      <c r="Y29" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG29" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI29" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ29" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK29" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR29" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>1</v>
+      </c>
+      <c r="B30" s="2">
+        <v>2</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F30" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G30" s="5">
+        <v>2</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L30" s="6">
+        <v>36</v>
+      </c>
+      <c r="M30" s="7">
+        <v>13468.73</v>
+      </c>
+      <c r="N30" s="6">
+        <v>1</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P30" s="8">
+        <v>374.13</v>
+      </c>
+      <c r="Q30" s="6">
+        <v>0</v>
+      </c>
+      <c r="R30" s="7">
+        <v>0</v>
+      </c>
+      <c r="S30" s="9">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U30" s="10">
+        <v>68418</v>
+      </c>
+      <c r="V30" s="11">
+        <v>11</v>
+      </c>
+      <c r="W30" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X30" s="12">
+        <v>0.3854167</v>
+      </c>
+      <c r="Y30" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG30" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI30" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ30" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK30" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR30" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>1</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F31" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G31" s="5">
+        <v>3</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L31" s="6">
+        <v>37</v>
+      </c>
+      <c r="M31" s="7">
+        <v>13842.86</v>
+      </c>
+      <c r="N31" s="6">
+        <v>1</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P31" s="8">
+        <v>374.13</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>0</v>
+      </c>
+      <c r="R31" s="7">
+        <v>0</v>
+      </c>
+      <c r="S31" s="9">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U31" s="10">
+        <v>68418</v>
+      </c>
+      <c r="V31" s="11">
+        <v>11</v>
+      </c>
+      <c r="W31" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X31" s="12">
+        <v>0.3854167</v>
+      </c>
+      <c r="Y31" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG31" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI31" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ31" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK31" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR31" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>1</v>
+      </c>
+      <c r="B32" s="2">
+        <v>2</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G32" s="5">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L32" s="6">
+        <v>38</v>
+      </c>
+      <c r="M32" s="7">
+        <v>14216.99</v>
+      </c>
+      <c r="N32" s="6">
+        <v>1</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P32" s="8">
+        <v>374.13</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>0</v>
+      </c>
+      <c r="R32" s="7">
+        <v>0</v>
+      </c>
+      <c r="S32" s="9">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U32" s="10">
+        <v>68418</v>
+      </c>
+      <c r="V32" s="11">
+        <v>11</v>
+      </c>
+      <c r="W32" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X32" s="12">
+        <v>0.3854167</v>
+      </c>
+      <c r="Y32" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI32" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ32" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK32" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR32" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>1</v>
+      </c>
+      <c r="B33" s="2">
+        <v>2</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G33" s="5">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L33" s="6">
+        <v>39</v>
+      </c>
+      <c r="M33" s="7">
+        <v>14591.13</v>
+      </c>
+      <c r="N33" s="6">
+        <v>1</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P33" s="8">
+        <v>374.13</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>0</v>
+      </c>
+      <c r="R33" s="7">
+        <v>0</v>
+      </c>
+      <c r="S33" s="9">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U33" s="10">
+        <v>68418</v>
+      </c>
+      <c r="V33" s="11">
+        <v>11</v>
+      </c>
+      <c r="W33" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X33" s="12">
+        <v>0.39166669999999998</v>
+      </c>
+      <c r="Y33" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG33" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI33" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ33" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK33" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR33" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>1</v>
+      </c>
+      <c r="B34" s="2">
+        <v>2</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G34" s="5">
+        <v>6</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L34" s="6">
+        <v>40</v>
+      </c>
+      <c r="M34" s="7">
+        <v>14965.26</v>
+      </c>
+      <c r="N34" s="6">
+        <v>1</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P34" s="8">
+        <v>374.13</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>0</v>
+      </c>
+      <c r="R34" s="7">
+        <v>0</v>
+      </c>
+      <c r="S34" s="9">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U34" s="10">
+        <v>68418</v>
+      </c>
+      <c r="V34" s="11">
+        <v>11</v>
+      </c>
+      <c r="W34" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X34" s="12">
+        <v>0.39166669999999998</v>
+      </c>
+      <c r="Y34" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG34" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI34" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ34" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK34" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR34" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>1</v>
+      </c>
+      <c r="B35" s="2">
+        <v>2</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F35" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G35" s="5">
+        <v>7</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L35" s="6">
+        <v>41</v>
+      </c>
+      <c r="M35" s="7">
+        <v>15339.39</v>
+      </c>
+      <c r="N35" s="6">
+        <v>1</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P35" s="8">
+        <v>374.13</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>0</v>
+      </c>
+      <c r="R35" s="7">
+        <v>0</v>
+      </c>
+      <c r="S35" s="9">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U35" s="10">
+        <v>68418</v>
+      </c>
+      <c r="V35" s="11">
+        <v>11</v>
+      </c>
+      <c r="W35" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X35" s="12">
+        <v>0.39166669999999998</v>
+      </c>
+      <c r="Y35" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG35" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI35" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ35" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK35" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM35" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR35" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>1</v>
+      </c>
+      <c r="B36" s="2">
+        <v>2</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F36" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G36" s="5">
+        <v>8</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L36" s="6">
+        <v>42</v>
+      </c>
+      <c r="M36" s="7">
+        <v>15713.52</v>
+      </c>
+      <c r="N36" s="6">
+        <v>1</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P36" s="8">
+        <v>374.13</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0</v>
+      </c>
+      <c r="R36" s="7">
+        <v>0</v>
+      </c>
+      <c r="S36" s="9">
+        <v>0</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U36" s="10">
+        <v>68418</v>
+      </c>
+      <c r="V36" s="11">
+        <v>11</v>
+      </c>
+      <c r="W36" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X36" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y36" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI36" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ36" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK36" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR36" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>1</v>
+      </c>
+      <c r="B37" s="2">
+        <v>2</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F37" s="4">
+        <v>46314</v>
+      </c>
+      <c r="G37" s="5">
+        <v>9</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L37" s="6">
+        <v>43</v>
+      </c>
+      <c r="M37" s="7">
+        <v>16087.65</v>
+      </c>
+      <c r="N37" s="6">
+        <v>1</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P37" s="8">
+        <v>374.13</v>
+      </c>
+      <c r="Q37" s="6">
+        <v>0</v>
+      </c>
+      <c r="R37" s="7">
+        <v>0</v>
+      </c>
+      <c r="S37" s="9">
+        <v>0</v>
+      </c>
+      <c r="T37" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U37" s="10">
+        <v>68418</v>
+      </c>
+      <c r="V37" s="11">
+        <v>11</v>
+      </c>
+      <c r="W37" s="4">
+        <v>46314</v>
+      </c>
+      <c r="X37" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y37" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG37" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI37" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ37" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK37" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL37" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM37" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR37" s="3" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F9F031B-6368-4EDC-8FC1-F757857B03BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7777F3E1-D843-4D5A-A81C-5E58C43CF23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7777F3E1-D843-4D5A-A81C-5E58C43CF23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{605DA410-27E1-4CD4-822D-9125EE326F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B30B092-9CDD-41F3-ACD9-FA7AF19F3C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE2100CB-61CD-4659-BE79-75E122875BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6722" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6992" uniqueCount="445">
   <si>
     <t>Sel</t>
   </si>
@@ -1213,6 +1213,51 @@
     <t>1881700005502</t>
   </si>
   <si>
+    <t>1881700005305</t>
+  </si>
+  <si>
+    <t>1881700005503</t>
+  </si>
+  <si>
+    <t>1881700005504</t>
+  </si>
+  <si>
+    <t>1881700005505</t>
+  </si>
+  <si>
+    <t>1881700005506</t>
+  </si>
+  <si>
+    <t>1881700005507</t>
+  </si>
+  <si>
+    <t>1881700005508</t>
+  </si>
+  <si>
+    <t>1881700005509</t>
+  </si>
+  <si>
+    <t>1881700005510</t>
+  </si>
+  <si>
+    <t>1881700005511</t>
+  </si>
+  <si>
+    <t>1881700005512</t>
+  </si>
+  <si>
+    <t>1881700005513</t>
+  </si>
+  <si>
+    <t>1881700005514</t>
+  </si>
+  <si>
+    <t>1881700005515</t>
+  </si>
+  <si>
+    <t>1881700005516</t>
+  </si>
+  <si>
     <t>10096354</t>
   </si>
   <si>
@@ -1885,7 +1930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR372"/>
+  <dimension ref="A1:AR387"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -47858,10 +47903,10 @@
         <v>2</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>397</v>
+        <v>44</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>398</v>
+        <v>45</v>
       </c>
       <c r="E344" s="3" t="s">
         <v>46</v>
@@ -47870,7 +47915,7 @@
         <v>46316</v>
       </c>
       <c r="G344" s="5">
-        <v>1</v>
+        <v>976</v>
       </c>
       <c r="H344" s="3" t="s">
         <v>47</v>
@@ -47885,19 +47930,19 @@
         <v>50</v>
       </c>
       <c r="L344" s="6">
-        <v>19</v>
+        <v>574</v>
       </c>
       <c r="M344" s="7">
-        <v>6390.7</v>
+        <v>97872.34</v>
       </c>
       <c r="N344" s="6">
         <v>1</v>
       </c>
       <c r="O344" s="3" t="s">
-        <v>399</v>
+        <v>51</v>
       </c>
       <c r="P344" s="8">
-        <v>336.35</v>
+        <v>170.51</v>
       </c>
       <c r="Q344" s="6">
         <v>0</v>
@@ -47912,7 +47957,7 @@
         <v>52</v>
       </c>
       <c r="U344" s="10">
-        <v>68501</v>
+        <v>68459</v>
       </c>
       <c r="V344" s="11">
         <v>11</v>
@@ -47921,7 +47966,7 @@
         <v>46316</v>
       </c>
       <c r="X344" s="12">
-        <v>0.3229167</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="Y344" s="10">
         <v>0</v>
@@ -47954,7 +47999,7 @@
         <v>53</v>
       </c>
       <c r="AI344" s="3" t="s">
-        <v>400</v>
+        <v>54</v>
       </c>
       <c r="AJ344" s="3" t="s">
         <v>52</v>
@@ -47981,7 +48026,7 @@
         <v>53</v>
       </c>
       <c r="AR344" s="3" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="345" spans="1:44" x14ac:dyDescent="0.3">
@@ -47992,10 +48037,10 @@
         <v>2</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>397</v>
+        <v>44</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>398</v>
+        <v>45</v>
       </c>
       <c r="E345" s="3" t="s">
         <v>46</v>
@@ -48004,7 +48049,7 @@
         <v>46316</v>
       </c>
       <c r="G345" s="5">
-        <v>2</v>
+        <v>977</v>
       </c>
       <c r="H345" s="3" t="s">
         <v>47</v>
@@ -48019,19 +48064,19 @@
         <v>50</v>
       </c>
       <c r="L345" s="6">
-        <v>20</v>
+        <v>575</v>
       </c>
       <c r="M345" s="7">
-        <v>6727.05</v>
+        <v>98042.85</v>
       </c>
       <c r="N345" s="6">
         <v>1</v>
       </c>
       <c r="O345" s="3" t="s">
-        <v>399</v>
+        <v>51</v>
       </c>
       <c r="P345" s="8">
-        <v>336.35</v>
+        <v>170.51</v>
       </c>
       <c r="Q345" s="6">
         <v>0</v>
@@ -48046,7 +48091,7 @@
         <v>52</v>
       </c>
       <c r="U345" s="10">
-        <v>68501</v>
+        <v>68459</v>
       </c>
       <c r="V345" s="11">
         <v>11</v>
@@ -48055,7 +48100,7 @@
         <v>46316</v>
       </c>
       <c r="X345" s="12">
-        <v>0.3229167</v>
+        <v>0.49652780000000002</v>
       </c>
       <c r="Y345" s="10">
         <v>0</v>
@@ -48088,7 +48133,7 @@
         <v>53</v>
       </c>
       <c r="AI345" s="3" t="s">
-        <v>400</v>
+        <v>54</v>
       </c>
       <c r="AJ345" s="3" t="s">
         <v>52</v>
@@ -48115,7 +48160,7 @@
         <v>53</v>
       </c>
       <c r="AR345" s="3" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="346" spans="1:44" x14ac:dyDescent="0.3">
@@ -48126,10 +48171,10 @@
         <v>2</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>397</v>
+        <v>44</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>398</v>
+        <v>45</v>
       </c>
       <c r="E346" s="3" t="s">
         <v>46</v>
@@ -48138,7 +48183,7 @@
         <v>46316</v>
       </c>
       <c r="G346" s="5">
-        <v>3</v>
+        <v>978</v>
       </c>
       <c r="H346" s="3" t="s">
         <v>47</v>
@@ -48153,19 +48198,19 @@
         <v>50</v>
       </c>
       <c r="L346" s="6">
-        <v>21</v>
+        <v>576</v>
       </c>
       <c r="M346" s="7">
-        <v>7063.41</v>
+        <v>98213.36</v>
       </c>
       <c r="N346" s="6">
         <v>1</v>
       </c>
       <c r="O346" s="3" t="s">
-        <v>399</v>
+        <v>51</v>
       </c>
       <c r="P346" s="8">
-        <v>336.35</v>
+        <v>170.51</v>
       </c>
       <c r="Q346" s="6">
         <v>0</v>
@@ -48180,7 +48225,7 @@
         <v>52</v>
       </c>
       <c r="U346" s="10">
-        <v>68501</v>
+        <v>68459</v>
       </c>
       <c r="V346" s="11">
         <v>11</v>
@@ -48189,7 +48234,7 @@
         <v>46316</v>
       </c>
       <c r="X346" s="12">
-        <v>0.3229167</v>
+        <v>0.49652780000000002</v>
       </c>
       <c r="Y346" s="10">
         <v>0</v>
@@ -48222,7 +48267,7 @@
         <v>53</v>
       </c>
       <c r="AI346" s="3" t="s">
-        <v>400</v>
+        <v>54</v>
       </c>
       <c r="AJ346" s="3" t="s">
         <v>52</v>
@@ -48249,7 +48294,7 @@
         <v>53</v>
       </c>
       <c r="AR346" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="347" spans="1:44" x14ac:dyDescent="0.3">
@@ -48260,10 +48305,10 @@
         <v>2</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>397</v>
+        <v>44</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>398</v>
+        <v>45</v>
       </c>
       <c r="E347" s="3" t="s">
         <v>46</v>
@@ -48272,7 +48317,7 @@
         <v>46316</v>
       </c>
       <c r="G347" s="5">
-        <v>4</v>
+        <v>979</v>
       </c>
       <c r="H347" s="3" t="s">
         <v>47</v>
@@ -48287,19 +48332,19 @@
         <v>50</v>
       </c>
       <c r="L347" s="6">
-        <v>22</v>
+        <v>577</v>
       </c>
       <c r="M347" s="7">
-        <v>7399.76</v>
+        <v>98383.87</v>
       </c>
       <c r="N347" s="6">
         <v>1</v>
       </c>
       <c r="O347" s="3" t="s">
-        <v>399</v>
+        <v>51</v>
       </c>
       <c r="P347" s="8">
-        <v>336.35</v>
+        <v>170.51</v>
       </c>
       <c r="Q347" s="6">
         <v>0</v>
@@ -48314,7 +48359,7 @@
         <v>52</v>
       </c>
       <c r="U347" s="10">
-        <v>68501</v>
+        <v>68459</v>
       </c>
       <c r="V347" s="11">
         <v>11</v>
@@ -48323,7 +48368,7 @@
         <v>46316</v>
       </c>
       <c r="X347" s="12">
-        <v>0.3229167</v>
+        <v>0.49652780000000002</v>
       </c>
       <c r="Y347" s="10">
         <v>0</v>
@@ -48356,34 +48401,34 @@
         <v>53</v>
       </c>
       <c r="AI347" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ347" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK347" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL347" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM347" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN347" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO347" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP347" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ347" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR347" s="3" t="s">
         <v>400</v>
-      </c>
-      <c r="AJ347" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AK347" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL347" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM347" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN347" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO347" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP347" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ347" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR347" s="3" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="348" spans="1:44" x14ac:dyDescent="0.3">
@@ -48394,10 +48439,10 @@
         <v>2</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>397</v>
+        <v>44</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>398</v>
+        <v>45</v>
       </c>
       <c r="E348" s="3" t="s">
         <v>46</v>
@@ -48406,7 +48451,7 @@
         <v>46316</v>
       </c>
       <c r="G348" s="5">
-        <v>5</v>
+        <v>980</v>
       </c>
       <c r="H348" s="3" t="s">
         <v>47</v>
@@ -48421,19 +48466,19 @@
         <v>50</v>
       </c>
       <c r="L348" s="6">
-        <v>23</v>
+        <v>578</v>
       </c>
       <c r="M348" s="7">
-        <v>7736.11</v>
+        <v>98554.38</v>
       </c>
       <c r="N348" s="6">
         <v>1</v>
       </c>
       <c r="O348" s="3" t="s">
-        <v>399</v>
+        <v>51</v>
       </c>
       <c r="P348" s="8">
-        <v>336.35</v>
+        <v>170.51</v>
       </c>
       <c r="Q348" s="6">
         <v>0</v>
@@ -48448,7 +48493,7 @@
         <v>52</v>
       </c>
       <c r="U348" s="10">
-        <v>68501</v>
+        <v>68459</v>
       </c>
       <c r="V348" s="11">
         <v>11</v>
@@ -48457,7 +48502,7 @@
         <v>46316</v>
       </c>
       <c r="X348" s="12">
-        <v>0.3229167</v>
+        <v>0.49652780000000002</v>
       </c>
       <c r="Y348" s="10">
         <v>0</v>
@@ -48490,7 +48535,7 @@
         <v>53</v>
       </c>
       <c r="AI348" s="3" t="s">
-        <v>400</v>
+        <v>54</v>
       </c>
       <c r="AJ348" s="3" t="s">
         <v>52</v>
@@ -48517,7 +48562,7 @@
         <v>53</v>
       </c>
       <c r="AR348" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="349" spans="1:44" x14ac:dyDescent="0.3">
@@ -48528,10 +48573,10 @@
         <v>2</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>397</v>
+        <v>44</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>398</v>
+        <v>45</v>
       </c>
       <c r="E349" s="3" t="s">
         <v>46</v>
@@ -48540,7 +48585,7 @@
         <v>46316</v>
       </c>
       <c r="G349" s="5">
-        <v>6</v>
+        <v>981</v>
       </c>
       <c r="H349" s="3" t="s">
         <v>47</v>
@@ -48555,19 +48600,19 @@
         <v>50</v>
       </c>
       <c r="L349" s="6">
-        <v>24</v>
+        <v>579</v>
       </c>
       <c r="M349" s="7">
-        <v>8072.46</v>
+        <v>98724.89</v>
       </c>
       <c r="N349" s="6">
         <v>1</v>
       </c>
       <c r="O349" s="3" t="s">
-        <v>399</v>
+        <v>51</v>
       </c>
       <c r="P349" s="8">
-        <v>336.35</v>
+        <v>170.51</v>
       </c>
       <c r="Q349" s="6">
         <v>0</v>
@@ -48582,7 +48627,7 @@
         <v>52</v>
       </c>
       <c r="U349" s="10">
-        <v>68501</v>
+        <v>68459</v>
       </c>
       <c r="V349" s="11">
         <v>11</v>
@@ -48591,7 +48636,7 @@
         <v>46316</v>
       </c>
       <c r="X349" s="12">
-        <v>0.3229167</v>
+        <v>0.49652780000000002</v>
       </c>
       <c r="Y349" s="10">
         <v>0</v>
@@ -48624,7 +48669,7 @@
         <v>53</v>
       </c>
       <c r="AI349" s="3" t="s">
-        <v>400</v>
+        <v>54</v>
       </c>
       <c r="AJ349" s="3" t="s">
         <v>52</v>
@@ -48651,7 +48696,7 @@
         <v>53</v>
       </c>
       <c r="AR349" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="350" spans="1:44" x14ac:dyDescent="0.3">
@@ -48662,10 +48707,10 @@
         <v>2</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>397</v>
+        <v>44</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>398</v>
+        <v>45</v>
       </c>
       <c r="E350" s="3" t="s">
         <v>46</v>
@@ -48674,7 +48719,7 @@
         <v>46316</v>
       </c>
       <c r="G350" s="5">
-        <v>7</v>
+        <v>982</v>
       </c>
       <c r="H350" s="3" t="s">
         <v>47</v>
@@ -48689,19 +48734,19 @@
         <v>50</v>
       </c>
       <c r="L350" s="6">
-        <v>25</v>
+        <v>580</v>
       </c>
       <c r="M350" s="7">
-        <v>8408.82</v>
+        <v>98895.4</v>
       </c>
       <c r="N350" s="6">
         <v>1</v>
       </c>
       <c r="O350" s="3" t="s">
-        <v>399</v>
+        <v>51</v>
       </c>
       <c r="P350" s="8">
-        <v>336.35</v>
+        <v>170.51</v>
       </c>
       <c r="Q350" s="6">
         <v>0</v>
@@ -48716,7 +48761,7 @@
         <v>52</v>
       </c>
       <c r="U350" s="10">
-        <v>68501</v>
+        <v>68459</v>
       </c>
       <c r="V350" s="11">
         <v>11</v>
@@ -48725,7 +48770,7 @@
         <v>46316</v>
       </c>
       <c r="X350" s="12">
-        <v>0.3229167</v>
+        <v>0.49652780000000002</v>
       </c>
       <c r="Y350" s="10">
         <v>0</v>
@@ -48758,7 +48803,7 @@
         <v>53</v>
       </c>
       <c r="AI350" s="3" t="s">
-        <v>400</v>
+        <v>54</v>
       </c>
       <c r="AJ350" s="3" t="s">
         <v>52</v>
@@ -48785,7 +48830,7 @@
         <v>53</v>
       </c>
       <c r="AR350" s="3" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="351" spans="1:44" x14ac:dyDescent="0.3">
@@ -48796,10 +48841,10 @@
         <v>2</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>397</v>
+        <v>44</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>398</v>
+        <v>45</v>
       </c>
       <c r="E351" s="3" t="s">
         <v>46</v>
@@ -48808,7 +48853,7 @@
         <v>46316</v>
       </c>
       <c r="G351" s="5">
-        <v>8</v>
+        <v>983</v>
       </c>
       <c r="H351" s="3" t="s">
         <v>47</v>
@@ -48823,19 +48868,19 @@
         <v>50</v>
       </c>
       <c r="L351" s="6">
-        <v>26</v>
+        <v>581</v>
       </c>
       <c r="M351" s="7">
-        <v>8745.17</v>
+        <v>99065.91</v>
       </c>
       <c r="N351" s="6">
         <v>1</v>
       </c>
       <c r="O351" s="3" t="s">
-        <v>399</v>
+        <v>51</v>
       </c>
       <c r="P351" s="8">
-        <v>336.35</v>
+        <v>170.51</v>
       </c>
       <c r="Q351" s="6">
         <v>0</v>
@@ -48850,7 +48895,7 @@
         <v>52</v>
       </c>
       <c r="U351" s="10">
-        <v>68501</v>
+        <v>68459</v>
       </c>
       <c r="V351" s="11">
         <v>11</v>
@@ -48859,7 +48904,7 @@
         <v>46316</v>
       </c>
       <c r="X351" s="12">
-        <v>0.3229167</v>
+        <v>0.49652780000000002</v>
       </c>
       <c r="Y351" s="10">
         <v>0</v>
@@ -48892,7 +48937,7 @@
         <v>53</v>
       </c>
       <c r="AI351" s="3" t="s">
-        <v>400</v>
+        <v>54</v>
       </c>
       <c r="AJ351" s="3" t="s">
         <v>52</v>
@@ -48919,7 +48964,7 @@
         <v>53</v>
       </c>
       <c r="AR351" s="3" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="352" spans="1:44" x14ac:dyDescent="0.3">
@@ -48930,10 +48975,10 @@
         <v>2</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>397</v>
+        <v>44</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>398</v>
+        <v>45</v>
       </c>
       <c r="E352" s="3" t="s">
         <v>46</v>
@@ -48942,7 +48987,7 @@
         <v>46316</v>
       </c>
       <c r="G352" s="5">
-        <v>9</v>
+        <v>984</v>
       </c>
       <c r="H352" s="3" t="s">
         <v>47</v>
@@ -48957,19 +49002,19 @@
         <v>50</v>
       </c>
       <c r="L352" s="6">
-        <v>27</v>
+        <v>582</v>
       </c>
       <c r="M352" s="7">
-        <v>9081.52</v>
+        <v>99236.42</v>
       </c>
       <c r="N352" s="6">
         <v>1</v>
       </c>
       <c r="O352" s="3" t="s">
-        <v>399</v>
+        <v>51</v>
       </c>
       <c r="P352" s="8">
-        <v>336.35</v>
+        <v>170.51</v>
       </c>
       <c r="Q352" s="6">
         <v>0</v>
@@ -48984,7 +49029,7 @@
         <v>52</v>
       </c>
       <c r="U352" s="10">
-        <v>68501</v>
+        <v>68459</v>
       </c>
       <c r="V352" s="11">
         <v>11</v>
@@ -48993,7 +49038,7 @@
         <v>46316</v>
       </c>
       <c r="X352" s="12">
-        <v>0.3229167</v>
+        <v>0.49652780000000002</v>
       </c>
       <c r="Y352" s="10">
         <v>0</v>
@@ -49026,7 +49071,7 @@
         <v>53</v>
       </c>
       <c r="AI352" s="3" t="s">
-        <v>400</v>
+        <v>54</v>
       </c>
       <c r="AJ352" s="3" t="s">
         <v>52</v>
@@ -49053,7 +49098,7 @@
         <v>53</v>
       </c>
       <c r="AR352" s="3" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="353" spans="1:44" x14ac:dyDescent="0.3">
@@ -49064,10 +49109,10 @@
         <v>2</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>397</v>
+        <v>44</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>398</v>
+        <v>45</v>
       </c>
       <c r="E353" s="3" t="s">
         <v>46</v>
@@ -49076,7 +49121,7 @@
         <v>46316</v>
       </c>
       <c r="G353" s="5">
-        <v>10</v>
+        <v>985</v>
       </c>
       <c r="H353" s="3" t="s">
         <v>47</v>
@@ -49091,19 +49136,19 @@
         <v>50</v>
       </c>
       <c r="L353" s="6">
-        <v>28</v>
+        <v>583</v>
       </c>
       <c r="M353" s="7">
-        <v>9417.8700000000008</v>
+        <v>99406.93</v>
       </c>
       <c r="N353" s="6">
         <v>1</v>
       </c>
       <c r="O353" s="3" t="s">
-        <v>399</v>
+        <v>51</v>
       </c>
       <c r="P353" s="8">
-        <v>336.35</v>
+        <v>170.51</v>
       </c>
       <c r="Q353" s="6">
         <v>0</v>
@@ -49118,7 +49163,7 @@
         <v>52</v>
       </c>
       <c r="U353" s="10">
-        <v>68501</v>
+        <v>68459</v>
       </c>
       <c r="V353" s="11">
         <v>11</v>
@@ -49127,7 +49172,7 @@
         <v>46316</v>
       </c>
       <c r="X353" s="12">
-        <v>0.3229167</v>
+        <v>0.49652780000000002</v>
       </c>
       <c r="Y353" s="10">
         <v>0</v>
@@ -49160,7 +49205,7 @@
         <v>53</v>
       </c>
       <c r="AI353" s="3" t="s">
-        <v>400</v>
+        <v>54</v>
       </c>
       <c r="AJ353" s="3" t="s">
         <v>52</v>
@@ -49187,7 +49232,7 @@
         <v>53</v>
       </c>
       <c r="AR353" s="3" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="354" spans="1:44" x14ac:dyDescent="0.3">
@@ -49198,10 +49243,10 @@
         <v>2</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>397</v>
+        <v>44</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>398</v>
+        <v>45</v>
       </c>
       <c r="E354" s="3" t="s">
         <v>46</v>
@@ -49210,7 +49255,7 @@
         <v>46316</v>
       </c>
       <c r="G354" s="5">
-        <v>11</v>
+        <v>986</v>
       </c>
       <c r="H354" s="3" t="s">
         <v>47</v>
@@ -49225,19 +49270,19 @@
         <v>50</v>
       </c>
       <c r="L354" s="6">
-        <v>29</v>
+        <v>584</v>
       </c>
       <c r="M354" s="7">
-        <v>9754.23</v>
+        <v>99577.44</v>
       </c>
       <c r="N354" s="6">
         <v>1</v>
       </c>
       <c r="O354" s="3" t="s">
-        <v>399</v>
+        <v>51</v>
       </c>
       <c r="P354" s="8">
-        <v>336.35</v>
+        <v>170.51</v>
       </c>
       <c r="Q354" s="6">
         <v>0</v>
@@ -49252,7 +49297,7 @@
         <v>52</v>
       </c>
       <c r="U354" s="10">
-        <v>68501</v>
+        <v>68459</v>
       </c>
       <c r="V354" s="11">
         <v>11</v>
@@ -49261,7 +49306,7 @@
         <v>46316</v>
       </c>
       <c r="X354" s="12">
-        <v>0.3229167</v>
+        <v>0.49652780000000002</v>
       </c>
       <c r="Y354" s="10">
         <v>0</v>
@@ -49294,7 +49339,7 @@
         <v>53</v>
       </c>
       <c r="AI354" s="3" t="s">
-        <v>400</v>
+        <v>54</v>
       </c>
       <c r="AJ354" s="3" t="s">
         <v>52</v>
@@ -49321,7 +49366,7 @@
         <v>53</v>
       </c>
       <c r="AR354" s="3" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="355" spans="1:44" x14ac:dyDescent="0.3">
@@ -49332,10 +49377,10 @@
         <v>2</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>397</v>
+        <v>44</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>398</v>
+        <v>45</v>
       </c>
       <c r="E355" s="3" t="s">
         <v>46</v>
@@ -49344,7 +49389,7 @@
         <v>46316</v>
       </c>
       <c r="G355" s="5">
-        <v>12</v>
+        <v>987</v>
       </c>
       <c r="H355" s="3" t="s">
         <v>47</v>
@@ -49359,19 +49404,19 @@
         <v>50</v>
       </c>
       <c r="L355" s="6">
-        <v>30</v>
+        <v>585</v>
       </c>
       <c r="M355" s="7">
-        <v>10090.58</v>
+        <v>99747.95</v>
       </c>
       <c r="N355" s="6">
         <v>1</v>
       </c>
       <c r="O355" s="3" t="s">
-        <v>399</v>
+        <v>51</v>
       </c>
       <c r="P355" s="8">
-        <v>336.35</v>
+        <v>170.51</v>
       </c>
       <c r="Q355" s="6">
         <v>0</v>
@@ -49386,7 +49431,7 @@
         <v>52</v>
       </c>
       <c r="U355" s="10">
-        <v>68501</v>
+        <v>68459</v>
       </c>
       <c r="V355" s="11">
         <v>11</v>
@@ -49395,7 +49440,7 @@
         <v>46316</v>
       </c>
       <c r="X355" s="12">
-        <v>0.3229167</v>
+        <v>0.49652780000000002</v>
       </c>
       <c r="Y355" s="10">
         <v>0</v>
@@ -49428,7 +49473,7 @@
         <v>53</v>
       </c>
       <c r="AI355" s="3" t="s">
-        <v>400</v>
+        <v>54</v>
       </c>
       <c r="AJ355" s="3" t="s">
         <v>52</v>
@@ -49455,7 +49500,7 @@
         <v>53</v>
       </c>
       <c r="AR355" s="3" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="356" spans="1:44" x14ac:dyDescent="0.3">
@@ -49466,10 +49511,10 @@
         <v>2</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>397</v>
+        <v>44</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>398</v>
+        <v>45</v>
       </c>
       <c r="E356" s="3" t="s">
         <v>46</v>
@@ -49478,7 +49523,7 @@
         <v>46316</v>
       </c>
       <c r="G356" s="5">
-        <v>13</v>
+        <v>988</v>
       </c>
       <c r="H356" s="3" t="s">
         <v>47</v>
@@ -49493,19 +49538,19 @@
         <v>50</v>
       </c>
       <c r="L356" s="6">
-        <v>31</v>
+        <v>586</v>
       </c>
       <c r="M356" s="7">
-        <v>10426.93</v>
+        <v>99918.46</v>
       </c>
       <c r="N356" s="6">
         <v>1</v>
       </c>
       <c r="O356" s="3" t="s">
-        <v>399</v>
+        <v>51</v>
       </c>
       <c r="P356" s="8">
-        <v>336.35</v>
+        <v>170.51</v>
       </c>
       <c r="Q356" s="6">
         <v>0</v>
@@ -49520,7 +49565,7 @@
         <v>52</v>
       </c>
       <c r="U356" s="10">
-        <v>68501</v>
+        <v>68459</v>
       </c>
       <c r="V356" s="11">
         <v>11</v>
@@ -49529,7 +49574,7 @@
         <v>46316</v>
       </c>
       <c r="X356" s="12">
-        <v>0.3229167</v>
+        <v>0.49652780000000002</v>
       </c>
       <c r="Y356" s="10">
         <v>0</v>
@@ -49562,7 +49607,7 @@
         <v>53</v>
       </c>
       <c r="AI356" s="3" t="s">
-        <v>400</v>
+        <v>54</v>
       </c>
       <c r="AJ356" s="3" t="s">
         <v>52</v>
@@ -49589,7 +49634,7 @@
         <v>53</v>
       </c>
       <c r="AR356" s="3" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="357" spans="1:44" x14ac:dyDescent="0.3">
@@ -49600,10 +49645,10 @@
         <v>2</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>397</v>
+        <v>44</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>398</v>
+        <v>45</v>
       </c>
       <c r="E357" s="3" t="s">
         <v>46</v>
@@ -49612,7 +49657,7 @@
         <v>46316</v>
       </c>
       <c r="G357" s="5">
-        <v>14</v>
+        <v>989</v>
       </c>
       <c r="H357" s="3" t="s">
         <v>47</v>
@@ -49627,19 +49672,19 @@
         <v>50</v>
       </c>
       <c r="L357" s="6">
-        <v>32</v>
+        <v>587</v>
       </c>
       <c r="M357" s="7">
-        <v>10763.28</v>
+        <v>100088.96000000001</v>
       </c>
       <c r="N357" s="6">
         <v>1</v>
       </c>
       <c r="O357" s="3" t="s">
-        <v>399</v>
+        <v>51</v>
       </c>
       <c r="P357" s="8">
-        <v>336.35</v>
+        <v>170.51</v>
       </c>
       <c r="Q357" s="6">
         <v>0</v>
@@ -49654,7 +49699,7 @@
         <v>52</v>
       </c>
       <c r="U357" s="10">
-        <v>68501</v>
+        <v>68459</v>
       </c>
       <c r="V357" s="11">
         <v>11</v>
@@ -49663,7 +49708,7 @@
         <v>46316</v>
       </c>
       <c r="X357" s="12">
-        <v>0.3229167</v>
+        <v>0.49652780000000002</v>
       </c>
       <c r="Y357" s="10">
         <v>0</v>
@@ -49696,7 +49741,7 @@
         <v>53</v>
       </c>
       <c r="AI357" s="3" t="s">
-        <v>400</v>
+        <v>54</v>
       </c>
       <c r="AJ357" s="3" t="s">
         <v>52</v>
@@ -49723,7 +49768,7 @@
         <v>53</v>
       </c>
       <c r="AR357" s="3" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="358" spans="1:44" x14ac:dyDescent="0.3">
@@ -49734,10 +49779,10 @@
         <v>2</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>397</v>
+        <v>44</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>398</v>
+        <v>45</v>
       </c>
       <c r="E358" s="3" t="s">
         <v>46</v>
@@ -49746,7 +49791,7 @@
         <v>46316</v>
       </c>
       <c r="G358" s="5">
-        <v>15</v>
+        <v>990</v>
       </c>
       <c r="H358" s="3" t="s">
         <v>47</v>
@@ -49761,19 +49806,19 @@
         <v>50</v>
       </c>
       <c r="L358" s="6">
-        <v>33</v>
+        <v>588</v>
       </c>
       <c r="M358" s="7">
-        <v>11099.64</v>
+        <v>100259.47</v>
       </c>
       <c r="N358" s="6">
         <v>1</v>
       </c>
       <c r="O358" s="3" t="s">
-        <v>399</v>
+        <v>51</v>
       </c>
       <c r="P358" s="8">
-        <v>336.35</v>
+        <v>170.51</v>
       </c>
       <c r="Q358" s="6">
         <v>0</v>
@@ -49788,7 +49833,7 @@
         <v>52</v>
       </c>
       <c r="U358" s="10">
-        <v>68501</v>
+        <v>68459</v>
       </c>
       <c r="V358" s="11">
         <v>11</v>
@@ -49797,7 +49842,7 @@
         <v>46316</v>
       </c>
       <c r="X358" s="12">
-        <v>0.3229167</v>
+        <v>0.49652780000000002</v>
       </c>
       <c r="Y358" s="10">
         <v>0</v>
@@ -49830,7 +49875,7 @@
         <v>53</v>
       </c>
       <c r="AI358" s="3" t="s">
-        <v>400</v>
+        <v>54</v>
       </c>
       <c r="AJ358" s="3" t="s">
         <v>52</v>
@@ -49857,7 +49902,7 @@
         <v>53</v>
       </c>
       <c r="AR358" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="359" spans="1:44" x14ac:dyDescent="0.3">
@@ -49868,10 +49913,10 @@
         <v>2</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="E359" s="3" t="s">
         <v>46</v>
@@ -49880,7 +49925,7 @@
         <v>46316</v>
       </c>
       <c r="G359" s="5">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H359" s="3" t="s">
         <v>47</v>
@@ -49895,16 +49940,16 @@
         <v>50</v>
       </c>
       <c r="L359" s="6">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="M359" s="7">
-        <v>11435.99</v>
+        <v>6390.7</v>
       </c>
       <c r="N359" s="6">
         <v>1</v>
       </c>
       <c r="O359" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="P359" s="8">
         <v>336.35</v>
@@ -49931,7 +49976,7 @@
         <v>46316</v>
       </c>
       <c r="X359" s="12">
-        <v>0.32986110000000002</v>
+        <v>0.3229167</v>
       </c>
       <c r="Y359" s="10">
         <v>0</v>
@@ -49964,7 +50009,7 @@
         <v>53</v>
       </c>
       <c r="AI359" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="AJ359" s="3" t="s">
         <v>52</v>
@@ -50002,10 +50047,10 @@
         <v>2</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="E360" s="3" t="s">
         <v>46</v>
@@ -50014,7 +50059,7 @@
         <v>46316</v>
       </c>
       <c r="G360" s="5">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H360" s="3" t="s">
         <v>47</v>
@@ -50029,16 +50074,16 @@
         <v>50</v>
       </c>
       <c r="L360" s="6">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="M360" s="7">
-        <v>11772.34</v>
+        <v>6727.05</v>
       </c>
       <c r="N360" s="6">
         <v>1</v>
       </c>
       <c r="O360" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="P360" s="8">
         <v>336.35</v>
@@ -50065,7 +50110,7 @@
         <v>46316</v>
       </c>
       <c r="X360" s="12">
-        <v>0.32986110000000002</v>
+        <v>0.3229167</v>
       </c>
       <c r="Y360" s="10">
         <v>0</v>
@@ -50098,7 +50143,7 @@
         <v>53</v>
       </c>
       <c r="AI360" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="AJ360" s="3" t="s">
         <v>52</v>
@@ -50136,10 +50181,10 @@
         <v>2</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="E361" s="3" t="s">
         <v>46</v>
@@ -50148,7 +50193,7 @@
         <v>46316</v>
       </c>
       <c r="G361" s="5">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H361" s="3" t="s">
         <v>47</v>
@@ -50163,16 +50208,16 @@
         <v>50</v>
       </c>
       <c r="L361" s="6">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="M361" s="7">
-        <v>12108.69</v>
+        <v>7063.41</v>
       </c>
       <c r="N361" s="6">
         <v>1</v>
       </c>
       <c r="O361" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="P361" s="8">
         <v>336.35</v>
@@ -50199,7 +50244,7 @@
         <v>46316</v>
       </c>
       <c r="X361" s="12">
-        <v>0.33680559999999998</v>
+        <v>0.3229167</v>
       </c>
       <c r="Y361" s="10">
         <v>0</v>
@@ -50232,7 +50277,7 @@
         <v>53</v>
       </c>
       <c r="AI361" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="AJ361" s="3" t="s">
         <v>52</v>
@@ -50270,10 +50315,10 @@
         <v>2</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="E362" s="3" t="s">
         <v>46</v>
@@ -50282,7 +50327,7 @@
         <v>46316</v>
       </c>
       <c r="G362" s="5">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H362" s="3" t="s">
         <v>47</v>
@@ -50297,16 +50342,16 @@
         <v>50</v>
       </c>
       <c r="L362" s="6">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="M362" s="7">
-        <v>12445.05</v>
+        <v>7399.76</v>
       </c>
       <c r="N362" s="6">
         <v>1</v>
       </c>
       <c r="O362" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="P362" s="8">
         <v>336.35</v>
@@ -50333,7 +50378,7 @@
         <v>46316</v>
       </c>
       <c r="X362" s="12">
-        <v>0.33680559999999998</v>
+        <v>0.3229167</v>
       </c>
       <c r="Y362" s="10">
         <v>0</v>
@@ -50366,7 +50411,7 @@
         <v>53</v>
       </c>
       <c r="AI362" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="AJ362" s="3" t="s">
         <v>52</v>
@@ -50404,10 +50449,10 @@
         <v>2</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="E363" s="3" t="s">
         <v>46</v>
@@ -50416,7 +50461,7 @@
         <v>46316</v>
       </c>
       <c r="G363" s="5">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H363" s="3" t="s">
         <v>47</v>
@@ -50431,16 +50476,16 @@
         <v>50</v>
       </c>
       <c r="L363" s="6">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="M363" s="7">
-        <v>12781.4</v>
+        <v>7736.11</v>
       </c>
       <c r="N363" s="6">
         <v>1</v>
       </c>
       <c r="O363" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="P363" s="8">
         <v>336.35</v>
@@ -50467,7 +50512,7 @@
         <v>46316</v>
       </c>
       <c r="X363" s="12">
-        <v>0.33680559999999998</v>
+        <v>0.3229167</v>
       </c>
       <c r="Y363" s="10">
         <v>0</v>
@@ -50500,7 +50545,7 @@
         <v>53</v>
       </c>
       <c r="AI363" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="AJ363" s="3" t="s">
         <v>52</v>
@@ -50538,10 +50583,10 @@
         <v>2</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="E364" s="3" t="s">
         <v>46</v>
@@ -50550,7 +50595,7 @@
         <v>46316</v>
       </c>
       <c r="G364" s="5">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H364" s="3" t="s">
         <v>47</v>
@@ -50565,16 +50610,16 @@
         <v>50</v>
       </c>
       <c r="L364" s="6">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="M364" s="7">
-        <v>13117.75</v>
+        <v>8072.46</v>
       </c>
       <c r="N364" s="6">
         <v>1</v>
       </c>
       <c r="O364" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="P364" s="8">
         <v>336.35</v>
@@ -50601,7 +50646,7 @@
         <v>46316</v>
       </c>
       <c r="X364" s="12">
-        <v>0.33680559999999998</v>
+        <v>0.3229167</v>
       </c>
       <c r="Y364" s="10">
         <v>0</v>
@@ -50634,7 +50679,7 @@
         <v>53</v>
       </c>
       <c r="AI364" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="AJ364" s="3" t="s">
         <v>52</v>
@@ -50672,10 +50717,10 @@
         <v>2</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="E365" s="3" t="s">
         <v>46</v>
@@ -50684,7 +50729,7 @@
         <v>46316</v>
       </c>
       <c r="G365" s="5">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H365" s="3" t="s">
         <v>47</v>
@@ -50699,16 +50744,16 @@
         <v>50</v>
       </c>
       <c r="L365" s="6">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M365" s="7">
-        <v>13454.11</v>
+        <v>8408.82</v>
       </c>
       <c r="N365" s="6">
         <v>1</v>
       </c>
       <c r="O365" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="P365" s="8">
         <v>336.35</v>
@@ -50735,7 +50780,7 @@
         <v>46316</v>
       </c>
       <c r="X365" s="12">
-        <v>0.33680559999999998</v>
+        <v>0.3229167</v>
       </c>
       <c r="Y365" s="10">
         <v>0</v>
@@ -50768,7 +50813,7 @@
         <v>53</v>
       </c>
       <c r="AI365" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="AJ365" s="3" t="s">
         <v>52</v>
@@ -50806,10 +50851,10 @@
         <v>2</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="E366" s="3" t="s">
         <v>46</v>
@@ -50818,7 +50863,7 @@
         <v>46316</v>
       </c>
       <c r="G366" s="5">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="H366" s="3" t="s">
         <v>47</v>
@@ -50833,16 +50878,16 @@
         <v>50</v>
       </c>
       <c r="L366" s="6">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="M366" s="7">
-        <v>13790.46</v>
+        <v>8745.17</v>
       </c>
       <c r="N366" s="6">
         <v>1</v>
       </c>
       <c r="O366" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="P366" s="8">
         <v>336.35</v>
@@ -50869,7 +50914,7 @@
         <v>46316</v>
       </c>
       <c r="X366" s="12">
-        <v>0.33680559999999998</v>
+        <v>0.3229167</v>
       </c>
       <c r="Y366" s="10">
         <v>0</v>
@@ -50902,7 +50947,7 @@
         <v>53</v>
       </c>
       <c r="AI366" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="AJ366" s="3" t="s">
         <v>52</v>
@@ -50940,10 +50985,10 @@
         <v>2</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="E367" s="3" t="s">
         <v>46</v>
@@ -50952,7 +50997,7 @@
         <v>46316</v>
       </c>
       <c r="G367" s="5">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H367" s="3" t="s">
         <v>47</v>
@@ -50967,16 +51012,16 @@
         <v>50</v>
       </c>
       <c r="L367" s="6">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="M367" s="7">
-        <v>14126.81</v>
+        <v>9081.52</v>
       </c>
       <c r="N367" s="6">
         <v>1</v>
       </c>
       <c r="O367" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="P367" s="8">
         <v>336.35</v>
@@ -51003,7 +51048,7 @@
         <v>46316</v>
       </c>
       <c r="X367" s="12">
-        <v>0.33750000000000002</v>
+        <v>0.3229167</v>
       </c>
       <c r="Y367" s="10">
         <v>0</v>
@@ -51036,7 +51081,7 @@
         <v>53</v>
       </c>
       <c r="AI367" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="AJ367" s="3" t="s">
         <v>52</v>
@@ -51074,10 +51119,10 @@
         <v>2</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="E368" s="3" t="s">
         <v>46</v>
@@ -51086,7 +51131,7 @@
         <v>46316</v>
       </c>
       <c r="G368" s="5">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H368" s="3" t="s">
         <v>47</v>
@@ -51101,16 +51146,16 @@
         <v>50</v>
       </c>
       <c r="L368" s="6">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="M368" s="7">
-        <v>14463.16</v>
+        <v>9417.8700000000008</v>
       </c>
       <c r="N368" s="6">
         <v>1</v>
       </c>
       <c r="O368" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="P368" s="8">
         <v>336.35</v>
@@ -51137,7 +51182,7 @@
         <v>46316</v>
       </c>
       <c r="X368" s="12">
-        <v>0.33750000000000002</v>
+        <v>0.3229167</v>
       </c>
       <c r="Y368" s="10">
         <v>0</v>
@@ -51170,7 +51215,7 @@
         <v>53</v>
       </c>
       <c r="AI368" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="AJ368" s="3" t="s">
         <v>52</v>
@@ -51208,10 +51253,10 @@
         <v>2</v>
       </c>
       <c r="C369" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="E369" s="3" t="s">
         <v>46</v>
@@ -51220,7 +51265,7 @@
         <v>46316</v>
       </c>
       <c r="G369" s="5">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H369" s="3" t="s">
         <v>47</v>
@@ -51235,16 +51280,16 @@
         <v>50</v>
       </c>
       <c r="L369" s="6">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="M369" s="7">
-        <v>14799.52</v>
+        <v>9754.23</v>
       </c>
       <c r="N369" s="6">
         <v>1</v>
       </c>
       <c r="O369" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="P369" s="8">
         <v>336.35</v>
@@ -51271,7 +51316,7 @@
         <v>46316</v>
       </c>
       <c r="X369" s="12">
-        <v>0.33750000000000002</v>
+        <v>0.3229167</v>
       </c>
       <c r="Y369" s="10">
         <v>0</v>
@@ -51304,7 +51349,7 @@
         <v>53</v>
       </c>
       <c r="AI369" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="AJ369" s="3" t="s">
         <v>52</v>
@@ -51342,10 +51387,10 @@
         <v>2</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="E370" s="3" t="s">
         <v>46</v>
@@ -51354,7 +51399,7 @@
         <v>46316</v>
       </c>
       <c r="G370" s="5">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H370" s="3" t="s">
         <v>47</v>
@@ -51369,16 +51414,16 @@
         <v>50</v>
       </c>
       <c r="L370" s="6">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="M370" s="7">
-        <v>15135.87</v>
+        <v>10090.58</v>
       </c>
       <c r="N370" s="6">
         <v>1</v>
       </c>
       <c r="O370" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="P370" s="8">
         <v>336.35</v>
@@ -51405,7 +51450,7 @@
         <v>46316</v>
       </c>
       <c r="X370" s="12">
-        <v>0.33750000000000002</v>
+        <v>0.3229167</v>
       </c>
       <c r="Y370" s="10">
         <v>0</v>
@@ -51438,7 +51483,7 @@
         <v>53</v>
       </c>
       <c r="AI370" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="AJ370" s="3" t="s">
         <v>52</v>
@@ -51476,10 +51521,10 @@
         <v>2</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="E371" s="3" t="s">
         <v>46</v>
@@ -51488,7 +51533,7 @@
         <v>46316</v>
       </c>
       <c r="G371" s="5">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H371" s="3" t="s">
         <v>47</v>
@@ -51503,16 +51548,16 @@
         <v>50</v>
       </c>
       <c r="L371" s="6">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="M371" s="7">
-        <v>15472.22</v>
+        <v>10426.93</v>
       </c>
       <c r="N371" s="6">
         <v>1</v>
       </c>
       <c r="O371" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="P371" s="8">
         <v>336.35</v>
@@ -51539,7 +51584,7 @@
         <v>46316</v>
       </c>
       <c r="X371" s="12">
-        <v>0.33750000000000002</v>
+        <v>0.3229167</v>
       </c>
       <c r="Y371" s="10">
         <v>0</v>
@@ -51572,7 +51617,7 @@
         <v>53</v>
       </c>
       <c r="AI371" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="AJ371" s="3" t="s">
         <v>52</v>
@@ -51610,10 +51655,10 @@
         <v>2</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="E372" s="3" t="s">
         <v>46</v>
@@ -51622,7 +51667,7 @@
         <v>46316</v>
       </c>
       <c r="G372" s="5">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="H372" s="3" t="s">
         <v>47</v>
@@ -51637,16 +51682,16 @@
         <v>50</v>
       </c>
       <c r="L372" s="6">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="M372" s="7">
-        <v>15808.57</v>
+        <v>10763.28</v>
       </c>
       <c r="N372" s="6">
         <v>1</v>
       </c>
       <c r="O372" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="P372" s="8">
         <v>336.35</v>
@@ -51673,7 +51718,7 @@
         <v>46316</v>
       </c>
       <c r="X372" s="12">
-        <v>0.33750000000000002</v>
+        <v>0.3229167</v>
       </c>
       <c r="Y372" s="10">
         <v>0</v>
@@ -51706,7 +51751,7 @@
         <v>53</v>
       </c>
       <c r="AI372" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="AJ372" s="3" t="s">
         <v>52</v>
@@ -51734,6 +51779,2016 @@
       </c>
       <c r="AR372" s="3" t="s">
         <v>429</v>
+      </c>
+    </row>
+    <row r="373" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A373" s="1">
+        <v>1</v>
+      </c>
+      <c r="B373" s="2">
+        <v>2</v>
+      </c>
+      <c r="C373" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D373" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E373" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F373" s="4">
+        <v>46316</v>
+      </c>
+      <c r="G373" s="5">
+        <v>15</v>
+      </c>
+      <c r="H373" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I373" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J373" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K373" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L373" s="6">
+        <v>33</v>
+      </c>
+      <c r="M373" s="7">
+        <v>11099.64</v>
+      </c>
+      <c r="N373" s="6">
+        <v>1</v>
+      </c>
+      <c r="O373" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="P373" s="8">
+        <v>336.35</v>
+      </c>
+      <c r="Q373" s="6">
+        <v>0</v>
+      </c>
+      <c r="R373" s="7">
+        <v>0</v>
+      </c>
+      <c r="S373" s="9">
+        <v>0</v>
+      </c>
+      <c r="T373" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U373" s="10">
+        <v>68501</v>
+      </c>
+      <c r="V373" s="11">
+        <v>11</v>
+      </c>
+      <c r="W373" s="4">
+        <v>46316</v>
+      </c>
+      <c r="X373" s="12">
+        <v>0.3229167</v>
+      </c>
+      <c r="Y373" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z373" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA373" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB373" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC373" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD373" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE373" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF373" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG373" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH373" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI373" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AJ373" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK373" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL373" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM373" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN373" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO373" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP373" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ373" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR373" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="374" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A374" s="1">
+        <v>1</v>
+      </c>
+      <c r="B374" s="2">
+        <v>2</v>
+      </c>
+      <c r="C374" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D374" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E374" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F374" s="4">
+        <v>46316</v>
+      </c>
+      <c r="G374" s="5">
+        <v>16</v>
+      </c>
+      <c r="H374" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I374" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J374" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K374" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L374" s="6">
+        <v>34</v>
+      </c>
+      <c r="M374" s="7">
+        <v>11435.99</v>
+      </c>
+      <c r="N374" s="6">
+        <v>1</v>
+      </c>
+      <c r="O374" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="P374" s="8">
+        <v>336.35</v>
+      </c>
+      <c r="Q374" s="6">
+        <v>0</v>
+      </c>
+      <c r="R374" s="7">
+        <v>0</v>
+      </c>
+      <c r="S374" s="9">
+        <v>0</v>
+      </c>
+      <c r="T374" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U374" s="10">
+        <v>68501</v>
+      </c>
+      <c r="V374" s="11">
+        <v>11</v>
+      </c>
+      <c r="W374" s="4">
+        <v>46316</v>
+      </c>
+      <c r="X374" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y374" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z374" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA374" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB374" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC374" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD374" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE374" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF374" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG374" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH374" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI374" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AJ374" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK374" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL374" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM374" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN374" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO374" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP374" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ374" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR374" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="375" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A375" s="1">
+        <v>1</v>
+      </c>
+      <c r="B375" s="2">
+        <v>2</v>
+      </c>
+      <c r="C375" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D375" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E375" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F375" s="4">
+        <v>46316</v>
+      </c>
+      <c r="G375" s="5">
+        <v>17</v>
+      </c>
+      <c r="H375" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I375" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J375" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K375" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L375" s="6">
+        <v>35</v>
+      </c>
+      <c r="M375" s="7">
+        <v>11772.34</v>
+      </c>
+      <c r="N375" s="6">
+        <v>1</v>
+      </c>
+      <c r="O375" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="P375" s="8">
+        <v>336.35</v>
+      </c>
+      <c r="Q375" s="6">
+        <v>0</v>
+      </c>
+      <c r="R375" s="7">
+        <v>0</v>
+      </c>
+      <c r="S375" s="9">
+        <v>0</v>
+      </c>
+      <c r="T375" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U375" s="10">
+        <v>68501</v>
+      </c>
+      <c r="V375" s="11">
+        <v>11</v>
+      </c>
+      <c r="W375" s="4">
+        <v>46316</v>
+      </c>
+      <c r="X375" s="12">
+        <v>0.32986110000000002</v>
+      </c>
+      <c r="Y375" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z375" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA375" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB375" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC375" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD375" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE375" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF375" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG375" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH375" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI375" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AJ375" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK375" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL375" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM375" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN375" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO375" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP375" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ375" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR375" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="376" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A376" s="1">
+        <v>1</v>
+      </c>
+      <c r="B376" s="2">
+        <v>2</v>
+      </c>
+      <c r="C376" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D376" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E376" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F376" s="4">
+        <v>46316</v>
+      </c>
+      <c r="G376" s="5">
+        <v>18</v>
+      </c>
+      <c r="H376" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I376" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J376" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K376" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L376" s="6">
+        <v>36</v>
+      </c>
+      <c r="M376" s="7">
+        <v>12108.69</v>
+      </c>
+      <c r="N376" s="6">
+        <v>1</v>
+      </c>
+      <c r="O376" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="P376" s="8">
+        <v>336.35</v>
+      </c>
+      <c r="Q376" s="6">
+        <v>0</v>
+      </c>
+      <c r="R376" s="7">
+        <v>0</v>
+      </c>
+      <c r="S376" s="9">
+        <v>0</v>
+      </c>
+      <c r="T376" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U376" s="10">
+        <v>68501</v>
+      </c>
+      <c r="V376" s="11">
+        <v>11</v>
+      </c>
+      <c r="W376" s="4">
+        <v>46316</v>
+      </c>
+      <c r="X376" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y376" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z376" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA376" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB376" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC376" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD376" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE376" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF376" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG376" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH376" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI376" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AJ376" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK376" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL376" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM376" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN376" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO376" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP376" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ376" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR376" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="377" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A377" s="1">
+        <v>1</v>
+      </c>
+      <c r="B377" s="2">
+        <v>2</v>
+      </c>
+      <c r="C377" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D377" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E377" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F377" s="4">
+        <v>46316</v>
+      </c>
+      <c r="G377" s="5">
+        <v>19</v>
+      </c>
+      <c r="H377" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I377" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J377" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K377" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L377" s="6">
+        <v>37</v>
+      </c>
+      <c r="M377" s="7">
+        <v>12445.05</v>
+      </c>
+      <c r="N377" s="6">
+        <v>1</v>
+      </c>
+      <c r="O377" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="P377" s="8">
+        <v>336.35</v>
+      </c>
+      <c r="Q377" s="6">
+        <v>0</v>
+      </c>
+      <c r="R377" s="7">
+        <v>0</v>
+      </c>
+      <c r="S377" s="9">
+        <v>0</v>
+      </c>
+      <c r="T377" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U377" s="10">
+        <v>68501</v>
+      </c>
+      <c r="V377" s="11">
+        <v>11</v>
+      </c>
+      <c r="W377" s="4">
+        <v>46316</v>
+      </c>
+      <c r="X377" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y377" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z377" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA377" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB377" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC377" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD377" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE377" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF377" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG377" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH377" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI377" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AJ377" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK377" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL377" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM377" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN377" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO377" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP377" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ377" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR377" s="3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="378" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A378" s="1">
+        <v>1</v>
+      </c>
+      <c r="B378" s="2">
+        <v>2</v>
+      </c>
+      <c r="C378" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D378" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E378" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F378" s="4">
+        <v>46316</v>
+      </c>
+      <c r="G378" s="5">
+        <v>20</v>
+      </c>
+      <c r="H378" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I378" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J378" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K378" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L378" s="6">
+        <v>38</v>
+      </c>
+      <c r="M378" s="7">
+        <v>12781.4</v>
+      </c>
+      <c r="N378" s="6">
+        <v>1</v>
+      </c>
+      <c r="O378" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="P378" s="8">
+        <v>336.35</v>
+      </c>
+      <c r="Q378" s="6">
+        <v>0</v>
+      </c>
+      <c r="R378" s="7">
+        <v>0</v>
+      </c>
+      <c r="S378" s="9">
+        <v>0</v>
+      </c>
+      <c r="T378" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U378" s="10">
+        <v>68501</v>
+      </c>
+      <c r="V378" s="11">
+        <v>11</v>
+      </c>
+      <c r="W378" s="4">
+        <v>46316</v>
+      </c>
+      <c r="X378" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y378" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z378" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA378" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB378" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC378" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD378" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE378" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF378" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG378" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH378" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI378" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AJ378" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK378" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL378" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM378" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN378" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO378" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP378" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ378" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR378" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="379" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A379" s="1">
+        <v>1</v>
+      </c>
+      <c r="B379" s="2">
+        <v>2</v>
+      </c>
+      <c r="C379" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D379" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E379" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F379" s="4">
+        <v>46316</v>
+      </c>
+      <c r="G379" s="5">
+        <v>21</v>
+      </c>
+      <c r="H379" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I379" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J379" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K379" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L379" s="6">
+        <v>39</v>
+      </c>
+      <c r="M379" s="7">
+        <v>13117.75</v>
+      </c>
+      <c r="N379" s="6">
+        <v>1</v>
+      </c>
+      <c r="O379" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="P379" s="8">
+        <v>336.35</v>
+      </c>
+      <c r="Q379" s="6">
+        <v>0</v>
+      </c>
+      <c r="R379" s="7">
+        <v>0</v>
+      </c>
+      <c r="S379" s="9">
+        <v>0</v>
+      </c>
+      <c r="T379" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U379" s="10">
+        <v>68501</v>
+      </c>
+      <c r="V379" s="11">
+        <v>11</v>
+      </c>
+      <c r="W379" s="4">
+        <v>46316</v>
+      </c>
+      <c r="X379" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y379" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z379" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA379" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB379" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC379" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD379" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE379" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF379" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG379" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH379" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI379" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AJ379" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK379" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL379" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM379" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN379" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO379" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP379" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ379" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR379" s="3" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="380" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A380" s="1">
+        <v>1</v>
+      </c>
+      <c r="B380" s="2">
+        <v>2</v>
+      </c>
+      <c r="C380" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D380" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E380" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F380" s="4">
+        <v>46316</v>
+      </c>
+      <c r="G380" s="5">
+        <v>22</v>
+      </c>
+      <c r="H380" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I380" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J380" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K380" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L380" s="6">
+        <v>40</v>
+      </c>
+      <c r="M380" s="7">
+        <v>13454.11</v>
+      </c>
+      <c r="N380" s="6">
+        <v>1</v>
+      </c>
+      <c r="O380" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="P380" s="8">
+        <v>336.35</v>
+      </c>
+      <c r="Q380" s="6">
+        <v>0</v>
+      </c>
+      <c r="R380" s="7">
+        <v>0</v>
+      </c>
+      <c r="S380" s="9">
+        <v>0</v>
+      </c>
+      <c r="T380" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U380" s="10">
+        <v>68501</v>
+      </c>
+      <c r="V380" s="11">
+        <v>11</v>
+      </c>
+      <c r="W380" s="4">
+        <v>46316</v>
+      </c>
+      <c r="X380" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y380" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB380" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG380" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI380" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AJ380" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK380" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM380" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR380" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="381" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A381" s="1">
+        <v>1</v>
+      </c>
+      <c r="B381" s="2">
+        <v>2</v>
+      </c>
+      <c r="C381" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D381" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E381" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F381" s="4">
+        <v>46316</v>
+      </c>
+      <c r="G381" s="5">
+        <v>23</v>
+      </c>
+      <c r="H381" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I381" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J381" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K381" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L381" s="6">
+        <v>41</v>
+      </c>
+      <c r="M381" s="7">
+        <v>13790.46</v>
+      </c>
+      <c r="N381" s="6">
+        <v>1</v>
+      </c>
+      <c r="O381" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="P381" s="8">
+        <v>336.35</v>
+      </c>
+      <c r="Q381" s="6">
+        <v>0</v>
+      </c>
+      <c r="R381" s="7">
+        <v>0</v>
+      </c>
+      <c r="S381" s="9">
+        <v>0</v>
+      </c>
+      <c r="T381" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U381" s="10">
+        <v>68501</v>
+      </c>
+      <c r="V381" s="11">
+        <v>11</v>
+      </c>
+      <c r="W381" s="4">
+        <v>46316</v>
+      </c>
+      <c r="X381" s="12">
+        <v>0.33680559999999998</v>
+      </c>
+      <c r="Y381" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z381" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA381" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB381" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC381" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD381" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE381" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF381" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG381" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH381" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI381" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AJ381" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK381" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL381" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM381" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN381" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO381" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP381" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ381" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR381" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="382" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A382" s="1">
+        <v>1</v>
+      </c>
+      <c r="B382" s="2">
+        <v>2</v>
+      </c>
+      <c r="C382" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D382" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E382" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F382" s="4">
+        <v>46316</v>
+      </c>
+      <c r="G382" s="5">
+        <v>24</v>
+      </c>
+      <c r="H382" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I382" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J382" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K382" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L382" s="6">
+        <v>42</v>
+      </c>
+      <c r="M382" s="7">
+        <v>14126.81</v>
+      </c>
+      <c r="N382" s="6">
+        <v>1</v>
+      </c>
+      <c r="O382" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="P382" s="8">
+        <v>336.35</v>
+      </c>
+      <c r="Q382" s="6">
+        <v>0</v>
+      </c>
+      <c r="R382" s="7">
+        <v>0</v>
+      </c>
+      <c r="S382" s="9">
+        <v>0</v>
+      </c>
+      <c r="T382" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U382" s="10">
+        <v>68501</v>
+      </c>
+      <c r="V382" s="11">
+        <v>11</v>
+      </c>
+      <c r="W382" s="4">
+        <v>46316</v>
+      </c>
+      <c r="X382" s="12">
+        <v>0.33750000000000002</v>
+      </c>
+      <c r="Y382" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z382" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA382" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB382" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC382" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD382" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE382" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF382" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG382" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH382" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI382" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AJ382" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK382" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL382" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM382" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN382" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO382" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP382" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ382" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR382" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="383" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A383" s="1">
+        <v>1</v>
+      </c>
+      <c r="B383" s="2">
+        <v>2</v>
+      </c>
+      <c r="C383" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D383" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E383" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F383" s="4">
+        <v>46316</v>
+      </c>
+      <c r="G383" s="5">
+        <v>25</v>
+      </c>
+      <c r="H383" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I383" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J383" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K383" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L383" s="6">
+        <v>43</v>
+      </c>
+      <c r="M383" s="7">
+        <v>14463.16</v>
+      </c>
+      <c r="N383" s="6">
+        <v>1</v>
+      </c>
+      <c r="O383" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="P383" s="8">
+        <v>336.35</v>
+      </c>
+      <c r="Q383" s="6">
+        <v>0</v>
+      </c>
+      <c r="R383" s="7">
+        <v>0</v>
+      </c>
+      <c r="S383" s="9">
+        <v>0</v>
+      </c>
+      <c r="T383" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U383" s="10">
+        <v>68501</v>
+      </c>
+      <c r="V383" s="11">
+        <v>11</v>
+      </c>
+      <c r="W383" s="4">
+        <v>46316</v>
+      </c>
+      <c r="X383" s="12">
+        <v>0.33750000000000002</v>
+      </c>
+      <c r="Y383" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z383" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA383" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB383" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC383" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD383" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE383" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF383" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG383" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH383" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI383" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AJ383" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK383" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL383" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM383" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN383" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO383" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP383" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ383" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR383" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="384" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A384" s="1">
+        <v>1</v>
+      </c>
+      <c r="B384" s="2">
+        <v>2</v>
+      </c>
+      <c r="C384" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D384" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E384" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F384" s="4">
+        <v>46316</v>
+      </c>
+      <c r="G384" s="5">
+        <v>26</v>
+      </c>
+      <c r="H384" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I384" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J384" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K384" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L384" s="6">
+        <v>44</v>
+      </c>
+      <c r="M384" s="7">
+        <v>14799.52</v>
+      </c>
+      <c r="N384" s="6">
+        <v>1</v>
+      </c>
+      <c r="O384" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="P384" s="8">
+        <v>336.35</v>
+      </c>
+      <c r="Q384" s="6">
+        <v>0</v>
+      </c>
+      <c r="R384" s="7">
+        <v>0</v>
+      </c>
+      <c r="S384" s="9">
+        <v>0</v>
+      </c>
+      <c r="T384" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U384" s="10">
+        <v>68501</v>
+      </c>
+      <c r="V384" s="11">
+        <v>11</v>
+      </c>
+      <c r="W384" s="4">
+        <v>46316</v>
+      </c>
+      <c r="X384" s="12">
+        <v>0.33750000000000002</v>
+      </c>
+      <c r="Y384" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z384" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA384" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB384" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC384" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD384" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE384" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF384" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG384" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH384" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI384" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AJ384" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK384" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL384" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM384" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN384" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO384" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP384" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ384" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR384" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="385" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A385" s="1">
+        <v>1</v>
+      </c>
+      <c r="B385" s="2">
+        <v>2</v>
+      </c>
+      <c r="C385" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D385" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E385" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F385" s="4">
+        <v>46316</v>
+      </c>
+      <c r="G385" s="5">
+        <v>27</v>
+      </c>
+      <c r="H385" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I385" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J385" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K385" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L385" s="6">
+        <v>45</v>
+      </c>
+      <c r="M385" s="7">
+        <v>15135.87</v>
+      </c>
+      <c r="N385" s="6">
+        <v>1</v>
+      </c>
+      <c r="O385" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="P385" s="8">
+        <v>336.35</v>
+      </c>
+      <c r="Q385" s="6">
+        <v>0</v>
+      </c>
+      <c r="R385" s="7">
+        <v>0</v>
+      </c>
+      <c r="S385" s="9">
+        <v>0</v>
+      </c>
+      <c r="T385" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U385" s="10">
+        <v>68501</v>
+      </c>
+      <c r="V385" s="11">
+        <v>11</v>
+      </c>
+      <c r="W385" s="4">
+        <v>46316</v>
+      </c>
+      <c r="X385" s="12">
+        <v>0.33750000000000002</v>
+      </c>
+      <c r="Y385" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z385" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA385" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB385" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC385" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD385" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE385" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF385" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG385" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH385" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI385" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AJ385" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK385" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL385" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM385" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN385" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO385" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP385" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ385" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR385" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="386" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A386" s="1">
+        <v>1</v>
+      </c>
+      <c r="B386" s="2">
+        <v>2</v>
+      </c>
+      <c r="C386" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D386" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E386" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F386" s="4">
+        <v>46316</v>
+      </c>
+      <c r="G386" s="5">
+        <v>28</v>
+      </c>
+      <c r="H386" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I386" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J386" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K386" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L386" s="6">
+        <v>46</v>
+      </c>
+      <c r="M386" s="7">
+        <v>15472.22</v>
+      </c>
+      <c r="N386" s="6">
+        <v>1</v>
+      </c>
+      <c r="O386" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="P386" s="8">
+        <v>336.35</v>
+      </c>
+      <c r="Q386" s="6">
+        <v>0</v>
+      </c>
+      <c r="R386" s="7">
+        <v>0</v>
+      </c>
+      <c r="S386" s="9">
+        <v>0</v>
+      </c>
+      <c r="T386" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U386" s="10">
+        <v>68501</v>
+      </c>
+      <c r="V386" s="11">
+        <v>11</v>
+      </c>
+      <c r="W386" s="4">
+        <v>46316</v>
+      </c>
+      <c r="X386" s="12">
+        <v>0.33750000000000002</v>
+      </c>
+      <c r="Y386" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z386" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA386" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB386" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC386" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD386" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE386" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF386" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG386" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH386" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI386" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AJ386" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK386" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL386" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM386" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN386" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO386" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP386" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ386" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR386" s="3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="387" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A387" s="1">
+        <v>1</v>
+      </c>
+      <c r="B387" s="2">
+        <v>2</v>
+      </c>
+      <c r="C387" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D387" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E387" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F387" s="4">
+        <v>46316</v>
+      </c>
+      <c r="G387" s="5">
+        <v>29</v>
+      </c>
+      <c r="H387" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I387" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J387" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K387" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L387" s="6">
+        <v>47</v>
+      </c>
+      <c r="M387" s="7">
+        <v>15808.57</v>
+      </c>
+      <c r="N387" s="6">
+        <v>1</v>
+      </c>
+      <c r="O387" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="P387" s="8">
+        <v>336.35</v>
+      </c>
+      <c r="Q387" s="6">
+        <v>0</v>
+      </c>
+      <c r="R387" s="7">
+        <v>0</v>
+      </c>
+      <c r="S387" s="9">
+        <v>0</v>
+      </c>
+      <c r="T387" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U387" s="10">
+        <v>68501</v>
+      </c>
+      <c r="V387" s="11">
+        <v>11</v>
+      </c>
+      <c r="W387" s="4">
+        <v>46316</v>
+      </c>
+      <c r="X387" s="12">
+        <v>0.33750000000000002</v>
+      </c>
+      <c r="Y387" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z387" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA387" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB387" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC387" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD387" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE387" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF387" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG387" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH387" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI387" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AJ387" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK387" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL387" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM387" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN387" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO387" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP387" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ387" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR387" s="3" t="s">
+        <v>444</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33273739-4B4E-4E2C-AE56-088A06DE5F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7C12364-4490-44CF-AB2B-BB89A3FE50BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="135">
   <si>
     <t>Sel</t>
   </si>
@@ -365,6 +365,66 @@
   </si>
   <si>
     <t>1858700158620</t>
+  </si>
+  <si>
+    <t>1858700158621</t>
+  </si>
+  <si>
+    <t>1858700158622</t>
+  </si>
+  <si>
+    <t>1858700158623</t>
+  </si>
+  <si>
+    <t>1858700158624</t>
+  </si>
+  <si>
+    <t>1858700158625</t>
+  </si>
+  <si>
+    <t>1858700158626</t>
+  </si>
+  <si>
+    <t>1858700158627</t>
+  </si>
+  <si>
+    <t>1858700158628</t>
+  </si>
+  <si>
+    <t>1858700158629</t>
+  </si>
+  <si>
+    <t>1858700158630</t>
+  </si>
+  <si>
+    <t>1858700158631</t>
+  </si>
+  <si>
+    <t>1858700158632</t>
+  </si>
+  <si>
+    <t>1858700158633</t>
+  </si>
+  <si>
+    <t>1858700158634</t>
+  </si>
+  <si>
+    <t>1858700158635</t>
+  </si>
+  <si>
+    <t>1858700158636</t>
+  </si>
+  <si>
+    <t>1858700158637</t>
+  </si>
+  <si>
+    <t>1858700158638</t>
+  </si>
+  <si>
+    <t>1858700158639</t>
+  </si>
+  <si>
+    <t>1858700158640</t>
   </si>
 </sst>
 </file>
@@ -940,7 +1000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR61"/>
+  <dimension ref="A1:AR81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -9115,6 +9175,2686 @@
       </c>
       <c r="AR61" s="3" t="s">
         <v>114</v>
+      </c>
+    </row>
+    <row r="62" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>1</v>
+      </c>
+      <c r="B62" s="2">
+        <v>2</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F62" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G62" s="5">
+        <v>61</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L62" s="6">
+        <v>5088</v>
+      </c>
+      <c r="M62" s="7">
+        <v>869772.92</v>
+      </c>
+      <c r="N62" s="6">
+        <v>1</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P62" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>0</v>
+      </c>
+      <c r="R62" s="7">
+        <v>0</v>
+      </c>
+      <c r="S62" s="9">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U62" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V62" s="11">
+        <v>11</v>
+      </c>
+      <c r="W62" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X62" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y62" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI62" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ62" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK62" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM62" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR62" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="63" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>1</v>
+      </c>
+      <c r="B63" s="2">
+        <v>2</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F63" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G63" s="5">
+        <v>62</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L63" s="6">
+        <v>5089</v>
+      </c>
+      <c r="M63" s="7">
+        <v>869943.86</v>
+      </c>
+      <c r="N63" s="6">
+        <v>1</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P63" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>0</v>
+      </c>
+      <c r="R63" s="7">
+        <v>0</v>
+      </c>
+      <c r="S63" s="9">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U63" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V63" s="11">
+        <v>11</v>
+      </c>
+      <c r="W63" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X63" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y63" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI63" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ63" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK63" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR63" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="64" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>1</v>
+      </c>
+      <c r="B64" s="2">
+        <v>2</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F64" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G64" s="5">
+        <v>63</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L64" s="6">
+        <v>5090</v>
+      </c>
+      <c r="M64" s="7">
+        <v>870114.81</v>
+      </c>
+      <c r="N64" s="6">
+        <v>1</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P64" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q64" s="6">
+        <v>0</v>
+      </c>
+      <c r="R64" s="7">
+        <v>0</v>
+      </c>
+      <c r="S64" s="9">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U64" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V64" s="11">
+        <v>11</v>
+      </c>
+      <c r="W64" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X64" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y64" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI64" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ64" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK64" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR64" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="65" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>1</v>
+      </c>
+      <c r="B65" s="2">
+        <v>2</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F65" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G65" s="5">
+        <v>64</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L65" s="6">
+        <v>5091</v>
+      </c>
+      <c r="M65" s="7">
+        <v>870285.75</v>
+      </c>
+      <c r="N65" s="6">
+        <v>1</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P65" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q65" s="6">
+        <v>0</v>
+      </c>
+      <c r="R65" s="7">
+        <v>0</v>
+      </c>
+      <c r="S65" s="9">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U65" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V65" s="11">
+        <v>11</v>
+      </c>
+      <c r="W65" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X65" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y65" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG65" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI65" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ65" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK65" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR65" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="66" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>1</v>
+      </c>
+      <c r="B66" s="2">
+        <v>2</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F66" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G66" s="5">
+        <v>65</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L66" s="6">
+        <v>5092</v>
+      </c>
+      <c r="M66" s="7">
+        <v>870456.7</v>
+      </c>
+      <c r="N66" s="6">
+        <v>1</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P66" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q66" s="6">
+        <v>0</v>
+      </c>
+      <c r="R66" s="7">
+        <v>0</v>
+      </c>
+      <c r="S66" s="9">
+        <v>0</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U66" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V66" s="11">
+        <v>11</v>
+      </c>
+      <c r="W66" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X66" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y66" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB66" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI66" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ66" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK66" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM66" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR66" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="67" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>1</v>
+      </c>
+      <c r="B67" s="2">
+        <v>2</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F67" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G67" s="5">
+        <v>66</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L67" s="6">
+        <v>5093</v>
+      </c>
+      <c r="M67" s="7">
+        <v>870627.65</v>
+      </c>
+      <c r="N67" s="6">
+        <v>1</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P67" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q67" s="6">
+        <v>0</v>
+      </c>
+      <c r="R67" s="7">
+        <v>0</v>
+      </c>
+      <c r="S67" s="9">
+        <v>0</v>
+      </c>
+      <c r="T67" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U67" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V67" s="11">
+        <v>11</v>
+      </c>
+      <c r="W67" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X67" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y67" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB67" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG67" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI67" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ67" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK67" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM67" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR67" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="68" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>1</v>
+      </c>
+      <c r="B68" s="2">
+        <v>2</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F68" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G68" s="5">
+        <v>67</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L68" s="6">
+        <v>5094</v>
+      </c>
+      <c r="M68" s="7">
+        <v>870798.59</v>
+      </c>
+      <c r="N68" s="6">
+        <v>1</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P68" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q68" s="6">
+        <v>0</v>
+      </c>
+      <c r="R68" s="7">
+        <v>0</v>
+      </c>
+      <c r="S68" s="9">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U68" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V68" s="11">
+        <v>11</v>
+      </c>
+      <c r="W68" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X68" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y68" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI68" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ68" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK68" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR68" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="69" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>1</v>
+      </c>
+      <c r="B69" s="2">
+        <v>2</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F69" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G69" s="5">
+        <v>68</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L69" s="6">
+        <v>5095</v>
+      </c>
+      <c r="M69" s="7">
+        <v>870969.54</v>
+      </c>
+      <c r="N69" s="6">
+        <v>1</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P69" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q69" s="6">
+        <v>0</v>
+      </c>
+      <c r="R69" s="7">
+        <v>0</v>
+      </c>
+      <c r="S69" s="9">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U69" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V69" s="11">
+        <v>11</v>
+      </c>
+      <c r="W69" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X69" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y69" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG69" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI69" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ69" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK69" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR69" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="70" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>1</v>
+      </c>
+      <c r="B70" s="2">
+        <v>2</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F70" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G70" s="5">
+        <v>69</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L70" s="6">
+        <v>5096</v>
+      </c>
+      <c r="M70" s="7">
+        <v>871140.48</v>
+      </c>
+      <c r="N70" s="6">
+        <v>1</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P70" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q70" s="6">
+        <v>0</v>
+      </c>
+      <c r="R70" s="7">
+        <v>0</v>
+      </c>
+      <c r="S70" s="9">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U70" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V70" s="11">
+        <v>11</v>
+      </c>
+      <c r="W70" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X70" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y70" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI70" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ70" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK70" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR70" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="71" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>1</v>
+      </c>
+      <c r="B71" s="2">
+        <v>2</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F71" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G71" s="5">
+        <v>70</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L71" s="6">
+        <v>5097</v>
+      </c>
+      <c r="M71" s="7">
+        <v>871311.43</v>
+      </c>
+      <c r="N71" s="6">
+        <v>1</v>
+      </c>
+      <c r="O71" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P71" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>0</v>
+      </c>
+      <c r="R71" s="7">
+        <v>0</v>
+      </c>
+      <c r="S71" s="9">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U71" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V71" s="11">
+        <v>11</v>
+      </c>
+      <c r="W71" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X71" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y71" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG71" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI71" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ71" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK71" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR71" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="72" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>1</v>
+      </c>
+      <c r="B72" s="2">
+        <v>2</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F72" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G72" s="5">
+        <v>71</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L72" s="6">
+        <v>5098</v>
+      </c>
+      <c r="M72" s="7">
+        <v>871482.38</v>
+      </c>
+      <c r="N72" s="6">
+        <v>1</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P72" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q72" s="6">
+        <v>0</v>
+      </c>
+      <c r="R72" s="7">
+        <v>0</v>
+      </c>
+      <c r="S72" s="9">
+        <v>0</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U72" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V72" s="11">
+        <v>11</v>
+      </c>
+      <c r="W72" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X72" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y72" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG72" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI72" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ72" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK72" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM72" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR72" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="73" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>1</v>
+      </c>
+      <c r="B73" s="2">
+        <v>2</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F73" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G73" s="5">
+        <v>72</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L73" s="6">
+        <v>5099</v>
+      </c>
+      <c r="M73" s="7">
+        <v>871653.32</v>
+      </c>
+      <c r="N73" s="6">
+        <v>1</v>
+      </c>
+      <c r="O73" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P73" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q73" s="6">
+        <v>0</v>
+      </c>
+      <c r="R73" s="7">
+        <v>0</v>
+      </c>
+      <c r="S73" s="9">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U73" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V73" s="11">
+        <v>11</v>
+      </c>
+      <c r="W73" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X73" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y73" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG73" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI73" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ73" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK73" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR73" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="74" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>1</v>
+      </c>
+      <c r="B74" s="2">
+        <v>2</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F74" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G74" s="5">
+        <v>73</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L74" s="6">
+        <v>5100</v>
+      </c>
+      <c r="M74" s="7">
+        <v>871824.27</v>
+      </c>
+      <c r="N74" s="6">
+        <v>1</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P74" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q74" s="6">
+        <v>0</v>
+      </c>
+      <c r="R74" s="7">
+        <v>0</v>
+      </c>
+      <c r="S74" s="9">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U74" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V74" s="11">
+        <v>11</v>
+      </c>
+      <c r="W74" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X74" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y74" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG74" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI74" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ74" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK74" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR74" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="75" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>1</v>
+      </c>
+      <c r="B75" s="2">
+        <v>2</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F75" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G75" s="5">
+        <v>74</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L75" s="6">
+        <v>5101</v>
+      </c>
+      <c r="M75" s="7">
+        <v>871995.21</v>
+      </c>
+      <c r="N75" s="6">
+        <v>1</v>
+      </c>
+      <c r="O75" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P75" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>0</v>
+      </c>
+      <c r="R75" s="7">
+        <v>0</v>
+      </c>
+      <c r="S75" s="9">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U75" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V75" s="11">
+        <v>11</v>
+      </c>
+      <c r="W75" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X75" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y75" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG75" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI75" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ75" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK75" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR75" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="76" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>1</v>
+      </c>
+      <c r="B76" s="2">
+        <v>2</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F76" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G76" s="5">
+        <v>75</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L76" s="6">
+        <v>5102</v>
+      </c>
+      <c r="M76" s="7">
+        <v>872166.16</v>
+      </c>
+      <c r="N76" s="6">
+        <v>1</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P76" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>0</v>
+      </c>
+      <c r="R76" s="7">
+        <v>0</v>
+      </c>
+      <c r="S76" s="9">
+        <v>0</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U76" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V76" s="11">
+        <v>11</v>
+      </c>
+      <c r="W76" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X76" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y76" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG76" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI76" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ76" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK76" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR76" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="77" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>1</v>
+      </c>
+      <c r="B77" s="2">
+        <v>2</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F77" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G77" s="5">
+        <v>76</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L77" s="6">
+        <v>5103</v>
+      </c>
+      <c r="M77" s="7">
+        <v>872337.11</v>
+      </c>
+      <c r="N77" s="6">
+        <v>1</v>
+      </c>
+      <c r="O77" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P77" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q77" s="6">
+        <v>0</v>
+      </c>
+      <c r="R77" s="7">
+        <v>0</v>
+      </c>
+      <c r="S77" s="9">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U77" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V77" s="11">
+        <v>11</v>
+      </c>
+      <c r="W77" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X77" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y77" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG77" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI77" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ77" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK77" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR77" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="78" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>1</v>
+      </c>
+      <c r="B78" s="2">
+        <v>2</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F78" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G78" s="5">
+        <v>77</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L78" s="6">
+        <v>5104</v>
+      </c>
+      <c r="M78" s="7">
+        <v>872508.05</v>
+      </c>
+      <c r="N78" s="6">
+        <v>1</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P78" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q78" s="6">
+        <v>0</v>
+      </c>
+      <c r="R78" s="7">
+        <v>0</v>
+      </c>
+      <c r="S78" s="9">
+        <v>0</v>
+      </c>
+      <c r="T78" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U78" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V78" s="11">
+        <v>11</v>
+      </c>
+      <c r="W78" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X78" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y78" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG78" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI78" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ78" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK78" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM78" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR78" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="79" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>1</v>
+      </c>
+      <c r="B79" s="2">
+        <v>2</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F79" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G79" s="5">
+        <v>78</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L79" s="6">
+        <v>5105</v>
+      </c>
+      <c r="M79" s="7">
+        <v>872679</v>
+      </c>
+      <c r="N79" s="6">
+        <v>1</v>
+      </c>
+      <c r="O79" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P79" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q79" s="6">
+        <v>0</v>
+      </c>
+      <c r="R79" s="7">
+        <v>0</v>
+      </c>
+      <c r="S79" s="9">
+        <v>0</v>
+      </c>
+      <c r="T79" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U79" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V79" s="11">
+        <v>11</v>
+      </c>
+      <c r="W79" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X79" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y79" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG79" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI79" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ79" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK79" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM79" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR79" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="80" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>1</v>
+      </c>
+      <c r="B80" s="2">
+        <v>2</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F80" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G80" s="5">
+        <v>79</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L80" s="6">
+        <v>5106</v>
+      </c>
+      <c r="M80" s="7">
+        <v>872849.94</v>
+      </c>
+      <c r="N80" s="6">
+        <v>1</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P80" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q80" s="6">
+        <v>0</v>
+      </c>
+      <c r="R80" s="7">
+        <v>0</v>
+      </c>
+      <c r="S80" s="9">
+        <v>0</v>
+      </c>
+      <c r="T80" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U80" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V80" s="11">
+        <v>11</v>
+      </c>
+      <c r="W80" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X80" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y80" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG80" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI80" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ80" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK80" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM80" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR80" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="81" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>1</v>
+      </c>
+      <c r="B81" s="2">
+        <v>2</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F81" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G81" s="5">
+        <v>80</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L81" s="6">
+        <v>5107</v>
+      </c>
+      <c r="M81" s="7">
+        <v>873020.89</v>
+      </c>
+      <c r="N81" s="6">
+        <v>1</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P81" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q81" s="6">
+        <v>0</v>
+      </c>
+      <c r="R81" s="7">
+        <v>0</v>
+      </c>
+      <c r="S81" s="9">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U81" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V81" s="11">
+        <v>11</v>
+      </c>
+      <c r="W81" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X81" s="12">
+        <v>0.33472220000000003</v>
+      </c>
+      <c r="Y81" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG81" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI81" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ81" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK81" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM81" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR81" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90EC9622-81EE-448F-8C07-D3DC817ED7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A182B5E0-65CA-43F2-99E4-D76B178A9BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="696" yWindow="708" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3644" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4724" uniqueCount="315">
   <si>
     <t>Sel</t>
   </si>
@@ -786,6 +786,186 @@
   <si>
     <t>1858700158760</t>
   </si>
+  <si>
+    <t>1858700158761</t>
+  </si>
+  <si>
+    <t>1858700158762</t>
+  </si>
+  <si>
+    <t>1858700158763</t>
+  </si>
+  <si>
+    <t>1858700158764</t>
+  </si>
+  <si>
+    <t>1858700158765</t>
+  </si>
+  <si>
+    <t>1858700158766</t>
+  </si>
+  <si>
+    <t>1858700158767</t>
+  </si>
+  <si>
+    <t>1858700158768</t>
+  </si>
+  <si>
+    <t>1858700158769</t>
+  </si>
+  <si>
+    <t>1858700158770</t>
+  </si>
+  <si>
+    <t>1858700158771</t>
+  </si>
+  <si>
+    <t>1858700158772</t>
+  </si>
+  <si>
+    <t>1858700158773</t>
+  </si>
+  <si>
+    <t>1858700158774</t>
+  </si>
+  <si>
+    <t>1858700158775</t>
+  </si>
+  <si>
+    <t>1858700158776</t>
+  </si>
+  <si>
+    <t>1858700158777</t>
+  </si>
+  <si>
+    <t>1858700158778</t>
+  </si>
+  <si>
+    <t>1858700158779</t>
+  </si>
+  <si>
+    <t>1858700158780</t>
+  </si>
+  <si>
+    <t>1858700158781</t>
+  </si>
+  <si>
+    <t>1858700158782</t>
+  </si>
+  <si>
+    <t>1858700158783</t>
+  </si>
+  <si>
+    <t>1858700158784</t>
+  </si>
+  <si>
+    <t>1858700158785</t>
+  </si>
+  <si>
+    <t>1858700158786</t>
+  </si>
+  <si>
+    <t>1858700158787</t>
+  </si>
+  <si>
+    <t>1858700158788</t>
+  </si>
+  <si>
+    <t>1858700158789</t>
+  </si>
+  <si>
+    <t>1858700158790</t>
+  </si>
+  <si>
+    <t>1858700158791</t>
+  </si>
+  <si>
+    <t>1858700158792</t>
+  </si>
+  <si>
+    <t>1858700158793</t>
+  </si>
+  <si>
+    <t>1858700158794</t>
+  </si>
+  <si>
+    <t>1858700158795</t>
+  </si>
+  <si>
+    <t>1858700158796</t>
+  </si>
+  <si>
+    <t>1858700158797</t>
+  </si>
+  <si>
+    <t>1858700158798</t>
+  </si>
+  <si>
+    <t>1858700158799</t>
+  </si>
+  <si>
+    <t>1858700158800</t>
+  </si>
+  <si>
+    <t>1858700158801</t>
+  </si>
+  <si>
+    <t>1858700158802</t>
+  </si>
+  <si>
+    <t>1858700158803</t>
+  </si>
+  <si>
+    <t>1858700158804</t>
+  </si>
+  <si>
+    <t>1858700158805</t>
+  </si>
+  <si>
+    <t>1858700158806</t>
+  </si>
+  <si>
+    <t>1858700158807</t>
+  </si>
+  <si>
+    <t>1858700158808</t>
+  </si>
+  <si>
+    <t>1858700158809</t>
+  </si>
+  <si>
+    <t>1858700158810</t>
+  </si>
+  <si>
+    <t>1858700158811</t>
+  </si>
+  <si>
+    <t>1858700158812</t>
+  </si>
+  <si>
+    <t>1858700158813</t>
+  </si>
+  <si>
+    <t>1858700158814</t>
+  </si>
+  <si>
+    <t>1858700158815</t>
+  </si>
+  <si>
+    <t>1858700158816</t>
+  </si>
+  <si>
+    <t>1858700158817</t>
+  </si>
+  <si>
+    <t>1858700158818</t>
+  </si>
+  <si>
+    <t>1858700158819</t>
+  </si>
+  <si>
+    <t>1858700158820</t>
+  </si>
 </sst>
 </file>
 
@@ -1360,7 +1540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR201"/>
+  <dimension ref="A1:AR261"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -28295,6 +28475,8046 @@
       </c>
       <c r="AR201" s="3" t="s">
         <v>254</v>
+      </c>
+    </row>
+    <row r="202" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A202" s="1">
+        <v>1</v>
+      </c>
+      <c r="B202" s="2">
+        <v>2</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F202" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G202" s="5">
+        <v>201</v>
+      </c>
+      <c r="H202" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I202" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J202" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K202" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L202" s="6">
+        <v>5228</v>
+      </c>
+      <c r="M202" s="7">
+        <v>893705.35</v>
+      </c>
+      <c r="N202" s="6">
+        <v>1</v>
+      </c>
+      <c r="O202" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P202" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q202" s="6">
+        <v>0</v>
+      </c>
+      <c r="R202" s="7">
+        <v>0</v>
+      </c>
+      <c r="S202" s="9">
+        <v>0</v>
+      </c>
+      <c r="T202" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U202" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V202" s="11">
+        <v>11</v>
+      </c>
+      <c r="W202" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X202" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y202" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z202" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA202" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB202" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC202" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD202" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE202" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF202" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG202" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH202" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI202" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ202" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK202" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL202" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM202" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN202" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO202" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP202" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ202" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR202" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="203" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A203" s="1">
+        <v>1</v>
+      </c>
+      <c r="B203" s="2">
+        <v>2</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F203" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G203" s="5">
+        <v>202</v>
+      </c>
+      <c r="H203" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I203" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J203" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K203" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L203" s="6">
+        <v>5229</v>
+      </c>
+      <c r="M203" s="7">
+        <v>893876.29</v>
+      </c>
+      <c r="N203" s="6">
+        <v>1</v>
+      </c>
+      <c r="O203" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P203" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q203" s="6">
+        <v>0</v>
+      </c>
+      <c r="R203" s="7">
+        <v>0</v>
+      </c>
+      <c r="S203" s="9">
+        <v>0</v>
+      </c>
+      <c r="T203" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U203" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V203" s="11">
+        <v>11</v>
+      </c>
+      <c r="W203" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X203" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y203" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z203" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA203" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB203" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC203" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD203" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE203" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF203" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG203" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH203" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI203" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ203" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK203" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL203" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM203" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN203" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO203" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP203" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ203" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR203" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="204" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A204" s="1">
+        <v>1</v>
+      </c>
+      <c r="B204" s="2">
+        <v>2</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F204" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G204" s="5">
+        <v>203</v>
+      </c>
+      <c r="H204" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I204" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J204" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K204" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L204" s="6">
+        <v>5230</v>
+      </c>
+      <c r="M204" s="7">
+        <v>894047.24</v>
+      </c>
+      <c r="N204" s="6">
+        <v>1</v>
+      </c>
+      <c r="O204" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P204" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q204" s="6">
+        <v>0</v>
+      </c>
+      <c r="R204" s="7">
+        <v>0</v>
+      </c>
+      <c r="S204" s="9">
+        <v>0</v>
+      </c>
+      <c r="T204" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U204" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V204" s="11">
+        <v>11</v>
+      </c>
+      <c r="W204" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X204" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y204" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z204" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA204" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB204" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC204" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD204" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE204" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF204" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG204" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH204" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI204" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ204" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK204" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL204" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM204" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN204" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO204" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP204" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ204" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR204" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="205" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A205" s="1">
+        <v>1</v>
+      </c>
+      <c r="B205" s="2">
+        <v>2</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F205" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G205" s="5">
+        <v>204</v>
+      </c>
+      <c r="H205" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I205" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J205" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K205" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L205" s="6">
+        <v>5231</v>
+      </c>
+      <c r="M205" s="7">
+        <v>894218.19</v>
+      </c>
+      <c r="N205" s="6">
+        <v>1</v>
+      </c>
+      <c r="O205" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P205" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q205" s="6">
+        <v>0</v>
+      </c>
+      <c r="R205" s="7">
+        <v>0</v>
+      </c>
+      <c r="S205" s="9">
+        <v>0</v>
+      </c>
+      <c r="T205" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U205" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V205" s="11">
+        <v>11</v>
+      </c>
+      <c r="W205" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X205" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y205" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z205" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA205" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB205" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC205" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD205" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE205" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF205" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG205" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH205" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI205" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ205" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK205" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL205" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM205" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN205" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO205" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP205" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ205" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR205" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="206" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A206" s="1">
+        <v>1</v>
+      </c>
+      <c r="B206" s="2">
+        <v>2</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F206" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G206" s="5">
+        <v>205</v>
+      </c>
+      <c r="H206" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I206" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J206" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K206" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L206" s="6">
+        <v>5232</v>
+      </c>
+      <c r="M206" s="7">
+        <v>894389.13</v>
+      </c>
+      <c r="N206" s="6">
+        <v>1</v>
+      </c>
+      <c r="O206" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P206" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q206" s="6">
+        <v>0</v>
+      </c>
+      <c r="R206" s="7">
+        <v>0</v>
+      </c>
+      <c r="S206" s="9">
+        <v>0</v>
+      </c>
+      <c r="T206" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U206" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V206" s="11">
+        <v>11</v>
+      </c>
+      <c r="W206" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X206" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y206" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z206" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA206" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB206" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC206" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD206" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE206" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF206" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG206" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH206" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI206" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ206" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK206" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL206" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM206" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN206" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO206" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP206" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ206" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR206" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="207" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A207" s="1">
+        <v>1</v>
+      </c>
+      <c r="B207" s="2">
+        <v>2</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F207" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G207" s="5">
+        <v>206</v>
+      </c>
+      <c r="H207" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I207" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J207" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K207" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L207" s="6">
+        <v>5233</v>
+      </c>
+      <c r="M207" s="7">
+        <v>894560.08</v>
+      </c>
+      <c r="N207" s="6">
+        <v>1</v>
+      </c>
+      <c r="O207" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P207" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q207" s="6">
+        <v>0</v>
+      </c>
+      <c r="R207" s="7">
+        <v>0</v>
+      </c>
+      <c r="S207" s="9">
+        <v>0</v>
+      </c>
+      <c r="T207" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U207" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V207" s="11">
+        <v>11</v>
+      </c>
+      <c r="W207" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X207" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y207" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z207" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB207" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC207" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD207" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE207" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF207" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG207" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH207" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI207" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ207" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK207" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL207" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM207" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN207" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO207" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP207" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ207" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR207" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="208" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A208" s="1">
+        <v>1</v>
+      </c>
+      <c r="B208" s="2">
+        <v>2</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F208" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G208" s="5">
+        <v>207</v>
+      </c>
+      <c r="H208" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I208" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J208" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K208" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L208" s="6">
+        <v>5234</v>
+      </c>
+      <c r="M208" s="7">
+        <v>894731.02</v>
+      </c>
+      <c r="N208" s="6">
+        <v>1</v>
+      </c>
+      <c r="O208" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P208" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q208" s="6">
+        <v>0</v>
+      </c>
+      <c r="R208" s="7">
+        <v>0</v>
+      </c>
+      <c r="S208" s="9">
+        <v>0</v>
+      </c>
+      <c r="T208" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U208" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V208" s="11">
+        <v>11</v>
+      </c>
+      <c r="W208" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X208" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y208" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z208" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA208" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB208" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC208" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD208" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE208" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF208" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG208" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH208" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI208" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ208" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK208" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL208" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM208" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN208" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO208" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP208" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ208" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR208" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="209" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A209" s="1">
+        <v>1</v>
+      </c>
+      <c r="B209" s="2">
+        <v>2</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F209" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G209" s="5">
+        <v>208</v>
+      </c>
+      <c r="H209" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I209" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J209" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K209" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L209" s="6">
+        <v>5235</v>
+      </c>
+      <c r="M209" s="7">
+        <v>894901.97</v>
+      </c>
+      <c r="N209" s="6">
+        <v>1</v>
+      </c>
+      <c r="O209" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P209" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q209" s="6">
+        <v>0</v>
+      </c>
+      <c r="R209" s="7">
+        <v>0</v>
+      </c>
+      <c r="S209" s="9">
+        <v>0</v>
+      </c>
+      <c r="T209" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U209" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V209" s="11">
+        <v>11</v>
+      </c>
+      <c r="W209" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X209" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y209" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z209" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA209" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB209" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC209" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD209" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE209" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF209" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG209" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH209" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI209" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ209" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK209" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL209" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM209" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN209" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO209" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP209" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ209" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR209" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="210" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A210" s="1">
+        <v>1</v>
+      </c>
+      <c r="B210" s="2">
+        <v>2</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F210" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G210" s="5">
+        <v>209</v>
+      </c>
+      <c r="H210" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I210" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J210" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K210" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L210" s="6">
+        <v>5236</v>
+      </c>
+      <c r="M210" s="7">
+        <v>895072.91</v>
+      </c>
+      <c r="N210" s="6">
+        <v>1</v>
+      </c>
+      <c r="O210" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P210" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q210" s="6">
+        <v>0</v>
+      </c>
+      <c r="R210" s="7">
+        <v>0</v>
+      </c>
+      <c r="S210" s="9">
+        <v>0</v>
+      </c>
+      <c r="T210" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U210" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V210" s="11">
+        <v>11</v>
+      </c>
+      <c r="W210" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X210" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y210" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z210" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA210" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB210" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC210" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD210" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE210" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF210" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG210" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH210" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI210" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ210" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK210" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL210" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM210" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN210" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO210" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP210" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ210" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR210" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="211" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A211" s="1">
+        <v>1</v>
+      </c>
+      <c r="B211" s="2">
+        <v>2</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F211" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G211" s="5">
+        <v>210</v>
+      </c>
+      <c r="H211" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I211" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J211" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K211" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L211" s="6">
+        <v>5237</v>
+      </c>
+      <c r="M211" s="7">
+        <v>895243.86</v>
+      </c>
+      <c r="N211" s="6">
+        <v>1</v>
+      </c>
+      <c r="O211" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P211" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q211" s="6">
+        <v>0</v>
+      </c>
+      <c r="R211" s="7">
+        <v>0</v>
+      </c>
+      <c r="S211" s="9">
+        <v>0</v>
+      </c>
+      <c r="T211" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U211" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V211" s="11">
+        <v>11</v>
+      </c>
+      <c r="W211" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X211" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y211" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z211" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA211" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB211" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC211" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD211" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE211" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF211" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG211" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH211" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI211" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ211" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK211" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL211" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM211" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN211" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO211" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP211" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ211" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR211" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="212" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A212" s="1">
+        <v>1</v>
+      </c>
+      <c r="B212" s="2">
+        <v>2</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F212" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G212" s="5">
+        <v>211</v>
+      </c>
+      <c r="H212" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I212" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J212" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K212" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L212" s="6">
+        <v>5238</v>
+      </c>
+      <c r="M212" s="7">
+        <v>895414.81</v>
+      </c>
+      <c r="N212" s="6">
+        <v>1</v>
+      </c>
+      <c r="O212" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P212" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q212" s="6">
+        <v>0</v>
+      </c>
+      <c r="R212" s="7">
+        <v>0</v>
+      </c>
+      <c r="S212" s="9">
+        <v>0</v>
+      </c>
+      <c r="T212" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U212" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V212" s="11">
+        <v>11</v>
+      </c>
+      <c r="W212" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X212" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y212" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z212" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA212" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB212" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC212" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD212" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE212" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF212" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG212" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH212" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI212" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ212" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK212" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL212" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM212" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN212" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO212" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP212" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ212" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR212" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="213" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A213" s="1">
+        <v>1</v>
+      </c>
+      <c r="B213" s="2">
+        <v>2</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F213" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G213" s="5">
+        <v>212</v>
+      </c>
+      <c r="H213" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I213" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J213" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K213" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L213" s="6">
+        <v>5239</v>
+      </c>
+      <c r="M213" s="7">
+        <v>895585.75</v>
+      </c>
+      <c r="N213" s="6">
+        <v>1</v>
+      </c>
+      <c r="O213" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P213" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q213" s="6">
+        <v>0</v>
+      </c>
+      <c r="R213" s="7">
+        <v>0</v>
+      </c>
+      <c r="S213" s="9">
+        <v>0</v>
+      </c>
+      <c r="T213" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U213" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V213" s="11">
+        <v>11</v>
+      </c>
+      <c r="W213" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X213" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y213" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z213" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA213" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB213" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC213" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD213" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE213" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF213" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG213" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH213" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI213" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ213" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK213" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL213" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM213" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN213" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO213" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP213" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ213" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR213" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="214" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A214" s="1">
+        <v>1</v>
+      </c>
+      <c r="B214" s="2">
+        <v>2</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F214" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G214" s="5">
+        <v>213</v>
+      </c>
+      <c r="H214" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I214" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J214" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K214" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L214" s="6">
+        <v>5240</v>
+      </c>
+      <c r="M214" s="7">
+        <v>895756.7</v>
+      </c>
+      <c r="N214" s="6">
+        <v>1</v>
+      </c>
+      <c r="O214" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P214" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q214" s="6">
+        <v>0</v>
+      </c>
+      <c r="R214" s="7">
+        <v>0</v>
+      </c>
+      <c r="S214" s="9">
+        <v>0</v>
+      </c>
+      <c r="T214" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U214" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V214" s="11">
+        <v>11</v>
+      </c>
+      <c r="W214" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X214" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y214" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z214" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA214" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB214" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC214" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD214" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE214" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF214" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG214" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH214" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI214" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ214" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK214" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL214" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM214" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN214" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO214" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP214" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ214" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR214" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="215" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A215" s="1">
+        <v>1</v>
+      </c>
+      <c r="B215" s="2">
+        <v>2</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F215" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G215" s="5">
+        <v>214</v>
+      </c>
+      <c r="H215" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I215" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J215" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K215" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L215" s="6">
+        <v>5241</v>
+      </c>
+      <c r="M215" s="7">
+        <v>895927.64</v>
+      </c>
+      <c r="N215" s="6">
+        <v>1</v>
+      </c>
+      <c r="O215" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P215" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q215" s="6">
+        <v>0</v>
+      </c>
+      <c r="R215" s="7">
+        <v>0</v>
+      </c>
+      <c r="S215" s="9">
+        <v>0</v>
+      </c>
+      <c r="T215" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U215" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V215" s="11">
+        <v>11</v>
+      </c>
+      <c r="W215" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X215" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y215" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z215" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA215" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB215" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC215" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD215" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE215" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF215" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG215" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH215" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI215" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ215" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK215" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL215" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM215" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN215" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO215" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP215" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ215" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR215" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="216" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A216" s="1">
+        <v>1</v>
+      </c>
+      <c r="B216" s="2">
+        <v>2</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F216" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G216" s="5">
+        <v>215</v>
+      </c>
+      <c r="H216" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I216" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J216" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K216" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L216" s="6">
+        <v>5242</v>
+      </c>
+      <c r="M216" s="7">
+        <v>896098.59</v>
+      </c>
+      <c r="N216" s="6">
+        <v>1</v>
+      </c>
+      <c r="O216" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P216" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q216" s="6">
+        <v>0</v>
+      </c>
+      <c r="R216" s="7">
+        <v>0</v>
+      </c>
+      <c r="S216" s="9">
+        <v>0</v>
+      </c>
+      <c r="T216" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U216" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V216" s="11">
+        <v>11</v>
+      </c>
+      <c r="W216" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X216" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y216" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z216" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA216" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB216" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC216" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD216" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE216" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF216" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG216" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH216" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI216" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ216" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK216" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL216" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM216" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN216" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO216" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP216" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ216" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR216" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="217" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A217" s="1">
+        <v>1</v>
+      </c>
+      <c r="B217" s="2">
+        <v>2</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F217" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G217" s="5">
+        <v>216</v>
+      </c>
+      <c r="H217" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I217" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J217" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K217" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L217" s="6">
+        <v>5243</v>
+      </c>
+      <c r="M217" s="7">
+        <v>896269.54</v>
+      </c>
+      <c r="N217" s="6">
+        <v>1</v>
+      </c>
+      <c r="O217" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P217" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q217" s="6">
+        <v>0</v>
+      </c>
+      <c r="R217" s="7">
+        <v>0</v>
+      </c>
+      <c r="S217" s="9">
+        <v>0</v>
+      </c>
+      <c r="T217" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U217" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V217" s="11">
+        <v>11</v>
+      </c>
+      <c r="W217" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X217" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y217" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z217" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA217" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB217" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC217" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD217" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE217" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF217" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG217" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH217" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI217" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ217" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK217" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL217" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM217" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN217" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO217" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP217" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ217" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR217" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="218" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A218" s="1">
+        <v>1</v>
+      </c>
+      <c r="B218" s="2">
+        <v>2</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F218" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G218" s="5">
+        <v>217</v>
+      </c>
+      <c r="H218" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I218" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J218" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K218" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L218" s="6">
+        <v>5244</v>
+      </c>
+      <c r="M218" s="7">
+        <v>896440.48</v>
+      </c>
+      <c r="N218" s="6">
+        <v>1</v>
+      </c>
+      <c r="O218" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P218" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q218" s="6">
+        <v>0</v>
+      </c>
+      <c r="R218" s="7">
+        <v>0</v>
+      </c>
+      <c r="S218" s="9">
+        <v>0</v>
+      </c>
+      <c r="T218" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U218" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V218" s="11">
+        <v>11</v>
+      </c>
+      <c r="W218" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X218" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y218" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z218" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA218" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB218" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC218" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD218" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE218" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF218" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG218" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH218" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI218" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ218" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK218" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL218" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM218" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN218" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO218" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP218" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ218" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR218" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="219" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A219" s="1">
+        <v>1</v>
+      </c>
+      <c r="B219" s="2">
+        <v>2</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F219" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G219" s="5">
+        <v>218</v>
+      </c>
+      <c r="H219" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I219" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J219" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K219" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L219" s="6">
+        <v>5245</v>
+      </c>
+      <c r="M219" s="7">
+        <v>896611.43</v>
+      </c>
+      <c r="N219" s="6">
+        <v>1</v>
+      </c>
+      <c r="O219" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P219" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q219" s="6">
+        <v>0</v>
+      </c>
+      <c r="R219" s="7">
+        <v>0</v>
+      </c>
+      <c r="S219" s="9">
+        <v>0</v>
+      </c>
+      <c r="T219" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U219" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V219" s="11">
+        <v>11</v>
+      </c>
+      <c r="W219" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X219" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y219" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z219" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA219" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB219" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC219" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD219" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE219" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF219" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG219" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH219" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI219" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ219" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK219" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL219" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM219" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN219" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO219" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP219" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ219" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR219" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="220" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A220" s="1">
+        <v>1</v>
+      </c>
+      <c r="B220" s="2">
+        <v>2</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F220" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G220" s="5">
+        <v>219</v>
+      </c>
+      <c r="H220" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I220" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J220" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K220" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L220" s="6">
+        <v>5246</v>
+      </c>
+      <c r="M220" s="7">
+        <v>896782.37</v>
+      </c>
+      <c r="N220" s="6">
+        <v>1</v>
+      </c>
+      <c r="O220" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P220" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q220" s="6">
+        <v>0</v>
+      </c>
+      <c r="R220" s="7">
+        <v>0</v>
+      </c>
+      <c r="S220" s="9">
+        <v>0</v>
+      </c>
+      <c r="T220" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U220" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V220" s="11">
+        <v>11</v>
+      </c>
+      <c r="W220" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X220" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y220" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z220" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA220" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB220" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC220" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD220" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE220" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF220" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG220" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH220" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI220" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ220" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK220" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL220" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM220" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN220" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO220" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP220" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ220" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR220" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="221" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A221" s="1">
+        <v>1</v>
+      </c>
+      <c r="B221" s="2">
+        <v>2</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F221" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G221" s="5">
+        <v>220</v>
+      </c>
+      <c r="H221" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I221" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J221" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K221" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L221" s="6">
+        <v>5247</v>
+      </c>
+      <c r="M221" s="7">
+        <v>896953.32</v>
+      </c>
+      <c r="N221" s="6">
+        <v>1</v>
+      </c>
+      <c r="O221" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P221" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q221" s="6">
+        <v>0</v>
+      </c>
+      <c r="R221" s="7">
+        <v>0</v>
+      </c>
+      <c r="S221" s="9">
+        <v>0</v>
+      </c>
+      <c r="T221" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U221" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V221" s="11">
+        <v>11</v>
+      </c>
+      <c r="W221" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X221" s="12">
+        <v>0.38472220000000001</v>
+      </c>
+      <c r="Y221" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z221" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA221" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB221" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC221" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD221" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE221" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF221" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG221" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH221" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI221" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ221" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK221" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL221" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM221" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN221" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO221" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP221" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ221" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR221" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="222" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A222" s="1">
+        <v>1</v>
+      </c>
+      <c r="B222" s="2">
+        <v>2</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F222" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G222" s="5">
+        <v>221</v>
+      </c>
+      <c r="H222" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I222" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J222" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K222" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L222" s="6">
+        <v>5248</v>
+      </c>
+      <c r="M222" s="7">
+        <v>897124.27</v>
+      </c>
+      <c r="N222" s="6">
+        <v>1</v>
+      </c>
+      <c r="O222" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P222" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q222" s="6">
+        <v>0</v>
+      </c>
+      <c r="R222" s="7">
+        <v>0</v>
+      </c>
+      <c r="S222" s="9">
+        <v>0</v>
+      </c>
+      <c r="T222" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U222" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V222" s="11">
+        <v>11</v>
+      </c>
+      <c r="W222" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X222" s="12">
+        <v>0.39791670000000001</v>
+      </c>
+      <c r="Y222" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z222" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA222" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB222" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC222" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD222" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE222" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF222" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG222" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH222" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI222" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ222" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK222" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL222" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM222" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN222" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO222" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP222" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ222" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR222" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="223" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A223" s="1">
+        <v>1</v>
+      </c>
+      <c r="B223" s="2">
+        <v>2</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F223" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G223" s="5">
+        <v>222</v>
+      </c>
+      <c r="H223" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I223" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J223" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K223" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L223" s="6">
+        <v>5249</v>
+      </c>
+      <c r="M223" s="7">
+        <v>897295.21</v>
+      </c>
+      <c r="N223" s="6">
+        <v>1</v>
+      </c>
+      <c r="O223" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P223" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q223" s="6">
+        <v>0</v>
+      </c>
+      <c r="R223" s="7">
+        <v>0</v>
+      </c>
+      <c r="S223" s="9">
+        <v>0</v>
+      </c>
+      <c r="T223" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U223" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V223" s="11">
+        <v>11</v>
+      </c>
+      <c r="W223" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X223" s="12">
+        <v>0.39791670000000001</v>
+      </c>
+      <c r="Y223" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z223" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA223" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB223" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC223" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD223" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE223" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF223" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG223" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH223" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI223" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ223" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK223" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL223" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM223" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN223" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO223" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP223" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ223" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR223" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="224" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A224" s="1">
+        <v>1</v>
+      </c>
+      <c r="B224" s="2">
+        <v>2</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F224" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G224" s="5">
+        <v>223</v>
+      </c>
+      <c r="H224" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I224" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J224" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K224" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L224" s="6">
+        <v>5250</v>
+      </c>
+      <c r="M224" s="7">
+        <v>897466.16</v>
+      </c>
+      <c r="N224" s="6">
+        <v>1</v>
+      </c>
+      <c r="O224" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P224" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q224" s="6">
+        <v>0</v>
+      </c>
+      <c r="R224" s="7">
+        <v>0</v>
+      </c>
+      <c r="S224" s="9">
+        <v>0</v>
+      </c>
+      <c r="T224" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U224" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V224" s="11">
+        <v>11</v>
+      </c>
+      <c r="W224" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X224" s="12">
+        <v>0.39791670000000001</v>
+      </c>
+      <c r="Y224" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z224" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA224" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB224" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC224" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD224" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE224" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF224" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG224" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH224" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI224" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ224" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK224" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL224" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM224" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN224" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO224" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP224" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ224" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR224" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="225" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A225" s="1">
+        <v>1</v>
+      </c>
+      <c r="B225" s="2">
+        <v>2</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F225" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G225" s="5">
+        <v>224</v>
+      </c>
+      <c r="H225" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I225" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J225" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K225" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L225" s="6">
+        <v>5251</v>
+      </c>
+      <c r="M225" s="7">
+        <v>897637.1</v>
+      </c>
+      <c r="N225" s="6">
+        <v>1</v>
+      </c>
+      <c r="O225" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P225" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q225" s="6">
+        <v>0</v>
+      </c>
+      <c r="R225" s="7">
+        <v>0</v>
+      </c>
+      <c r="S225" s="9">
+        <v>0</v>
+      </c>
+      <c r="T225" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U225" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V225" s="11">
+        <v>11</v>
+      </c>
+      <c r="W225" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X225" s="12">
+        <v>0.39791670000000001</v>
+      </c>
+      <c r="Y225" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z225" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA225" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB225" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC225" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD225" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE225" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF225" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG225" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH225" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI225" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ225" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK225" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL225" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM225" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN225" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO225" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP225" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ225" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR225" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="226" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A226" s="1">
+        <v>1</v>
+      </c>
+      <c r="B226" s="2">
+        <v>2</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F226" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G226" s="5">
+        <v>225</v>
+      </c>
+      <c r="H226" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I226" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J226" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K226" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L226" s="6">
+        <v>5252</v>
+      </c>
+      <c r="M226" s="7">
+        <v>897808.05</v>
+      </c>
+      <c r="N226" s="6">
+        <v>1</v>
+      </c>
+      <c r="O226" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P226" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q226" s="6">
+        <v>0</v>
+      </c>
+      <c r="R226" s="7">
+        <v>0</v>
+      </c>
+      <c r="S226" s="9">
+        <v>0</v>
+      </c>
+      <c r="T226" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U226" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V226" s="11">
+        <v>11</v>
+      </c>
+      <c r="W226" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X226" s="12">
+        <v>0.39791670000000001</v>
+      </c>
+      <c r="Y226" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z226" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA226" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB226" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC226" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD226" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE226" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF226" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG226" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH226" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI226" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ226" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK226" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL226" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM226" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN226" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO226" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP226" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ226" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR226" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="227" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A227" s="1">
+        <v>1</v>
+      </c>
+      <c r="B227" s="2">
+        <v>2</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F227" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G227" s="5">
+        <v>226</v>
+      </c>
+      <c r="H227" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I227" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J227" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K227" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L227" s="6">
+        <v>5253</v>
+      </c>
+      <c r="M227" s="7">
+        <v>897979</v>
+      </c>
+      <c r="N227" s="6">
+        <v>1</v>
+      </c>
+      <c r="O227" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P227" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q227" s="6">
+        <v>0</v>
+      </c>
+      <c r="R227" s="7">
+        <v>0</v>
+      </c>
+      <c r="S227" s="9">
+        <v>0</v>
+      </c>
+      <c r="T227" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U227" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V227" s="11">
+        <v>11</v>
+      </c>
+      <c r="W227" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X227" s="12">
+        <v>0.39791670000000001</v>
+      </c>
+      <c r="Y227" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z227" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA227" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB227" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC227" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD227" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE227" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF227" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG227" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH227" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI227" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ227" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK227" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL227" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM227" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN227" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO227" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP227" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ227" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR227" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="228" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A228" s="1">
+        <v>1</v>
+      </c>
+      <c r="B228" s="2">
+        <v>2</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F228" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G228" s="5">
+        <v>227</v>
+      </c>
+      <c r="H228" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I228" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J228" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K228" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L228" s="6">
+        <v>5254</v>
+      </c>
+      <c r="M228" s="7">
+        <v>898149.94</v>
+      </c>
+      <c r="N228" s="6">
+        <v>1</v>
+      </c>
+      <c r="O228" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P228" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q228" s="6">
+        <v>0</v>
+      </c>
+      <c r="R228" s="7">
+        <v>0</v>
+      </c>
+      <c r="S228" s="9">
+        <v>0</v>
+      </c>
+      <c r="T228" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U228" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V228" s="11">
+        <v>11</v>
+      </c>
+      <c r="W228" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X228" s="12">
+        <v>0.39791670000000001</v>
+      </c>
+      <c r="Y228" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z228" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA228" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB228" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC228" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD228" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE228" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF228" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG228" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH228" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI228" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ228" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK228" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL228" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM228" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN228" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO228" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP228" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ228" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR228" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="229" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A229" s="1">
+        <v>1</v>
+      </c>
+      <c r="B229" s="2">
+        <v>2</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F229" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G229" s="5">
+        <v>228</v>
+      </c>
+      <c r="H229" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I229" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J229" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K229" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L229" s="6">
+        <v>5255</v>
+      </c>
+      <c r="M229" s="7">
+        <v>898320.89</v>
+      </c>
+      <c r="N229" s="6">
+        <v>1</v>
+      </c>
+      <c r="O229" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P229" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q229" s="6">
+        <v>0</v>
+      </c>
+      <c r="R229" s="7">
+        <v>0</v>
+      </c>
+      <c r="S229" s="9">
+        <v>0</v>
+      </c>
+      <c r="T229" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U229" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V229" s="11">
+        <v>11</v>
+      </c>
+      <c r="W229" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X229" s="12">
+        <v>0.39791670000000001</v>
+      </c>
+      <c r="Y229" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z229" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA229" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB229" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC229" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD229" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE229" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF229" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG229" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH229" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI229" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ229" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK229" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL229" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM229" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN229" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO229" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP229" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ229" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR229" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="230" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A230" s="1">
+        <v>1</v>
+      </c>
+      <c r="B230" s="2">
+        <v>2</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F230" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G230" s="5">
+        <v>229</v>
+      </c>
+      <c r="H230" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I230" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J230" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K230" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L230" s="6">
+        <v>5256</v>
+      </c>
+      <c r="M230" s="7">
+        <v>898491.83</v>
+      </c>
+      <c r="N230" s="6">
+        <v>1</v>
+      </c>
+      <c r="O230" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P230" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q230" s="6">
+        <v>0</v>
+      </c>
+      <c r="R230" s="7">
+        <v>0</v>
+      </c>
+      <c r="S230" s="9">
+        <v>0</v>
+      </c>
+      <c r="T230" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U230" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V230" s="11">
+        <v>11</v>
+      </c>
+      <c r="W230" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X230" s="12">
+        <v>0.39791670000000001</v>
+      </c>
+      <c r="Y230" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z230" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA230" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB230" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC230" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD230" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE230" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF230" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG230" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH230" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI230" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ230" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK230" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL230" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM230" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN230" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO230" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP230" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ230" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR230" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="231" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A231" s="1">
+        <v>1</v>
+      </c>
+      <c r="B231" s="2">
+        <v>2</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F231" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G231" s="5">
+        <v>230</v>
+      </c>
+      <c r="H231" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I231" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J231" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K231" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L231" s="6">
+        <v>5257</v>
+      </c>
+      <c r="M231" s="7">
+        <v>898662.78</v>
+      </c>
+      <c r="N231" s="6">
+        <v>1</v>
+      </c>
+      <c r="O231" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P231" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q231" s="6">
+        <v>0</v>
+      </c>
+      <c r="R231" s="7">
+        <v>0</v>
+      </c>
+      <c r="S231" s="9">
+        <v>0</v>
+      </c>
+      <c r="T231" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U231" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V231" s="11">
+        <v>11</v>
+      </c>
+      <c r="W231" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X231" s="12">
+        <v>0.39791670000000001</v>
+      </c>
+      <c r="Y231" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z231" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA231" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB231" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC231" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD231" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE231" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF231" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG231" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH231" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI231" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ231" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK231" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL231" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM231" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN231" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO231" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP231" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ231" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR231" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="232" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A232" s="1">
+        <v>1</v>
+      </c>
+      <c r="B232" s="2">
+        <v>2</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F232" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G232" s="5">
+        <v>231</v>
+      </c>
+      <c r="H232" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I232" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J232" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K232" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L232" s="6">
+        <v>5258</v>
+      </c>
+      <c r="M232" s="7">
+        <v>898833.73</v>
+      </c>
+      <c r="N232" s="6">
+        <v>1</v>
+      </c>
+      <c r="O232" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P232" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q232" s="6">
+        <v>0</v>
+      </c>
+      <c r="R232" s="7">
+        <v>0</v>
+      </c>
+      <c r="S232" s="9">
+        <v>0</v>
+      </c>
+      <c r="T232" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U232" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V232" s="11">
+        <v>11</v>
+      </c>
+      <c r="W232" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X232" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y232" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z232" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA232" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB232" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC232" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD232" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE232" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF232" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG232" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH232" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI232" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ232" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK232" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL232" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM232" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN232" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO232" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP232" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ232" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR232" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="233" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A233" s="1">
+        <v>1</v>
+      </c>
+      <c r="B233" s="2">
+        <v>2</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F233" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G233" s="5">
+        <v>232</v>
+      </c>
+      <c r="H233" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I233" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J233" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K233" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L233" s="6">
+        <v>5259</v>
+      </c>
+      <c r="M233" s="7">
+        <v>899004.67</v>
+      </c>
+      <c r="N233" s="6">
+        <v>1</v>
+      </c>
+      <c r="O233" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P233" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q233" s="6">
+        <v>0</v>
+      </c>
+      <c r="R233" s="7">
+        <v>0</v>
+      </c>
+      <c r="S233" s="9">
+        <v>0</v>
+      </c>
+      <c r="T233" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U233" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V233" s="11">
+        <v>11</v>
+      </c>
+      <c r="W233" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X233" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y233" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z233" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA233" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB233" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC233" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD233" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE233" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF233" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG233" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH233" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI233" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ233" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK233" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL233" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM233" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN233" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO233" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP233" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ233" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR233" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="234" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A234" s="1">
+        <v>1</v>
+      </c>
+      <c r="B234" s="2">
+        <v>2</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F234" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G234" s="5">
+        <v>233</v>
+      </c>
+      <c r="H234" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I234" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J234" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K234" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L234" s="6">
+        <v>5260</v>
+      </c>
+      <c r="M234" s="7">
+        <v>899175.62</v>
+      </c>
+      <c r="N234" s="6">
+        <v>1</v>
+      </c>
+      <c r="O234" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P234" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q234" s="6">
+        <v>0</v>
+      </c>
+      <c r="R234" s="7">
+        <v>0</v>
+      </c>
+      <c r="S234" s="9">
+        <v>0</v>
+      </c>
+      <c r="T234" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U234" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V234" s="11">
+        <v>11</v>
+      </c>
+      <c r="W234" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X234" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y234" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z234" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA234" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB234" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC234" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD234" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE234" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF234" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG234" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH234" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI234" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ234" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK234" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL234" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM234" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN234" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO234" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP234" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ234" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR234" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="235" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A235" s="1">
+        <v>1</v>
+      </c>
+      <c r="B235" s="2">
+        <v>2</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F235" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G235" s="5">
+        <v>234</v>
+      </c>
+      <c r="H235" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I235" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J235" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K235" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L235" s="6">
+        <v>5261</v>
+      </c>
+      <c r="M235" s="7">
+        <v>899346.56</v>
+      </c>
+      <c r="N235" s="6">
+        <v>1</v>
+      </c>
+      <c r="O235" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P235" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q235" s="6">
+        <v>0</v>
+      </c>
+      <c r="R235" s="7">
+        <v>0</v>
+      </c>
+      <c r="S235" s="9">
+        <v>0</v>
+      </c>
+      <c r="T235" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U235" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V235" s="11">
+        <v>11</v>
+      </c>
+      <c r="W235" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X235" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y235" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z235" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA235" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB235" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC235" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD235" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE235" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF235" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG235" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH235" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI235" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ235" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK235" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL235" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM235" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN235" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO235" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP235" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ235" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR235" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="236" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A236" s="1">
+        <v>1</v>
+      </c>
+      <c r="B236" s="2">
+        <v>2</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F236" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G236" s="5">
+        <v>235</v>
+      </c>
+      <c r="H236" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I236" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J236" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K236" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L236" s="6">
+        <v>5262</v>
+      </c>
+      <c r="M236" s="7">
+        <v>899517.51</v>
+      </c>
+      <c r="N236" s="6">
+        <v>1</v>
+      </c>
+      <c r="O236" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P236" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q236" s="6">
+        <v>0</v>
+      </c>
+      <c r="R236" s="7">
+        <v>0</v>
+      </c>
+      <c r="S236" s="9">
+        <v>0</v>
+      </c>
+      <c r="T236" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U236" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V236" s="11">
+        <v>11</v>
+      </c>
+      <c r="W236" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X236" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y236" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z236" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA236" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB236" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC236" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD236" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE236" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF236" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG236" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH236" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI236" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ236" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK236" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL236" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM236" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN236" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO236" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP236" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ236" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR236" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="237" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A237" s="1">
+        <v>1</v>
+      </c>
+      <c r="B237" s="2">
+        <v>2</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F237" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G237" s="5">
+        <v>236</v>
+      </c>
+      <c r="H237" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I237" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J237" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K237" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L237" s="6">
+        <v>5263</v>
+      </c>
+      <c r="M237" s="7">
+        <v>899688.46</v>
+      </c>
+      <c r="N237" s="6">
+        <v>1</v>
+      </c>
+      <c r="O237" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P237" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q237" s="6">
+        <v>0</v>
+      </c>
+      <c r="R237" s="7">
+        <v>0</v>
+      </c>
+      <c r="S237" s="9">
+        <v>0</v>
+      </c>
+      <c r="T237" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U237" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V237" s="11">
+        <v>11</v>
+      </c>
+      <c r="W237" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X237" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y237" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z237" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA237" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB237" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC237" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD237" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE237" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF237" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG237" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH237" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI237" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ237" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK237" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL237" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM237" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN237" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO237" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP237" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ237" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR237" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="238" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A238" s="1">
+        <v>1</v>
+      </c>
+      <c r="B238" s="2">
+        <v>2</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F238" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G238" s="5">
+        <v>237</v>
+      </c>
+      <c r="H238" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I238" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J238" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K238" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L238" s="6">
+        <v>5264</v>
+      </c>
+      <c r="M238" s="7">
+        <v>899859.4</v>
+      </c>
+      <c r="N238" s="6">
+        <v>1</v>
+      </c>
+      <c r="O238" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P238" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q238" s="6">
+        <v>0</v>
+      </c>
+      <c r="R238" s="7">
+        <v>0</v>
+      </c>
+      <c r="S238" s="9">
+        <v>0</v>
+      </c>
+      <c r="T238" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U238" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V238" s="11">
+        <v>11</v>
+      </c>
+      <c r="W238" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X238" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y238" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z238" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA238" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB238" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC238" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD238" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE238" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF238" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG238" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH238" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI238" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ238" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK238" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL238" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM238" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN238" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO238" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP238" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ238" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR238" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="239" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A239" s="1">
+        <v>1</v>
+      </c>
+      <c r="B239" s="2">
+        <v>2</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F239" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G239" s="5">
+        <v>238</v>
+      </c>
+      <c r="H239" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I239" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J239" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K239" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L239" s="6">
+        <v>5265</v>
+      </c>
+      <c r="M239" s="7">
+        <v>900030.35</v>
+      </c>
+      <c r="N239" s="6">
+        <v>1</v>
+      </c>
+      <c r="O239" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P239" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q239" s="6">
+        <v>0</v>
+      </c>
+      <c r="R239" s="7">
+        <v>0</v>
+      </c>
+      <c r="S239" s="9">
+        <v>0</v>
+      </c>
+      <c r="T239" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U239" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V239" s="11">
+        <v>11</v>
+      </c>
+      <c r="W239" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X239" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y239" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z239" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA239" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB239" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC239" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD239" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE239" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF239" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG239" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH239" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI239" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ239" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK239" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL239" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM239" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN239" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO239" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP239" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ239" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR239" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="240" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A240" s="1">
+        <v>1</v>
+      </c>
+      <c r="B240" s="2">
+        <v>2</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F240" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G240" s="5">
+        <v>239</v>
+      </c>
+      <c r="H240" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I240" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J240" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K240" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L240" s="6">
+        <v>5266</v>
+      </c>
+      <c r="M240" s="7">
+        <v>900201.29</v>
+      </c>
+      <c r="N240" s="6">
+        <v>1</v>
+      </c>
+      <c r="O240" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P240" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q240" s="6">
+        <v>0</v>
+      </c>
+      <c r="R240" s="7">
+        <v>0</v>
+      </c>
+      <c r="S240" s="9">
+        <v>0</v>
+      </c>
+      <c r="T240" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U240" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V240" s="11">
+        <v>11</v>
+      </c>
+      <c r="W240" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X240" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y240" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z240" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA240" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB240" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC240" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD240" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE240" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF240" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG240" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH240" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI240" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ240" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK240" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL240" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM240" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN240" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO240" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP240" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ240" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR240" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="241" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A241" s="1">
+        <v>1</v>
+      </c>
+      <c r="B241" s="2">
+        <v>2</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F241" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G241" s="5">
+        <v>240</v>
+      </c>
+      <c r="H241" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I241" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J241" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K241" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L241" s="6">
+        <v>5267</v>
+      </c>
+      <c r="M241" s="7">
+        <v>900372.24</v>
+      </c>
+      <c r="N241" s="6">
+        <v>1</v>
+      </c>
+      <c r="O241" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P241" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q241" s="6">
+        <v>0</v>
+      </c>
+      <c r="R241" s="7">
+        <v>0</v>
+      </c>
+      <c r="S241" s="9">
+        <v>0</v>
+      </c>
+      <c r="T241" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U241" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V241" s="11">
+        <v>11</v>
+      </c>
+      <c r="W241" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X241" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y241" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z241" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA241" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB241" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC241" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD241" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE241" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF241" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG241" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH241" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI241" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ241" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK241" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL241" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM241" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN241" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO241" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP241" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ241" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR241" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="242" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A242" s="1">
+        <v>1</v>
+      </c>
+      <c r="B242" s="2">
+        <v>2</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F242" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G242" s="5">
+        <v>241</v>
+      </c>
+      <c r="H242" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I242" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J242" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K242" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L242" s="6">
+        <v>5268</v>
+      </c>
+      <c r="M242" s="7">
+        <v>900543.18</v>
+      </c>
+      <c r="N242" s="6">
+        <v>1</v>
+      </c>
+      <c r="O242" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P242" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q242" s="6">
+        <v>0</v>
+      </c>
+      <c r="R242" s="7">
+        <v>0</v>
+      </c>
+      <c r="S242" s="9">
+        <v>0</v>
+      </c>
+      <c r="T242" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U242" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V242" s="11">
+        <v>11</v>
+      </c>
+      <c r="W242" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X242" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y242" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z242" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA242" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB242" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC242" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD242" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE242" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF242" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG242" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH242" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI242" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ242" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK242" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL242" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM242" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN242" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO242" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP242" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ242" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR242" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="243" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A243" s="1">
+        <v>1</v>
+      </c>
+      <c r="B243" s="2">
+        <v>2</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F243" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G243" s="5">
+        <v>242</v>
+      </c>
+      <c r="H243" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I243" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J243" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K243" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L243" s="6">
+        <v>5269</v>
+      </c>
+      <c r="M243" s="7">
+        <v>900714.13</v>
+      </c>
+      <c r="N243" s="6">
+        <v>1</v>
+      </c>
+      <c r="O243" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P243" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q243" s="6">
+        <v>0</v>
+      </c>
+      <c r="R243" s="7">
+        <v>0</v>
+      </c>
+      <c r="S243" s="9">
+        <v>0</v>
+      </c>
+      <c r="T243" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U243" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V243" s="11">
+        <v>11</v>
+      </c>
+      <c r="W243" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X243" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y243" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z243" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA243" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB243" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC243" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD243" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE243" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF243" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG243" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH243" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI243" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ243" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK243" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL243" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM243" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN243" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO243" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP243" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ243" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR243" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="244" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A244" s="1">
+        <v>1</v>
+      </c>
+      <c r="B244" s="2">
+        <v>2</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F244" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G244" s="5">
+        <v>243</v>
+      </c>
+      <c r="H244" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I244" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J244" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K244" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L244" s="6">
+        <v>5270</v>
+      </c>
+      <c r="M244" s="7">
+        <v>900885.08</v>
+      </c>
+      <c r="N244" s="6">
+        <v>1</v>
+      </c>
+      <c r="O244" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P244" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q244" s="6">
+        <v>0</v>
+      </c>
+      <c r="R244" s="7">
+        <v>0</v>
+      </c>
+      <c r="S244" s="9">
+        <v>0</v>
+      </c>
+      <c r="T244" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U244" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V244" s="11">
+        <v>11</v>
+      </c>
+      <c r="W244" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X244" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y244" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z244" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA244" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB244" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC244" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD244" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE244" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF244" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG244" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH244" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI244" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ244" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK244" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL244" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM244" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN244" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO244" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP244" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ244" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR244" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="245" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A245" s="1">
+        <v>1</v>
+      </c>
+      <c r="B245" s="2">
+        <v>2</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E245" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F245" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G245" s="5">
+        <v>244</v>
+      </c>
+      <c r="H245" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I245" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J245" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K245" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L245" s="6">
+        <v>5271</v>
+      </c>
+      <c r="M245" s="7">
+        <v>901056.02</v>
+      </c>
+      <c r="N245" s="6">
+        <v>1</v>
+      </c>
+      <c r="O245" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P245" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q245" s="6">
+        <v>0</v>
+      </c>
+      <c r="R245" s="7">
+        <v>0</v>
+      </c>
+      <c r="S245" s="9">
+        <v>0</v>
+      </c>
+      <c r="T245" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U245" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V245" s="11">
+        <v>11</v>
+      </c>
+      <c r="W245" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X245" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y245" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z245" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA245" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB245" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC245" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD245" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE245" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF245" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG245" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH245" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI245" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ245" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK245" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL245" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM245" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN245" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO245" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP245" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ245" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR245" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="246" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A246" s="1">
+        <v>1</v>
+      </c>
+      <c r="B246" s="2">
+        <v>2</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F246" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G246" s="5">
+        <v>245</v>
+      </c>
+      <c r="H246" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I246" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J246" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K246" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L246" s="6">
+        <v>5272</v>
+      </c>
+      <c r="M246" s="7">
+        <v>901226.97</v>
+      </c>
+      <c r="N246" s="6">
+        <v>1</v>
+      </c>
+      <c r="O246" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P246" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q246" s="6">
+        <v>0</v>
+      </c>
+      <c r="R246" s="7">
+        <v>0</v>
+      </c>
+      <c r="S246" s="9">
+        <v>0</v>
+      </c>
+      <c r="T246" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U246" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V246" s="11">
+        <v>11</v>
+      </c>
+      <c r="W246" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X246" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y246" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z246" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA246" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB246" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC246" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD246" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE246" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF246" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG246" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH246" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI246" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ246" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK246" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL246" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM246" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN246" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO246" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP246" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ246" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR246" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="247" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A247" s="1">
+        <v>1</v>
+      </c>
+      <c r="B247" s="2">
+        <v>2</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E247" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F247" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G247" s="5">
+        <v>246</v>
+      </c>
+      <c r="H247" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I247" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J247" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K247" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L247" s="6">
+        <v>5273</v>
+      </c>
+      <c r="M247" s="7">
+        <v>901397.91</v>
+      </c>
+      <c r="N247" s="6">
+        <v>1</v>
+      </c>
+      <c r="O247" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P247" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q247" s="6">
+        <v>0</v>
+      </c>
+      <c r="R247" s="7">
+        <v>0</v>
+      </c>
+      <c r="S247" s="9">
+        <v>0</v>
+      </c>
+      <c r="T247" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U247" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V247" s="11">
+        <v>11</v>
+      </c>
+      <c r="W247" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X247" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y247" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z247" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA247" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB247" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC247" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD247" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE247" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF247" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG247" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH247" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI247" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ247" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK247" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL247" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM247" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN247" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO247" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP247" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ247" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR247" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="248" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A248" s="1">
+        <v>1</v>
+      </c>
+      <c r="B248" s="2">
+        <v>2</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F248" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G248" s="5">
+        <v>247</v>
+      </c>
+      <c r="H248" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I248" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J248" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K248" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L248" s="6">
+        <v>5274</v>
+      </c>
+      <c r="M248" s="7">
+        <v>901568.86</v>
+      </c>
+      <c r="N248" s="6">
+        <v>1</v>
+      </c>
+      <c r="O248" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P248" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q248" s="6">
+        <v>0</v>
+      </c>
+      <c r="R248" s="7">
+        <v>0</v>
+      </c>
+      <c r="S248" s="9">
+        <v>0</v>
+      </c>
+      <c r="T248" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U248" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V248" s="11">
+        <v>11</v>
+      </c>
+      <c r="W248" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X248" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y248" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z248" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA248" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB248" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC248" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD248" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE248" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF248" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG248" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH248" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI248" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ248" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK248" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL248" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM248" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN248" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO248" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP248" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ248" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR248" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="249" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A249" s="1">
+        <v>1</v>
+      </c>
+      <c r="B249" s="2">
+        <v>2</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F249" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G249" s="5">
+        <v>248</v>
+      </c>
+      <c r="H249" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I249" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J249" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K249" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L249" s="6">
+        <v>5275</v>
+      </c>
+      <c r="M249" s="7">
+        <v>901739.81</v>
+      </c>
+      <c r="N249" s="6">
+        <v>1</v>
+      </c>
+      <c r="O249" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P249" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q249" s="6">
+        <v>0</v>
+      </c>
+      <c r="R249" s="7">
+        <v>0</v>
+      </c>
+      <c r="S249" s="9">
+        <v>0</v>
+      </c>
+      <c r="T249" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U249" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V249" s="11">
+        <v>11</v>
+      </c>
+      <c r="W249" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X249" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y249" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z249" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA249" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB249" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC249" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD249" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE249" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF249" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG249" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH249" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI249" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ249" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK249" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL249" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM249" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN249" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO249" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP249" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ249" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR249" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="250" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A250" s="1">
+        <v>1</v>
+      </c>
+      <c r="B250" s="2">
+        <v>2</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F250" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G250" s="5">
+        <v>249</v>
+      </c>
+      <c r="H250" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I250" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J250" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K250" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L250" s="6">
+        <v>5276</v>
+      </c>
+      <c r="M250" s="7">
+        <v>901910.75</v>
+      </c>
+      <c r="N250" s="6">
+        <v>1</v>
+      </c>
+      <c r="O250" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P250" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q250" s="6">
+        <v>0</v>
+      </c>
+      <c r="R250" s="7">
+        <v>0</v>
+      </c>
+      <c r="S250" s="9">
+        <v>0</v>
+      </c>
+      <c r="T250" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U250" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V250" s="11">
+        <v>11</v>
+      </c>
+      <c r="W250" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X250" s="12">
+        <v>0.40555560000000002</v>
+      </c>
+      <c r="Y250" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z250" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA250" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB250" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC250" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD250" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE250" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF250" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG250" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH250" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI250" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ250" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK250" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL250" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM250" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN250" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO250" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP250" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ250" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR250" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="251" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A251" s="1">
+        <v>1</v>
+      </c>
+      <c r="B251" s="2">
+        <v>2</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F251" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G251" s="5">
+        <v>250</v>
+      </c>
+      <c r="H251" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I251" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J251" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K251" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L251" s="6">
+        <v>5277</v>
+      </c>
+      <c r="M251" s="7">
+        <v>902081.7</v>
+      </c>
+      <c r="N251" s="6">
+        <v>1</v>
+      </c>
+      <c r="O251" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P251" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q251" s="6">
+        <v>0</v>
+      </c>
+      <c r="R251" s="7">
+        <v>0</v>
+      </c>
+      <c r="S251" s="9">
+        <v>0</v>
+      </c>
+      <c r="T251" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U251" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V251" s="11">
+        <v>11</v>
+      </c>
+      <c r="W251" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X251" s="12">
+        <v>0.40555560000000002</v>
+      </c>
+      <c r="Y251" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z251" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA251" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB251" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC251" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD251" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE251" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF251" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG251" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH251" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI251" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ251" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK251" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL251" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM251" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN251" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO251" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP251" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ251" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR251" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="252" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A252" s="1">
+        <v>1</v>
+      </c>
+      <c r="B252" s="2">
+        <v>2</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E252" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F252" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G252" s="5">
+        <v>251</v>
+      </c>
+      <c r="H252" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I252" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J252" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K252" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L252" s="6">
+        <v>5278</v>
+      </c>
+      <c r="M252" s="7">
+        <v>902252.64</v>
+      </c>
+      <c r="N252" s="6">
+        <v>1</v>
+      </c>
+      <c r="O252" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P252" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q252" s="6">
+        <v>0</v>
+      </c>
+      <c r="R252" s="7">
+        <v>0</v>
+      </c>
+      <c r="S252" s="9">
+        <v>0</v>
+      </c>
+      <c r="T252" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U252" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V252" s="11">
+        <v>11</v>
+      </c>
+      <c r="W252" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X252" s="12">
+        <v>0.40555560000000002</v>
+      </c>
+      <c r="Y252" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z252" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA252" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB252" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC252" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD252" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE252" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF252" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG252" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH252" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI252" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ252" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK252" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL252" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM252" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN252" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO252" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP252" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ252" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR252" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="253" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A253" s="1">
+        <v>1</v>
+      </c>
+      <c r="B253" s="2">
+        <v>2</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F253" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G253" s="5">
+        <v>252</v>
+      </c>
+      <c r="H253" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I253" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J253" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K253" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L253" s="6">
+        <v>5279</v>
+      </c>
+      <c r="M253" s="7">
+        <v>902423.59</v>
+      </c>
+      <c r="N253" s="6">
+        <v>1</v>
+      </c>
+      <c r="O253" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P253" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q253" s="6">
+        <v>0</v>
+      </c>
+      <c r="R253" s="7">
+        <v>0</v>
+      </c>
+      <c r="S253" s="9">
+        <v>0</v>
+      </c>
+      <c r="T253" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U253" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V253" s="11">
+        <v>11</v>
+      </c>
+      <c r="W253" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X253" s="12">
+        <v>0.40555560000000002</v>
+      </c>
+      <c r="Y253" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z253" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA253" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB253" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC253" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD253" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE253" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF253" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG253" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH253" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI253" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ253" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK253" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL253" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM253" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN253" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO253" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP253" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ253" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR253" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="254" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A254" s="1">
+        <v>1</v>
+      </c>
+      <c r="B254" s="2">
+        <v>2</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E254" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F254" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G254" s="5">
+        <v>253</v>
+      </c>
+      <c r="H254" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I254" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J254" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K254" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L254" s="6">
+        <v>5280</v>
+      </c>
+      <c r="M254" s="7">
+        <v>902594.54</v>
+      </c>
+      <c r="N254" s="6">
+        <v>1</v>
+      </c>
+      <c r="O254" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P254" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q254" s="6">
+        <v>0</v>
+      </c>
+      <c r="R254" s="7">
+        <v>0</v>
+      </c>
+      <c r="S254" s="9">
+        <v>0</v>
+      </c>
+      <c r="T254" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U254" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V254" s="11">
+        <v>11</v>
+      </c>
+      <c r="W254" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X254" s="12">
+        <v>0.40555560000000002</v>
+      </c>
+      <c r="Y254" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z254" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA254" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB254" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC254" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD254" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE254" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF254" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG254" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH254" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI254" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ254" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK254" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL254" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM254" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN254" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO254" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP254" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ254" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR254" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="255" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A255" s="1">
+        <v>1</v>
+      </c>
+      <c r="B255" s="2">
+        <v>2</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F255" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G255" s="5">
+        <v>254</v>
+      </c>
+      <c r="H255" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I255" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J255" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K255" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L255" s="6">
+        <v>5281</v>
+      </c>
+      <c r="M255" s="7">
+        <v>902765.48</v>
+      </c>
+      <c r="N255" s="6">
+        <v>1</v>
+      </c>
+      <c r="O255" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P255" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q255" s="6">
+        <v>0</v>
+      </c>
+      <c r="R255" s="7">
+        <v>0</v>
+      </c>
+      <c r="S255" s="9">
+        <v>0</v>
+      </c>
+      <c r="T255" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U255" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V255" s="11">
+        <v>11</v>
+      </c>
+      <c r="W255" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X255" s="12">
+        <v>0.40555560000000002</v>
+      </c>
+      <c r="Y255" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z255" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA255" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB255" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC255" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD255" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE255" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF255" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG255" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH255" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI255" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ255" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK255" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL255" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM255" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN255" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO255" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP255" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ255" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR255" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="256" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A256" s="1">
+        <v>1</v>
+      </c>
+      <c r="B256" s="2">
+        <v>2</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F256" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G256" s="5">
+        <v>255</v>
+      </c>
+      <c r="H256" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I256" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J256" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K256" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L256" s="6">
+        <v>5282</v>
+      </c>
+      <c r="M256" s="7">
+        <v>902936.43</v>
+      </c>
+      <c r="N256" s="6">
+        <v>1</v>
+      </c>
+      <c r="O256" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P256" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q256" s="6">
+        <v>0</v>
+      </c>
+      <c r="R256" s="7">
+        <v>0</v>
+      </c>
+      <c r="S256" s="9">
+        <v>0</v>
+      </c>
+      <c r="T256" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U256" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V256" s="11">
+        <v>11</v>
+      </c>
+      <c r="W256" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X256" s="12">
+        <v>0.40555560000000002</v>
+      </c>
+      <c r="Y256" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z256" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA256" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB256" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC256" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD256" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE256" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF256" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG256" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH256" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI256" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ256" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK256" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL256" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM256" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN256" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO256" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP256" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ256" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR256" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="257" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A257" s="1">
+        <v>1</v>
+      </c>
+      <c r="B257" s="2">
+        <v>2</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F257" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G257" s="5">
+        <v>256</v>
+      </c>
+      <c r="H257" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I257" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J257" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K257" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L257" s="6">
+        <v>5283</v>
+      </c>
+      <c r="M257" s="7">
+        <v>903107.37</v>
+      </c>
+      <c r="N257" s="6">
+        <v>1</v>
+      </c>
+      <c r="O257" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P257" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q257" s="6">
+        <v>0</v>
+      </c>
+      <c r="R257" s="7">
+        <v>0</v>
+      </c>
+      <c r="S257" s="9">
+        <v>0</v>
+      </c>
+      <c r="T257" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U257" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V257" s="11">
+        <v>11</v>
+      </c>
+      <c r="W257" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X257" s="12">
+        <v>0.40555560000000002</v>
+      </c>
+      <c r="Y257" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z257" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA257" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB257" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC257" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD257" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE257" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF257" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG257" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH257" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI257" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ257" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK257" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL257" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM257" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN257" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO257" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP257" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ257" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR257" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="258" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A258" s="1">
+        <v>1</v>
+      </c>
+      <c r="B258" s="2">
+        <v>2</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F258" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G258" s="5">
+        <v>257</v>
+      </c>
+      <c r="H258" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I258" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J258" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K258" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L258" s="6">
+        <v>5284</v>
+      </c>
+      <c r="M258" s="7">
+        <v>903278.32</v>
+      </c>
+      <c r="N258" s="6">
+        <v>1</v>
+      </c>
+      <c r="O258" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P258" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q258" s="6">
+        <v>0</v>
+      </c>
+      <c r="R258" s="7">
+        <v>0</v>
+      </c>
+      <c r="S258" s="9">
+        <v>0</v>
+      </c>
+      <c r="T258" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U258" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V258" s="11">
+        <v>11</v>
+      </c>
+      <c r="W258" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X258" s="12">
+        <v>0.40555560000000002</v>
+      </c>
+      <c r="Y258" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z258" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA258" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB258" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC258" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD258" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE258" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF258" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG258" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH258" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI258" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ258" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK258" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL258" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM258" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN258" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO258" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP258" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ258" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR258" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="259" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A259" s="1">
+        <v>1</v>
+      </c>
+      <c r="B259" s="2">
+        <v>2</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F259" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G259" s="5">
+        <v>258</v>
+      </c>
+      <c r="H259" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I259" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J259" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K259" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L259" s="6">
+        <v>5285</v>
+      </c>
+      <c r="M259" s="7">
+        <v>903449.27</v>
+      </c>
+      <c r="N259" s="6">
+        <v>1</v>
+      </c>
+      <c r="O259" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P259" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q259" s="6">
+        <v>0</v>
+      </c>
+      <c r="R259" s="7">
+        <v>0</v>
+      </c>
+      <c r="S259" s="9">
+        <v>0</v>
+      </c>
+      <c r="T259" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U259" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V259" s="11">
+        <v>11</v>
+      </c>
+      <c r="W259" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X259" s="12">
+        <v>0.40555560000000002</v>
+      </c>
+      <c r="Y259" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z259" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA259" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB259" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC259" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD259" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE259" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF259" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG259" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH259" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI259" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ259" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK259" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL259" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM259" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN259" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO259" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP259" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ259" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR259" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="260" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A260" s="1">
+        <v>1</v>
+      </c>
+      <c r="B260" s="2">
+        <v>2</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F260" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G260" s="5">
+        <v>259</v>
+      </c>
+      <c r="H260" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I260" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J260" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K260" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L260" s="6">
+        <v>5286</v>
+      </c>
+      <c r="M260" s="7">
+        <v>903620.21</v>
+      </c>
+      <c r="N260" s="6">
+        <v>1</v>
+      </c>
+      <c r="O260" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P260" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q260" s="6">
+        <v>0</v>
+      </c>
+      <c r="R260" s="7">
+        <v>0</v>
+      </c>
+      <c r="S260" s="9">
+        <v>0</v>
+      </c>
+      <c r="T260" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U260" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V260" s="11">
+        <v>11</v>
+      </c>
+      <c r="W260" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X260" s="12">
+        <v>0.40555560000000002</v>
+      </c>
+      <c r="Y260" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z260" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA260" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB260" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC260" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD260" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE260" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF260" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG260" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH260" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI260" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ260" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK260" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL260" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM260" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN260" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO260" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP260" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ260" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR260" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="261" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A261" s="1">
+        <v>1</v>
+      </c>
+      <c r="B261" s="2">
+        <v>2</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E261" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F261" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G261" s="5">
+        <v>260</v>
+      </c>
+      <c r="H261" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I261" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J261" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K261" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L261" s="6">
+        <v>5287</v>
+      </c>
+      <c r="M261" s="7">
+        <v>903791.16</v>
+      </c>
+      <c r="N261" s="6">
+        <v>1</v>
+      </c>
+      <c r="O261" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P261" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q261" s="6">
+        <v>0</v>
+      </c>
+      <c r="R261" s="7">
+        <v>0</v>
+      </c>
+      <c r="S261" s="9">
+        <v>0</v>
+      </c>
+      <c r="T261" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U261" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V261" s="11">
+        <v>11</v>
+      </c>
+      <c r="W261" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X261" s="12">
+        <v>0.40555560000000002</v>
+      </c>
+      <c r="Y261" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z261" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA261" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB261" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC261" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD261" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE261" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF261" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG261" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH261" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI261" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ261" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK261" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL261" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM261" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN261" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO261" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP261" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ261" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR261" s="3" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A182B5E0-65CA-43F2-99E4-D76B178A9BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A901D02-914D-4536-9CF5-80DB5471E4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="696" yWindow="708" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4724" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6020" uniqueCount="387">
   <si>
     <t>Sel</t>
   </si>
@@ -966,6 +966,222 @@
   <si>
     <t>1858700158820</t>
   </si>
+  <si>
+    <t>1858700158821</t>
+  </si>
+  <si>
+    <t>1858700158822</t>
+  </si>
+  <si>
+    <t>1858700158823</t>
+  </si>
+  <si>
+    <t>1858700158824</t>
+  </si>
+  <si>
+    <t>1858700158825</t>
+  </si>
+  <si>
+    <t>1858700158826</t>
+  </si>
+  <si>
+    <t>1858700158827</t>
+  </si>
+  <si>
+    <t>1858700158828</t>
+  </si>
+  <si>
+    <t>1858700158829</t>
+  </si>
+  <si>
+    <t>1858700158830</t>
+  </si>
+  <si>
+    <t>1858700158831</t>
+  </si>
+  <si>
+    <t>1858700158832</t>
+  </si>
+  <si>
+    <t>1858700158833</t>
+  </si>
+  <si>
+    <t>1858700158834</t>
+  </si>
+  <si>
+    <t>1858700158835</t>
+  </si>
+  <si>
+    <t>1858700158836</t>
+  </si>
+  <si>
+    <t>1858700158837</t>
+  </si>
+  <si>
+    <t>1858700158838</t>
+  </si>
+  <si>
+    <t>1858700158839</t>
+  </si>
+  <si>
+    <t>1858700158840</t>
+  </si>
+  <si>
+    <t>1858700158841</t>
+  </si>
+  <si>
+    <t>1858700158842</t>
+  </si>
+  <si>
+    <t>1858700158843</t>
+  </si>
+  <si>
+    <t>1858700158844</t>
+  </si>
+  <si>
+    <t>1858700158845</t>
+  </si>
+  <si>
+    <t>1858700158846</t>
+  </si>
+  <si>
+    <t>1858700158847</t>
+  </si>
+  <si>
+    <t>1858700158848</t>
+  </si>
+  <si>
+    <t>1858700158849</t>
+  </si>
+  <si>
+    <t>1858700158850</t>
+  </si>
+  <si>
+    <t>1858700158851</t>
+  </si>
+  <si>
+    <t>1858700158852</t>
+  </si>
+  <si>
+    <t>1858700158853</t>
+  </si>
+  <si>
+    <t>1858700158854</t>
+  </si>
+  <si>
+    <t>1858700158855</t>
+  </si>
+  <si>
+    <t>1858700158856</t>
+  </si>
+  <si>
+    <t>1858700158857</t>
+  </si>
+  <si>
+    <t>1858700158858</t>
+  </si>
+  <si>
+    <t>1858700158859</t>
+  </si>
+  <si>
+    <t>1858700158860</t>
+  </si>
+  <si>
+    <t>1858700158861</t>
+  </si>
+  <si>
+    <t>1858700158862</t>
+  </si>
+  <si>
+    <t>1858700158863</t>
+  </si>
+  <si>
+    <t>1858700158864</t>
+  </si>
+  <si>
+    <t>1858700158865</t>
+  </si>
+  <si>
+    <t>1858700158866</t>
+  </si>
+  <si>
+    <t>1858700158867</t>
+  </si>
+  <si>
+    <t>1858700158868</t>
+  </si>
+  <si>
+    <t>1858700158869</t>
+  </si>
+  <si>
+    <t>1858700158870</t>
+  </si>
+  <si>
+    <t>1858700158871</t>
+  </si>
+  <si>
+    <t>1858700158872</t>
+  </si>
+  <si>
+    <t>1858700158873</t>
+  </si>
+  <si>
+    <t>1858700158874</t>
+  </si>
+  <si>
+    <t>1858700158875</t>
+  </si>
+  <si>
+    <t>1858700158876</t>
+  </si>
+  <si>
+    <t>1858700158877</t>
+  </si>
+  <si>
+    <t>1858700158878</t>
+  </si>
+  <si>
+    <t>1858700158879</t>
+  </si>
+  <si>
+    <t>1858700158880</t>
+  </si>
+  <si>
+    <t>1858700158881</t>
+  </si>
+  <si>
+    <t>1858700158882</t>
+  </si>
+  <si>
+    <t>1858700158883</t>
+  </si>
+  <si>
+    <t>1858700158884</t>
+  </si>
+  <si>
+    <t>1858700158885</t>
+  </si>
+  <si>
+    <t>1858700158886</t>
+  </si>
+  <si>
+    <t>1858700158887</t>
+  </si>
+  <si>
+    <t>1858700158888</t>
+  </si>
+  <si>
+    <t>1858700158889</t>
+  </si>
+  <si>
+    <t>1858700158890</t>
+  </si>
+  <si>
+    <t>1858700158891</t>
+  </si>
+  <si>
+    <t>1858700158892</t>
+  </si>
 </sst>
 </file>
 
@@ -1540,7 +1756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR261"/>
+  <dimension ref="A1:AR333"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -36515,6 +36731,9654 @@
       </c>
       <c r="AR261" s="3" t="s">
         <v>314</v>
+      </c>
+    </row>
+    <row r="262" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A262" s="1">
+        <v>1</v>
+      </c>
+      <c r="B262" s="2">
+        <v>2</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E262" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F262" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G262" s="5">
+        <v>442</v>
+      </c>
+      <c r="H262" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I262" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J262" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K262" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L262" s="6">
+        <v>5288</v>
+      </c>
+      <c r="M262" s="7">
+        <v>903962.1</v>
+      </c>
+      <c r="N262" s="6">
+        <v>1</v>
+      </c>
+      <c r="O262" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P262" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q262" s="6">
+        <v>0</v>
+      </c>
+      <c r="R262" s="7">
+        <v>0</v>
+      </c>
+      <c r="S262" s="9">
+        <v>0</v>
+      </c>
+      <c r="T262" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U262" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V262" s="11">
+        <v>11</v>
+      </c>
+      <c r="W262" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X262" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y262" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z262" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA262" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB262" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC262" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD262" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE262" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF262" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG262" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH262" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI262" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ262" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK262" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL262" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM262" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN262" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO262" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP262" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ262" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR262" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="263" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A263" s="1">
+        <v>1</v>
+      </c>
+      <c r="B263" s="2">
+        <v>2</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E263" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F263" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G263" s="5">
+        <v>443</v>
+      </c>
+      <c r="H263" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I263" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J263" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K263" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L263" s="6">
+        <v>5289</v>
+      </c>
+      <c r="M263" s="7">
+        <v>904133.05</v>
+      </c>
+      <c r="N263" s="6">
+        <v>1</v>
+      </c>
+      <c r="O263" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P263" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q263" s="6">
+        <v>0</v>
+      </c>
+      <c r="R263" s="7">
+        <v>0</v>
+      </c>
+      <c r="S263" s="9">
+        <v>0</v>
+      </c>
+      <c r="T263" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U263" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V263" s="11">
+        <v>11</v>
+      </c>
+      <c r="W263" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X263" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y263" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z263" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA263" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB263" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC263" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD263" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE263" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF263" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG263" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH263" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI263" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ263" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK263" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL263" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM263" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN263" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO263" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP263" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ263" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR263" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="264" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A264" s="1">
+        <v>1</v>
+      </c>
+      <c r="B264" s="2">
+        <v>2</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E264" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F264" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G264" s="5">
+        <v>444</v>
+      </c>
+      <c r="H264" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I264" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J264" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K264" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L264" s="6">
+        <v>5290</v>
+      </c>
+      <c r="M264" s="7">
+        <v>904304</v>
+      </c>
+      <c r="N264" s="6">
+        <v>1</v>
+      </c>
+      <c r="O264" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P264" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q264" s="6">
+        <v>0</v>
+      </c>
+      <c r="R264" s="7">
+        <v>0</v>
+      </c>
+      <c r="S264" s="9">
+        <v>0</v>
+      </c>
+      <c r="T264" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U264" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V264" s="11">
+        <v>11</v>
+      </c>
+      <c r="W264" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X264" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y264" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z264" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA264" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB264" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC264" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD264" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE264" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF264" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG264" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH264" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI264" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ264" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK264" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL264" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM264" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN264" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO264" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP264" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ264" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR264" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="265" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A265" s="1">
+        <v>1</v>
+      </c>
+      <c r="B265" s="2">
+        <v>2</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E265" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F265" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G265" s="5">
+        <v>445</v>
+      </c>
+      <c r="H265" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I265" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J265" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K265" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L265" s="6">
+        <v>5291</v>
+      </c>
+      <c r="M265" s="7">
+        <v>904474.94</v>
+      </c>
+      <c r="N265" s="6">
+        <v>1</v>
+      </c>
+      <c r="O265" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P265" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q265" s="6">
+        <v>0</v>
+      </c>
+      <c r="R265" s="7">
+        <v>0</v>
+      </c>
+      <c r="S265" s="9">
+        <v>0</v>
+      </c>
+      <c r="T265" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U265" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V265" s="11">
+        <v>11</v>
+      </c>
+      <c r="W265" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X265" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y265" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z265" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA265" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB265" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC265" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD265" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE265" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF265" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG265" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH265" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI265" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ265" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK265" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL265" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM265" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN265" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO265" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP265" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ265" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR265" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="266" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A266" s="1">
+        <v>1</v>
+      </c>
+      <c r="B266" s="2">
+        <v>2</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E266" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F266" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G266" s="5">
+        <v>446</v>
+      </c>
+      <c r="H266" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I266" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J266" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K266" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L266" s="6">
+        <v>5292</v>
+      </c>
+      <c r="M266" s="7">
+        <v>904645.89</v>
+      </c>
+      <c r="N266" s="6">
+        <v>1</v>
+      </c>
+      <c r="O266" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P266" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q266" s="6">
+        <v>0</v>
+      </c>
+      <c r="R266" s="7">
+        <v>0</v>
+      </c>
+      <c r="S266" s="9">
+        <v>0</v>
+      </c>
+      <c r="T266" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U266" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V266" s="11">
+        <v>11</v>
+      </c>
+      <c r="W266" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X266" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y266" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z266" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA266" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB266" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC266" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD266" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE266" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF266" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG266" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH266" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI266" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ266" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK266" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL266" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM266" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN266" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO266" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP266" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ266" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR266" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="267" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A267" s="1">
+        <v>1</v>
+      </c>
+      <c r="B267" s="2">
+        <v>2</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E267" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F267" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G267" s="5">
+        <v>447</v>
+      </c>
+      <c r="H267" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I267" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J267" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K267" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L267" s="6">
+        <v>5293</v>
+      </c>
+      <c r="M267" s="7">
+        <v>904816.83</v>
+      </c>
+      <c r="N267" s="6">
+        <v>1</v>
+      </c>
+      <c r="O267" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P267" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q267" s="6">
+        <v>0</v>
+      </c>
+      <c r="R267" s="7">
+        <v>0</v>
+      </c>
+      <c r="S267" s="9">
+        <v>0</v>
+      </c>
+      <c r="T267" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U267" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V267" s="11">
+        <v>11</v>
+      </c>
+      <c r="W267" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X267" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y267" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z267" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA267" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB267" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC267" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD267" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE267" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF267" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG267" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH267" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI267" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ267" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK267" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL267" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM267" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN267" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO267" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP267" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ267" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR267" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="268" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A268" s="1">
+        <v>1</v>
+      </c>
+      <c r="B268" s="2">
+        <v>2</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E268" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F268" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G268" s="5">
+        <v>448</v>
+      </c>
+      <c r="H268" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I268" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J268" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K268" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L268" s="6">
+        <v>5294</v>
+      </c>
+      <c r="M268" s="7">
+        <v>904987.78</v>
+      </c>
+      <c r="N268" s="6">
+        <v>1</v>
+      </c>
+      <c r="O268" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P268" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q268" s="6">
+        <v>0</v>
+      </c>
+      <c r="R268" s="7">
+        <v>0</v>
+      </c>
+      <c r="S268" s="9">
+        <v>0</v>
+      </c>
+      <c r="T268" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U268" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V268" s="11">
+        <v>11</v>
+      </c>
+      <c r="W268" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X268" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y268" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z268" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA268" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB268" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC268" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD268" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE268" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF268" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG268" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH268" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI268" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ268" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK268" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL268" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM268" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN268" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO268" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP268" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ268" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR268" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="269" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A269" s="1">
+        <v>1</v>
+      </c>
+      <c r="B269" s="2">
+        <v>2</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F269" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G269" s="5">
+        <v>449</v>
+      </c>
+      <c r="H269" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I269" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J269" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K269" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L269" s="6">
+        <v>5295</v>
+      </c>
+      <c r="M269" s="7">
+        <v>905158.73</v>
+      </c>
+      <c r="N269" s="6">
+        <v>1</v>
+      </c>
+      <c r="O269" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P269" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q269" s="6">
+        <v>0</v>
+      </c>
+      <c r="R269" s="7">
+        <v>0</v>
+      </c>
+      <c r="S269" s="9">
+        <v>0</v>
+      </c>
+      <c r="T269" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U269" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V269" s="11">
+        <v>11</v>
+      </c>
+      <c r="W269" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X269" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y269" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z269" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA269" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB269" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC269" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD269" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE269" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF269" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG269" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH269" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI269" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ269" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK269" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL269" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM269" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN269" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO269" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP269" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ269" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR269" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="270" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A270" s="1">
+        <v>1</v>
+      </c>
+      <c r="B270" s="2">
+        <v>2</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E270" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F270" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G270" s="5">
+        <v>450</v>
+      </c>
+      <c r="H270" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I270" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J270" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K270" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L270" s="6">
+        <v>5296</v>
+      </c>
+      <c r="M270" s="7">
+        <v>905329.67</v>
+      </c>
+      <c r="N270" s="6">
+        <v>1</v>
+      </c>
+      <c r="O270" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P270" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q270" s="6">
+        <v>0</v>
+      </c>
+      <c r="R270" s="7">
+        <v>0</v>
+      </c>
+      <c r="S270" s="9">
+        <v>0</v>
+      </c>
+      <c r="T270" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U270" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V270" s="11">
+        <v>11</v>
+      </c>
+      <c r="W270" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X270" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y270" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z270" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA270" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB270" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC270" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD270" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE270" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF270" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG270" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH270" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI270" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ270" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK270" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL270" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM270" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN270" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO270" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP270" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ270" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR270" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="271" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A271" s="1">
+        <v>1</v>
+      </c>
+      <c r="B271" s="2">
+        <v>2</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E271" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F271" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G271" s="5">
+        <v>451</v>
+      </c>
+      <c r="H271" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I271" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J271" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K271" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L271" s="6">
+        <v>5297</v>
+      </c>
+      <c r="M271" s="7">
+        <v>905500.62</v>
+      </c>
+      <c r="N271" s="6">
+        <v>1</v>
+      </c>
+      <c r="O271" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P271" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q271" s="6">
+        <v>0</v>
+      </c>
+      <c r="R271" s="7">
+        <v>0</v>
+      </c>
+      <c r="S271" s="9">
+        <v>0</v>
+      </c>
+      <c r="T271" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U271" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V271" s="11">
+        <v>11</v>
+      </c>
+      <c r="W271" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X271" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y271" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z271" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA271" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB271" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC271" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD271" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE271" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF271" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG271" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH271" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI271" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ271" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK271" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL271" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM271" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN271" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO271" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP271" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ271" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR271" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="272" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A272" s="1">
+        <v>1</v>
+      </c>
+      <c r="B272" s="2">
+        <v>2</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E272" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F272" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G272" s="5">
+        <v>452</v>
+      </c>
+      <c r="H272" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I272" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J272" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K272" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L272" s="6">
+        <v>5298</v>
+      </c>
+      <c r="M272" s="7">
+        <v>905671.56</v>
+      </c>
+      <c r="N272" s="6">
+        <v>1</v>
+      </c>
+      <c r="O272" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P272" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q272" s="6">
+        <v>0</v>
+      </c>
+      <c r="R272" s="7">
+        <v>0</v>
+      </c>
+      <c r="S272" s="9">
+        <v>0</v>
+      </c>
+      <c r="T272" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U272" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V272" s="11">
+        <v>11</v>
+      </c>
+      <c r="W272" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X272" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y272" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z272" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA272" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB272" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC272" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD272" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE272" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF272" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG272" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH272" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI272" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ272" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK272" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL272" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM272" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN272" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO272" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP272" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ272" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR272" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="273" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A273" s="1">
+        <v>1</v>
+      </c>
+      <c r="B273" s="2">
+        <v>2</v>
+      </c>
+      <c r="C273" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E273" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F273" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G273" s="5">
+        <v>453</v>
+      </c>
+      <c r="H273" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I273" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J273" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K273" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L273" s="6">
+        <v>5299</v>
+      </c>
+      <c r="M273" s="7">
+        <v>905842.51</v>
+      </c>
+      <c r="N273" s="6">
+        <v>1</v>
+      </c>
+      <c r="O273" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P273" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q273" s="6">
+        <v>0</v>
+      </c>
+      <c r="R273" s="7">
+        <v>0</v>
+      </c>
+      <c r="S273" s="9">
+        <v>0</v>
+      </c>
+      <c r="T273" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U273" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V273" s="11">
+        <v>11</v>
+      </c>
+      <c r="W273" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X273" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y273" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z273" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA273" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB273" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC273" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD273" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE273" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF273" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG273" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH273" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI273" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ273" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK273" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL273" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM273" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN273" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO273" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP273" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ273" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR273" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="274" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A274" s="1">
+        <v>1</v>
+      </c>
+      <c r="B274" s="2">
+        <v>2</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E274" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F274" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G274" s="5">
+        <v>454</v>
+      </c>
+      <c r="H274" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I274" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J274" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K274" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L274" s="6">
+        <v>5300</v>
+      </c>
+      <c r="M274" s="7">
+        <v>906013.45</v>
+      </c>
+      <c r="N274" s="6">
+        <v>1</v>
+      </c>
+      <c r="O274" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P274" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q274" s="6">
+        <v>0</v>
+      </c>
+      <c r="R274" s="7">
+        <v>0</v>
+      </c>
+      <c r="S274" s="9">
+        <v>0</v>
+      </c>
+      <c r="T274" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U274" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V274" s="11">
+        <v>11</v>
+      </c>
+      <c r="W274" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X274" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y274" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z274" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA274" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB274" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC274" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD274" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE274" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF274" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG274" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH274" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI274" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ274" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK274" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL274" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM274" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN274" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO274" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP274" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ274" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR274" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="275" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A275" s="1">
+        <v>1</v>
+      </c>
+      <c r="B275" s="2">
+        <v>2</v>
+      </c>
+      <c r="C275" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F275" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G275" s="5">
+        <v>455</v>
+      </c>
+      <c r="H275" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I275" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J275" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K275" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L275" s="6">
+        <v>5301</v>
+      </c>
+      <c r="M275" s="7">
+        <v>906184.4</v>
+      </c>
+      <c r="N275" s="6">
+        <v>1</v>
+      </c>
+      <c r="O275" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P275" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q275" s="6">
+        <v>0</v>
+      </c>
+      <c r="R275" s="7">
+        <v>0</v>
+      </c>
+      <c r="S275" s="9">
+        <v>0</v>
+      </c>
+      <c r="T275" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U275" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V275" s="11">
+        <v>11</v>
+      </c>
+      <c r="W275" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X275" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y275" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z275" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA275" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB275" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC275" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD275" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE275" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF275" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG275" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH275" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI275" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ275" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK275" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL275" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM275" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN275" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO275" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP275" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ275" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR275" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="276" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A276" s="1">
+        <v>1</v>
+      </c>
+      <c r="B276" s="2">
+        <v>2</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E276" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F276" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G276" s="5">
+        <v>456</v>
+      </c>
+      <c r="H276" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I276" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J276" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K276" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L276" s="6">
+        <v>5302</v>
+      </c>
+      <c r="M276" s="7">
+        <v>906355.35</v>
+      </c>
+      <c r="N276" s="6">
+        <v>1</v>
+      </c>
+      <c r="O276" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P276" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q276" s="6">
+        <v>0</v>
+      </c>
+      <c r="R276" s="7">
+        <v>0</v>
+      </c>
+      <c r="S276" s="9">
+        <v>0</v>
+      </c>
+      <c r="T276" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U276" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V276" s="11">
+        <v>11</v>
+      </c>
+      <c r="W276" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X276" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y276" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z276" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA276" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB276" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC276" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD276" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE276" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF276" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG276" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH276" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI276" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ276" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK276" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL276" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM276" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN276" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO276" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP276" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ276" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR276" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="277" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A277" s="1">
+        <v>1</v>
+      </c>
+      <c r="B277" s="2">
+        <v>2</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E277" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F277" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G277" s="5">
+        <v>457</v>
+      </c>
+      <c r="H277" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I277" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J277" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K277" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L277" s="6">
+        <v>5303</v>
+      </c>
+      <c r="M277" s="7">
+        <v>906526.29</v>
+      </c>
+      <c r="N277" s="6">
+        <v>1</v>
+      </c>
+      <c r="O277" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P277" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q277" s="6">
+        <v>0</v>
+      </c>
+      <c r="R277" s="7">
+        <v>0</v>
+      </c>
+      <c r="S277" s="9">
+        <v>0</v>
+      </c>
+      <c r="T277" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U277" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V277" s="11">
+        <v>11</v>
+      </c>
+      <c r="W277" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X277" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y277" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z277" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA277" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB277" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC277" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD277" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE277" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF277" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG277" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH277" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI277" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ277" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK277" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL277" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM277" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN277" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO277" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP277" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ277" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR277" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="278" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A278" s="1">
+        <v>1</v>
+      </c>
+      <c r="B278" s="2">
+        <v>2</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E278" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F278" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G278" s="5">
+        <v>458</v>
+      </c>
+      <c r="H278" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I278" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J278" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K278" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L278" s="6">
+        <v>5304</v>
+      </c>
+      <c r="M278" s="7">
+        <v>906697.24</v>
+      </c>
+      <c r="N278" s="6">
+        <v>1</v>
+      </c>
+      <c r="O278" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P278" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q278" s="6">
+        <v>0</v>
+      </c>
+      <c r="R278" s="7">
+        <v>0</v>
+      </c>
+      <c r="S278" s="9">
+        <v>0</v>
+      </c>
+      <c r="T278" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U278" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V278" s="11">
+        <v>11</v>
+      </c>
+      <c r="W278" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X278" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y278" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z278" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA278" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB278" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC278" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD278" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE278" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF278" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG278" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH278" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI278" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ278" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK278" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL278" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM278" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN278" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO278" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP278" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ278" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR278" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="279" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A279" s="1">
+        <v>1</v>
+      </c>
+      <c r="B279" s="2">
+        <v>2</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F279" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G279" s="5">
+        <v>459</v>
+      </c>
+      <c r="H279" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I279" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J279" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K279" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L279" s="6">
+        <v>5305</v>
+      </c>
+      <c r="M279" s="7">
+        <v>906868.18</v>
+      </c>
+      <c r="N279" s="6">
+        <v>1</v>
+      </c>
+      <c r="O279" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P279" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q279" s="6">
+        <v>0</v>
+      </c>
+      <c r="R279" s="7">
+        <v>0</v>
+      </c>
+      <c r="S279" s="9">
+        <v>0</v>
+      </c>
+      <c r="T279" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U279" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V279" s="11">
+        <v>11</v>
+      </c>
+      <c r="W279" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X279" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y279" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z279" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA279" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB279" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC279" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD279" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE279" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF279" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG279" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH279" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI279" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ279" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK279" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL279" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM279" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN279" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO279" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP279" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ279" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR279" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="280" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A280" s="1">
+        <v>1</v>
+      </c>
+      <c r="B280" s="2">
+        <v>2</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E280" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F280" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G280" s="5">
+        <v>460</v>
+      </c>
+      <c r="H280" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I280" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J280" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K280" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L280" s="6">
+        <v>5306</v>
+      </c>
+      <c r="M280" s="7">
+        <v>907039.13</v>
+      </c>
+      <c r="N280" s="6">
+        <v>1</v>
+      </c>
+      <c r="O280" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P280" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q280" s="6">
+        <v>0</v>
+      </c>
+      <c r="R280" s="7">
+        <v>0</v>
+      </c>
+      <c r="S280" s="9">
+        <v>0</v>
+      </c>
+      <c r="T280" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U280" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V280" s="11">
+        <v>11</v>
+      </c>
+      <c r="W280" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X280" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y280" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z280" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA280" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB280" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC280" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD280" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE280" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF280" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG280" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH280" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI280" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ280" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK280" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL280" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM280" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN280" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO280" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP280" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ280" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR280" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="281" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A281" s="1">
+        <v>1</v>
+      </c>
+      <c r="B281" s="2">
+        <v>2</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E281" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F281" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G281" s="5">
+        <v>461</v>
+      </c>
+      <c r="H281" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I281" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J281" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K281" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L281" s="6">
+        <v>5307</v>
+      </c>
+      <c r="M281" s="7">
+        <v>907210.08</v>
+      </c>
+      <c r="N281" s="6">
+        <v>1</v>
+      </c>
+      <c r="O281" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P281" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q281" s="6">
+        <v>0</v>
+      </c>
+      <c r="R281" s="7">
+        <v>0</v>
+      </c>
+      <c r="S281" s="9">
+        <v>0</v>
+      </c>
+      <c r="T281" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U281" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V281" s="11">
+        <v>11</v>
+      </c>
+      <c r="W281" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X281" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y281" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z281" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA281" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB281" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC281" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD281" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE281" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF281" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG281" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH281" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI281" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ281" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK281" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL281" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM281" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN281" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO281" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP281" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ281" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR281" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="282" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A282" s="1">
+        <v>1</v>
+      </c>
+      <c r="B282" s="2">
+        <v>2</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E282" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F282" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G282" s="5">
+        <v>462</v>
+      </c>
+      <c r="H282" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I282" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J282" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K282" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L282" s="6">
+        <v>5308</v>
+      </c>
+      <c r="M282" s="7">
+        <v>907381.02</v>
+      </c>
+      <c r="N282" s="6">
+        <v>1</v>
+      </c>
+      <c r="O282" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P282" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q282" s="6">
+        <v>0</v>
+      </c>
+      <c r="R282" s="7">
+        <v>0</v>
+      </c>
+      <c r="S282" s="9">
+        <v>0</v>
+      </c>
+      <c r="T282" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U282" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V282" s="11">
+        <v>11</v>
+      </c>
+      <c r="W282" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X282" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y282" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z282" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA282" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB282" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC282" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD282" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE282" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF282" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG282" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH282" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI282" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ282" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK282" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL282" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM282" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN282" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO282" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP282" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ282" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR282" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="283" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A283" s="1">
+        <v>1</v>
+      </c>
+      <c r="B283" s="2">
+        <v>2</v>
+      </c>
+      <c r="C283" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E283" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F283" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G283" s="5">
+        <v>463</v>
+      </c>
+      <c r="H283" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I283" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J283" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K283" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L283" s="6">
+        <v>5309</v>
+      </c>
+      <c r="M283" s="7">
+        <v>907551.97</v>
+      </c>
+      <c r="N283" s="6">
+        <v>1</v>
+      </c>
+      <c r="O283" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P283" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q283" s="6">
+        <v>0</v>
+      </c>
+      <c r="R283" s="7">
+        <v>0</v>
+      </c>
+      <c r="S283" s="9">
+        <v>0</v>
+      </c>
+      <c r="T283" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U283" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V283" s="11">
+        <v>11</v>
+      </c>
+      <c r="W283" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X283" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y283" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z283" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA283" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB283" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC283" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD283" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE283" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF283" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG283" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH283" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI283" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ283" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK283" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL283" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM283" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN283" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO283" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP283" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ283" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR283" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="284" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A284" s="1">
+        <v>1</v>
+      </c>
+      <c r="B284" s="2">
+        <v>2</v>
+      </c>
+      <c r="C284" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D284" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E284" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F284" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G284" s="5">
+        <v>464</v>
+      </c>
+      <c r="H284" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I284" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J284" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K284" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L284" s="6">
+        <v>5310</v>
+      </c>
+      <c r="M284" s="7">
+        <v>907722.91</v>
+      </c>
+      <c r="N284" s="6">
+        <v>1</v>
+      </c>
+      <c r="O284" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P284" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q284" s="6">
+        <v>0</v>
+      </c>
+      <c r="R284" s="7">
+        <v>0</v>
+      </c>
+      <c r="S284" s="9">
+        <v>0</v>
+      </c>
+      <c r="T284" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U284" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V284" s="11">
+        <v>11</v>
+      </c>
+      <c r="W284" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X284" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y284" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z284" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA284" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB284" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC284" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD284" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE284" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF284" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG284" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH284" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI284" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ284" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK284" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL284" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM284" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN284" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO284" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP284" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ284" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR284" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="285" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A285" s="1">
+        <v>1</v>
+      </c>
+      <c r="B285" s="2">
+        <v>2</v>
+      </c>
+      <c r="C285" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E285" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F285" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G285" s="5">
+        <v>465</v>
+      </c>
+      <c r="H285" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I285" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J285" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K285" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L285" s="6">
+        <v>5311</v>
+      </c>
+      <c r="M285" s="7">
+        <v>907893.86</v>
+      </c>
+      <c r="N285" s="6">
+        <v>1</v>
+      </c>
+      <c r="O285" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P285" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q285" s="6">
+        <v>0</v>
+      </c>
+      <c r="R285" s="7">
+        <v>0</v>
+      </c>
+      <c r="S285" s="9">
+        <v>0</v>
+      </c>
+      <c r="T285" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U285" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V285" s="11">
+        <v>11</v>
+      </c>
+      <c r="W285" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X285" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y285" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z285" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA285" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB285" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC285" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD285" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE285" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF285" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG285" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH285" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI285" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ285" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK285" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL285" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM285" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN285" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO285" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP285" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ285" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR285" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="286" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A286" s="1">
+        <v>1</v>
+      </c>
+      <c r="B286" s="2">
+        <v>2</v>
+      </c>
+      <c r="C286" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D286" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E286" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F286" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G286" s="5">
+        <v>466</v>
+      </c>
+      <c r="H286" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I286" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J286" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K286" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L286" s="6">
+        <v>5312</v>
+      </c>
+      <c r="M286" s="7">
+        <v>908064.81</v>
+      </c>
+      <c r="N286" s="6">
+        <v>1</v>
+      </c>
+      <c r="O286" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P286" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q286" s="6">
+        <v>0</v>
+      </c>
+      <c r="R286" s="7">
+        <v>0</v>
+      </c>
+      <c r="S286" s="9">
+        <v>0</v>
+      </c>
+      <c r="T286" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U286" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V286" s="11">
+        <v>11</v>
+      </c>
+      <c r="W286" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X286" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y286" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z286" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA286" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB286" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC286" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD286" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE286" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF286" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG286" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH286" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI286" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ286" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK286" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL286" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM286" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN286" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO286" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP286" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ286" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR286" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="287" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A287" s="1">
+        <v>1</v>
+      </c>
+      <c r="B287" s="2">
+        <v>2</v>
+      </c>
+      <c r="C287" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E287" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F287" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G287" s="5">
+        <v>467</v>
+      </c>
+      <c r="H287" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I287" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J287" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K287" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L287" s="6">
+        <v>5313</v>
+      </c>
+      <c r="M287" s="7">
+        <v>908235.75</v>
+      </c>
+      <c r="N287" s="6">
+        <v>1</v>
+      </c>
+      <c r="O287" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P287" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q287" s="6">
+        <v>0</v>
+      </c>
+      <c r="R287" s="7">
+        <v>0</v>
+      </c>
+      <c r="S287" s="9">
+        <v>0</v>
+      </c>
+      <c r="T287" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U287" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V287" s="11">
+        <v>11</v>
+      </c>
+      <c r="W287" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X287" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y287" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z287" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA287" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB287" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC287" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD287" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE287" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF287" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG287" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH287" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI287" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ287" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK287" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL287" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM287" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN287" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO287" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP287" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ287" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR287" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="288" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A288" s="1">
+        <v>1</v>
+      </c>
+      <c r="B288" s="2">
+        <v>2</v>
+      </c>
+      <c r="C288" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E288" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F288" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G288" s="5">
+        <v>468</v>
+      </c>
+      <c r="H288" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I288" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J288" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K288" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L288" s="6">
+        <v>5314</v>
+      </c>
+      <c r="M288" s="7">
+        <v>908406.7</v>
+      </c>
+      <c r="N288" s="6">
+        <v>1</v>
+      </c>
+      <c r="O288" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P288" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q288" s="6">
+        <v>0</v>
+      </c>
+      <c r="R288" s="7">
+        <v>0</v>
+      </c>
+      <c r="S288" s="9">
+        <v>0</v>
+      </c>
+      <c r="T288" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U288" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V288" s="11">
+        <v>11</v>
+      </c>
+      <c r="W288" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X288" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y288" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z288" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA288" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB288" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC288" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD288" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE288" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF288" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG288" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH288" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI288" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ288" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK288" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL288" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM288" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN288" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO288" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP288" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ288" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR288" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="289" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A289" s="1">
+        <v>1</v>
+      </c>
+      <c r="B289" s="2">
+        <v>2</v>
+      </c>
+      <c r="C289" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D289" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E289" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F289" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G289" s="5">
+        <v>469</v>
+      </c>
+      <c r="H289" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I289" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J289" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K289" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L289" s="6">
+        <v>5315</v>
+      </c>
+      <c r="M289" s="7">
+        <v>908577.64</v>
+      </c>
+      <c r="N289" s="6">
+        <v>1</v>
+      </c>
+      <c r="O289" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P289" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q289" s="6">
+        <v>0</v>
+      </c>
+      <c r="R289" s="7">
+        <v>0</v>
+      </c>
+      <c r="S289" s="9">
+        <v>0</v>
+      </c>
+      <c r="T289" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U289" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V289" s="11">
+        <v>11</v>
+      </c>
+      <c r="W289" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X289" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y289" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z289" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA289" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB289" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC289" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD289" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE289" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF289" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG289" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH289" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI289" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ289" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK289" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL289" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM289" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN289" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO289" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP289" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ289" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR289" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="290" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A290" s="1">
+        <v>1</v>
+      </c>
+      <c r="B290" s="2">
+        <v>2</v>
+      </c>
+      <c r="C290" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D290" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E290" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F290" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G290" s="5">
+        <v>470</v>
+      </c>
+      <c r="H290" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I290" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J290" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K290" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L290" s="6">
+        <v>5316</v>
+      </c>
+      <c r="M290" s="7">
+        <v>908748.59</v>
+      </c>
+      <c r="N290" s="6">
+        <v>1</v>
+      </c>
+      <c r="O290" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P290" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q290" s="6">
+        <v>0</v>
+      </c>
+      <c r="R290" s="7">
+        <v>0</v>
+      </c>
+      <c r="S290" s="9">
+        <v>0</v>
+      </c>
+      <c r="T290" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U290" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V290" s="11">
+        <v>11</v>
+      </c>
+      <c r="W290" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X290" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y290" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z290" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA290" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB290" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC290" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD290" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE290" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF290" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG290" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH290" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI290" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ290" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK290" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL290" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM290" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN290" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO290" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP290" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ290" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR290" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="291" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A291" s="1">
+        <v>1</v>
+      </c>
+      <c r="B291" s="2">
+        <v>2</v>
+      </c>
+      <c r="C291" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D291" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E291" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F291" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G291" s="5">
+        <v>471</v>
+      </c>
+      <c r="H291" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I291" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J291" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K291" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L291" s="6">
+        <v>5317</v>
+      </c>
+      <c r="M291" s="7">
+        <v>908919.54</v>
+      </c>
+      <c r="N291" s="6">
+        <v>1</v>
+      </c>
+      <c r="O291" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P291" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q291" s="6">
+        <v>0</v>
+      </c>
+      <c r="R291" s="7">
+        <v>0</v>
+      </c>
+      <c r="S291" s="9">
+        <v>0</v>
+      </c>
+      <c r="T291" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U291" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V291" s="11">
+        <v>11</v>
+      </c>
+      <c r="W291" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X291" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y291" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z291" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA291" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB291" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC291" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD291" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE291" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF291" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG291" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH291" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI291" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ291" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK291" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL291" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM291" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN291" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO291" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP291" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ291" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR291" s="3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="292" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A292" s="1">
+        <v>1</v>
+      </c>
+      <c r="B292" s="2">
+        <v>2</v>
+      </c>
+      <c r="C292" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E292" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F292" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G292" s="5">
+        <v>472</v>
+      </c>
+      <c r="H292" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I292" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J292" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K292" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L292" s="6">
+        <v>5318</v>
+      </c>
+      <c r="M292" s="7">
+        <v>909090.48</v>
+      </c>
+      <c r="N292" s="6">
+        <v>1</v>
+      </c>
+      <c r="O292" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P292" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q292" s="6">
+        <v>0</v>
+      </c>
+      <c r="R292" s="7">
+        <v>0</v>
+      </c>
+      <c r="S292" s="9">
+        <v>0</v>
+      </c>
+      <c r="T292" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U292" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V292" s="11">
+        <v>11</v>
+      </c>
+      <c r="W292" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X292" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y292" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z292" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA292" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB292" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC292" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD292" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE292" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF292" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG292" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH292" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI292" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ292" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK292" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL292" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM292" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN292" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO292" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP292" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ292" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR292" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="293" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A293" s="1">
+        <v>1</v>
+      </c>
+      <c r="B293" s="2">
+        <v>2</v>
+      </c>
+      <c r="C293" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E293" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F293" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G293" s="5">
+        <v>473</v>
+      </c>
+      <c r="H293" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I293" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J293" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K293" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L293" s="6">
+        <v>5319</v>
+      </c>
+      <c r="M293" s="7">
+        <v>909261.43</v>
+      </c>
+      <c r="N293" s="6">
+        <v>1</v>
+      </c>
+      <c r="O293" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P293" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q293" s="6">
+        <v>0</v>
+      </c>
+      <c r="R293" s="7">
+        <v>0</v>
+      </c>
+      <c r="S293" s="9">
+        <v>0</v>
+      </c>
+      <c r="T293" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U293" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V293" s="11">
+        <v>11</v>
+      </c>
+      <c r="W293" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X293" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y293" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z293" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA293" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB293" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC293" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD293" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE293" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF293" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG293" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH293" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI293" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ293" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK293" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL293" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM293" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN293" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO293" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP293" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ293" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR293" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="294" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A294" s="1">
+        <v>1</v>
+      </c>
+      <c r="B294" s="2">
+        <v>2</v>
+      </c>
+      <c r="C294" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D294" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E294" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F294" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G294" s="5">
+        <v>474</v>
+      </c>
+      <c r="H294" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I294" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J294" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K294" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L294" s="6">
+        <v>5320</v>
+      </c>
+      <c r="M294" s="7">
+        <v>909432.37</v>
+      </c>
+      <c r="N294" s="6">
+        <v>1</v>
+      </c>
+      <c r="O294" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P294" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q294" s="6">
+        <v>0</v>
+      </c>
+      <c r="R294" s="7">
+        <v>0</v>
+      </c>
+      <c r="S294" s="9">
+        <v>0</v>
+      </c>
+      <c r="T294" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U294" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V294" s="11">
+        <v>11</v>
+      </c>
+      <c r="W294" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X294" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y294" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z294" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA294" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB294" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC294" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD294" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE294" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF294" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG294" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH294" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI294" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ294" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK294" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL294" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM294" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN294" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO294" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP294" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ294" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR294" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="295" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A295" s="1">
+        <v>1</v>
+      </c>
+      <c r="B295" s="2">
+        <v>2</v>
+      </c>
+      <c r="C295" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E295" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F295" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G295" s="5">
+        <v>475</v>
+      </c>
+      <c r="H295" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I295" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J295" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K295" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L295" s="6">
+        <v>5321</v>
+      </c>
+      <c r="M295" s="7">
+        <v>909603.32</v>
+      </c>
+      <c r="N295" s="6">
+        <v>1</v>
+      </c>
+      <c r="O295" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P295" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q295" s="6">
+        <v>0</v>
+      </c>
+      <c r="R295" s="7">
+        <v>0</v>
+      </c>
+      <c r="S295" s="9">
+        <v>0</v>
+      </c>
+      <c r="T295" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U295" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V295" s="11">
+        <v>11</v>
+      </c>
+      <c r="W295" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X295" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y295" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z295" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA295" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB295" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC295" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD295" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE295" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF295" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG295" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH295" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI295" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ295" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK295" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL295" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM295" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN295" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO295" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP295" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ295" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR295" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="296" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A296" s="1">
+        <v>1</v>
+      </c>
+      <c r="B296" s="2">
+        <v>2</v>
+      </c>
+      <c r="C296" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D296" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E296" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F296" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G296" s="5">
+        <v>476</v>
+      </c>
+      <c r="H296" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I296" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J296" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K296" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L296" s="6">
+        <v>5322</v>
+      </c>
+      <c r="M296" s="7">
+        <v>909774.27</v>
+      </c>
+      <c r="N296" s="6">
+        <v>1</v>
+      </c>
+      <c r="O296" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P296" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q296" s="6">
+        <v>0</v>
+      </c>
+      <c r="R296" s="7">
+        <v>0</v>
+      </c>
+      <c r="S296" s="9">
+        <v>0</v>
+      </c>
+      <c r="T296" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U296" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V296" s="11">
+        <v>11</v>
+      </c>
+      <c r="W296" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X296" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y296" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z296" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA296" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB296" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC296" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD296" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE296" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF296" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG296" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH296" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI296" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ296" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK296" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL296" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM296" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN296" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO296" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP296" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ296" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR296" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="297" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A297" s="1">
+        <v>1</v>
+      </c>
+      <c r="B297" s="2">
+        <v>2</v>
+      </c>
+      <c r="C297" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D297" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E297" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F297" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G297" s="5">
+        <v>477</v>
+      </c>
+      <c r="H297" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I297" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J297" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K297" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L297" s="6">
+        <v>5323</v>
+      </c>
+      <c r="M297" s="7">
+        <v>909945.21</v>
+      </c>
+      <c r="N297" s="6">
+        <v>1</v>
+      </c>
+      <c r="O297" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P297" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q297" s="6">
+        <v>0</v>
+      </c>
+      <c r="R297" s="7">
+        <v>0</v>
+      </c>
+      <c r="S297" s="9">
+        <v>0</v>
+      </c>
+      <c r="T297" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U297" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V297" s="11">
+        <v>11</v>
+      </c>
+      <c r="W297" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X297" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y297" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z297" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA297" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB297" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC297" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD297" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE297" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF297" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG297" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH297" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI297" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ297" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK297" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL297" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM297" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN297" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO297" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP297" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ297" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR297" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="298" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A298" s="1">
+        <v>1</v>
+      </c>
+      <c r="B298" s="2">
+        <v>2</v>
+      </c>
+      <c r="C298" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D298" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E298" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F298" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G298" s="5">
+        <v>478</v>
+      </c>
+      <c r="H298" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I298" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J298" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K298" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L298" s="6">
+        <v>5324</v>
+      </c>
+      <c r="M298" s="7">
+        <v>910116.16</v>
+      </c>
+      <c r="N298" s="6">
+        <v>1</v>
+      </c>
+      <c r="O298" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P298" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q298" s="6">
+        <v>0</v>
+      </c>
+      <c r="R298" s="7">
+        <v>0</v>
+      </c>
+      <c r="S298" s="9">
+        <v>0</v>
+      </c>
+      <c r="T298" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U298" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V298" s="11">
+        <v>11</v>
+      </c>
+      <c r="W298" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X298" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y298" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z298" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA298" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB298" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC298" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD298" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE298" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF298" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG298" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH298" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI298" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ298" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK298" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL298" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM298" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN298" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO298" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP298" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ298" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR298" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="299" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A299" s="1">
+        <v>1</v>
+      </c>
+      <c r="B299" s="2">
+        <v>2</v>
+      </c>
+      <c r="C299" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D299" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E299" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F299" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G299" s="5">
+        <v>479</v>
+      </c>
+      <c r="H299" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I299" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J299" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K299" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L299" s="6">
+        <v>5325</v>
+      </c>
+      <c r="M299" s="7">
+        <v>910287.1</v>
+      </c>
+      <c r="N299" s="6">
+        <v>1</v>
+      </c>
+      <c r="O299" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P299" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q299" s="6">
+        <v>0</v>
+      </c>
+      <c r="R299" s="7">
+        <v>0</v>
+      </c>
+      <c r="S299" s="9">
+        <v>0</v>
+      </c>
+      <c r="T299" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U299" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V299" s="11">
+        <v>11</v>
+      </c>
+      <c r="W299" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X299" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y299" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z299" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA299" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB299" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC299" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD299" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE299" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF299" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG299" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH299" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI299" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ299" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK299" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL299" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM299" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN299" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO299" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP299" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ299" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR299" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="300" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A300" s="1">
+        <v>1</v>
+      </c>
+      <c r="B300" s="2">
+        <v>2</v>
+      </c>
+      <c r="C300" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D300" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E300" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F300" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G300" s="5">
+        <v>480</v>
+      </c>
+      <c r="H300" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I300" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J300" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K300" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L300" s="6">
+        <v>5326</v>
+      </c>
+      <c r="M300" s="7">
+        <v>910458.05</v>
+      </c>
+      <c r="N300" s="6">
+        <v>1</v>
+      </c>
+      <c r="O300" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P300" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q300" s="6">
+        <v>0</v>
+      </c>
+      <c r="R300" s="7">
+        <v>0</v>
+      </c>
+      <c r="S300" s="9">
+        <v>0</v>
+      </c>
+      <c r="T300" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U300" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V300" s="11">
+        <v>11</v>
+      </c>
+      <c r="W300" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X300" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y300" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z300" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA300" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB300" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC300" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD300" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE300" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF300" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG300" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH300" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI300" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ300" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK300" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL300" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM300" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN300" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO300" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP300" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ300" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR300" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="301" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A301" s="1">
+        <v>1</v>
+      </c>
+      <c r="B301" s="2">
+        <v>2</v>
+      </c>
+      <c r="C301" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D301" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E301" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F301" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G301" s="5">
+        <v>481</v>
+      </c>
+      <c r="H301" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I301" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J301" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K301" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L301" s="6">
+        <v>5327</v>
+      </c>
+      <c r="M301" s="7">
+        <v>910628.99</v>
+      </c>
+      <c r="N301" s="6">
+        <v>1</v>
+      </c>
+      <c r="O301" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P301" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q301" s="6">
+        <v>0</v>
+      </c>
+      <c r="R301" s="7">
+        <v>0</v>
+      </c>
+      <c r="S301" s="9">
+        <v>0</v>
+      </c>
+      <c r="T301" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U301" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V301" s="11">
+        <v>11</v>
+      </c>
+      <c r="W301" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X301" s="12">
+        <v>0.43958330000000001</v>
+      </c>
+      <c r="Y301" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z301" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA301" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB301" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC301" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD301" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE301" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF301" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG301" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH301" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI301" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ301" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK301" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL301" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM301" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN301" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO301" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP301" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ301" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR301" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="302" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A302" s="1">
+        <v>1</v>
+      </c>
+      <c r="B302" s="2">
+        <v>2</v>
+      </c>
+      <c r="C302" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D302" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E302" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F302" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G302" s="5">
+        <v>482</v>
+      </c>
+      <c r="H302" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I302" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J302" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K302" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L302" s="6">
+        <v>5328</v>
+      </c>
+      <c r="M302" s="7">
+        <v>910799.94</v>
+      </c>
+      <c r="N302" s="6">
+        <v>1</v>
+      </c>
+      <c r="O302" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P302" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q302" s="6">
+        <v>0</v>
+      </c>
+      <c r="R302" s="7">
+        <v>0</v>
+      </c>
+      <c r="S302" s="9">
+        <v>0</v>
+      </c>
+      <c r="T302" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U302" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V302" s="11">
+        <v>11</v>
+      </c>
+      <c r="W302" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X302" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y302" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z302" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA302" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB302" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC302" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD302" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE302" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF302" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG302" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH302" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI302" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ302" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK302" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL302" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM302" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN302" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO302" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP302" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ302" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR302" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="303" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A303" s="1">
+        <v>1</v>
+      </c>
+      <c r="B303" s="2">
+        <v>2</v>
+      </c>
+      <c r="C303" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D303" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E303" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F303" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G303" s="5">
+        <v>483</v>
+      </c>
+      <c r="H303" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I303" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J303" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K303" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L303" s="6">
+        <v>5329</v>
+      </c>
+      <c r="M303" s="7">
+        <v>910970.89</v>
+      </c>
+      <c r="N303" s="6">
+        <v>1</v>
+      </c>
+      <c r="O303" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P303" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q303" s="6">
+        <v>0</v>
+      </c>
+      <c r="R303" s="7">
+        <v>0</v>
+      </c>
+      <c r="S303" s="9">
+        <v>0</v>
+      </c>
+      <c r="T303" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U303" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V303" s="11">
+        <v>11</v>
+      </c>
+      <c r="W303" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X303" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y303" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z303" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA303" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB303" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC303" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD303" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE303" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF303" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG303" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH303" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI303" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ303" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK303" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL303" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM303" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN303" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO303" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP303" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ303" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR303" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="304" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A304" s="1">
+        <v>1</v>
+      </c>
+      <c r="B304" s="2">
+        <v>2</v>
+      </c>
+      <c r="C304" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D304" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E304" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F304" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G304" s="5">
+        <v>484</v>
+      </c>
+      <c r="H304" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I304" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J304" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K304" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L304" s="6">
+        <v>5330</v>
+      </c>
+      <c r="M304" s="7">
+        <v>911141.83</v>
+      </c>
+      <c r="N304" s="6">
+        <v>1</v>
+      </c>
+      <c r="O304" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P304" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q304" s="6">
+        <v>0</v>
+      </c>
+      <c r="R304" s="7">
+        <v>0</v>
+      </c>
+      <c r="S304" s="9">
+        <v>0</v>
+      </c>
+      <c r="T304" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U304" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V304" s="11">
+        <v>11</v>
+      </c>
+      <c r="W304" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X304" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y304" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z304" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA304" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB304" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC304" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD304" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE304" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF304" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG304" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH304" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI304" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ304" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK304" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL304" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM304" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN304" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO304" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP304" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ304" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR304" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="305" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A305" s="1">
+        <v>1</v>
+      </c>
+      <c r="B305" s="2">
+        <v>2</v>
+      </c>
+      <c r="C305" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D305" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E305" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F305" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G305" s="5">
+        <v>485</v>
+      </c>
+      <c r="H305" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I305" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J305" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K305" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L305" s="6">
+        <v>5331</v>
+      </c>
+      <c r="M305" s="7">
+        <v>911312.78</v>
+      </c>
+      <c r="N305" s="6">
+        <v>1</v>
+      </c>
+      <c r="O305" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P305" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q305" s="6">
+        <v>0</v>
+      </c>
+      <c r="R305" s="7">
+        <v>0</v>
+      </c>
+      <c r="S305" s="9">
+        <v>0</v>
+      </c>
+      <c r="T305" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U305" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V305" s="11">
+        <v>11</v>
+      </c>
+      <c r="W305" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X305" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y305" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z305" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA305" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB305" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC305" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD305" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE305" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF305" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG305" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH305" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI305" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ305" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK305" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL305" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM305" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN305" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO305" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP305" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ305" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR305" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="306" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A306" s="1">
+        <v>1</v>
+      </c>
+      <c r="B306" s="2">
+        <v>2</v>
+      </c>
+      <c r="C306" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D306" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E306" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F306" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G306" s="5">
+        <v>486</v>
+      </c>
+      <c r="H306" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I306" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J306" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K306" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L306" s="6">
+        <v>5332</v>
+      </c>
+      <c r="M306" s="7">
+        <v>911483.72</v>
+      </c>
+      <c r="N306" s="6">
+        <v>1</v>
+      </c>
+      <c r="O306" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P306" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q306" s="6">
+        <v>0</v>
+      </c>
+      <c r="R306" s="7">
+        <v>0</v>
+      </c>
+      <c r="S306" s="9">
+        <v>0</v>
+      </c>
+      <c r="T306" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U306" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V306" s="11">
+        <v>11</v>
+      </c>
+      <c r="W306" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X306" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y306" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z306" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA306" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB306" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC306" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD306" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE306" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF306" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG306" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH306" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI306" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ306" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK306" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL306" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM306" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN306" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO306" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP306" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ306" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR306" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="307" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A307" s="1">
+        <v>1</v>
+      </c>
+      <c r="B307" s="2">
+        <v>2</v>
+      </c>
+      <c r="C307" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D307" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E307" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F307" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G307" s="5">
+        <v>487</v>
+      </c>
+      <c r="H307" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I307" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J307" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K307" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L307" s="6">
+        <v>5333</v>
+      </c>
+      <c r="M307" s="7">
+        <v>911654.67</v>
+      </c>
+      <c r="N307" s="6">
+        <v>1</v>
+      </c>
+      <c r="O307" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P307" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q307" s="6">
+        <v>0</v>
+      </c>
+      <c r="R307" s="7">
+        <v>0</v>
+      </c>
+      <c r="S307" s="9">
+        <v>0</v>
+      </c>
+      <c r="T307" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U307" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V307" s="11">
+        <v>11</v>
+      </c>
+      <c r="W307" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X307" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y307" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z307" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA307" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB307" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC307" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD307" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE307" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF307" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG307" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH307" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI307" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ307" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK307" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL307" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM307" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN307" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO307" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP307" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ307" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR307" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="308" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A308" s="1">
+        <v>1</v>
+      </c>
+      <c r="B308" s="2">
+        <v>2</v>
+      </c>
+      <c r="C308" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D308" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E308" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F308" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G308" s="5">
+        <v>488</v>
+      </c>
+      <c r="H308" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I308" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J308" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K308" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L308" s="6">
+        <v>5334</v>
+      </c>
+      <c r="M308" s="7">
+        <v>911825.62</v>
+      </c>
+      <c r="N308" s="6">
+        <v>1</v>
+      </c>
+      <c r="O308" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P308" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q308" s="6">
+        <v>0</v>
+      </c>
+      <c r="R308" s="7">
+        <v>0</v>
+      </c>
+      <c r="S308" s="9">
+        <v>0</v>
+      </c>
+      <c r="T308" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U308" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V308" s="11">
+        <v>11</v>
+      </c>
+      <c r="W308" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X308" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y308" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z308" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA308" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB308" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC308" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD308" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE308" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF308" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG308" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH308" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI308" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ308" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK308" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL308" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM308" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN308" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO308" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP308" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ308" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR308" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="309" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A309" s="1">
+        <v>1</v>
+      </c>
+      <c r="B309" s="2">
+        <v>2</v>
+      </c>
+      <c r="C309" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D309" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E309" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F309" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G309" s="5">
+        <v>489</v>
+      </c>
+      <c r="H309" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I309" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J309" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K309" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L309" s="6">
+        <v>5335</v>
+      </c>
+      <c r="M309" s="7">
+        <v>911996.56</v>
+      </c>
+      <c r="N309" s="6">
+        <v>1</v>
+      </c>
+      <c r="O309" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P309" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q309" s="6">
+        <v>0</v>
+      </c>
+      <c r="R309" s="7">
+        <v>0</v>
+      </c>
+      <c r="S309" s="9">
+        <v>0</v>
+      </c>
+      <c r="T309" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U309" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V309" s="11">
+        <v>11</v>
+      </c>
+      <c r="W309" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X309" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y309" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z309" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA309" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB309" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC309" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD309" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE309" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF309" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG309" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH309" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI309" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ309" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK309" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL309" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM309" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN309" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO309" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP309" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ309" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR309" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="310" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A310" s="1">
+        <v>1</v>
+      </c>
+      <c r="B310" s="2">
+        <v>2</v>
+      </c>
+      <c r="C310" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D310" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E310" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F310" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G310" s="5">
+        <v>490</v>
+      </c>
+      <c r="H310" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I310" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J310" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K310" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L310" s="6">
+        <v>5336</v>
+      </c>
+      <c r="M310" s="7">
+        <v>912167.51</v>
+      </c>
+      <c r="N310" s="6">
+        <v>1</v>
+      </c>
+      <c r="O310" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P310" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q310" s="6">
+        <v>0</v>
+      </c>
+      <c r="R310" s="7">
+        <v>0</v>
+      </c>
+      <c r="S310" s="9">
+        <v>0</v>
+      </c>
+      <c r="T310" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U310" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V310" s="11">
+        <v>11</v>
+      </c>
+      <c r="W310" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X310" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y310" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z310" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA310" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB310" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC310" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD310" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE310" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF310" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG310" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH310" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI310" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ310" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK310" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL310" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM310" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN310" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO310" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP310" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ310" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR310" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="311" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A311" s="1">
+        <v>1</v>
+      </c>
+      <c r="B311" s="2">
+        <v>2</v>
+      </c>
+      <c r="C311" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D311" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E311" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F311" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G311" s="5">
+        <v>491</v>
+      </c>
+      <c r="H311" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I311" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J311" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K311" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L311" s="6">
+        <v>5337</v>
+      </c>
+      <c r="M311" s="7">
+        <v>912338.45</v>
+      </c>
+      <c r="N311" s="6">
+        <v>1</v>
+      </c>
+      <c r="O311" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P311" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q311" s="6">
+        <v>0</v>
+      </c>
+      <c r="R311" s="7">
+        <v>0</v>
+      </c>
+      <c r="S311" s="9">
+        <v>0</v>
+      </c>
+      <c r="T311" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U311" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V311" s="11">
+        <v>11</v>
+      </c>
+      <c r="W311" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X311" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y311" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z311" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA311" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB311" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC311" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD311" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE311" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF311" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG311" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH311" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI311" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ311" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK311" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL311" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM311" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN311" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO311" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP311" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ311" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR311" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="312" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A312" s="1">
+        <v>1</v>
+      </c>
+      <c r="B312" s="2">
+        <v>2</v>
+      </c>
+      <c r="C312" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D312" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E312" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F312" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G312" s="5">
+        <v>492</v>
+      </c>
+      <c r="H312" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I312" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J312" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K312" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L312" s="6">
+        <v>5338</v>
+      </c>
+      <c r="M312" s="7">
+        <v>912509.4</v>
+      </c>
+      <c r="N312" s="6">
+        <v>1</v>
+      </c>
+      <c r="O312" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P312" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q312" s="6">
+        <v>0</v>
+      </c>
+      <c r="R312" s="7">
+        <v>0</v>
+      </c>
+      <c r="S312" s="9">
+        <v>0</v>
+      </c>
+      <c r="T312" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U312" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V312" s="11">
+        <v>11</v>
+      </c>
+      <c r="W312" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X312" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y312" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z312" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA312" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB312" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC312" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD312" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE312" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF312" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG312" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH312" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI312" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ312" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK312" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL312" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM312" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN312" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO312" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP312" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ312" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR312" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="313" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A313" s="1">
+        <v>1</v>
+      </c>
+      <c r="B313" s="2">
+        <v>2</v>
+      </c>
+      <c r="C313" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D313" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E313" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F313" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G313" s="5">
+        <v>493</v>
+      </c>
+      <c r="H313" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I313" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J313" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K313" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L313" s="6">
+        <v>5339</v>
+      </c>
+      <c r="M313" s="7">
+        <v>912680.35</v>
+      </c>
+      <c r="N313" s="6">
+        <v>1</v>
+      </c>
+      <c r="O313" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P313" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q313" s="6">
+        <v>0</v>
+      </c>
+      <c r="R313" s="7">
+        <v>0</v>
+      </c>
+      <c r="S313" s="9">
+        <v>0</v>
+      </c>
+      <c r="T313" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U313" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V313" s="11">
+        <v>11</v>
+      </c>
+      <c r="W313" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X313" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y313" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z313" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA313" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB313" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC313" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD313" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE313" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF313" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG313" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH313" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI313" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ313" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK313" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL313" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM313" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN313" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO313" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP313" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ313" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR313" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="314" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A314" s="1">
+        <v>1</v>
+      </c>
+      <c r="B314" s="2">
+        <v>2</v>
+      </c>
+      <c r="C314" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D314" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E314" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F314" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G314" s="5">
+        <v>494</v>
+      </c>
+      <c r="H314" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I314" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J314" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K314" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L314" s="6">
+        <v>5340</v>
+      </c>
+      <c r="M314" s="7">
+        <v>912851.29</v>
+      </c>
+      <c r="N314" s="6">
+        <v>1</v>
+      </c>
+      <c r="O314" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P314" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q314" s="6">
+        <v>0</v>
+      </c>
+      <c r="R314" s="7">
+        <v>0</v>
+      </c>
+      <c r="S314" s="9">
+        <v>0</v>
+      </c>
+      <c r="T314" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U314" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V314" s="11">
+        <v>11</v>
+      </c>
+      <c r="W314" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X314" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y314" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z314" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA314" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB314" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC314" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD314" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE314" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF314" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG314" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH314" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI314" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ314" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK314" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL314" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM314" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN314" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO314" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP314" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ314" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR314" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="315" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A315" s="1">
+        <v>1</v>
+      </c>
+      <c r="B315" s="2">
+        <v>2</v>
+      </c>
+      <c r="C315" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D315" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E315" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F315" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G315" s="5">
+        <v>495</v>
+      </c>
+      <c r="H315" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I315" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J315" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K315" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L315" s="6">
+        <v>5341</v>
+      </c>
+      <c r="M315" s="7">
+        <v>913022.24</v>
+      </c>
+      <c r="N315" s="6">
+        <v>1</v>
+      </c>
+      <c r="O315" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P315" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q315" s="6">
+        <v>0</v>
+      </c>
+      <c r="R315" s="7">
+        <v>0</v>
+      </c>
+      <c r="S315" s="9">
+        <v>0</v>
+      </c>
+      <c r="T315" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U315" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V315" s="11">
+        <v>11</v>
+      </c>
+      <c r="W315" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X315" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y315" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z315" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA315" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB315" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC315" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD315" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE315" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF315" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG315" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH315" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI315" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ315" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK315" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL315" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM315" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN315" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO315" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP315" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ315" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR315" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="316" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A316" s="1">
+        <v>1</v>
+      </c>
+      <c r="B316" s="2">
+        <v>2</v>
+      </c>
+      <c r="C316" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D316" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E316" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F316" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G316" s="5">
+        <v>496</v>
+      </c>
+      <c r="H316" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I316" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J316" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K316" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L316" s="6">
+        <v>5342</v>
+      </c>
+      <c r="M316" s="7">
+        <v>913193.18</v>
+      </c>
+      <c r="N316" s="6">
+        <v>1</v>
+      </c>
+      <c r="O316" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P316" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q316" s="6">
+        <v>0</v>
+      </c>
+      <c r="R316" s="7">
+        <v>0</v>
+      </c>
+      <c r="S316" s="9">
+        <v>0</v>
+      </c>
+      <c r="T316" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U316" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V316" s="11">
+        <v>11</v>
+      </c>
+      <c r="W316" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X316" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y316" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z316" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA316" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB316" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC316" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD316" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE316" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF316" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG316" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH316" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI316" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ316" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK316" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL316" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM316" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN316" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO316" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP316" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ316" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR316" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="317" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A317" s="1">
+        <v>1</v>
+      </c>
+      <c r="B317" s="2">
+        <v>2</v>
+      </c>
+      <c r="C317" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D317" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E317" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F317" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G317" s="5">
+        <v>497</v>
+      </c>
+      <c r="H317" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I317" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J317" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K317" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L317" s="6">
+        <v>5343</v>
+      </c>
+      <c r="M317" s="7">
+        <v>913364.13</v>
+      </c>
+      <c r="N317" s="6">
+        <v>1</v>
+      </c>
+      <c r="O317" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P317" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q317" s="6">
+        <v>0</v>
+      </c>
+      <c r="R317" s="7">
+        <v>0</v>
+      </c>
+      <c r="S317" s="9">
+        <v>0</v>
+      </c>
+      <c r="T317" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U317" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V317" s="11">
+        <v>11</v>
+      </c>
+      <c r="W317" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X317" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y317" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z317" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA317" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB317" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC317" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD317" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE317" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF317" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG317" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH317" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI317" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ317" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK317" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL317" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM317" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN317" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO317" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP317" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ317" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR317" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="318" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A318" s="1">
+        <v>1</v>
+      </c>
+      <c r="B318" s="2">
+        <v>2</v>
+      </c>
+      <c r="C318" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D318" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E318" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F318" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G318" s="5">
+        <v>498</v>
+      </c>
+      <c r="H318" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I318" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J318" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K318" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L318" s="6">
+        <v>5344</v>
+      </c>
+      <c r="M318" s="7">
+        <v>913535.08</v>
+      </c>
+      <c r="N318" s="6">
+        <v>1</v>
+      </c>
+      <c r="O318" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P318" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q318" s="6">
+        <v>0</v>
+      </c>
+      <c r="R318" s="7">
+        <v>0</v>
+      </c>
+      <c r="S318" s="9">
+        <v>0</v>
+      </c>
+      <c r="T318" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U318" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V318" s="11">
+        <v>11</v>
+      </c>
+      <c r="W318" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X318" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y318" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z318" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA318" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB318" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC318" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD318" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE318" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF318" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG318" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH318" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI318" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ318" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK318" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL318" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM318" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN318" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO318" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP318" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ318" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR318" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="319" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A319" s="1">
+        <v>1</v>
+      </c>
+      <c r="B319" s="2">
+        <v>2</v>
+      </c>
+      <c r="C319" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D319" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E319" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F319" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G319" s="5">
+        <v>499</v>
+      </c>
+      <c r="H319" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I319" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J319" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K319" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L319" s="6">
+        <v>5345</v>
+      </c>
+      <c r="M319" s="7">
+        <v>913706.02</v>
+      </c>
+      <c r="N319" s="6">
+        <v>1</v>
+      </c>
+      <c r="O319" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P319" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q319" s="6">
+        <v>0</v>
+      </c>
+      <c r="R319" s="7">
+        <v>0</v>
+      </c>
+      <c r="S319" s="9">
+        <v>0</v>
+      </c>
+      <c r="T319" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U319" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V319" s="11">
+        <v>11</v>
+      </c>
+      <c r="W319" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X319" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y319" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z319" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA319" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB319" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC319" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD319" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE319" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF319" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG319" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH319" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI319" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ319" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK319" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL319" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM319" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN319" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO319" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP319" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ319" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR319" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="320" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A320" s="1">
+        <v>1</v>
+      </c>
+      <c r="B320" s="2">
+        <v>2</v>
+      </c>
+      <c r="C320" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D320" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E320" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F320" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G320" s="5">
+        <v>500</v>
+      </c>
+      <c r="H320" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I320" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J320" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K320" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L320" s="6">
+        <v>5346</v>
+      </c>
+      <c r="M320" s="7">
+        <v>913876.97</v>
+      </c>
+      <c r="N320" s="6">
+        <v>1</v>
+      </c>
+      <c r="O320" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P320" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q320" s="6">
+        <v>0</v>
+      </c>
+      <c r="R320" s="7">
+        <v>0</v>
+      </c>
+      <c r="S320" s="9">
+        <v>0</v>
+      </c>
+      <c r="T320" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U320" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V320" s="11">
+        <v>11</v>
+      </c>
+      <c r="W320" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X320" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y320" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z320" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA320" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB320" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC320" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD320" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE320" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF320" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG320" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH320" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI320" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ320" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK320" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL320" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM320" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN320" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO320" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP320" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ320" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR320" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="321" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A321" s="1">
+        <v>1</v>
+      </c>
+      <c r="B321" s="2">
+        <v>2</v>
+      </c>
+      <c r="C321" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D321" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E321" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F321" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G321" s="5">
+        <v>501</v>
+      </c>
+      <c r="H321" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I321" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J321" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K321" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L321" s="6">
+        <v>5347</v>
+      </c>
+      <c r="M321" s="7">
+        <v>914047.91</v>
+      </c>
+      <c r="N321" s="6">
+        <v>1</v>
+      </c>
+      <c r="O321" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P321" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q321" s="6">
+        <v>0</v>
+      </c>
+      <c r="R321" s="7">
+        <v>0</v>
+      </c>
+      <c r="S321" s="9">
+        <v>0</v>
+      </c>
+      <c r="T321" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U321" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V321" s="11">
+        <v>11</v>
+      </c>
+      <c r="W321" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X321" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y321" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z321" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA321" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB321" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC321" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD321" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE321" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF321" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG321" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH321" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI321" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ321" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK321" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL321" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM321" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN321" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO321" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP321" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ321" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR321" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="322" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A322" s="1">
+        <v>1</v>
+      </c>
+      <c r="B322" s="2">
+        <v>2</v>
+      </c>
+      <c r="C322" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D322" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E322" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F322" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G322" s="5">
+        <v>502</v>
+      </c>
+      <c r="H322" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I322" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J322" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K322" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L322" s="6">
+        <v>5348</v>
+      </c>
+      <c r="M322" s="7">
+        <v>914218.86</v>
+      </c>
+      <c r="N322" s="6">
+        <v>1</v>
+      </c>
+      <c r="O322" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P322" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q322" s="6">
+        <v>0</v>
+      </c>
+      <c r="R322" s="7">
+        <v>0</v>
+      </c>
+      <c r="S322" s="9">
+        <v>0</v>
+      </c>
+      <c r="T322" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U322" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V322" s="11">
+        <v>11</v>
+      </c>
+      <c r="W322" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X322" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y322" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z322" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA322" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB322" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC322" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD322" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE322" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF322" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG322" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH322" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI322" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ322" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK322" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL322" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM322" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN322" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO322" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP322" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ322" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR322" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="323" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A323" s="1">
+        <v>1</v>
+      </c>
+      <c r="B323" s="2">
+        <v>2</v>
+      </c>
+      <c r="C323" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D323" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E323" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F323" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G323" s="5">
+        <v>503</v>
+      </c>
+      <c r="H323" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I323" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J323" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K323" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L323" s="6">
+        <v>5349</v>
+      </c>
+      <c r="M323" s="7">
+        <v>914389.81</v>
+      </c>
+      <c r="N323" s="6">
+        <v>1</v>
+      </c>
+      <c r="O323" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P323" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q323" s="6">
+        <v>0</v>
+      </c>
+      <c r="R323" s="7">
+        <v>0</v>
+      </c>
+      <c r="S323" s="9">
+        <v>0</v>
+      </c>
+      <c r="T323" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U323" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V323" s="11">
+        <v>11</v>
+      </c>
+      <c r="W323" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X323" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y323" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z323" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA323" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB323" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC323" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD323" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE323" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF323" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG323" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH323" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI323" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ323" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK323" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL323" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM323" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN323" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO323" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP323" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ323" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR323" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="324" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A324" s="1">
+        <v>1</v>
+      </c>
+      <c r="B324" s="2">
+        <v>2</v>
+      </c>
+      <c r="C324" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D324" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E324" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F324" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G324" s="5">
+        <v>504</v>
+      </c>
+      <c r="H324" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I324" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J324" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K324" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L324" s="6">
+        <v>5350</v>
+      </c>
+      <c r="M324" s="7">
+        <v>914560.75</v>
+      </c>
+      <c r="N324" s="6">
+        <v>1</v>
+      </c>
+      <c r="O324" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P324" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q324" s="6">
+        <v>0</v>
+      </c>
+      <c r="R324" s="7">
+        <v>0</v>
+      </c>
+      <c r="S324" s="9">
+        <v>0</v>
+      </c>
+      <c r="T324" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U324" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V324" s="11">
+        <v>11</v>
+      </c>
+      <c r="W324" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X324" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y324" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z324" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA324" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB324" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC324" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD324" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE324" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF324" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG324" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH324" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI324" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ324" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK324" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL324" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM324" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN324" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO324" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP324" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ324" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR324" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="325" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A325" s="1">
+        <v>1</v>
+      </c>
+      <c r="B325" s="2">
+        <v>2</v>
+      </c>
+      <c r="C325" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D325" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E325" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F325" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G325" s="5">
+        <v>505</v>
+      </c>
+      <c r="H325" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I325" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J325" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K325" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L325" s="6">
+        <v>5351</v>
+      </c>
+      <c r="M325" s="7">
+        <v>914731.7</v>
+      </c>
+      <c r="N325" s="6">
+        <v>1</v>
+      </c>
+      <c r="O325" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P325" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q325" s="6">
+        <v>0</v>
+      </c>
+      <c r="R325" s="7">
+        <v>0</v>
+      </c>
+      <c r="S325" s="9">
+        <v>0</v>
+      </c>
+      <c r="T325" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U325" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V325" s="11">
+        <v>11</v>
+      </c>
+      <c r="W325" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X325" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y325" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z325" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA325" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB325" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC325" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD325" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE325" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF325" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG325" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH325" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI325" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ325" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK325" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL325" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM325" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN325" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO325" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP325" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ325" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR325" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="326" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A326" s="1">
+        <v>1</v>
+      </c>
+      <c r="B326" s="2">
+        <v>2</v>
+      </c>
+      <c r="C326" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D326" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E326" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F326" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G326" s="5">
+        <v>506</v>
+      </c>
+      <c r="H326" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I326" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J326" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K326" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L326" s="6">
+        <v>5352</v>
+      </c>
+      <c r="M326" s="7">
+        <v>914902.64</v>
+      </c>
+      <c r="N326" s="6">
+        <v>1</v>
+      </c>
+      <c r="O326" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P326" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q326" s="6">
+        <v>0</v>
+      </c>
+      <c r="R326" s="7">
+        <v>0</v>
+      </c>
+      <c r="S326" s="9">
+        <v>0</v>
+      </c>
+      <c r="T326" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U326" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V326" s="11">
+        <v>11</v>
+      </c>
+      <c r="W326" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X326" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y326" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z326" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA326" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB326" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC326" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD326" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE326" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF326" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG326" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH326" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI326" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ326" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK326" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL326" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM326" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN326" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO326" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP326" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ326" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR326" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="327" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A327" s="1">
+        <v>1</v>
+      </c>
+      <c r="B327" s="2">
+        <v>2</v>
+      </c>
+      <c r="C327" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D327" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E327" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F327" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G327" s="5">
+        <v>507</v>
+      </c>
+      <c r="H327" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I327" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J327" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K327" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L327" s="6">
+        <v>5353</v>
+      </c>
+      <c r="M327" s="7">
+        <v>915073.59</v>
+      </c>
+      <c r="N327" s="6">
+        <v>1</v>
+      </c>
+      <c r="O327" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P327" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q327" s="6">
+        <v>0</v>
+      </c>
+      <c r="R327" s="7">
+        <v>0</v>
+      </c>
+      <c r="S327" s="9">
+        <v>0</v>
+      </c>
+      <c r="T327" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U327" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V327" s="11">
+        <v>11</v>
+      </c>
+      <c r="W327" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X327" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y327" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z327" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA327" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB327" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC327" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD327" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE327" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF327" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG327" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH327" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI327" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ327" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK327" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL327" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM327" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN327" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO327" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP327" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ327" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR327" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="328" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A328" s="1">
+        <v>1</v>
+      </c>
+      <c r="B328" s="2">
+        <v>2</v>
+      </c>
+      <c r="C328" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D328" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E328" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F328" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G328" s="5">
+        <v>508</v>
+      </c>
+      <c r="H328" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I328" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J328" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K328" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L328" s="6">
+        <v>5354</v>
+      </c>
+      <c r="M328" s="7">
+        <v>915244.54</v>
+      </c>
+      <c r="N328" s="6">
+        <v>1</v>
+      </c>
+      <c r="O328" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P328" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q328" s="6">
+        <v>0</v>
+      </c>
+      <c r="R328" s="7">
+        <v>0</v>
+      </c>
+      <c r="S328" s="9">
+        <v>0</v>
+      </c>
+      <c r="T328" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U328" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V328" s="11">
+        <v>11</v>
+      </c>
+      <c r="W328" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X328" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y328" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z328" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA328" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB328" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC328" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD328" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE328" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF328" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG328" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH328" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI328" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ328" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK328" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL328" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM328" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN328" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO328" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP328" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ328" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR328" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="329" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A329" s="1">
+        <v>1</v>
+      </c>
+      <c r="B329" s="2">
+        <v>2</v>
+      </c>
+      <c r="C329" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D329" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E329" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F329" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G329" s="5">
+        <v>509</v>
+      </c>
+      <c r="H329" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I329" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J329" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K329" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L329" s="6">
+        <v>5355</v>
+      </c>
+      <c r="M329" s="7">
+        <v>915415.48</v>
+      </c>
+      <c r="N329" s="6">
+        <v>1</v>
+      </c>
+      <c r="O329" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P329" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q329" s="6">
+        <v>0</v>
+      </c>
+      <c r="R329" s="7">
+        <v>0</v>
+      </c>
+      <c r="S329" s="9">
+        <v>0</v>
+      </c>
+      <c r="T329" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U329" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V329" s="11">
+        <v>11</v>
+      </c>
+      <c r="W329" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X329" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y329" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z329" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA329" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB329" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC329" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD329" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE329" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF329" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG329" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH329" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI329" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ329" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK329" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL329" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM329" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN329" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO329" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP329" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ329" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR329" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="330" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A330" s="1">
+        <v>1</v>
+      </c>
+      <c r="B330" s="2">
+        <v>2</v>
+      </c>
+      <c r="C330" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D330" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E330" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F330" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G330" s="5">
+        <v>510</v>
+      </c>
+      <c r="H330" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I330" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J330" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K330" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L330" s="6">
+        <v>5356</v>
+      </c>
+      <c r="M330" s="7">
+        <v>915586.43</v>
+      </c>
+      <c r="N330" s="6">
+        <v>1</v>
+      </c>
+      <c r="O330" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P330" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q330" s="6">
+        <v>0</v>
+      </c>
+      <c r="R330" s="7">
+        <v>0</v>
+      </c>
+      <c r="S330" s="9">
+        <v>0</v>
+      </c>
+      <c r="T330" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U330" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V330" s="11">
+        <v>11</v>
+      </c>
+      <c r="W330" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X330" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y330" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z330" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA330" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB330" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC330" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD330" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE330" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF330" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG330" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH330" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI330" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ330" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK330" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL330" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM330" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN330" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO330" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP330" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ330" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR330" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="331" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A331" s="1">
+        <v>1</v>
+      </c>
+      <c r="B331" s="2">
+        <v>2</v>
+      </c>
+      <c r="C331" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D331" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E331" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F331" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G331" s="5">
+        <v>511</v>
+      </c>
+      <c r="H331" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I331" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J331" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K331" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L331" s="6">
+        <v>5357</v>
+      </c>
+      <c r="M331" s="7">
+        <v>915757.37</v>
+      </c>
+      <c r="N331" s="6">
+        <v>1</v>
+      </c>
+      <c r="O331" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P331" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q331" s="6">
+        <v>0</v>
+      </c>
+      <c r="R331" s="7">
+        <v>0</v>
+      </c>
+      <c r="S331" s="9">
+        <v>0</v>
+      </c>
+      <c r="T331" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U331" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V331" s="11">
+        <v>11</v>
+      </c>
+      <c r="W331" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X331" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y331" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z331" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA331" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB331" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC331" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD331" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE331" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF331" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG331" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH331" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI331" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ331" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK331" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL331" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM331" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN331" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO331" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP331" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ331" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR331" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="332" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A332" s="1">
+        <v>1</v>
+      </c>
+      <c r="B332" s="2">
+        <v>2</v>
+      </c>
+      <c r="C332" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D332" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E332" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F332" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G332" s="5">
+        <v>512</v>
+      </c>
+      <c r="H332" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I332" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J332" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K332" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L332" s="6">
+        <v>5358</v>
+      </c>
+      <c r="M332" s="7">
+        <v>915928.32</v>
+      </c>
+      <c r="N332" s="6">
+        <v>1</v>
+      </c>
+      <c r="O332" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P332" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q332" s="6">
+        <v>0</v>
+      </c>
+      <c r="R332" s="7">
+        <v>0</v>
+      </c>
+      <c r="S332" s="9">
+        <v>0</v>
+      </c>
+      <c r="T332" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U332" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V332" s="11">
+        <v>11</v>
+      </c>
+      <c r="W332" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X332" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y332" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z332" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA332" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB332" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC332" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD332" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE332" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF332" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG332" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH332" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI332" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ332" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK332" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL332" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM332" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN332" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO332" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP332" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ332" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR332" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="333" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A333" s="1">
+        <v>1</v>
+      </c>
+      <c r="B333" s="2">
+        <v>2</v>
+      </c>
+      <c r="C333" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D333" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E333" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F333" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G333" s="5">
+        <v>513</v>
+      </c>
+      <c r="H333" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I333" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J333" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K333" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L333" s="6">
+        <v>5359</v>
+      </c>
+      <c r="M333" s="7">
+        <v>916099.26</v>
+      </c>
+      <c r="N333" s="6">
+        <v>1</v>
+      </c>
+      <c r="O333" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P333" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q333" s="6">
+        <v>0</v>
+      </c>
+      <c r="R333" s="7">
+        <v>0</v>
+      </c>
+      <c r="S333" s="9">
+        <v>0</v>
+      </c>
+      <c r="T333" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U333" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V333" s="11">
+        <v>11</v>
+      </c>
+      <c r="W333" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X333" s="12">
+        <v>0.4402778</v>
+      </c>
+      <c r="Y333" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z333" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA333" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB333" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC333" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD333" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE333" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF333" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG333" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH333" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI333" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ333" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK333" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL333" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM333" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN333" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO333" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP333" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ333" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR333" s="3" t="s">
+        <v>386</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A901D02-914D-4536-9CF5-80DB5471E4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E53B08C-EA07-4116-A423-9FC3CE1D27A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="696" yWindow="708" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6020" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6866" uniqueCount="434">
   <si>
     <t>Sel</t>
   </si>
@@ -1182,6 +1182,147 @@
   <si>
     <t>1858700158892</t>
   </si>
+  <si>
+    <t>1858700158893</t>
+  </si>
+  <si>
+    <t>1858700158894</t>
+  </si>
+  <si>
+    <t>1858700158895</t>
+  </si>
+  <si>
+    <t>1858700158896</t>
+  </si>
+  <si>
+    <t>1858700158897</t>
+  </si>
+  <si>
+    <t>1858700158898</t>
+  </si>
+  <si>
+    <t>1858700158899</t>
+  </si>
+  <si>
+    <t>1858700158900</t>
+  </si>
+  <si>
+    <t>1858700158901</t>
+  </si>
+  <si>
+    <t>1858700158902</t>
+  </si>
+  <si>
+    <t>1858700158903</t>
+  </si>
+  <si>
+    <t>1858700158904</t>
+  </si>
+  <si>
+    <t>1858700158905</t>
+  </si>
+  <si>
+    <t>1858700158906</t>
+  </si>
+  <si>
+    <t>1858700158907</t>
+  </si>
+  <si>
+    <t>1858700158908</t>
+  </si>
+  <si>
+    <t>1858700158909</t>
+  </si>
+  <si>
+    <t>1858700158910</t>
+  </si>
+  <si>
+    <t>1858700158911</t>
+  </si>
+  <si>
+    <t>1858700158912</t>
+  </si>
+  <si>
+    <t>1858700158913</t>
+  </si>
+  <si>
+    <t>1858700158914</t>
+  </si>
+  <si>
+    <t>1858700158915</t>
+  </si>
+  <si>
+    <t>1858700158916</t>
+  </si>
+  <si>
+    <t>1858700158917</t>
+  </si>
+  <si>
+    <t>1858700158918</t>
+  </si>
+  <si>
+    <t>1858700158919</t>
+  </si>
+  <si>
+    <t>1858700158920</t>
+  </si>
+  <si>
+    <t>1858700158921</t>
+  </si>
+  <si>
+    <t>1858700158922</t>
+  </si>
+  <si>
+    <t>1858700158923</t>
+  </si>
+  <si>
+    <t>1858700158924</t>
+  </si>
+  <si>
+    <t>1858700158925</t>
+  </si>
+  <si>
+    <t>1858700158926</t>
+  </si>
+  <si>
+    <t>1858700158927</t>
+  </si>
+  <si>
+    <t>1858700158928</t>
+  </si>
+  <si>
+    <t>1858700158929</t>
+  </si>
+  <si>
+    <t>1858700158930</t>
+  </si>
+  <si>
+    <t>1858700158931</t>
+  </si>
+  <si>
+    <t>1858700158932</t>
+  </si>
+  <si>
+    <t>1858700158933</t>
+  </si>
+  <si>
+    <t>1858700158934</t>
+  </si>
+  <si>
+    <t>1858700158935</t>
+  </si>
+  <si>
+    <t>1858700158936</t>
+  </si>
+  <si>
+    <t>1858700158937</t>
+  </si>
+  <si>
+    <t>1858700158938</t>
+  </si>
+  <si>
+    <t>1858700158939</t>
+  </si>
 </sst>
 </file>
 
@@ -1756,7 +1897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR333"/>
+  <dimension ref="A1:AR380"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -46379,6 +46520,6304 @@
       </c>
       <c r="AR333" s="3" t="s">
         <v>386</v>
+      </c>
+    </row>
+    <row r="334" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A334" s="1">
+        <v>1</v>
+      </c>
+      <c r="B334" s="2">
+        <v>2</v>
+      </c>
+      <c r="C334" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D334" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E334" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F334" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G334" s="5">
+        <v>514</v>
+      </c>
+      <c r="H334" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I334" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J334" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K334" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L334" s="6">
+        <v>5360</v>
+      </c>
+      <c r="M334" s="7">
+        <v>916270.21</v>
+      </c>
+      <c r="N334" s="6">
+        <v>1</v>
+      </c>
+      <c r="O334" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P334" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q334" s="6">
+        <v>0</v>
+      </c>
+      <c r="R334" s="7">
+        <v>0</v>
+      </c>
+      <c r="S334" s="9">
+        <v>0</v>
+      </c>
+      <c r="T334" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U334" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V334" s="11">
+        <v>11</v>
+      </c>
+      <c r="W334" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X334" s="12">
+        <v>0.4479167</v>
+      </c>
+      <c r="Y334" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z334" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA334" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB334" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC334" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD334" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE334" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF334" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG334" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH334" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI334" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ334" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK334" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL334" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM334" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN334" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO334" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP334" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ334" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR334" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="335" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A335" s="1">
+        <v>1</v>
+      </c>
+      <c r="B335" s="2">
+        <v>2</v>
+      </c>
+      <c r="C335" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D335" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E335" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F335" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G335" s="5">
+        <v>515</v>
+      </c>
+      <c r="H335" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I335" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J335" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K335" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L335" s="6">
+        <v>5361</v>
+      </c>
+      <c r="M335" s="7">
+        <v>916441.16</v>
+      </c>
+      <c r="N335" s="6">
+        <v>1</v>
+      </c>
+      <c r="O335" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P335" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q335" s="6">
+        <v>0</v>
+      </c>
+      <c r="R335" s="7">
+        <v>0</v>
+      </c>
+      <c r="S335" s="9">
+        <v>0</v>
+      </c>
+      <c r="T335" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U335" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V335" s="11">
+        <v>11</v>
+      </c>
+      <c r="W335" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X335" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y335" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z335" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA335" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB335" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC335" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD335" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE335" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF335" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG335" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH335" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI335" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ335" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK335" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL335" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM335" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN335" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO335" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP335" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ335" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR335" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="336" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A336" s="1">
+        <v>1</v>
+      </c>
+      <c r="B336" s="2">
+        <v>2</v>
+      </c>
+      <c r="C336" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D336" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E336" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F336" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G336" s="5">
+        <v>516</v>
+      </c>
+      <c r="H336" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I336" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J336" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K336" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L336" s="6">
+        <v>5362</v>
+      </c>
+      <c r="M336" s="7">
+        <v>916612.1</v>
+      </c>
+      <c r="N336" s="6">
+        <v>1</v>
+      </c>
+      <c r="O336" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P336" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q336" s="6">
+        <v>0</v>
+      </c>
+      <c r="R336" s="7">
+        <v>0</v>
+      </c>
+      <c r="S336" s="9">
+        <v>0</v>
+      </c>
+      <c r="T336" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U336" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V336" s="11">
+        <v>11</v>
+      </c>
+      <c r="W336" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X336" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y336" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z336" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA336" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB336" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC336" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD336" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE336" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF336" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG336" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH336" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI336" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ336" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK336" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL336" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM336" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN336" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO336" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP336" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ336" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR336" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="337" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A337" s="1">
+        <v>1</v>
+      </c>
+      <c r="B337" s="2">
+        <v>2</v>
+      </c>
+      <c r="C337" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D337" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E337" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F337" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G337" s="5">
+        <v>517</v>
+      </c>
+      <c r="H337" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I337" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J337" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K337" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L337" s="6">
+        <v>5363</v>
+      </c>
+      <c r="M337" s="7">
+        <v>916783.05</v>
+      </c>
+      <c r="N337" s="6">
+        <v>1</v>
+      </c>
+      <c r="O337" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P337" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q337" s="6">
+        <v>0</v>
+      </c>
+      <c r="R337" s="7">
+        <v>0</v>
+      </c>
+      <c r="S337" s="9">
+        <v>0</v>
+      </c>
+      <c r="T337" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U337" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V337" s="11">
+        <v>11</v>
+      </c>
+      <c r="W337" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X337" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y337" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z337" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA337" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB337" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC337" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD337" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE337" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF337" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG337" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH337" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI337" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ337" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK337" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL337" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM337" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN337" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO337" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP337" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ337" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR337" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="338" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A338" s="1">
+        <v>1</v>
+      </c>
+      <c r="B338" s="2">
+        <v>2</v>
+      </c>
+      <c r="C338" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D338" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E338" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F338" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G338" s="5">
+        <v>518</v>
+      </c>
+      <c r="H338" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I338" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J338" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K338" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L338" s="6">
+        <v>5364</v>
+      </c>
+      <c r="M338" s="7">
+        <v>916953.99</v>
+      </c>
+      <c r="N338" s="6">
+        <v>1</v>
+      </c>
+      <c r="O338" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P338" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q338" s="6">
+        <v>0</v>
+      </c>
+      <c r="R338" s="7">
+        <v>0</v>
+      </c>
+      <c r="S338" s="9">
+        <v>0</v>
+      </c>
+      <c r="T338" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U338" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V338" s="11">
+        <v>11</v>
+      </c>
+      <c r="W338" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X338" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y338" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z338" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA338" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB338" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC338" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD338" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE338" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF338" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG338" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH338" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI338" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ338" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK338" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL338" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM338" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN338" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO338" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP338" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ338" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR338" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="339" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A339" s="1">
+        <v>1</v>
+      </c>
+      <c r="B339" s="2">
+        <v>2</v>
+      </c>
+      <c r="C339" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D339" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E339" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F339" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G339" s="5">
+        <v>519</v>
+      </c>
+      <c r="H339" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I339" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J339" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K339" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L339" s="6">
+        <v>5365</v>
+      </c>
+      <c r="M339" s="7">
+        <v>917124.94</v>
+      </c>
+      <c r="N339" s="6">
+        <v>1</v>
+      </c>
+      <c r="O339" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P339" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q339" s="6">
+        <v>0</v>
+      </c>
+      <c r="R339" s="7">
+        <v>0</v>
+      </c>
+      <c r="S339" s="9">
+        <v>0</v>
+      </c>
+      <c r="T339" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U339" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V339" s="11">
+        <v>11</v>
+      </c>
+      <c r="W339" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X339" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y339" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z339" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA339" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB339" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC339" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD339" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE339" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF339" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG339" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH339" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI339" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ339" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK339" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL339" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM339" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN339" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO339" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP339" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ339" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR339" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="340" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A340" s="1">
+        <v>1</v>
+      </c>
+      <c r="B340" s="2">
+        <v>2</v>
+      </c>
+      <c r="C340" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D340" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E340" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F340" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G340" s="5">
+        <v>520</v>
+      </c>
+      <c r="H340" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I340" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J340" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K340" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L340" s="6">
+        <v>5366</v>
+      </c>
+      <c r="M340" s="7">
+        <v>917295.89</v>
+      </c>
+      <c r="N340" s="6">
+        <v>1</v>
+      </c>
+      <c r="O340" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P340" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q340" s="6">
+        <v>0</v>
+      </c>
+      <c r="R340" s="7">
+        <v>0</v>
+      </c>
+      <c r="S340" s="9">
+        <v>0</v>
+      </c>
+      <c r="T340" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U340" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V340" s="11">
+        <v>11</v>
+      </c>
+      <c r="W340" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X340" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y340" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z340" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA340" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB340" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC340" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD340" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE340" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF340" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG340" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH340" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI340" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ340" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK340" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL340" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM340" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN340" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO340" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP340" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ340" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR340" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="341" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A341" s="1">
+        <v>1</v>
+      </c>
+      <c r="B341" s="2">
+        <v>2</v>
+      </c>
+      <c r="C341" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D341" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E341" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F341" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G341" s="5">
+        <v>521</v>
+      </c>
+      <c r="H341" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I341" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J341" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K341" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L341" s="6">
+        <v>5367</v>
+      </c>
+      <c r="M341" s="7">
+        <v>917466.83</v>
+      </c>
+      <c r="N341" s="6">
+        <v>1</v>
+      </c>
+      <c r="O341" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P341" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q341" s="6">
+        <v>0</v>
+      </c>
+      <c r="R341" s="7">
+        <v>0</v>
+      </c>
+      <c r="S341" s="9">
+        <v>0</v>
+      </c>
+      <c r="T341" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U341" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V341" s="11">
+        <v>11</v>
+      </c>
+      <c r="W341" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X341" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y341" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z341" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA341" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB341" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC341" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD341" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE341" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF341" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG341" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH341" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI341" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ341" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK341" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL341" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM341" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN341" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO341" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP341" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ341" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR341" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="342" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A342" s="1">
+        <v>1</v>
+      </c>
+      <c r="B342" s="2">
+        <v>2</v>
+      </c>
+      <c r="C342" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D342" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E342" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F342" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G342" s="5">
+        <v>522</v>
+      </c>
+      <c r="H342" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I342" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J342" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K342" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L342" s="6">
+        <v>5368</v>
+      </c>
+      <c r="M342" s="7">
+        <v>917637.78</v>
+      </c>
+      <c r="N342" s="6">
+        <v>1</v>
+      </c>
+      <c r="O342" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P342" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q342" s="6">
+        <v>0</v>
+      </c>
+      <c r="R342" s="7">
+        <v>0</v>
+      </c>
+      <c r="S342" s="9">
+        <v>0</v>
+      </c>
+      <c r="T342" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U342" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V342" s="11">
+        <v>11</v>
+      </c>
+      <c r="W342" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X342" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y342" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z342" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA342" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB342" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC342" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD342" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE342" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF342" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG342" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH342" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI342" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ342" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK342" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL342" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM342" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN342" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO342" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP342" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ342" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR342" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="343" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A343" s="1">
+        <v>1</v>
+      </c>
+      <c r="B343" s="2">
+        <v>2</v>
+      </c>
+      <c r="C343" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D343" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E343" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F343" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G343" s="5">
+        <v>523</v>
+      </c>
+      <c r="H343" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I343" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J343" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K343" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L343" s="6">
+        <v>5369</v>
+      </c>
+      <c r="M343" s="7">
+        <v>917808.72</v>
+      </c>
+      <c r="N343" s="6">
+        <v>1</v>
+      </c>
+      <c r="O343" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P343" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q343" s="6">
+        <v>0</v>
+      </c>
+      <c r="R343" s="7">
+        <v>0</v>
+      </c>
+      <c r="S343" s="9">
+        <v>0</v>
+      </c>
+      <c r="T343" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U343" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V343" s="11">
+        <v>11</v>
+      </c>
+      <c r="W343" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X343" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y343" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z343" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA343" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB343" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC343" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD343" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE343" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF343" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG343" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH343" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI343" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ343" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK343" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL343" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM343" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN343" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO343" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP343" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ343" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR343" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="344" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A344" s="1">
+        <v>1</v>
+      </c>
+      <c r="B344" s="2">
+        <v>2</v>
+      </c>
+      <c r="C344" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D344" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E344" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F344" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G344" s="5">
+        <v>524</v>
+      </c>
+      <c r="H344" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I344" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J344" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K344" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L344" s="6">
+        <v>5370</v>
+      </c>
+      <c r="M344" s="7">
+        <v>917979.67</v>
+      </c>
+      <c r="N344" s="6">
+        <v>1</v>
+      </c>
+      <c r="O344" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P344" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q344" s="6">
+        <v>0</v>
+      </c>
+      <c r="R344" s="7">
+        <v>0</v>
+      </c>
+      <c r="S344" s="9">
+        <v>0</v>
+      </c>
+      <c r="T344" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U344" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V344" s="11">
+        <v>11</v>
+      </c>
+      <c r="W344" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X344" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y344" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z344" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA344" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB344" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC344" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD344" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE344" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF344" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG344" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH344" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI344" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ344" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK344" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL344" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM344" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN344" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO344" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP344" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ344" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR344" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="345" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A345" s="1">
+        <v>1</v>
+      </c>
+      <c r="B345" s="2">
+        <v>2</v>
+      </c>
+      <c r="C345" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D345" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E345" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F345" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G345" s="5">
+        <v>525</v>
+      </c>
+      <c r="H345" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I345" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J345" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K345" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L345" s="6">
+        <v>5371</v>
+      </c>
+      <c r="M345" s="7">
+        <v>918150.62</v>
+      </c>
+      <c r="N345" s="6">
+        <v>1</v>
+      </c>
+      <c r="O345" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P345" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q345" s="6">
+        <v>0</v>
+      </c>
+      <c r="R345" s="7">
+        <v>0</v>
+      </c>
+      <c r="S345" s="9">
+        <v>0</v>
+      </c>
+      <c r="T345" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U345" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V345" s="11">
+        <v>11</v>
+      </c>
+      <c r="W345" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X345" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y345" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z345" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA345" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB345" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC345" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD345" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE345" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF345" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG345" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH345" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI345" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ345" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK345" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL345" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM345" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN345" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO345" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP345" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ345" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR345" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="346" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A346" s="1">
+        <v>1</v>
+      </c>
+      <c r="B346" s="2">
+        <v>2</v>
+      </c>
+      <c r="C346" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D346" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E346" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F346" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G346" s="5">
+        <v>526</v>
+      </c>
+      <c r="H346" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I346" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J346" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K346" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L346" s="6">
+        <v>5372</v>
+      </c>
+      <c r="M346" s="7">
+        <v>918321.56</v>
+      </c>
+      <c r="N346" s="6">
+        <v>1</v>
+      </c>
+      <c r="O346" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P346" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q346" s="6">
+        <v>0</v>
+      </c>
+      <c r="R346" s="7">
+        <v>0</v>
+      </c>
+      <c r="S346" s="9">
+        <v>0</v>
+      </c>
+      <c r="T346" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U346" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V346" s="11">
+        <v>11</v>
+      </c>
+      <c r="W346" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X346" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y346" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z346" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA346" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB346" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC346" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD346" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE346" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF346" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG346" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH346" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI346" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ346" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK346" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL346" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM346" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN346" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO346" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP346" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ346" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR346" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="347" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A347" s="1">
+        <v>1</v>
+      </c>
+      <c r="B347" s="2">
+        <v>2</v>
+      </c>
+      <c r="C347" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D347" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E347" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F347" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G347" s="5">
+        <v>527</v>
+      </c>
+      <c r="H347" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I347" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J347" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K347" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L347" s="6">
+        <v>5373</v>
+      </c>
+      <c r="M347" s="7">
+        <v>918492.51</v>
+      </c>
+      <c r="N347" s="6">
+        <v>1</v>
+      </c>
+      <c r="O347" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P347" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q347" s="6">
+        <v>0</v>
+      </c>
+      <c r="R347" s="7">
+        <v>0</v>
+      </c>
+      <c r="S347" s="9">
+        <v>0</v>
+      </c>
+      <c r="T347" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U347" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V347" s="11">
+        <v>11</v>
+      </c>
+      <c r="W347" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X347" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y347" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z347" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA347" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB347" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC347" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD347" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE347" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF347" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG347" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH347" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI347" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ347" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK347" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL347" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM347" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN347" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO347" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP347" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ347" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR347" s="3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="348" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A348" s="1">
+        <v>1</v>
+      </c>
+      <c r="B348" s="2">
+        <v>2</v>
+      </c>
+      <c r="C348" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D348" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E348" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F348" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G348" s="5">
+        <v>528</v>
+      </c>
+      <c r="H348" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I348" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J348" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K348" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L348" s="6">
+        <v>5374</v>
+      </c>
+      <c r="M348" s="7">
+        <v>918663.45</v>
+      </c>
+      <c r="N348" s="6">
+        <v>1</v>
+      </c>
+      <c r="O348" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P348" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q348" s="6">
+        <v>0</v>
+      </c>
+      <c r="R348" s="7">
+        <v>0</v>
+      </c>
+      <c r="S348" s="9">
+        <v>0</v>
+      </c>
+      <c r="T348" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U348" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V348" s="11">
+        <v>11</v>
+      </c>
+      <c r="W348" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X348" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y348" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z348" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA348" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB348" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC348" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD348" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE348" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF348" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG348" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH348" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI348" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ348" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK348" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL348" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM348" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN348" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO348" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP348" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ348" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR348" s="3" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="349" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A349" s="1">
+        <v>1</v>
+      </c>
+      <c r="B349" s="2">
+        <v>2</v>
+      </c>
+      <c r="C349" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D349" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E349" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F349" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G349" s="5">
+        <v>529</v>
+      </c>
+      <c r="H349" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I349" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J349" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K349" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L349" s="6">
+        <v>5375</v>
+      </c>
+      <c r="M349" s="7">
+        <v>918834.4</v>
+      </c>
+      <c r="N349" s="6">
+        <v>1</v>
+      </c>
+      <c r="O349" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P349" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q349" s="6">
+        <v>0</v>
+      </c>
+      <c r="R349" s="7">
+        <v>0</v>
+      </c>
+      <c r="S349" s="9">
+        <v>0</v>
+      </c>
+      <c r="T349" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U349" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V349" s="11">
+        <v>11</v>
+      </c>
+      <c r="W349" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X349" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y349" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z349" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA349" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB349" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC349" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD349" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE349" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF349" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG349" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH349" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI349" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ349" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK349" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL349" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM349" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN349" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO349" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP349" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ349" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR349" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="350" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A350" s="1">
+        <v>1</v>
+      </c>
+      <c r="B350" s="2">
+        <v>2</v>
+      </c>
+      <c r="C350" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D350" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E350" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F350" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G350" s="5">
+        <v>530</v>
+      </c>
+      <c r="H350" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I350" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J350" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K350" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L350" s="6">
+        <v>5376</v>
+      </c>
+      <c r="M350" s="7">
+        <v>919005.35</v>
+      </c>
+      <c r="N350" s="6">
+        <v>1</v>
+      </c>
+      <c r="O350" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P350" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q350" s="6">
+        <v>0</v>
+      </c>
+      <c r="R350" s="7">
+        <v>0</v>
+      </c>
+      <c r="S350" s="9">
+        <v>0</v>
+      </c>
+      <c r="T350" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U350" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V350" s="11">
+        <v>11</v>
+      </c>
+      <c r="W350" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X350" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y350" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z350" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA350" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB350" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC350" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD350" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE350" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF350" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG350" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH350" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI350" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ350" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK350" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL350" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM350" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN350" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO350" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP350" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ350" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR350" s="3" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="351" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A351" s="1">
+        <v>1</v>
+      </c>
+      <c r="B351" s="2">
+        <v>2</v>
+      </c>
+      <c r="C351" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D351" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E351" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F351" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G351" s="5">
+        <v>531</v>
+      </c>
+      <c r="H351" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I351" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J351" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K351" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L351" s="6">
+        <v>5377</v>
+      </c>
+      <c r="M351" s="7">
+        <v>919176.29</v>
+      </c>
+      <c r="N351" s="6">
+        <v>1</v>
+      </c>
+      <c r="O351" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P351" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q351" s="6">
+        <v>0</v>
+      </c>
+      <c r="R351" s="7">
+        <v>0</v>
+      </c>
+      <c r="S351" s="9">
+        <v>0</v>
+      </c>
+      <c r="T351" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U351" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V351" s="11">
+        <v>11</v>
+      </c>
+      <c r="W351" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X351" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y351" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z351" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA351" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB351" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC351" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD351" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE351" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF351" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG351" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH351" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI351" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ351" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK351" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL351" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM351" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN351" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO351" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP351" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ351" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR351" s="3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="352" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A352" s="1">
+        <v>1</v>
+      </c>
+      <c r="B352" s="2">
+        <v>2</v>
+      </c>
+      <c r="C352" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D352" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E352" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F352" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G352" s="5">
+        <v>532</v>
+      </c>
+      <c r="H352" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I352" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J352" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K352" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L352" s="6">
+        <v>5378</v>
+      </c>
+      <c r="M352" s="7">
+        <v>919347.24</v>
+      </c>
+      <c r="N352" s="6">
+        <v>1</v>
+      </c>
+      <c r="O352" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P352" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q352" s="6">
+        <v>0</v>
+      </c>
+      <c r="R352" s="7">
+        <v>0</v>
+      </c>
+      <c r="S352" s="9">
+        <v>0</v>
+      </c>
+      <c r="T352" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U352" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V352" s="11">
+        <v>11</v>
+      </c>
+      <c r="W352" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X352" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y352" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z352" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA352" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB352" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC352" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD352" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE352" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF352" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG352" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH352" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI352" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ352" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK352" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL352" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM352" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN352" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO352" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP352" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ352" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR352" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="353" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A353" s="1">
+        <v>1</v>
+      </c>
+      <c r="B353" s="2">
+        <v>2</v>
+      </c>
+      <c r="C353" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D353" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E353" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F353" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G353" s="5">
+        <v>533</v>
+      </c>
+      <c r="H353" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I353" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J353" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K353" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L353" s="6">
+        <v>5379</v>
+      </c>
+      <c r="M353" s="7">
+        <v>919518.18</v>
+      </c>
+      <c r="N353" s="6">
+        <v>1</v>
+      </c>
+      <c r="O353" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P353" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q353" s="6">
+        <v>0</v>
+      </c>
+      <c r="R353" s="7">
+        <v>0</v>
+      </c>
+      <c r="S353" s="9">
+        <v>0</v>
+      </c>
+      <c r="T353" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U353" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V353" s="11">
+        <v>11</v>
+      </c>
+      <c r="W353" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X353" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y353" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z353" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA353" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB353" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC353" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD353" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE353" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF353" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG353" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH353" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI353" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ353" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK353" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL353" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM353" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN353" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO353" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP353" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ353" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR353" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="354" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A354" s="1">
+        <v>1</v>
+      </c>
+      <c r="B354" s="2">
+        <v>2</v>
+      </c>
+      <c r="C354" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D354" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E354" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F354" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G354" s="5">
+        <v>534</v>
+      </c>
+      <c r="H354" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I354" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J354" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K354" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L354" s="6">
+        <v>5380</v>
+      </c>
+      <c r="M354" s="7">
+        <v>919689.13</v>
+      </c>
+      <c r="N354" s="6">
+        <v>1</v>
+      </c>
+      <c r="O354" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P354" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q354" s="6">
+        <v>0</v>
+      </c>
+      <c r="R354" s="7">
+        <v>0</v>
+      </c>
+      <c r="S354" s="9">
+        <v>0</v>
+      </c>
+      <c r="T354" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U354" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V354" s="11">
+        <v>11</v>
+      </c>
+      <c r="W354" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X354" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y354" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z354" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA354" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB354" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC354" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD354" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE354" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF354" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG354" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH354" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI354" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ354" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK354" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL354" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM354" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN354" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO354" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP354" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ354" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR354" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="355" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A355" s="1">
+        <v>1</v>
+      </c>
+      <c r="B355" s="2">
+        <v>2</v>
+      </c>
+      <c r="C355" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D355" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E355" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F355" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G355" s="5">
+        <v>535</v>
+      </c>
+      <c r="H355" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I355" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J355" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K355" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L355" s="6">
+        <v>5381</v>
+      </c>
+      <c r="M355" s="7">
+        <v>919860.08</v>
+      </c>
+      <c r="N355" s="6">
+        <v>1</v>
+      </c>
+      <c r="O355" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P355" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q355" s="6">
+        <v>0</v>
+      </c>
+      <c r="R355" s="7">
+        <v>0</v>
+      </c>
+      <c r="S355" s="9">
+        <v>0</v>
+      </c>
+      <c r="T355" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U355" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V355" s="11">
+        <v>11</v>
+      </c>
+      <c r="W355" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X355" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y355" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z355" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA355" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB355" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC355" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD355" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE355" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF355" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG355" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH355" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI355" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ355" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK355" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL355" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM355" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN355" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO355" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP355" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ355" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR355" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="356" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A356" s="1">
+        <v>1</v>
+      </c>
+      <c r="B356" s="2">
+        <v>2</v>
+      </c>
+      <c r="C356" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D356" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E356" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F356" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G356" s="5">
+        <v>536</v>
+      </c>
+      <c r="H356" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I356" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J356" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K356" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L356" s="6">
+        <v>5382</v>
+      </c>
+      <c r="M356" s="7">
+        <v>920031.02</v>
+      </c>
+      <c r="N356" s="6">
+        <v>1</v>
+      </c>
+      <c r="O356" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P356" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q356" s="6">
+        <v>0</v>
+      </c>
+      <c r="R356" s="7">
+        <v>0</v>
+      </c>
+      <c r="S356" s="9">
+        <v>0</v>
+      </c>
+      <c r="T356" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U356" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V356" s="11">
+        <v>11</v>
+      </c>
+      <c r="W356" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X356" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y356" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z356" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA356" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB356" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC356" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD356" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE356" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF356" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG356" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH356" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI356" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ356" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK356" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL356" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM356" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN356" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO356" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP356" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ356" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR356" s="3" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="357" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A357" s="1">
+        <v>1</v>
+      </c>
+      <c r="B357" s="2">
+        <v>2</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D357" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E357" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F357" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G357" s="5">
+        <v>537</v>
+      </c>
+      <c r="H357" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I357" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J357" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K357" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L357" s="6">
+        <v>5383</v>
+      </c>
+      <c r="M357" s="7">
+        <v>920201.97</v>
+      </c>
+      <c r="N357" s="6">
+        <v>1</v>
+      </c>
+      <c r="O357" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P357" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q357" s="6">
+        <v>0</v>
+      </c>
+      <c r="R357" s="7">
+        <v>0</v>
+      </c>
+      <c r="S357" s="9">
+        <v>0</v>
+      </c>
+      <c r="T357" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U357" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V357" s="11">
+        <v>11</v>
+      </c>
+      <c r="W357" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X357" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y357" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z357" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA357" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB357" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC357" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD357" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE357" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF357" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG357" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH357" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI357" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ357" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK357" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL357" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM357" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN357" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO357" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP357" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ357" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR357" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="358" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A358" s="1">
+        <v>1</v>
+      </c>
+      <c r="B358" s="2">
+        <v>2</v>
+      </c>
+      <c r="C358" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D358" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E358" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F358" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G358" s="5">
+        <v>538</v>
+      </c>
+      <c r="H358" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I358" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J358" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K358" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L358" s="6">
+        <v>5384</v>
+      </c>
+      <c r="M358" s="7">
+        <v>920372.91</v>
+      </c>
+      <c r="N358" s="6">
+        <v>1</v>
+      </c>
+      <c r="O358" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P358" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q358" s="6">
+        <v>0</v>
+      </c>
+      <c r="R358" s="7">
+        <v>0</v>
+      </c>
+      <c r="S358" s="9">
+        <v>0</v>
+      </c>
+      <c r="T358" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U358" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V358" s="11">
+        <v>11</v>
+      </c>
+      <c r="W358" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X358" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y358" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z358" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA358" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB358" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC358" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD358" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE358" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF358" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG358" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH358" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI358" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ358" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK358" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL358" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM358" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN358" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO358" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP358" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ358" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR358" s="3" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="359" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A359" s="1">
+        <v>1</v>
+      </c>
+      <c r="B359" s="2">
+        <v>2</v>
+      </c>
+      <c r="C359" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D359" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E359" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F359" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G359" s="5">
+        <v>539</v>
+      </c>
+      <c r="H359" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I359" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J359" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K359" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L359" s="6">
+        <v>5385</v>
+      </c>
+      <c r="M359" s="7">
+        <v>920543.86</v>
+      </c>
+      <c r="N359" s="6">
+        <v>1</v>
+      </c>
+      <c r="O359" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P359" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q359" s="6">
+        <v>0</v>
+      </c>
+      <c r="R359" s="7">
+        <v>0</v>
+      </c>
+      <c r="S359" s="9">
+        <v>0</v>
+      </c>
+      <c r="T359" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U359" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V359" s="11">
+        <v>11</v>
+      </c>
+      <c r="W359" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X359" s="12">
+        <v>0.44861109999999998</v>
+      </c>
+      <c r="Y359" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z359" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA359" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB359" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC359" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD359" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE359" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF359" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG359" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH359" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI359" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ359" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK359" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL359" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM359" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN359" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO359" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP359" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ359" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR359" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="360" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A360" s="1">
+        <v>1</v>
+      </c>
+      <c r="B360" s="2">
+        <v>2</v>
+      </c>
+      <c r="C360" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D360" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E360" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F360" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G360" s="5">
+        <v>540</v>
+      </c>
+      <c r="H360" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I360" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J360" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K360" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L360" s="6">
+        <v>5386</v>
+      </c>
+      <c r="M360" s="7">
+        <v>920714.81</v>
+      </c>
+      <c r="N360" s="6">
+        <v>1</v>
+      </c>
+      <c r="O360" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P360" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q360" s="6">
+        <v>0</v>
+      </c>
+      <c r="R360" s="7">
+        <v>0</v>
+      </c>
+      <c r="S360" s="9">
+        <v>0</v>
+      </c>
+      <c r="T360" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U360" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V360" s="11">
+        <v>11</v>
+      </c>
+      <c r="W360" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X360" s="12">
+        <v>0.45347219999999999</v>
+      </c>
+      <c r="Y360" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z360" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA360" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB360" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC360" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD360" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE360" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF360" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG360" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH360" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI360" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ360" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK360" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL360" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM360" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN360" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO360" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP360" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ360" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR360" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="361" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A361" s="1">
+        <v>1</v>
+      </c>
+      <c r="B361" s="2">
+        <v>2</v>
+      </c>
+      <c r="C361" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D361" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E361" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F361" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G361" s="5">
+        <v>541</v>
+      </c>
+      <c r="H361" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I361" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J361" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K361" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L361" s="6">
+        <v>5387</v>
+      </c>
+      <c r="M361" s="7">
+        <v>920885.75</v>
+      </c>
+      <c r="N361" s="6">
+        <v>1</v>
+      </c>
+      <c r="O361" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P361" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q361" s="6">
+        <v>0</v>
+      </c>
+      <c r="R361" s="7">
+        <v>0</v>
+      </c>
+      <c r="S361" s="9">
+        <v>0</v>
+      </c>
+      <c r="T361" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U361" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V361" s="11">
+        <v>11</v>
+      </c>
+      <c r="W361" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X361" s="12">
+        <v>0.45347219999999999</v>
+      </c>
+      <c r="Y361" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z361" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA361" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB361" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC361" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD361" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE361" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF361" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG361" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH361" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI361" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ361" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK361" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL361" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM361" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN361" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO361" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP361" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ361" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR361" s="3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="362" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A362" s="1">
+        <v>1</v>
+      </c>
+      <c r="B362" s="2">
+        <v>2</v>
+      </c>
+      <c r="C362" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D362" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E362" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F362" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G362" s="5">
+        <v>542</v>
+      </c>
+      <c r="H362" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I362" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J362" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K362" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L362" s="6">
+        <v>5388</v>
+      </c>
+      <c r="M362" s="7">
+        <v>921056.7</v>
+      </c>
+      <c r="N362" s="6">
+        <v>1</v>
+      </c>
+      <c r="O362" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P362" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q362" s="6">
+        <v>0</v>
+      </c>
+      <c r="R362" s="7">
+        <v>0</v>
+      </c>
+      <c r="S362" s="9">
+        <v>0</v>
+      </c>
+      <c r="T362" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U362" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V362" s="11">
+        <v>11</v>
+      </c>
+      <c r="W362" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X362" s="12">
+        <v>0.45347219999999999</v>
+      </c>
+      <c r="Y362" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z362" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA362" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB362" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC362" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD362" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE362" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF362" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG362" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH362" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI362" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ362" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK362" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL362" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM362" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN362" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO362" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP362" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ362" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR362" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="363" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A363" s="1">
+        <v>1</v>
+      </c>
+      <c r="B363" s="2">
+        <v>2</v>
+      </c>
+      <c r="C363" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D363" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E363" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F363" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G363" s="5">
+        <v>543</v>
+      </c>
+      <c r="H363" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I363" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J363" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K363" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L363" s="6">
+        <v>5389</v>
+      </c>
+      <c r="M363" s="7">
+        <v>921227.64</v>
+      </c>
+      <c r="N363" s="6">
+        <v>1</v>
+      </c>
+      <c r="O363" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P363" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q363" s="6">
+        <v>0</v>
+      </c>
+      <c r="R363" s="7">
+        <v>0</v>
+      </c>
+      <c r="S363" s="9">
+        <v>0</v>
+      </c>
+      <c r="T363" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U363" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V363" s="11">
+        <v>11</v>
+      </c>
+      <c r="W363" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X363" s="12">
+        <v>0.45347219999999999</v>
+      </c>
+      <c r="Y363" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z363" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA363" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB363" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC363" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD363" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE363" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF363" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG363" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH363" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI363" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ363" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK363" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL363" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM363" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN363" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO363" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP363" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ363" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR363" s="3" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="364" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A364" s="1">
+        <v>1</v>
+      </c>
+      <c r="B364" s="2">
+        <v>2</v>
+      </c>
+      <c r="C364" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D364" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E364" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F364" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G364" s="5">
+        <v>544</v>
+      </c>
+      <c r="H364" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I364" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J364" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K364" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L364" s="6">
+        <v>5390</v>
+      </c>
+      <c r="M364" s="7">
+        <v>921398.59</v>
+      </c>
+      <c r="N364" s="6">
+        <v>1</v>
+      </c>
+      <c r="O364" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P364" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q364" s="6">
+        <v>0</v>
+      </c>
+      <c r="R364" s="7">
+        <v>0</v>
+      </c>
+      <c r="S364" s="9">
+        <v>0</v>
+      </c>
+      <c r="T364" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U364" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V364" s="11">
+        <v>11</v>
+      </c>
+      <c r="W364" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X364" s="12">
+        <v>0.45347219999999999</v>
+      </c>
+      <c r="Y364" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z364" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA364" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB364" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC364" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD364" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE364" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF364" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG364" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH364" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI364" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ364" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK364" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL364" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM364" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN364" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO364" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP364" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ364" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR364" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="365" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A365" s="1">
+        <v>1</v>
+      </c>
+      <c r="B365" s="2">
+        <v>2</v>
+      </c>
+      <c r="C365" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D365" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E365" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F365" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G365" s="5">
+        <v>545</v>
+      </c>
+      <c r="H365" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I365" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J365" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K365" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L365" s="6">
+        <v>5391</v>
+      </c>
+      <c r="M365" s="7">
+        <v>921569.53</v>
+      </c>
+      <c r="N365" s="6">
+        <v>1</v>
+      </c>
+      <c r="O365" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P365" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q365" s="6">
+        <v>0</v>
+      </c>
+      <c r="R365" s="7">
+        <v>0</v>
+      </c>
+      <c r="S365" s="9">
+        <v>0</v>
+      </c>
+      <c r="T365" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U365" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V365" s="11">
+        <v>11</v>
+      </c>
+      <c r="W365" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X365" s="12">
+        <v>0.45347219999999999</v>
+      </c>
+      <c r="Y365" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z365" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA365" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB365" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC365" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD365" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE365" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF365" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG365" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH365" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI365" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ365" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK365" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL365" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM365" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN365" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO365" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP365" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ365" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR365" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="366" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A366" s="1">
+        <v>1</v>
+      </c>
+      <c r="B366" s="2">
+        <v>2</v>
+      </c>
+      <c r="C366" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D366" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E366" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F366" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G366" s="5">
+        <v>546</v>
+      </c>
+      <c r="H366" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I366" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J366" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K366" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L366" s="6">
+        <v>5392</v>
+      </c>
+      <c r="M366" s="7">
+        <v>921740.48</v>
+      </c>
+      <c r="N366" s="6">
+        <v>1</v>
+      </c>
+      <c r="O366" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P366" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q366" s="6">
+        <v>0</v>
+      </c>
+      <c r="R366" s="7">
+        <v>0</v>
+      </c>
+      <c r="S366" s="9">
+        <v>0</v>
+      </c>
+      <c r="T366" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U366" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V366" s="11">
+        <v>11</v>
+      </c>
+      <c r="W366" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X366" s="12">
+        <v>0.45347219999999999</v>
+      </c>
+      <c r="Y366" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z366" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA366" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB366" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC366" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD366" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE366" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF366" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG366" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH366" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI366" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ366" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK366" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL366" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM366" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN366" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO366" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP366" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ366" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR366" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="367" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A367" s="1">
+        <v>1</v>
+      </c>
+      <c r="B367" s="2">
+        <v>2</v>
+      </c>
+      <c r="C367" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D367" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E367" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F367" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G367" s="5">
+        <v>547</v>
+      </c>
+      <c r="H367" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I367" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J367" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K367" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L367" s="6">
+        <v>5393</v>
+      </c>
+      <c r="M367" s="7">
+        <v>921911.43</v>
+      </c>
+      <c r="N367" s="6">
+        <v>1</v>
+      </c>
+      <c r="O367" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P367" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q367" s="6">
+        <v>0</v>
+      </c>
+      <c r="R367" s="7">
+        <v>0</v>
+      </c>
+      <c r="S367" s="9">
+        <v>0</v>
+      </c>
+      <c r="T367" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U367" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V367" s="11">
+        <v>11</v>
+      </c>
+      <c r="W367" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X367" s="12">
+        <v>0.45347219999999999</v>
+      </c>
+      <c r="Y367" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z367" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA367" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB367" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC367" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD367" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE367" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF367" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG367" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH367" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI367" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ367" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK367" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL367" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM367" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN367" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO367" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP367" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ367" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR367" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="368" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A368" s="1">
+        <v>1</v>
+      </c>
+      <c r="B368" s="2">
+        <v>2</v>
+      </c>
+      <c r="C368" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D368" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E368" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F368" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G368" s="5">
+        <v>548</v>
+      </c>
+      <c r="H368" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I368" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J368" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K368" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L368" s="6">
+        <v>5394</v>
+      </c>
+      <c r="M368" s="7">
+        <v>922082.37</v>
+      </c>
+      <c r="N368" s="6">
+        <v>1</v>
+      </c>
+      <c r="O368" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P368" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q368" s="6">
+        <v>0</v>
+      </c>
+      <c r="R368" s="7">
+        <v>0</v>
+      </c>
+      <c r="S368" s="9">
+        <v>0</v>
+      </c>
+      <c r="T368" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U368" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V368" s="11">
+        <v>11</v>
+      </c>
+      <c r="W368" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X368" s="12">
+        <v>0.45347219999999999</v>
+      </c>
+      <c r="Y368" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z368" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA368" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB368" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC368" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD368" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE368" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF368" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG368" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH368" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI368" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ368" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK368" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL368" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM368" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN368" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO368" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP368" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ368" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR368" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="369" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A369" s="1">
+        <v>1</v>
+      </c>
+      <c r="B369" s="2">
+        <v>2</v>
+      </c>
+      <c r="C369" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D369" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E369" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F369" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G369" s="5">
+        <v>549</v>
+      </c>
+      <c r="H369" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I369" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J369" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K369" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L369" s="6">
+        <v>5395</v>
+      </c>
+      <c r="M369" s="7">
+        <v>922253.32</v>
+      </c>
+      <c r="N369" s="6">
+        <v>1</v>
+      </c>
+      <c r="O369" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P369" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q369" s="6">
+        <v>0</v>
+      </c>
+      <c r="R369" s="7">
+        <v>0</v>
+      </c>
+      <c r="S369" s="9">
+        <v>0</v>
+      </c>
+      <c r="T369" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U369" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V369" s="11">
+        <v>11</v>
+      </c>
+      <c r="W369" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X369" s="12">
+        <v>0.45347219999999999</v>
+      </c>
+      <c r="Y369" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z369" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA369" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB369" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC369" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD369" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE369" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF369" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG369" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH369" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI369" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ369" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK369" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL369" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM369" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN369" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO369" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP369" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ369" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR369" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="370" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A370" s="1">
+        <v>1</v>
+      </c>
+      <c r="B370" s="2">
+        <v>2</v>
+      </c>
+      <c r="C370" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D370" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E370" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F370" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G370" s="5">
+        <v>550</v>
+      </c>
+      <c r="H370" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I370" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J370" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K370" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L370" s="6">
+        <v>5396</v>
+      </c>
+      <c r="M370" s="7">
+        <v>922424.26</v>
+      </c>
+      <c r="N370" s="6">
+        <v>1</v>
+      </c>
+      <c r="O370" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P370" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q370" s="6">
+        <v>0</v>
+      </c>
+      <c r="R370" s="7">
+        <v>0</v>
+      </c>
+      <c r="S370" s="9">
+        <v>0</v>
+      </c>
+      <c r="T370" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U370" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V370" s="11">
+        <v>11</v>
+      </c>
+      <c r="W370" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X370" s="12">
+        <v>0.45347219999999999</v>
+      </c>
+      <c r="Y370" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z370" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA370" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB370" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC370" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD370" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE370" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF370" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG370" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH370" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI370" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ370" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK370" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL370" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM370" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN370" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO370" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP370" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ370" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR370" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="371" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A371" s="1">
+        <v>1</v>
+      </c>
+      <c r="B371" s="2">
+        <v>2</v>
+      </c>
+      <c r="C371" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D371" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E371" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F371" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G371" s="5">
+        <v>551</v>
+      </c>
+      <c r="H371" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I371" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J371" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K371" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L371" s="6">
+        <v>5397</v>
+      </c>
+      <c r="M371" s="7">
+        <v>922595.21</v>
+      </c>
+      <c r="N371" s="6">
+        <v>1</v>
+      </c>
+      <c r="O371" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P371" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q371" s="6">
+        <v>0</v>
+      </c>
+      <c r="R371" s="7">
+        <v>0</v>
+      </c>
+      <c r="S371" s="9">
+        <v>0</v>
+      </c>
+      <c r="T371" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U371" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V371" s="11">
+        <v>11</v>
+      </c>
+      <c r="W371" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X371" s="12">
+        <v>0.4611111</v>
+      </c>
+      <c r="Y371" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z371" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA371" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB371" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC371" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD371" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE371" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF371" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG371" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH371" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI371" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ371" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK371" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL371" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM371" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN371" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO371" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP371" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ371" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR371" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="372" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A372" s="1">
+        <v>1</v>
+      </c>
+      <c r="B372" s="2">
+        <v>2</v>
+      </c>
+      <c r="C372" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D372" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E372" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F372" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G372" s="5">
+        <v>552</v>
+      </c>
+      <c r="H372" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I372" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J372" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K372" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L372" s="6">
+        <v>5398</v>
+      </c>
+      <c r="M372" s="7">
+        <v>922766.16</v>
+      </c>
+      <c r="N372" s="6">
+        <v>1</v>
+      </c>
+      <c r="O372" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P372" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q372" s="6">
+        <v>0</v>
+      </c>
+      <c r="R372" s="7">
+        <v>0</v>
+      </c>
+      <c r="S372" s="9">
+        <v>0</v>
+      </c>
+      <c r="T372" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U372" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V372" s="11">
+        <v>11</v>
+      </c>
+      <c r="W372" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X372" s="12">
+        <v>0.4611111</v>
+      </c>
+      <c r="Y372" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z372" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA372" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB372" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC372" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD372" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE372" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF372" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG372" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH372" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI372" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ372" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK372" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL372" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM372" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN372" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO372" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP372" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ372" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR372" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="373" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A373" s="1">
+        <v>1</v>
+      </c>
+      <c r="B373" s="2">
+        <v>2</v>
+      </c>
+      <c r="C373" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D373" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E373" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F373" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G373" s="5">
+        <v>553</v>
+      </c>
+      <c r="H373" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I373" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J373" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K373" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L373" s="6">
+        <v>5399</v>
+      </c>
+      <c r="M373" s="7">
+        <v>922937.1</v>
+      </c>
+      <c r="N373" s="6">
+        <v>1</v>
+      </c>
+      <c r="O373" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P373" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q373" s="6">
+        <v>0</v>
+      </c>
+      <c r="R373" s="7">
+        <v>0</v>
+      </c>
+      <c r="S373" s="9">
+        <v>0</v>
+      </c>
+      <c r="T373" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U373" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V373" s="11">
+        <v>11</v>
+      </c>
+      <c r="W373" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X373" s="12">
+        <v>0.4611111</v>
+      </c>
+      <c r="Y373" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z373" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA373" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB373" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC373" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD373" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE373" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF373" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG373" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH373" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI373" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ373" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK373" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL373" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM373" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN373" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO373" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP373" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ373" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR373" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="374" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A374" s="1">
+        <v>1</v>
+      </c>
+      <c r="B374" s="2">
+        <v>2</v>
+      </c>
+      <c r="C374" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D374" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E374" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F374" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G374" s="5">
+        <v>554</v>
+      </c>
+      <c r="H374" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I374" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J374" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K374" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L374" s="6">
+        <v>5400</v>
+      </c>
+      <c r="M374" s="7">
+        <v>923108.05</v>
+      </c>
+      <c r="N374" s="6">
+        <v>1</v>
+      </c>
+      <c r="O374" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P374" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q374" s="6">
+        <v>0</v>
+      </c>
+      <c r="R374" s="7">
+        <v>0</v>
+      </c>
+      <c r="S374" s="9">
+        <v>0</v>
+      </c>
+      <c r="T374" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U374" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V374" s="11">
+        <v>11</v>
+      </c>
+      <c r="W374" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X374" s="12">
+        <v>0.4611111</v>
+      </c>
+      <c r="Y374" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z374" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA374" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB374" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC374" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD374" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE374" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF374" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG374" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH374" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI374" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ374" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK374" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL374" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM374" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN374" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO374" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP374" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ374" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR374" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="375" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A375" s="1">
+        <v>1</v>
+      </c>
+      <c r="B375" s="2">
+        <v>2</v>
+      </c>
+      <c r="C375" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D375" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E375" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F375" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G375" s="5">
+        <v>555</v>
+      </c>
+      <c r="H375" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I375" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J375" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K375" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L375" s="6">
+        <v>5401</v>
+      </c>
+      <c r="M375" s="7">
+        <v>923278.99</v>
+      </c>
+      <c r="N375" s="6">
+        <v>1</v>
+      </c>
+      <c r="O375" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P375" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q375" s="6">
+        <v>0</v>
+      </c>
+      <c r="R375" s="7">
+        <v>0</v>
+      </c>
+      <c r="S375" s="9">
+        <v>0</v>
+      </c>
+      <c r="T375" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U375" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V375" s="11">
+        <v>11</v>
+      </c>
+      <c r="W375" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X375" s="12">
+        <v>0.4611111</v>
+      </c>
+      <c r="Y375" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z375" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA375" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB375" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC375" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD375" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE375" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF375" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG375" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH375" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI375" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ375" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK375" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL375" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM375" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN375" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO375" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP375" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ375" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR375" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="376" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A376" s="1">
+        <v>1</v>
+      </c>
+      <c r="B376" s="2">
+        <v>2</v>
+      </c>
+      <c r="C376" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D376" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E376" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F376" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G376" s="5">
+        <v>556</v>
+      </c>
+      <c r="H376" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I376" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J376" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K376" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L376" s="6">
+        <v>5402</v>
+      </c>
+      <c r="M376" s="7">
+        <v>923449.94</v>
+      </c>
+      <c r="N376" s="6">
+        <v>1</v>
+      </c>
+      <c r="O376" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P376" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q376" s="6">
+        <v>0</v>
+      </c>
+      <c r="R376" s="7">
+        <v>0</v>
+      </c>
+      <c r="S376" s="9">
+        <v>0</v>
+      </c>
+      <c r="T376" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U376" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V376" s="11">
+        <v>11</v>
+      </c>
+      <c r="W376" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X376" s="12">
+        <v>0.4611111</v>
+      </c>
+      <c r="Y376" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z376" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA376" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB376" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC376" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD376" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE376" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF376" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG376" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH376" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI376" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ376" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK376" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL376" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM376" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN376" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO376" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP376" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ376" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR376" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="377" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A377" s="1">
+        <v>1</v>
+      </c>
+      <c r="B377" s="2">
+        <v>2</v>
+      </c>
+      <c r="C377" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D377" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E377" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F377" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G377" s="5">
+        <v>557</v>
+      </c>
+      <c r="H377" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I377" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J377" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K377" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L377" s="6">
+        <v>5403</v>
+      </c>
+      <c r="M377" s="7">
+        <v>923620.89</v>
+      </c>
+      <c r="N377" s="6">
+        <v>1</v>
+      </c>
+      <c r="O377" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P377" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q377" s="6">
+        <v>0</v>
+      </c>
+      <c r="R377" s="7">
+        <v>0</v>
+      </c>
+      <c r="S377" s="9">
+        <v>0</v>
+      </c>
+      <c r="T377" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U377" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V377" s="11">
+        <v>11</v>
+      </c>
+      <c r="W377" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X377" s="12">
+        <v>0.4611111</v>
+      </c>
+      <c r="Y377" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z377" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA377" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB377" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC377" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD377" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE377" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF377" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG377" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH377" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI377" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ377" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK377" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL377" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM377" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN377" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO377" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP377" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ377" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR377" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="378" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A378" s="1">
+        <v>1</v>
+      </c>
+      <c r="B378" s="2">
+        <v>2</v>
+      </c>
+      <c r="C378" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D378" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E378" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F378" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G378" s="5">
+        <v>558</v>
+      </c>
+      <c r="H378" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I378" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J378" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K378" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L378" s="6">
+        <v>5404</v>
+      </c>
+      <c r="M378" s="7">
+        <v>923791.83</v>
+      </c>
+      <c r="N378" s="6">
+        <v>1</v>
+      </c>
+      <c r="O378" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P378" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q378" s="6">
+        <v>0</v>
+      </c>
+      <c r="R378" s="7">
+        <v>0</v>
+      </c>
+      <c r="S378" s="9">
+        <v>0</v>
+      </c>
+      <c r="T378" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U378" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V378" s="11">
+        <v>11</v>
+      </c>
+      <c r="W378" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X378" s="12">
+        <v>0.4611111</v>
+      </c>
+      <c r="Y378" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z378" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA378" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB378" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC378" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD378" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE378" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF378" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG378" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH378" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI378" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ378" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK378" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL378" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM378" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN378" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO378" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP378" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ378" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR378" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="379" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A379" s="1">
+        <v>1</v>
+      </c>
+      <c r="B379" s="2">
+        <v>2</v>
+      </c>
+      <c r="C379" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D379" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E379" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F379" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G379" s="5">
+        <v>559</v>
+      </c>
+      <c r="H379" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I379" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J379" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K379" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L379" s="6">
+        <v>5405</v>
+      </c>
+      <c r="M379" s="7">
+        <v>923962.78</v>
+      </c>
+      <c r="N379" s="6">
+        <v>1</v>
+      </c>
+      <c r="O379" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P379" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q379" s="6">
+        <v>0</v>
+      </c>
+      <c r="R379" s="7">
+        <v>0</v>
+      </c>
+      <c r="S379" s="9">
+        <v>0</v>
+      </c>
+      <c r="T379" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U379" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V379" s="11">
+        <v>11</v>
+      </c>
+      <c r="W379" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X379" s="12">
+        <v>0.4611111</v>
+      </c>
+      <c r="Y379" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z379" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA379" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB379" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC379" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD379" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE379" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF379" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG379" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH379" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI379" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ379" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK379" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL379" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM379" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN379" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO379" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP379" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ379" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR379" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="380" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A380" s="1">
+        <v>1</v>
+      </c>
+      <c r="B380" s="2">
+        <v>2</v>
+      </c>
+      <c r="C380" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D380" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E380" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F380" s="4">
+        <v>46317</v>
+      </c>
+      <c r="G380" s="5">
+        <v>560</v>
+      </c>
+      <c r="H380" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I380" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J380" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K380" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L380" s="6">
+        <v>5406</v>
+      </c>
+      <c r="M380" s="7">
+        <v>924133.72</v>
+      </c>
+      <c r="N380" s="6">
+        <v>1</v>
+      </c>
+      <c r="O380" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P380" s="8">
+        <v>170.95</v>
+      </c>
+      <c r="Q380" s="6">
+        <v>0</v>
+      </c>
+      <c r="R380" s="7">
+        <v>0</v>
+      </c>
+      <c r="S380" s="9">
+        <v>0</v>
+      </c>
+      <c r="T380" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U380" s="10">
+        <v>68458</v>
+      </c>
+      <c r="V380" s="11">
+        <v>11</v>
+      </c>
+      <c r="W380" s="4">
+        <v>46317</v>
+      </c>
+      <c r="X380" s="12">
+        <v>0.4611111</v>
+      </c>
+      <c r="Y380" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB380" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG380" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI380" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ380" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK380" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL380" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM380" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ380" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR380" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27899BF4-4213-4D0B-BD34-7001AB8C6D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77E2B31E-EBE4-44CF-8115-0475EE99E687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="696" yWindow="708" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D60CB459-0D56-4236-8E50-7D8359D0B515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6437C4AB-8435-46A8-9747-43F9498DE6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="696" yWindow="708" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="158">
   <si>
     <t>Sel</t>
   </si>
@@ -262,6 +262,117 @@
     <t>10016398</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>FORNO ELETRICO NARDELLI EMBUTIR 80L BLACK - NARDELLI EMBUTIR 80L BLACK - 127 V</t>
+  </si>
+  <si>
+    <t>1882900000034</t>
+  </si>
+  <si>
+    <t>1882900000035</t>
+  </si>
+  <si>
+    <t>1882900000036</t>
+  </si>
+  <si>
+    <t>1882900000037</t>
+  </si>
+  <si>
+    <t>1882900000038</t>
+  </si>
+  <si>
+    <t>1882900000039</t>
+  </si>
+  <si>
+    <t>1882900000040</t>
+  </si>
+  <si>
+    <t>1882900000041</t>
+  </si>
+  <si>
+    <t>1882900000042</t>
+  </si>
+  <si>
+    <t>1882900000043</t>
+  </si>
+  <si>
+    <t>1882900000044</t>
+  </si>
+  <si>
+    <t>1882900000045</t>
+  </si>
+  <si>
+    <t>1882900000046</t>
+  </si>
+  <si>
+    <t>1882900000047</t>
+  </si>
+  <si>
+    <t>1882900000048</t>
+  </si>
+  <si>
+    <t>1882900000049</t>
+  </si>
+  <si>
+    <t>1882900000050</t>
+  </si>
+  <si>
+    <t>1882900000051</t>
+  </si>
+  <si>
+    <t>1882900000052</t>
+  </si>
+  <si>
+    <t>1882900000053</t>
+  </si>
+  <si>
+    <t>1882900000014</t>
+  </si>
+  <si>
+    <t>1882900000015</t>
+  </si>
+  <si>
+    <t>1882900000016</t>
+  </si>
+  <si>
+    <t>1882900000017</t>
+  </si>
+  <si>
+    <t>1882900000018</t>
+  </si>
+  <si>
+    <t>1882900000019</t>
+  </si>
+  <si>
+    <t>1882900000020</t>
+  </si>
+  <si>
+    <t>1882900000021</t>
+  </si>
+  <si>
+    <t>1882900000022</t>
+  </si>
+  <si>
+    <t>1882900000023</t>
+  </si>
+  <si>
+    <t>1882900000024</t>
+  </si>
+  <si>
+    <t>1882900000025</t>
+  </si>
+  <si>
+    <t>1882900000026</t>
+  </si>
+  <si>
+    <t>1882900000027</t>
+  </si>
+  <si>
+    <t>1882900000028</t>
+  </si>
+  <si>
     <t>FORNO ELETRICO NARDELLI EMBUTIR 80L BLACK - NARDELLI EMBUTIR 80L BLACK - 220 V</t>
   </si>
   <si>
@@ -341,6 +452,48 @@
   </si>
   <si>
     <t>1883100000073</t>
+  </si>
+  <si>
+    <t>1883100000040</t>
+  </si>
+  <si>
+    <t>1883100000041</t>
+  </si>
+  <si>
+    <t>1883100000042</t>
+  </si>
+  <si>
+    <t>1883100000043</t>
+  </si>
+  <si>
+    <t>1883100000044</t>
+  </si>
+  <si>
+    <t>1883100000045</t>
+  </si>
+  <si>
+    <t>1883100000046</t>
+  </si>
+  <si>
+    <t>1883100000047</t>
+  </si>
+  <si>
+    <t>1883100000048</t>
+  </si>
+  <si>
+    <t>1883100000049</t>
+  </si>
+  <si>
+    <t>1883100000050</t>
+  </si>
+  <si>
+    <t>1883100000051</t>
+  </si>
+  <si>
+    <t>1883100000052</t>
+  </si>
+  <si>
+    <t>1883100000053</t>
   </si>
 </sst>
 </file>
@@ -916,7 +1069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR51"/>
+  <dimension ref="A1:AR100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -4280,7 +4433,7 @@
         <v>79</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>46</v>
@@ -4289,7 +4442,7 @@
         <v>46318</v>
       </c>
       <c r="G26" s="5">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>47</v>
@@ -4313,10 +4466,10 @@
         <v>1</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P26" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q26" s="6">
         <v>0</v>
@@ -4331,7 +4484,7 @@
         <v>52</v>
       </c>
       <c r="U26" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V26" s="11">
         <v>11</v>
@@ -4340,7 +4493,7 @@
         <v>46318</v>
       </c>
       <c r="X26" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y26" s="10">
         <v>0</v>
@@ -4400,7 +4553,7 @@
         <v>53</v>
       </c>
       <c r="AR26" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:44" x14ac:dyDescent="0.3">
@@ -4414,7 +4567,7 @@
         <v>79</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>46</v>
@@ -4423,7 +4576,7 @@
         <v>46318</v>
       </c>
       <c r="G27" s="5">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>47</v>
@@ -4441,16 +4594,16 @@
         <v>1</v>
       </c>
       <c r="M27" s="7">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="N27" s="6">
         <v>1</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P27" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q27" s="6">
         <v>0</v>
@@ -4465,7 +4618,7 @@
         <v>52</v>
       </c>
       <c r="U27" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V27" s="11">
         <v>11</v>
@@ -4474,7 +4627,7 @@
         <v>46318</v>
       </c>
       <c r="X27" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y27" s="10">
         <v>0</v>
@@ -4534,7 +4687,7 @@
         <v>53</v>
       </c>
       <c r="AR27" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:44" x14ac:dyDescent="0.3">
@@ -4548,7 +4701,7 @@
         <v>79</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>46</v>
@@ -4557,7 +4710,7 @@
         <v>46318</v>
       </c>
       <c r="G28" s="5">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>47</v>
@@ -4575,16 +4728,16 @@
         <v>2</v>
       </c>
       <c r="M28" s="7">
-        <v>761.15</v>
+        <v>749.6</v>
       </c>
       <c r="N28" s="6">
         <v>1</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P28" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q28" s="6">
         <v>0</v>
@@ -4599,7 +4752,7 @@
         <v>52</v>
       </c>
       <c r="U28" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V28" s="11">
         <v>11</v>
@@ -4608,7 +4761,7 @@
         <v>46318</v>
       </c>
       <c r="X28" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y28" s="10">
         <v>0</v>
@@ -4668,7 +4821,7 @@
         <v>53</v>
       </c>
       <c r="AR28" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.3">
@@ -4682,7 +4835,7 @@
         <v>79</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>46</v>
@@ -4691,7 +4844,7 @@
         <v>46318</v>
       </c>
       <c r="G29" s="5">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>47</v>
@@ -4709,16 +4862,16 @@
         <v>3</v>
       </c>
       <c r="M29" s="7">
-        <v>1141.72</v>
+        <v>1124.3900000000001</v>
       </c>
       <c r="N29" s="6">
         <v>1</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P29" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q29" s="6">
         <v>0</v>
@@ -4733,7 +4886,7 @@
         <v>52</v>
       </c>
       <c r="U29" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V29" s="11">
         <v>11</v>
@@ -4742,7 +4895,7 @@
         <v>46318</v>
       </c>
       <c r="X29" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y29" s="10">
         <v>0</v>
@@ -4802,7 +4955,7 @@
         <v>53</v>
       </c>
       <c r="AR29" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:44" x14ac:dyDescent="0.3">
@@ -4816,7 +4969,7 @@
         <v>79</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>46</v>
@@ -4825,7 +4978,7 @@
         <v>46318</v>
       </c>
       <c r="G30" s="5">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>47</v>
@@ -4843,16 +4996,16 @@
         <v>4</v>
       </c>
       <c r="M30" s="7">
-        <v>1522.29</v>
+        <v>1499.19</v>
       </c>
       <c r="N30" s="6">
         <v>1</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P30" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q30" s="6">
         <v>0</v>
@@ -4867,7 +5020,7 @@
         <v>52</v>
       </c>
       <c r="U30" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V30" s="11">
         <v>11</v>
@@ -4876,7 +5029,7 @@
         <v>46318</v>
       </c>
       <c r="X30" s="12">
-        <v>0.35763889999999998</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y30" s="10">
         <v>0</v>
@@ -4936,7 +5089,7 @@
         <v>53</v>
       </c>
       <c r="AR30" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:44" x14ac:dyDescent="0.3">
@@ -4950,7 +5103,7 @@
         <v>79</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>46</v>
@@ -4959,7 +5112,7 @@
         <v>46318</v>
       </c>
       <c r="G31" s="5">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>47</v>
@@ -4977,16 +5130,16 @@
         <v>5</v>
       </c>
       <c r="M31" s="7">
-        <v>1902.87</v>
+        <v>1873.99</v>
       </c>
       <c r="N31" s="6">
         <v>1</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P31" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q31" s="6">
         <v>0</v>
@@ -5001,7 +5154,7 @@
         <v>52</v>
       </c>
       <c r="U31" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V31" s="11">
         <v>11</v>
@@ -5010,7 +5163,7 @@
         <v>46318</v>
       </c>
       <c r="X31" s="12">
-        <v>0.3854167</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y31" s="10">
         <v>0</v>
@@ -5070,7 +5223,7 @@
         <v>53</v>
       </c>
       <c r="AR31" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.3">
@@ -5084,7 +5237,7 @@
         <v>79</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>46</v>
@@ -5093,7 +5246,7 @@
         <v>46318</v>
       </c>
       <c r="G32" s="5">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>47</v>
@@ -5111,16 +5264,16 @@
         <v>6</v>
       </c>
       <c r="M32" s="7">
-        <v>2283.44</v>
+        <v>2248.79</v>
       </c>
       <c r="N32" s="6">
         <v>1</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P32" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q32" s="6">
         <v>0</v>
@@ -5135,7 +5288,7 @@
         <v>52</v>
       </c>
       <c r="U32" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V32" s="11">
         <v>11</v>
@@ -5144,7 +5297,7 @@
         <v>46318</v>
       </c>
       <c r="X32" s="12">
-        <v>0.3854167</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y32" s="10">
         <v>0</v>
@@ -5204,7 +5357,7 @@
         <v>53</v>
       </c>
       <c r="AR32" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.3">
@@ -5218,7 +5371,7 @@
         <v>79</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>46</v>
@@ -5227,7 +5380,7 @@
         <v>46318</v>
       </c>
       <c r="G33" s="5">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>47</v>
@@ -5245,16 +5398,16 @@
         <v>7</v>
       </c>
       <c r="M33" s="7">
-        <v>2664.01</v>
+        <v>2623.59</v>
       </c>
       <c r="N33" s="6">
         <v>1</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P33" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q33" s="6">
         <v>0</v>
@@ -5269,7 +5422,7 @@
         <v>52</v>
       </c>
       <c r="U33" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V33" s="11">
         <v>11</v>
@@ -5278,7 +5431,7 @@
         <v>46318</v>
       </c>
       <c r="X33" s="12">
-        <v>0.3854167</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y33" s="10">
         <v>0</v>
@@ -5338,7 +5491,7 @@
         <v>53</v>
       </c>
       <c r="AR33" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:44" x14ac:dyDescent="0.3">
@@ -5352,7 +5505,7 @@
         <v>79</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>46</v>
@@ -5361,7 +5514,7 @@
         <v>46318</v>
       </c>
       <c r="G34" s="5">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>47</v>
@@ -5379,16 +5532,16 @@
         <v>8</v>
       </c>
       <c r="M34" s="7">
-        <v>3044.59</v>
+        <v>2998.39</v>
       </c>
       <c r="N34" s="6">
         <v>1</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P34" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q34" s="6">
         <v>0</v>
@@ -5403,7 +5556,7 @@
         <v>52</v>
       </c>
       <c r="U34" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V34" s="11">
         <v>11</v>
@@ -5412,7 +5565,7 @@
         <v>46318</v>
       </c>
       <c r="X34" s="12">
-        <v>0.3986111</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y34" s="10">
         <v>0</v>
@@ -5472,7 +5625,7 @@
         <v>53</v>
       </c>
       <c r="AR34" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.3">
@@ -5486,7 +5639,7 @@
         <v>79</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>46</v>
@@ -5495,7 +5648,7 @@
         <v>46318</v>
       </c>
       <c r="G35" s="5">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>47</v>
@@ -5513,16 +5666,16 @@
         <v>9</v>
       </c>
       <c r="M35" s="7">
-        <v>3425.16</v>
+        <v>3373.18</v>
       </c>
       <c r="N35" s="6">
         <v>1</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P35" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q35" s="6">
         <v>0</v>
@@ -5537,7 +5690,7 @@
         <v>52</v>
       </c>
       <c r="U35" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V35" s="11">
         <v>11</v>
@@ -5546,7 +5699,7 @@
         <v>46318</v>
       </c>
       <c r="X35" s="12">
-        <v>0.3986111</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y35" s="10">
         <v>0</v>
@@ -5606,7 +5759,7 @@
         <v>53</v>
       </c>
       <c r="AR35" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.3">
@@ -5620,7 +5773,7 @@
         <v>79</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>46</v>
@@ -5629,7 +5782,7 @@
         <v>46318</v>
       </c>
       <c r="G36" s="5">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>47</v>
@@ -5647,16 +5800,16 @@
         <v>10</v>
       </c>
       <c r="M36" s="7">
-        <v>3805.73</v>
+        <v>3747.98</v>
       </c>
       <c r="N36" s="6">
         <v>1</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P36" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q36" s="6">
         <v>0</v>
@@ -5671,7 +5824,7 @@
         <v>52</v>
       </c>
       <c r="U36" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V36" s="11">
         <v>11</v>
@@ -5680,7 +5833,7 @@
         <v>46318</v>
       </c>
       <c r="X36" s="12">
-        <v>0.4270833</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y36" s="10">
         <v>0</v>
@@ -5740,7 +5893,7 @@
         <v>53</v>
       </c>
       <c r="AR36" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.3">
@@ -5754,7 +5907,7 @@
         <v>79</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>46</v>
@@ -5763,7 +5916,7 @@
         <v>46318</v>
       </c>
       <c r="G37" s="5">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>47</v>
@@ -5781,16 +5934,16 @@
         <v>11</v>
       </c>
       <c r="M37" s="7">
-        <v>4186.3100000000004</v>
+        <v>4122.78</v>
       </c>
       <c r="N37" s="6">
         <v>1</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P37" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q37" s="6">
         <v>0</v>
@@ -5805,7 +5958,7 @@
         <v>52</v>
       </c>
       <c r="U37" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V37" s="11">
         <v>11</v>
@@ -5814,7 +5967,7 @@
         <v>46318</v>
       </c>
       <c r="X37" s="12">
-        <v>0.4270833</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y37" s="10">
         <v>0</v>
@@ -5874,7 +6027,7 @@
         <v>53</v>
       </c>
       <c r="AR37" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:44" x14ac:dyDescent="0.3">
@@ -5888,7 +6041,7 @@
         <v>79</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>46</v>
@@ -5897,7 +6050,7 @@
         <v>46318</v>
       </c>
       <c r="G38" s="5">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>47</v>
@@ -5915,16 +6068,16 @@
         <v>12</v>
       </c>
       <c r="M38" s="7">
-        <v>4566.88</v>
+        <v>4497.58</v>
       </c>
       <c r="N38" s="6">
         <v>1</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P38" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q38" s="6">
         <v>0</v>
@@ -5939,7 +6092,7 @@
         <v>52</v>
       </c>
       <c r="U38" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V38" s="11">
         <v>11</v>
@@ -5948,7 +6101,7 @@
         <v>46318</v>
       </c>
       <c r="X38" s="12">
-        <v>0.4270833</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y38" s="10">
         <v>0</v>
@@ -6008,7 +6161,7 @@
         <v>53</v>
       </c>
       <c r="AR38" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:44" x14ac:dyDescent="0.3">
@@ -6022,7 +6175,7 @@
         <v>79</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>46</v>
@@ -6031,7 +6184,7 @@
         <v>46318</v>
       </c>
       <c r="G39" s="5">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>47</v>
@@ -6049,16 +6202,16 @@
         <v>13</v>
       </c>
       <c r="M39" s="7">
-        <v>4947.45</v>
+        <v>4872.38</v>
       </c>
       <c r="N39" s="6">
         <v>1</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P39" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q39" s="6">
         <v>0</v>
@@ -6073,7 +6226,7 @@
         <v>52</v>
       </c>
       <c r="U39" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V39" s="11">
         <v>11</v>
@@ -6082,7 +6235,7 @@
         <v>46318</v>
       </c>
       <c r="X39" s="12">
-        <v>0.4270833</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y39" s="10">
         <v>0</v>
@@ -6142,7 +6295,7 @@
         <v>53</v>
       </c>
       <c r="AR39" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:44" x14ac:dyDescent="0.3">
@@ -6156,7 +6309,7 @@
         <v>79</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>46</v>
@@ -6165,7 +6318,7 @@
         <v>46318</v>
       </c>
       <c r="G40" s="5">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>47</v>
@@ -6183,16 +6336,16 @@
         <v>14</v>
       </c>
       <c r="M40" s="7">
-        <v>5328.03</v>
+        <v>5247.17</v>
       </c>
       <c r="N40" s="6">
         <v>1</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P40" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q40" s="6">
         <v>0</v>
@@ -6207,7 +6360,7 @@
         <v>52</v>
       </c>
       <c r="U40" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V40" s="11">
         <v>11</v>
@@ -6216,7 +6369,7 @@
         <v>46318</v>
       </c>
       <c r="X40" s="12">
-        <v>0.4270833</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y40" s="10">
         <v>0</v>
@@ -6276,7 +6429,7 @@
         <v>53</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:44" x14ac:dyDescent="0.3">
@@ -6290,7 +6443,7 @@
         <v>79</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>46</v>
@@ -6299,7 +6452,7 @@
         <v>46318</v>
       </c>
       <c r="G41" s="5">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>47</v>
@@ -6317,16 +6470,16 @@
         <v>15</v>
       </c>
       <c r="M41" s="7">
-        <v>5708.6</v>
+        <v>5621.97</v>
       </c>
       <c r="N41" s="6">
         <v>1</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P41" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q41" s="6">
         <v>0</v>
@@ -6341,7 +6494,7 @@
         <v>52</v>
       </c>
       <c r="U41" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V41" s="11">
         <v>11</v>
@@ -6350,7 +6503,7 @@
         <v>46318</v>
       </c>
       <c r="X41" s="12">
-        <v>0.4270833</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y41" s="10">
         <v>0</v>
@@ -6410,7 +6563,7 @@
         <v>53</v>
       </c>
       <c r="AR41" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:44" x14ac:dyDescent="0.3">
@@ -6424,7 +6577,7 @@
         <v>79</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>46</v>
@@ -6433,7 +6586,7 @@
         <v>46318</v>
       </c>
       <c r="G42" s="5">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>47</v>
@@ -6451,16 +6604,16 @@
         <v>16</v>
       </c>
       <c r="M42" s="7">
-        <v>6089.17</v>
+        <v>5996.77</v>
       </c>
       <c r="N42" s="6">
         <v>1</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P42" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q42" s="6">
         <v>0</v>
@@ -6475,7 +6628,7 @@
         <v>52</v>
       </c>
       <c r="U42" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V42" s="11">
         <v>11</v>
@@ -6484,7 +6637,7 @@
         <v>46318</v>
       </c>
       <c r="X42" s="12">
-        <v>0.4270833</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y42" s="10">
         <v>0</v>
@@ -6544,7 +6697,7 @@
         <v>53</v>
       </c>
       <c r="AR42" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:44" x14ac:dyDescent="0.3">
@@ -6558,7 +6711,7 @@
         <v>79</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>46</v>
@@ -6567,7 +6720,7 @@
         <v>46318</v>
       </c>
       <c r="G43" s="5">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>47</v>
@@ -6585,16 +6738,16 @@
         <v>17</v>
       </c>
       <c r="M43" s="7">
-        <v>6469.75</v>
+        <v>6371.57</v>
       </c>
       <c r="N43" s="6">
         <v>1</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P43" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q43" s="6">
         <v>0</v>
@@ -6609,7 +6762,7 @@
         <v>52</v>
       </c>
       <c r="U43" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V43" s="11">
         <v>11</v>
@@ -6618,7 +6771,7 @@
         <v>46318</v>
       </c>
       <c r="X43" s="12">
-        <v>0.4270833</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y43" s="10">
         <v>0</v>
@@ -6678,7 +6831,7 @@
         <v>53</v>
       </c>
       <c r="AR43" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:44" x14ac:dyDescent="0.3">
@@ -6692,7 +6845,7 @@
         <v>79</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>46</v>
@@ -6701,7 +6854,7 @@
         <v>46318</v>
       </c>
       <c r="G44" s="5">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>47</v>
@@ -6719,16 +6872,16 @@
         <v>18</v>
       </c>
       <c r="M44" s="7">
-        <v>6850.32</v>
+        <v>6746.37</v>
       </c>
       <c r="N44" s="6">
         <v>1</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P44" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q44" s="6">
         <v>0</v>
@@ -6743,7 +6896,7 @@
         <v>52</v>
       </c>
       <c r="U44" s="10">
-        <v>68586</v>
+        <v>68585</v>
       </c>
       <c r="V44" s="11">
         <v>11</v>
@@ -6752,7 +6905,7 @@
         <v>46318</v>
       </c>
       <c r="X44" s="12">
-        <v>0.4270833</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y44" s="10">
         <v>0</v>
@@ -6812,7 +6965,7 @@
         <v>53</v>
       </c>
       <c r="AR44" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:44" x14ac:dyDescent="0.3">
@@ -6826,7 +6979,7 @@
         <v>79</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>46</v>
@@ -6835,7 +6988,7 @@
         <v>46318</v>
       </c>
       <c r="G45" s="5">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>47</v>
@@ -6853,16 +7006,16 @@
         <v>19</v>
       </c>
       <c r="M45" s="7">
-        <v>7230.89</v>
+        <v>7121.17</v>
       </c>
       <c r="N45" s="6">
         <v>1</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P45" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q45" s="6">
         <v>0</v>
@@ -6877,7 +7030,7 @@
         <v>52</v>
       </c>
       <c r="U45" s="10">
-        <v>68404</v>
+        <v>68585</v>
       </c>
       <c r="V45" s="11">
         <v>11</v>
@@ -6886,7 +7039,7 @@
         <v>46318</v>
       </c>
       <c r="X45" s="12">
-        <v>0.43194440000000001</v>
+        <v>0.54305559999999997</v>
       </c>
       <c r="Y45" s="10">
         <v>0</v>
@@ -6946,7 +7099,7 @@
         <v>53</v>
       </c>
       <c r="AR45" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:44" x14ac:dyDescent="0.3">
@@ -6960,7 +7113,7 @@
         <v>79</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>46</v>
@@ -6969,7 +7122,7 @@
         <v>46318</v>
       </c>
       <c r="G46" s="5">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>47</v>
@@ -6987,16 +7140,16 @@
         <v>20</v>
       </c>
       <c r="M46" s="7">
-        <v>7611.47</v>
+        <v>7495.96</v>
       </c>
       <c r="N46" s="6">
         <v>1</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P46" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q46" s="6">
         <v>0</v>
@@ -7011,7 +7164,7 @@
         <v>52</v>
       </c>
       <c r="U46" s="10">
-        <v>68404</v>
+        <v>68403</v>
       </c>
       <c r="V46" s="11">
         <v>11</v>
@@ -7020,7 +7173,7 @@
         <v>46318</v>
       </c>
       <c r="X46" s="12">
-        <v>0.43194440000000001</v>
+        <v>0.56319439999999998</v>
       </c>
       <c r="Y46" s="10">
         <v>0</v>
@@ -7080,7 +7233,7 @@
         <v>53</v>
       </c>
       <c r="AR46" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:44" x14ac:dyDescent="0.3">
@@ -7094,7 +7247,7 @@
         <v>79</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>46</v>
@@ -7103,7 +7256,7 @@
         <v>46318</v>
       </c>
       <c r="G47" s="5">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>47</v>
@@ -7121,16 +7274,16 @@
         <v>21</v>
       </c>
       <c r="M47" s="7">
-        <v>7992.04</v>
+        <v>7870.76</v>
       </c>
       <c r="N47" s="6">
         <v>1</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P47" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q47" s="6">
         <v>0</v>
@@ -7145,7 +7298,7 @@
         <v>52</v>
       </c>
       <c r="U47" s="10">
-        <v>68404</v>
+        <v>68403</v>
       </c>
       <c r="V47" s="11">
         <v>11</v>
@@ -7154,7 +7307,7 @@
         <v>46318</v>
       </c>
       <c r="X47" s="12">
-        <v>0.43194440000000001</v>
+        <v>0.56319439999999998</v>
       </c>
       <c r="Y47" s="10">
         <v>0</v>
@@ -7214,7 +7367,7 @@
         <v>53</v>
       </c>
       <c r="AR47" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:44" x14ac:dyDescent="0.3">
@@ -7228,7 +7381,7 @@
         <v>79</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>46</v>
@@ -7237,7 +7390,7 @@
         <v>46318</v>
       </c>
       <c r="G48" s="5">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>47</v>
@@ -7255,16 +7408,16 @@
         <v>22</v>
       </c>
       <c r="M48" s="7">
-        <v>8372.61</v>
+        <v>8245.56</v>
       </c>
       <c r="N48" s="6">
         <v>1</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P48" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q48" s="6">
         <v>0</v>
@@ -7279,7 +7432,7 @@
         <v>52</v>
       </c>
       <c r="U48" s="10">
-        <v>68404</v>
+        <v>68403</v>
       </c>
       <c r="V48" s="11">
         <v>11</v>
@@ -7288,7 +7441,7 @@
         <v>46318</v>
       </c>
       <c r="X48" s="12">
-        <v>0.43194440000000001</v>
+        <v>0.56319439999999998</v>
       </c>
       <c r="Y48" s="10">
         <v>0</v>
@@ -7348,7 +7501,7 @@
         <v>53</v>
       </c>
       <c r="AR48" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:44" x14ac:dyDescent="0.3">
@@ -7362,7 +7515,7 @@
         <v>79</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>46</v>
@@ -7371,7 +7524,7 @@
         <v>46318</v>
       </c>
       <c r="G49" s="5">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>47</v>
@@ -7389,16 +7542,16 @@
         <v>23</v>
       </c>
       <c r="M49" s="7">
-        <v>8753.19</v>
+        <v>8620.36</v>
       </c>
       <c r="N49" s="6">
         <v>1</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P49" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q49" s="6">
         <v>0</v>
@@ -7413,7 +7566,7 @@
         <v>52</v>
       </c>
       <c r="U49" s="10">
-        <v>68404</v>
+        <v>68403</v>
       </c>
       <c r="V49" s="11">
         <v>11</v>
@@ -7422,7 +7575,7 @@
         <v>46318</v>
       </c>
       <c r="X49" s="12">
-        <v>0.43194440000000001</v>
+        <v>0.56319439999999998</v>
       </c>
       <c r="Y49" s="10">
         <v>0</v>
@@ -7482,7 +7635,7 @@
         <v>53</v>
       </c>
       <c r="AR49" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:44" x14ac:dyDescent="0.3">
@@ -7496,7 +7649,7 @@
         <v>79</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>46</v>
@@ -7505,7 +7658,7 @@
         <v>46318</v>
       </c>
       <c r="G50" s="5">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>47</v>
@@ -7523,16 +7676,16 @@
         <v>24</v>
       </c>
       <c r="M50" s="7">
-        <v>9133.76</v>
+        <v>8995.16</v>
       </c>
       <c r="N50" s="6">
         <v>1</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P50" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q50" s="6">
         <v>0</v>
@@ -7547,7 +7700,7 @@
         <v>52</v>
       </c>
       <c r="U50" s="10">
-        <v>68404</v>
+        <v>68403</v>
       </c>
       <c r="V50" s="11">
         <v>11</v>
@@ -7556,7 +7709,7 @@
         <v>46318</v>
       </c>
       <c r="X50" s="12">
-        <v>0.43194440000000001</v>
+        <v>0.56319439999999998</v>
       </c>
       <c r="Y50" s="10">
         <v>0</v>
@@ -7616,7 +7769,7 @@
         <v>53</v>
       </c>
       <c r="AR50" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:44" x14ac:dyDescent="0.3">
@@ -7630,7 +7783,7 @@
         <v>79</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>46</v>
@@ -7639,7 +7792,7 @@
         <v>46318</v>
       </c>
       <c r="G51" s="5">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>47</v>
@@ -7657,16 +7810,16 @@
         <v>25</v>
       </c>
       <c r="M51" s="7">
-        <v>9514.33</v>
+        <v>9369.9500000000007</v>
       </c>
       <c r="N51" s="6">
         <v>1</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P51" s="8">
-        <v>380.57</v>
+        <v>374.8</v>
       </c>
       <c r="Q51" s="6">
         <v>0</v>
@@ -7681,7 +7834,7 @@
         <v>52</v>
       </c>
       <c r="U51" s="10">
-        <v>68586</v>
+        <v>68403</v>
       </c>
       <c r="V51" s="11">
         <v>11</v>
@@ -7690,7 +7843,7 @@
         <v>46318</v>
       </c>
       <c r="X51" s="12">
-        <v>0.43402780000000002</v>
+        <v>0.56319439999999998</v>
       </c>
       <c r="Y51" s="10">
         <v>0</v>
@@ -7750,7 +7903,6573 @@
         <v>53</v>
       </c>
       <c r="AR51" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>1</v>
+      </c>
+      <c r="B52" s="2">
+        <v>2</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F52" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G52" s="5">
+        <v>95</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L52" s="6">
+        <v>26</v>
+      </c>
+      <c r="M52" s="7">
+        <v>9744.75</v>
+      </c>
+      <c r="N52" s="6">
+        <v>1</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="P52" s="8">
+        <v>374.8</v>
+      </c>
+      <c r="Q52" s="6">
+        <v>0</v>
+      </c>
+      <c r="R52" s="7">
+        <v>0</v>
+      </c>
+      <c r="S52" s="9">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U52" s="10">
+        <v>68403</v>
+      </c>
+      <c r="V52" s="11">
+        <v>11</v>
+      </c>
+      <c r="W52" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X52" s="12">
+        <v>0.56319439999999998</v>
+      </c>
+      <c r="Y52" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG52" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI52" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ52" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK52" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM52" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR52" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>1</v>
+      </c>
+      <c r="B53" s="2">
+        <v>2</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F53" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G53" s="5">
+        <v>96</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L53" s="6">
+        <v>27</v>
+      </c>
+      <c r="M53" s="7">
+        <v>10119.549999999999</v>
+      </c>
+      <c r="N53" s="6">
+        <v>1</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="P53" s="8">
+        <v>374.8</v>
+      </c>
+      <c r="Q53" s="6">
+        <v>0</v>
+      </c>
+      <c r="R53" s="7">
+        <v>0</v>
+      </c>
+      <c r="S53" s="9">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U53" s="10">
+        <v>68403</v>
+      </c>
+      <c r="V53" s="11">
+        <v>11</v>
+      </c>
+      <c r="W53" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X53" s="12">
+        <v>0.56319439999999998</v>
+      </c>
+      <c r="Y53" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG53" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI53" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ53" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK53" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR53" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="54" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>1</v>
+      </c>
+      <c r="B54" s="2">
+        <v>2</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F54" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G54" s="5">
+        <v>97</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L54" s="6">
+        <v>28</v>
+      </c>
+      <c r="M54" s="7">
+        <v>10494.35</v>
+      </c>
+      <c r="N54" s="6">
+        <v>1</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="P54" s="8">
+        <v>374.8</v>
+      </c>
+      <c r="Q54" s="6">
+        <v>0</v>
+      </c>
+      <c r="R54" s="7">
+        <v>0</v>
+      </c>
+      <c r="S54" s="9">
+        <v>0</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U54" s="10">
+        <v>68403</v>
+      </c>
+      <c r="V54" s="11">
+        <v>11</v>
+      </c>
+      <c r="W54" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X54" s="12">
+        <v>0.56319439999999998</v>
+      </c>
+      <c r="Y54" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI54" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ54" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK54" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL54" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM54" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR54" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>1</v>
+      </c>
+      <c r="B55" s="2">
+        <v>2</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F55" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G55" s="5">
+        <v>98</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L55" s="6">
+        <v>29</v>
+      </c>
+      <c r="M55" s="7">
+        <v>10869.15</v>
+      </c>
+      <c r="N55" s="6">
+        <v>1</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="P55" s="8">
+        <v>374.8</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>0</v>
+      </c>
+      <c r="R55" s="7">
+        <v>0</v>
+      </c>
+      <c r="S55" s="9">
+        <v>0</v>
+      </c>
+      <c r="T55" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U55" s="10">
+        <v>68403</v>
+      </c>
+      <c r="V55" s="11">
+        <v>11</v>
+      </c>
+      <c r="W55" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X55" s="12">
+        <v>0.56319439999999998</v>
+      </c>
+      <c r="Y55" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI55" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ55" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK55" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL55" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM55" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR55" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>1</v>
+      </c>
+      <c r="B56" s="2">
+        <v>2</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F56" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G56" s="5">
+        <v>99</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L56" s="6">
+        <v>30</v>
+      </c>
+      <c r="M56" s="7">
+        <v>11243.95</v>
+      </c>
+      <c r="N56" s="6">
+        <v>1</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="P56" s="8">
+        <v>374.8</v>
+      </c>
+      <c r="Q56" s="6">
+        <v>0</v>
+      </c>
+      <c r="R56" s="7">
+        <v>0</v>
+      </c>
+      <c r="S56" s="9">
+        <v>0</v>
+      </c>
+      <c r="T56" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U56" s="10">
+        <v>68403</v>
+      </c>
+      <c r="V56" s="11">
+        <v>11</v>
+      </c>
+      <c r="W56" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X56" s="12">
+        <v>0.56319439999999998</v>
+      </c>
+      <c r="Y56" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI56" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ56" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK56" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL56" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM56" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR56" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>1</v>
+      </c>
+      <c r="B57" s="2">
+        <v>2</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F57" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G57" s="5">
+        <v>100</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L57" s="6">
+        <v>31</v>
+      </c>
+      <c r="M57" s="7">
+        <v>11618.74</v>
+      </c>
+      <c r="N57" s="6">
+        <v>1</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="P57" s="8">
+        <v>374.8</v>
+      </c>
+      <c r="Q57" s="6">
+        <v>0</v>
+      </c>
+      <c r="R57" s="7">
+        <v>0</v>
+      </c>
+      <c r="S57" s="9">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U57" s="10">
+        <v>68403</v>
+      </c>
+      <c r="V57" s="11">
+        <v>11</v>
+      </c>
+      <c r="W57" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X57" s="12">
+        <v>0.56319439999999998</v>
+      </c>
+      <c r="Y57" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG57" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI57" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ57" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK57" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL57" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM57" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR57" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>1</v>
+      </c>
+      <c r="B58" s="2">
+        <v>2</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F58" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G58" s="5">
+        <v>101</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L58" s="6">
+        <v>32</v>
+      </c>
+      <c r="M58" s="7">
+        <v>11993.54</v>
+      </c>
+      <c r="N58" s="6">
+        <v>1</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="P58" s="8">
+        <v>374.8</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0</v>
+      </c>
+      <c r="R58" s="7">
+        <v>0</v>
+      </c>
+      <c r="S58" s="9">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U58" s="10">
+        <v>68403</v>
+      </c>
+      <c r="V58" s="11">
+        <v>11</v>
+      </c>
+      <c r="W58" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X58" s="12">
+        <v>0.56319439999999998</v>
+      </c>
+      <c r="Y58" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI58" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ58" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK58" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR58" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>1</v>
+      </c>
+      <c r="B59" s="2">
+        <v>2</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F59" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G59" s="5">
+        <v>102</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L59" s="6">
+        <v>33</v>
+      </c>
+      <c r="M59" s="7">
+        <v>12368.34</v>
+      </c>
+      <c r="N59" s="6">
+        <v>1</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="P59" s="8">
+        <v>374.8</v>
+      </c>
+      <c r="Q59" s="6">
+        <v>0</v>
+      </c>
+      <c r="R59" s="7">
+        <v>0</v>
+      </c>
+      <c r="S59" s="9">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U59" s="10">
+        <v>68403</v>
+      </c>
+      <c r="V59" s="11">
+        <v>11</v>
+      </c>
+      <c r="W59" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X59" s="12">
+        <v>0.56319439999999998</v>
+      </c>
+      <c r="Y59" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG59" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI59" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ59" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK59" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL59" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM59" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR59" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="60" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>1</v>
+      </c>
+      <c r="B60" s="2">
+        <v>2</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F60" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G60" s="5">
+        <v>103</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L60" s="6">
+        <v>34</v>
+      </c>
+      <c r="M60" s="7">
+        <v>12743.14</v>
+      </c>
+      <c r="N60" s="6">
+        <v>1</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="P60" s="8">
+        <v>374.8</v>
+      </c>
+      <c r="Q60" s="6">
+        <v>0</v>
+      </c>
+      <c r="R60" s="7">
+        <v>0</v>
+      </c>
+      <c r="S60" s="9">
+        <v>0</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U60" s="10">
+        <v>68403</v>
+      </c>
+      <c r="V60" s="11">
+        <v>11</v>
+      </c>
+      <c r="W60" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X60" s="12">
+        <v>0.56319439999999998</v>
+      </c>
+      <c r="Y60" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI60" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ60" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK60" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL60" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM60" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR60" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>1</v>
+      </c>
+      <c r="B61" s="2">
+        <v>2</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F61" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G61" s="5">
+        <v>1</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L61" s="6">
+        <v>0</v>
+      </c>
+      <c r="M61" s="7">
+        <v>0</v>
+      </c>
+      <c r="N61" s="6">
+        <v>1</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P61" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q61" s="6">
+        <v>0</v>
+      </c>
+      <c r="R61" s="7">
+        <v>0</v>
+      </c>
+      <c r="S61" s="9">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U61" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V61" s="11">
+        <v>11</v>
+      </c>
+      <c r="W61" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X61" s="12">
+        <v>0.35763889999999998</v>
+      </c>
+      <c r="Y61" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG61" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI61" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ61" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK61" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR61" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="62" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>1</v>
+      </c>
+      <c r="B62" s="2">
+        <v>2</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F62" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G62" s="5">
+        <v>2</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L62" s="6">
+        <v>1</v>
+      </c>
+      <c r="M62" s="7">
+        <v>380.57</v>
+      </c>
+      <c r="N62" s="6">
+        <v>1</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P62" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>0</v>
+      </c>
+      <c r="R62" s="7">
+        <v>0</v>
+      </c>
+      <c r="S62" s="9">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U62" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V62" s="11">
+        <v>11</v>
+      </c>
+      <c r="W62" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X62" s="12">
+        <v>0.35763889999999998</v>
+      </c>
+      <c r="Y62" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI62" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ62" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK62" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL62" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM62" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR62" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="63" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>1</v>
+      </c>
+      <c r="B63" s="2">
+        <v>2</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F63" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G63" s="5">
+        <v>3</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L63" s="6">
+        <v>2</v>
+      </c>
+      <c r="M63" s="7">
+        <v>761.15</v>
+      </c>
+      <c r="N63" s="6">
+        <v>1</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P63" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>0</v>
+      </c>
+      <c r="R63" s="7">
+        <v>0</v>
+      </c>
+      <c r="S63" s="9">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U63" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V63" s="11">
+        <v>11</v>
+      </c>
+      <c r="W63" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X63" s="12">
+        <v>0.35763889999999998</v>
+      </c>
+      <c r="Y63" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI63" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ63" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK63" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR63" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="64" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>1</v>
+      </c>
+      <c r="B64" s="2">
+        <v>2</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F64" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G64" s="5">
+        <v>4</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L64" s="6">
+        <v>3</v>
+      </c>
+      <c r="M64" s="7">
+        <v>1141.72</v>
+      </c>
+      <c r="N64" s="6">
+        <v>1</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P64" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q64" s="6">
+        <v>0</v>
+      </c>
+      <c r="R64" s="7">
+        <v>0</v>
+      </c>
+      <c r="S64" s="9">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U64" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V64" s="11">
+        <v>11</v>
+      </c>
+      <c r="W64" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X64" s="12">
+        <v>0.35763889999999998</v>
+      </c>
+      <c r="Y64" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI64" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ64" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK64" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR64" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="65" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>1</v>
+      </c>
+      <c r="B65" s="2">
+        <v>2</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F65" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G65" s="5">
+        <v>5</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L65" s="6">
+        <v>4</v>
+      </c>
+      <c r="M65" s="7">
+        <v>1522.29</v>
+      </c>
+      <c r="N65" s="6">
+        <v>1</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P65" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q65" s="6">
+        <v>0</v>
+      </c>
+      <c r="R65" s="7">
+        <v>0</v>
+      </c>
+      <c r="S65" s="9">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U65" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V65" s="11">
+        <v>11</v>
+      </c>
+      <c r="W65" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X65" s="12">
+        <v>0.35763889999999998</v>
+      </c>
+      <c r="Y65" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG65" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI65" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ65" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK65" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR65" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="66" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>1</v>
+      </c>
+      <c r="B66" s="2">
+        <v>2</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F66" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G66" s="5">
+        <v>6</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L66" s="6">
+        <v>5</v>
+      </c>
+      <c r="M66" s="7">
+        <v>1902.87</v>
+      </c>
+      <c r="N66" s="6">
+        <v>1</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P66" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q66" s="6">
+        <v>0</v>
+      </c>
+      <c r="R66" s="7">
+        <v>0</v>
+      </c>
+      <c r="S66" s="9">
+        <v>0</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U66" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V66" s="11">
+        <v>11</v>
+      </c>
+      <c r="W66" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X66" s="12">
+        <v>0.3854167</v>
+      </c>
+      <c r="Y66" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB66" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI66" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ66" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK66" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL66" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM66" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR66" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="67" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>1</v>
+      </c>
+      <c r="B67" s="2">
+        <v>2</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F67" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G67" s="5">
+        <v>7</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L67" s="6">
+        <v>6</v>
+      </c>
+      <c r="M67" s="7">
+        <v>2283.44</v>
+      </c>
+      <c r="N67" s="6">
+        <v>1</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P67" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q67" s="6">
+        <v>0</v>
+      </c>
+      <c r="R67" s="7">
+        <v>0</v>
+      </c>
+      <c r="S67" s="9">
+        <v>0</v>
+      </c>
+      <c r="T67" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U67" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V67" s="11">
+        <v>11</v>
+      </c>
+      <c r="W67" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X67" s="12">
+        <v>0.3854167</v>
+      </c>
+      <c r="Y67" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB67" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG67" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI67" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ67" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK67" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL67" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM67" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR67" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="68" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>1</v>
+      </c>
+      <c r="B68" s="2">
+        <v>2</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F68" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G68" s="5">
+        <v>8</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L68" s="6">
+        <v>7</v>
+      </c>
+      <c r="M68" s="7">
+        <v>2664.01</v>
+      </c>
+      <c r="N68" s="6">
+        <v>1</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P68" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q68" s="6">
+        <v>0</v>
+      </c>
+      <c r="R68" s="7">
+        <v>0</v>
+      </c>
+      <c r="S68" s="9">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U68" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V68" s="11">
+        <v>11</v>
+      </c>
+      <c r="W68" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X68" s="12">
+        <v>0.3854167</v>
+      </c>
+      <c r="Y68" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI68" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ68" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK68" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR68" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="69" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>1</v>
+      </c>
+      <c r="B69" s="2">
+        <v>2</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F69" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G69" s="5">
+        <v>9</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L69" s="6">
+        <v>8</v>
+      </c>
+      <c r="M69" s="7">
+        <v>3044.59</v>
+      </c>
+      <c r="N69" s="6">
+        <v>1</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P69" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q69" s="6">
+        <v>0</v>
+      </c>
+      <c r="R69" s="7">
+        <v>0</v>
+      </c>
+      <c r="S69" s="9">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U69" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V69" s="11">
+        <v>11</v>
+      </c>
+      <c r="W69" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X69" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y69" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG69" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI69" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ69" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK69" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR69" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="70" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>1</v>
+      </c>
+      <c r="B70" s="2">
+        <v>2</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F70" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G70" s="5">
+        <v>10</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L70" s="6">
+        <v>9</v>
+      </c>
+      <c r="M70" s="7">
+        <v>3425.16</v>
+      </c>
+      <c r="N70" s="6">
+        <v>1</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P70" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q70" s="6">
+        <v>0</v>
+      </c>
+      <c r="R70" s="7">
+        <v>0</v>
+      </c>
+      <c r="S70" s="9">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U70" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V70" s="11">
+        <v>11</v>
+      </c>
+      <c r="W70" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X70" s="12">
+        <v>0.3986111</v>
+      </c>
+      <c r="Y70" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI70" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ70" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK70" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR70" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="71" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>1</v>
+      </c>
+      <c r="B71" s="2">
+        <v>2</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F71" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G71" s="5">
+        <v>22</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L71" s="6">
+        <v>10</v>
+      </c>
+      <c r="M71" s="7">
+        <v>3805.73</v>
+      </c>
+      <c r="N71" s="6">
+        <v>1</v>
+      </c>
+      <c r="O71" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P71" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>0</v>
+      </c>
+      <c r="R71" s="7">
+        <v>0</v>
+      </c>
+      <c r="S71" s="9">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U71" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V71" s="11">
+        <v>11</v>
+      </c>
+      <c r="W71" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X71" s="12">
+        <v>0.4270833</v>
+      </c>
+      <c r="Y71" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG71" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI71" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ71" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK71" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR71" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="72" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>1</v>
+      </c>
+      <c r="B72" s="2">
+        <v>2</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F72" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G72" s="5">
+        <v>23</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L72" s="6">
+        <v>11</v>
+      </c>
+      <c r="M72" s="7">
+        <v>4186.3100000000004</v>
+      </c>
+      <c r="N72" s="6">
+        <v>1</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P72" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q72" s="6">
+        <v>0</v>
+      </c>
+      <c r="R72" s="7">
+        <v>0</v>
+      </c>
+      <c r="S72" s="9">
+        <v>0</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U72" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V72" s="11">
+        <v>11</v>
+      </c>
+      <c r="W72" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X72" s="12">
+        <v>0.4270833</v>
+      </c>
+      <c r="Y72" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG72" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI72" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ72" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK72" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL72" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM72" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR72" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="73" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>1</v>
+      </c>
+      <c r="B73" s="2">
+        <v>2</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F73" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G73" s="5">
+        <v>24</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L73" s="6">
+        <v>12</v>
+      </c>
+      <c r="M73" s="7">
+        <v>4566.88</v>
+      </c>
+      <c r="N73" s="6">
+        <v>1</v>
+      </c>
+      <c r="O73" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P73" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q73" s="6">
+        <v>0</v>
+      </c>
+      <c r="R73" s="7">
+        <v>0</v>
+      </c>
+      <c r="S73" s="9">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U73" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V73" s="11">
+        <v>11</v>
+      </c>
+      <c r="W73" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X73" s="12">
+        <v>0.4270833</v>
+      </c>
+      <c r="Y73" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG73" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI73" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ73" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK73" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR73" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="74" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>1</v>
+      </c>
+      <c r="B74" s="2">
+        <v>2</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F74" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G74" s="5">
+        <v>25</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L74" s="6">
+        <v>13</v>
+      </c>
+      <c r="M74" s="7">
+        <v>4947.45</v>
+      </c>
+      <c r="N74" s="6">
+        <v>1</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P74" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q74" s="6">
+        <v>0</v>
+      </c>
+      <c r="R74" s="7">
+        <v>0</v>
+      </c>
+      <c r="S74" s="9">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U74" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V74" s="11">
+        <v>11</v>
+      </c>
+      <c r="W74" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X74" s="12">
+        <v>0.4270833</v>
+      </c>
+      <c r="Y74" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG74" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI74" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ74" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK74" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR74" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="75" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>1</v>
+      </c>
+      <c r="B75" s="2">
+        <v>2</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F75" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G75" s="5">
+        <v>26</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L75" s="6">
+        <v>14</v>
+      </c>
+      <c r="M75" s="7">
+        <v>5328.03</v>
+      </c>
+      <c r="N75" s="6">
+        <v>1</v>
+      </c>
+      <c r="O75" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P75" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>0</v>
+      </c>
+      <c r="R75" s="7">
+        <v>0</v>
+      </c>
+      <c r="S75" s="9">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U75" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V75" s="11">
+        <v>11</v>
+      </c>
+      <c r="W75" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X75" s="12">
+        <v>0.4270833</v>
+      </c>
+      <c r="Y75" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG75" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI75" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ75" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK75" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR75" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="76" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>1</v>
+      </c>
+      <c r="B76" s="2">
+        <v>2</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F76" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G76" s="5">
+        <v>27</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L76" s="6">
+        <v>15</v>
+      </c>
+      <c r="M76" s="7">
+        <v>5708.6</v>
+      </c>
+      <c r="N76" s="6">
+        <v>1</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P76" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>0</v>
+      </c>
+      <c r="R76" s="7">
+        <v>0</v>
+      </c>
+      <c r="S76" s="9">
+        <v>0</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U76" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V76" s="11">
+        <v>11</v>
+      </c>
+      <c r="W76" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X76" s="12">
+        <v>0.4270833</v>
+      </c>
+      <c r="Y76" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG76" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI76" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ76" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK76" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL76" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR76" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="77" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>1</v>
+      </c>
+      <c r="B77" s="2">
+        <v>2</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F77" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G77" s="5">
+        <v>28</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L77" s="6">
+        <v>16</v>
+      </c>
+      <c r="M77" s="7">
+        <v>6089.17</v>
+      </c>
+      <c r="N77" s="6">
+        <v>1</v>
+      </c>
+      <c r="O77" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P77" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q77" s="6">
+        <v>0</v>
+      </c>
+      <c r="R77" s="7">
+        <v>0</v>
+      </c>
+      <c r="S77" s="9">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U77" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V77" s="11">
+        <v>11</v>
+      </c>
+      <c r="W77" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X77" s="12">
+        <v>0.4270833</v>
+      </c>
+      <c r="Y77" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG77" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI77" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ77" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK77" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR77" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="78" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>1</v>
+      </c>
+      <c r="B78" s="2">
+        <v>2</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F78" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G78" s="5">
+        <v>29</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L78" s="6">
+        <v>17</v>
+      </c>
+      <c r="M78" s="7">
+        <v>6469.75</v>
+      </c>
+      <c r="N78" s="6">
+        <v>1</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P78" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q78" s="6">
+        <v>0</v>
+      </c>
+      <c r="R78" s="7">
+        <v>0</v>
+      </c>
+      <c r="S78" s="9">
+        <v>0</v>
+      </c>
+      <c r="T78" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U78" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V78" s="11">
+        <v>11</v>
+      </c>
+      <c r="W78" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X78" s="12">
+        <v>0.4270833</v>
+      </c>
+      <c r="Y78" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG78" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI78" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ78" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK78" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL78" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM78" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR78" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="79" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>1</v>
+      </c>
+      <c r="B79" s="2">
+        <v>2</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F79" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G79" s="5">
+        <v>30</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L79" s="6">
+        <v>18</v>
+      </c>
+      <c r="M79" s="7">
+        <v>6850.32</v>
+      </c>
+      <c r="N79" s="6">
+        <v>1</v>
+      </c>
+      <c r="O79" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P79" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q79" s="6">
+        <v>0</v>
+      </c>
+      <c r="R79" s="7">
+        <v>0</v>
+      </c>
+      <c r="S79" s="9">
+        <v>0</v>
+      </c>
+      <c r="T79" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U79" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V79" s="11">
+        <v>11</v>
+      </c>
+      <c r="W79" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X79" s="12">
+        <v>0.4270833</v>
+      </c>
+      <c r="Y79" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG79" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI79" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ79" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK79" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL79" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM79" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR79" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="80" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>1</v>
+      </c>
+      <c r="B80" s="2">
+        <v>2</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F80" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G80" s="5">
+        <v>31</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L80" s="6">
+        <v>19</v>
+      </c>
+      <c r="M80" s="7">
+        <v>7230.89</v>
+      </c>
+      <c r="N80" s="6">
+        <v>1</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P80" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q80" s="6">
+        <v>0</v>
+      </c>
+      <c r="R80" s="7">
+        <v>0</v>
+      </c>
+      <c r="S80" s="9">
+        <v>0</v>
+      </c>
+      <c r="T80" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U80" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V80" s="11">
+        <v>11</v>
+      </c>
+      <c r="W80" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X80" s="12">
+        <v>0.43194440000000001</v>
+      </c>
+      <c r="Y80" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG80" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI80" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ80" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK80" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL80" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM80" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ80" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR80" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="81" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>1</v>
+      </c>
+      <c r="B81" s="2">
+        <v>2</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F81" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G81" s="5">
+        <v>32</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L81" s="6">
+        <v>20</v>
+      </c>
+      <c r="M81" s="7">
+        <v>7611.47</v>
+      </c>
+      <c r="N81" s="6">
+        <v>1</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P81" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q81" s="6">
+        <v>0</v>
+      </c>
+      <c r="R81" s="7">
+        <v>0</v>
+      </c>
+      <c r="S81" s="9">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U81" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V81" s="11">
+        <v>11</v>
+      </c>
+      <c r="W81" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X81" s="12">
+        <v>0.43194440000000001</v>
+      </c>
+      <c r="Y81" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG81" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI81" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ81" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK81" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL81" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM81" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR81" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="82" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>1</v>
+      </c>
+      <c r="B82" s="2">
+        <v>2</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F82" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G82" s="5">
+        <v>33</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L82" s="6">
+        <v>21</v>
+      </c>
+      <c r="M82" s="7">
+        <v>7992.04</v>
+      </c>
+      <c r="N82" s="6">
+        <v>1</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P82" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q82" s="6">
+        <v>0</v>
+      </c>
+      <c r="R82" s="7">
+        <v>0</v>
+      </c>
+      <c r="S82" s="9">
+        <v>0</v>
+      </c>
+      <c r="T82" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U82" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V82" s="11">
+        <v>11</v>
+      </c>
+      <c r="W82" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X82" s="12">
+        <v>0.43194440000000001</v>
+      </c>
+      <c r="Y82" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA82" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB82" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD82" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG82" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH82" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI82" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ82" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK82" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL82" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM82" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN82" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO82" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP82" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ82" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR82" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="83" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>1</v>
+      </c>
+      <c r="B83" s="2">
+        <v>2</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F83" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G83" s="5">
+        <v>34</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L83" s="6">
+        <v>22</v>
+      </c>
+      <c r="M83" s="7">
+        <v>8372.61</v>
+      </c>
+      <c r="N83" s="6">
+        <v>1</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P83" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q83" s="6">
+        <v>0</v>
+      </c>
+      <c r="R83" s="7">
+        <v>0</v>
+      </c>
+      <c r="S83" s="9">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U83" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V83" s="11">
+        <v>11</v>
+      </c>
+      <c r="W83" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X83" s="12">
+        <v>0.43194440000000001</v>
+      </c>
+      <c r="Y83" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG83" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI83" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ83" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK83" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL83" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM83" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN83" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO83" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP83" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ83" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR83" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="84" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>1</v>
+      </c>
+      <c r="B84" s="2">
+        <v>2</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F84" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G84" s="5">
+        <v>35</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L84" s="6">
+        <v>23</v>
+      </c>
+      <c r="M84" s="7">
+        <v>8753.19</v>
+      </c>
+      <c r="N84" s="6">
+        <v>1</v>
+      </c>
+      <c r="O84" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P84" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q84" s="6">
+        <v>0</v>
+      </c>
+      <c r="R84" s="7">
+        <v>0</v>
+      </c>
+      <c r="S84" s="9">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U84" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V84" s="11">
+        <v>11</v>
+      </c>
+      <c r="W84" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X84" s="12">
+        <v>0.43194440000000001</v>
+      </c>
+      <c r="Y84" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG84" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI84" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ84" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK84" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN84" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO84" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP84" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ84" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR84" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="85" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>1</v>
+      </c>
+      <c r="B85" s="2">
+        <v>2</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F85" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G85" s="5">
+        <v>36</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L85" s="6">
+        <v>24</v>
+      </c>
+      <c r="M85" s="7">
+        <v>9133.76</v>
+      </c>
+      <c r="N85" s="6">
+        <v>1</v>
+      </c>
+      <c r="O85" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P85" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q85" s="6">
+        <v>0</v>
+      </c>
+      <c r="R85" s="7">
+        <v>0</v>
+      </c>
+      <c r="S85" s="9">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U85" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V85" s="11">
+        <v>11</v>
+      </c>
+      <c r="W85" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X85" s="12">
+        <v>0.43194440000000001</v>
+      </c>
+      <c r="Y85" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG85" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI85" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ85" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK85" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN85" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO85" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP85" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ85" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR85" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="86" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>1</v>
+      </c>
+      <c r="B86" s="2">
+        <v>2</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F86" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G86" s="5">
+        <v>37</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L86" s="6">
+        <v>25</v>
+      </c>
+      <c r="M86" s="7">
+        <v>9514.33</v>
+      </c>
+      <c r="N86" s="6">
+        <v>1</v>
+      </c>
+      <c r="O86" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P86" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q86" s="6">
+        <v>0</v>
+      </c>
+      <c r="R86" s="7">
+        <v>0</v>
+      </c>
+      <c r="S86" s="9">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U86" s="10">
+        <v>68586</v>
+      </c>
+      <c r="V86" s="11">
+        <v>11</v>
+      </c>
+      <c r="W86" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X86" s="12">
+        <v>0.43402780000000002</v>
+      </c>
+      <c r="Y86" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG86" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI86" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ86" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK86" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN86" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO86" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP86" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ86" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR86" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="87" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>1</v>
+      </c>
+      <c r="B87" s="2">
+        <v>2</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F87" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G87" s="5">
+        <v>73</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L87" s="6">
+        <v>26</v>
+      </c>
+      <c r="M87" s="7">
+        <v>9894.91</v>
+      </c>
+      <c r="N87" s="6">
+        <v>1</v>
+      </c>
+      <c r="O87" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P87" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q87" s="6">
+        <v>0</v>
+      </c>
+      <c r="R87" s="7">
+        <v>0</v>
+      </c>
+      <c r="S87" s="9">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U87" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V87" s="11">
+        <v>11</v>
+      </c>
+      <c r="W87" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X87" s="12">
+        <v>0.47291670000000002</v>
+      </c>
+      <c r="Y87" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG87" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI87" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ87" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK87" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN87" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO87" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP87" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ87" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR87" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="88" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>1</v>
+      </c>
+      <c r="B88" s="2">
+        <v>2</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F88" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G88" s="5">
+        <v>74</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L88" s="6">
+        <v>27</v>
+      </c>
+      <c r="M88" s="7">
+        <v>10275.48</v>
+      </c>
+      <c r="N88" s="6">
+        <v>1</v>
+      </c>
+      <c r="O88" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P88" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q88" s="6">
+        <v>0</v>
+      </c>
+      <c r="R88" s="7">
+        <v>0</v>
+      </c>
+      <c r="S88" s="9">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U88" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V88" s="11">
+        <v>11</v>
+      </c>
+      <c r="W88" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X88" s="12">
+        <v>0.47291670000000002</v>
+      </c>
+      <c r="Y88" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG88" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI88" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ88" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK88" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN88" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO88" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP88" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ88" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR88" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="89" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>1</v>
+      </c>
+      <c r="B89" s="2">
+        <v>2</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F89" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G89" s="5">
+        <v>75</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L89" s="6">
+        <v>28</v>
+      </c>
+      <c r="M89" s="7">
+        <v>10656.05</v>
+      </c>
+      <c r="N89" s="6">
+        <v>1</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P89" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>0</v>
+      </c>
+      <c r="R89" s="7">
+        <v>0</v>
+      </c>
+      <c r="S89" s="9">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U89" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V89" s="11">
+        <v>11</v>
+      </c>
+      <c r="W89" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X89" s="12">
+        <v>0.47291670000000002</v>
+      </c>
+      <c r="Y89" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI89" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ89" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK89" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM89" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN89" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO89" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP89" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ89" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR89" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="90" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>1</v>
+      </c>
+      <c r="B90" s="2">
+        <v>2</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F90" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G90" s="5">
+        <v>76</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L90" s="6">
+        <v>29</v>
+      </c>
+      <c r="M90" s="7">
+        <v>11036.63</v>
+      </c>
+      <c r="N90" s="6">
+        <v>1</v>
+      </c>
+      <c r="O90" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P90" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q90" s="6">
+        <v>0</v>
+      </c>
+      <c r="R90" s="7">
+        <v>0</v>
+      </c>
+      <c r="S90" s="9">
+        <v>0</v>
+      </c>
+      <c r="T90" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U90" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V90" s="11">
+        <v>11</v>
+      </c>
+      <c r="W90" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X90" s="12">
+        <v>0.47291670000000002</v>
+      </c>
+      <c r="Y90" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF90" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG90" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI90" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ90" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK90" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM90" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN90" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO90" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP90" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ90" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR90" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="91" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>1</v>
+      </c>
+      <c r="B91" s="2">
+        <v>2</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F91" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G91" s="5">
+        <v>77</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L91" s="6">
+        <v>30</v>
+      </c>
+      <c r="M91" s="7">
+        <v>11417.2</v>
+      </c>
+      <c r="N91" s="6">
+        <v>1</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P91" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q91" s="6">
+        <v>0</v>
+      </c>
+      <c r="R91" s="7">
+        <v>0</v>
+      </c>
+      <c r="S91" s="9">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U91" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V91" s="11">
+        <v>11</v>
+      </c>
+      <c r="W91" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X91" s="12">
+        <v>0.47291670000000002</v>
+      </c>
+      <c r="Y91" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG91" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI91" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ91" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK91" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM91" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN91" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO91" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP91" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ91" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR91" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="92" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>1</v>
+      </c>
+      <c r="B92" s="2">
+        <v>2</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F92" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G92" s="5">
+        <v>78</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L92" s="6">
+        <v>31</v>
+      </c>
+      <c r="M92" s="7">
+        <v>11797.77</v>
+      </c>
+      <c r="N92" s="6">
+        <v>1</v>
+      </c>
+      <c r="O92" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P92" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q92" s="6">
+        <v>0</v>
+      </c>
+      <c r="R92" s="7">
+        <v>0</v>
+      </c>
+      <c r="S92" s="9">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U92" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V92" s="11">
+        <v>11</v>
+      </c>
+      <c r="W92" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X92" s="12">
+        <v>0.47291670000000002</v>
+      </c>
+      <c r="Y92" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG92" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI92" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ92" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK92" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN92" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO92" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP92" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ92" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR92" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="93" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>1</v>
+      </c>
+      <c r="B93" s="2">
+        <v>2</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F93" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G93" s="5">
+        <v>79</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K93" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L93" s="6">
+        <v>32</v>
+      </c>
+      <c r="M93" s="7">
+        <v>12178.35</v>
+      </c>
+      <c r="N93" s="6">
+        <v>1</v>
+      </c>
+      <c r="O93" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P93" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q93" s="6">
+        <v>0</v>
+      </c>
+      <c r="R93" s="7">
+        <v>0</v>
+      </c>
+      <c r="S93" s="9">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U93" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V93" s="11">
+        <v>11</v>
+      </c>
+      <c r="W93" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X93" s="12">
+        <v>0.47291670000000002</v>
+      </c>
+      <c r="Y93" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG93" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI93" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ93" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK93" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM93" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN93" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO93" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP93" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ93" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR93" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="94" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>1</v>
+      </c>
+      <c r="B94" s="2">
+        <v>2</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F94" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G94" s="5">
+        <v>80</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L94" s="6">
+        <v>33</v>
+      </c>
+      <c r="M94" s="7">
+        <v>12558.92</v>
+      </c>
+      <c r="N94" s="6">
+        <v>1</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P94" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q94" s="6">
+        <v>0</v>
+      </c>
+      <c r="R94" s="7">
+        <v>0</v>
+      </c>
+      <c r="S94" s="9">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U94" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V94" s="11">
+        <v>11</v>
+      </c>
+      <c r="W94" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X94" s="12">
+        <v>0.47291670000000002</v>
+      </c>
+      <c r="Y94" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG94" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI94" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ94" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK94" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM94" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR94" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="95" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>1</v>
+      </c>
+      <c r="B95" s="2">
+        <v>2</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F95" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G95" s="5">
+        <v>81</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L95" s="6">
+        <v>34</v>
+      </c>
+      <c r="M95" s="7">
+        <v>12939.49</v>
+      </c>
+      <c r="N95" s="6">
+        <v>1</v>
+      </c>
+      <c r="O95" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P95" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q95" s="6">
+        <v>0</v>
+      </c>
+      <c r="R95" s="7">
+        <v>0</v>
+      </c>
+      <c r="S95" s="9">
+        <v>0</v>
+      </c>
+      <c r="T95" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U95" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V95" s="11">
+        <v>11</v>
+      </c>
+      <c r="W95" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X95" s="12">
+        <v>0.47291670000000002</v>
+      </c>
+      <c r="Y95" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB95" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG95" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI95" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ95" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK95" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL95" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM95" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR95" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="96" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>1</v>
+      </c>
+      <c r="B96" s="2">
+        <v>2</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F96" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G96" s="5">
+        <v>82</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L96" s="6">
+        <v>35</v>
+      </c>
+      <c r="M96" s="7">
+        <v>13320.07</v>
+      </c>
+      <c r="N96" s="6">
+        <v>1</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P96" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q96" s="6">
+        <v>0</v>
+      </c>
+      <c r="R96" s="7">
+        <v>0</v>
+      </c>
+      <c r="S96" s="9">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U96" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V96" s="11">
+        <v>11</v>
+      </c>
+      <c r="W96" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X96" s="12">
+        <v>0.47291670000000002</v>
+      </c>
+      <c r="Y96" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG96" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI96" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ96" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK96" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR96" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="97" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>1</v>
+      </c>
+      <c r="B97" s="2">
+        <v>2</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F97" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G97" s="5">
+        <v>83</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L97" s="6">
+        <v>36</v>
+      </c>
+      <c r="M97" s="7">
+        <v>13700.64</v>
+      </c>
+      <c r="N97" s="6">
+        <v>1</v>
+      </c>
+      <c r="O97" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P97" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q97" s="6">
+        <v>0</v>
+      </c>
+      <c r="R97" s="7">
+        <v>0</v>
+      </c>
+      <c r="S97" s="9">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U97" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V97" s="11">
+        <v>11</v>
+      </c>
+      <c r="W97" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X97" s="12">
+        <v>0.47291670000000002</v>
+      </c>
+      <c r="Y97" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG97" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI97" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ97" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK97" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR97" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="98" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>1</v>
+      </c>
+      <c r="B98" s="2">
+        <v>2</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F98" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G98" s="5">
+        <v>84</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L98" s="6">
+        <v>37</v>
+      </c>
+      <c r="M98" s="7">
+        <v>14081.21</v>
+      </c>
+      <c r="N98" s="6">
+        <v>1</v>
+      </c>
+      <c r="O98" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P98" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q98" s="6">
+        <v>0</v>
+      </c>
+      <c r="R98" s="7">
+        <v>0</v>
+      </c>
+      <c r="S98" s="9">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U98" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V98" s="11">
+        <v>11</v>
+      </c>
+      <c r="W98" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X98" s="12">
+        <v>0.47291670000000002</v>
+      </c>
+      <c r="Y98" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG98" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI98" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ98" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK98" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ98" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR98" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="99" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>1</v>
+      </c>
+      <c r="B99" s="2">
+        <v>2</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F99" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G99" s="5">
+        <v>85</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L99" s="6">
+        <v>38</v>
+      </c>
+      <c r="M99" s="7">
+        <v>14461.79</v>
+      </c>
+      <c r="N99" s="6">
+        <v>1</v>
+      </c>
+      <c r="O99" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P99" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q99" s="6">
+        <v>0</v>
+      </c>
+      <c r="R99" s="7">
+        <v>0</v>
+      </c>
+      <c r="S99" s="9">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U99" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V99" s="11">
+        <v>11</v>
+      </c>
+      <c r="W99" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X99" s="12">
+        <v>0.47291670000000002</v>
+      </c>
+      <c r="Y99" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG99" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI99" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ99" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK99" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR99" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="100" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>1</v>
+      </c>
+      <c r="B100" s="2">
+        <v>2</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F100" s="4">
+        <v>46318</v>
+      </c>
+      <c r="G100" s="5">
+        <v>86</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L100" s="6">
+        <v>39</v>
+      </c>
+      <c r="M100" s="7">
+        <v>14842.36</v>
+      </c>
+      <c r="N100" s="6">
+        <v>1</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P100" s="8">
+        <v>380.57</v>
+      </c>
+      <c r="Q100" s="6">
+        <v>0</v>
+      </c>
+      <c r="R100" s="7">
+        <v>0</v>
+      </c>
+      <c r="S100" s="9">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U100" s="10">
+        <v>68404</v>
+      </c>
+      <c r="V100" s="11">
+        <v>11</v>
+      </c>
+      <c r="W100" s="4">
+        <v>46318</v>
+      </c>
+      <c r="X100" s="12">
+        <v>0.47986109999999998</v>
+      </c>
+      <c r="Y100" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG100" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI100" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ100" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK100" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL100" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM100" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ100" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR100" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/movimentos_estoque_dados.xlsx
+++ b/movimentos_estoque_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jucieli\Desktop\automacao_senior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6437C4AB-8435-46A8-9747-43F9498DE6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF429BE1-7F68-497C-B189-4114C3662521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="143">
   <si>
     <t>Sel</t>
   </si>
@@ -154,346 +154,301 @@
     <t>Nº Série</t>
   </si>
   <si>
+    <t>10014754</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>90201</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>UN</t>
+  </si>
+  <si>
+    <t>FORNO ELETRICO NARDELLI TOP 60L BLACK - NARDELLI TOP 60 - 220 V</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>FORNOS</t>
+  </si>
+  <si>
+    <t>1858700159325</t>
+  </si>
+  <si>
+    <t>1858700159326</t>
+  </si>
+  <si>
+    <t>1858700159327</t>
+  </si>
+  <si>
+    <t>1858700159328</t>
+  </si>
+  <si>
+    <t>1858700159329</t>
+  </si>
+  <si>
+    <t>1858700159330</t>
+  </si>
+  <si>
+    <t>1858700159331</t>
+  </si>
+  <si>
+    <t>1858700159332</t>
+  </si>
+  <si>
+    <t>1858700159333</t>
+  </si>
+  <si>
+    <t>1858700159334</t>
+  </si>
+  <si>
+    <t>1858700159335</t>
+  </si>
+  <si>
+    <t>1858700159336</t>
+  </si>
+  <si>
+    <t>1858700159337</t>
+  </si>
+  <si>
+    <t>1858700159338</t>
+  </si>
+  <si>
+    <t>1858700159339</t>
+  </si>
+  <si>
+    <t>1858700159340</t>
+  </si>
+  <si>
+    <t>1858700159341</t>
+  </si>
+  <si>
+    <t>1858700159342</t>
+  </si>
+  <si>
+    <t>1858700159343</t>
+  </si>
+  <si>
+    <t>1858700159344</t>
+  </si>
+  <si>
+    <t>1858700159345</t>
+  </si>
+  <si>
+    <t>1858700159346</t>
+  </si>
+  <si>
+    <t>1858700159347</t>
+  </si>
+  <si>
+    <t>1858700159348</t>
+  </si>
+  <si>
+    <t>1858700159349</t>
+  </si>
+  <si>
+    <t>1858700159350</t>
+  </si>
+  <si>
+    <t>1858700159351</t>
+  </si>
+  <si>
+    <t>1858700159352</t>
+  </si>
+  <si>
+    <t>1858700159353</t>
+  </si>
+  <si>
+    <t>1858700159354</t>
+  </si>
+  <si>
+    <t>1858700159355</t>
+  </si>
+  <si>
+    <t>1858700159356</t>
+  </si>
+  <si>
+    <t>1858700159357</t>
+  </si>
+  <si>
+    <t>1858700159358</t>
+  </si>
+  <si>
+    <t>1858700159359</t>
+  </si>
+  <si>
+    <t>1858700159360</t>
+  </si>
+  <si>
+    <t>1858700159361</t>
+  </si>
+  <si>
+    <t>1858700159362</t>
+  </si>
+  <si>
+    <t>1858700159363</t>
+  </si>
+  <si>
+    <t>1858700159364</t>
+  </si>
+  <si>
+    <t>1858700159365</t>
+  </si>
+  <si>
+    <t>1858700159366</t>
+  </si>
+  <si>
+    <t>1858700159367</t>
+  </si>
+  <si>
+    <t>1858700159368</t>
+  </si>
+  <si>
+    <t>1858700159369</t>
+  </si>
+  <si>
+    <t>1858700159370</t>
+  </si>
+  <si>
+    <t>1858700159371</t>
+  </si>
+  <si>
+    <t>1858700159372</t>
+  </si>
+  <si>
+    <t>1858700159373</t>
+  </si>
+  <si>
+    <t>1858700159374</t>
+  </si>
+  <si>
+    <t>1858700159375</t>
+  </si>
+  <si>
+    <t>1858700159376</t>
+  </si>
+  <si>
+    <t>1858700159377</t>
+  </si>
+  <si>
+    <t>1858700159378</t>
+  </si>
+  <si>
+    <t>1858700159379</t>
+  </si>
+  <si>
+    <t>1858700159380</t>
+  </si>
+  <si>
+    <t>1858700159381</t>
+  </si>
+  <si>
+    <t>1858700159382</t>
+  </si>
+  <si>
+    <t>1858700159383</t>
+  </si>
+  <si>
+    <t>1858700159384</t>
+  </si>
+  <si>
+    <t>1858700159385</t>
+  </si>
+  <si>
+    <t>1858700159386</t>
+  </si>
+  <si>
+    <t>1858700159387</t>
+  </si>
+  <si>
+    <t>1858700159388</t>
+  </si>
+  <si>
+    <t>1858700159389</t>
+  </si>
+  <si>
+    <t>1858700159390</t>
+  </si>
+  <si>
     <t>10016354</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>500</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>90201</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>UN</t>
-  </si>
-  <si>
     <t>FORNO ELETRICO NARDELLI EMBUTIR 60L BLACK - NARDELLI EMBUTIR 60L BLACK - 220 V</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>FORNOE</t>
   </si>
   <si>
-    <t>1871600010556</t>
-  </si>
-  <si>
-    <t>1871600010557</t>
-  </si>
-  <si>
-    <t>1871600010558</t>
-  </si>
-  <si>
-    <t>1871600010559</t>
-  </si>
-  <si>
-    <t>1871600010560</t>
-  </si>
-  <si>
-    <t>1871600010561</t>
-  </si>
-  <si>
-    <t>1871600010562</t>
-  </si>
-  <si>
-    <t>1871600010563</t>
-  </si>
-  <si>
-    <t>1871600010564</t>
-  </si>
-  <si>
-    <t>1871600010565</t>
-  </si>
-  <si>
-    <t>1871600010566</t>
-  </si>
-  <si>
-    <t>1871600010567</t>
-  </si>
-  <si>
-    <t>1871600010568</t>
-  </si>
-  <si>
-    <t>1871600010569</t>
-  </si>
-  <si>
-    <t>1871600010570</t>
-  </si>
-  <si>
-    <t>1871600010571</t>
-  </si>
-  <si>
-    <t>1871600010572</t>
-  </si>
-  <si>
-    <t>1871600010573</t>
-  </si>
-  <si>
-    <t>1871600010574</t>
-  </si>
-  <si>
-    <t>1871600010575</t>
-  </si>
-  <si>
-    <t>1871600010576</t>
-  </si>
-  <si>
-    <t>1871600010577</t>
-  </si>
-  <si>
-    <t>1871600010578</t>
-  </si>
-  <si>
-    <t>1871600010579</t>
-  </si>
-  <si>
-    <t>10016398</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>FORNO ELETRICO NARDELLI EMBUTIR 80L BLACK - NARDELLI EMBUTIR 80L BLACK - 127 V</t>
-  </si>
-  <si>
-    <t>1882900000034</t>
-  </si>
-  <si>
-    <t>1882900000035</t>
-  </si>
-  <si>
-    <t>1882900000036</t>
-  </si>
-  <si>
-    <t>1882900000037</t>
-  </si>
-  <si>
-    <t>1882900000038</t>
-  </si>
-  <si>
-    <t>1882900000039</t>
-  </si>
-  <si>
-    <t>1882900000040</t>
-  </si>
-  <si>
-    <t>1882900000041</t>
-  </si>
-  <si>
-    <t>1882900000042</t>
-  </si>
-  <si>
-    <t>1882900000043</t>
-  </si>
-  <si>
-    <t>1882900000044</t>
-  </si>
-  <si>
-    <t>1882900000045</t>
-  </si>
-  <si>
-    <t>1882900000046</t>
-  </si>
-  <si>
-    <t>1882900000047</t>
-  </si>
-  <si>
-    <t>1882900000048</t>
-  </si>
-  <si>
-    <t>1882900000049</t>
-  </si>
-  <si>
-    <t>1882900000050</t>
-  </si>
-  <si>
-    <t>1882900000051</t>
-  </si>
-  <si>
-    <t>1882900000052</t>
-  </si>
-  <si>
-    <t>1882900000053</t>
-  </si>
-  <si>
-    <t>1882900000014</t>
-  </si>
-  <si>
-    <t>1882900000015</t>
-  </si>
-  <si>
-    <t>1882900000016</t>
-  </si>
-  <si>
-    <t>1882900000017</t>
-  </si>
-  <si>
-    <t>1882900000018</t>
-  </si>
-  <si>
-    <t>1882900000019</t>
-  </si>
-  <si>
-    <t>1882900000020</t>
-  </si>
-  <si>
-    <t>1882900000021</t>
-  </si>
-  <si>
-    <t>1882900000022</t>
-  </si>
-  <si>
-    <t>1882900000023</t>
-  </si>
-  <si>
-    <t>1882900000024</t>
-  </si>
-  <si>
-    <t>1882900000025</t>
-  </si>
-  <si>
-    <t>1882900000026</t>
-  </si>
-  <si>
-    <t>1882900000027</t>
-  </si>
-  <si>
-    <t>1882900000028</t>
-  </si>
-  <si>
-    <t>FORNO ELETRICO NARDELLI EMBUTIR 80L BLACK - NARDELLI EMBUTIR 80L BLACK - 220 V</t>
-  </si>
-  <si>
-    <t>1883100000054</t>
-  </si>
-  <si>
-    <t>1883100000055</t>
-  </si>
-  <si>
-    <t>1883100000056</t>
-  </si>
-  <si>
-    <t>1883100000057</t>
-  </si>
-  <si>
-    <t>1883100000058</t>
-  </si>
-  <si>
-    <t>1883100000059</t>
-  </si>
-  <si>
-    <t>1883100000060</t>
-  </si>
-  <si>
-    <t>1883100000061</t>
-  </si>
-  <si>
-    <t>1883100000062</t>
-  </si>
-  <si>
-    <t>1883100000063</t>
-  </si>
-  <si>
-    <t>1883100000064</t>
-  </si>
-  <si>
-    <t>1883100000065</t>
-  </si>
-  <si>
-    <t>1883100000066</t>
-  </si>
-  <si>
-    <t>1883100000067</t>
-  </si>
-  <si>
-    <t>1883100000068</t>
-  </si>
-  <si>
-    <t>1883100000069</t>
-  </si>
-  <si>
-    <t>1883100000070</t>
-  </si>
-  <si>
-    <t>1883100000071</t>
-  </si>
-  <si>
-    <t>1883100000072</t>
-  </si>
-  <si>
-    <t>1883100000034</t>
-  </si>
-  <si>
-    <t>1883100000035</t>
-  </si>
-  <si>
-    <t>1883100000036</t>
-  </si>
-  <si>
-    <t>1883100000037</t>
-  </si>
-  <si>
-    <t>1883100000038</t>
-  </si>
-  <si>
-    <t>1883100000039</t>
-  </si>
-  <si>
-    <t>1883100000073</t>
-  </si>
-  <si>
-    <t>1883100000040</t>
-  </si>
-  <si>
-    <t>1883100000041</t>
-  </si>
-  <si>
-    <t>1883100000042</t>
-  </si>
-  <si>
-    <t>1883100000043</t>
-  </si>
-  <si>
-    <t>1883100000044</t>
-  </si>
-  <si>
-    <t>1883100000045</t>
-  </si>
-  <si>
-    <t>1883100000046</t>
-  </si>
-  <si>
-    <t>1883100000047</t>
-  </si>
-  <si>
-    <t>1883100000048</t>
-  </si>
-  <si>
-    <t>1883100000049</t>
-  </si>
-  <si>
-    <t>1883100000050</t>
-  </si>
-  <si>
-    <t>1883100000051</t>
-  </si>
-  <si>
-    <t>1883100000052</t>
-  </si>
-  <si>
-    <t>1883100000053</t>
+    <t>1871600010601</t>
+  </si>
+  <si>
+    <t>1871600010602</t>
+  </si>
+  <si>
+    <t>1871600010603</t>
+  </si>
+  <si>
+    <t>1871600010604</t>
+  </si>
+  <si>
+    <t>1871600010605</t>
+  </si>
+  <si>
+    <t>1871600010606</t>
+  </si>
+  <si>
+    <t>1871600010607</t>
+  </si>
+  <si>
+    <t>1871600010608</t>
+  </si>
+  <si>
+    <t>1871600010609</t>
+  </si>
+  <si>
+    <t>1871600010610</t>
+  </si>
+  <si>
+    <t>1871600010611</t>
+  </si>
+  <si>
+    <t>1871600010612</t>
+  </si>
+  <si>
+    <t>1871600010613</t>
+  </si>
+  <si>
+    <t>1871600010614</t>
+  </si>
+  <si>
+    <t>1871600010615</t>
+  </si>
+  <si>
+    <t>1871600010616</t>
+  </si>
+  <si>
+    <t>1871600010617</t>
+  </si>
+  <si>
+    <t>1871600010618</t>
+  </si>
+  <si>
+    <t>1871600010619</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR100"/>
+  <dimension ref="A1:AR86"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -1223,10 +1178,10 @@
         <v>46</v>
       </c>
       <c r="F2" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G2" s="5">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>47</v>
@@ -1241,10 +1196,10 @@
         <v>50</v>
       </c>
       <c r="L2" s="6">
-        <v>487</v>
+        <v>5756</v>
       </c>
       <c r="M2" s="7">
-        <v>161372.43</v>
+        <v>982693.95</v>
       </c>
       <c r="N2" s="6">
         <v>1</v>
@@ -1253,7 +1208,7 @@
         <v>51</v>
       </c>
       <c r="P2" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q2" s="6">
         <v>0</v>
@@ -1268,16 +1223,16 @@
         <v>52</v>
       </c>
       <c r="U2" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V2" s="11">
         <v>11</v>
       </c>
       <c r="W2" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X2" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.30694440000000001</v>
       </c>
       <c r="Y2" s="10">
         <v>0</v>
@@ -1357,10 +1312,10 @@
         <v>46</v>
       </c>
       <c r="F3" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G3" s="5">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>47</v>
@@ -1375,10 +1330,10 @@
         <v>50</v>
       </c>
       <c r="L3" s="6">
-        <v>488</v>
+        <v>5757</v>
       </c>
       <c r="M3" s="7">
-        <v>161703.79</v>
+        <v>982864.67</v>
       </c>
       <c r="N3" s="6">
         <v>1</v>
@@ -1387,7 +1342,7 @@
         <v>51</v>
       </c>
       <c r="P3" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q3" s="6">
         <v>0</v>
@@ -1402,16 +1357,16 @@
         <v>52</v>
       </c>
       <c r="U3" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V3" s="11">
         <v>11</v>
       </c>
       <c r="W3" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X3" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.30694440000000001</v>
       </c>
       <c r="Y3" s="10">
         <v>0</v>
@@ -1491,10 +1446,10 @@
         <v>46</v>
       </c>
       <c r="F4" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G4" s="5">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>47</v>
@@ -1509,10 +1464,10 @@
         <v>50</v>
       </c>
       <c r="L4" s="6">
-        <v>489</v>
+        <v>5758</v>
       </c>
       <c r="M4" s="7">
-        <v>162035.15</v>
+        <v>983035.4</v>
       </c>
       <c r="N4" s="6">
         <v>1</v>
@@ -1521,7 +1476,7 @@
         <v>51</v>
       </c>
       <c r="P4" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q4" s="6">
         <v>0</v>
@@ -1536,16 +1491,16 @@
         <v>52</v>
       </c>
       <c r="U4" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V4" s="11">
         <v>11</v>
       </c>
       <c r="W4" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X4" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.30694440000000001</v>
       </c>
       <c r="Y4" s="10">
         <v>0</v>
@@ -1625,10 +1580,10 @@
         <v>46</v>
       </c>
       <c r="F5" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G5" s="5">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>47</v>
@@ -1643,10 +1598,10 @@
         <v>50</v>
       </c>
       <c r="L5" s="6">
-        <v>490</v>
+        <v>5759</v>
       </c>
       <c r="M5" s="7">
-        <v>162366.51</v>
+        <v>983206.12</v>
       </c>
       <c r="N5" s="6">
         <v>1</v>
@@ -1655,7 +1610,7 @@
         <v>51</v>
       </c>
       <c r="P5" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q5" s="6">
         <v>0</v>
@@ -1670,16 +1625,16 @@
         <v>52</v>
       </c>
       <c r="U5" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V5" s="11">
         <v>11</v>
       </c>
       <c r="W5" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X5" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.30694440000000001</v>
       </c>
       <c r="Y5" s="10">
         <v>0</v>
@@ -1759,10 +1714,10 @@
         <v>46</v>
       </c>
       <c r="F6" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G6" s="5">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>47</v>
@@ -1777,10 +1732,10 @@
         <v>50</v>
       </c>
       <c r="L6" s="6">
-        <v>491</v>
+        <v>5760</v>
       </c>
       <c r="M6" s="7">
-        <v>162697.87</v>
+        <v>983376.85</v>
       </c>
       <c r="N6" s="6">
         <v>1</v>
@@ -1789,7 +1744,7 @@
         <v>51</v>
       </c>
       <c r="P6" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q6" s="6">
         <v>0</v>
@@ -1804,16 +1759,16 @@
         <v>52</v>
       </c>
       <c r="U6" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V6" s="11">
         <v>11</v>
       </c>
       <c r="W6" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X6" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.30694440000000001</v>
       </c>
       <c r="Y6" s="10">
         <v>0</v>
@@ -1893,10 +1848,10 @@
         <v>46</v>
       </c>
       <c r="F7" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G7" s="5">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>47</v>
@@ -1911,10 +1866,10 @@
         <v>50</v>
       </c>
       <c r="L7" s="6">
-        <v>492</v>
+        <v>5761</v>
       </c>
       <c r="M7" s="7">
-        <v>163029.23000000001</v>
+        <v>983547.57</v>
       </c>
       <c r="N7" s="6">
         <v>1</v>
@@ -1923,7 +1878,7 @@
         <v>51</v>
       </c>
       <c r="P7" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q7" s="6">
         <v>0</v>
@@ -1938,16 +1893,16 @@
         <v>52</v>
       </c>
       <c r="U7" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V7" s="11">
         <v>11</v>
       </c>
       <c r="W7" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X7" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.30694440000000001</v>
       </c>
       <c r="Y7" s="10">
         <v>0</v>
@@ -2027,10 +1982,10 @@
         <v>46</v>
       </c>
       <c r="F8" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G8" s="5">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>47</v>
@@ -2045,10 +2000,10 @@
         <v>50</v>
       </c>
       <c r="L8" s="6">
-        <v>493</v>
+        <v>5762</v>
       </c>
       <c r="M8" s="7">
-        <v>163360.59</v>
+        <v>983718.3</v>
       </c>
       <c r="N8" s="6">
         <v>1</v>
@@ -2057,7 +2012,7 @@
         <v>51</v>
       </c>
       <c r="P8" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q8" s="6">
         <v>0</v>
@@ -2072,16 +2027,16 @@
         <v>52</v>
       </c>
       <c r="U8" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V8" s="11">
         <v>11</v>
       </c>
       <c r="W8" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X8" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.30694440000000001</v>
       </c>
       <c r="Y8" s="10">
         <v>0</v>
@@ -2161,10 +2116,10 @@
         <v>46</v>
       </c>
       <c r="F9" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G9" s="5">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>47</v>
@@ -2179,10 +2134,10 @@
         <v>50</v>
       </c>
       <c r="L9" s="6">
-        <v>494</v>
+        <v>5763</v>
       </c>
       <c r="M9" s="7">
-        <v>163691.95000000001</v>
+        <v>983889.02</v>
       </c>
       <c r="N9" s="6">
         <v>1</v>
@@ -2191,7 +2146,7 @@
         <v>51</v>
       </c>
       <c r="P9" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q9" s="6">
         <v>0</v>
@@ -2206,16 +2161,16 @@
         <v>52</v>
       </c>
       <c r="U9" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V9" s="11">
         <v>11</v>
       </c>
       <c r="W9" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X9" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.30694440000000001</v>
       </c>
       <c r="Y9" s="10">
         <v>0</v>
@@ -2295,10 +2250,10 @@
         <v>46</v>
       </c>
       <c r="F10" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G10" s="5">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>47</v>
@@ -2313,10 +2268,10 @@
         <v>50</v>
       </c>
       <c r="L10" s="6">
-        <v>495</v>
+        <v>5764</v>
       </c>
       <c r="M10" s="7">
-        <v>164023.31</v>
+        <v>984059.75</v>
       </c>
       <c r="N10" s="6">
         <v>1</v>
@@ -2325,7 +2280,7 @@
         <v>51</v>
       </c>
       <c r="P10" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q10" s="6">
         <v>0</v>
@@ -2340,16 +2295,16 @@
         <v>52</v>
       </c>
       <c r="U10" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V10" s="11">
         <v>11</v>
       </c>
       <c r="W10" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X10" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.31388890000000003</v>
       </c>
       <c r="Y10" s="10">
         <v>0</v>
@@ -2429,10 +2384,10 @@
         <v>46</v>
       </c>
       <c r="F11" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G11" s="5">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>47</v>
@@ -2447,10 +2402,10 @@
         <v>50</v>
       </c>
       <c r="L11" s="6">
-        <v>496</v>
+        <v>5765</v>
       </c>
       <c r="M11" s="7">
-        <v>164354.67000000001</v>
+        <v>984230.47</v>
       </c>
       <c r="N11" s="6">
         <v>1</v>
@@ -2459,7 +2414,7 @@
         <v>51</v>
       </c>
       <c r="P11" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q11" s="6">
         <v>0</v>
@@ -2474,16 +2429,16 @@
         <v>52</v>
       </c>
       <c r="U11" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V11" s="11">
         <v>11</v>
       </c>
       <c r="W11" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X11" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.31388890000000003</v>
       </c>
       <c r="Y11" s="10">
         <v>0</v>
@@ -2563,10 +2518,10 @@
         <v>46</v>
       </c>
       <c r="F12" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G12" s="5">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>47</v>
@@ -2581,10 +2536,10 @@
         <v>50</v>
       </c>
       <c r="L12" s="6">
-        <v>497</v>
+        <v>5766</v>
       </c>
       <c r="M12" s="7">
-        <v>164686.03</v>
+        <v>984401.2</v>
       </c>
       <c r="N12" s="6">
         <v>1</v>
@@ -2593,7 +2548,7 @@
         <v>51</v>
       </c>
       <c r="P12" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q12" s="6">
         <v>0</v>
@@ -2608,16 +2563,16 @@
         <v>52</v>
       </c>
       <c r="U12" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V12" s="11">
         <v>11</v>
       </c>
       <c r="W12" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X12" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.31388890000000003</v>
       </c>
       <c r="Y12" s="10">
         <v>0</v>
@@ -2697,10 +2652,10 @@
         <v>46</v>
       </c>
       <c r="F13" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G13" s="5">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>47</v>
@@ -2715,10 +2670,10 @@
         <v>50</v>
       </c>
       <c r="L13" s="6">
-        <v>498</v>
+        <v>5767</v>
       </c>
       <c r="M13" s="7">
-        <v>165017.39000000001</v>
+        <v>984571.92</v>
       </c>
       <c r="N13" s="6">
         <v>1</v>
@@ -2727,7 +2682,7 @@
         <v>51</v>
       </c>
       <c r="P13" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q13" s="6">
         <v>0</v>
@@ -2742,16 +2697,16 @@
         <v>52</v>
       </c>
       <c r="U13" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V13" s="11">
         <v>11</v>
       </c>
       <c r="W13" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X13" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.31388890000000003</v>
       </c>
       <c r="Y13" s="10">
         <v>0</v>
@@ -2831,10 +2786,10 @@
         <v>46</v>
       </c>
       <c r="F14" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G14" s="5">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>47</v>
@@ -2849,10 +2804,10 @@
         <v>50</v>
       </c>
       <c r="L14" s="6">
-        <v>499</v>
+        <v>5768</v>
       </c>
       <c r="M14" s="7">
-        <v>165348.75</v>
+        <v>984742.65</v>
       </c>
       <c r="N14" s="6">
         <v>1</v>
@@ -2861,7 +2816,7 @@
         <v>51</v>
       </c>
       <c r="P14" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q14" s="6">
         <v>0</v>
@@ -2876,16 +2831,16 @@
         <v>52</v>
       </c>
       <c r="U14" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V14" s="11">
         <v>11</v>
       </c>
       <c r="W14" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X14" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.31388890000000003</v>
       </c>
       <c r="Y14" s="10">
         <v>0</v>
@@ -2965,10 +2920,10 @@
         <v>46</v>
       </c>
       <c r="F15" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G15" s="5">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>47</v>
@@ -2983,10 +2938,10 @@
         <v>50</v>
       </c>
       <c r="L15" s="6">
-        <v>500</v>
+        <v>5769</v>
       </c>
       <c r="M15" s="7">
-        <v>165680.10999999999</v>
+        <v>984913.37</v>
       </c>
       <c r="N15" s="6">
         <v>1</v>
@@ -2995,7 +2950,7 @@
         <v>51</v>
       </c>
       <c r="P15" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q15" s="6">
         <v>0</v>
@@ -3010,16 +2965,16 @@
         <v>52</v>
       </c>
       <c r="U15" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V15" s="11">
         <v>11</v>
       </c>
       <c r="W15" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X15" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.31388890000000003</v>
       </c>
       <c r="Y15" s="10">
         <v>0</v>
@@ -3099,10 +3054,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G16" s="5">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>47</v>
@@ -3117,10 +3072,10 @@
         <v>50</v>
       </c>
       <c r="L16" s="6">
-        <v>501</v>
+        <v>5770</v>
       </c>
       <c r="M16" s="7">
-        <v>166011.47</v>
+        <v>985084.1</v>
       </c>
       <c r="N16" s="6">
         <v>1</v>
@@ -3129,7 +3084,7 @@
         <v>51</v>
       </c>
       <c r="P16" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q16" s="6">
         <v>0</v>
@@ -3144,16 +3099,16 @@
         <v>52</v>
       </c>
       <c r="U16" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V16" s="11">
         <v>11</v>
       </c>
       <c r="W16" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X16" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.31388890000000003</v>
       </c>
       <c r="Y16" s="10">
         <v>0</v>
@@ -3233,10 +3188,10 @@
         <v>46</v>
       </c>
       <c r="F17" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G17" s="5">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>47</v>
@@ -3251,10 +3206,10 @@
         <v>50</v>
       </c>
       <c r="L17" s="6">
-        <v>502</v>
+        <v>5771</v>
       </c>
       <c r="M17" s="7">
-        <v>166342.82999999999</v>
+        <v>985254.82</v>
       </c>
       <c r="N17" s="6">
         <v>1</v>
@@ -3263,7 +3218,7 @@
         <v>51</v>
       </c>
       <c r="P17" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q17" s="6">
         <v>0</v>
@@ -3278,16 +3233,16 @@
         <v>52</v>
       </c>
       <c r="U17" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V17" s="11">
         <v>11</v>
       </c>
       <c r="W17" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X17" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.31388890000000003</v>
       </c>
       <c r="Y17" s="10">
         <v>0</v>
@@ -3367,10 +3322,10 @@
         <v>46</v>
       </c>
       <c r="F18" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G18" s="5">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>47</v>
@@ -3385,10 +3340,10 @@
         <v>50</v>
       </c>
       <c r="L18" s="6">
-        <v>503</v>
+        <v>5772</v>
       </c>
       <c r="M18" s="7">
-        <v>166674.19</v>
+        <v>985425.55</v>
       </c>
       <c r="N18" s="6">
         <v>1</v>
@@ -3397,7 +3352,7 @@
         <v>51</v>
       </c>
       <c r="P18" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q18" s="6">
         <v>0</v>
@@ -3412,16 +3367,16 @@
         <v>52</v>
       </c>
       <c r="U18" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V18" s="11">
         <v>11</v>
       </c>
       <c r="W18" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X18" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.31388890000000003</v>
       </c>
       <c r="Y18" s="10">
         <v>0</v>
@@ -3501,10 +3456,10 @@
         <v>46</v>
       </c>
       <c r="F19" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G19" s="5">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>47</v>
@@ -3519,10 +3474,10 @@
         <v>50</v>
       </c>
       <c r="L19" s="6">
-        <v>504</v>
+        <v>5773</v>
       </c>
       <c r="M19" s="7">
-        <v>167005.54999999999</v>
+        <v>985596.27</v>
       </c>
       <c r="N19" s="6">
         <v>1</v>
@@ -3531,7 +3486,7 @@
         <v>51</v>
       </c>
       <c r="P19" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q19" s="6">
         <v>0</v>
@@ -3546,16 +3501,16 @@
         <v>52</v>
       </c>
       <c r="U19" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V19" s="11">
         <v>11</v>
       </c>
       <c r="W19" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X19" s="12">
-        <v>0.33472220000000003</v>
+        <v>0.31388890000000003</v>
       </c>
       <c r="Y19" s="10">
         <v>0</v>
@@ -3635,10 +3590,10 @@
         <v>46</v>
       </c>
       <c r="F20" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G20" s="5">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>47</v>
@@ -3653,10 +3608,10 @@
         <v>50</v>
       </c>
       <c r="L20" s="6">
-        <v>505</v>
+        <v>5774</v>
       </c>
       <c r="M20" s="7">
-        <v>167336.91</v>
+        <v>985767</v>
       </c>
       <c r="N20" s="6">
         <v>1</v>
@@ -3665,7 +3620,7 @@
         <v>51</v>
       </c>
       <c r="P20" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q20" s="6">
         <v>0</v>
@@ -3680,16 +3635,16 @@
         <v>52</v>
       </c>
       <c r="U20" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V20" s="11">
         <v>11</v>
       </c>
       <c r="W20" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X20" s="12">
-        <v>0.33541670000000001</v>
+        <v>0.32083329999999999</v>
       </c>
       <c r="Y20" s="10">
         <v>0</v>
@@ -3769,10 +3724,10 @@
         <v>46</v>
       </c>
       <c r="F21" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G21" s="5">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>47</v>
@@ -3787,10 +3742,10 @@
         <v>50</v>
       </c>
       <c r="L21" s="6">
-        <v>506</v>
+        <v>5775</v>
       </c>
       <c r="M21" s="7">
-        <v>167668.26999999999</v>
+        <v>985937.72</v>
       </c>
       <c r="N21" s="6">
         <v>1</v>
@@ -3799,7 +3754,7 @@
         <v>51</v>
       </c>
       <c r="P21" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q21" s="6">
         <v>0</v>
@@ -3814,16 +3769,16 @@
         <v>52</v>
       </c>
       <c r="U21" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V21" s="11">
         <v>11</v>
       </c>
       <c r="W21" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X21" s="12">
-        <v>0.33541670000000001</v>
+        <v>0.32083329999999999</v>
       </c>
       <c r="Y21" s="10">
         <v>0</v>
@@ -3903,10 +3858,10 @@
         <v>46</v>
       </c>
       <c r="F22" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G22" s="5">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>47</v>
@@ -3921,10 +3876,10 @@
         <v>50</v>
       </c>
       <c r="L22" s="6">
-        <v>507</v>
+        <v>5776</v>
       </c>
       <c r="M22" s="7">
-        <v>167999.64</v>
+        <v>986108.45</v>
       </c>
       <c r="N22" s="6">
         <v>1</v>
@@ -3933,7 +3888,7 @@
         <v>51</v>
       </c>
       <c r="P22" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q22" s="6">
         <v>0</v>
@@ -3948,16 +3903,16 @@
         <v>52</v>
       </c>
       <c r="U22" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V22" s="11">
         <v>11</v>
       </c>
       <c r="W22" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X22" s="12">
-        <v>0.34236109999999997</v>
+        <v>0.32083329999999999</v>
       </c>
       <c r="Y22" s="10">
         <v>0</v>
@@ -4037,10 +3992,10 @@
         <v>46</v>
       </c>
       <c r="F23" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G23" s="5">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>47</v>
@@ -4055,10 +4010,10 @@
         <v>50</v>
       </c>
       <c r="L23" s="6">
-        <v>508</v>
+        <v>5777</v>
       </c>
       <c r="M23" s="7">
-        <v>168331</v>
+        <v>986279.17</v>
       </c>
       <c r="N23" s="6">
         <v>1</v>
@@ -4067,7 +4022,7 @@
         <v>51</v>
       </c>
       <c r="P23" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q23" s="6">
         <v>0</v>
@@ -4082,16 +4037,16 @@
         <v>52</v>
       </c>
       <c r="U23" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V23" s="11">
         <v>11</v>
       </c>
       <c r="W23" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X23" s="12">
-        <v>0.34236109999999997</v>
+        <v>0.32083329999999999</v>
       </c>
       <c r="Y23" s="10">
         <v>0</v>
@@ -4171,10 +4126,10 @@
         <v>46</v>
       </c>
       <c r="F24" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G24" s="5">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>47</v>
@@ -4189,10 +4144,10 @@
         <v>50</v>
       </c>
       <c r="L24" s="6">
-        <v>509</v>
+        <v>5778</v>
       </c>
       <c r="M24" s="7">
-        <v>168662.36</v>
+        <v>986449.9</v>
       </c>
       <c r="N24" s="6">
         <v>1</v>
@@ -4201,7 +4156,7 @@
         <v>51</v>
       </c>
       <c r="P24" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q24" s="6">
         <v>0</v>
@@ -4216,16 +4171,16 @@
         <v>52</v>
       </c>
       <c r="U24" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V24" s="11">
         <v>11</v>
       </c>
       <c r="W24" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X24" s="12">
-        <v>0.34930559999999999</v>
+        <v>0.32083329999999999</v>
       </c>
       <c r="Y24" s="10">
         <v>0</v>
@@ -4305,10 +4260,10 @@
         <v>46</v>
       </c>
       <c r="F25" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G25" s="5">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>47</v>
@@ -4323,10 +4278,10 @@
         <v>50</v>
       </c>
       <c r="L25" s="6">
-        <v>510</v>
+        <v>5779</v>
       </c>
       <c r="M25" s="7">
-        <v>168993.72</v>
+        <v>986620.62</v>
       </c>
       <c r="N25" s="6">
         <v>1</v>
@@ -4335,7 +4290,7 @@
         <v>51</v>
       </c>
       <c r="P25" s="8">
-        <v>331.36</v>
+        <v>170.73</v>
       </c>
       <c r="Q25" s="6">
         <v>0</v>
@@ -4350,16 +4305,16 @@
         <v>52</v>
       </c>
       <c r="U25" s="10">
-        <v>68570</v>
+        <v>68529</v>
       </c>
       <c r="V25" s="11">
         <v>11</v>
       </c>
       <c r="W25" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X25" s="12">
-        <v>0.34930559999999999</v>
+        <v>0.32083329999999999</v>
       </c>
       <c r="Y25" s="10">
         <v>0</v>
@@ -4430,19 +4385,19 @@
         <v>2</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F26" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G26" s="5">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>47</v>
@@ -4457,19 +4412,19 @@
         <v>50</v>
       </c>
       <c r="L26" s="6">
-        <v>0</v>
+        <v>5780</v>
       </c>
       <c r="M26" s="7">
-        <v>0</v>
+        <v>986791.35</v>
       </c>
       <c r="N26" s="6">
         <v>1</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="P26" s="8">
-        <v>374.8</v>
+        <v>170.73</v>
       </c>
       <c r="Q26" s="6">
         <v>0</v>
@@ -4484,16 +4439,16 @@
         <v>52</v>
       </c>
       <c r="U26" s="10">
-        <v>68585</v>
+        <v>68529</v>
       </c>
       <c r="V26" s="11">
         <v>11</v>
       </c>
       <c r="W26" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X26" s="12">
-        <v>0.54305559999999997</v>
+        <v>0.32083329999999999</v>
       </c>
       <c r="Y26" s="10">
         <v>0</v>
@@ -4553,7 +4508,7 @@
         <v>53</v>
       </c>
       <c r="AR26" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:44" x14ac:dyDescent="0.3">
@@ -4564,19 +4519,19 @@
         <v>2</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F27" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G27" s="5">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>47</v>
@@ -4591,19 +4546,19 @@
         <v>50</v>
       </c>
       <c r="L27" s="6">
-        <v>1</v>
+        <v>5781</v>
       </c>
       <c r="M27" s="7">
-        <v>374.8</v>
+        <v>986962.07</v>
       </c>
       <c r="N27" s="6">
         <v>1</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="P27" s="8">
-        <v>374.8</v>
+        <v>170.73</v>
       </c>
       <c r="Q27" s="6">
         <v>0</v>
@@ -4618,16 +4573,16 @@
         <v>52</v>
       </c>
       <c r="U27" s="10">
-        <v>68585</v>
+        <v>68529</v>
       </c>
       <c r="V27" s="11">
         <v>11</v>
       </c>
       <c r="W27" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X27" s="12">
-        <v>0.54305559999999997</v>
+        <v>0.32083329999999999</v>
       </c>
       <c r="Y27" s="10">
         <v>0</v>
@@ -4687,7 +4642,7 @@
         <v>53</v>
       </c>
       <c r="AR27" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:44" x14ac:dyDescent="0.3">
@@ -4698,19 +4653,19 @@
         <v>2</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F28" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G28" s="5">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>47</v>
@@ -4725,19 +4680,19 @@
         <v>50</v>
       </c>
       <c r="L28" s="6">
-        <v>2</v>
+        <v>5782</v>
       </c>
       <c r="M28" s="7">
-        <v>749.6</v>
+        <v>987132.8</v>
       </c>
       <c r="N28" s="6">
         <v>1</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="P28" s="8">
-        <v>374.8</v>
+        <v>170.73</v>
       </c>
       <c r="Q28" s="6">
         <v>0</v>
@@ -4752,16 +4707,16 @@
         <v>52</v>
       </c>
       <c r="U28" s="10">
-        <v>68585</v>
+        <v>68529</v>
       </c>
       <c r="V28" s="11">
         <v>11</v>
       </c>
       <c r="W28" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X28" s="12">
-        <v>0.54305559999999997</v>
+        <v>0.32083329999999999</v>
       </c>
       <c r="Y28" s="10">
         <v>0</v>
@@ -4821,7 +4776,7 @@
         <v>53</v>
       </c>
       <c r="AR28" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.3">
@@ -4832,19 +4787,19 @@
         <v>2</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F29" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G29" s="5">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>47</v>
@@ -4859,19 +4814,19 @@
         <v>50</v>
       </c>
       <c r="L29" s="6">
-        <v>3</v>
+        <v>5783</v>
       </c>
       <c r="M29" s="7">
-        <v>1124.3900000000001</v>
+        <v>987303.52</v>
       </c>
       <c r="N29" s="6">
         <v>1</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="P29" s="8">
-        <v>374.8</v>
+        <v>170.73</v>
       </c>
       <c r="Q29" s="6">
         <v>0</v>
@@ -4886,16 +4841,16 @@
         <v>52</v>
       </c>
       <c r="U29" s="10">
-        <v>68585</v>
+        <v>68529</v>
       </c>
       <c r="V29" s="11">
         <v>11</v>
       </c>
       <c r="W29" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X29" s="12">
-        <v>0.54305559999999997</v>
+        <v>0.32083329999999999</v>
       </c>
       <c r="Y29" s="10">
         <v>0</v>
@@ -4955,7 +4910,7 @@
         <v>53</v>
       </c>
       <c r="AR29" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:44" x14ac:dyDescent="0.3">
@@ -4966,19 +4921,19 @@
         <v>2</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F30" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G30" s="5">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>47</v>
@@ -4993,19 +4948,19 @@
         <v>50</v>
       </c>
       <c r="L30" s="6">
-        <v>4</v>
+        <v>5784</v>
       </c>
       <c r="M30" s="7">
-        <v>1499.19</v>
+        <v>987474.25</v>
       </c>
       <c r="N30" s="6">
         <v>1</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="P30" s="8">
-        <v>374.8</v>
+        <v>170.73</v>
       </c>
       <c r="Q30" s="6">
         <v>0</v>
@@ -5020,16 +4975,16 @@
         <v>52</v>
       </c>
       <c r="U30" s="10">
-        <v>68585</v>
+        <v>68529</v>
       </c>
       <c r="V30" s="11">
         <v>11</v>
       </c>
       <c r="W30" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X30" s="12">
-        <v>0.54305559999999997</v>
+        <v>0.32083329999999999</v>
       </c>
       <c r="Y30" s="10">
         <v>0</v>
@@ -5089,7 +5044,7 @@
         <v>53</v>
       </c>
       <c r="AR30" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:44" x14ac:dyDescent="0.3">
@@ -5100,19 +5055,19 @@
         <v>2</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F31" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G31" s="5">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>47</v>
@@ -5127,19 +5082,19 @@
         <v>50</v>
       </c>
       <c r="L31" s="6">
-        <v>5</v>
+        <v>5785</v>
       </c>
       <c r="M31" s="7">
-        <v>1873.99</v>
+        <v>987644.97</v>
       </c>
       <c r="N31" s="6">
         <v>1</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="P31" s="8">
-        <v>374.8</v>
+        <v>170.73</v>
       </c>
       <c r="Q31" s="6">
         <v>0</v>
@@ -5154,16 +5109,16 @@
         <v>52</v>
       </c>
       <c r="U31" s="10">
-        <v>68585</v>
+        <v>68529</v>
       </c>
       <c r="V31" s="11">
         <v>11</v>
       </c>
       <c r="W31" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X31" s="12">
-        <v>0.54305559999999997</v>
+        <v>0.32083329999999999</v>
       </c>
       <c r="Y31" s="10">
         <v>0</v>
@@ -5223,7 +5178,7 @@
         <v>53</v>
       </c>
       <c r="AR31" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.3">
@@ -5234,19 +5189,19 @@
         <v>2</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F32" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G32" s="5">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>47</v>
@@ -5261,19 +5216,19 @@
         <v>50</v>
       </c>
       <c r="L32" s="6">
-        <v>6</v>
+        <v>5786</v>
       </c>
       <c r="M32" s="7">
-        <v>2248.79</v>
+        <v>987815.7</v>
       </c>
       <c r="N32" s="6">
         <v>1</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="P32" s="8">
-        <v>374.8</v>
+        <v>170.73</v>
       </c>
       <c r="Q32" s="6">
         <v>0</v>
@@ -5288,16 +5243,16 @@
         <v>52</v>
       </c>
       <c r="U32" s="10">
-        <v>68585</v>
+        <v>68529</v>
       </c>
       <c r="V32" s="11">
         <v>11</v>
       </c>
       <c r="W32" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X32" s="12">
-        <v>0.54305559999999997</v>
+        <v>0.32083329999999999</v>
       </c>
       <c r="Y32" s="10">
         <v>0</v>
@@ -5357,7 +5312,7 @@
         <v>53</v>
       </c>
       <c r="AR32" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.3">
@@ -5368,19 +5323,19 @@
         <v>2</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F33" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G33" s="5">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>47</v>
@@ -5395,19 +5350,19 @@
         <v>50</v>
       </c>
       <c r="L33" s="6">
-        <v>7</v>
+        <v>5787</v>
       </c>
       <c r="M33" s="7">
-        <v>2623.59</v>
+        <v>987986.42</v>
       </c>
       <c r="N33" s="6">
         <v>1</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="P33" s="8">
-        <v>374.8</v>
+        <v>170.73</v>
       </c>
       <c r="Q33" s="6">
         <v>0</v>
@@ -5422,16 +5377,16 @@
         <v>52</v>
       </c>
       <c r="U33" s="10">
-        <v>68585</v>
+        <v>68529</v>
       </c>
       <c r="V33" s="11">
         <v>11</v>
       </c>
       <c r="W33" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X33" s="12">
-        <v>0.54305559999999997</v>
+        <v>0.32083329999999999</v>
       </c>
       <c r="Y33" s="10">
         <v>0</v>
@@ -5491,7 +5446,7 @@
         <v>53</v>
       </c>
       <c r="AR33" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:44" x14ac:dyDescent="0.3">
@@ -5502,19 +5457,19 @@
         <v>2</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F34" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G34" s="5">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>47</v>
@@ -5529,19 +5484,19 @@
         <v>50</v>
       </c>
       <c r="L34" s="6">
-        <v>8</v>
+        <v>5788</v>
       </c>
       <c r="M34" s="7">
-        <v>2998.39</v>
+        <v>988157.15</v>
       </c>
       <c r="N34" s="6">
         <v>1</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="P34" s="8">
-        <v>374.8</v>
+        <v>170.73</v>
       </c>
       <c r="Q34" s="6">
         <v>0</v>
@@ -5556,16 +5511,16 @@
         <v>52</v>
       </c>
       <c r="U34" s="10">
-        <v>68585</v>
+        <v>68529</v>
       </c>
       <c r="V34" s="11">
         <v>11</v>
       </c>
       <c r="W34" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X34" s="12">
-        <v>0.54305559999999997</v>
+        <v>0.32083329999999999</v>
       </c>
       <c r="Y34" s="10">
         <v>0</v>
@@ -5625,7 +5580,7 @@
         <v>53</v>
       </c>
       <c r="AR34" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.3">
@@ -5636,19 +5591,19 @@
         <v>2</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F35" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G35" s="5">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>47</v>
@@ -5663,19 +5618,19 @@
         <v>50</v>
       </c>
       <c r="L35" s="6">
-        <v>9</v>
+        <v>5789</v>
       </c>
       <c r="M35" s="7">
-        <v>3373.18</v>
+        <v>988327.88</v>
       </c>
       <c r="N35" s="6">
         <v>1</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="P35" s="8">
-        <v>374.8</v>
+        <v>170.73</v>
       </c>
       <c r="Q35" s="6">
         <v>0</v>
@@ -5690,16 +5645,16 @@
         <v>52</v>
       </c>
       <c r="U35" s="10">
-        <v>68585</v>
+        <v>68529</v>
       </c>
       <c r="V35" s="11">
         <v>11</v>
       </c>
       <c r="W35" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X35" s="12">
-        <v>0.54305559999999997</v>
+        <v>0.32777780000000001</v>
       </c>
       <c r="Y35" s="10">
         <v>0</v>
@@ -5759,7 +5714,7 @@
         <v>53</v>
       </c>
       <c r="AR35" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.3">
@@ -5770,19 +5725,19 @@
         <v>2</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F36" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G36" s="5">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>47</v>
@@ -5797,19 +5752,19 @@
         <v>50</v>
       </c>
       <c r="L36" s="6">
-        <v>10</v>
+        <v>5790</v>
       </c>
       <c r="M36" s="7">
-        <v>3747.98</v>
+        <v>988498.6</v>
       </c>
       <c r="N36" s="6">
         <v>1</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="P36" s="8">
-        <v>374.8</v>
+        <v>170.73</v>
       </c>
       <c r="Q36" s="6">
         <v>0</v>
@@ -5824,16 +5779,16 @@
         <v>52</v>
       </c>
       <c r="U36" s="10">
-        <v>68585</v>
+        <v>68529</v>
       </c>
       <c r="V36" s="11">
         <v>11</v>
       </c>
       <c r="W36" s="4">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="X36" s="12">
-        <v>0.54305559999999997</v>
+        <v>0.32777780000000001</v>
       </c>
       <c r="Y36" s="10">
         <v>0</v>
@@ -5893,7 +5848,7 @@
         <v>53</v>
       </c>
       <c r="AR36" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.3">
@@ -5904,19 +5859,19 @@
         <v>2</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>79</v>